--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3143" uniqueCount="1832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3279" uniqueCount="1922">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -5487,6 +5487,276 @@
   </si>
   <si>
     <t xml:space="preserve">You finished your trips on the road at:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activityCategories.work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activityCategories.school</t>
+  </si>
+  <si>
+    <t xml:space="preserve">École</t>
+  </si>
+  <si>
+    <t xml:space="preserve">School</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Études</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Studies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activityCategories.shoppingServiceRestaurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magasinage, Service ou Restauration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopping, Services or Restaurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activityCategories.dropFetchSomeone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reconduire ou Aller chercher quelqu'un</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drop someone off or Pick someone up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activityCategories.leisure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loisirs (sport, arts, promenade, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leisure (sport, arts, stroll, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activityCategories.other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activityCategories.otherParentHome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domicile de l'autre parent ou tuteur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home of the other parent or guardian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activityCategories.home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.workUsual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travail au lieu habituel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work (out-of-home fixed location)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.workNotUsual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travail dans un autre lieu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work (other place)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.workOnTheRoad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travail sur la route</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work on the road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.volunteering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bénévolat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volunteering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.schoolUsual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Études au lieu principal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Studies ([établissement scolaire]/high school, college, university)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.schoolNotUsual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Études dans un autre lieu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Studies (different location)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.shopping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magasinage (achats, station-service, épicerie, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopping (store, gas station, grocery)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.restaurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restaurant, café, bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restaurant, coffee shop, bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service (coiffeur, réparations, avocat, banque, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service (hairdresser, repairs, lawyer, bank)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santé (hôpital, clinique, physiothérapie, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical (clinic, hospital, physiotherapy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.veterinarian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vétérinaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veterinary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.worship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lieu de culte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Place of worship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.pickClassifiedPurchase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Récupérer un achat chez un particulier (petites annonces)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick up an item from a private seller (online marketplace/classifieds)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.dropSomeone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reconduire quelqu'un</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drop someone off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.fetchSomeone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aller chercher quelqu'un</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick someone up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.accompanySomeone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accompagner quelqu'un</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accompany someone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.leisureStroll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promenade sans destination fixe (ex. : aller courir, promener le chien)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stroll with no fixed destination (ex: go running/jogging, walk with pet, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.leisureSports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sport, entrainement, aller au parc (destination fixe)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sport, training, park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.leisureArtsMusicCulture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arts, Musique ou culture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arts, Music ou culture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.leisureTourism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacances, tourisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacation, tourism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.visiting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visite chez ami.e.s, copain.e ou famille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visiting friends, partner or family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.secondaryHome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résidence secondaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secondary residence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.schoolNotStudent</t>
   </si>
   <si>
     <t xml:space="preserve">errors.selectDontKnowWhenNoOtherChoiceSelected</t>
@@ -17076,7 +17346,7 @@
       <c r="F54" s="63"/>
       <c r="G54" s="63"/>
     </row>
-    <row r="55" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="27" t="s">
         <v>312</v>
       </c>
@@ -17092,14 +17362,13 @@
       <c r="E55" s="29" t="s">
         <v>894</v>
       </c>
-      <c r="F55" s="63"/>
-      <c r="G55" s="63"/>
-    </row>
-    <row r="56" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+    </row>
+    <row r="56" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="27" t="s">
         <v>321</v>
       </c>
-      <c r="B56" s="63"/>
       <c r="C56" s="27" t="s">
         <v>892</v>
       </c>
@@ -17109,10 +17378,10 @@
       <c r="E56" s="29" t="s">
         <v>894</v>
       </c>
-      <c r="F56" s="63"/>
-      <c r="G56" s="63"/>
-    </row>
-    <row r="57" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="27" t="s">
         <v>321</v>
       </c>
@@ -17128,10 +17397,10 @@
       <c r="E57" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="F57" s="63"/>
-      <c r="G57" s="63"/>
-    </row>
-    <row r="58" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="27" t="s">
         <v>321</v>
       </c>
@@ -17147,8 +17416,8 @@
       <c r="E58" s="30" t="s">
         <v>850</v>
       </c>
-      <c r="F58" s="63"/>
-      <c r="G58" s="63"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="76" t="s">
@@ -17164,11 +17433,10 @@
         <v>898</v>
       </c>
     </row>
-    <row r="60" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="63" t="s">
         <v>480</v>
       </c>
-      <c r="B60" s="63"/>
       <c r="C60" s="63" t="s">
         <v>897</v>
       </c>
@@ -17178,14 +17446,13 @@
       <c r="E60" s="30" t="s">
         <v>899</v>
       </c>
-      <c r="F60" s="63"/>
-      <c r="G60" s="63"/>
-    </row>
-    <row r="61" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="63" t="s">
         <v>506</v>
       </c>
-      <c r="B61" s="63"/>
       <c r="C61" s="63" t="s">
         <v>897</v>
       </c>
@@ -17195,14 +17462,13 @@
       <c r="E61" s="30" t="s">
         <v>900</v>
       </c>
-      <c r="F61" s="63"/>
-      <c r="G61" s="63"/>
-    </row>
-    <row r="62" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="63" t="s">
         <v>519</v>
       </c>
-      <c r="B62" s="63"/>
       <c r="C62" s="63" t="s">
         <v>897</v>
       </c>
@@ -17212,14 +17478,13 @@
       <c r="E62" s="30" t="s">
         <v>901</v>
       </c>
-      <c r="F62" s="63"/>
-      <c r="G62" s="63"/>
-    </row>
-    <row r="63" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+    </row>
+    <row r="63" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="63" t="s">
         <v>565</v>
       </c>
-      <c r="B63" s="63"/>
       <c r="C63" s="63" t="s">
         <v>897</v>
       </c>
@@ -17229,14 +17494,13 @@
       <c r="E63" s="30" t="s">
         <v>898</v>
       </c>
-      <c r="F63" s="63"/>
-      <c r="G63" s="63"/>
-    </row>
-    <row r="64" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+    </row>
+    <row r="64" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="63" t="s">
         <v>500</v>
       </c>
-      <c r="B64" s="63"/>
       <c r="C64" s="10" t="s">
         <v>902</v>
       </c>
@@ -17246,10 +17510,10 @@
       <c r="E64" s="30" t="s">
         <v>903</v>
       </c>
-      <c r="F64" s="63"/>
-      <c r="G64" s="63"/>
-    </row>
-    <row r="65" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+    </row>
+    <row r="65" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="63" t="s">
         <v>500</v>
       </c>
@@ -17265,10 +17529,10 @@
       <c r="E65" s="30" t="s">
         <v>905</v>
       </c>
-      <c r="F65" s="63"/>
-      <c r="G65" s="63"/>
-    </row>
-    <row r="66" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+    </row>
+    <row r="66" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="63" t="s">
         <v>500</v>
       </c>
@@ -17287,9 +17551,10 @@
       <c r="F66" s="63" t="s">
         <v>906</v>
       </c>
-      <c r="G66" s="63"/>
-    </row>
-    <row r="67" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+    </row>
+    <row r="67" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="63" t="s">
         <v>500</v>
       </c>
@@ -17308,9 +17573,10 @@
       <c r="F67" s="63" t="s">
         <v>907</v>
       </c>
-      <c r="G67" s="63"/>
-    </row>
-    <row r="68" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+    </row>
+    <row r="68" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="63" t="s">
         <v>500</v>
       </c>
@@ -17329,9 +17595,10 @@
       <c r="F68" s="63" t="s">
         <v>906</v>
       </c>
-      <c r="G68" s="63"/>
-    </row>
-    <row r="69" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+    </row>
+    <row r="69" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="63" t="s">
         <v>500</v>
       </c>
@@ -17350,9 +17617,10 @@
       <c r="F69" s="63" t="s">
         <v>907</v>
       </c>
-      <c r="G69" s="63"/>
-    </row>
-    <row r="70" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+    </row>
+    <row r="70" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="63" t="s">
         <v>500</v>
       </c>
@@ -17371,9 +17639,10 @@
       <c r="F70" s="63" t="s">
         <v>906</v>
       </c>
-      <c r="G70" s="63"/>
-    </row>
-    <row r="71" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+    </row>
+    <row r="71" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="63" t="s">
         <v>500</v>
       </c>
@@ -17392,9 +17661,10 @@
       <c r="F71" s="63" t="s">
         <v>907</v>
       </c>
-      <c r="G71" s="63"/>
-    </row>
-    <row r="72" s="2" customFormat="true" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+    </row>
+    <row r="72" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="63" t="s">
         <v>500</v>
       </c>
@@ -17413,9 +17683,10 @@
       <c r="F72" s="63" t="s">
         <v>906</v>
       </c>
-      <c r="G72" s="63"/>
-    </row>
-    <row r="73" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+    </row>
+    <row r="73" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="63" t="s">
         <v>500</v>
       </c>
@@ -17434,9 +17705,10 @@
       <c r="F73" s="63" t="s">
         <v>907</v>
       </c>
-      <c r="G73" s="63"/>
-    </row>
-    <row r="74" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+    </row>
+    <row r="74" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="63" t="s">
         <v>500</v>
       </c>
@@ -17455,9 +17727,10 @@
       <c r="F74" s="63" t="s">
         <v>906</v>
       </c>
-      <c r="G74" s="63"/>
-    </row>
-    <row r="75" s="2" customFormat="true" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+    </row>
+    <row r="75" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="63" t="s">
         <v>500</v>
       </c>
@@ -17476,13 +17749,13 @@
       <c r="F75" s="63" t="s">
         <v>907</v>
       </c>
-      <c r="G75" s="63"/>
-    </row>
-    <row r="76" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+    </row>
+    <row r="76" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="63" t="s">
         <v>910</v>
       </c>
-      <c r="B76" s="63"/>
       <c r="C76" s="27" t="s">
         <v>911</v>
       </c>
@@ -17492,14 +17765,13 @@
       <c r="E76" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F76" s="63"/>
-      <c r="G76" s="63"/>
-    </row>
-    <row r="77" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+    </row>
+    <row r="77" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="63" t="s">
         <v>912</v>
       </c>
-      <c r="B77" s="63"/>
       <c r="C77" s="27" t="s">
         <v>911</v>
       </c>
@@ -17509,14 +17781,13 @@
       <c r="E77" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F77" s="63"/>
-      <c r="G77" s="63"/>
-    </row>
-    <row r="78" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+    </row>
+    <row r="78" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
         <v>703</v>
       </c>
-      <c r="B78" s="63"/>
       <c r="C78" s="27" t="s">
         <v>913</v>
       </c>
@@ -17526,8 +17797,8 @@
       <c r="E78" s="30" t="s">
         <v>850</v>
       </c>
-      <c r="F78" s="63"/>
-      <c r="G78" s="63"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
     </row>
     <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -18882,7 +19153,7 @@
       <c r="G54" s="29"/>
       <c r="H54" s="29"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="82" t="s">
         <v>206</v>
       </c>
@@ -18899,8 +19170,9 @@
       <c r="F55" s="29"/>
       <c r="G55" s="29"/>
       <c r="H55" s="29"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I55" s="79"/>
+    </row>
+    <row r="56" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="82" t="s">
         <v>206</v>
       </c>
@@ -18917,8 +19189,9 @@
       <c r="F56" s="29"/>
       <c r="G56" s="29"/>
       <c r="H56" s="29"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I56" s="79"/>
+    </row>
+    <row r="57" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="82" t="s">
         <v>1050</v>
       </c>
@@ -18931,8 +19204,13 @@
       <c r="D57" s="79" t="s">
         <v>1040</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E57" s="79"/>
+      <c r="F57" s="79"/>
+      <c r="G57" s="79"/>
+      <c r="H57" s="79"/>
+      <c r="I57" s="79"/>
+    </row>
+    <row r="58" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="82" t="s">
         <v>1050</v>
       </c>
@@ -18945,8 +19223,13 @@
       <c r="D58" s="79" t="s">
         <v>1053</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E58" s="79"/>
+      <c r="F58" s="79"/>
+      <c r="G58" s="79"/>
+      <c r="H58" s="79"/>
+      <c r="I58" s="79"/>
+    </row>
+    <row r="59" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="82" t="s">
         <v>1050</v>
       </c>
@@ -18959,8 +19242,13 @@
       <c r="D59" s="79" t="s">
         <v>1055</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E59" s="79"/>
+      <c r="F59" s="79"/>
+      <c r="G59" s="79"/>
+      <c r="H59" s="79"/>
+      <c r="I59" s="79"/>
+    </row>
+    <row r="60" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="82" t="s">
         <v>737</v>
       </c>
@@ -18973,8 +19261,13 @@
       <c r="D60" s="79" t="s">
         <v>1058</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E60" s="79"/>
+      <c r="F60" s="79"/>
+      <c r="G60" s="79"/>
+      <c r="H60" s="79"/>
+      <c r="I60" s="79"/>
+    </row>
+    <row r="61" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="82" t="s">
         <v>737</v>
       </c>
@@ -18987,8 +19280,13 @@
       <c r="D61" s="79" t="s">
         <v>1061</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E61" s="79"/>
+      <c r="F61" s="79"/>
+      <c r="G61" s="79"/>
+      <c r="H61" s="79"/>
+      <c r="I61" s="79"/>
+    </row>
+    <row r="62" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="82" t="s">
         <v>737</v>
       </c>
@@ -19001,8 +19299,13 @@
       <c r="D62" s="79" t="s">
         <v>1064</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E62" s="79"/>
+      <c r="F62" s="79"/>
+      <c r="G62" s="79"/>
+      <c r="H62" s="79"/>
+      <c r="I62" s="79"/>
+    </row>
+    <row r="63" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="82" t="s">
         <v>737</v>
       </c>
@@ -19015,8 +19318,13 @@
       <c r="D63" s="79" t="s">
         <v>1067</v>
       </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E63" s="79"/>
+      <c r="F63" s="79"/>
+      <c r="G63" s="79"/>
+      <c r="H63" s="79"/>
+      <c r="I63" s="79"/>
+    </row>
+    <row r="64" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="79" t="s">
         <v>771</v>
       </c>
@@ -19029,8 +19337,13 @@
       <c r="D64" s="79" t="s">
         <v>1070</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E64" s="79"/>
+      <c r="F64" s="79"/>
+      <c r="G64" s="79"/>
+      <c r="H64" s="79"/>
+      <c r="I64" s="79"/>
+    </row>
+    <row r="65" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="79" t="s">
         <v>771</v>
       </c>
@@ -19045,8 +19358,11 @@
       </c>
       <c r="E65" s="83"/>
       <c r="F65" s="83"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G65" s="79"/>
+      <c r="H65" s="79"/>
+      <c r="I65" s="79"/>
+    </row>
+    <row r="66" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="79" t="s">
         <v>771</v>
       </c>
@@ -19061,8 +19377,11 @@
       </c>
       <c r="E66" s="83"/>
       <c r="F66" s="83"/>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G66" s="79"/>
+      <c r="H66" s="79"/>
+      <c r="I66" s="79"/>
+    </row>
+    <row r="67" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="79" t="s">
         <v>771</v>
       </c>
@@ -19077,8 +19396,11 @@
       </c>
       <c r="E67" s="83"/>
       <c r="F67" s="83"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G67" s="79"/>
+      <c r="H67" s="79"/>
+      <c r="I67" s="79"/>
+    </row>
+    <row r="68" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="79" t="s">
         <v>771</v>
       </c>
@@ -19093,8 +19415,11 @@
       </c>
       <c r="E68" s="83"/>
       <c r="F68" s="83"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G68" s="79"/>
+      <c r="H68" s="79"/>
+      <c r="I68" s="79"/>
+    </row>
+    <row r="69" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="79" t="s">
         <v>771</v>
       </c>
@@ -19109,8 +19434,11 @@
       </c>
       <c r="E69" s="83"/>
       <c r="F69" s="83"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G69" s="79"/>
+      <c r="H69" s="79"/>
+      <c r="I69" s="79"/>
+    </row>
+    <row r="70" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="79" t="s">
         <v>771</v>
       </c>
@@ -19125,8 +19453,11 @@
       </c>
       <c r="E70" s="83"/>
       <c r="F70" s="83"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G70" s="79"/>
+      <c r="H70" s="79"/>
+      <c r="I70" s="79"/>
+    </row>
+    <row r="71" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="79" t="s">
         <v>771</v>
       </c>
@@ -19141,8 +19472,11 @@
       </c>
       <c r="E71" s="83"/>
       <c r="F71" s="83"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G71" s="79"/>
+      <c r="H71" s="79"/>
+      <c r="I71" s="79"/>
+    </row>
+    <row r="72" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="79" t="s">
         <v>771</v>
       </c>
@@ -19157,8 +19491,11 @@
       </c>
       <c r="E72" s="83"/>
       <c r="F72" s="83"/>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G72" s="79"/>
+      <c r="H72" s="79"/>
+      <c r="I72" s="79"/>
+    </row>
+    <row r="73" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="79" t="s">
         <v>771</v>
       </c>
@@ -19173,8 +19510,11 @@
       </c>
       <c r="E73" s="83"/>
       <c r="F73" s="83"/>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G73" s="79"/>
+      <c r="H73" s="79"/>
+      <c r="I73" s="79"/>
+    </row>
+    <row r="74" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="79" t="s">
         <v>771</v>
       </c>
@@ -19189,8 +19529,11 @@
       </c>
       <c r="E74" s="83"/>
       <c r="F74" s="83"/>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G74" s="79"/>
+      <c r="H74" s="79"/>
+      <c r="I74" s="79"/>
+    </row>
+    <row r="75" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="79" t="s">
         <v>771</v>
       </c>
@@ -19205,8 +19548,11 @@
       </c>
       <c r="E75" s="83"/>
       <c r="F75" s="83"/>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G75" s="79"/>
+      <c r="H75" s="79"/>
+      <c r="I75" s="79"/>
+    </row>
+    <row r="76" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="79" t="s">
         <v>771</v>
       </c>
@@ -19219,6 +19565,11 @@
       <c r="D76" s="79" t="s">
         <v>1106</v>
       </c>
+      <c r="E76" s="79"/>
+      <c r="F76" s="79"/>
+      <c r="G76" s="79"/>
+      <c r="H76" s="79"/>
+      <c r="I76" s="79"/>
     </row>
     <row r="77" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="79" t="s">
@@ -19376,7 +19727,7 @@
       </c>
       <c r="I84" s="29"/>
     </row>
-    <row r="85" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" s="2" customFormat="true" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="85" t="s">
         <v>304</v>
       </c>
@@ -19395,7 +19746,7 @@
       <c r="H85" s="29"/>
       <c r="I85" s="29"/>
     </row>
-    <row r="86" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" s="2" customFormat="true" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="85" t="s">
         <v>304</v>
       </c>
@@ -19414,7 +19765,7 @@
       <c r="H86" s="29"/>
       <c r="I86" s="29"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="87" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="85" t="s">
         <v>304</v>
       </c>
@@ -19433,7 +19784,7 @@
       <c r="H87" s="29"/>
       <c r="I87" s="29"/>
     </row>
-    <row r="88" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" s="2" customFormat="true" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="85" t="s">
         <v>304</v>
       </c>
@@ -19863,22 +20214,15 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="117" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="87" t="s">
         <v>175</v>
       </c>
-      <c r="B117" s="79"/>
-      <c r="C117" s="79"/>
-      <c r="D117" s="79"/>
-      <c r="E117" s="79"/>
-      <c r="F117" s="79"/>
       <c r="G117" s="29" t="s">
         <v>854</v>
       </c>
-      <c r="H117" s="79"/>
-      <c r="I117" s="79"/>
-    </row>
-    <row r="118" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="82" t="s">
         <v>1198</v>
       </c>
@@ -19898,10 +20242,8 @@
         <v>1202</v>
       </c>
       <c r="G118" s="82"/>
-      <c r="H118" s="79"/>
-      <c r="I118" s="79"/>
-    </row>
-    <row r="119" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="82" t="s">
         <v>1198</v>
       </c>
@@ -19920,11 +20262,8 @@
       <c r="F119" s="29" t="s">
         <v>1206</v>
       </c>
-      <c r="G119" s="79"/>
-      <c r="H119" s="79"/>
-      <c r="I119" s="79"/>
-    </row>
-    <row r="120" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="82" t="s">
         <v>1198</v>
       </c>
@@ -19943,11 +20282,8 @@
       <c r="F120" s="29" t="s">
         <v>1210</v>
       </c>
-      <c r="G120" s="79"/>
-      <c r="H120" s="79"/>
-      <c r="I120" s="79"/>
-    </row>
-    <row r="121" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="82" t="s">
         <v>1198</v>
       </c>
@@ -19966,11 +20302,8 @@
       <c r="F121" s="29" t="s">
         <v>1214</v>
       </c>
-      <c r="G121" s="79"/>
-      <c r="H121" s="79"/>
-      <c r="I121" s="79"/>
-    </row>
-    <row r="122" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="82" t="s">
         <v>1198</v>
       </c>
@@ -19989,11 +20322,8 @@
       <c r="F122" s="29" t="s">
         <v>1218</v>
       </c>
-      <c r="G122" s="79"/>
-      <c r="H122" s="79"/>
-      <c r="I122" s="79"/>
-    </row>
-    <row r="123" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="123" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="27" t="s">
         <v>578</v>
       </c>
@@ -20006,13 +20336,8 @@
       <c r="D123" s="30" t="s">
         <v>1221</v>
       </c>
-      <c r="E123" s="79"/>
-      <c r="F123" s="79"/>
-      <c r="G123" s="79"/>
-      <c r="H123" s="79"/>
-      <c r="I123" s="79"/>
-    </row>
-    <row r="124" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="124" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="27" t="s">
         <v>578</v>
       </c>
@@ -20025,15 +20350,11 @@
       <c r="D124" s="30" t="s">
         <v>1222</v>
       </c>
-      <c r="E124" s="79"/>
-      <c r="F124" s="79"/>
-      <c r="G124" s="79"/>
       <c r="H124" s="88" t="s">
         <v>896</v>
       </c>
-      <c r="I124" s="79"/>
-    </row>
-    <row r="125" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="125" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="27" t="s">
         <v>578</v>
       </c>
@@ -20046,15 +20367,11 @@
       <c r="D125" s="30" t="s">
         <v>1225</v>
       </c>
-      <c r="E125" s="79"/>
-      <c r="F125" s="79"/>
-      <c r="G125" s="79"/>
       <c r="H125" s="89" t="s">
         <v>1226</v>
       </c>
-      <c r="I125" s="79"/>
-    </row>
-    <row r="126" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="126" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="27" t="s">
         <v>578</v>
       </c>
@@ -20067,15 +20384,11 @@
       <c r="D126" s="30" t="s">
         <v>1229</v>
       </c>
-      <c r="E126" s="79"/>
-      <c r="F126" s="79"/>
-      <c r="G126" s="79"/>
       <c r="H126" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="I126" s="79"/>
-    </row>
-    <row r="127" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="127" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="27" t="s">
         <v>578</v>
       </c>
@@ -20088,28 +20401,18 @@
       <c r="D127" s="30" t="s">
         <v>1232</v>
       </c>
-      <c r="E127" s="79"/>
-      <c r="F127" s="79"/>
-      <c r="G127" s="79"/>
-      <c r="H127" s="79"/>
-      <c r="I127" s="79"/>
-    </row>
-    <row r="128" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="128" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="27" t="s">
         <v>578</v>
       </c>
-      <c r="B128" s="79"/>
       <c r="C128" s="30"/>
       <c r="D128" s="30"/>
-      <c r="E128" s="79"/>
-      <c r="F128" s="79"/>
       <c r="G128" s="79" t="s">
         <v>161</v>
       </c>
-      <c r="H128" s="79"/>
-      <c r="I128" s="79"/>
-    </row>
-    <row r="129" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="129" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="27" t="s">
         <v>584</v>
       </c>
@@ -20122,13 +20425,8 @@
       <c r="D129" s="30" t="s">
         <v>1221</v>
       </c>
-      <c r="E129" s="79"/>
-      <c r="F129" s="79"/>
-      <c r="G129" s="79"/>
-      <c r="H129" s="79"/>
-      <c r="I129" s="79"/>
-    </row>
-    <row r="130" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="130" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="27" t="s">
         <v>584</v>
       </c>
@@ -20141,13 +20439,8 @@
       <c r="D130" s="30" t="s">
         <v>1235</v>
       </c>
-      <c r="E130" s="79"/>
-      <c r="F130" s="79"/>
-      <c r="G130" s="79"/>
-      <c r="H130" s="79"/>
-      <c r="I130" s="79"/>
-    </row>
-    <row r="131" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="131" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="27" t="s">
         <v>584</v>
       </c>
@@ -20160,15 +20453,11 @@
       <c r="D131" s="30" t="s">
         <v>1229</v>
       </c>
-      <c r="E131" s="79"/>
-      <c r="F131" s="79"/>
-      <c r="G131" s="79"/>
       <c r="H131" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="I131" s="79"/>
-    </row>
-    <row r="132" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="132" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="27" t="s">
         <v>584</v>
       </c>
@@ -20181,13 +20470,8 @@
       <c r="D132" s="30" t="s">
         <v>1232</v>
       </c>
-      <c r="E132" s="79"/>
-      <c r="F132" s="79"/>
-      <c r="G132" s="79"/>
-      <c r="H132" s="79"/>
-      <c r="I132" s="79"/>
-    </row>
-    <row r="133" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="133" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="27" t="s">
         <v>584</v>
       </c>
@@ -20200,13 +20484,8 @@
       <c r="D133" s="30" t="s">
         <v>1238</v>
       </c>
-      <c r="E133" s="79"/>
-      <c r="F133" s="79"/>
-      <c r="G133" s="79"/>
-      <c r="H133" s="79"/>
-      <c r="I133" s="79"/>
-    </row>
-    <row r="134" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="134" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="27" t="s">
         <v>584</v>
       </c>
@@ -20219,28 +20498,18 @@
       <c r="D134" s="30" t="s">
         <v>1241</v>
       </c>
-      <c r="E134" s="79"/>
-      <c r="F134" s="79"/>
-      <c r="G134" s="79"/>
-      <c r="H134" s="79"/>
-      <c r="I134" s="79"/>
-    </row>
-    <row r="135" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="135" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="27" t="s">
         <v>584</v>
       </c>
-      <c r="B135" s="79"/>
       <c r="C135" s="30"/>
       <c r="D135" s="30"/>
-      <c r="E135" s="79"/>
-      <c r="F135" s="79"/>
       <c r="G135" s="29" t="s">
         <v>962</v>
       </c>
-      <c r="H135" s="79"/>
-      <c r="I135" s="79"/>
-    </row>
-    <row r="136" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="136" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="27" t="s">
         <v>462</v>
       </c>
@@ -20253,15 +20522,11 @@
       <c r="D136" s="30" t="s">
         <v>1244</v>
       </c>
-      <c r="E136" s="79"/>
-      <c r="F136" s="79"/>
-      <c r="G136" s="79"/>
       <c r="H136" s="27" t="s">
         <v>1245</v>
       </c>
-      <c r="I136" s="79"/>
-    </row>
-    <row r="137" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="137" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="27" t="s">
         <v>462</v>
       </c>
@@ -20274,15 +20539,11 @@
       <c r="D137" s="30" t="s">
         <v>1247</v>
       </c>
-      <c r="E137" s="79"/>
-      <c r="F137" s="79"/>
-      <c r="G137" s="79"/>
       <c r="H137" s="63" t="s">
         <v>1248</v>
       </c>
-      <c r="I137" s="79"/>
-    </row>
-    <row r="138" s="2" customFormat="true" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="138" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="27" t="s">
         <v>462</v>
       </c>
@@ -20295,13 +20556,8 @@
       <c r="D138" s="30" t="s">
         <v>1250</v>
       </c>
-      <c r="E138" s="79"/>
-      <c r="F138" s="79"/>
-      <c r="G138" s="79"/>
-      <c r="H138" s="79"/>
-      <c r="I138" s="79"/>
-    </row>
-    <row r="139" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="139" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="27" t="s">
         <v>462</v>
       </c>
@@ -20314,28 +20570,18 @@
       <c r="D139" s="30" t="s">
         <v>1253</v>
       </c>
-      <c r="E139" s="79"/>
-      <c r="F139" s="79"/>
-      <c r="G139" s="79"/>
-      <c r="H139" s="79"/>
-      <c r="I139" s="79"/>
-    </row>
-    <row r="140" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="140" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="27" t="s">
         <v>462</v>
       </c>
-      <c r="B140" s="79"/>
       <c r="C140" s="30"/>
       <c r="D140" s="30"/>
-      <c r="E140" s="79"/>
-      <c r="F140" s="79"/>
       <c r="G140" s="79" t="s">
         <v>965</v>
       </c>
-      <c r="H140" s="79"/>
-      <c r="I140" s="79"/>
-    </row>
-    <row r="141" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="141" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="79" t="s">
         <v>501</v>
       </c>
@@ -20348,13 +20594,8 @@
       <c r="D141" s="30" t="s">
         <v>1255</v>
       </c>
-      <c r="E141" s="79"/>
-      <c r="F141" s="79"/>
-      <c r="G141" s="79"/>
-      <c r="H141" s="79"/>
-      <c r="I141" s="79"/>
-    </row>
-    <row r="142" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="142" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="79" t="s">
         <v>501</v>
       </c>
@@ -20367,28 +20608,18 @@
       <c r="D142" s="30" t="s">
         <v>1258</v>
       </c>
-      <c r="E142" s="79"/>
-      <c r="F142" s="79"/>
-      <c r="G142" s="79"/>
-      <c r="H142" s="79"/>
-      <c r="I142" s="79"/>
-    </row>
-    <row r="143" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="79" t="s">
         <v>501</v>
       </c>
-      <c r="B143" s="79"/>
       <c r="C143" s="30"/>
       <c r="D143" s="30"/>
-      <c r="E143" s="79"/>
-      <c r="F143" s="79"/>
       <c r="G143" s="79" t="s">
         <v>965</v>
       </c>
-      <c r="H143" s="79"/>
-      <c r="I143" s="79"/>
-    </row>
-    <row r="144" s="2" customFormat="true" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="144" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="27" t="s">
         <v>531</v>
       </c>
@@ -20401,13 +20632,8 @@
       <c r="D144" s="30" t="s">
         <v>1261</v>
       </c>
-      <c r="E144" s="79"/>
-      <c r="F144" s="79"/>
-      <c r="G144" s="79"/>
-      <c r="H144" s="79"/>
-      <c r="I144" s="79"/>
-    </row>
-    <row r="145" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="145" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="27" t="s">
         <v>531</v>
       </c>
@@ -20420,43 +20646,28 @@
       <c r="D145" s="30" t="s">
         <v>1264</v>
       </c>
-      <c r="E145" s="79"/>
-      <c r="F145" s="79"/>
-      <c r="G145" s="79"/>
-      <c r="H145" s="79"/>
-      <c r="I145" s="79"/>
-    </row>
-    <row r="146" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="146" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="27" t="s">
         <v>531</v>
       </c>
-      <c r="B146" s="79"/>
       <c r="C146" s="30"/>
       <c r="D146" s="30"/>
-      <c r="E146" s="79"/>
-      <c r="F146" s="79"/>
       <c r="G146" s="29" t="s">
         <v>962</v>
       </c>
-      <c r="H146" s="79"/>
-      <c r="I146" s="79"/>
-    </row>
-    <row r="147" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="147" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="27" t="s">
         <v>531</v>
       </c>
-      <c r="B147" s="79"/>
       <c r="C147" s="30"/>
       <c r="D147" s="30"/>
-      <c r="E147" s="79"/>
-      <c r="F147" s="79"/>
       <c r="G147" s="79" t="s">
         <v>965</v>
       </c>
-      <c r="H147" s="79"/>
-      <c r="I147" s="79"/>
-    </row>
-    <row r="148" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="148" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="27" t="s">
         <v>538</v>
       </c>
@@ -20469,13 +20680,8 @@
       <c r="D148" s="30" t="s">
         <v>1267</v>
       </c>
-      <c r="E148" s="79"/>
-      <c r="F148" s="79"/>
-      <c r="G148" s="79"/>
-      <c r="H148" s="79"/>
-      <c r="I148" s="79"/>
-    </row>
-    <row r="149" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="149" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="27" t="s">
         <v>538</v>
       </c>
@@ -20488,13 +20694,8 @@
       <c r="D149" s="30" t="s">
         <v>1269</v>
       </c>
-      <c r="E149" s="79"/>
-      <c r="F149" s="79"/>
-      <c r="G149" s="79"/>
-      <c r="H149" s="79"/>
-      <c r="I149" s="79"/>
-    </row>
-    <row r="150" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="150" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="27" t="s">
         <v>538</v>
       </c>
@@ -20507,13 +20708,8 @@
       <c r="D150" s="63" t="s">
         <v>1271</v>
       </c>
-      <c r="E150" s="79"/>
-      <c r="F150" s="79"/>
-      <c r="G150" s="79"/>
-      <c r="H150" s="79"/>
-      <c r="I150" s="79"/>
-    </row>
-    <row r="151" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="151" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="27" t="s">
         <v>538</v>
       </c>
@@ -20526,43 +20722,28 @@
       <c r="D151" s="63" t="s">
         <v>1273</v>
       </c>
-      <c r="E151" s="79"/>
-      <c r="F151" s="79"/>
-      <c r="G151" s="79"/>
-      <c r="H151" s="79"/>
-      <c r="I151" s="79"/>
-    </row>
-    <row r="152" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="152" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="27" t="s">
         <v>538</v>
       </c>
-      <c r="B152" s="79"/>
       <c r="C152" s="30"/>
       <c r="D152" s="30"/>
-      <c r="E152" s="79"/>
-      <c r="F152" s="79"/>
       <c r="G152" s="29" t="s">
         <v>962</v>
       </c>
-      <c r="H152" s="79"/>
-      <c r="I152" s="79"/>
-    </row>
-    <row r="153" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="153" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="27" t="s">
         <v>538</v>
       </c>
-      <c r="B153" s="79"/>
       <c r="C153" s="30"/>
       <c r="D153" s="30"/>
-      <c r="E153" s="79"/>
-      <c r="F153" s="79"/>
       <c r="G153" s="79" t="s">
         <v>965</v>
       </c>
-      <c r="H153" s="79"/>
-      <c r="I153" s="79"/>
-    </row>
-    <row r="154" s="2" customFormat="true" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="154" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="27" t="s">
         <v>543</v>
       </c>
@@ -20575,13 +20756,8 @@
       <c r="D154" s="30" t="s">
         <v>1276</v>
       </c>
-      <c r="E154" s="79"/>
-      <c r="F154" s="79"/>
-      <c r="G154" s="79"/>
-      <c r="H154" s="79"/>
-      <c r="I154" s="79"/>
-    </row>
-    <row r="155" s="2" customFormat="true" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="155" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="27" t="s">
         <v>543</v>
       </c>
@@ -20594,13 +20770,8 @@
       <c r="D155" s="30" t="s">
         <v>1279</v>
       </c>
-      <c r="E155" s="79"/>
-      <c r="F155" s="79"/>
-      <c r="G155" s="79"/>
-      <c r="H155" s="79"/>
-      <c r="I155" s="79"/>
-    </row>
-    <row r="156" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="156" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="27" t="s">
         <v>543</v>
       </c>
@@ -20613,13 +20784,8 @@
       <c r="D156" s="30" t="s">
         <v>1281</v>
       </c>
-      <c r="E156" s="79"/>
-      <c r="F156" s="79"/>
-      <c r="G156" s="79"/>
-      <c r="H156" s="79"/>
-      <c r="I156" s="79"/>
-    </row>
-    <row r="157" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="157" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="27" t="s">
         <v>543</v>
       </c>
@@ -20632,13 +20798,8 @@
       <c r="D157" s="63" t="s">
         <v>1283</v>
       </c>
-      <c r="E157" s="79"/>
-      <c r="F157" s="79"/>
-      <c r="G157" s="79"/>
-      <c r="H157" s="79"/>
-      <c r="I157" s="79"/>
-    </row>
-    <row r="158" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="158" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="27" t="s">
         <v>543</v>
       </c>
@@ -20651,43 +20812,28 @@
       <c r="D158" s="30" t="s">
         <v>1286</v>
       </c>
-      <c r="E158" s="79"/>
-      <c r="F158" s="79"/>
-      <c r="G158" s="79"/>
-      <c r="H158" s="79"/>
-      <c r="I158" s="79"/>
-    </row>
-    <row r="159" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="159" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="27" t="s">
         <v>543</v>
       </c>
-      <c r="B159" s="79"/>
       <c r="C159" s="30"/>
       <c r="D159" s="30"/>
-      <c r="E159" s="79"/>
-      <c r="F159" s="79"/>
       <c r="G159" s="29" t="s">
         <v>962</v>
       </c>
-      <c r="H159" s="79"/>
-      <c r="I159" s="79"/>
-    </row>
-    <row r="160" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="160" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="27" t="s">
         <v>543</v>
       </c>
-      <c r="B160" s="79"/>
       <c r="C160" s="30"/>
       <c r="D160" s="30"/>
-      <c r="E160" s="79"/>
-      <c r="F160" s="79"/>
       <c r="G160" s="79" t="s">
         <v>965</v>
       </c>
-      <c r="H160" s="79"/>
-      <c r="I160" s="79"/>
-    </row>
-    <row r="161" s="2" customFormat="true" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="161" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="27" t="s">
         <v>678</v>
       </c>
@@ -21070,7 +21216,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F166"/>
+  <dimension ref="A1:F1048576"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="16.72"/>
@@ -21932,921 +22078,897 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
+    <row r="55" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C55" s="28" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D55" s="28" t="s">
+        <v>1527</v>
+      </c>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C56" s="28" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D56" s="28" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E56" s="28"/>
+      <c r="F56" s="28"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C57" s="28" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D57" s="28" t="s">
+        <v>1532</v>
+      </c>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C58" s="28" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D58" s="28" t="s">
+        <v>1535</v>
+      </c>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C59" s="28" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D59" s="28" t="s">
+        <v>1538</v>
+      </c>
+      <c r="E59" s="28"/>
+      <c r="F59" s="28"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C60" s="28" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D60" s="28" t="s">
+        <v>1541</v>
+      </c>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>963</v>
+      </c>
+      <c r="D61" s="28" t="s">
+        <v>964</v>
+      </c>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C62" s="28" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D62" s="28" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C63" s="28" t="s">
+        <v>922</v>
+      </c>
+      <c r="D63" s="28" t="s">
+        <v>923</v>
+      </c>
+      <c r="E63" s="28"/>
+      <c r="F63" s="28"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C64" s="28" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D64" s="28" t="s">
+        <v>1549</v>
+      </c>
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C65" s="28" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D65" s="28" t="s">
+        <v>1552</v>
+      </c>
+      <c r="E65" s="28"/>
+      <c r="F65" s="28"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C66" s="28" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D66" s="28" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E66" s="28"/>
+      <c r="F66" s="28"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C67" s="28" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D67" s="28" t="s">
+        <v>1558</v>
+      </c>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C68" s="28" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D68" s="28" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E68" s="28"/>
+      <c r="F68" s="28"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C69" s="28" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D69" s="28" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E69" s="28"/>
+      <c r="F69" s="28"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C70" s="28" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D70" s="28" t="s">
+        <v>1567</v>
+      </c>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C71" s="28" t="s">
+        <v>1569</v>
+      </c>
+      <c r="D71" s="28" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E71" s="28"/>
+      <c r="F71" s="28"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C72" s="28" t="s">
+        <v>1572</v>
+      </c>
+      <c r="D72" s="28" t="s">
+        <v>1573</v>
+      </c>
+      <c r="E72" s="28"/>
+      <c r="F72" s="28"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C73" s="28" t="s">
+        <v>1575</v>
+      </c>
+      <c r="D73" s="28" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E73" s="28"/>
+      <c r="F73" s="28"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C74" s="28" t="s">
+        <v>1578</v>
+      </c>
+      <c r="D74" s="28" t="s">
+        <v>1579</v>
+      </c>
+      <c r="E74" s="28"/>
+      <c r="F74" s="28"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C75" s="28" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D75" s="28" t="s">
+        <v>1582</v>
+      </c>
+      <c r="E75" s="28"/>
+      <c r="F75" s="28"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C76" s="28" t="s">
+        <v>1584</v>
+      </c>
+      <c r="D76" s="28" t="s">
+        <v>1585</v>
+      </c>
+      <c r="E76" s="28"/>
+      <c r="F76" s="28"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C77" s="28" t="s">
+        <v>963</v>
+      </c>
+      <c r="D77" s="28" t="s">
+        <v>964</v>
+      </c>
+      <c r="E77" s="28"/>
+      <c r="F77" s="28"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C78" s="28" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D78" s="28" t="s">
+        <v>1589</v>
+      </c>
+      <c r="E78" s="28"/>
+      <c r="F78" s="28"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C79" s="28" t="s">
+        <v>1591</v>
+      </c>
+      <c r="D79" s="28" t="s">
+        <v>1592</v>
+      </c>
+      <c r="E79" s="28"/>
+      <c r="F79" s="28"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C80" s="28" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D80" s="28" t="s">
+        <v>1595</v>
+      </c>
+      <c r="E80" s="28"/>
+      <c r="F80" s="28"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C81" s="28" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D81" s="28" t="s">
+        <v>1598</v>
+      </c>
+      <c r="E81" s="28"/>
+      <c r="F81" s="28"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C82" s="28" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D82" s="28" t="s">
+        <v>1601</v>
+      </c>
+      <c r="E82" s="28"/>
+      <c r="F82" s="28"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B83" s="10" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C83" s="28" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D83" s="28" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E83" s="28"/>
+      <c r="F83" s="28"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B84" s="10" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C84" s="28" t="s">
+        <v>1606</v>
+      </c>
+      <c r="D84" s="28" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E84" s="28"/>
+      <c r="F84" s="28"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B85" s="10" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C85" s="28" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D85" s="28" t="s">
+        <v>1610</v>
+      </c>
+      <c r="E85" s="28"/>
+      <c r="F85" s="28"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C86" s="28" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D86" s="28" t="s">
+        <v>1558</v>
+      </c>
+      <c r="E86" s="28"/>
+      <c r="F86" s="28"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C87" s="28" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D87" s="28" t="s">
+        <v>1613</v>
+      </c>
+      <c r="E87" s="28"/>
+      <c r="F87" s="28"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B88" s="10" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C88" s="28" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D88" s="28" t="s">
+        <v>1532</v>
+      </c>
+      <c r="E88" s="28"/>
+      <c r="F88" s="28"/>
+    </row>
+    <row r="89" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>1525</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>1526</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>1527</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
+      <c r="B89" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>1616</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>1528</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>1529</v>
-      </c>
-      <c r="D56" s="10" t="s">
-        <v>1530</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="s">
+      <c r="B90" s="2" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>1531</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>1532</v>
-      </c>
-      <c r="D57" s="10" t="s">
-        <v>1533</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="s">
+      <c r="B91" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>1534</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>1535</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>1536</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="s">
+      <c r="B92" s="2" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>1625</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B59" s="92" t="s">
-        <v>1537</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>1538</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
+      <c r="B93" s="92" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C93" s="10" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B60" s="10" t="s">
-        <v>1540</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>1541</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>1542</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
+      <c r="B94" s="10" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B61" s="10" t="s">
-        <v>1543</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>1544</v>
-      </c>
-      <c r="D61" s="10" t="s">
-        <v>1545</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="s">
+      <c r="B95" s="10" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C95" s="10" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D95" s="10" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B62" s="10" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>1547</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>1548</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>1549</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>1550</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="s">
+      <c r="B96" s="10" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C96" s="10" t="s">
+        <v>1637</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>1638</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>1639</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B63" s="41" t="s">
-        <v>1551</v>
-      </c>
-      <c r="C63" s="41" t="s">
-        <v>1552</v>
-      </c>
-      <c r="D63" s="92" t="s">
-        <v>1553</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="s">
+      <c r="B97" s="41" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C97" s="41" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D97" s="92" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B64" s="41" t="s">
-        <v>1554</v>
-      </c>
-      <c r="C64" s="41" t="s">
-        <v>1555</v>
-      </c>
-      <c r="D64" s="92" t="s">
-        <v>1556</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="22" t="s">
+      <c r="B98" s="41" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C98" s="41" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D98" s="92" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="22" t="s">
         <v>332</v>
       </c>
-      <c r="B65" s="30" t="s">
-        <v>1557</v>
-      </c>
-      <c r="C65" s="30" t="s">
+      <c r="B99" s="30" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C99" s="30" t="s">
         <v>922</v>
       </c>
-      <c r="D65" s="30" t="s">
+      <c r="D99" s="30" t="s">
         <v>923</v>
       </c>
-      <c r="E65" s="30"/>
-      <c r="F65" s="30"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="22" t="s">
+      <c r="E99" s="30"/>
+      <c r="F99" s="30"/>
+    </row>
+    <row r="100" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="22" t="s">
         <v>332</v>
       </c>
-      <c r="B66" s="30" t="s">
-        <v>1558</v>
-      </c>
-      <c r="C66" s="30" t="s">
+      <c r="B100" s="30" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C100" s="30" t="s">
         <v>1138</v>
       </c>
-      <c r="D66" s="30" t="s">
+      <c r="D100" s="30" t="s">
         <v>1139</v>
       </c>
-      <c r="E66" s="30"/>
-      <c r="F66" s="30"/>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="22" t="s">
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+    </row>
+    <row r="101" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="22" t="s">
         <v>332</v>
       </c>
-      <c r="B67" s="30" t="s">
-        <v>1559</v>
-      </c>
-      <c r="C67" s="30" t="s">
+      <c r="B101" s="30" t="s">
+        <v>1649</v>
+      </c>
+      <c r="C101" s="30" t="s">
         <v>1140</v>
       </c>
-      <c r="D67" s="30" t="s">
+      <c r="D101" s="30" t="s">
         <v>1141</v>
       </c>
-      <c r="E67" s="30"/>
-      <c r="F67" s="30"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="22" t="s">
+      <c r="E101" s="30"/>
+      <c r="F101" s="30"/>
+    </row>
+    <row r="102" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="22" t="s">
         <v>332</v>
       </c>
-      <c r="B68" s="10" t="s">
-        <v>1560</v>
-      </c>
-      <c r="C68" s="10" t="s">
+      <c r="B102" s="10" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C102" s="10" t="s">
         <v>1143</v>
       </c>
-      <c r="D68" s="10" t="s">
+      <c r="D102" s="10" t="s">
         <v>1144</v>
       </c>
-      <c r="E68" s="10" t="s">
+      <c r="E102" s="10" t="s">
         <v>1145</v>
       </c>
-      <c r="F68" s="10" t="s">
+      <c r="F102" s="10" t="s">
         <v>1146</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
+    <row r="103" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B69" s="10" t="s">
-        <v>1561</v>
-      </c>
-      <c r="C69" s="10" t="s">
-        <v>1562</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>1563</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2" t="s">
+      <c r="B103" s="10" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C103" s="10" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D103" s="10" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B70" s="10" t="s">
-        <v>1564</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>1565</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>1566</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2" t="s">
+      <c r="B104" s="10" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D104" s="10" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B71" s="10" t="s">
-        <v>1567</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>1568</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>1569</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="B72" s="10" t="s">
-        <v>1570</v>
-      </c>
-      <c r="C72" s="10" t="s">
-        <v>1571</v>
-      </c>
-      <c r="D72" s="10" t="s">
-        <v>1572</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B73" s="30" t="s">
-        <v>1573</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>1150</v>
-      </c>
-      <c r="D73" s="10" t="s">
-        <v>1151</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>1152</v>
-      </c>
-      <c r="F73" s="10" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B74" s="30" t="s">
-        <v>1574</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>1155</v>
-      </c>
-      <c r="D74" s="10" t="s">
-        <v>1156</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>1157</v>
-      </c>
-      <c r="F74" s="10" t="s">
-        <v>1158</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B75" s="30" t="s">
-        <v>1575</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>1576</v>
-      </c>
-      <c r="D75" s="10" t="s">
-        <v>1577</v>
-      </c>
-      <c r="E75" s="10"/>
-      <c r="F75" s="10"/>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B76" s="30" t="s">
-        <v>1578</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>1579</v>
-      </c>
-      <c r="D76" s="10" t="s">
-        <v>1580</v>
-      </c>
-      <c r="E76" s="10"/>
-      <c r="F76" s="10"/>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B77" s="30" t="s">
-        <v>1581</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>1582</v>
-      </c>
-      <c r="D77" s="10" t="s">
-        <v>1583</v>
-      </c>
-      <c r="E77" s="10"/>
-      <c r="F77" s="10"/>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B78" s="10" t="s">
-        <v>1584</v>
-      </c>
-      <c r="C78" s="10" t="s">
-        <v>1585</v>
-      </c>
-      <c r="D78" s="10" t="s">
-        <v>1586</v>
-      </c>
-      <c r="E78" s="10"/>
-      <c r="F78" s="10"/>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B79" s="10" t="s">
-        <v>1587</v>
-      </c>
-      <c r="C79" s="27" t="s">
-        <v>1588</v>
-      </c>
-      <c r="D79" s="27" t="s">
-        <v>1589</v>
-      </c>
-      <c r="E79" s="10"/>
-      <c r="F79" s="10"/>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B80" s="10" t="s">
-        <v>1590</v>
-      </c>
-      <c r="C80" s="27" t="s">
-        <v>1591</v>
-      </c>
-      <c r="D80" s="27" t="s">
-        <v>1592</v>
-      </c>
-      <c r="E80" s="10"/>
-      <c r="F80" s="10"/>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B81" s="10" t="s">
-        <v>1593</v>
-      </c>
-      <c r="C81" s="27" t="s">
-        <v>1594</v>
-      </c>
-      <c r="D81" s="27" t="s">
-        <v>1595</v>
-      </c>
-      <c r="E81" s="10"/>
-      <c r="F81" s="10"/>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B82" s="10" t="s">
-        <v>1596</v>
-      </c>
-      <c r="C82" s="27" t="s">
-        <v>1597</v>
-      </c>
-      <c r="D82" s="27" t="s">
-        <v>1598</v>
-      </c>
-      <c r="E82" s="10"/>
-      <c r="F82" s="10"/>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B83" s="41" t="s">
-        <v>1599</v>
-      </c>
-      <c r="C83" s="27" t="s">
-        <v>1600</v>
-      </c>
-      <c r="D83" s="27" t="s">
-        <v>1601</v>
-      </c>
-      <c r="E83" s="10"/>
-      <c r="F83" s="10"/>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B84" s="41" t="s">
-        <v>1602</v>
-      </c>
-      <c r="C84" s="27" t="s">
-        <v>1603</v>
-      </c>
-      <c r="D84" s="27" t="s">
-        <v>1604</v>
-      </c>
-      <c r="E84" s="10"/>
-      <c r="F84" s="10"/>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B85" s="41" t="s">
-        <v>1605</v>
-      </c>
-      <c r="C85" s="27" t="s">
-        <v>1606</v>
-      </c>
-      <c r="D85" s="27" t="s">
-        <v>1607</v>
-      </c>
-      <c r="E85" s="10"/>
-      <c r="F85" s="10"/>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B86" s="41" t="s">
-        <v>1608</v>
-      </c>
-      <c r="C86" s="27" t="s">
-        <v>1609</v>
-      </c>
-      <c r="D86" s="27" t="s">
-        <v>1610</v>
-      </c>
-      <c r="E86" s="10"/>
-      <c r="F86" s="10"/>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B87" s="41" t="s">
-        <v>1611</v>
-      </c>
-      <c r="C87" s="27" t="s">
-        <v>1612</v>
-      </c>
-      <c r="D87" s="27" t="s">
-        <v>1613</v>
-      </c>
-      <c r="E87" s="10"/>
-      <c r="F87" s="10"/>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B88" s="41" t="s">
-        <v>1614</v>
-      </c>
-      <c r="C88" s="27" t="s">
-        <v>1615</v>
-      </c>
-      <c r="D88" s="27" t="s">
-        <v>1616</v>
-      </c>
-      <c r="E88" s="10"/>
-      <c r="F88" s="10"/>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B89" s="41" t="s">
-        <v>1617</v>
-      </c>
-      <c r="C89" s="27" t="s">
-        <v>1618</v>
-      </c>
-      <c r="D89" s="27" t="s">
-        <v>1619</v>
-      </c>
-      <c r="E89" s="10"/>
-      <c r="F89" s="10"/>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B90" s="41" t="s">
-        <v>1620</v>
-      </c>
-      <c r="C90" s="27" t="s">
-        <v>1609</v>
-      </c>
-      <c r="D90" s="27" t="s">
-        <v>1610</v>
-      </c>
-      <c r="E90" s="10"/>
-      <c r="F90" s="10"/>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B91" s="41" t="s">
-        <v>1621</v>
-      </c>
-      <c r="C91" s="27" t="s">
-        <v>1622</v>
-      </c>
-      <c r="D91" s="27" t="s">
-        <v>1623</v>
-      </c>
-      <c r="E91" s="10"/>
-      <c r="F91" s="10"/>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B92" s="41" t="s">
-        <v>1624</v>
-      </c>
-      <c r="C92" s="27" t="s">
-        <v>1625</v>
-      </c>
-      <c r="D92" s="27" t="s">
-        <v>1626</v>
-      </c>
-      <c r="E92" s="10"/>
-      <c r="F92" s="10"/>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B93" s="41" t="s">
-        <v>1627</v>
-      </c>
-      <c r="C93" s="27" t="s">
-        <v>1628</v>
-      </c>
-      <c r="D93" s="27" t="s">
-        <v>1629</v>
-      </c>
-      <c r="E93" s="10"/>
-      <c r="F93" s="10"/>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B94" s="41" t="s">
-        <v>1630</v>
-      </c>
-      <c r="C94" s="27" t="s">
-        <v>1631</v>
-      </c>
-      <c r="D94" s="27" t="s">
-        <v>1632</v>
-      </c>
-      <c r="E94" s="10"/>
-      <c r="F94" s="10"/>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B95" s="41" t="s">
-        <v>1633</v>
-      </c>
-      <c r="C95" s="27" t="s">
-        <v>1634</v>
-      </c>
-      <c r="D95" s="27" t="s">
-        <v>1635</v>
-      </c>
-      <c r="E95" s="10"/>
-      <c r="F95" s="10"/>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B96" s="41" t="s">
-        <v>1636</v>
-      </c>
-      <c r="C96" s="27" t="s">
-        <v>1637</v>
-      </c>
-      <c r="D96" s="27" t="s">
-        <v>1638</v>
-      </c>
-      <c r="E96" s="10"/>
-      <c r="F96" s="10"/>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B97" s="41" t="s">
-        <v>1639</v>
-      </c>
-      <c r="C97" s="27" t="s">
-        <v>1640</v>
-      </c>
-      <c r="D97" s="27" t="s">
-        <v>1641</v>
-      </c>
-      <c r="E97" s="10"/>
-      <c r="F97" s="10"/>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B98" s="41" t="s">
-        <v>1642</v>
-      </c>
-      <c r="C98" s="27" t="s">
-        <v>1643</v>
-      </c>
-      <c r="D98" s="27" t="s">
-        <v>1644</v>
-      </c>
-      <c r="E98" s="10"/>
-      <c r="F98" s="10"/>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B99" s="41" t="s">
-        <v>1645</v>
-      </c>
-      <c r="C99" s="27" t="s">
-        <v>1646</v>
-      </c>
-      <c r="D99" s="27" t="s">
-        <v>1647</v>
-      </c>
-      <c r="E99" s="10"/>
-      <c r="F99" s="10"/>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B100" s="41" t="s">
-        <v>1648</v>
-      </c>
-      <c r="C100" s="27" t="s">
-        <v>1637</v>
-      </c>
-      <c r="D100" s="27" t="s">
-        <v>1638</v>
-      </c>
-      <c r="E100" s="10"/>
-      <c r="F100" s="10"/>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B101" s="41" t="s">
-        <v>1649</v>
-      </c>
-      <c r="C101" s="27" t="s">
-        <v>1650</v>
-      </c>
-      <c r="D101" s="27" t="s">
-        <v>1651</v>
-      </c>
-      <c r="E101" s="10"/>
-      <c r="F101" s="10"/>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="B102" s="41" t="s">
-        <v>1652</v>
-      </c>
-      <c r="C102" s="27" t="s">
-        <v>1653</v>
-      </c>
-      <c r="D102" s="27" t="s">
-        <v>1654</v>
-      </c>
-      <c r="E102" s="10"/>
-      <c r="F102" s="10"/>
-    </row>
-    <row r="103" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>1655</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>1200</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>1201</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>1656</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>1203</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>1204</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>1205</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>1206</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B105" s="21" t="s">
+      <c r="B105" s="10" t="s">
         <v>1657</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>1207</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>1210</v>
+      <c r="C105" s="10" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D105" s="10" t="s">
+        <v>1659</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B106" s="21" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>1211</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>1212</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>1214</v>
+        <v>332</v>
+      </c>
+      <c r="B106" s="10" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D106" s="10" t="s">
+        <v>1662</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B107" s="21" t="s">
-        <v>1659</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>1215</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>1216</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>1217</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>1218</v>
+      <c r="A107" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B107" s="30" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F107" s="10" t="s">
+        <v>1153</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B108" s="93" t="s">
-        <v>1660</v>
-      </c>
-      <c r="C108" s="63" t="s">
-        <v>1661</v>
-      </c>
-      <c r="D108" s="28" t="s">
-        <v>1662</v>
-      </c>
-      <c r="E108" s="10"/>
-      <c r="F108" s="10"/>
+      <c r="A108" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B108" s="30" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D108" s="10" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F108" s="10" t="s">
+        <v>1158</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B109" s="10" t="s">
-        <v>1663</v>
+      <c r="A109" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B109" s="30" t="s">
+        <v>1665</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="E109" s="10"/>
       <c r="F109" s="10"/>
     </row>
-    <row r="110" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>1666</v>
+    <row r="110" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B110" s="30" t="s">
+        <v>1668</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>1668</v>
-      </c>
-      <c r="E110" s="10" t="s">
-        <v>1669</v>
-      </c>
-      <c r="F110" s="10" t="s">
         <v>1670</v>
       </c>
-    </row>
-    <row r="111" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B111" s="2" t="s">
+      <c r="E110" s="10"/>
+      <c r="F110" s="10"/>
+    </row>
+    <row r="111" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B111" s="30" t="s">
         <v>1671</v>
       </c>
       <c r="C111" s="10" t="s">
@@ -22855,829 +22977,1413 @@
       <c r="D111" s="10" t="s">
         <v>1673</v>
       </c>
-      <c r="E111" s="10" t="s">
+      <c r="E111" s="10"/>
+      <c r="F111" s="10"/>
+    </row>
+    <row r="112" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B112" s="10" t="s">
         <v>1674</v>
       </c>
-      <c r="F111" s="10" t="s">
+      <c r="C112" s="10" t="s">
         <v>1675</v>
       </c>
-    </row>
-    <row r="112" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="2" t="s">
+      <c r="D112" s="10" t="s">
+        <v>1676</v>
+      </c>
+      <c r="E112" s="10"/>
+      <c r="F112" s="10"/>
+    </row>
+    <row r="113" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B113" s="10" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C113" s="27" t="s">
+        <v>1678</v>
+      </c>
+      <c r="D113" s="27" t="s">
+        <v>1679</v>
+      </c>
+      <c r="E113" s="10"/>
+      <c r="F113" s="10"/>
+    </row>
+    <row r="114" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C114" s="27" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D114" s="27" t="s">
+        <v>1682</v>
+      </c>
+      <c r="E114" s="10"/>
+      <c r="F114" s="10"/>
+    </row>
+    <row r="115" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B115" s="10" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C115" s="27" t="s">
+        <v>1684</v>
+      </c>
+      <c r="D115" s="27" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E115" s="10"/>
+      <c r="F115" s="10"/>
+    </row>
+    <row r="116" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B116" s="10" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C116" s="27" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D116" s="27" t="s">
+        <v>1688</v>
+      </c>
+      <c r="E116" s="10"/>
+      <c r="F116" s="10"/>
+    </row>
+    <row r="117" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B117" s="41" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C117" s="27" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D117" s="27" t="s">
+        <v>1691</v>
+      </c>
+      <c r="E117" s="10"/>
+      <c r="F117" s="10"/>
+    </row>
+    <row r="118" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B118" s="41" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C118" s="27" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D118" s="27" t="s">
+        <v>1694</v>
+      </c>
+      <c r="E118" s="10"/>
+      <c r="F118" s="10"/>
+    </row>
+    <row r="119" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B119" s="41" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C119" s="27" t="s">
+        <v>1696</v>
+      </c>
+      <c r="D119" s="27" t="s">
+        <v>1697</v>
+      </c>
+      <c r="E119" s="10"/>
+      <c r="F119" s="10"/>
+    </row>
+    <row r="120" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B120" s="41" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C120" s="27" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D120" s="27" t="s">
+        <v>1700</v>
+      </c>
+      <c r="E120" s="10"/>
+      <c r="F120" s="10"/>
+    </row>
+    <row r="121" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B121" s="41" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C121" s="27" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D121" s="27" t="s">
+        <v>1703</v>
+      </c>
+      <c r="E121" s="10"/>
+      <c r="F121" s="10"/>
+    </row>
+    <row r="122" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B122" s="41" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C122" s="27" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D122" s="27" t="s">
+        <v>1706</v>
+      </c>
+      <c r="E122" s="10"/>
+      <c r="F122" s="10"/>
+    </row>
+    <row r="123" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B123" s="41" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C123" s="27" t="s">
+        <v>1708</v>
+      </c>
+      <c r="D123" s="27" t="s">
+        <v>1709</v>
+      </c>
+      <c r="E123" s="10"/>
+      <c r="F123" s="10"/>
+    </row>
+    <row r="124" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B124" s="41" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C124" s="27" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D124" s="27" t="s">
+        <v>1700</v>
+      </c>
+      <c r="E124" s="10"/>
+      <c r="F124" s="10"/>
+    </row>
+    <row r="125" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B125" s="41" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C125" s="27" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D125" s="27" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E125" s="10"/>
+      <c r="F125" s="10"/>
+    </row>
+    <row r="126" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B126" s="41" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C126" s="27" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D126" s="27" t="s">
+        <v>1716</v>
+      </c>
+      <c r="E126" s="10"/>
+      <c r="F126" s="10"/>
+    </row>
+    <row r="127" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B127" s="41" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C127" s="27" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D127" s="27" t="s">
+        <v>1719</v>
+      </c>
+      <c r="E127" s="10"/>
+      <c r="F127" s="10"/>
+    </row>
+    <row r="128" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B128" s="41" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C128" s="27" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D128" s="27" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E128" s="10"/>
+      <c r="F128" s="10"/>
+    </row>
+    <row r="129" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B129" s="41" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C129" s="27" t="s">
+        <v>1724</v>
+      </c>
+      <c r="D129" s="27" t="s">
+        <v>1725</v>
+      </c>
+      <c r="E129" s="10"/>
+      <c r="F129" s="10"/>
+    </row>
+    <row r="130" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B130" s="41" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C130" s="27" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D130" s="27" t="s">
+        <v>1728</v>
+      </c>
+      <c r="E130" s="10"/>
+      <c r="F130" s="10"/>
+    </row>
+    <row r="131" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B131" s="41" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C131" s="27" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D131" s="27" t="s">
+        <v>1731</v>
+      </c>
+      <c r="E131" s="10"/>
+      <c r="F131" s="10"/>
+    </row>
+    <row r="132" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B132" s="41" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C132" s="27" t="s">
+        <v>1733</v>
+      </c>
+      <c r="D132" s="27" t="s">
+        <v>1734</v>
+      </c>
+      <c r="E132" s="10"/>
+      <c r="F132" s="10"/>
+    </row>
+    <row r="133" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B133" s="41" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C133" s="27" t="s">
+        <v>1736</v>
+      </c>
+      <c r="D133" s="27" t="s">
+        <v>1737</v>
+      </c>
+      <c r="E133" s="10"/>
+      <c r="F133" s="10"/>
+    </row>
+    <row r="134" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B134" s="41" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C134" s="27" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D134" s="27" t="s">
+        <v>1728</v>
+      </c>
+      <c r="E134" s="10"/>
+      <c r="F134" s="10"/>
+    </row>
+    <row r="135" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B135" s="41" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C135" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="D135" s="27" t="s">
+        <v>1741</v>
+      </c>
+      <c r="E135" s="10"/>
+      <c r="F135" s="10"/>
+    </row>
+    <row r="136" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B136" s="41" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C136" s="27" t="s">
+        <v>1743</v>
+      </c>
+      <c r="D136" s="27" t="s">
+        <v>1744</v>
+      </c>
+      <c r="E136" s="10"/>
+      <c r="F136" s="10"/>
+    </row>
+    <row r="137" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>1746</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B139" s="21" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B140" s="21" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B141" s="21" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>1676</v>
-      </c>
-      <c r="C112" s="28" t="s">
-        <v>1677</v>
-      </c>
-      <c r="D112" s="28" t="s">
-        <v>1678</v>
-      </c>
-      <c r="E112" s="28" t="s">
-        <v>1679</v>
-      </c>
-      <c r="F112" s="28" t="s">
-        <v>1680</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>1681</v>
-      </c>
-      <c r="C113" s="28" t="s">
-        <v>1682</v>
-      </c>
-      <c r="D113" s="28" t="s">
-        <v>1683</v>
-      </c>
-      <c r="E113" s="28" t="s">
-        <v>1684</v>
-      </c>
-      <c r="F113" s="28" t="s">
-        <v>1685</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>1686</v>
-      </c>
-      <c r="C114" s="28" t="s">
-        <v>1687</v>
-      </c>
-      <c r="D114" s="28" t="s">
-        <v>1688</v>
-      </c>
-      <c r="E114" s="28" t="s">
-        <v>1689</v>
-      </c>
-      <c r="F114" s="28" t="s">
-        <v>1690</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>1691</v>
-      </c>
-      <c r="C115" s="28" t="s">
-        <v>1692</v>
-      </c>
-      <c r="D115" s="63" t="s">
-        <v>1693</v>
-      </c>
-      <c r="E115" s="28" t="s">
-        <v>1694</v>
-      </c>
-      <c r="F115" s="63" t="s">
-        <v>1695</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B116" s="10" t="s">
-        <v>1696</v>
-      </c>
-      <c r="C116" s="28" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D116" s="63" t="s">
-        <v>1698</v>
-      </c>
-      <c r="E116" s="28" t="s">
-        <v>1699</v>
-      </c>
-      <c r="F116" s="63" t="s">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B117" s="10" t="s">
-        <v>1701</v>
-      </c>
-      <c r="C117" s="28" t="s">
-        <v>1702</v>
-      </c>
-      <c r="D117" s="63" t="s">
-        <v>1703</v>
-      </c>
-      <c r="E117" s="28"/>
-      <c r="F117" s="63"/>
-    </row>
-    <row r="118" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B118" s="10" t="s">
-        <v>1704</v>
-      </c>
-      <c r="C118" s="28" t="s">
-        <v>1705</v>
-      </c>
-      <c r="D118" s="28" t="s">
-        <v>1706</v>
-      </c>
-      <c r="E118" s="28"/>
-      <c r="F118" s="63"/>
-    </row>
-    <row r="119" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>1707</v>
-      </c>
-      <c r="C119" s="10" t="s">
-        <v>1708</v>
-      </c>
-      <c r="D119" s="10" t="s">
-        <v>1709</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>1710</v>
-      </c>
-      <c r="C120" s="10" t="s">
-        <v>1293</v>
-      </c>
-      <c r="D120" s="10" t="s">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>1711</v>
-      </c>
-      <c r="C121" s="10" t="s">
-        <v>1296</v>
-      </c>
-      <c r="D121" s="10" t="s">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>1712</v>
-      </c>
-      <c r="C122" s="10" t="s">
-        <v>1713</v>
-      </c>
-      <c r="D122" s="10" t="s">
-        <v>1714</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>1715</v>
-      </c>
-      <c r="C123" s="10" t="s">
-        <v>1716</v>
-      </c>
-      <c r="D123" s="10" t="s">
-        <v>1717</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>1718</v>
-      </c>
-      <c r="C124" s="10" t="s">
-        <v>1719</v>
-      </c>
-      <c r="D124" s="10" t="s">
-        <v>1720</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>1721</v>
-      </c>
-      <c r="C125" s="10" t="s">
-        <v>1722</v>
-      </c>
-      <c r="D125" s="10" t="s">
-        <v>1723</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>1724</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>1725</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>1726</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>1727</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>1728</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>1728</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>1729</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>1730</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>1731</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>1732</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>1733</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>1734</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>1735</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>1736</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>1737</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>1738</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>1739</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>1740</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>1741</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>1742</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>1743</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>1744</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>1745</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>1746</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>1747</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>1748</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>1749</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B135" s="2" t="s">
+      <c r="B142" s="93" t="s">
         <v>1750</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C142" s="63" t="s">
         <v>1751</v>
       </c>
-      <c r="D135" s="2" t="s">
+      <c r="D142" s="28" t="s">
         <v>1752</v>
       </c>
-    </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>1753</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>1287</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>1754</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>1755</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>1756</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>1757</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>1758</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>1759</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>1760</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>1761</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>1762</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>1763</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>1764</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>1765</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>1766</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>1767</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>1768</v>
-      </c>
-    </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>1769</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>1289</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>1290</v>
-      </c>
+      <c r="E142" s="10"/>
+      <c r="F142" s="10"/>
     </row>
     <row r="143" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B143" s="79" t="s">
+        <v>243</v>
+      </c>
+      <c r="B143" s="10" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C143" s="10" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D143" s="10" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E143" s="10"/>
+      <c r="F143" s="10"/>
+    </row>
+    <row r="144" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C144" s="10" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D144" s="10" t="s">
+        <v>1758</v>
+      </c>
+      <c r="E144" s="10" t="s">
+        <v>1759</v>
+      </c>
+      <c r="F144" s="10" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>1761</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D145" s="10" t="s">
+        <v>1763</v>
+      </c>
+      <c r="E145" s="10" t="s">
+        <v>1764</v>
+      </c>
+      <c r="F145" s="10" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C146" s="28" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D146" s="28" t="s">
+        <v>1768</v>
+      </c>
+      <c r="E146" s="28" t="s">
+        <v>1769</v>
+      </c>
+      <c r="F146" s="28" t="s">
         <v>1770</v>
       </c>
-      <c r="C143" s="63" t="s">
+    </row>
+    <row r="147" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>1771</v>
       </c>
-      <c r="D143" s="30" t="s">
+      <c r="C147" s="28" t="s">
         <v>1772</v>
       </c>
-    </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B144" s="2" t="s">
+      <c r="D147" s="28" t="s">
         <v>1773</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="E147" s="28" t="s">
         <v>1774</v>
       </c>
-      <c r="D144" s="2" t="s">
+      <c r="F147" s="28" t="s">
         <v>1775</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B145" s="2" t="s">
+    <row r="148" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>1776</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C148" s="28" t="s">
         <v>1777</v>
       </c>
-      <c r="D145" s="2" t="s">
+      <c r="D148" s="28" t="s">
         <v>1778</v>
       </c>
-    </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B146" s="2" t="s">
+      <c r="E148" s="28" t="s">
         <v>1779</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="F148" s="28" t="s">
         <v>1780</v>
       </c>
-      <c r="D146" s="2" t="s">
+    </row>
+    <row r="149" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B149" s="2" t="s">
         <v>1781</v>
       </c>
-    </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B147" s="2" t="s">
+      <c r="C149" s="28" t="s">
         <v>1782</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="D149" s="63" t="s">
         <v>1783</v>
       </c>
-      <c r="D147" s="2" t="s">
+      <c r="E149" s="28" t="s">
         <v>1784</v>
       </c>
-    </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B148" s="2" t="s">
+      <c r="F149" s="63" t="s">
         <v>1785</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>1786</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>1787</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>1788</v>
-      </c>
-      <c r="C149" s="63" t="s">
-        <v>1789</v>
-      </c>
-      <c r="D149" s="30" t="s">
-        <v>1790</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B150" s="79" t="s">
-        <v>1791</v>
-      </c>
-      <c r="C150" s="63" t="s">
-        <v>1792</v>
-      </c>
-      <c r="D150" s="30" t="s">
-        <v>1793</v>
+        <v>243</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>1786</v>
+      </c>
+      <c r="C150" s="28" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D150" s="63" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E150" s="28" t="s">
+        <v>1789</v>
+      </c>
+      <c r="F150" s="63" t="s">
+        <v>1790</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B151" s="79" t="s">
+        <v>243</v>
+      </c>
+      <c r="B151" s="10" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C151" s="28" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D151" s="63" t="s">
+        <v>1793</v>
+      </c>
+      <c r="E151" s="28"/>
+      <c r="F151" s="63"/>
+    </row>
+    <row r="152" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B152" s="10" t="s">
         <v>1794</v>
       </c>
-      <c r="C151" s="63" t="s">
+      <c r="C152" s="28" t="s">
         <v>1795</v>
       </c>
-      <c r="D151" s="30" t="s">
+      <c r="D152" s="28" t="s">
         <v>1796</v>
       </c>
-    </row>
-    <row r="152" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B152" s="79" t="s">
-        <v>1797</v>
-      </c>
-      <c r="C152" s="63" t="s">
-        <v>1798</v>
-      </c>
-      <c r="D152" s="30" t="s">
-        <v>1799</v>
-      </c>
+      <c r="E152" s="28"/>
+      <c r="F152" s="63"/>
     </row>
     <row r="153" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B153" s="79" t="s">
-        <v>1800</v>
-      </c>
-      <c r="C153" s="63" t="s">
-        <v>1220</v>
-      </c>
-      <c r="D153" s="30" t="s">
-        <v>1221</v>
+        <v>762</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C153" s="10" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D153" s="10" t="s">
+        <v>1799</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B154" s="79" t="s">
-        <v>1801</v>
-      </c>
-      <c r="C154" s="63" t="s">
-        <v>1802</v>
-      </c>
-      <c r="D154" s="30" t="s">
-        <v>1803</v>
+      <c r="B154" s="2" t="s">
+        <v>1800</v>
+      </c>
+      <c r="C154" s="10" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D154" s="10" t="s">
+        <v>1294</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B155" s="79" t="s">
-        <v>1804</v>
-      </c>
-      <c r="C155" s="63" t="s">
-        <v>1220</v>
-      </c>
-      <c r="D155" s="30" t="s">
-        <v>1221</v>
+      <c r="B155" s="2" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C155" s="10" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D155" s="10" t="s">
+        <v>1297</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B156" s="79" t="s">
-        <v>1805</v>
-      </c>
-      <c r="C156" s="63" t="s">
+      <c r="B156" s="2" t="s">
         <v>1802</v>
       </c>
-      <c r="D156" s="30" t="s">
+      <c r="C156" s="10" t="s">
         <v>1803</v>
+      </c>
+      <c r="D156" s="10" t="s">
+        <v>1804</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B157" s="79" t="s">
+      <c r="B157" s="2" t="s">
+        <v>1805</v>
+      </c>
+      <c r="C157" s="10" t="s">
         <v>1806</v>
       </c>
-      <c r="C157" s="63" t="s">
-        <v>1771</v>
-      </c>
-      <c r="D157" s="30" t="s">
-        <v>1772</v>
+      <c r="D157" s="10" t="s">
+        <v>1807</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B158" s="79" t="s">
-        <v>1807</v>
-      </c>
-      <c r="C158" s="63" t="s">
-        <v>1228</v>
-      </c>
-      <c r="D158" s="30" t="s">
-        <v>1229</v>
+      <c r="B158" s="2" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C158" s="10" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D158" s="10" t="s">
+        <v>1810</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B159" s="79" t="s">
-        <v>1808</v>
-      </c>
-      <c r="C159" s="63" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D159" s="30" t="s">
-        <v>1232</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B159" s="2" t="s">
+        <v>1811</v>
+      </c>
+      <c r="C159" s="10" t="s">
+        <v>1812</v>
+      </c>
+      <c r="D159" s="10" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B160" s="79" t="s">
-        <v>1809</v>
-      </c>
-      <c r="C160" s="63" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D160" s="30" t="s">
-        <v>1241</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B160" s="2" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B161" s="10" t="s">
-        <v>1810</v>
-      </c>
-      <c r="C161" s="10" t="s">
-        <v>1811</v>
-      </c>
-      <c r="D161" s="30" t="s">
-        <v>1812</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="49" t="s">
+      <c r="B161" s="2" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>1819</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>1834</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>1841</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B177" s="79" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C177" s="63" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D177" s="30" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C183" s="63" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D183" s="30" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B184" s="79" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C184" s="63" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D184" s="30" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B185" s="79" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C185" s="63" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D185" s="30" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B186" s="79" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C186" s="63" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D186" s="30" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B187" s="79" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C187" s="63" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D187" s="30" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B188" s="79" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C188" s="63" t="s">
+        <v>1892</v>
+      </c>
+      <c r="D188" s="30" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B189" s="79" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C189" s="63" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D189" s="30" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B190" s="79" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C190" s="63" t="s">
+        <v>1892</v>
+      </c>
+      <c r="D190" s="30" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B191" s="79" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C191" s="63" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D191" s="30" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B192" s="79" t="s">
+        <v>1897</v>
+      </c>
+      <c r="C192" s="63" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D192" s="30" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B193" s="79" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C193" s="63" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D193" s="30" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B194" s="79" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C194" s="63" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D194" s="30" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B195" s="10" t="s">
+        <v>1900</v>
+      </c>
+      <c r="C195" s="10" t="s">
+        <v>1901</v>
+      </c>
+      <c r="D195" s="30" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="49" t="s">
         <v>635</v>
       </c>
-      <c r="B162" s="27" t="s">
-        <v>1813</v>
-      </c>
-      <c r="C162" s="10" t="s">
-        <v>1814</v>
-      </c>
-      <c r="D162" s="94" t="s">
-        <v>1815</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="2" t="s">
+      <c r="B196" s="27" t="s">
+        <v>1903</v>
+      </c>
+      <c r="C196" s="10" t="s">
+        <v>1904</v>
+      </c>
+      <c r="D196" s="94" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="B163" s="2" t="s">
-        <v>1816</v>
-      </c>
-      <c r="C163" s="49" t="s">
-        <v>1817</v>
-      </c>
-      <c r="D163" s="28" t="s">
-        <v>1818</v>
-      </c>
-    </row>
-    <row r="164" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="2" t="s">
+      <c r="B197" s="2" t="s">
+        <v>1906</v>
+      </c>
+      <c r="C197" s="49" t="s">
+        <v>1907</v>
+      </c>
+      <c r="D197" s="28" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="B164" s="2" t="s">
-        <v>1819</v>
-      </c>
-      <c r="C164" s="63" t="s">
-        <v>1820</v>
-      </c>
-      <c r="D164" s="28" t="s">
-        <v>1821</v>
-      </c>
-    </row>
-    <row r="165" customFormat="false" ht="261.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="2" t="s">
+      <c r="B198" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="C198" s="63" t="s">
+        <v>1910</v>
+      </c>
+      <c r="D198" s="28" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="261.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="B165" s="29" t="s">
-        <v>1822</v>
-      </c>
-      <c r="C165" s="27" t="s">
-        <v>1823</v>
-      </c>
-      <c r="D165" s="27" t="s">
-        <v>1824</v>
-      </c>
-      <c r="E165" s="27" t="s">
-        <v>1825</v>
-      </c>
-      <c r="F165" s="27" t="s">
-        <v>1826</v>
-      </c>
-    </row>
-    <row r="166" customFormat="false" ht="218.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="2" t="s">
+      <c r="B199" s="29" t="s">
+        <v>1912</v>
+      </c>
+      <c r="C199" s="27" t="s">
+        <v>1913</v>
+      </c>
+      <c r="D199" s="27" t="s">
+        <v>1914</v>
+      </c>
+      <c r="E199" s="27" t="s">
+        <v>1915</v>
+      </c>
+      <c r="F199" s="27" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="218.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="B166" s="29" t="s">
-        <v>1827</v>
-      </c>
-      <c r="C166" s="27" t="s">
-        <v>1828</v>
-      </c>
-      <c r="D166" s="27" t="s">
-        <v>1829</v>
-      </c>
-      <c r="E166" s="27" t="s">
-        <v>1830</v>
-      </c>
-      <c r="F166" s="27" t="s">
-        <v>1831</v>
-      </c>
-    </row>
+      <c r="B200" s="29" t="s">
+        <v>1917</v>
+      </c>
+      <c r="C200" s="27" t="s">
+        <v>1918</v>
+      </c>
+      <c r="D200" s="27" t="s">
+        <v>1919</v>
+      </c>
+      <c r="E200" s="27" t="s">
+        <v>1920</v>
+      </c>
+      <c r="F200" s="27" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2353" uniqueCount="1390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2353" uniqueCount="1392">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -3841,6 +3841,12 @@
   </si>
   <si>
     <t xml:space="preserve">Very burdensome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">namespace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">key</t>
   </si>
   <si>
     <t xml:space="preserve">addGroupedObject</t>
@@ -15619,10 +15625,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>3</v>
+        <v>1039</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5</v>
+        <v>1040</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>6</v>
@@ -15642,13 +15648,13 @@
         <v>107</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -15658,13 +15664,13 @@
         <v>107</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
@@ -15674,13 +15680,13 @@
         <v>415</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="E4" s="10"/>
     </row>
@@ -15689,13 +15695,13 @@
         <v>415</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15703,13 +15709,13 @@
         <v>415</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15717,13 +15723,13 @@
         <v>415</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15731,13 +15737,13 @@
         <v>415</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15745,13 +15751,13 @@
         <v>415</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15759,13 +15765,13 @@
         <v>415</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15773,13 +15779,13 @@
         <v>415</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15787,13 +15793,13 @@
         <v>415</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15801,13 +15807,13 @@
         <v>415</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15815,7 +15821,7 @@
         <v>415</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>747</v>
@@ -15829,13 +15835,13 @@
         <v>415</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15843,19 +15849,19 @@
         <v>328</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15863,19 +15869,19 @@
         <v>328</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15883,19 +15889,19 @@
         <v>328</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15903,19 +15909,19 @@
         <v>328</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15923,19 +15929,19 @@
         <v>328</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15943,19 +15949,19 @@
         <v>328</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15963,13 +15969,13 @@
         <v>328</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15977,13 +15983,13 @@
         <v>328</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15991,13 +15997,13 @@
         <v>328</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16005,13 +16011,13 @@
         <v>328</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16019,19 +16025,19 @@
         <v>328</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16039,13 +16045,13 @@
         <v>328</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16053,13 +16059,13 @@
         <v>328</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16067,13 +16073,13 @@
         <v>328</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16081,13 +16087,13 @@
         <v>328</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16095,13 +16101,13 @@
         <v>328</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16109,13 +16115,13 @@
         <v>328</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16123,13 +16129,13 @@
         <v>328</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16137,13 +16143,13 @@
         <v>328</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16151,13 +16157,13 @@
         <v>328</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16165,13 +16171,13 @@
         <v>328</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16179,13 +16185,13 @@
         <v>328</v>
       </c>
       <c r="B37" s="10" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C37" s="10" t="s">
         <v>1156</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>1154</v>
-      </c>
       <c r="D37" s="10" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16193,13 +16199,13 @@
         <v>328</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16207,13 +16213,13 @@
         <v>328</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16221,13 +16227,13 @@
         <v>328</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16235,13 +16241,13 @@
         <v>328</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16249,13 +16255,13 @@
         <v>328</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16263,13 +16269,13 @@
         <v>328</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16277,13 +16283,13 @@
         <v>328</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16291,13 +16297,13 @@
         <v>328</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16305,13 +16311,13 @@
         <v>328</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16319,13 +16325,13 @@
         <v>328</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16333,19 +16339,19 @@
         <v>328</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16353,19 +16359,19 @@
         <v>328</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16373,19 +16379,19 @@
         <v>328</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16393,19 +16399,19 @@
         <v>328</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16413,19 +16419,19 @@
         <v>328</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16433,19 +16439,19 @@
         <v>328</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16453,19 +16459,19 @@
         <v>328</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16473,19 +16479,19 @@
         <v>328</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16493,13 +16499,13 @@
         <v>107</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16507,13 +16513,13 @@
         <v>107</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16521,13 +16527,13 @@
         <v>107</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16535,13 +16541,13 @@
         <v>107</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16549,13 +16555,13 @@
         <v>107</v>
       </c>
       <c r="B60" s="75" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16563,13 +16569,13 @@
         <v>107</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16577,13 +16583,13 @@
         <v>107</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16591,19 +16597,19 @@
         <v>107</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16611,13 +16617,13 @@
         <v>107</v>
       </c>
       <c r="B64" s="34" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="C64" s="34" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="D64" s="75" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
@@ -16627,13 +16633,13 @@
         <v>107</v>
       </c>
       <c r="B65" s="34" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="C65" s="34" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="D65" s="75" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
@@ -16643,7 +16649,7 @@
         <v>328</v>
       </c>
       <c r="B66" s="59" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="C66" s="59" t="s">
         <v>703</v>
@@ -16659,7 +16665,7 @@
         <v>328</v>
       </c>
       <c r="B67" s="59" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="C67" s="59" t="s">
         <v>921</v>
@@ -16675,7 +16681,7 @@
         <v>328</v>
       </c>
       <c r="B68" s="59" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="C68" s="59" t="s">
         <v>923</v>
@@ -16691,7 +16697,7 @@
         <v>328</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>926</v>
@@ -16711,7 +16717,7 @@
         <v>415</v>
       </c>
       <c r="B70" s="59" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>933</v>
@@ -16731,7 +16737,7 @@
         <v>415</v>
       </c>
       <c r="B71" s="59" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>938</v>
@@ -16751,13 +16757,13 @@
         <v>415</v>
       </c>
       <c r="B72" s="59" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="E72" s="10"/>
       <c r="F72" s="10"/>
@@ -16767,13 +16773,13 @@
         <v>415</v>
       </c>
       <c r="B73" s="59" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="E73" s="10"/>
       <c r="F73" s="10"/>
@@ -16783,13 +16789,13 @@
         <v>415</v>
       </c>
       <c r="B74" s="59" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="E74" s="10"/>
       <c r="F74" s="10"/>
@@ -16799,13 +16805,13 @@
         <v>415</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="E75" s="10"/>
       <c r="F75" s="10"/>
@@ -16815,13 +16821,13 @@
         <v>328</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16829,13 +16835,13 @@
         <v>328</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16843,13 +16849,13 @@
         <v>328</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16857,13 +16863,13 @@
         <v>328</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16871,7 +16877,7 @@
         <v>107</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>982</v>
@@ -16891,7 +16897,7 @@
         <v>107</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>986</v>
@@ -16911,7 +16917,7 @@
         <v>107</v>
       </c>
       <c r="B82" s="20" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>990</v>
@@ -16931,7 +16937,7 @@
         <v>107</v>
       </c>
       <c r="B83" s="20" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>994</v>
@@ -16951,7 +16957,7 @@
         <v>107</v>
       </c>
       <c r="B84" s="20" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>998</v>
@@ -16971,19 +16977,19 @@
         <v>277</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16991,19 +16997,19 @@
         <v>277</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17011,13 +17017,13 @@
         <v>572</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17025,13 +17031,13 @@
         <v>415</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17039,13 +17045,13 @@
         <v>415</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17053,13 +17059,13 @@
         <v>415</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17067,13 +17073,13 @@
         <v>415</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17081,13 +17087,13 @@
         <v>415</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17095,13 +17101,13 @@
         <v>415</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17109,13 +17115,13 @@
         <v>415</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17123,13 +17129,13 @@
         <v>415</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17137,13 +17143,13 @@
         <v>415</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17151,13 +17157,13 @@
         <v>415</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17165,13 +17171,13 @@
         <v>415</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17179,13 +17185,13 @@
         <v>415</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17193,13 +17199,13 @@
         <v>415</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17207,13 +17213,13 @@
         <v>415</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17221,13 +17227,13 @@
         <v>415</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17235,13 +17241,13 @@
         <v>415</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17249,13 +17255,13 @@
         <v>415</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17263,13 +17269,13 @@
         <v>415</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17277,13 +17283,13 @@
         <v>415</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17291,13 +17297,13 @@
         <v>415</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17305,13 +17311,13 @@
         <v>415</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17319,13 +17325,13 @@
         <v>415</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17333,13 +17339,13 @@
         <v>415</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17347,13 +17353,13 @@
         <v>415</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17361,13 +17367,13 @@
         <v>415</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17375,13 +17381,13 @@
         <v>415</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17389,13 +17395,13 @@
         <v>415</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17403,13 +17409,13 @@
         <v>415</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
     </row>
   </sheetData>

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -53,15 +53,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>33</xdr:colOff>
+                <xdr:colOff>18</xdr:colOff>
                 <xdr:row>42</xdr:row>
-                <xdr:rowOff>10</xdr:rowOff>
+                <xdr:rowOff>5</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>18</xdr:col>
-                <xdr:colOff>4</xdr:colOff>
+                <xdr:colOff>2</xdr:colOff>
                 <xdr:row>60</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:rowOff>4</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4244" uniqueCount="2358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4245" uniqueCount="2358">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -19392,7 +19392,7 @@
         <v>1</v>
       </c>
       <c r="T169" s="11"/>
-      <c r="U169" s="0"/>
+      <c r="U169" s="2"/>
       <c r="V169" s="11"/>
       <c r="W169" s="11"/>
       <c r="X169" s="11"/>
@@ -19452,7 +19452,7 @@
         <v>1</v>
       </c>
       <c r="T170" s="11"/>
-      <c r="U170" s="0"/>
+      <c r="U170" s="2"/>
       <c r="V170" s="11"/>
       <c r="W170" s="11"/>
       <c r="X170" s="11"/>
@@ -21293,7 +21293,6 @@
       <c r="F65" s="10" t="s">
         <v>1064</v>
       </c>
-      <c r="G65" s="0"/>
       <c r="H65" s="2" t="s">
         <v>1075</v>
       </c>
@@ -22536,7 +22535,6 @@
         <v>906</v>
       </c>
       <c r="F130" s="78"/>
-      <c r="G130" s="0"/>
     </row>
     <row r="131" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="11" t="s">
@@ -22590,7 +22588,7 @@
         <v>1078</v>
       </c>
       <c r="F133" s="78"/>
-      <c r="G133" s="0"/>
+      <c r="G133" s="2"/>
       <c r="H133" s="78" t="s">
         <v>1114</v>
       </c>
@@ -22904,8 +22902,8 @@
         <v>1146</v>
       </c>
       <c r="E10" s="84" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="F10" s="84" t="n">
         <f aca="false">FALSE()</f>
@@ -22914,6 +22912,9 @@
       <c r="G10" s="84" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>907</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -53,7 +53,7 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>3</xdr:colOff>
+                <xdr:colOff>2</xdr:colOff>
                 <xdr:row>42</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4622" uniqueCount="2535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4618" uniqueCount="2535">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -5910,271 +5910,271 @@
     <t xml:space="preserve">Work</t>
   </si>
   <si>
-    <t xml:space="preserve">activityCategories.school</t>
-  </si>
-  <si>
-    <t xml:space="preserve">École</t>
-  </si>
-  <si>
-    <t xml:space="preserve">School</t>
+    <t xml:space="preserve">activityCategories.schoolStudies_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1-15)[École];(15-inf)[Études];</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1-15)[School];(15-inf)[Studies];</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activityCategories.shoppingServiceRestaurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magasinage, Service ou Restauration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopping, Services or Restaurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activityCategories.dropFetchSomeone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reconduire ou Aller chercher quelqu'un</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drop someone off or Pick someone up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activityCategories.leisure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loisirs (sport, arts, promenade, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leisure (sport, arts, stroll, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activityCategories.other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activityCategories.otherParentHome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domicile de l'autre parent ou tuteur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home of the other parent or guardian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activityCategories.home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.workUsual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travail au lieu habituel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work (out-of-home fixed location)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.workNotUsual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travail dans un autre lieu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work (other place)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.workOnTheRoad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travail sur la route</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work on the road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.volunteering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bénévolat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volunteering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.schoolUsual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Études au lieu principal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Studies ([établissement scolaire]/high school, college, university)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.schoolNotUsual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Études dans un autre lieu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Studies (different location)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.shopping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magasinage (achats, station-service, épicerie, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopping (store, gas station, grocery)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.restaurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restaurant, café, bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restaurant, coffee shop, bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service (coiffeur, réparations, avocat, banque, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service (hairdresser, repairs, lawyer, bank)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santé (hôpital, clinique, physiothérapie, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical (clinic, hospital, physiotherapy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.veterinarian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vétérinaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veterinary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.worship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lieu de culte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Place of worship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.pickClassifiedPurchase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Récupérer un achat chez un particulier (petites annonces)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick up an item from a private seller (online marketplace/classifieds)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.dropSomeone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reconduire quelqu'un</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drop someone off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.fetchSomeone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aller chercher quelqu'un</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick someone up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.accompanySomeone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accompagner quelqu'un</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accompany someone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.leisureStroll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promenade sans destination fixe (ex. : aller courir, promener le chien)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stroll with no fixed destination (ex: go running/jogging, walk with pet, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.leisureSports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sport, entrainement, aller au parc (destination fixe)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sport, training, park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.leisureArtsMusicCulture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arts, Musique ou culture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arts, Music ou culture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.leisureTourism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacances, tourisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacation, tourism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.visiting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visite chez ami.e.s, copain.e ou famille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visiting friends, partner or family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.secondaryHome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résidence secondaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secondary residence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activities.schoolNotStudent</t>
   </si>
   <si>
     <t xml:space="preserve">Études</t>
   </si>
   <si>
     <t xml:space="preserve">Studies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activityCategories.shoppingServiceRestaurant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magasinage, Service ou Restauration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopping, Services or Restaurant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activityCategories.dropFetchSomeone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reconduire ou Aller chercher quelqu'un</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drop someone off or Pick someone up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activityCategories.leisure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loisirs (sport, arts, promenade, etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leisure (sport, arts, stroll, etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activityCategories.other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activityCategories.otherParentHome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domicile de l'autre parent ou tuteur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home of the other parent or guardian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activityCategories.home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.workUsual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Travail au lieu habituel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Work (out-of-home fixed location)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.workNotUsual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Travail dans un autre lieu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Work (other place)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.workOnTheRoad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Travail sur la route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Work on the road</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.volunteering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bénévolat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volunteering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.schoolUsual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Études au lieu principal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Studies ([établissement scolaire]/high school, college, university)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.schoolNotUsual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Études dans un autre lieu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Studies (different location)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.shopping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magasinage (achats, station-service, épicerie, etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopping (store, gas station, grocery)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.restaurant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restaurant, café, bar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restaurant, coffee shop, bar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service (coiffeur, réparations, avocat, banque, etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service (hairdresser, repairs, lawyer, bank)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santé (hôpital, clinique, physiothérapie, etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medical (clinic, hospital, physiotherapy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.veterinarian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vétérinaire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veterinary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.worship</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lieu de culte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Place of worship</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.pickClassifiedPurchase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Récupérer un achat chez un particulier (petites annonces)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick up an item from a private seller (online marketplace/classifieds)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.dropSomeone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reconduire quelqu'un</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drop someone off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.fetchSomeone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aller chercher quelqu'un</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick someone up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.accompanySomeone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accompagner quelqu'un</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accompany someone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.leisureStroll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promenade sans destination fixe (ex. : aller courir, promener le chien)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stroll with no fixed destination (ex: go running/jogging, walk with pet, etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.leisureSports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sport, entrainement, aller au parc (destination fixe)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sport, training, park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.leisureArtsMusicCulture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arts, Musique ou culture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arts, Music ou culture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.leisureTourism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vacances, tourisme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vacation, tourism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.visiting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visite chez ami.e.s, copain.e ou famille</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visiting friends, partner or family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.secondaryHome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Résidence secondaire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secondary residence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activities.schoolNotStudent</t>
   </si>
   <si>
     <t xml:space="preserve">onTheRoadNextPlaceCategoryChoices.wentBackHome</t>
@@ -9356,7 +9356,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9714,6 +9714,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -14547,7 +14551,7 @@
       <c r="V75" s="18"/>
       <c r="W75" s="18"/>
     </row>
-    <row r="76" s="2" customFormat="true" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" s="2" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="28" t="s">
         <v>449</v>
       </c>
@@ -24136,7 +24140,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" s="2" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="77" t="s">
         <v>385</v>
       </c>
@@ -24152,6 +24156,10 @@
       <c r="E75" s="65" t="s">
         <v>1142</v>
       </c>
+      <c r="F75" s="65"/>
+      <c r="G75" s="65"/>
+      <c r="H75" s="65"/>
+      <c r="I75" s="65"/>
     </row>
     <row r="76" s="2" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="11" t="s">
@@ -24314,11 +24322,10 @@
       <c r="F84" s="65"/>
       <c r="G84" s="65"/>
     </row>
-    <row r="85" s="2" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="65" t="s">
         <v>659</v>
       </c>
-      <c r="B85" s="65"/>
       <c r="C85" s="65" t="s">
         <v>1211</v>
       </c>
@@ -24328,8 +24335,8 @@
       <c r="E85" s="35" t="s">
         <v>1212</v>
       </c>
-      <c r="F85" s="65"/>
-      <c r="G85" s="65"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
     </row>
     <row r="86" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="65" t="s">
@@ -24694,7 +24701,7 @@
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
     </row>
-    <row r="104" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" s="2" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="11" t="s">
         <v>111</v>
       </c>
@@ -24714,8 +24721,6 @@
         <v>1184</v>
       </c>
       <c r="G104" s="10"/>
-      <c r="H104" s="2"/>
-      <c r="I104" s="2"/>
     </row>
     <row r="105" s="2" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="11" t="s">
@@ -24875,11 +24880,10 @@
       <c r="F112" s="65"/>
       <c r="G112" s="65"/>
     </row>
-    <row r="113" s="2" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="65" t="s">
         <v>123</v>
       </c>
-      <c r="B113" s="65"/>
       <c r="C113" s="28" t="s">
         <v>85</v>
       </c>
@@ -24889,12 +24893,13 @@
       <c r="E113" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="F113" s="65"/>
       <c r="G113" s="65" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="114" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H113" s="2"/>
+      <c r="I113" s="2"/>
+    </row>
+    <row r="114" s="2" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="65" t="s">
         <v>123</v>
       </c>
@@ -24910,8 +24915,8 @@
       <c r="E114" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="H114" s="2"/>
-      <c r="I114" s="2"/>
+      <c r="F114" s="65"/>
+      <c r="G114" s="65"/>
     </row>
     <row r="115" s="2" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="65" t="s">
@@ -24950,7 +24955,7 @@
       </c>
       <c r="G116" s="65"/>
     </row>
-    <row r="117" s="2" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="65" t="s">
         <v>183</v>
       </c>
@@ -24966,8 +24971,8 @@
       <c r="E117" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F117" s="65"/>
-      <c r="G117" s="65"/>
+      <c r="H117" s="2"/>
+      <c r="I117" s="2"/>
     </row>
     <row r="118" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="65" t="s">
@@ -25008,7 +25013,7 @@
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
     </row>
-    <row r="120" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" s="2" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="65" t="s">
         <v>188</v>
       </c>
@@ -25027,8 +25032,7 @@
       <c r="F120" s="65" t="s">
         <v>1183</v>
       </c>
-      <c r="H120" s="2"/>
-      <c r="I120" s="2"/>
+      <c r="G120" s="65"/>
     </row>
     <row r="121" s="2" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="65" t="s">
@@ -25104,7 +25108,7 @@
       <c r="F124" s="65"/>
       <c r="G124" s="65"/>
     </row>
-    <row r="125" s="2" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="11" t="s">
         <v>202</v>
       </c>
@@ -25120,8 +25124,8 @@
       <c r="E125" s="35" t="s">
         <v>1142</v>
       </c>
-      <c r="F125" s="65"/>
-      <c r="G125" s="65"/>
+      <c r="H125" s="2"/>
+      <c r="I125" s="2"/>
     </row>
     <row r="126" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="65" t="s">
@@ -26048,7 +26052,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F227"/>
+  <dimension ref="A1:F1048576"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="16.72"/>
@@ -27134,34 +27138,32 @@
       <c r="E68" s="28"/>
       <c r="F68" s="28"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="22" t="s">
+    <row r="69" s="90" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="90" t="s">
         <v>431</v>
       </c>
-      <c r="B69" s="10" t="s">
+      <c r="B69" s="90" t="s">
         <v>1552</v>
       </c>
-      <c r="C69" s="28" t="s">
+      <c r="C69" s="90" t="s">
         <v>1553</v>
       </c>
-      <c r="D69" s="28" t="s">
+      <c r="D69" s="90" t="s">
         <v>1554</v>
       </c>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="22" t="s">
         <v>431</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>1552</v>
+        <v>1555</v>
       </c>
       <c r="C70" s="28" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="D70" s="28" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="E70" s="28"/>
       <c r="F70" s="28"/>
@@ -27171,13 +27173,13 @@
         <v>431</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="C71" s="28" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="D71" s="28" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="E71" s="28"/>
       <c r="F71" s="28"/>
@@ -27187,13 +27189,13 @@
         <v>431</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="C72" s="28" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="D72" s="28" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="E72" s="28"/>
       <c r="F72" s="28"/>
@@ -27203,13 +27205,13 @@
         <v>431</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="C73" s="28" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="D73" s="28" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="E73" s="28"/>
       <c r="F73" s="28"/>
@@ -27219,13 +27221,13 @@
         <v>431</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="C74" s="28" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="D74" s="28" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="E74" s="28"/>
       <c r="F74" s="28"/>
@@ -27235,13 +27237,13 @@
         <v>431</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="C75" s="28" t="s">
-        <v>1570</v>
+        <v>1245</v>
       </c>
       <c r="D75" s="28" t="s">
-        <v>1571</v>
+        <v>1246</v>
       </c>
       <c r="E75" s="28"/>
       <c r="F75" s="28"/>
@@ -27251,13 +27253,13 @@
         <v>431</v>
       </c>
       <c r="B76" s="10" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C76" s="28" t="s">
         <v>1572</v>
       </c>
-      <c r="C76" s="28" t="s">
-        <v>1245</v>
-      </c>
       <c r="D76" s="28" t="s">
-        <v>1246</v>
+        <v>1573</v>
       </c>
       <c r="E76" s="28"/>
       <c r="F76" s="28"/>
@@ -27267,13 +27269,13 @@
         <v>431</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="C77" s="28" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="D77" s="28" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="E77" s="28"/>
       <c r="F77" s="28"/>
@@ -27283,13 +27285,13 @@
         <v>431</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="C78" s="28" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="D78" s="28" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="E78" s="28"/>
       <c r="F78" s="28"/>
@@ -27299,13 +27301,13 @@
         <v>431</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="C79" s="28" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="D79" s="28" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="E79" s="28"/>
       <c r="F79" s="28"/>
@@ -27315,13 +27317,13 @@
         <v>431</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="C80" s="28" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="D80" s="28" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="E80" s="28"/>
       <c r="F80" s="28"/>
@@ -27331,13 +27333,13 @@
         <v>431</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="C81" s="28" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="D81" s="28" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="E81" s="28"/>
       <c r="F81" s="28"/>
@@ -27347,13 +27349,13 @@
         <v>431</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="C82" s="28" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="D82" s="28" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="E82" s="28"/>
       <c r="F82" s="28"/>
@@ -27363,13 +27365,13 @@
         <v>431</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="C83" s="28" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="D83" s="28" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="E83" s="28"/>
       <c r="F83" s="28"/>
@@ -27379,13 +27381,13 @@
         <v>431</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="C84" s="28" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="D84" s="28" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="E84" s="28"/>
       <c r="F84" s="28"/>
@@ -27395,13 +27397,13 @@
         <v>431</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="C85" s="28" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="D85" s="28" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="E85" s="28"/>
       <c r="F85" s="28"/>
@@ -27411,13 +27413,13 @@
         <v>431</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="C86" s="28" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="D86" s="28" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="E86" s="28"/>
       <c r="F86" s="28"/>
@@ -27427,13 +27429,13 @@
         <v>431</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="C87" s="28" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="D87" s="28" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="E87" s="28"/>
       <c r="F87" s="28"/>
@@ -27443,13 +27445,13 @@
         <v>431</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="C88" s="28" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="D88" s="28" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="E88" s="28"/>
       <c r="F88" s="28"/>
@@ -27459,13 +27461,13 @@
         <v>431</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="C89" s="28" t="s">
-        <v>1610</v>
+        <v>1565</v>
       </c>
       <c r="D89" s="28" t="s">
-        <v>1611</v>
+        <v>1566</v>
       </c>
       <c r="E89" s="28"/>
       <c r="F89" s="28"/>
@@ -27475,13 +27477,13 @@
         <v>431</v>
       </c>
       <c r="B90" s="10" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C90" s="28" t="s">
         <v>1612</v>
       </c>
-      <c r="C90" s="28" t="s">
-        <v>1567</v>
-      </c>
       <c r="D90" s="28" t="s">
-        <v>1568</v>
+        <v>1613</v>
       </c>
       <c r="E90" s="28"/>
       <c r="F90" s="28"/>
@@ -27491,13 +27493,13 @@
         <v>431</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="C91" s="28" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="D91" s="28" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="E91" s="28"/>
       <c r="F91" s="28"/>
@@ -27507,13 +27509,13 @@
         <v>431</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="C92" s="28" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="D92" s="28" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="E92" s="28"/>
       <c r="F92" s="28"/>
@@ -27523,13 +27525,13 @@
         <v>431</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="C93" s="28" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="D93" s="28" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="E93" s="28"/>
       <c r="F93" s="28"/>
@@ -27539,13 +27541,13 @@
         <v>431</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="C94" s="28" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="D94" s="28" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="E94" s="28"/>
       <c r="F94" s="28"/>
@@ -27555,13 +27557,13 @@
         <v>431</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="C95" s="28" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="D95" s="28" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="E95" s="28"/>
       <c r="F95" s="28"/>
@@ -27571,13 +27573,13 @@
         <v>431</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="C96" s="28" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="D96" s="28" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="E96" s="28"/>
       <c r="F96" s="28"/>
@@ -27587,13 +27589,13 @@
         <v>431</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="C97" s="28" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="D97" s="28" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="E97" s="28"/>
       <c r="F97" s="28"/>
@@ -27603,13 +27605,13 @@
         <v>431</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>1634</v>
+        <v>1580</v>
       </c>
       <c r="C98" s="28" t="s">
-        <v>1635</v>
+        <v>1581</v>
       </c>
       <c r="D98" s="28" t="s">
-        <v>1636</v>
+        <v>1582</v>
       </c>
       <c r="E98" s="28"/>
       <c r="F98" s="28"/>
@@ -27619,13 +27621,13 @@
         <v>431</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>1582</v>
+        <v>1635</v>
       </c>
       <c r="C99" s="28" t="s">
-        <v>1583</v>
+        <v>1636</v>
       </c>
       <c r="D99" s="28" t="s">
-        <v>1584</v>
+        <v>1637</v>
       </c>
       <c r="E99" s="28"/>
       <c r="F99" s="28"/>
@@ -27635,99 +27637,91 @@
         <v>431</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="C100" s="28" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="E100" s="28"/>
       <c r="F100" s="28"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="22" t="s">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B101" s="10" t="s">
-        <v>1640</v>
-      </c>
-      <c r="C101" s="28" t="s">
-        <v>1555</v>
-      </c>
-      <c r="D101" s="28" t="s">
-        <v>1556</v>
-      </c>
-      <c r="E101" s="28"/>
-      <c r="F101" s="28"/>
+      <c r="B101" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>1246</v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+      <c r="A102" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B102" s="0" t="s">
-        <v>1641</v>
-      </c>
-      <c r="C102" s="0" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D102" s="0" t="s">
-        <v>1246</v>
-      </c>
-      <c r="E102" s="0"/>
-      <c r="F102" s="0"/>
+      <c r="B102" s="2" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>1644</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
+      <c r="A103" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B103" s="0" t="s">
-        <v>1642</v>
-      </c>
-      <c r="C103" s="0" t="s">
-        <v>1643</v>
-      </c>
-      <c r="D103" s="0" t="s">
-        <v>1644</v>
-      </c>
-      <c r="E103" s="0"/>
-      <c r="F103" s="0"/>
+      <c r="B103" s="2" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>1647</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+      <c r="A104" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B104" s="0" t="s">
-        <v>1645</v>
-      </c>
-      <c r="C104" s="0" t="s">
-        <v>1646</v>
-      </c>
-      <c r="D104" s="0" t="s">
-        <v>1647</v>
-      </c>
-      <c r="E104" s="0"/>
-      <c r="F104" s="0"/>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
-        <v>431</v>
-      </c>
-      <c r="B105" s="0" t="s">
+      <c r="B104" s="2" t="s">
         <v>1648</v>
       </c>
-      <c r="C105" s="0" t="s">
+      <c r="C104" s="2" t="s">
         <v>1649</v>
       </c>
-      <c r="D105" s="0" t="s">
+      <c r="D104" s="2" t="s">
         <v>1650</v>
       </c>
-      <c r="E105" s="0" t="s">
+      <c r="E104" s="2" t="s">
         <v>1651</v>
       </c>
-      <c r="F105" s="0" t="s">
+      <c r="F104" s="2" t="s">
         <v>1652</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D105" s="10" t="s">
+        <v>1655</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27735,13 +27729,13 @@
         <v>152</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1653</v>
+        <v>1656</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>1654</v>
+        <v>1657</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>1655</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27749,13 +27743,13 @@
         <v>152</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1656</v>
+        <v>1659</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>1657</v>
+        <v>1660</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>1658</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27763,13 +27757,13 @@
         <v>152</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1659</v>
+        <v>1662</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>1660</v>
+        <v>1663</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>1661</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27777,41 +27771,41 @@
         <v>152</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1662</v>
+        <v>1665</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>1664</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>1665</v>
+      <c r="B110" s="91" t="s">
+        <v>1668</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>1666</v>
+        <v>1669</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>1667</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B111" s="90" t="s">
-        <v>1668</v>
+      <c r="B111" s="10" t="s">
+        <v>1671</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>1669</v>
+        <v>1672</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>1670</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27819,13 +27813,13 @@
         <v>152</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>1671</v>
+        <v>1674</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>1672</v>
+        <v>1675</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>1673</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27833,33 +27827,33 @@
         <v>152</v>
       </c>
       <c r="B113" s="10" t="s">
-        <v>1674</v>
+        <v>1677</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>1675</v>
-      </c>
-      <c r="D113" s="10" t="s">
-        <v>1676</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1678</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>1679</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B114" s="10" t="s">
-        <v>1677</v>
-      </c>
-      <c r="C114" s="10" t="s">
-        <v>1678</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>1681</v>
+      <c r="B114" s="45" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C114" s="45" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D114" s="91" t="s">
+        <v>1684</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27867,27 +27861,27 @@
         <v>152</v>
       </c>
       <c r="B115" s="45" t="s">
-        <v>1682</v>
+        <v>1685</v>
       </c>
       <c r="C115" s="45" t="s">
-        <v>1683</v>
-      </c>
-      <c r="D115" s="90" t="s">
-        <v>1684</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1686</v>
+      </c>
+      <c r="D115" s="91" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B116" s="45" t="s">
-        <v>1685</v>
+      <c r="B116" s="10" t="s">
+        <v>1688</v>
       </c>
       <c r="C116" s="45" t="s">
-        <v>1686</v>
-      </c>
-      <c r="D116" s="90" t="s">
-        <v>1687</v>
+        <v>1689</v>
+      </c>
+      <c r="D116" s="91" t="s">
+        <v>1690</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27895,13 +27889,13 @@
         <v>152</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>1688</v>
-      </c>
-      <c r="C117" s="45" t="s">
-        <v>1689</v>
-      </c>
-      <c r="D117" s="90" t="s">
-        <v>1690</v>
+        <v>1691</v>
+      </c>
+      <c r="C117" s="28" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D117" s="28" t="s">
+        <v>1693</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27909,41 +27903,43 @@
         <v>152</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>1691</v>
-      </c>
-      <c r="C118" s="28" t="s">
-        <v>1692</v>
-      </c>
-      <c r="D118" s="28" t="s">
-        <v>1693</v>
+        <v>1694</v>
+      </c>
+      <c r="C118" s="92" t="s">
+        <v>1695</v>
+      </c>
+      <c r="D118" s="92" t="s">
+        <v>1695</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B119" s="10" t="s">
-        <v>1694</v>
-      </c>
-      <c r="C119" s="91" t="s">
-        <v>1695</v>
-      </c>
-      <c r="D119" s="91" t="s">
-        <v>1695</v>
-      </c>
+      <c r="A119" s="18" t="s">
+        <v>431</v>
+      </c>
+      <c r="B119" s="35" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C119" s="35" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D119" s="35" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E119" s="35"/>
+      <c r="F119" s="35"/>
     </row>
     <row r="120" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="18" t="s">
         <v>431</v>
       </c>
       <c r="B120" s="35" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="C120" s="35" t="s">
-        <v>1245</v>
+        <v>1643</v>
       </c>
       <c r="D120" s="35" t="s">
-        <v>1246</v>
+        <v>1644</v>
       </c>
       <c r="E120" s="35"/>
       <c r="F120" s="35"/>
@@ -27953,51 +27949,49 @@
         <v>431</v>
       </c>
       <c r="B121" s="35" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="C121" s="35" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="D121" s="35" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
       <c r="E121" s="35"/>
       <c r="F121" s="35"/>
     </row>
-    <row r="122" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="18" t="s">
         <v>431</v>
       </c>
-      <c r="B122" s="35" t="s">
-        <v>1698</v>
-      </c>
-      <c r="C122" s="35" t="s">
-        <v>1646</v>
-      </c>
-      <c r="D122" s="35" t="s">
-        <v>1647</v>
-      </c>
-      <c r="E122" s="35"/>
-      <c r="F122" s="35"/>
-    </row>
-    <row r="123" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="18" t="s">
+      <c r="B122" s="10" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C122" s="10" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D122" s="10" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E122" s="10" t="s">
+        <v>1651</v>
+      </c>
+      <c r="F122" s="10" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="2" t="s">
         <v>431</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>1649</v>
+        <v>1701</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>1650</v>
-      </c>
-      <c r="E123" s="10" t="s">
-        <v>1651</v>
-      </c>
-      <c r="F123" s="10" t="s">
-        <v>1652</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28005,27 +27999,27 @@
         <v>431</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>1701</v>
+        <v>1704</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>1702</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
         <v>431</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>1704</v>
+        <v>1707</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28033,47 +28027,53 @@
         <v>431</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>1706</v>
+        <v>1709</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>1707</v>
+        <v>1710</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>1708</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B127" s="10" t="s">
-        <v>1709</v>
+      <c r="A127" s="18" t="s">
+        <v>526</v>
+      </c>
+      <c r="B127" s="35" t="s">
+        <v>1712</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>1710</v>
+        <v>1713</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>1711</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1714</v>
+      </c>
+      <c r="E127" s="10" t="s">
+        <v>1715</v>
+      </c>
+      <c r="F127" s="10" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="18" t="s">
         <v>526</v>
       </c>
       <c r="B128" s="35" t="s">
-        <v>1712</v>
+        <v>1717</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>1713</v>
+        <v>1718</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>1714</v>
+        <v>1719</v>
       </c>
       <c r="E128" s="10" t="s">
-        <v>1715</v>
+        <v>1720</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28081,33 +28081,29 @@
         <v>526</v>
       </c>
       <c r="B129" s="35" t="s">
-        <v>1717</v>
+        <v>1722</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>1718</v>
+        <v>1723</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>1719</v>
-      </c>
-      <c r="E129" s="10" t="s">
-        <v>1720</v>
-      </c>
-      <c r="F129" s="10" t="s">
-        <v>1721</v>
-      </c>
+        <v>1724</v>
+      </c>
+      <c r="E129" s="10"/>
+      <c r="F129" s="10"/>
     </row>
     <row r="130" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="18" t="s">
         <v>526</v>
       </c>
       <c r="B130" s="35" t="s">
-        <v>1722</v>
+        <v>1725</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>1723</v>
+        <v>1726</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>1724</v>
+        <v>1727</v>
       </c>
       <c r="E130" s="10"/>
       <c r="F130" s="10"/>
@@ -28117,29 +28113,29 @@
         <v>526</v>
       </c>
       <c r="B131" s="35" t="s">
-        <v>1725</v>
+        <v>1728</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>1726</v>
+        <v>1729</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>1727</v>
+        <v>1730</v>
       </c>
       <c r="E131" s="10"/>
       <c r="F131" s="10"/>
     </row>
-    <row r="132" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="18" t="s">
         <v>526</v>
       </c>
-      <c r="B132" s="35" t="s">
-        <v>1728</v>
+      <c r="B132" s="10" t="s">
+        <v>1731</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>1729</v>
+        <v>1732</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>1730</v>
+        <v>1733</v>
       </c>
       <c r="E132" s="10"/>
       <c r="F132" s="10"/>
@@ -28149,13 +28145,13 @@
         <v>526</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>1731</v>
-      </c>
-      <c r="C133" s="10" t="s">
-        <v>1732</v>
-      </c>
-      <c r="D133" s="10" t="s">
-        <v>1733</v>
+        <v>1734</v>
+      </c>
+      <c r="C133" s="11" t="s">
+        <v>1735</v>
+      </c>
+      <c r="D133" s="11" t="s">
+        <v>1736</v>
       </c>
       <c r="E133" s="10"/>
       <c r="F133" s="10"/>
@@ -28165,13 +28161,13 @@
         <v>526</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
       <c r="E134" s="10"/>
       <c r="F134" s="10"/>
@@ -28181,29 +28177,29 @@
         <v>526</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
       <c r="E135" s="10"/>
       <c r="F135" s="10"/>
     </row>
-    <row r="136" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="18" t="s">
         <v>526</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
       <c r="E136" s="10"/>
       <c r="F136" s="10"/>
@@ -28212,14 +28208,14 @@
       <c r="A137" s="18" t="s">
         <v>526</v>
       </c>
-      <c r="B137" s="10" t="s">
-        <v>1743</v>
+      <c r="B137" s="45" t="s">
+        <v>1746</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="D137" s="11" t="s">
-        <v>1745</v>
+        <v>1748</v>
       </c>
       <c r="E137" s="10"/>
       <c r="F137" s="10"/>
@@ -28229,13 +28225,13 @@
         <v>526</v>
       </c>
       <c r="B138" s="45" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="E138" s="10"/>
       <c r="F138" s="10"/>
@@ -28245,13 +28241,13 @@
         <v>526</v>
       </c>
       <c r="B139" s="45" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="D139" s="11" t="s">
-        <v>1751</v>
+        <v>1754</v>
       </c>
       <c r="E139" s="10"/>
       <c r="F139" s="10"/>
@@ -28261,13 +28257,13 @@
         <v>526</v>
       </c>
       <c r="B140" s="45" t="s">
-        <v>1752</v>
+        <v>1755</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>1754</v>
+        <v>1757</v>
       </c>
       <c r="E140" s="10"/>
       <c r="F140" s="10"/>
@@ -28277,13 +28273,13 @@
         <v>526</v>
       </c>
       <c r="B141" s="45" t="s">
-        <v>1755</v>
+        <v>1758</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>1756</v>
+        <v>1759</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>1757</v>
+        <v>1760</v>
       </c>
       <c r="E141" s="10"/>
       <c r="F141" s="10"/>
@@ -28293,13 +28289,13 @@
         <v>526</v>
       </c>
       <c r="B142" s="45" t="s">
-        <v>1758</v>
+        <v>1761</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>1759</v>
+        <v>1762</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>1760</v>
+        <v>1763</v>
       </c>
       <c r="E142" s="10"/>
       <c r="F142" s="10"/>
@@ -28309,13 +28305,13 @@
         <v>526</v>
       </c>
       <c r="B143" s="45" t="s">
-        <v>1761</v>
+        <v>1764</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>1763</v>
+        <v>1766</v>
       </c>
       <c r="E143" s="10"/>
       <c r="F143" s="10"/>
@@ -28325,13 +28321,13 @@
         <v>526</v>
       </c>
       <c r="B144" s="45" t="s">
-        <v>1764</v>
+        <v>1767</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>1765</v>
+        <v>1756</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>1766</v>
+        <v>1757</v>
       </c>
       <c r="E144" s="10"/>
       <c r="F144" s="10"/>
@@ -28341,13 +28337,13 @@
         <v>526</v>
       </c>
       <c r="B145" s="45" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>1756</v>
+        <v>1769</v>
       </c>
       <c r="D145" s="11" t="s">
-        <v>1757</v>
+        <v>1770</v>
       </c>
       <c r="E145" s="10"/>
       <c r="F145" s="10"/>
@@ -28357,13 +28353,13 @@
         <v>526</v>
       </c>
       <c r="B146" s="45" t="s">
-        <v>1768</v>
+        <v>1771</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>1769</v>
+        <v>1772</v>
       </c>
       <c r="D146" s="11" t="s">
-        <v>1770</v>
+        <v>1773</v>
       </c>
       <c r="E146" s="10"/>
       <c r="F146" s="10"/>
@@ -28373,13 +28369,13 @@
         <v>526</v>
       </c>
       <c r="B147" s="45" t="s">
-        <v>1771</v>
+        <v>1774</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>1772</v>
+        <v>1775</v>
       </c>
       <c r="D147" s="11" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="E147" s="10"/>
       <c r="F147" s="10"/>
@@ -28389,13 +28385,13 @@
         <v>526</v>
       </c>
       <c r="B148" s="45" t="s">
-        <v>1774</v>
+        <v>1777</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>1775</v>
+        <v>1778</v>
       </c>
       <c r="D148" s="11" t="s">
-        <v>1776</v>
+        <v>1779</v>
       </c>
       <c r="E148" s="10"/>
       <c r="F148" s="10"/>
@@ -28405,13 +28401,13 @@
         <v>526</v>
       </c>
       <c r="B149" s="45" t="s">
-        <v>1777</v>
+        <v>1780</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>1778</v>
+        <v>1781</v>
       </c>
       <c r="D149" s="11" t="s">
-        <v>1779</v>
+        <v>1782</v>
       </c>
       <c r="E149" s="10"/>
       <c r="F149" s="10"/>
@@ -28421,13 +28417,13 @@
         <v>526</v>
       </c>
       <c r="B150" s="45" t="s">
-        <v>1780</v>
+        <v>1783</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>1781</v>
+        <v>1784</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>1782</v>
+        <v>1785</v>
       </c>
       <c r="E150" s="10"/>
       <c r="F150" s="10"/>
@@ -28437,13 +28433,13 @@
         <v>526</v>
       </c>
       <c r="B151" s="45" t="s">
-        <v>1783</v>
+        <v>1786</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>1784</v>
+        <v>1787</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>1785</v>
+        <v>1788</v>
       </c>
       <c r="E151" s="10"/>
       <c r="F151" s="10"/>
@@ -28453,13 +28449,13 @@
         <v>526</v>
       </c>
       <c r="B152" s="45" t="s">
-        <v>1786</v>
+        <v>1789</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>1787</v>
+        <v>1790</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>1788</v>
+        <v>1791</v>
       </c>
       <c r="E152" s="10"/>
       <c r="F152" s="10"/>
@@ -28469,13 +28465,13 @@
         <v>526</v>
       </c>
       <c r="B153" s="45" t="s">
-        <v>1789</v>
+        <v>1792</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>1790</v>
+        <v>1793</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>1791</v>
+        <v>1794</v>
       </c>
       <c r="E153" s="10"/>
       <c r="F153" s="10"/>
@@ -28485,13 +28481,13 @@
         <v>526</v>
       </c>
       <c r="B154" s="45" t="s">
-        <v>1792</v>
+        <v>1795</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>1793</v>
+        <v>1784</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>1794</v>
+        <v>1785</v>
       </c>
       <c r="E154" s="10"/>
       <c r="F154" s="10"/>
@@ -28501,13 +28497,13 @@
         <v>526</v>
       </c>
       <c r="B155" s="45" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>1784</v>
+        <v>1797</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>1785</v>
+        <v>1798</v>
       </c>
       <c r="E155" s="10"/>
       <c r="F155" s="10"/>
@@ -28517,183 +28513,187 @@
         <v>526</v>
       </c>
       <c r="B156" s="45" t="s">
-        <v>1796</v>
+        <v>1799</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>1797</v>
+        <v>1800</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>1798</v>
+        <v>1801</v>
       </c>
       <c r="E156" s="10"/>
       <c r="F156" s="10"/>
     </row>
-    <row r="157" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="18" t="s">
-        <v>526</v>
-      </c>
-      <c r="B157" s="45" t="s">
-        <v>1799</v>
-      </c>
-      <c r="C157" s="11" t="s">
-        <v>1800</v>
-      </c>
-      <c r="D157" s="11" t="s">
-        <v>1801</v>
-      </c>
-      <c r="E157" s="10"/>
-      <c r="F157" s="10"/>
-    </row>
-    <row r="158" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>1803</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>1805</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
         <v>152</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>1802</v>
+        <v>1807</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>1803</v>
+        <v>1808</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>1804</v>
+        <v>1809</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>1805</v>
+        <v>1810</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1806</v>
-      </c>
-    </row>
-    <row r="159" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>1807</v>
+      <c r="B159" s="93" t="s">
+        <v>1812</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>1808</v>
+        <v>1813</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>1809</v>
+        <v>1814</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>1810</v>
+        <v>1815</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1811</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B160" s="92" t="s">
-        <v>1812</v>
+      <c r="B160" s="93" t="s">
+        <v>1817</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>1813</v>
+        <v>1818</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>1815</v>
+        <v>1820</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>1816</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B161" s="92" t="s">
-        <v>1817</v>
+      <c r="B161" s="93" t="s">
+        <v>1822</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>1818</v>
+        <v>1823</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>1819</v>
+        <v>1824</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>1820</v>
+        <v>1825</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1821</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B162" s="92" t="s">
-        <v>1822</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>1823</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>1824</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>1825</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>1826</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="B162" s="94" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C162" s="65" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D162" s="28" t="s">
+        <v>1829</v>
+      </c>
+      <c r="E162" s="10"/>
+      <c r="F162" s="10"/>
     </row>
     <row r="163" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B163" s="93" t="s">
-        <v>1827</v>
-      </c>
-      <c r="C163" s="65" t="s">
-        <v>1828</v>
-      </c>
-      <c r="D163" s="28" t="s">
-        <v>1829</v>
+      <c r="B163" s="10" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C163" s="10" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D163" s="10" t="s">
+        <v>1832</v>
       </c>
       <c r="E163" s="10"/>
       <c r="F163" s="10"/>
     </row>
-    <row r="164" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B164" s="10" t="s">
-        <v>1830</v>
+      <c r="B164" s="2" t="s">
+        <v>1833</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>1831</v>
+        <v>1834</v>
       </c>
       <c r="D164" s="10" t="s">
-        <v>1832</v>
-      </c>
-      <c r="E164" s="10"/>
-      <c r="F164" s="10"/>
+        <v>1835</v>
+      </c>
+      <c r="E164" s="10" t="s">
+        <v>1836</v>
+      </c>
+      <c r="F164" s="10" t="s">
+        <v>1837</v>
+      </c>
     </row>
     <row r="165" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2" t="s">
         <v>342</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>1833</v>
+        <v>1838</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>1834</v>
+        <v>1839</v>
       </c>
       <c r="D165" s="10" t="s">
-        <v>1835</v>
+        <v>1840</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>1836</v>
+        <v>1841</v>
       </c>
       <c r="F165" s="10" t="s">
-        <v>1837</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28701,59 +28701,59 @@
         <v>342</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>1838</v>
-      </c>
-      <c r="C166" s="10" t="s">
-        <v>1839</v>
-      </c>
-      <c r="D166" s="10" t="s">
-        <v>1840</v>
-      </c>
-      <c r="E166" s="10" t="s">
-        <v>1841</v>
-      </c>
-      <c r="F166" s="10" t="s">
-        <v>1842</v>
-      </c>
-    </row>
-    <row r="167" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1843</v>
+      </c>
+      <c r="C166" s="28" t="s">
+        <v>1844</v>
+      </c>
+      <c r="D166" s="28" t="s">
+        <v>1845</v>
+      </c>
+      <c r="E166" s="28" t="s">
+        <v>1846</v>
+      </c>
+      <c r="F166" s="28" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2" t="s">
         <v>342</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>1843</v>
+        <v>1848</v>
       </c>
       <c r="C167" s="28" t="s">
-        <v>1844</v>
+        <v>1849</v>
       </c>
       <c r="D167" s="28" t="s">
-        <v>1845</v>
+        <v>1850</v>
       </c>
       <c r="E167" s="28" t="s">
-        <v>1846</v>
+        <v>1851</v>
       </c>
       <c r="F167" s="28" t="s">
-        <v>1847</v>
-      </c>
-    </row>
-    <row r="168" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2" t="s">
         <v>342</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>1848</v>
+        <v>1853</v>
       </c>
       <c r="C168" s="28" t="s">
-        <v>1849</v>
+        <v>1854</v>
       </c>
       <c r="D168" s="28" t="s">
-        <v>1850</v>
+        <v>1855</v>
       </c>
       <c r="E168" s="28" t="s">
-        <v>1851</v>
+        <v>1856</v>
       </c>
       <c r="F168" s="28" t="s">
-        <v>1852</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28761,39 +28761,39 @@
         <v>342</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>1853</v>
+        <v>1858</v>
       </c>
       <c r="C169" s="28" t="s">
-        <v>1854</v>
-      </c>
-      <c r="D169" s="28" t="s">
-        <v>1855</v>
+        <v>1859</v>
+      </c>
+      <c r="D169" s="65" t="s">
+        <v>1860</v>
       </c>
       <c r="E169" s="28" t="s">
-        <v>1856</v>
-      </c>
-      <c r="F169" s="28" t="s">
-        <v>1857</v>
-      </c>
-    </row>
-    <row r="170" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1861</v>
+      </c>
+      <c r="F169" s="65" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B170" s="2" t="s">
-        <v>1858</v>
+      <c r="B170" s="10" t="s">
+        <v>1863</v>
       </c>
       <c r="C170" s="28" t="s">
-        <v>1859</v>
+        <v>1864</v>
       </c>
       <c r="D170" s="65" t="s">
-        <v>1860</v>
+        <v>1865</v>
       </c>
       <c r="E170" s="28" t="s">
-        <v>1861</v>
+        <v>1866</v>
       </c>
       <c r="F170" s="65" t="s">
-        <v>1862</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28801,65 +28801,59 @@
         <v>342</v>
       </c>
       <c r="B171" s="10" t="s">
-        <v>1863</v>
+        <v>1868</v>
       </c>
       <c r="C171" s="28" t="s">
-        <v>1864</v>
+        <v>1869</v>
       </c>
       <c r="D171" s="65" t="s">
-        <v>1865</v>
-      </c>
-      <c r="E171" s="28" t="s">
-        <v>1866</v>
-      </c>
-      <c r="F171" s="65" t="s">
-        <v>1867</v>
-      </c>
-    </row>
-    <row r="172" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1870</v>
+      </c>
+      <c r="E171" s="28"/>
+      <c r="F171" s="65"/>
+    </row>
+    <row r="172" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2" t="s">
         <v>342</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>1868</v>
+        <v>1871</v>
       </c>
       <c r="C172" s="28" t="s">
-        <v>1869</v>
-      </c>
-      <c r="D172" s="65" t="s">
-        <v>1870</v>
+        <v>1872</v>
+      </c>
+      <c r="D172" s="28" t="s">
+        <v>1873</v>
       </c>
       <c r="E172" s="28"/>
       <c r="F172" s="65"/>
     </row>
-    <row r="173" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="B173" s="10" t="s">
-        <v>1871</v>
-      </c>
-      <c r="C173" s="28" t="s">
-        <v>1872</v>
-      </c>
-      <c r="D173" s="28" t="s">
-        <v>1873</v>
-      </c>
-      <c r="E173" s="28"/>
-      <c r="F173" s="65"/>
+        <v>1027</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>1874</v>
+      </c>
+      <c r="C173" s="10" t="s">
+        <v>1875</v>
+      </c>
+      <c r="D173" s="10" t="s">
+        <v>1876</v>
+      </c>
     </row>
     <row r="174" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2" t="s">
-        <v>1027</v>
+        <v>526</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>1874</v>
+        <v>1877</v>
       </c>
       <c r="C174" s="10" t="s">
-        <v>1875</v>
+        <v>1878</v>
       </c>
       <c r="D174" s="10" t="s">
-        <v>1876</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28867,13 +28861,13 @@
         <v>526</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>1877</v>
+        <v>1880</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>1878</v>
+        <v>1881</v>
       </c>
       <c r="D175" s="10" t="s">
-        <v>1879</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28881,13 +28875,13 @@
         <v>526</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>1880</v>
+        <v>1883</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>1881</v>
+        <v>1884</v>
       </c>
       <c r="D176" s="10" t="s">
-        <v>1882</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28895,13 +28889,13 @@
         <v>526</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>1883</v>
+        <v>1886</v>
       </c>
       <c r="C177" s="10" t="s">
-        <v>1884</v>
+        <v>1887</v>
       </c>
       <c r="D177" s="10" t="s">
-        <v>1885</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28909,13 +28903,13 @@
         <v>526</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>1886</v>
+        <v>1889</v>
       </c>
       <c r="C178" s="10" t="s">
-        <v>1887</v>
+        <v>1890</v>
       </c>
       <c r="D178" s="10" t="s">
-        <v>1888</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28923,27 +28917,27 @@
         <v>526</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>1889</v>
+        <v>1892</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>1890</v>
+        <v>1893</v>
       </c>
       <c r="D179" s="10" t="s">
-        <v>1891</v>
-      </c>
-    </row>
-    <row r="180" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="2" t="s">
         <v>526</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>1892</v>
-      </c>
-      <c r="C180" s="10" t="s">
-        <v>1893</v>
-      </c>
-      <c r="D180" s="10" t="s">
-        <v>1894</v>
+        <v>1895</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>1897</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28951,13 +28945,13 @@
         <v>526</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>1895</v>
+        <v>1898</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>1896</v>
+        <v>1899</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>1897</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28965,13 +28959,13 @@
         <v>526</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>1899</v>
+        <v>1901</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28979,13 +28973,13 @@
         <v>526</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>1900</v>
+        <v>1903</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>1901</v>
+        <v>1904</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28993,13 +28987,13 @@
         <v>526</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>1904</v>
+        <v>1907</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>1905</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29007,13 +29001,13 @@
         <v>526</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>1906</v>
+        <v>1909</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>1907</v>
+        <v>1910</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>1908</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29021,13 +29015,13 @@
         <v>526</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>1909</v>
+        <v>1912</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>1910</v>
+        <v>1913</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>1911</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29035,13 +29029,13 @@
         <v>526</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>1912</v>
+        <v>1915</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>1913</v>
+        <v>1916</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>1914</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29049,13 +29043,13 @@
         <v>526</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>1915</v>
+        <v>1918</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>1916</v>
+        <v>1919</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>1917</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29063,13 +29057,13 @@
         <v>526</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>1918</v>
+        <v>1921</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>1919</v>
+        <v>1922</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>1920</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29077,13 +29071,13 @@
         <v>526</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>1922</v>
+        <v>1925</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>1923</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29091,13 +29085,13 @@
         <v>526</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>1924</v>
+        <v>1927</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>1925</v>
+        <v>1928</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>1926</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29105,13 +29099,13 @@
         <v>526</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>1928</v>
+        <v>1931</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>1929</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29119,13 +29113,13 @@
         <v>526</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>1931</v>
+        <v>1934</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>1932</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29133,13 +29127,13 @@
         <v>526</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>1933</v>
+        <v>1936</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>1934</v>
+        <v>1937</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>1935</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29147,13 +29141,13 @@
         <v>526</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>1937</v>
+        <v>1940</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>1938</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29161,41 +29155,41 @@
         <v>526</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>1939</v>
+        <v>1942</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>1940</v>
+        <v>1943</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>1941</v>
-      </c>
-    </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B197" s="2" t="s">
-        <v>1942</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>1943</v>
-      </c>
-      <c r="D197" s="2" t="s">
-        <v>1944</v>
-      </c>
-    </row>
-    <row r="198" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B197" s="29" t="s">
+        <v>1945</v>
+      </c>
+      <c r="C197" s="65" t="s">
+        <v>1946</v>
+      </c>
+      <c r="D197" s="35" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B198" s="29" t="s">
-        <v>1945</v>
-      </c>
-      <c r="C198" s="65" t="s">
-        <v>1946</v>
-      </c>
-      <c r="D198" s="35" t="s">
-        <v>1947</v>
+      <c r="B198" s="2" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>1950</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29203,13 +29197,13 @@
         <v>526</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>1948</v>
+        <v>1951</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>1949</v>
+        <v>1952</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>1950</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29217,13 +29211,13 @@
         <v>526</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>1951</v>
+        <v>1954</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>1952</v>
+        <v>1955</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>1953</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29231,13 +29225,13 @@
         <v>526</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>1954</v>
+        <v>1957</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>1955</v>
+        <v>1958</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>1956</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29245,41 +29239,41 @@
         <v>526</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>1957</v>
+        <v>1960</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>1958</v>
+        <v>1961</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>1959</v>
-      </c>
-    </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2" t="s">
         <v>526</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>1960</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>1961</v>
-      </c>
-      <c r="D203" s="2" t="s">
-        <v>1962</v>
+        <v>1963</v>
+      </c>
+      <c r="C203" s="65" t="s">
+        <v>1964</v>
+      </c>
+      <c r="D203" s="35" t="s">
+        <v>1965</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B204" s="2" t="s">
-        <v>1963</v>
+      <c r="B204" s="29" t="s">
+        <v>1966</v>
       </c>
       <c r="C204" s="65" t="s">
-        <v>1964</v>
+        <v>1967</v>
       </c>
       <c r="D204" s="35" t="s">
-        <v>1965</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29287,13 +29281,13 @@
         <v>526</v>
       </c>
       <c r="B205" s="29" t="s">
-        <v>1966</v>
+        <v>1969</v>
       </c>
       <c r="C205" s="65" t="s">
-        <v>1967</v>
+        <v>1970</v>
       </c>
       <c r="D205" s="35" t="s">
-        <v>1968</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29301,13 +29295,13 @@
         <v>526</v>
       </c>
       <c r="B206" s="29" t="s">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="C206" s="65" t="s">
-        <v>1970</v>
+        <v>1973</v>
       </c>
       <c r="D206" s="35" t="s">
-        <v>1971</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29315,13 +29309,13 @@
         <v>526</v>
       </c>
       <c r="B207" s="29" t="s">
-        <v>1972</v>
+        <v>1975</v>
       </c>
       <c r="C207" s="65" t="s">
-        <v>1973</v>
+        <v>1976</v>
       </c>
       <c r="D207" s="35" t="s">
-        <v>1974</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29329,13 +29323,13 @@
         <v>526</v>
       </c>
       <c r="B208" s="29" t="s">
-        <v>1975</v>
+        <v>1978</v>
       </c>
       <c r="C208" s="65" t="s">
-        <v>1976</v>
+        <v>1979</v>
       </c>
       <c r="D208" s="35" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29343,13 +29337,13 @@
         <v>526</v>
       </c>
       <c r="B209" s="29" t="s">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="C209" s="65" t="s">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="D209" s="35" t="s">
-        <v>1980</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29357,13 +29351,13 @@
         <v>526</v>
       </c>
       <c r="B210" s="29" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="C210" s="65" t="s">
-        <v>1976</v>
+        <v>1979</v>
       </c>
       <c r="D210" s="35" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29371,13 +29365,13 @@
         <v>526</v>
       </c>
       <c r="B211" s="29" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="C211" s="65" t="s">
-        <v>1979</v>
+        <v>1946</v>
       </c>
       <c r="D211" s="35" t="s">
-        <v>1980</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29385,13 +29379,13 @@
         <v>526</v>
       </c>
       <c r="B212" s="29" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="C212" s="65" t="s">
-        <v>1946</v>
+        <v>1985</v>
       </c>
       <c r="D212" s="35" t="s">
-        <v>1947</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29399,13 +29393,13 @@
         <v>526</v>
       </c>
       <c r="B213" s="29" t="s">
-        <v>1984</v>
+        <v>1987</v>
       </c>
       <c r="C213" s="65" t="s">
-        <v>1985</v>
+        <v>1988</v>
       </c>
       <c r="D213" s="35" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29413,179 +29407,179 @@
         <v>526</v>
       </c>
       <c r="B214" s="29" t="s">
-        <v>1987</v>
+        <v>1990</v>
       </c>
       <c r="C214" s="65" t="s">
-        <v>1988</v>
+        <v>1991</v>
       </c>
       <c r="D214" s="35" t="s">
-        <v>1989</v>
-      </c>
-    </row>
-    <row r="215" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B215" s="29" t="s">
-        <v>1990</v>
-      </c>
-      <c r="C215" s="65" t="s">
-        <v>1991</v>
+      <c r="B215" s="10" t="s">
+        <v>1993</v>
+      </c>
+      <c r="C215" s="10" t="s">
+        <v>1994</v>
       </c>
       <c r="D215" s="35" t="s">
-        <v>1992</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="B216" s="10" t="s">
-        <v>1993</v>
+      <c r="A216" s="21" t="s">
+        <v>729</v>
+      </c>
+      <c r="B216" s="11" t="s">
+        <v>1996</v>
       </c>
       <c r="C216" s="10" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D216" s="35" t="s">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="217" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="21" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D216" s="95" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="B217" s="11" t="s">
-        <v>1996</v>
-      </c>
-      <c r="C217" s="10" t="s">
-        <v>1997</v>
-      </c>
-      <c r="D217" s="94" t="s">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="218" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B217" s="2" t="s">
+        <v>1999</v>
+      </c>
+      <c r="C217" s="21" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D217" s="28" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2" t="s">
         <v>729</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>1999</v>
-      </c>
-      <c r="C218" s="21" t="s">
-        <v>1336</v>
+        <v>2000</v>
+      </c>
+      <c r="C218" s="65" t="s">
+        <v>2001</v>
       </c>
       <c r="D218" s="28" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="219" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="268.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="B219" s="2" t="s">
-        <v>2000</v>
-      </c>
-      <c r="C219" s="65" t="s">
-        <v>2001</v>
-      </c>
-      <c r="D219" s="28" t="s">
-        <v>2002</v>
-      </c>
-    </row>
-    <row r="220" customFormat="false" ht="268.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B219" s="22" t="s">
+        <v>2003</v>
+      </c>
+      <c r="C219" s="11" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D219" s="11" t="s">
+        <v>2005</v>
+      </c>
+      <c r="E219" s="11" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F219" s="11" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="223.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="s">
         <v>729</v>
       </c>
       <c r="B220" s="22" t="s">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="C220" s="11" t="s">
-        <v>2004</v>
+        <v>2009</v>
       </c>
       <c r="D220" s="11" t="s">
-        <v>2005</v>
+        <v>2010</v>
       </c>
       <c r="E220" s="11" t="s">
-        <v>2006</v>
+        <v>2011</v>
       </c>
       <c r="F220" s="11" t="s">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="221" customFormat="false" ht="223.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="B221" s="22" t="s">
-        <v>2008</v>
-      </c>
-      <c r="C221" s="11" t="s">
-        <v>2009</v>
-      </c>
-      <c r="D221" s="11" t="s">
-        <v>2010</v>
-      </c>
-      <c r="E221" s="11" t="s">
-        <v>2011</v>
-      </c>
-      <c r="F221" s="11" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="222" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>816</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C221" s="21" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D221" s="28" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2" t="s">
         <v>816</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C222" s="21" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C222" s="65" t="s">
+        <v>2015</v>
+      </c>
+      <c r="D222" s="10" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>2017</v>
+      </c>
+      <c r="C223" s="21" t="s">
         <v>1336</v>
       </c>
-      <c r="D222" s="28" t="s">
+      <c r="D223" s="28" t="s">
         <v>1337</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>2014</v>
-      </c>
-      <c r="C223" s="65" t="s">
-        <v>2015</v>
-      </c>
-      <c r="D223" s="10" t="s">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="224" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="75.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2" t="s">
         <v>1027</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>2017</v>
-      </c>
-      <c r="C224" s="21" t="s">
-        <v>1336</v>
+        <v>2018</v>
+      </c>
+      <c r="C224" s="65" t="s">
+        <v>2019</v>
       </c>
       <c r="D224" s="28" t="s">
-        <v>1337</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="75.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>2018</v>
-      </c>
-      <c r="C225" s="65" t="s">
-        <v>2019</v>
-      </c>
-      <c r="D225" s="28" t="s">
-        <v>2020</v>
+        <v>974</v>
+      </c>
+      <c r="B225" s="11" t="s">
+        <v>2021</v>
+      </c>
+      <c r="C225" s="11" t="s">
+        <v>2022</v>
+      </c>
+      <c r="D225" s="11" t="s">
+        <v>2023</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="75.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29593,29 +29587,16 @@
         <v>974</v>
       </c>
       <c r="B226" s="11" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="C226" s="11" t="s">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D226" s="11" t="s">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="227" customFormat="false" ht="75.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="2" t="s">
-        <v>974</v>
-      </c>
-      <c r="B227" s="11" t="s">
-        <v>2024</v>
-      </c>
-      <c r="C227" s="11" t="s">
-        <v>2025</v>
-      </c>
-      <c r="D227" s="11" t="s">
         <v>2026</v>
       </c>
     </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -29644,28 +29625,28 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="96" t="s">
         <v>2027</v>
       </c>
-      <c r="B1" s="95" t="s">
+      <c r="B1" s="96" t="s">
         <v>1134</v>
       </c>
-      <c r="C1" s="95" t="s">
+      <c r="C1" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="95" t="s">
+      <c r="D1" s="96" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="96" t="s">
+      <c r="E1" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="96" t="s">
+      <c r="F1" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="95" t="s">
+      <c r="G1" s="96" t="s">
         <v>2028</v>
       </c>
-      <c r="H1" s="95" t="s">
+      <c r="H1" s="96" t="s">
         <v>12</v>
       </c>
       <c r="I1" s="29" t="s">
@@ -29734,10 +29715,10 @@
         <v>212</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="E5" s="22"/>
       <c r="F5" s="22"/>
@@ -29917,7 +29898,7 @@
       <c r="I16" s="22"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="97" t="s">
+      <c r="A17" s="98" t="s">
         <v>2044</v>
       </c>
       <c r="B17" s="22" t="s">
@@ -29935,7 +29916,7 @@
       <c r="H17" s="22"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="97" t="s">
+      <c r="A18" s="98" t="s">
         <v>2044</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -29953,7 +29934,7 @@
       <c r="H18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="97" t="s">
+      <c r="A19" s="98" t="s">
         <v>2044</v>
       </c>
       <c r="B19" s="22"/>
@@ -29967,7 +29948,7 @@
       <c r="H19" s="22"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="98" t="s">
         <v>170</v>
       </c>
       <c r="B20" s="22" t="s">
@@ -29985,7 +29966,7 @@
       <c r="H20" s="22"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="97" t="s">
+      <c r="A21" s="98" t="s">
         <v>170</v>
       </c>
       <c r="B21" s="22" t="s">
@@ -30003,7 +29984,7 @@
       <c r="H21" s="22"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="97" t="s">
+      <c r="A22" s="98" t="s">
         <v>170</v>
       </c>
       <c r="B22" s="22" t="s">
@@ -30021,7 +30002,7 @@
       <c r="H22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="97" t="s">
+      <c r="A23" s="98" t="s">
         <v>170</v>
       </c>
       <c r="B23" s="22"/>
@@ -30151,7 +30132,7 @@
       <c r="F30" s="22"/>
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
-      <c r="I30" s="98" t="n">
+      <c r="I30" s="99" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -30173,7 +30154,7 @@
       <c r="F31" s="22"/>
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
-      <c r="I31" s="98" t="n">
+      <c r="I31" s="99" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -30195,7 +30176,7 @@
       <c r="F32" s="22"/>
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
-      <c r="I32" s="98" t="n">
+      <c r="I32" s="99" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -30217,7 +30198,7 @@
       <c r="F33" s="22"/>
       <c r="G33" s="22"/>
       <c r="H33" s="22"/>
-      <c r="I33" s="98" t="n">
+      <c r="I33" s="99" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -30239,7 +30220,7 @@
       <c r="F34" s="22"/>
       <c r="G34" s="22"/>
       <c r="H34" s="22"/>
-      <c r="I34" s="98" t="n">
+      <c r="I34" s="99" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -30797,7 +30778,7 @@
       <c r="I64" s="22"/>
     </row>
     <row r="65" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="97" t="s">
+      <c r="A65" s="98" t="s">
         <v>303</v>
       </c>
       <c r="B65" s="22" t="s">
@@ -30816,7 +30797,7 @@
       <c r="I65" s="29"/>
     </row>
     <row r="66" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="97" t="s">
+      <c r="A66" s="98" t="s">
         <v>303</v>
       </c>
       <c r="B66" s="22" t="s">
@@ -30835,7 +30816,7 @@
       <c r="I66" s="29"/>
     </row>
     <row r="67" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="97" t="s">
+      <c r="A67" s="98" t="s">
         <v>303</v>
       </c>
       <c r="B67" s="22" t="s">
@@ -30854,7 +30835,7 @@
       <c r="I67" s="29"/>
     </row>
     <row r="68" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="97" t="s">
+      <c r="A68" s="98" t="s">
         <v>303</v>
       </c>
       <c r="B68" s="22" t="s">
@@ -30873,7 +30854,7 @@
       <c r="I68" s="29"/>
     </row>
     <row r="69" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="97" t="s">
+      <c r="A69" s="98" t="s">
         <v>303</v>
       </c>
       <c r="B69" s="22" t="s">
@@ -30892,7 +30873,7 @@
       <c r="I69" s="29"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="97" t="s">
+      <c r="A70" s="98" t="s">
         <v>878</v>
       </c>
       <c r="B70" s="29" t="s">
@@ -30906,7 +30887,7 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="97" t="s">
+      <c r="A71" s="98" t="s">
         <v>878</v>
       </c>
       <c r="B71" s="29" t="s">
@@ -30920,7 +30901,7 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="97" t="s">
+      <c r="A72" s="98" t="s">
         <v>878</v>
       </c>
       <c r="B72" s="29" t="s">
@@ -30933,8 +30914,8 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="97" t="s">
+    <row r="73" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="98" t="s">
         <v>878</v>
       </c>
       <c r="B73" s="29" t="s">
@@ -30946,6 +30927,11 @@
       <c r="D73" s="29" t="s">
         <v>2165</v>
       </c>
+      <c r="E73" s="29"/>
+      <c r="F73" s="29"/>
+      <c r="G73" s="29"/>
+      <c r="H73" s="29"/>
+      <c r="I73" s="29"/>
     </row>
     <row r="74" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="29" t="s">
@@ -31213,7 +31199,7 @@
       <c r="H87" s="29"/>
       <c r="I87" s="29"/>
     </row>
-    <row r="88" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="29" t="s">
         <v>1055</v>
       </c>
@@ -31226,14 +31212,9 @@
       <c r="D88" s="29" t="s">
         <v>2206</v>
       </c>
-      <c r="E88" s="29"/>
-      <c r="F88" s="29"/>
-      <c r="G88" s="29"/>
-      <c r="H88" s="29"/>
-      <c r="I88" s="29"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="99" t="s">
+      <c r="A89" s="100" t="s">
         <v>81</v>
       </c>
       <c r="B89" s="60" t="s">
@@ -31247,7 +31228,7 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="99" t="s">
+      <c r="A90" s="100" t="s">
         <v>81</v>
       </c>
       <c r="B90" s="29" t="s">
@@ -31261,21 +31242,21 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="99" t="s">
+      <c r="A91" s="100" t="s">
         <v>81</v>
       </c>
       <c r="B91" s="29" t="s">
         <v>212</v>
       </c>
       <c r="C91" s="29" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="D91" s="29" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="99" t="s">
+      <c r="A92" s="100" t="s">
         <v>81</v>
       </c>
       <c r="B92" s="29" t="s">
@@ -31291,7 +31272,7 @@
       <c r="F92" s="60"/>
     </row>
     <row r="93" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="100" t="s">
+      <c r="A93" s="101" t="s">
         <v>403</v>
       </c>
       <c r="B93" s="22" t="s">
@@ -31312,7 +31293,7 @@
       <c r="I93" s="22"/>
     </row>
     <row r="94" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="100" t="s">
+      <c r="A94" s="101" t="s">
         <v>403</v>
       </c>
       <c r="B94" s="22" t="s">
@@ -31333,7 +31314,7 @@
       <c r="I94" s="22"/>
     </row>
     <row r="95" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="100" t="s">
+      <c r="A95" s="101" t="s">
         <v>403</v>
       </c>
       <c r="B95" s="22" t="s">
@@ -31352,7 +31333,7 @@
       <c r="I95" s="22"/>
     </row>
     <row r="96" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="100" t="s">
+      <c r="A96" s="101" t="s">
         <v>403</v>
       </c>
       <c r="B96" s="22" t="s">
@@ -31371,7 +31352,7 @@
       <c r="I96" s="22"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="100" t="s">
+      <c r="A97" s="101" t="s">
         <v>403</v>
       </c>
       <c r="B97" s="22" t="s">
@@ -31390,7 +31371,7 @@
       <c r="I97" s="22"/>
     </row>
     <row r="98" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="100" t="s">
+      <c r="A98" s="101" t="s">
         <v>403</v>
       </c>
       <c r="B98" s="22" t="s">
@@ -31411,7 +31392,7 @@
       <c r="I98" s="22"/>
     </row>
     <row r="99" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="100" t="s">
+      <c r="A99" s="101" t="s">
         <v>403</v>
       </c>
       <c r="B99" s="22" t="s">
@@ -31430,7 +31411,7 @@
       <c r="I99" s="22"/>
     </row>
     <row r="100" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="100" t="s">
+      <c r="A100" s="101" t="s">
         <v>403</v>
       </c>
       <c r="B100" s="22" t="s">
@@ -31451,17 +31432,17 @@
       <c r="I100" s="22"/>
     </row>
     <row r="101" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="100" t="s">
+      <c r="A101" s="101" t="s">
         <v>403</v>
       </c>
       <c r="B101" s="22" t="s">
         <v>212</v>
       </c>
       <c r="C101" s="28" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="D101" s="65" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="E101" s="28"/>
       <c r="F101" s="28"/>
@@ -31470,7 +31451,7 @@
       <c r="I101" s="22"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="101" t="s">
+      <c r="A102" s="102" t="s">
         <v>2235</v>
       </c>
       <c r="B102" s="29" t="s">
@@ -31490,7 +31471,7 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="101" t="s">
+      <c r="A103" s="102" t="s">
         <v>2235</v>
       </c>
       <c r="B103" s="29" t="s">
@@ -31510,7 +31491,7 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="101" t="s">
+      <c r="A104" s="102" t="s">
         <v>2235</v>
       </c>
       <c r="B104" s="29" t="s">
@@ -31524,7 +31505,7 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="101" t="s">
+      <c r="A105" s="102" t="s">
         <v>744</v>
       </c>
       <c r="B105" s="60" t="s">
@@ -31538,7 +31519,7 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="101" t="s">
+      <c r="A106" s="102" t="s">
         <v>744</v>
       </c>
       <c r="B106" s="60" t="s">
@@ -31552,7 +31533,7 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="101" t="s">
+      <c r="A107" s="102" t="s">
         <v>744</v>
       </c>
       <c r="B107" s="60" t="s">
@@ -31566,7 +31547,7 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="101" t="s">
+      <c r="A108" s="102" t="s">
         <v>744</v>
       </c>
       <c r="B108" s="60" t="s">
@@ -31580,7 +31561,7 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="101" t="s">
+      <c r="A109" s="102" t="s">
         <v>744</v>
       </c>
       <c r="G109" s="22" t="s">
@@ -31588,7 +31569,7 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="101" t="s">
+      <c r="A110" s="102" t="s">
         <v>744</v>
       </c>
       <c r="G110" s="22" t="s">
@@ -31596,7 +31577,7 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="101" t="s">
+      <c r="A111" s="102" t="s">
         <v>812</v>
       </c>
       <c r="B111" s="60" t="s">
@@ -31610,7 +31591,7 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="101" t="s">
+      <c r="A112" s="102" t="s">
         <v>812</v>
       </c>
       <c r="B112" s="60" t="s">
@@ -31624,7 +31605,7 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="101" t="s">
+      <c r="A113" s="102" t="s">
         <v>812</v>
       </c>
       <c r="B113" s="60" t="s">
@@ -31638,7 +31619,7 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="101" t="s">
+      <c r="A114" s="102" t="s">
         <v>812</v>
       </c>
       <c r="B114" s="22" t="s">
@@ -31652,7 +31633,7 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="101" t="s">
+      <c r="A115" s="102" t="s">
         <v>812</v>
       </c>
       <c r="G115" s="22" t="s">
@@ -31660,7 +31641,7 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="101" t="s">
+      <c r="A116" s="102" t="s">
         <v>812</v>
       </c>
       <c r="G116" s="22" t="s">
@@ -31668,7 +31649,7 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="102" t="s">
+      <c r="A117" s="103" t="s">
         <v>322</v>
       </c>
       <c r="B117" s="60" t="s">
@@ -31682,7 +31663,7 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="102" t="s">
+      <c r="A118" s="103" t="s">
         <v>322</v>
       </c>
       <c r="B118" s="29" t="s">
@@ -31696,7 +31677,7 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="102" t="s">
+      <c r="A119" s="103" t="s">
         <v>322</v>
       </c>
       <c r="B119" s="60" t="s">
@@ -31710,7 +31691,7 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="102" t="s">
+      <c r="A120" s="103" t="s">
         <v>322</v>
       </c>
       <c r="B120" s="60" t="s">
@@ -31724,7 +31705,7 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="102" t="s">
+      <c r="A121" s="103" t="s">
         <v>322</v>
       </c>
       <c r="B121" s="60" t="s">
@@ -31738,7 +31719,7 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="102" t="s">
+      <c r="A122" s="103" t="s">
         <v>322</v>
       </c>
       <c r="B122" s="60" t="s">
@@ -31752,7 +31733,7 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="102" t="s">
+      <c r="A123" s="103" t="s">
         <v>322</v>
       </c>
       <c r="G123" s="22" t="s">
@@ -31760,7 +31741,7 @@
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="97" t="s">
+      <c r="A124" s="98" t="s">
         <v>2277</v>
       </c>
       <c r="B124" s="22" t="s">
@@ -31778,10 +31759,10 @@
       <c r="F124" s="22" t="s">
         <v>1806</v>
       </c>
-      <c r="G124" s="97"/>
+      <c r="G124" s="98"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="97" t="s">
+      <c r="A125" s="98" t="s">
         <v>2277</v>
       </c>
       <c r="B125" s="22" t="s">
@@ -31801,7 +31782,7 @@
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="97" t="s">
+      <c r="A126" s="98" t="s">
         <v>2277</v>
       </c>
       <c r="B126" s="22" t="s">
@@ -31821,7 +31802,7 @@
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="97" t="s">
+      <c r="A127" s="98" t="s">
         <v>2277</v>
       </c>
       <c r="B127" s="22" t="s">
@@ -31841,7 +31822,7 @@
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="97" t="s">
+      <c r="A128" s="98" t="s">
         <v>2277</v>
       </c>
       <c r="B128" s="22" t="s">
@@ -31887,7 +31868,7 @@
       <c r="D130" s="35" t="s">
         <v>2279</v>
       </c>
-      <c r="H130" s="103" t="s">
+      <c r="H130" s="104" t="s">
         <v>1210</v>
       </c>
     </row>
@@ -31904,7 +31885,7 @@
       <c r="D131" s="35" t="s">
         <v>2282</v>
       </c>
-      <c r="H131" s="104" t="s">
+      <c r="H131" s="105" t="s">
         <v>2283</v>
       </c>
     </row>
@@ -33105,7 +33086,7 @@
       <c r="E203" s="22"/>
       <c r="F203" s="22"/>
       <c r="G203" s="22"/>
-      <c r="H203" s="105"/>
+      <c r="H203" s="106"/>
       <c r="I203" s="22"/>
     </row>
     <row r="204" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33200,7 +33181,7 @@
       <c r="E208" s="22"/>
       <c r="F208" s="22"/>
       <c r="G208" s="22"/>
-      <c r="H208" s="105" t="s">
+      <c r="H208" s="106" t="s">
         <v>1198</v>
       </c>
       <c r="I208" s="22"/>
@@ -33499,7 +33480,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="29" t="s">
         <v>860</v>
       </c>
@@ -33512,6 +33493,11 @@
       <c r="D229" s="29" t="s">
         <v>2426</v>
       </c>
+      <c r="E229" s="29"/>
+      <c r="F229" s="29"/>
+      <c r="G229" s="29"/>
+      <c r="H229" s="29"/>
+      <c r="I229" s="29"/>
     </row>
     <row r="230" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="29" t="s">
@@ -33827,7 +33813,7 @@
       <c r="H245" s="29"/>
       <c r="I245" s="29"/>
     </row>
-    <row r="246" s="2" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="11" t="s">
         <v>1064</v>
       </c>
@@ -33840,21 +33826,21 @@
       <c r="D246" s="28" t="s">
         <v>2498</v>
       </c>
-      <c r="E246" s="29"/>
-      <c r="F246" s="29"/>
-      <c r="G246" s="29"/>
-      <c r="H246" s="29"/>
-      <c r="I246" s="29"/>
-    </row>
-    <row r="247" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="247" s="2" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="11" t="s">
         <v>1064</v>
       </c>
+      <c r="B247" s="29"/>
       <c r="C247" s="65"/>
       <c r="D247" s="65"/>
+      <c r="E247" s="29"/>
+      <c r="F247" s="29"/>
       <c r="G247" s="22" t="s">
         <v>2036</v>
       </c>
+      <c r="H247" s="29"/>
+      <c r="I247" s="29"/>
     </row>
     <row r="248" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2" t="s">
@@ -34116,7 +34102,7 @@
       <c r="H262" s="29"/>
       <c r="I262" s="29"/>
     </row>
-    <row r="263" s="2" customFormat="true" ht="75.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" customFormat="false" ht="75.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="29" t="s">
         <v>986</v>
       </c>
@@ -34129,11 +34115,6 @@
       <c r="D263" s="28" t="s">
         <v>2534</v>
       </c>
-      <c r="E263" s="29"/>
-      <c r="F263" s="29"/>
-      <c r="G263" s="29"/>
-      <c r="H263" s="29"/>
-      <c r="I263" s="29"/>
     </row>
     <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4628" uniqueCount="2538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4631" uniqueCount="2541">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -2642,28 +2642,28 @@
     <t xml:space="preserve">Other mode of transportation used for the trip before arrival?</t>
   </si>
   <si>
-    <t xml:space="preserve">tripCommun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{nickname}} a-t-{{gender: il/elle/iel/il(-elle)}} réalisé ce déplacement avec une autre personne du ménage?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Did {{nickname}} make this trip with another member of the household?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avez-vous réalisé ce déplacement avec une autre personne du ménage?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Did you make this trip with another member of the household?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tripCommunCustomConditional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tripCommunCustomChoices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIXME tripCommun : tripCommunCustomConditonal · Issue #38 · chairemobilite/od_mtl</t>
+    <t xml:space="preserve">personTripsCommonTripWith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commonTripWith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce déplacement (entre {{origin}} et {{destination}}) a-t-il été effectué, en tout ou en partie, **avec un autre membre du ménage**?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was this trip (between {{origin}} and {{destination}}) made, in part or entirely, **with another household member**?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">customLabels={{commonTripCustomLabel}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commonTripCustomConditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commonTripCustomValidation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commonTripCustomChoices</t>
   </si>
   <si>
     <t xml:space="preserve">buttonSaveTrip</t>
@@ -6850,6 +6850,15 @@
   </si>
   <si>
     <t xml:space="preserve">None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">errors.tripCommonNoOnlySelection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vous ne pouvez sélectionner des membres du ménage et l'option "Non" en même temps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You cannot select other household members and the option "No" at the same time</t>
   </si>
   <si>
     <t xml:space="preserve">workPlaceBeforeLeaveTypeChoicesOnLocation</t>
@@ -9551,7 +9560,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="106">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9918,10 +9927,6 @@
     </xf>
     <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -16458,7 +16463,7 @@
       <c r="XFC109" s="2"/>
       <c r="XFD109" s="2"/>
     </row>
-    <row r="110" s="17" customFormat="true" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" s="17" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="11" t="s">
         <v>596</v>
       </c>
@@ -17912,7 +17917,7 @@
       <c r="V128" s="18"/>
       <c r="W128" s="18"/>
     </row>
-    <row r="129" s="17" customFormat="true" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" s="17" customFormat="true" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="11" t="s">
         <v>705</v>
       </c>
@@ -17930,28 +17935,28 @@
         <v>533</v>
       </c>
       <c r="F129" s="11" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G129" s="11" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H129" s="11" t="s">
-        <v>707</v>
-      </c>
-      <c r="I129" s="11" t="s">
         <v>708</v>
       </c>
-      <c r="J129" s="11" t="s">
+      <c r="I129" s="11"/>
+      <c r="J129" s="11"/>
+      <c r="K129" s="11" t="s">
         <v>709</v>
       </c>
-      <c r="K129" s="11"/>
       <c r="L129" s="11"/>
       <c r="M129" s="10" t="s">
         <v>710</v>
       </c>
-      <c r="N129" s="11"/>
+      <c r="N129" s="11" t="s">
+        <v>711</v>
+      </c>
       <c r="O129" s="11" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="P129" s="11"/>
       <c r="Q129" s="2"/>
@@ -17964,9 +17969,7 @@
       <c r="U129" s="11"/>
       <c r="V129" s="11"/>
       <c r="W129" s="11"/>
-      <c r="X129" s="38" t="s">
-        <v>712</v>
-      </c>
+      <c r="X129" s="38"/>
       <c r="XDQ129" s="2"/>
       <c r="XDR129" s="2"/>
       <c r="XDS129" s="2"/>
@@ -23024,7 +23027,7 @@
     <hyperlink ref="X99" r:id="rId7" display="segmentSameModeAsPreviousTrip : sameModeAsPreviousTripCustomConditional · Issue #15 · chairemobilite/od_mtl&#10;segmentSameModeAsPreviousTrip : implication · Issue #43 · chairemobilite/od_mtl"/>
     <hyperlink ref="X100" r:id="rId8" display="FIXME Valider segmentMode · Issue #16 · chairemobilite/od_mtl"/>
     <hyperlink ref="X104" r:id="rId9" display="FIXME Valider traductions pour segmentDriver : driverCustomChoices · Issue #53 · chairemobilite/od_mtl"/>
-    <hyperlink ref="X110" r:id="rId10" display="FIXME Validations: segmentTrainStationEnd : trainValidation · Issue #20 · chairemobilite/od_mtl"/>
+    <hyperlink ref="X110" r:id="rId10" display="Custom à cause de l'utilisation du nouveau widget `selectFeature` pour le tri par lieu géographique&#10;FIXME Validations: segmentTrainStationEnd : trainValidation · Issue #20 · chairemobilite/od_mtl"/>
     <hyperlink ref="X113" r:id="rId11" display="FIXME segmentPlaneStationStart : planeStationStartCustomConditional · Issue #26 · chairemobilite/od_mtl"/>
     <hyperlink ref="X114" r:id="rId12" display="FIXME segmentIntercityRailStationStart : intercityRailStationStartCustomConditional · Issue #27 · chairemobilite/od_mtl"/>
     <hyperlink ref="X115" r:id="rId13" display="FIXME segmentIntercityBusStationStart : intercityBusStationStartCustomConditional · Issue #28 · chairemobilite/od_mtl"/>
@@ -23037,10 +23040,9 @@
     <hyperlink ref="X124" r:id="rId20" display="Needs custom label because of interpolations and custom conditional because of distance calculations&#10;&#10;FIXME segmentIntercityEgressMode : intercityEgressCustomConditional · Issue #34 · chairemobilite/od_mtl"/>
     <hyperlink ref="X125" r:id="rId21" display="FIXME tripJunctionPrivateBus : choix · Issue #36 · chairemobilite/od_mtl"/>
     <hyperlink ref="X127" r:id="rId22" display="Custom label because of placeholders&#10;&#10;FIXME tripJunctionPaidParking : junctionPaidParkingCustomConditional · Issue #37 · chairemobilite/od_mtl"/>
-    <hyperlink ref="X129" r:id="rId23" display="FIXME tripCommun : tripCommunCustomConditonal · Issue #38 · chairemobilite/od_mtl"/>
-    <hyperlink ref="Z206" r:id="rId24" display="householdPluginHybridCarNumber : pluginHybridCarNumberCustomChoices · Issue #54 · chairemobilite/od_mtl"/>
-    <hyperlink ref="Z207" r:id="rId25" display="householdElectricCarNumber : electricCarNumberCustomChoices · Issue #55 · chairemobilite/od_mtl"/>
-    <hyperlink ref="G224" r:id="rId26" display=" &lt;div style=&quot;text-align:center;&quot;&gt;&lt;img src=&quot;https://www.artm.quebec/wp-content/uploads/2018/05/Carte_ARTM.jpg&quot; alt=&quot;Territoire ARTM&quot; style=&quot;max-width:1000px;width:100%;height:auto;&quot; /&gt;&lt;/div&gt;"/>
+    <hyperlink ref="Z206" r:id="rId23" display="householdPluginHybridCarNumber : pluginHybridCarNumberCustomChoices · Issue #54 · chairemobilite/od_mtl"/>
+    <hyperlink ref="Z207" r:id="rId24" display="householdElectricCarNumber : electricCarNumberCustomChoices · Issue #55 · chairemobilite/od_mtl"/>
+    <hyperlink ref="G224" r:id="rId25" display=" &lt;div style=&quot;text-align:center;&quot;&gt;&lt;img src=&quot;https://www.artm.quebec/wp-content/uploads/2018/05/Carte_ARTM.jpg&quot; alt=&quot;Territoire ARTM&quot; style=&quot;max-width:1000px;width:100%;height:auto;&quot; /&gt;&lt;/div&gt;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -23049,8 +23051,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId27"/>
-  <legacyDrawing r:id="rId28"/>
+  <drawing r:id="rId26"/>
+  <legacyDrawing r:id="rId27"/>
 </worksheet>
 </file>
 
@@ -26247,7 +26249,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F228"/>
+  <dimension ref="A1:F229"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="16.72"/>
@@ -28723,7 +28725,7 @@
       <c r="A157" s="18" t="s">
         <v>526</v>
       </c>
-      <c r="B157" s="92" t="s">
+      <c r="B157" s="10" t="s">
         <v>1801</v>
       </c>
       <c r="C157" s="11" t="s">
@@ -28735,143 +28737,143 @@
       <c r="E157" s="10"/>
       <c r="F157" s="10"/>
     </row>
-    <row r="158" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B158" s="1" t="s">
+    <row r="158" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="18" t="s">
+        <v>526</v>
+      </c>
+      <c r="B158" s="10" t="s">
         <v>1804</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="C158" s="11" t="s">
         <v>1805</v>
       </c>
-      <c r="D158" s="1" t="s">
+      <c r="D158" s="11" t="s">
         <v>1806</v>
       </c>
-      <c r="E158" s="1" t="s">
-        <v>1807</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>1808</v>
-      </c>
-    </row>
-    <row r="159" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E158" s="10"/>
+      <c r="F158" s="10"/>
+    </row>
+    <row r="159" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
         <v>152</v>
       </c>
       <c r="B159" s="1" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>1809</v>
       </c>
-      <c r="C159" s="1" t="s">
+      <c r="E159" s="1" t="s">
         <v>1810</v>
       </c>
-      <c r="D159" s="1" t="s">
+      <c r="F159" s="1" t="s">
         <v>1811</v>
       </c>
-      <c r="E159" s="1" t="s">
-        <v>1812</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>1813</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="160" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B160" s="93" t="s">
+      <c r="B160" s="1" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>1813</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>1814</v>
       </c>
-      <c r="C160" s="1" t="s">
+      <c r="E160" s="1" t="s">
         <v>1815</v>
       </c>
-      <c r="D160" s="1" t="s">
+      <c r="F160" s="1" t="s">
         <v>1816</v>
       </c>
-      <c r="E160" s="1" t="s">
-        <v>1817</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>1818</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="161" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B161" s="93" t="s">
+      <c r="B161" s="92" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>1819</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="E161" s="1" t="s">
         <v>1820</v>
       </c>
-      <c r="D161" s="1" t="s">
+      <c r="F161" s="1" t="s">
         <v>1821</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>1822</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>1823</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B162" s="93" t="s">
+      <c r="B162" s="92" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>1824</v>
       </c>
-      <c r="C162" s="1" t="s">
+      <c r="E162" s="1" t="s">
         <v>1825</v>
       </c>
-      <c r="D162" s="1" t="s">
+      <c r="F162" s="1" t="s">
         <v>1826</v>
       </c>
-      <c r="E162" s="1" t="s">
+    </row>
+    <row r="163" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B163" s="92" t="s">
         <v>1827</v>
       </c>
-      <c r="F162" s="1" t="s">
+      <c r="C163" s="1" t="s">
         <v>1828</v>
       </c>
-    </row>
-    <row r="163" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="B163" s="94" t="s">
+      <c r="D163" s="1" t="s">
         <v>1829</v>
       </c>
-      <c r="C163" s="65" t="s">
+      <c r="E163" s="1" t="s">
         <v>1830</v>
       </c>
-      <c r="D163" s="28" t="s">
+      <c r="F163" s="1" t="s">
         <v>1831</v>
       </c>
-      <c r="E163" s="10"/>
-      <c r="F163" s="10"/>
     </row>
     <row r="164" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B164" s="10" t="s">
+      <c r="B164" s="93" t="s">
         <v>1832</v>
       </c>
-      <c r="C164" s="10" t="s">
+      <c r="C164" s="65" t="s">
         <v>1833</v>
       </c>
-      <c r="D164" s="10" t="s">
+      <c r="D164" s="28" t="s">
         <v>1834</v>
       </c>
       <c r="E164" s="10"/>
       <c r="F164" s="10"/>
     </row>
-    <row r="165" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B165" s="2" t="s">
+      <c r="B165" s="10" t="s">
         <v>1835</v>
       </c>
       <c r="C165" s="10" t="s">
@@ -28880,31 +28882,27 @@
       <c r="D165" s="10" t="s">
         <v>1837</v>
       </c>
-      <c r="E165" s="10" t="s">
-        <v>1838</v>
-      </c>
-      <c r="F165" s="10" t="s">
-        <v>1839</v>
-      </c>
+      <c r="E165" s="10"/>
+      <c r="F165" s="10"/>
     </row>
     <row r="166" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2" t="s">
         <v>342</v>
       </c>
       <c r="B166" s="2" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C166" s="10" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D166" s="10" t="s">
         <v>1840</v>
       </c>
-      <c r="C166" s="10" t="s">
+      <c r="E166" s="10" t="s">
         <v>1841</v>
       </c>
-      <c r="D166" s="10" t="s">
+      <c r="F166" s="10" t="s">
         <v>1842</v>
-      </c>
-      <c r="E166" s="10" t="s">
-        <v>1843</v>
-      </c>
-      <c r="F166" s="10" t="s">
-        <v>1844</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28912,59 +28910,59 @@
         <v>342</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C167" s="10" t="s">
+        <v>1844</v>
+      </c>
+      <c r="D167" s="10" t="s">
         <v>1845</v>
       </c>
-      <c r="C167" s="28" t="s">
+      <c r="E167" s="10" t="s">
         <v>1846</v>
       </c>
-      <c r="D167" s="28" t="s">
+      <c r="F167" s="10" t="s">
         <v>1847</v>
       </c>
-      <c r="E167" s="28" t="s">
-        <v>1848</v>
-      </c>
-      <c r="F167" s="28" t="s">
-        <v>1849</v>
-      </c>
-    </row>
-    <row r="168" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="168" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2" t="s">
         <v>342</v>
       </c>
       <c r="B168" s="2" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C168" s="28" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D168" s="28" t="s">
         <v>1850</v>
       </c>
-      <c r="C168" s="28" t="s">
+      <c r="E168" s="28" t="s">
         <v>1851</v>
       </c>
-      <c r="D168" s="28" t="s">
+      <c r="F168" s="28" t="s">
         <v>1852</v>
       </c>
-      <c r="E168" s="28" t="s">
-        <v>1853</v>
-      </c>
-      <c r="F168" s="28" t="s">
-        <v>1854</v>
-      </c>
-    </row>
-    <row r="169" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="169" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2" t="s">
         <v>342</v>
       </c>
       <c r="B169" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C169" s="28" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D169" s="28" t="s">
         <v>1855</v>
       </c>
-      <c r="C169" s="28" t="s">
+      <c r="E169" s="28" t="s">
         <v>1856</v>
       </c>
-      <c r="D169" s="28" t="s">
+      <c r="F169" s="28" t="s">
         <v>1857</v>
-      </c>
-      <c r="E169" s="28" t="s">
-        <v>1858</v>
-      </c>
-      <c r="F169" s="28" t="s">
-        <v>1859</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28972,39 +28970,39 @@
         <v>342</v>
       </c>
       <c r="B170" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C170" s="28" t="s">
+        <v>1859</v>
+      </c>
+      <c r="D170" s="28" t="s">
         <v>1860</v>
       </c>
-      <c r="C170" s="28" t="s">
+      <c r="E170" s="28" t="s">
         <v>1861</v>
       </c>
-      <c r="D170" s="65" t="s">
+      <c r="F170" s="28" t="s">
         <v>1862</v>
       </c>
-      <c r="E170" s="28" t="s">
-        <v>1863</v>
-      </c>
-      <c r="F170" s="65" t="s">
-        <v>1864</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="171" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B171" s="10" t="s">
+      <c r="B171" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C171" s="28" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D171" s="65" t="s">
         <v>1865</v>
       </c>
-      <c r="C171" s="28" t="s">
+      <c r="E171" s="28" t="s">
         <v>1866</v>
       </c>
-      <c r="D171" s="65" t="s">
+      <c r="F171" s="65" t="s">
         <v>1867</v>
-      </c>
-      <c r="E171" s="28" t="s">
-        <v>1868</v>
-      </c>
-      <c r="F171" s="65" t="s">
-        <v>1869</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29012,18 +29010,22 @@
         <v>342</v>
       </c>
       <c r="B172" s="10" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C172" s="28" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D172" s="65" t="s">
         <v>1870</v>
       </c>
-      <c r="C172" s="28" t="s">
+      <c r="E172" s="28" t="s">
         <v>1871</v>
       </c>
-      <c r="D172" s="65" t="s">
+      <c r="F172" s="65" t="s">
         <v>1872</v>
       </c>
-      <c r="E172" s="28"/>
-      <c r="F172" s="65"/>
-    </row>
-    <row r="173" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="173" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2" t="s">
         <v>342</v>
       </c>
@@ -29033,29 +29035,31 @@
       <c r="C173" s="28" t="s">
         <v>1874</v>
       </c>
-      <c r="D173" s="28" t="s">
+      <c r="D173" s="65" t="s">
         <v>1875</v>
       </c>
       <c r="E173" s="28"/>
       <c r="F173" s="65"/>
     </row>
-    <row r="174" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B174" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B174" s="10" t="s">
         <v>1876</v>
       </c>
-      <c r="C174" s="10" t="s">
+      <c r="C174" s="28" t="s">
         <v>1877</v>
       </c>
-      <c r="D174" s="10" t="s">
+      <c r="D174" s="28" t="s">
         <v>1878</v>
       </c>
+      <c r="E174" s="28"/>
+      <c r="F174" s="65"/>
     </row>
     <row r="175" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2" t="s">
-        <v>526</v>
+        <v>1026</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>1879</v>
@@ -29137,17 +29141,17 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="s">
         <v>526</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>1897</v>
       </c>
-      <c r="C181" s="2" t="s">
+      <c r="C181" s="10" t="s">
         <v>1898</v>
       </c>
-      <c r="D181" s="2" t="s">
+      <c r="D181" s="10" t="s">
         <v>1899</v>
       </c>
     </row>
@@ -29162,7 +29166,7 @@
         <v>1901</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29170,10 +29174,10 @@
         <v>526</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>1904</v>
@@ -29375,31 +29379,31 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B198" s="29" t="s">
+      <c r="B198" s="2" t="s">
         <v>1947</v>
       </c>
-      <c r="C198" s="65" t="s">
+      <c r="C198" s="2" t="s">
         <v>1948</v>
       </c>
-      <c r="D198" s="35" t="s">
+      <c r="D198" s="2" t="s">
         <v>1949</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B199" s="2" t="s">
+      <c r="B199" s="29" t="s">
         <v>1950</v>
       </c>
-      <c r="C199" s="2" t="s">
+      <c r="C199" s="65" t="s">
         <v>1951</v>
       </c>
-      <c r="D199" s="2" t="s">
+      <c r="D199" s="35" t="s">
         <v>1952</v>
       </c>
     </row>
@@ -29459,17 +29463,17 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="s">
         <v>526</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>1965</v>
       </c>
-      <c r="C204" s="65" t="s">
+      <c r="C204" s="2" t="s">
         <v>1966</v>
       </c>
-      <c r="D204" s="35" t="s">
+      <c r="D204" s="2" t="s">
         <v>1967</v>
       </c>
     </row>
@@ -29477,7 +29481,7 @@
       <c r="A205" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B205" s="29" t="s">
+      <c r="B205" s="2" t="s">
         <v>1968</v>
       </c>
       <c r="C205" s="65" t="s">
@@ -29551,10 +29555,10 @@
         <v>1983</v>
       </c>
       <c r="C210" s="65" t="s">
-        <v>1978</v>
+        <v>1984</v>
       </c>
       <c r="D210" s="35" t="s">
-        <v>1979</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29562,7 +29566,7 @@
         <v>526</v>
       </c>
       <c r="B211" s="29" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="C211" s="65" t="s">
         <v>1981</v>
@@ -29576,13 +29580,13 @@
         <v>526</v>
       </c>
       <c r="B212" s="29" t="s">
+        <v>1987</v>
+      </c>
+      <c r="C212" s="65" t="s">
+        <v>1984</v>
+      </c>
+      <c r="D212" s="35" t="s">
         <v>1985</v>
-      </c>
-      <c r="C212" s="65" t="s">
-        <v>1948</v>
-      </c>
-      <c r="D212" s="35" t="s">
-        <v>1949</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29590,13 +29594,13 @@
         <v>526</v>
       </c>
       <c r="B213" s="29" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="C213" s="65" t="s">
-        <v>1987</v>
+        <v>1951</v>
       </c>
       <c r="D213" s="35" t="s">
-        <v>1988</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29627,14 +29631,14 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B216" s="10" t="s">
+      <c r="B216" s="29" t="s">
         <v>1995</v>
       </c>
-      <c r="C216" s="10" t="s">
+      <c r="C216" s="65" t="s">
         <v>1996</v>
       </c>
       <c r="D216" s="35" t="s">
@@ -29642,116 +29646,116 @@
       </c>
     </row>
     <row r="217" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="21" t="s">
-        <v>719</v>
-      </c>
-      <c r="B217" s="11" t="s">
+      <c r="A217" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B217" s="10" t="s">
         <v>1998</v>
       </c>
       <c r="C217" s="10" t="s">
         <v>1999</v>
       </c>
-      <c r="D217" s="95" t="s">
+      <c r="D217" s="35" t="s">
         <v>2000</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="2" t="s">
+    <row r="218" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="21" t="s">
         <v>719</v>
       </c>
-      <c r="B218" s="2" t="s">
+      <c r="B218" s="11" t="s">
         <v>2001</v>
       </c>
-      <c r="C218" s="21" t="s">
-        <v>1335</v>
-      </c>
-      <c r="D218" s="28" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="219" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C218" s="10" t="s">
+        <v>2002</v>
+      </c>
+      <c r="D218" s="94" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2" t="s">
         <v>719</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>2002</v>
-      </c>
-      <c r="C219" s="65" t="s">
-        <v>2003</v>
+        <v>2004</v>
+      </c>
+      <c r="C219" s="21" t="s">
+        <v>1335</v>
       </c>
       <c r="D219" s="28" t="s">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="220" customFormat="false" ht="268.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="B220" s="22" t="s">
+      <c r="B220" s="2" t="s">
         <v>2005</v>
       </c>
-      <c r="C220" s="11" t="s">
+      <c r="C220" s="65" t="s">
         <v>2006</v>
       </c>
-      <c r="D220" s="11" t="s">
+      <c r="D220" s="28" t="s">
         <v>2007</v>
       </c>
-      <c r="E220" s="11" t="s">
-        <v>2008</v>
-      </c>
-      <c r="F220" s="11" t="s">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="221" customFormat="false" ht="223.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="221" customFormat="false" ht="268.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2" t="s">
         <v>719</v>
       </c>
       <c r="B221" s="22" t="s">
+        <v>2008</v>
+      </c>
+      <c r="C221" s="11" t="s">
+        <v>2009</v>
+      </c>
+      <c r="D221" s="11" t="s">
         <v>2010</v>
       </c>
-      <c r="C221" s="11" t="s">
+      <c r="E221" s="11" t="s">
         <v>2011</v>
       </c>
-      <c r="D221" s="11" t="s">
+      <c r="F221" s="11" t="s">
         <v>2012</v>
       </c>
-      <c r="E221" s="11" t="s">
+    </row>
+    <row r="222" customFormat="false" ht="223.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="B222" s="22" t="s">
         <v>2013</v>
       </c>
-      <c r="F221" s="11" t="s">
+      <c r="C222" s="11" t="s">
         <v>2014</v>
       </c>
-    </row>
-    <row r="222" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="B222" s="2" t="s">
+      <c r="D222" s="11" t="s">
         <v>2015</v>
       </c>
-      <c r="C222" s="21" t="s">
-        <v>1335</v>
-      </c>
-      <c r="D222" s="28" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="223" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E222" s="11" t="s">
+        <v>2016</v>
+      </c>
+      <c r="F222" s="11" t="s">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2" t="s">
         <v>806</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C223" s="65" t="s">
-        <v>2017</v>
-      </c>
-      <c r="D223" s="10" t="s">
         <v>2018</v>
       </c>
-    </row>
-    <row r="224" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C223" s="21" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D223" s="28" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2" t="s">
         <v>806</v>
       </c>
@@ -29759,51 +29763,51 @@
         <v>2019</v>
       </c>
       <c r="C224" s="65" t="s">
-        <v>1397</v>
+        <v>2020</v>
       </c>
       <c r="D224" s="10" t="s">
-        <v>1398</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2" t="s">
-        <v>1026</v>
+        <v>806</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>2020</v>
-      </c>
-      <c r="C225" s="21" t="s">
-        <v>1335</v>
-      </c>
-      <c r="D225" s="28" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="226" customFormat="false" ht="75.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2022</v>
+      </c>
+      <c r="C225" s="65" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D225" s="10" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2" t="s">
         <v>1026</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>2021</v>
-      </c>
-      <c r="C226" s="65" t="s">
-        <v>2022</v>
+        <v>2023</v>
+      </c>
+      <c r="C226" s="21" t="s">
+        <v>1335</v>
       </c>
       <c r="D226" s="28" t="s">
-        <v>2023</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="75.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2" t="s">
-        <v>973</v>
-      </c>
-      <c r="B227" s="11" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B227" s="2" t="s">
         <v>2024</v>
       </c>
-      <c r="C227" s="11" t="s">
+      <c r="C227" s="65" t="s">
         <v>2025</v>
       </c>
-      <c r="D227" s="11" t="s">
+      <c r="D227" s="28" t="s">
         <v>2026</v>
       </c>
     </row>
@@ -29819,6 +29823,20 @@
       </c>
       <c r="D228" s="11" t="s">
         <v>2029</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="75.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="B229" s="11" t="s">
+        <v>2030</v>
+      </c>
+      <c r="C229" s="11" t="s">
+        <v>2031</v>
+      </c>
+      <c r="D229" s="11" t="s">
+        <v>2032</v>
       </c>
     </row>
   </sheetData>
@@ -29849,32 +29867,32 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="96" t="s">
-        <v>2030</v>
-      </c>
-      <c r="B1" s="96" t="s">
+      <c r="A1" s="95" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B1" s="95" t="s">
         <v>1133</v>
       </c>
-      <c r="C1" s="96" t="s">
+      <c r="C1" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="96" t="s">
+      <c r="D1" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="97" t="s">
+      <c r="E1" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="97" t="s">
+      <c r="F1" s="96" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="96" t="s">
-        <v>2031</v>
-      </c>
-      <c r="H1" s="96" t="s">
+      <c r="G1" s="95" t="s">
+        <v>2034</v>
+      </c>
+      <c r="H1" s="95" t="s">
         <v>12</v>
       </c>
       <c r="I1" s="29" t="s">
-        <v>2032</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29885,10 +29903,10 @@
         <v>1141</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>2034</v>
+        <v>2037</v>
       </c>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
@@ -29903,10 +29921,10 @@
         <v>1199</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
@@ -29921,10 +29939,10 @@
         <v>212</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
@@ -29933,7 +29951,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>212</v>
@@ -29951,10 +29969,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>1400</v>
@@ -29975,10 +29993,10 @@
         <v>1145</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
@@ -30037,7 +30055,7 @@
       <c r="E11" s="22"/>
       <c r="F11" s="22"/>
       <c r="G11" s="22" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="H11" s="22"/>
     </row>
@@ -30091,10 +30109,10 @@
         <v>1141</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="D15" s="65" t="s">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="E15" s="28"/>
       <c r="F15" s="28"/>
@@ -30110,10 +30128,10 @@
         <v>1199</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="D16" s="65" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="E16" s="28"/>
       <c r="F16" s="28"/>
@@ -30122,17 +30140,17 @@
       <c r="I16" s="22"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="98" t="s">
-        <v>2047</v>
+      <c r="A17" s="97" t="s">
+        <v>2050</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>2048</v>
+        <v>2051</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="E17" s="22"/>
       <c r="F17" s="22"/>
@@ -30140,17 +30158,17 @@
       <c r="H17" s="22"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="98" t="s">
-        <v>2047</v>
+      <c r="A18" s="97" t="s">
+        <v>2050</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>2051</v>
+        <v>2054</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>2052</v>
+        <v>2055</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>2053</v>
+        <v>2056</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="22"/>
@@ -30158,8 +30176,8 @@
       <c r="H18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="98" t="s">
-        <v>2047</v>
+      <c r="A19" s="97" t="s">
+        <v>2050</v>
       </c>
       <c r="B19" s="22"/>
       <c r="C19" s="22"/>
@@ -30172,17 +30190,17 @@
       <c r="H19" s="22"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="98" t="s">
+      <c r="A20" s="97" t="s">
         <v>170</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>2048</v>
+        <v>2051</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>2054</v>
+        <v>2057</v>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
@@ -30190,17 +30208,17 @@
       <c r="H20" s="22"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="98" t="s">
+      <c r="A21" s="97" t="s">
         <v>170</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>2051</v>
+        <v>2054</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>2052</v>
+        <v>2055</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="E21" s="22"/>
       <c r="F21" s="22"/>
@@ -30208,17 +30226,17 @@
       <c r="H21" s="22"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="98" t="s">
+      <c r="A22" s="97" t="s">
         <v>170</v>
       </c>
       <c r="B22" s="22" t="s">
         <v>172</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>2056</v>
+        <v>2059</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>2057</v>
+        <v>2060</v>
       </c>
       <c r="E22" s="22"/>
       <c r="F22" s="22"/>
@@ -30226,7 +30244,7 @@
       <c r="H22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="98" t="s">
+      <c r="A23" s="97" t="s">
         <v>170</v>
       </c>
       <c r="B23" s="22"/>
@@ -30244,13 +30262,13 @@
         <v>289</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>2059</v>
+        <v>2062</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>2060</v>
+        <v>2063</v>
       </c>
       <c r="E24" s="22"/>
       <c r="F24" s="22"/>
@@ -30262,13 +30280,13 @@
         <v>289</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>2061</v>
+        <v>2064</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>2062</v>
+        <v>2065</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>2063</v>
+        <v>2066</v>
       </c>
       <c r="E25" s="22"/>
       <c r="F25" s="22"/>
@@ -30294,13 +30312,13 @@
         <v>282</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>2064</v>
+        <v>2067</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>2065</v>
+        <v>2068</v>
       </c>
       <c r="E27" s="22"/>
       <c r="F27" s="22"/>
@@ -30312,13 +30330,13 @@
         <v>282</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>2061</v>
+        <v>2064</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>2066</v>
+        <v>2069</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>2067</v>
+        <v>2070</v>
       </c>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
@@ -30347,16 +30365,16 @@
         <v>1165</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>2068</v>
+        <v>2071</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>2069</v>
+        <v>2072</v>
       </c>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
-      <c r="I30" s="99" t="n">
+      <c r="I30" s="98" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -30369,16 +30387,16 @@
         <v>1166</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>2070</v>
+        <v>2073</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>2071</v>
+        <v>2074</v>
       </c>
       <c r="E31" s="22"/>
       <c r="F31" s="22"/>
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
-      <c r="I31" s="99" t="n">
+      <c r="I31" s="98" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -30391,16 +30409,16 @@
         <v>1167</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>2073</v>
+        <v>2076</v>
       </c>
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
-      <c r="I32" s="99" t="n">
+      <c r="I32" s="98" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -30413,16 +30431,16 @@
         <v>1169</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>2075</v>
+        <v>2078</v>
       </c>
       <c r="E33" s="22"/>
       <c r="F33" s="22"/>
       <c r="G33" s="22"/>
       <c r="H33" s="22"/>
-      <c r="I33" s="99" t="n">
+      <c r="I33" s="98" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -30435,16 +30453,16 @@
         <v>1170</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>2076</v>
+        <v>2079</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>2077</v>
+        <v>2080</v>
       </c>
       <c r="E34" s="22"/>
       <c r="F34" s="22"/>
       <c r="G34" s="22"/>
       <c r="H34" s="22"/>
-      <c r="I34" s="99" t="n">
+      <c r="I34" s="98" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -30454,13 +30472,13 @@
         <v>325</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>2078</v>
+        <v>2081</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>2079</v>
+        <v>2082</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>2080</v>
+        <v>2083</v>
       </c>
       <c r="E35" s="22"/>
       <c r="F35" s="22"/>
@@ -30475,13 +30493,13 @@
         <v>325</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>2081</v>
+        <v>2084</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>2082</v>
+        <v>2085</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>2083</v>
+        <v>2086</v>
       </c>
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
@@ -30494,13 +30512,13 @@
         <v>325</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>2084</v>
+        <v>2087</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>2085</v>
+        <v>2088</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="E37" s="22"/>
       <c r="F37" s="22"/>
@@ -30513,13 +30531,13 @@
         <v>325</v>
       </c>
       <c r="B38" s="60" t="s">
-        <v>2087</v>
+        <v>2090</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>2089</v>
+        <v>2092</v>
       </c>
       <c r="E38" s="22"/>
       <c r="F38" s="22"/>
@@ -30532,13 +30550,13 @@
         <v>325</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>2090</v>
+        <v>2093</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>2091</v>
+        <v>2094</v>
       </c>
       <c r="D39" s="22" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="E39" s="22"/>
       <c r="F39" s="22"/>
@@ -30551,13 +30569,13 @@
         <v>325</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>2094</v>
+        <v>2097</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>2095</v>
+        <v>2098</v>
       </c>
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
@@ -30575,7 +30593,7 @@
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
       <c r="G41" s="22" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="H41" s="22"/>
       <c r="I41" s="29"/>
@@ -30600,13 +30618,13 @@
         <v>296</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>2096</v>
+        <v>2099</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>2097</v>
+        <v>2100</v>
       </c>
       <c r="D43" s="65" t="s">
-        <v>2098</v>
+        <v>2101</v>
       </c>
       <c r="E43" s="22"/>
       <c r="F43" s="22"/>
@@ -30619,13 +30637,13 @@
         <v>296</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>2099</v>
+        <v>2102</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>2100</v>
+        <v>2103</v>
       </c>
       <c r="D44" s="65" t="s">
-        <v>2101</v>
+        <v>2104</v>
       </c>
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
@@ -30638,13 +30656,13 @@
         <v>296</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>2102</v>
+        <v>2105</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>2103</v>
+        <v>2106</v>
       </c>
       <c r="D45" s="65" t="s">
-        <v>2104</v>
+        <v>2107</v>
       </c>
       <c r="E45" s="22"/>
       <c r="F45" s="22"/>
@@ -30657,13 +30675,13 @@
         <v>296</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>2105</v>
+        <v>2108</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>2106</v>
+        <v>2109</v>
       </c>
       <c r="D46" s="65" t="s">
-        <v>2107</v>
+        <v>2110</v>
       </c>
       <c r="E46" s="22"/>
       <c r="F46" s="22"/>
@@ -30681,7 +30699,7 @@
       <c r="E47" s="22"/>
       <c r="F47" s="22"/>
       <c r="G47" s="22" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="H47" s="22"/>
       <c r="I47" s="22"/>
@@ -30694,10 +30712,10 @@
         <v>1230</v>
       </c>
       <c r="C48" s="28" t="s">
-        <v>2108</v>
+        <v>2111</v>
       </c>
       <c r="D48" s="65" t="s">
-        <v>2109</v>
+        <v>2112</v>
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="22"/>
@@ -30712,13 +30730,13 @@
         <v>203</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>2110</v>
+        <v>2113</v>
       </c>
       <c r="C49" s="28" t="s">
-        <v>2111</v>
+        <v>2114</v>
       </c>
       <c r="D49" s="65" t="s">
-        <v>2112</v>
+        <v>2115</v>
       </c>
       <c r="E49" s="22"/>
       <c r="F49" s="22"/>
@@ -30733,13 +30751,13 @@
         <v>203</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>2113</v>
+        <v>2116</v>
       </c>
       <c r="C50" s="28" t="s">
-        <v>2114</v>
+        <v>2117</v>
       </c>
       <c r="D50" s="65" t="s">
-        <v>2115</v>
+        <v>2118</v>
       </c>
       <c r="E50" s="22"/>
       <c r="F50" s="22"/>
@@ -30755,10 +30773,10 @@
         <v>212</v>
       </c>
       <c r="C51" s="28" t="s">
-        <v>2116</v>
+        <v>2119</v>
       </c>
       <c r="D51" s="65" t="s">
-        <v>2117</v>
+        <v>2120</v>
       </c>
       <c r="E51" s="22"/>
       <c r="F51" s="22"/>
@@ -30776,7 +30794,7 @@
       <c r="E52" s="22"/>
       <c r="F52" s="22"/>
       <c r="G52" s="22" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="H52" s="22"/>
       <c r="I52" s="22"/>
@@ -30786,13 +30804,13 @@
         <v>209</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>2118</v>
+        <v>2121</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>2119</v>
+        <v>2122</v>
       </c>
       <c r="D53" s="65" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
       <c r="E53" s="22"/>
       <c r="F53" s="22"/>
@@ -30805,13 +30823,13 @@
         <v>209</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>2121</v>
+        <v>2124</v>
       </c>
       <c r="C54" s="28" t="s">
-        <v>2122</v>
+        <v>2125</v>
       </c>
       <c r="D54" s="65" t="s">
-        <v>2123</v>
+        <v>2126</v>
       </c>
       <c r="E54" s="22"/>
       <c r="F54" s="22"/>
@@ -30824,13 +30842,13 @@
         <v>209</v>
       </c>
       <c r="B55" s="22" t="s">
-        <v>2124</v>
+        <v>2127</v>
       </c>
       <c r="C55" s="28" t="s">
-        <v>2125</v>
+        <v>2128</v>
       </c>
       <c r="D55" s="65" t="s">
-        <v>2126</v>
+        <v>2129</v>
       </c>
       <c r="E55" s="22"/>
       <c r="F55" s="22"/>
@@ -30843,13 +30861,13 @@
         <v>209</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>2127</v>
+        <v>2130</v>
       </c>
       <c r="C56" s="28" t="s">
-        <v>2128</v>
+        <v>2131</v>
       </c>
       <c r="D56" s="65" t="s">
-        <v>2129</v>
+        <v>2132</v>
       </c>
       <c r="E56" s="22"/>
       <c r="F56" s="22"/>
@@ -30862,13 +30880,13 @@
         <v>209</v>
       </c>
       <c r="B57" s="22" t="s">
-        <v>2130</v>
+        <v>2133</v>
       </c>
       <c r="C57" s="28" t="s">
-        <v>2131</v>
+        <v>2134</v>
       </c>
       <c r="D57" s="65" t="s">
-        <v>2131</v>
+        <v>2134</v>
       </c>
       <c r="E57" s="22"/>
       <c r="F57" s="22"/>
@@ -30881,13 +30899,13 @@
         <v>209</v>
       </c>
       <c r="B58" s="22" t="s">
-        <v>2132</v>
+        <v>2135</v>
       </c>
       <c r="C58" s="28" t="s">
-        <v>2133</v>
+        <v>2136</v>
       </c>
       <c r="D58" s="65" t="s">
-        <v>2134</v>
+        <v>2137</v>
       </c>
       <c r="E58" s="22"/>
       <c r="F58" s="22"/>
@@ -30900,13 +30918,13 @@
         <v>209</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>2135</v>
+        <v>2138</v>
       </c>
       <c r="C59" s="28" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="D59" s="65" t="s">
-        <v>2137</v>
+        <v>2140</v>
       </c>
       <c r="E59" s="22"/>
       <c r="F59" s="22"/>
@@ -30919,13 +30937,13 @@
         <v>209</v>
       </c>
       <c r="B60" s="22" t="s">
-        <v>2138</v>
+        <v>2141</v>
       </c>
       <c r="C60" s="28" t="s">
-        <v>2139</v>
+        <v>2142</v>
       </c>
       <c r="D60" s="65" t="s">
-        <v>2140</v>
+        <v>2143</v>
       </c>
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
@@ -30953,13 +30971,13 @@
         <v>209</v>
       </c>
       <c r="B62" s="22" t="s">
-        <v>2141</v>
+        <v>2144</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>2142</v>
+        <v>2145</v>
       </c>
       <c r="D62" s="65" t="s">
-        <v>2143</v>
+        <v>2146</v>
       </c>
       <c r="E62" s="22"/>
       <c r="F62" s="22"/>
@@ -30977,7 +30995,7 @@
       <c r="E63" s="22"/>
       <c r="F63" s="22"/>
       <c r="G63" s="22" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="H63" s="22"/>
       <c r="I63" s="22"/>
@@ -30990,10 +31008,10 @@
         <v>1141</v>
       </c>
       <c r="C64" s="28" t="s">
-        <v>2144</v>
+        <v>2147</v>
       </c>
       <c r="D64" s="65" t="s">
-        <v>2145</v>
+        <v>2148</v>
       </c>
       <c r="E64" s="22"/>
       <c r="F64" s="22"/>
@@ -31002,17 +31020,17 @@
       <c r="I64" s="22"/>
     </row>
     <row r="65" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="98" t="s">
+      <c r="A65" s="97" t="s">
         <v>303</v>
       </c>
       <c r="B65" s="22" t="s">
         <v>1173</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>2146</v>
+        <v>2149</v>
       </c>
       <c r="D65" s="22" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="E65" s="22"/>
       <c r="F65" s="22"/>
@@ -31021,17 +31039,17 @@
       <c r="I65" s="29"/>
     </row>
     <row r="66" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="98" t="s">
+      <c r="A66" s="97" t="s">
         <v>303</v>
       </c>
       <c r="B66" s="22" t="s">
         <v>1174</v>
       </c>
       <c r="C66" s="22" t="s">
-        <v>2148</v>
+        <v>2151</v>
       </c>
       <c r="D66" s="22" t="s">
-        <v>2149</v>
+        <v>2152</v>
       </c>
       <c r="E66" s="22"/>
       <c r="F66" s="22"/>
@@ -31040,17 +31058,17 @@
       <c r="I66" s="29"/>
     </row>
     <row r="67" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="98" t="s">
+      <c r="A67" s="97" t="s">
         <v>303</v>
       </c>
       <c r="B67" s="22" t="s">
         <v>1175</v>
       </c>
       <c r="C67" s="22" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="D67" s="22" t="s">
-        <v>2151</v>
+        <v>2154</v>
       </c>
       <c r="E67" s="22"/>
       <c r="F67" s="22"/>
@@ -31059,17 +31077,17 @@
       <c r="I67" s="29"/>
     </row>
     <row r="68" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="98" t="s">
+      <c r="A68" s="97" t="s">
         <v>303</v>
       </c>
       <c r="B68" s="22" t="s">
-        <v>2152</v>
+        <v>2155</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>2153</v>
+        <v>2156</v>
       </c>
       <c r="D68" s="22" t="s">
-        <v>2154</v>
+        <v>2157</v>
       </c>
       <c r="E68" s="22"/>
       <c r="F68" s="22"/>
@@ -31078,17 +31096,17 @@
       <c r="I68" s="29"/>
     </row>
     <row r="69" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="98" t="s">
+      <c r="A69" s="97" t="s">
         <v>303</v>
       </c>
       <c r="B69" s="22" t="s">
         <v>1187</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="D69" s="22" t="s">
-        <v>2156</v>
+        <v>2159</v>
       </c>
       <c r="E69" s="22"/>
       <c r="F69" s="22"/>
@@ -31097,59 +31115,59 @@
       <c r="I69" s="29"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="98" t="s">
+      <c r="A70" s="97" t="s">
         <v>877</v>
       </c>
       <c r="B70" s="29" t="s">
-        <v>2157</v>
+        <v>2160</v>
       </c>
       <c r="C70" s="29" t="s">
-        <v>2158</v>
+        <v>2161</v>
       </c>
       <c r="D70" s="29" t="s">
-        <v>2159</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="98" t="s">
+      <c r="A71" s="97" t="s">
         <v>877</v>
       </c>
       <c r="B71" s="29" t="s">
-        <v>2160</v>
+        <v>2163</v>
       </c>
       <c r="C71" s="29" t="s">
-        <v>2161</v>
+        <v>2164</v>
       </c>
       <c r="D71" s="29" t="s">
-        <v>2162</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="98" t="s">
+      <c r="A72" s="97" t="s">
         <v>877</v>
       </c>
       <c r="B72" s="29" t="s">
-        <v>2163</v>
+        <v>2166</v>
       </c>
       <c r="C72" s="29" t="s">
-        <v>2164</v>
+        <v>2167</v>
       </c>
       <c r="D72" s="29" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="73" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="98" t="s">
+      <c r="A73" s="97" t="s">
         <v>877</v>
       </c>
       <c r="B73" s="29" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="C73" s="29" t="s">
-        <v>2167</v>
+        <v>2170</v>
       </c>
       <c r="D73" s="29" t="s">
-        <v>2168</v>
+        <v>2171</v>
       </c>
       <c r="E73" s="29"/>
       <c r="F73" s="29"/>
@@ -31162,13 +31180,13 @@
         <v>1054</v>
       </c>
       <c r="B74" s="29" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="C74" s="29" t="s">
-        <v>2170</v>
+        <v>2173</v>
       </c>
       <c r="D74" s="29" t="s">
-        <v>2171</v>
+        <v>2174</v>
       </c>
       <c r="E74" s="29"/>
       <c r="F74" s="29"/>
@@ -31181,13 +31199,13 @@
         <v>1054</v>
       </c>
       <c r="B75" s="60" t="s">
-        <v>2172</v>
+        <v>2175</v>
       </c>
       <c r="C75" s="60" t="s">
-        <v>2173</v>
+        <v>2176</v>
       </c>
       <c r="D75" s="60" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="E75" s="60"/>
       <c r="F75" s="60"/>
@@ -31200,13 +31218,13 @@
         <v>1054</v>
       </c>
       <c r="B76" s="60" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="C76" s="60" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="D76" s="60" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="E76" s="60"/>
       <c r="F76" s="60"/>
@@ -31219,13 +31237,13 @@
         <v>1054</v>
       </c>
       <c r="B77" s="60" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="C77" s="60" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="D77" s="60" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="E77" s="60"/>
       <c r="F77" s="60"/>
@@ -31238,13 +31256,13 @@
         <v>1054</v>
       </c>
       <c r="B78" s="60" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="C78" s="60" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="D78" s="60" t="s">
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="E78" s="60"/>
       <c r="F78" s="60"/>
@@ -31257,13 +31275,13 @@
         <v>1054</v>
       </c>
       <c r="B79" s="60" t="s">
-        <v>2184</v>
+        <v>2187</v>
       </c>
       <c r="C79" s="60" t="s">
-        <v>2185</v>
+        <v>2188</v>
       </c>
       <c r="D79" s="60" t="s">
-        <v>2186</v>
+        <v>2189</v>
       </c>
       <c r="E79" s="60"/>
       <c r="F79" s="60"/>
@@ -31276,13 +31294,13 @@
         <v>1054</v>
       </c>
       <c r="B80" s="60" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="C80" s="60" t="s">
-        <v>2188</v>
+        <v>2191</v>
       </c>
       <c r="D80" s="60" t="s">
-        <v>2189</v>
+        <v>2192</v>
       </c>
       <c r="E80" s="60"/>
       <c r="F80" s="60"/>
@@ -31295,13 +31313,13 @@
         <v>1054</v>
       </c>
       <c r="B81" s="60" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="C81" s="60" t="s">
-        <v>2191</v>
+        <v>2194</v>
       </c>
       <c r="D81" s="60" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="E81" s="60"/>
       <c r="F81" s="60"/>
@@ -31314,13 +31332,13 @@
         <v>1054</v>
       </c>
       <c r="B82" s="60" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="C82" s="60" t="s">
-        <v>2194</v>
+        <v>2197</v>
       </c>
       <c r="D82" s="60" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="E82" s="60"/>
       <c r="F82" s="60"/>
@@ -31333,13 +31351,13 @@
         <v>1054</v>
       </c>
       <c r="B83" s="60" t="s">
-        <v>2196</v>
+        <v>2199</v>
       </c>
       <c r="C83" s="60" t="s">
-        <v>2197</v>
+        <v>2200</v>
       </c>
       <c r="D83" s="60" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="E83" s="60"/>
       <c r="F83" s="60"/>
@@ -31352,13 +31370,13 @@
         <v>1054</v>
       </c>
       <c r="B84" s="60" t="s">
-        <v>2199</v>
+        <v>2202</v>
       </c>
       <c r="C84" s="60" t="s">
-        <v>2200</v>
+        <v>2203</v>
       </c>
       <c r="D84" s="60" t="s">
-        <v>2201</v>
+        <v>2204</v>
       </c>
       <c r="E84" s="60"/>
       <c r="F84" s="60"/>
@@ -31371,13 +31389,13 @@
         <v>1054</v>
       </c>
       <c r="B85" s="60" t="s">
-        <v>2202</v>
+        <v>2205</v>
       </c>
       <c r="C85" s="60" t="s">
-        <v>2203</v>
+        <v>2206</v>
       </c>
       <c r="D85" s="60" t="s">
-        <v>2204</v>
+        <v>2207</v>
       </c>
       <c r="E85" s="60"/>
       <c r="F85" s="60"/>
@@ -31390,13 +31408,13 @@
         <v>1054</v>
       </c>
       <c r="B86" s="29" t="s">
-        <v>2205</v>
+        <v>2208</v>
       </c>
       <c r="C86" s="29" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="D86" s="29" t="s">
-        <v>2207</v>
+        <v>2210</v>
       </c>
       <c r="E86" s="29"/>
       <c r="F86" s="29"/>
@@ -31409,7 +31427,7 @@
         <v>1054</v>
       </c>
       <c r="B87" s="29" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="C87" s="29" t="s">
         <v>1400</v>
@@ -31428,45 +31446,45 @@
         <v>1054</v>
       </c>
       <c r="B88" s="29" t="s">
-        <v>2208</v>
+        <v>2211</v>
       </c>
       <c r="C88" s="29" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="D88" s="29" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="100" t="s">
+      <c r="A89" s="99" t="s">
         <v>81</v>
       </c>
       <c r="B89" s="60" t="s">
-        <v>2210</v>
+        <v>2213</v>
       </c>
       <c r="C89" s="29" t="s">
-        <v>2211</v>
+        <v>2214</v>
       </c>
       <c r="D89" s="29" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="100" t="s">
+      <c r="A90" s="99" t="s">
         <v>81</v>
       </c>
       <c r="B90" s="29" t="s">
-        <v>2213</v>
+        <v>2216</v>
       </c>
       <c r="C90" s="29" t="s">
-        <v>2214</v>
+        <v>2217</v>
       </c>
       <c r="D90" s="29" t="s">
-        <v>2215</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="100" t="s">
+      <c r="A91" s="99" t="s">
         <v>81</v>
       </c>
       <c r="B91" s="29" t="s">
@@ -31480,33 +31498,33 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="100" t="s">
+      <c r="A92" s="99" t="s">
         <v>81</v>
       </c>
       <c r="B92" s="29" t="s">
         <v>1145</v>
       </c>
       <c r="C92" s="60" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="D92" s="60" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="E92" s="60"/>
       <c r="F92" s="60"/>
     </row>
     <row r="93" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="101" t="s">
+      <c r="A93" s="100" t="s">
         <v>403</v>
       </c>
       <c r="B93" s="22" t="s">
-        <v>2216</v>
+        <v>2219</v>
       </c>
       <c r="C93" s="28" t="s">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="D93" s="65" t="s">
-        <v>2218</v>
+        <v>2221</v>
       </c>
       <c r="E93" s="28"/>
       <c r="F93" s="28"/>
@@ -31517,17 +31535,17 @@
       <c r="I93" s="22"/>
     </row>
     <row r="94" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="101" t="s">
+      <c r="A94" s="100" t="s">
         <v>403</v>
       </c>
       <c r="B94" s="22" t="s">
-        <v>2219</v>
+        <v>2222</v>
       </c>
       <c r="C94" s="28" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="D94" s="65" t="s">
-        <v>2221</v>
+        <v>2224</v>
       </c>
       <c r="E94" s="28"/>
       <c r="F94" s="28"/>
@@ -31538,17 +31556,17 @@
       <c r="I94" s="22"/>
     </row>
     <row r="95" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="101" t="s">
+      <c r="A95" s="100" t="s">
         <v>403</v>
       </c>
       <c r="B95" s="22" t="s">
-        <v>2222</v>
+        <v>2225</v>
       </c>
       <c r="C95" s="28" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
       <c r="D95" s="65" t="s">
-        <v>2224</v>
+        <v>2227</v>
       </c>
       <c r="E95" s="28"/>
       <c r="F95" s="28"/>
@@ -31557,17 +31575,17 @@
       <c r="I95" s="22"/>
     </row>
     <row r="96" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="101" t="s">
+      <c r="A96" s="100" t="s">
         <v>403</v>
       </c>
       <c r="B96" s="22" t="s">
-        <v>2225</v>
+        <v>2228</v>
       </c>
       <c r="C96" s="28" t="s">
-        <v>2226</v>
+        <v>2229</v>
       </c>
       <c r="D96" s="65" t="s">
-        <v>2227</v>
+        <v>2230</v>
       </c>
       <c r="E96" s="28"/>
       <c r="F96" s="28"/>
@@ -31576,17 +31594,17 @@
       <c r="I96" s="22"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="101" t="s">
+      <c r="A97" s="100" t="s">
         <v>403</v>
       </c>
       <c r="B97" s="22" t="s">
-        <v>2228</v>
+        <v>2231</v>
       </c>
       <c r="C97" s="28" t="s">
-        <v>2229</v>
+        <v>2232</v>
       </c>
       <c r="D97" s="65" t="s">
-        <v>2230</v>
+        <v>2233</v>
       </c>
       <c r="E97" s="28"/>
       <c r="F97" s="28"/>
@@ -31595,17 +31613,17 @@
       <c r="I97" s="22"/>
     </row>
     <row r="98" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="101" t="s">
+      <c r="A98" s="100" t="s">
         <v>403</v>
       </c>
       <c r="B98" s="22" t="s">
         <v>1206</v>
       </c>
       <c r="C98" s="28" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="D98" s="65" t="s">
-        <v>2232</v>
+        <v>2235</v>
       </c>
       <c r="E98" s="28"/>
       <c r="F98" s="28"/>
@@ -31616,17 +31634,17 @@
       <c r="I98" s="22"/>
     </row>
     <row r="99" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="101" t="s">
+      <c r="A99" s="100" t="s">
         <v>403</v>
       </c>
       <c r="B99" s="22" t="s">
         <v>1207</v>
       </c>
       <c r="C99" s="28" t="s">
-        <v>2233</v>
+        <v>2236</v>
       </c>
       <c r="D99" s="65" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="E99" s="28"/>
       <c r="F99" s="28"/>
@@ -31635,17 +31653,17 @@
       <c r="I99" s="22"/>
     </row>
     <row r="100" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="101" t="s">
+      <c r="A100" s="100" t="s">
         <v>403</v>
       </c>
       <c r="B100" s="22" t="s">
-        <v>2235</v>
+        <v>2238</v>
       </c>
       <c r="C100" s="28" t="s">
-        <v>2236</v>
+        <v>2239</v>
       </c>
       <c r="D100" s="65" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="E100" s="28"/>
       <c r="F100" s="28"/>
@@ -31656,7 +31674,7 @@
       <c r="I100" s="22"/>
     </row>
     <row r="101" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="101" t="s">
+      <c r="A101" s="100" t="s">
         <v>403</v>
       </c>
       <c r="B101" s="22" t="s">
@@ -31675,11 +31693,11 @@
       <c r="I101" s="22"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="102" t="s">
-        <v>2238</v>
+      <c r="A102" s="101" t="s">
+        <v>2241</v>
       </c>
       <c r="B102" s="29" t="s">
-        <v>2239</v>
+        <v>2242</v>
       </c>
       <c r="C102" s="60" t="s">
         <v>1712</v>
@@ -31695,11 +31713,11 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="102" t="s">
-        <v>2238</v>
+      <c r="A103" s="101" t="s">
+        <v>2241</v>
       </c>
       <c r="B103" s="29" t="s">
-        <v>2240</v>
+        <v>2243</v>
       </c>
       <c r="C103" s="60" t="s">
         <v>1717</v>
@@ -31715,249 +31733,249 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="102" t="s">
-        <v>2238</v>
+      <c r="A104" s="101" t="s">
+        <v>2241</v>
       </c>
       <c r="B104" s="29" t="s">
         <v>1199</v>
       </c>
       <c r="C104" s="29" t="s">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="D104" s="29" t="s">
-        <v>2036</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="102" t="s">
+      <c r="A105" s="101" t="s">
         <v>734</v>
       </c>
       <c r="B105" s="60" t="s">
-        <v>2241</v>
+        <v>2244</v>
       </c>
       <c r="C105" s="60" t="s">
-        <v>2242</v>
+        <v>2245</v>
       </c>
       <c r="D105" s="60" t="s">
-        <v>2243</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="102" t="s">
+      <c r="A106" s="101" t="s">
         <v>734</v>
       </c>
       <c r="B106" s="60" t="s">
-        <v>2244</v>
+        <v>2247</v>
       </c>
       <c r="C106" s="60" t="s">
-        <v>2245</v>
+        <v>2248</v>
       </c>
       <c r="D106" s="60" t="s">
-        <v>2246</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="102" t="s">
+      <c r="A107" s="101" t="s">
         <v>734</v>
       </c>
       <c r="B107" s="60" t="s">
-        <v>2247</v>
+        <v>2250</v>
       </c>
       <c r="C107" s="60" t="s">
-        <v>2248</v>
+        <v>2251</v>
       </c>
       <c r="D107" s="60" t="s">
-        <v>2249</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="102" t="s">
+      <c r="A108" s="101" t="s">
         <v>734</v>
       </c>
       <c r="B108" s="60" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C108" s="60" t="s">
+        <v>2254</v>
+      </c>
+      <c r="D108" s="60" t="s">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="101" t="s">
+        <v>734</v>
+      </c>
+      <c r="G109" s="22" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="101" t="s">
+        <v>734</v>
+      </c>
+      <c r="G110" s="22" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="101" t="s">
+        <v>802</v>
+      </c>
+      <c r="B111" s="60" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C111" s="60" t="s">
+        <v>2257</v>
+      </c>
+      <c r="D111" s="60" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="101" t="s">
+        <v>802</v>
+      </c>
+      <c r="B112" s="60" t="s">
+        <v>2259</v>
+      </c>
+      <c r="C112" s="60" t="s">
+        <v>2260</v>
+      </c>
+      <c r="D112" s="60" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="101" t="s">
+        <v>802</v>
+      </c>
+      <c r="B113" s="60" t="s">
         <v>2250</v>
       </c>
-      <c r="C108" s="60" t="s">
+      <c r="C113" s="60" t="s">
         <v>2251</v>
       </c>
-      <c r="D108" s="60" t="s">
+      <c r="D113" s="60" t="s">
         <v>2252</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="102" t="s">
-        <v>734</v>
-      </c>
-      <c r="G109" s="22" t="s">
-        <v>2039</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="102" t="s">
-        <v>734</v>
-      </c>
-      <c r="G110" s="22" t="s">
-        <v>2040</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="102" t="s">
+    <row r="114" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="101" t="s">
         <v>802</v>
       </c>
-      <c r="B111" s="60" t="s">
-        <v>2253</v>
-      </c>
-      <c r="C111" s="60" t="s">
-        <v>2254</v>
-      </c>
-      <c r="D111" s="60" t="s">
-        <v>2255</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="102" t="s">
+      <c r="B114" s="22" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C114" s="28" t="s">
+        <v>2263</v>
+      </c>
+      <c r="D114" s="21" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="101" t="s">
         <v>802</v>
       </c>
-      <c r="B112" s="60" t="s">
-        <v>2256</v>
-      </c>
-      <c r="C112" s="60" t="s">
-        <v>2257</v>
-      </c>
-      <c r="D112" s="60" t="s">
-        <v>2258</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="102" t="s">
+      <c r="G115" s="22" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="101" t="s">
         <v>802</v>
       </c>
-      <c r="B113" s="60" t="s">
-        <v>2247</v>
-      </c>
-      <c r="C113" s="60" t="s">
-        <v>2248</v>
-      </c>
-      <c r="D113" s="60" t="s">
-        <v>2249</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="102" t="s">
-        <v>802</v>
-      </c>
-      <c r="B114" s="22" t="s">
-        <v>2259</v>
-      </c>
-      <c r="C114" s="28" t="s">
-        <v>2260</v>
-      </c>
-      <c r="D114" s="21" t="s">
-        <v>2261</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="102" t="s">
-        <v>802</v>
-      </c>
-      <c r="G115" s="22" t="s">
-        <v>2039</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="102" t="s">
-        <v>802</v>
-      </c>
       <c r="G116" s="22" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="103" t="s">
+      <c r="A117" s="102" t="s">
         <v>322</v>
       </c>
       <c r="B117" s="60" t="s">
-        <v>2262</v>
+        <v>2265</v>
       </c>
       <c r="C117" s="29" t="s">
-        <v>2263</v>
+        <v>2266</v>
       </c>
       <c r="D117" s="29" t="s">
-        <v>2264</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="103" t="s">
+      <c r="A118" s="102" t="s">
         <v>322</v>
       </c>
       <c r="B118" s="29" t="s">
-        <v>2265</v>
+        <v>2268</v>
       </c>
       <c r="C118" s="29" t="s">
-        <v>2266</v>
+        <v>2269</v>
       </c>
       <c r="D118" s="29" t="s">
-        <v>2267</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="103" t="s">
+      <c r="A119" s="102" t="s">
         <v>322</v>
       </c>
       <c r="B119" s="60" t="s">
-        <v>2268</v>
+        <v>2271</v>
       </c>
       <c r="C119" s="29" t="s">
-        <v>2269</v>
+        <v>2272</v>
       </c>
       <c r="D119" s="29" t="s">
-        <v>2270</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="103" t="s">
+      <c r="A120" s="102" t="s">
         <v>322</v>
       </c>
       <c r="B120" s="60" t="s">
-        <v>2271</v>
+        <v>2274</v>
       </c>
       <c r="C120" s="29" t="s">
-        <v>2272</v>
+        <v>2275</v>
       </c>
       <c r="D120" s="29" t="s">
-        <v>2273</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="103" t="s">
+      <c r="A121" s="102" t="s">
         <v>322</v>
       </c>
       <c r="B121" s="60" t="s">
-        <v>2274</v>
+        <v>2277</v>
       </c>
       <c r="C121" s="29" t="s">
-        <v>2275</v>
+        <v>2278</v>
       </c>
       <c r="D121" s="29" t="s">
-        <v>2276</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="103" t="s">
+      <c r="A122" s="102" t="s">
         <v>322</v>
       </c>
       <c r="B122" s="60" t="s">
-        <v>2277</v>
+        <v>2280</v>
       </c>
       <c r="C122" s="29" t="s">
-        <v>2278</v>
+        <v>2281</v>
       </c>
       <c r="D122" s="29" t="s">
-        <v>2279</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="103" t="s">
+      <c r="A123" s="102" t="s">
         <v>322</v>
       </c>
       <c r="G123" s="22" t="s">
@@ -31965,104 +31983,104 @@
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="98" t="s">
-        <v>2280</v>
+      <c r="A124" s="97" t="s">
+        <v>2283</v>
       </c>
       <c r="B124" s="22" t="s">
         <v>1173</v>
       </c>
       <c r="C124" s="22" t="s">
-        <v>1805</v>
+        <v>1808</v>
       </c>
       <c r="D124" s="22" t="s">
-        <v>1806</v>
+        <v>1809</v>
       </c>
       <c r="E124" s="22" t="s">
-        <v>1807</v>
+        <v>1810</v>
       </c>
       <c r="F124" s="22" t="s">
-        <v>1808</v>
-      </c>
-      <c r="G124" s="98"/>
+        <v>1811</v>
+      </c>
+      <c r="G124" s="97"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="98" t="s">
-        <v>2280</v>
+      <c r="A125" s="97" t="s">
+        <v>2283</v>
       </c>
       <c r="B125" s="22" t="s">
         <v>1174</v>
       </c>
       <c r="C125" s="22" t="s">
-        <v>1810</v>
+        <v>1813</v>
       </c>
       <c r="D125" s="22" t="s">
-        <v>1811</v>
+        <v>1814</v>
       </c>
       <c r="E125" s="22" t="s">
-        <v>1812</v>
+        <v>1815</v>
       </c>
       <c r="F125" s="22" t="s">
-        <v>1813</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="98" t="s">
-        <v>2280</v>
+      <c r="A126" s="97" t="s">
+        <v>2283</v>
       </c>
       <c r="B126" s="22" t="s">
         <v>1175</v>
       </c>
       <c r="C126" s="22" t="s">
-        <v>1815</v>
+        <v>1818</v>
       </c>
       <c r="D126" s="22" t="s">
-        <v>1816</v>
+        <v>1819</v>
       </c>
       <c r="E126" s="22" t="s">
-        <v>1817</v>
+        <v>1820</v>
       </c>
       <c r="F126" s="22" t="s">
-        <v>1818</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="98" t="s">
-        <v>2280</v>
+      <c r="A127" s="97" t="s">
+        <v>2283</v>
       </c>
       <c r="B127" s="22" t="s">
-        <v>2152</v>
+        <v>2155</v>
       </c>
       <c r="C127" s="22" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="D127" s="22" t="s">
-        <v>1821</v>
+        <v>1824</v>
       </c>
       <c r="E127" s="22" t="s">
-        <v>1822</v>
+        <v>1825</v>
       </c>
       <c r="F127" s="22" t="s">
-        <v>1823</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="98" t="s">
-        <v>2280</v>
+      <c r="A128" s="97" t="s">
+        <v>2283</v>
       </c>
       <c r="B128" s="22" t="s">
         <v>1187</v>
       </c>
       <c r="C128" s="22" t="s">
-        <v>1825</v>
+        <v>1828</v>
       </c>
       <c r="D128" s="22" t="s">
-        <v>1826</v>
+        <v>1829</v>
       </c>
       <c r="E128" s="22" t="s">
-        <v>1827</v>
+        <v>1830</v>
       </c>
       <c r="F128" s="22" t="s">
-        <v>1828</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32070,13 +32088,13 @@
         <v>661</v>
       </c>
       <c r="B129" s="29" t="s">
-        <v>2281</v>
+        <v>2284</v>
       </c>
       <c r="C129" s="65" t="s">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="D129" s="35" t="s">
-        <v>1979</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32087,12 +32105,12 @@
         <v>1211</v>
       </c>
       <c r="C130" s="65" t="s">
-        <v>2282</v>
+        <v>2285</v>
       </c>
       <c r="D130" s="35" t="s">
-        <v>2282</v>
-      </c>
-      <c r="H130" s="104" t="s">
+        <v>2285</v>
+      </c>
+      <c r="H130" s="103" t="s">
         <v>1209</v>
       </c>
     </row>
@@ -32101,16 +32119,16 @@
         <v>661</v>
       </c>
       <c r="B131" s="29" t="s">
-        <v>2283</v>
+        <v>2286</v>
       </c>
       <c r="C131" s="65" t="s">
-        <v>2284</v>
+        <v>2287</v>
       </c>
       <c r="D131" s="35" t="s">
-        <v>2285</v>
-      </c>
-      <c r="H131" s="105" t="s">
-        <v>2286</v>
+        <v>2288</v>
+      </c>
+      <c r="H131" s="104" t="s">
+        <v>2289</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32118,13 +32136,13 @@
         <v>661</v>
       </c>
       <c r="B132" s="29" t="s">
-        <v>2287</v>
+        <v>2290</v>
       </c>
       <c r="C132" s="65" t="s">
-        <v>1987</v>
+        <v>1990</v>
       </c>
       <c r="D132" s="35" t="s">
-        <v>1988</v>
+        <v>1991</v>
       </c>
       <c r="H132" s="28" t="s">
         <v>935</v>
@@ -32135,13 +32153,13 @@
         <v>661</v>
       </c>
       <c r="B133" s="29" t="s">
-        <v>2288</v>
+        <v>2291</v>
       </c>
       <c r="C133" s="65" t="s">
-        <v>1990</v>
+        <v>1993</v>
       </c>
       <c r="D133" s="35" t="s">
-        <v>1991</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32159,13 +32177,13 @@
         <v>667</v>
       </c>
       <c r="B135" s="29" t="s">
-        <v>2281</v>
+        <v>2284</v>
       </c>
       <c r="C135" s="65" t="s">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="D135" s="35" t="s">
-        <v>1979</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32173,13 +32191,13 @@
         <v>667</v>
       </c>
       <c r="B136" s="29" t="s">
-        <v>2289</v>
+        <v>2292</v>
       </c>
       <c r="C136" s="65" t="s">
-        <v>2290</v>
+        <v>2293</v>
       </c>
       <c r="D136" s="35" t="s">
-        <v>2291</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32187,13 +32205,13 @@
         <v>667</v>
       </c>
       <c r="B137" s="29" t="s">
-        <v>2287</v>
+        <v>2290</v>
       </c>
       <c r="C137" s="65" t="s">
-        <v>1987</v>
+        <v>1990</v>
       </c>
       <c r="D137" s="35" t="s">
-        <v>1988</v>
+        <v>1991</v>
       </c>
       <c r="H137" s="28" t="s">
         <v>935</v>
@@ -32204,13 +32222,13 @@
         <v>667</v>
       </c>
       <c r="B138" s="29" t="s">
-        <v>2288</v>
+        <v>2291</v>
       </c>
       <c r="C138" s="65" t="s">
-        <v>1990</v>
+        <v>1993</v>
       </c>
       <c r="D138" s="35" t="s">
-        <v>1991</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32218,13 +32236,13 @@
         <v>667</v>
       </c>
       <c r="B139" s="29" t="s">
-        <v>2292</v>
+        <v>2295</v>
       </c>
       <c r="C139" s="65" t="s">
-        <v>2293</v>
+        <v>2296</v>
       </c>
       <c r="D139" s="35" t="s">
-        <v>2294</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32232,13 +32250,13 @@
         <v>667</v>
       </c>
       <c r="B140" s="29" t="s">
-        <v>2295</v>
+        <v>2298</v>
       </c>
       <c r="C140" s="65" t="s">
-        <v>1993</v>
+        <v>1996</v>
       </c>
       <c r="D140" s="35" t="s">
-        <v>1994</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32248,7 +32266,7 @@
       <c r="C141" s="35"/>
       <c r="D141" s="35"/>
       <c r="G141" s="22" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32256,16 +32274,16 @@
         <v>557</v>
       </c>
       <c r="B142" s="29" t="s">
-        <v>2296</v>
+        <v>2299</v>
       </c>
       <c r="C142" s="35" t="s">
-        <v>2297</v>
+        <v>2300</v>
       </c>
       <c r="D142" s="35" t="s">
-        <v>2298</v>
+        <v>2301</v>
       </c>
       <c r="H142" s="11" t="s">
-        <v>2299</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32276,13 +32294,13 @@
         <v>1199</v>
       </c>
       <c r="C143" s="35" t="s">
-        <v>2300</v>
+        <v>2303</v>
       </c>
       <c r="D143" s="35" t="s">
-        <v>2301</v>
+        <v>2304</v>
       </c>
       <c r="H143" s="65" t="s">
-        <v>2302</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32293,10 +32311,10 @@
         <v>1141</v>
       </c>
       <c r="C144" s="35" t="s">
-        <v>2303</v>
+        <v>2306</v>
       </c>
       <c r="D144" s="35" t="s">
-        <v>2304</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32304,13 +32322,13 @@
         <v>557</v>
       </c>
       <c r="B145" s="29" t="s">
-        <v>2305</v>
+        <v>2308</v>
       </c>
       <c r="C145" s="35" t="s">
-        <v>2306</v>
+        <v>2309</v>
       </c>
       <c r="D145" s="35" t="s">
-        <v>2307</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32320,7 +32338,7 @@
       <c r="C146" s="35"/>
       <c r="D146" s="35"/>
       <c r="G146" s="29" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32328,13 +32346,13 @@
         <v>590</v>
       </c>
       <c r="B147" s="29" t="s">
-        <v>2308</v>
+        <v>2311</v>
       </c>
       <c r="C147" s="35" t="s">
-        <v>2309</v>
+        <v>2312</v>
       </c>
       <c r="D147" s="35" t="s">
-        <v>2309</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32342,13 +32360,13 @@
         <v>590</v>
       </c>
       <c r="B148" s="29" t="s">
-        <v>2310</v>
+        <v>2313</v>
       </c>
       <c r="C148" s="35" t="s">
-        <v>2311</v>
+        <v>2314</v>
       </c>
       <c r="D148" s="35" t="s">
-        <v>2312</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32358,7 +32376,7 @@
       <c r="C149" s="35"/>
       <c r="D149" s="35"/>
       <c r="G149" s="29" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32366,13 +32384,13 @@
         <v>614</v>
       </c>
       <c r="B150" s="29" t="s">
-        <v>2313</v>
+        <v>2316</v>
       </c>
       <c r="C150" s="65" t="s">
-        <v>2314</v>
+        <v>2317</v>
       </c>
       <c r="D150" s="35" t="s">
-        <v>2315</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32380,13 +32398,13 @@
         <v>614</v>
       </c>
       <c r="B151" s="29" t="s">
-        <v>2316</v>
+        <v>2319</v>
       </c>
       <c r="C151" s="65" t="s">
-        <v>2317</v>
+        <v>2320</v>
       </c>
       <c r="D151" s="35" t="s">
-        <v>2318</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32396,7 +32414,7 @@
       <c r="C152" s="35"/>
       <c r="D152" s="35"/>
       <c r="G152" s="22" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32406,7 +32424,7 @@
       <c r="C153" s="35"/>
       <c r="D153" s="35"/>
       <c r="G153" s="29" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32414,13 +32432,13 @@
         <v>621</v>
       </c>
       <c r="B154" s="29" t="s">
-        <v>2319</v>
+        <v>2322</v>
       </c>
       <c r="C154" s="65" t="s">
-        <v>2320</v>
+        <v>2323</v>
       </c>
       <c r="D154" s="35" t="s">
-        <v>2321</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32428,13 +32446,13 @@
         <v>621</v>
       </c>
       <c r="B155" s="29" t="s">
-        <v>2322</v>
+        <v>2325</v>
       </c>
       <c r="C155" s="65" t="s">
-        <v>2323</v>
+        <v>2326</v>
       </c>
       <c r="D155" s="35" t="s">
-        <v>2323</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32442,13 +32460,13 @@
         <v>621</v>
       </c>
       <c r="B156" s="29" t="s">
-        <v>2324</v>
+        <v>2327</v>
       </c>
       <c r="C156" s="65" t="s">
-        <v>2325</v>
+        <v>2328</v>
       </c>
       <c r="D156" s="65" t="s">
-        <v>2325</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32456,13 +32474,13 @@
         <v>621</v>
       </c>
       <c r="B157" s="29" t="s">
-        <v>2326</v>
+        <v>2329</v>
       </c>
       <c r="C157" s="65" t="s">
-        <v>2327</v>
+        <v>2330</v>
       </c>
       <c r="D157" s="65" t="s">
-        <v>2327</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32472,7 +32490,7 @@
       <c r="C158" s="35"/>
       <c r="D158" s="35"/>
       <c r="G158" s="22" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32482,7 +32500,7 @@
       <c r="C159" s="35"/>
       <c r="D159" s="35"/>
       <c r="G159" s="29" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32490,13 +32508,13 @@
         <v>626</v>
       </c>
       <c r="B160" s="29" t="s">
-        <v>2328</v>
+        <v>2331</v>
       </c>
       <c r="C160" s="65" t="s">
-        <v>2329</v>
+        <v>2332</v>
       </c>
       <c r="D160" s="35" t="s">
-        <v>2330</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32504,13 +32522,13 @@
         <v>626</v>
       </c>
       <c r="B161" s="29" t="s">
-        <v>2331</v>
+        <v>2334</v>
       </c>
       <c r="C161" s="65" t="s">
-        <v>2332</v>
+        <v>2335</v>
       </c>
       <c r="D161" s="35" t="s">
-        <v>2333</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32518,13 +32536,13 @@
         <v>626</v>
       </c>
       <c r="B162" s="29" t="s">
-        <v>2313</v>
+        <v>2316</v>
       </c>
       <c r="C162" s="65" t="s">
-        <v>2334</v>
+        <v>2337</v>
       </c>
       <c r="D162" s="35" t="s">
-        <v>2335</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32532,13 +32550,13 @@
         <v>626</v>
       </c>
       <c r="B163" s="29" t="s">
-        <v>2336</v>
+        <v>2339</v>
       </c>
       <c r="C163" s="65" t="s">
-        <v>2337</v>
+        <v>2340</v>
       </c>
       <c r="D163" s="65" t="s">
-        <v>2337</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32546,13 +32564,13 @@
         <v>626</v>
       </c>
       <c r="B164" s="29" t="s">
-        <v>2338</v>
+        <v>2341</v>
       </c>
       <c r="C164" s="65" t="s">
-        <v>2339</v>
+        <v>2342</v>
       </c>
       <c r="D164" s="35" t="s">
-        <v>2340</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32562,7 +32580,7 @@
       <c r="C165" s="35"/>
       <c r="D165" s="35"/>
       <c r="G165" s="22" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32572,7 +32590,7 @@
       <c r="C166" s="35"/>
       <c r="D166" s="35"/>
       <c r="G166" s="29" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32580,13 +32598,13 @@
         <v>762</v>
       </c>
       <c r="B167" s="22" t="s">
-        <v>2287</v>
+        <v>2290</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>1928</v>
+        <v>1931</v>
       </c>
       <c r="E167" s="22"/>
       <c r="F167" s="22"/>
@@ -32599,13 +32617,13 @@
         <v>762</v>
       </c>
       <c r="B168" s="22" t="s">
-        <v>2288</v>
+        <v>2291</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>1946</v>
+        <v>1949</v>
       </c>
       <c r="E168" s="22"/>
       <c r="F168" s="22"/>
@@ -32618,13 +32636,13 @@
         <v>762</v>
       </c>
       <c r="B169" s="22" t="s">
-        <v>2295</v>
+        <v>2298</v>
       </c>
       <c r="C169" s="65" t="s">
-        <v>2341</v>
+        <v>2344</v>
       </c>
       <c r="D169" s="35" t="s">
-        <v>2342</v>
+        <v>2345</v>
       </c>
       <c r="E169" s="22"/>
       <c r="F169" s="22"/>
@@ -32637,13 +32655,13 @@
         <v>762</v>
       </c>
       <c r="B170" s="22" t="s">
-        <v>2281</v>
+        <v>2284</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>1880</v>
+        <v>1883</v>
       </c>
       <c r="D170" s="10" t="s">
-        <v>1881</v>
+        <v>1884</v>
       </c>
       <c r="E170" s="22"/>
       <c r="F170" s="22"/>
@@ -32656,13 +32674,13 @@
         <v>762</v>
       </c>
       <c r="B171" s="22" t="s">
-        <v>2343</v>
+        <v>2346</v>
       </c>
       <c r="C171" s="10" t="s">
-        <v>1883</v>
+        <v>1886</v>
       </c>
       <c r="D171" s="10" t="s">
-        <v>1884</v>
+        <v>1887</v>
       </c>
       <c r="E171" s="22"/>
       <c r="F171" s="22"/>
@@ -32678,10 +32696,10 @@
         <v>212</v>
       </c>
       <c r="C172" s="28" t="s">
-        <v>2344</v>
+        <v>2347</v>
       </c>
       <c r="D172" s="65" t="s">
-        <v>2345</v>
+        <v>2348</v>
       </c>
       <c r="E172" s="22"/>
       <c r="F172" s="22"/>
@@ -32696,13 +32714,13 @@
         <v>762</v>
       </c>
       <c r="B173" s="22" t="s">
-        <v>2346</v>
+        <v>2349</v>
       </c>
       <c r="C173" s="28" t="s">
-        <v>2347</v>
+        <v>2350</v>
       </c>
       <c r="D173" s="65" t="s">
-        <v>2348</v>
+        <v>2351</v>
       </c>
       <c r="E173" s="22"/>
       <c r="F173" s="22"/>
@@ -32717,13 +32735,13 @@
         <v>112</v>
       </c>
       <c r="B174" s="22" t="s">
-        <v>2349</v>
+        <v>2352</v>
       </c>
       <c r="C174" s="28" t="s">
-        <v>2350</v>
+        <v>2353</v>
       </c>
       <c r="D174" s="65" t="s">
-        <v>2351</v>
+        <v>2354</v>
       </c>
       <c r="E174" s="22"/>
       <c r="F174" s="22"/>
@@ -32736,13 +32754,13 @@
         <v>112</v>
       </c>
       <c r="B175" s="22" t="s">
-        <v>2352</v>
+        <v>2355</v>
       </c>
       <c r="C175" s="28" t="s">
-        <v>2353</v>
+        <v>2356</v>
       </c>
       <c r="D175" s="65" t="s">
-        <v>2354</v>
+        <v>2357</v>
       </c>
       <c r="E175" s="22"/>
       <c r="F175" s="22"/>
@@ -32796,10 +32814,10 @@
         <v>2</v>
       </c>
       <c r="C178" s="74" t="s">
-        <v>2355</v>
+        <v>2358</v>
       </c>
       <c r="D178" s="74" t="s">
-        <v>2355</v>
+        <v>2358</v>
       </c>
       <c r="E178" s="22"/>
       <c r="F178" s="22"/>
@@ -32815,10 +32833,10 @@
         <v>1141</v>
       </c>
       <c r="C179" s="28" t="s">
-        <v>2356</v>
+        <v>2359</v>
       </c>
       <c r="D179" s="10" t="s">
-        <v>2357</v>
+        <v>2360</v>
       </c>
       <c r="E179" s="22"/>
       <c r="F179" s="22"/>
@@ -32834,10 +32852,10 @@
         <v>1199</v>
       </c>
       <c r="C180" s="28" t="s">
-        <v>2358</v>
+        <v>2361</v>
       </c>
       <c r="D180" s="10" t="s">
-        <v>2359</v>
+        <v>2362</v>
       </c>
       <c r="E180" s="22"/>
       <c r="F180" s="22"/>
@@ -32855,7 +32873,7 @@
       <c r="E181" s="22"/>
       <c r="F181" s="22"/>
       <c r="G181" s="22" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="H181" s="22"/>
       <c r="I181" s="22"/>
@@ -32865,13 +32883,13 @@
         <v>229</v>
       </c>
       <c r="B182" s="22" t="s">
-        <v>2360</v>
+        <v>2363</v>
       </c>
       <c r="C182" s="21" t="s">
-        <v>2361</v>
+        <v>2364</v>
       </c>
       <c r="D182" s="65" t="s">
-        <v>2362</v>
+        <v>2365</v>
       </c>
       <c r="E182" s="22"/>
       <c r="F182" s="22"/>
@@ -32886,13 +32904,13 @@
         <v>229</v>
       </c>
       <c r="B183" s="22" t="s">
-        <v>2363</v>
+        <v>2366</v>
       </c>
       <c r="C183" s="21" t="s">
-        <v>2364</v>
+        <v>2367</v>
       </c>
       <c r="D183" s="65" t="s">
-        <v>2365</v>
+        <v>2368</v>
       </c>
       <c r="E183" s="22"/>
       <c r="F183" s="22"/>
@@ -32907,13 +32925,13 @@
         <v>229</v>
       </c>
       <c r="B184" s="22" t="s">
-        <v>2366</v>
+        <v>2369</v>
       </c>
       <c r="C184" s="21" t="s">
-        <v>2367</v>
+        <v>2370</v>
       </c>
       <c r="D184" s="65" t="s">
-        <v>2368</v>
+        <v>2371</v>
       </c>
       <c r="E184" s="22"/>
       <c r="F184" s="22"/>
@@ -32928,13 +32946,13 @@
         <v>229</v>
       </c>
       <c r="B185" s="22" t="s">
-        <v>2369</v>
+        <v>2372</v>
       </c>
       <c r="C185" s="21" t="s">
-        <v>2370</v>
+        <v>2373</v>
       </c>
       <c r="D185" s="65" t="s">
-        <v>2371</v>
+        <v>2374</v>
       </c>
       <c r="E185" s="22"/>
       <c r="F185" s="22"/>
@@ -32949,13 +32967,13 @@
         <v>229</v>
       </c>
       <c r="B186" s="22" t="s">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="C186" s="21" t="s">
-        <v>2373</v>
+        <v>2376</v>
       </c>
       <c r="D186" s="65" t="s">
-        <v>2374</v>
+        <v>2377</v>
       </c>
       <c r="E186" s="22"/>
       <c r="F186" s="22"/>
@@ -32970,13 +32988,13 @@
         <v>229</v>
       </c>
       <c r="B187" s="22" t="s">
-        <v>2375</v>
+        <v>2378</v>
       </c>
       <c r="C187" s="21" t="s">
-        <v>2376</v>
+        <v>2379</v>
       </c>
       <c r="D187" s="65" t="s">
-        <v>2377</v>
+        <v>2380</v>
       </c>
       <c r="E187" s="22"/>
       <c r="F187" s="22"/>
@@ -32991,13 +33009,13 @@
         <v>229</v>
       </c>
       <c r="B188" s="22" t="s">
-        <v>2378</v>
+        <v>2381</v>
       </c>
       <c r="C188" s="21" t="s">
-        <v>2379</v>
+        <v>2382</v>
       </c>
       <c r="D188" s="65" t="s">
-        <v>2380</v>
+        <v>2383</v>
       </c>
       <c r="E188" s="22"/>
       <c r="F188" s="22"/>
@@ -33012,13 +33030,13 @@
         <v>229</v>
       </c>
       <c r="B189" s="22" t="s">
-        <v>2381</v>
+        <v>2384</v>
       </c>
       <c r="C189" s="21" t="s">
-        <v>2382</v>
+        <v>2385</v>
       </c>
       <c r="D189" s="65" t="s">
-        <v>2383</v>
+        <v>2386</v>
       </c>
       <c r="E189" s="22"/>
       <c r="F189" s="22"/>
@@ -33033,13 +33051,13 @@
         <v>229</v>
       </c>
       <c r="B190" s="22" t="s">
-        <v>2384</v>
+        <v>2387</v>
       </c>
       <c r="C190" s="21" t="s">
-        <v>2385</v>
+        <v>2388</v>
       </c>
       <c r="D190" s="65" t="s">
-        <v>2386</v>
+        <v>2389</v>
       </c>
       <c r="E190" s="22"/>
       <c r="F190" s="22"/>
@@ -33057,10 +33075,10 @@
         <v>212</v>
       </c>
       <c r="C191" s="21" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
       <c r="D191" s="65" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="E191" s="22"/>
       <c r="F191" s="22"/>
@@ -33090,13 +33108,13 @@
         <v>241</v>
       </c>
       <c r="B193" s="22" t="s">
-        <v>2387</v>
+        <v>2390</v>
       </c>
       <c r="C193" s="21" t="s">
-        <v>2388</v>
+        <v>2391</v>
       </c>
       <c r="D193" s="65" t="s">
-        <v>2389</v>
+        <v>2392</v>
       </c>
       <c r="E193" s="22"/>
       <c r="F193" s="22"/>
@@ -33111,13 +33129,13 @@
         <v>241</v>
       </c>
       <c r="B194" s="22" t="s">
-        <v>2390</v>
+        <v>2393</v>
       </c>
       <c r="C194" s="21" t="s">
-        <v>2391</v>
+        <v>2394</v>
       </c>
       <c r="D194" s="65" t="s">
-        <v>2392</v>
+        <v>2395</v>
       </c>
       <c r="E194" s="22"/>
       <c r="F194" s="22"/>
@@ -33132,13 +33150,13 @@
         <v>241</v>
       </c>
       <c r="B195" s="22" t="s">
-        <v>2393</v>
+        <v>2396</v>
       </c>
       <c r="C195" s="21" t="s">
-        <v>2394</v>
+        <v>2397</v>
       </c>
       <c r="D195" s="65" t="s">
-        <v>2395</v>
+        <v>2398</v>
       </c>
       <c r="E195" s="22"/>
       <c r="F195" s="22"/>
@@ -33153,13 +33171,13 @@
         <v>241</v>
       </c>
       <c r="B196" s="22" t="s">
-        <v>2396</v>
+        <v>2399</v>
       </c>
       <c r="C196" s="21" t="s">
-        <v>2397</v>
+        <v>2400</v>
       </c>
       <c r="D196" s="65" t="s">
-        <v>2398</v>
+        <v>2401</v>
       </c>
       <c r="E196" s="22"/>
       <c r="F196" s="22"/>
@@ -33174,13 +33192,13 @@
         <v>241</v>
       </c>
       <c r="B197" s="22" t="s">
-        <v>2399</v>
+        <v>2402</v>
       </c>
       <c r="C197" s="21" t="s">
-        <v>2400</v>
+        <v>2403</v>
       </c>
       <c r="D197" s="65" t="s">
-        <v>2401</v>
+        <v>2404</v>
       </c>
       <c r="E197" s="22"/>
       <c r="F197" s="22"/>
@@ -33195,13 +33213,13 @@
         <v>241</v>
       </c>
       <c r="B198" s="22" t="s">
-        <v>2402</v>
+        <v>2405</v>
       </c>
       <c r="C198" s="21" t="s">
-        <v>2403</v>
+        <v>2406</v>
       </c>
       <c r="D198" s="65" t="s">
-        <v>2404</v>
+        <v>2407</v>
       </c>
       <c r="E198" s="22"/>
       <c r="F198" s="22"/>
@@ -33216,13 +33234,13 @@
         <v>241</v>
       </c>
       <c r="B199" s="22" t="s">
-        <v>2405</v>
+        <v>2408</v>
       </c>
       <c r="C199" s="21" t="s">
-        <v>2406</v>
+        <v>2409</v>
       </c>
       <c r="D199" s="65" t="s">
-        <v>2407</v>
+        <v>2410</v>
       </c>
       <c r="E199" s="22"/>
       <c r="F199" s="22"/>
@@ -33240,10 +33258,10 @@
         <v>1181</v>
       </c>
       <c r="C200" s="21" t="s">
-        <v>2408</v>
+        <v>2411</v>
       </c>
       <c r="D200" s="65" t="s">
-        <v>2409</v>
+        <v>2412</v>
       </c>
       <c r="E200" s="22"/>
       <c r="F200" s="22"/>
@@ -33260,10 +33278,10 @@
         <v>212</v>
       </c>
       <c r="C201" s="21" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
       <c r="D201" s="65" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="E201" s="22"/>
       <c r="F201" s="22"/>
@@ -33281,10 +33299,10 @@
         <v>1145</v>
       </c>
       <c r="C202" s="22" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="D202" s="22" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="E202" s="22"/>
       <c r="F202" s="22"/>
@@ -33299,18 +33317,18 @@
         <v>270</v>
       </c>
       <c r="B203" s="22" t="s">
-        <v>2410</v>
+        <v>2413</v>
       </c>
       <c r="C203" s="21" t="s">
-        <v>2411</v>
+        <v>2414</v>
       </c>
       <c r="D203" s="65" t="s">
-        <v>2412</v>
+        <v>2415</v>
       </c>
       <c r="E203" s="22"/>
       <c r="F203" s="22"/>
       <c r="G203" s="22"/>
-      <c r="H203" s="106"/>
+      <c r="H203" s="105"/>
       <c r="I203" s="22"/>
     </row>
     <row r="204" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33318,13 +33336,13 @@
         <v>270</v>
       </c>
       <c r="B204" s="22" t="s">
-        <v>2413</v>
+        <v>2416</v>
       </c>
       <c r="C204" s="21" t="s">
-        <v>2414</v>
+        <v>2417</v>
       </c>
       <c r="D204" s="65" t="s">
-        <v>2415</v>
+        <v>2418</v>
       </c>
       <c r="E204" s="22"/>
       <c r="F204" s="22"/>
@@ -33337,13 +33355,13 @@
         <v>270</v>
       </c>
       <c r="B205" s="22" t="s">
-        <v>2416</v>
+        <v>2419</v>
       </c>
       <c r="C205" s="21" t="s">
-        <v>2417</v>
+        <v>2420</v>
       </c>
       <c r="D205" s="65" t="s">
-        <v>2418</v>
+        <v>2421</v>
       </c>
       <c r="E205" s="22"/>
       <c r="F205" s="22"/>
@@ -33356,13 +33374,13 @@
         <v>270</v>
       </c>
       <c r="B206" s="22" t="s">
-        <v>2419</v>
+        <v>2422</v>
       </c>
       <c r="C206" s="21" t="s">
-        <v>2420</v>
+        <v>2423</v>
       </c>
       <c r="D206" s="65" t="s">
-        <v>2421</v>
+        <v>2424</v>
       </c>
       <c r="E206" s="22"/>
       <c r="F206" s="22"/>
@@ -33375,13 +33393,13 @@
         <v>270</v>
       </c>
       <c r="B207" s="22" t="s">
-        <v>2422</v>
+        <v>2425</v>
       </c>
       <c r="C207" s="21" t="s">
-        <v>2423</v>
+        <v>2426</v>
       </c>
       <c r="D207" s="65" t="s">
-        <v>2424</v>
+        <v>2427</v>
       </c>
       <c r="E207" s="22"/>
       <c r="F207" s="22"/>
@@ -33394,18 +33412,18 @@
         <v>277</v>
       </c>
       <c r="B208" s="22" t="s">
-        <v>2410</v>
+        <v>2413</v>
       </c>
       <c r="C208" s="21" t="s">
-        <v>2411</v>
+        <v>2414</v>
       </c>
       <c r="D208" s="65" t="s">
-        <v>2412</v>
+        <v>2415</v>
       </c>
       <c r="E208" s="22"/>
       <c r="F208" s="22"/>
       <c r="G208" s="22"/>
-      <c r="H208" s="106" t="s">
+      <c r="H208" s="105" t="s">
         <v>1197</v>
       </c>
       <c r="I208" s="22"/>
@@ -33415,13 +33433,13 @@
         <v>277</v>
       </c>
       <c r="B209" s="22" t="s">
-        <v>2413</v>
+        <v>2416</v>
       </c>
       <c r="C209" s="21" t="s">
-        <v>2414</v>
+        <v>2417</v>
       </c>
       <c r="D209" s="65" t="s">
-        <v>2415</v>
+        <v>2418</v>
       </c>
       <c r="E209" s="22"/>
       <c r="F209" s="22"/>
@@ -33434,13 +33452,13 @@
         <v>277</v>
       </c>
       <c r="B210" s="22" t="s">
-        <v>2416</v>
+        <v>2419</v>
       </c>
       <c r="C210" s="21" t="s">
-        <v>2417</v>
+        <v>2420</v>
       </c>
       <c r="D210" s="65" t="s">
-        <v>2418</v>
+        <v>2421</v>
       </c>
       <c r="E210" s="22"/>
       <c r="F210" s="22"/>
@@ -33453,13 +33471,13 @@
         <v>277</v>
       </c>
       <c r="B211" s="22" t="s">
-        <v>2419</v>
+        <v>2422</v>
       </c>
       <c r="C211" s="21" t="s">
-        <v>2420</v>
+        <v>2423</v>
       </c>
       <c r="D211" s="65" t="s">
-        <v>2421</v>
+        <v>2424</v>
       </c>
       <c r="E211" s="22"/>
       <c r="F211" s="22"/>
@@ -33472,13 +33490,13 @@
         <v>277</v>
       </c>
       <c r="B212" s="22" t="s">
-        <v>2422</v>
+        <v>2425</v>
       </c>
       <c r="C212" s="21" t="s">
-        <v>2423</v>
+        <v>2426</v>
       </c>
       <c r="D212" s="65" t="s">
-        <v>2424</v>
+        <v>2427</v>
       </c>
       <c r="E212" s="22"/>
       <c r="F212" s="22"/>
@@ -33491,13 +33509,13 @@
         <v>830</v>
       </c>
       <c r="B213" s="29" t="s">
-        <v>2281</v>
+        <v>2284</v>
       </c>
       <c r="C213" s="29" t="s">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="D213" s="29" t="s">
-        <v>1979</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33505,13 +33523,13 @@
         <v>830</v>
       </c>
       <c r="B214" s="29" t="s">
-        <v>2289</v>
+        <v>2292</v>
       </c>
       <c r="C214" s="29" t="s">
-        <v>2290</v>
+        <v>2293</v>
       </c>
       <c r="D214" s="29" t="s">
-        <v>2291</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33519,13 +33537,13 @@
         <v>830</v>
       </c>
       <c r="B215" s="29" t="s">
-        <v>2425</v>
+        <v>2428</v>
       </c>
       <c r="C215" s="29" t="s">
-        <v>2426</v>
+        <v>2429</v>
       </c>
       <c r="D215" s="29" t="s">
-        <v>2427</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33533,13 +33551,13 @@
         <v>830</v>
       </c>
       <c r="B216" s="29" t="s">
-        <v>2295</v>
+        <v>2298</v>
       </c>
       <c r="C216" s="29" t="s">
-        <v>2428</v>
+        <v>2431</v>
       </c>
       <c r="D216" s="29" t="s">
-        <v>2429</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33547,7 +33565,7 @@
         <v>830</v>
       </c>
       <c r="G217" s="29" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33555,13 +33573,13 @@
         <v>855</v>
       </c>
       <c r="B218" s="29" t="s">
-        <v>2430</v>
+        <v>2433</v>
       </c>
       <c r="C218" s="29" t="s">
-        <v>2431</v>
+        <v>2434</v>
       </c>
       <c r="D218" s="29" t="s">
-        <v>2432</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33569,13 +33587,13 @@
         <v>855</v>
       </c>
       <c r="B219" s="29" t="s">
-        <v>2433</v>
+        <v>2436</v>
       </c>
       <c r="C219" s="29" t="s">
-        <v>2434</v>
+        <v>2437</v>
       </c>
       <c r="D219" s="29" t="s">
-        <v>2435</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33583,13 +33601,13 @@
         <v>855</v>
       </c>
       <c r="B220" s="29" t="s">
-        <v>2436</v>
+        <v>2439</v>
       </c>
       <c r="C220" s="29" t="s">
-        <v>2437</v>
+        <v>2440</v>
       </c>
       <c r="D220" s="29" t="s">
-        <v>2438</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33597,13 +33615,13 @@
         <v>855</v>
       </c>
       <c r="B221" s="29" t="s">
-        <v>2439</v>
+        <v>2442</v>
       </c>
       <c r="C221" s="29" t="s">
-        <v>2440</v>
+        <v>2443</v>
       </c>
       <c r="D221" s="29" t="s">
-        <v>2441</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33611,13 +33629,13 @@
         <v>855</v>
       </c>
       <c r="B222" s="29" t="s">
-        <v>2442</v>
+        <v>2445</v>
       </c>
       <c r="C222" s="29" t="s">
-        <v>2443</v>
+        <v>2446</v>
       </c>
       <c r="D222" s="29" t="s">
-        <v>2444</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33625,13 +33643,13 @@
         <v>855</v>
       </c>
       <c r="B223" s="29" t="s">
-        <v>2445</v>
+        <v>2448</v>
       </c>
       <c r="C223" s="29" t="s">
-        <v>2446</v>
+        <v>2449</v>
       </c>
       <c r="D223" s="29" t="s">
-        <v>2447</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33642,10 +33660,10 @@
         <v>212</v>
       </c>
       <c r="C224" s="29" t="s">
-        <v>2448</v>
+        <v>2451</v>
       </c>
       <c r="D224" s="29" t="s">
-        <v>2449</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33653,13 +33671,13 @@
         <v>859</v>
       </c>
       <c r="B225" s="29" t="s">
-        <v>2281</v>
+        <v>2284</v>
       </c>
       <c r="C225" s="29" t="s">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="D225" s="29" t="s">
-        <v>1979</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33667,13 +33685,13 @@
         <v>859</v>
       </c>
       <c r="B226" s="29" t="s">
-        <v>2289</v>
+        <v>2292</v>
       </c>
       <c r="C226" s="29" t="s">
-        <v>2290</v>
+        <v>2293</v>
       </c>
       <c r="D226" s="29" t="s">
-        <v>2291</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33681,13 +33699,13 @@
         <v>859</v>
       </c>
       <c r="B227" s="29" t="s">
-        <v>2287</v>
+        <v>2290</v>
       </c>
       <c r="C227" s="29" t="s">
-        <v>2450</v>
+        <v>2453</v>
       </c>
       <c r="D227" s="29" t="s">
-        <v>2451</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33695,13 +33713,13 @@
         <v>859</v>
       </c>
       <c r="B228" s="29" t="s">
-        <v>2288</v>
+        <v>2291</v>
       </c>
       <c r="C228" s="29" t="s">
-        <v>2452</v>
+        <v>2455</v>
       </c>
       <c r="D228" s="29" t="s">
-        <v>2453</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="229" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33709,13 +33727,13 @@
         <v>859</v>
       </c>
       <c r="B229" s="29" t="s">
-        <v>2295</v>
+        <v>2298</v>
       </c>
       <c r="C229" s="29" t="s">
-        <v>2428</v>
+        <v>2431</v>
       </c>
       <c r="D229" s="29" t="s">
-        <v>2429</v>
+        <v>2432</v>
       </c>
       <c r="E229" s="29"/>
       <c r="F229" s="29"/>
@@ -33731,10 +33749,10 @@
         <v>212</v>
       </c>
       <c r="C230" s="29" t="s">
-        <v>2454</v>
+        <v>2457</v>
       </c>
       <c r="D230" s="29" t="s">
-        <v>2455</v>
+        <v>2458</v>
       </c>
       <c r="E230" s="29"/>
       <c r="F230" s="29"/>
@@ -33750,10 +33768,10 @@
         <v>1232</v>
       </c>
       <c r="C231" s="65" t="s">
-        <v>2456</v>
+        <v>2459</v>
       </c>
       <c r="D231" s="65" t="s">
-        <v>2457</v>
+        <v>2460</v>
       </c>
       <c r="E231" s="29"/>
       <c r="F231" s="29"/>
@@ -33766,13 +33784,13 @@
         <v>1025</v>
       </c>
       <c r="B232" s="29" t="s">
-        <v>2458</v>
+        <v>2461</v>
       </c>
       <c r="C232" s="65" t="s">
-        <v>2459</v>
+        <v>2462</v>
       </c>
       <c r="D232" s="65" t="s">
-        <v>2460</v>
+        <v>2463</v>
       </c>
       <c r="E232" s="29"/>
       <c r="F232" s="29"/>
@@ -33787,13 +33805,13 @@
         <v>1025</v>
       </c>
       <c r="B233" s="29" t="s">
-        <v>2461</v>
+        <v>2464</v>
       </c>
       <c r="C233" s="65" t="s">
-        <v>2462</v>
+        <v>2465</v>
       </c>
       <c r="D233" s="65" t="s">
-        <v>2463</v>
+        <v>2466</v>
       </c>
       <c r="E233" s="29"/>
       <c r="F233" s="29"/>
@@ -33808,13 +33826,13 @@
         <v>1025</v>
       </c>
       <c r="B234" s="29" t="s">
-        <v>2464</v>
+        <v>2467</v>
       </c>
       <c r="C234" s="65" t="s">
-        <v>2465</v>
+        <v>2468</v>
       </c>
       <c r="D234" s="28" t="s">
-        <v>2466</v>
+        <v>2469</v>
       </c>
       <c r="E234" s="29"/>
       <c r="F234" s="29"/>
@@ -33829,13 +33847,13 @@
         <v>1025</v>
       </c>
       <c r="B235" s="29" t="s">
-        <v>2467</v>
+        <v>2470</v>
       </c>
       <c r="C235" s="65" t="s">
-        <v>2468</v>
+        <v>2471</v>
       </c>
       <c r="D235" s="21" t="s">
-        <v>2469</v>
+        <v>2472</v>
       </c>
       <c r="E235" s="29"/>
       <c r="F235" s="29"/>
@@ -33848,13 +33866,13 @@
         <v>1031</v>
       </c>
       <c r="B236" s="29" t="s">
-        <v>2470</v>
+        <v>2473</v>
       </c>
       <c r="C236" s="65" t="s">
-        <v>2471</v>
+        <v>2474</v>
       </c>
       <c r="D236" s="65" t="s">
-        <v>2472</v>
+        <v>2475</v>
       </c>
       <c r="E236" s="29"/>
       <c r="F236" s="29"/>
@@ -33869,13 +33887,13 @@
         <v>1031</v>
       </c>
       <c r="B237" s="29" t="s">
-        <v>2473</v>
+        <v>2476</v>
       </c>
       <c r="C237" s="65" t="s">
-        <v>2474</v>
+        <v>2477</v>
       </c>
       <c r="D237" s="65" t="s">
-        <v>2475</v>
+        <v>2478</v>
       </c>
       <c r="E237" s="29"/>
       <c r="F237" s="29"/>
@@ -33890,13 +33908,13 @@
         <v>1031</v>
       </c>
       <c r="B238" s="29" t="s">
-        <v>2476</v>
+        <v>2479</v>
       </c>
       <c r="C238" s="65" t="s">
-        <v>2477</v>
+        <v>2480</v>
       </c>
       <c r="D238" s="65" t="s">
-        <v>2478</v>
+        <v>2481</v>
       </c>
       <c r="E238" s="29"/>
       <c r="F238" s="29"/>
@@ -33906,16 +33924,16 @@
     </row>
     <row r="239" s="2" customFormat="true" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="11" t="s">
-        <v>2479</v>
+        <v>2482</v>
       </c>
       <c r="B239" s="29" t="s">
         <v>1141</v>
       </c>
       <c r="C239" s="28" t="s">
-        <v>2480</v>
+        <v>2483</v>
       </c>
       <c r="D239" s="65" t="s">
-        <v>2481</v>
+        <v>2484</v>
       </c>
       <c r="E239" s="29"/>
       <c r="F239" s="29"/>
@@ -33925,16 +33943,16 @@
     </row>
     <row r="240" s="2" customFormat="true" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="11" t="s">
-        <v>2479</v>
+        <v>2482</v>
       </c>
       <c r="B240" s="29" t="s">
         <v>1199</v>
       </c>
       <c r="C240" s="28" t="s">
-        <v>2482</v>
+        <v>2485</v>
       </c>
       <c r="D240" s="21" t="s">
-        <v>2483</v>
+        <v>2486</v>
       </c>
       <c r="E240" s="29"/>
       <c r="F240" s="29"/>
@@ -33947,13 +33965,13 @@
         <v>1063</v>
       </c>
       <c r="B241" s="29" t="s">
-        <v>2484</v>
+        <v>2487</v>
       </c>
       <c r="C241" s="65" t="s">
-        <v>2485</v>
+        <v>2488</v>
       </c>
       <c r="D241" s="28" t="s">
-        <v>2486</v>
+        <v>2489</v>
       </c>
       <c r="E241" s="29"/>
       <c r="F241" s="29"/>
@@ -33966,13 +33984,13 @@
         <v>1063</v>
       </c>
       <c r="B242" s="29" t="s">
-        <v>2487</v>
+        <v>2490</v>
       </c>
       <c r="C242" s="65" t="s">
-        <v>2488</v>
+        <v>2491</v>
       </c>
       <c r="D242" s="28" t="s">
-        <v>2489</v>
+        <v>2492</v>
       </c>
       <c r="E242" s="29"/>
       <c r="F242" s="29"/>
@@ -33985,13 +34003,13 @@
         <v>1063</v>
       </c>
       <c r="B243" s="29" t="s">
-        <v>2490</v>
+        <v>2493</v>
       </c>
       <c r="C243" s="65" t="s">
-        <v>2491</v>
+        <v>2494</v>
       </c>
       <c r="D243" s="28" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="E243" s="29"/>
       <c r="F243" s="29"/>
@@ -34004,13 +34022,13 @@
         <v>1063</v>
       </c>
       <c r="B244" s="29" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="C244" s="65" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="D244" s="28" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="E244" s="29"/>
       <c r="F244" s="29"/>
@@ -34023,13 +34041,13 @@
         <v>1063</v>
       </c>
       <c r="B245" s="29" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="C245" s="65" t="s">
-        <v>2497</v>
+        <v>2500</v>
       </c>
       <c r="D245" s="28" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="E245" s="29"/>
       <c r="F245" s="29"/>
@@ -34042,13 +34060,13 @@
         <v>1063</v>
       </c>
       <c r="B246" s="29" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="C246" s="65" t="s">
-        <v>2500</v>
+        <v>2503</v>
       </c>
       <c r="D246" s="28" t="s">
-        <v>2501</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="247" s="2" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34061,7 +34079,7 @@
       <c r="E247" s="29"/>
       <c r="F247" s="29"/>
       <c r="G247" s="22" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="H247" s="29"/>
       <c r="I247" s="29"/>
@@ -34071,13 +34089,13 @@
         <v>918</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>2502</v>
+        <v>2505</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>2503</v>
+        <v>2506</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>2504</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="249" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34085,13 +34103,13 @@
         <v>918</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>2416</v>
+        <v>2419</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>2505</v>
+        <v>2508</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>2506</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="250" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34099,13 +34117,13 @@
         <v>918</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>2507</v>
+        <v>2510</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>2508</v>
+        <v>2511</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>2509</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="251" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34113,13 +34131,13 @@
         <v>918</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>2510</v>
+        <v>2513</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>2511</v>
+        <v>2514</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>2512</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="252" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34127,13 +34145,13 @@
         <v>918</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>2513</v>
+        <v>2516</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>2514</v>
+        <v>2517</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>2515</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="253" s="2" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34144,10 +34162,10 @@
         <v>-2</v>
       </c>
       <c r="C253" s="35" t="s">
-        <v>2516</v>
+        <v>2519</v>
       </c>
       <c r="D253" s="35" t="s">
-        <v>2517</v>
+        <v>2520</v>
       </c>
       <c r="E253" s="29"/>
       <c r="F253" s="29"/>
@@ -34163,10 +34181,10 @@
         <v>-1</v>
       </c>
       <c r="C254" s="35" t="s">
-        <v>2518</v>
+        <v>2521</v>
       </c>
       <c r="D254" s="35" t="s">
-        <v>2519</v>
+        <v>2522</v>
       </c>
       <c r="E254" s="29"/>
       <c r="F254" s="29"/>
@@ -34182,10 +34200,10 @@
         <v>0</v>
       </c>
       <c r="C255" s="35" t="s">
-        <v>2520</v>
+        <v>2523</v>
       </c>
       <c r="D255" s="35" t="s">
-        <v>2521</v>
+        <v>2524</v>
       </c>
       <c r="E255" s="29"/>
       <c r="F255" s="29"/>
@@ -34201,10 +34219,10 @@
         <v>1</v>
       </c>
       <c r="C256" s="35" t="s">
-        <v>2522</v>
+        <v>2525</v>
       </c>
       <c r="D256" s="35" t="s">
-        <v>2523</v>
+        <v>2526</v>
       </c>
       <c r="E256" s="29"/>
       <c r="F256" s="29"/>
@@ -34220,10 +34238,10 @@
         <v>2</v>
       </c>
       <c r="C257" s="35" t="s">
-        <v>2524</v>
+        <v>2527</v>
       </c>
       <c r="D257" s="35" t="s">
-        <v>2525</v>
+        <v>2528</v>
       </c>
       <c r="E257" s="29"/>
       <c r="F257" s="29"/>
@@ -34239,10 +34257,10 @@
         <v>0</v>
       </c>
       <c r="C258" s="21" t="s">
-        <v>2526</v>
+        <v>2529</v>
       </c>
       <c r="D258" s="35" t="s">
-        <v>2527</v>
+        <v>2530</v>
       </c>
       <c r="E258" s="29"/>
       <c r="F258" s="29"/>
@@ -34258,10 +34276,10 @@
         <v>1</v>
       </c>
       <c r="C259" s="21" t="s">
-        <v>2528</v>
+        <v>2531</v>
       </c>
       <c r="D259" s="28" t="s">
-        <v>2529</v>
+        <v>2532</v>
       </c>
       <c r="E259" s="29"/>
       <c r="F259" s="29"/>
@@ -34277,10 +34295,10 @@
         <v>2</v>
       </c>
       <c r="C260" s="21" t="s">
-        <v>2530</v>
+        <v>2533</v>
       </c>
       <c r="D260" s="28" t="s">
-        <v>2531</v>
+        <v>2534</v>
       </c>
       <c r="E260" s="29"/>
       <c r="F260" s="29"/>
@@ -34296,10 +34314,10 @@
         <v>3</v>
       </c>
       <c r="C261" s="21" t="s">
-        <v>2532</v>
+        <v>2535</v>
       </c>
       <c r="D261" s="28" t="s">
-        <v>2533</v>
+        <v>2536</v>
       </c>
       <c r="E261" s="29"/>
       <c r="F261" s="29"/>
@@ -34315,10 +34333,10 @@
         <v>4</v>
       </c>
       <c r="C262" s="21" t="s">
-        <v>2534</v>
+        <v>2537</v>
       </c>
       <c r="D262" s="28" t="s">
-        <v>2535</v>
+        <v>2538</v>
       </c>
       <c r="E262" s="29"/>
       <c r="F262" s="29"/>
@@ -34334,10 +34352,10 @@
         <v>-1</v>
       </c>
       <c r="C263" s="21" t="s">
-        <v>2536</v>
+        <v>2539</v>
       </c>
       <c r="D263" s="28" t="s">
-        <v>2537</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4631" uniqueCount="2541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4635" uniqueCount="2544">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -1964,16 +1964,16 @@
     <t xml:space="preserve">_previousDepartureTime</t>
   </si>
   <si>
-    <t xml:space="preserve">À quelle heure {{nickname}} a-t-{{gender:il/elle/iel/il(-elle)}} quitté le lieu précédent ({{previousVisitedPlaceDescription}})?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At what time did {{nickname}} leave the previous location ({{previousVisitedPlaceDescription}})?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">À quelle heure avez-vous quitté le lieu précédent ({{previousVisitedPlaceDescription}})?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At what time did you leave the previous location ({{previousVisitedPlaceDescription}})?</t>
+    <t xml:space="preserve">À quelle heure {{nickname}} a-t-{{gender:il/elle/iel/il(-elle)}} quitté le lieu précédent ({{previousVisitedPlaceDescription}})?{{reminderText}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At what time did {{nickname}} leave the previous location ({{previousVisitedPlaceDescription}})?{{reminderText}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À quelle heure avez-vous quitté le lieu précédent ({{previousVisitedPlaceDescription}})?{{reminderText}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At what time did you leave the previous location ({{previousVisitedPlaceDescription}})?{{reminderText}}</t>
   </si>
   <si>
     <t xml:space="preserve">visitedPlaceArrivalTime</t>
@@ -2003,19 +2003,19 @@
     <t xml:space="preserve">nextPlaceCategory</t>
   </si>
   <si>
-    <t xml:space="preserve">Après avoir été {{atPlace}}, {{nickname}} est…
+    <t xml:space="preserve">Après avoir été {{atPlace}}, {{nickname}} est…{{reminderText}}
 __Si {{nickname}} a quitté le lieu après 4h du matin le lendemain, merci de considérer pour l'enquête qu'{{gender :il/elle/iel/il(-elle)}} y est rest{{gender :é/ée/é(e)/é(e)}} jusqu'au lendemain et de sélectionner la réponse adaptée.__</t>
   </si>
   <si>
-    <t xml:space="preserve">After being {{atPlace}}, {{nickname}}…
+    <t xml:space="preserve">After being {{atPlace}}, {{nickname}}…{{reminderText}}
 __If {{nickname}} left this place after 4 AM the following day, please consider for the purposes of the survey that they stayed there until the next day and select the appropriate answer.__</t>
   </si>
   <si>
-    <t xml:space="preserve">Après avoir été {{atPlace}}, vous êtes…
+    <t xml:space="preserve">Après avoir été {{atPlace}}, vous êtes…{{reminderText}}
 __Si vous avez quitté le lieu après 4h du matin le lendemain, merci de considérer pour l'enquête que vous y êtes rest{{gender :é/ée/é(e)/é(e)}} jusqu'au lendemain et de sélectionner la réponse adaptée.__</t>
   </si>
   <si>
-    <t xml:space="preserve">After being {{atPlace}}, you…
+    <t xml:space="preserve">After being {{atPlace}}, you…{{reminderText}}
 __If you left this place after 4 AM the following day, please consider for the purposes of the survey that you stayed there until the next day and select the appropriate answer.__</t>
   </si>
   <si>
@@ -2043,16 +2043,16 @@
     <t xml:space="preserve">departureTime</t>
   </si>
   <si>
-    <t xml:space="preserve">{{nickname}} a quitté {{place}} à:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{nickname}} left {{place}} at:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vous avez quitté {{place}} à:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You left {{place}} at:</t>
+    <t xml:space="preserve">{{nickname}} a quitté {{place}} à:{{reminderText}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{nickname}} left {{place}} at:{{reminderText}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vous avez quitté {{place}} à:{{reminderText}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You left {{place}} at:{{reminderText}}</t>
   </si>
   <si>
     <t xml:space="preserve">buttonSaveVisitedPlace</t>
@@ -5667,28 +5667,28 @@
     <t xml:space="preserve">ActivityCategoryFirstLocation</t>
   </si>
   <si>
-    <t xml:space="preserve">Activité principale au lieu de départ de la journée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main activity carried out at the starting point of the day</t>
+    <t xml:space="preserve">Activité principale au lieu de départ de la journée{{reminderText}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main activity carried out at the starting point of the day{{reminderText}}</t>
   </si>
   <si>
     <t xml:space="preserve">ActivityCategoryAfterHome</t>
   </si>
   <si>
-    <t xml:space="preserve">Activité principale au premier lieu visité dans la journée après avoir quitté le domicile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main activity carried out at the first location visited after leaving home</t>
+    <t xml:space="preserve">Activité principale au premier lieu visité dans la journée après avoir quitté le domicile{{reminderText}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main activity carried out at the first location visited after leaving home{{reminderText}}</t>
   </si>
   <si>
     <t xml:space="preserve">ActivityCategory</t>
   </si>
   <si>
-    <t xml:space="preserve">Activité principale à ce lieu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main activity carried out at this location</t>
+    <t xml:space="preserve">Activité principale à ce lieu{{reminderText}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main activity carried out at this location{{reminderText}}</t>
   </si>
   <si>
     <t xml:space="preserve">VisitedPlaceSequence</t>
@@ -6571,6 +6571,67 @@
   </si>
   <si>
     <t xml:space="preserve">Returned home directly ({{address}})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reminderText</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt;span style="background-color:#fff6cc;"&gt;&amp;#x26A0; Rappel: déplacement avec {{otherNickname}} à {{time}} &amp;#8594; {{origin}} vers {{destination}}&lt;/span&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+&lt;span style="background-color:#fff6cc;"&gt;&amp;#x26A0;Reminder: trip with {{otherNickname}} at {{time}} </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&amp;#8594;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> {{origin}} to {{destination}}&lt;/span&gt;</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">onDemandChoicesPickupAtOrigin</t>
@@ -9222,7 +9283,7 @@
     <numFmt numFmtId="166" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
     <numFmt numFmtId="167" formatCode="@"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9451,6 +9512,14 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -9969,11 +10038,11 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -26249,7 +26318,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F229"/>
+  <dimension ref="A1:F230"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="16.72"/>
@@ -28233,44 +28302,40 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="18" t="s">
-        <v>526</v>
-      </c>
-      <c r="B127" s="35" t="s">
+    <row r="127" customFormat="false" ht="75.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B127" s="92" t="s">
         <v>1711</v>
       </c>
-      <c r="C127" s="10" t="s">
+      <c r="C127" s="1" t="s">
         <v>1712</v>
       </c>
-      <c r="D127" s="10" t="s">
+      <c r="D127" s="1" t="s">
         <v>1713</v>
       </c>
-      <c r="E127" s="10" t="s">
-        <v>1714</v>
-      </c>
-      <c r="F127" s="10" t="s">
-        <v>1715</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E127" s="1"/>
+      <c r="F127" s="1"/>
+    </row>
+    <row r="128" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="18" t="s">
         <v>526</v>
       </c>
       <c r="B128" s="35" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C128" s="10" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D128" s="10" t="s">
         <v>1716</v>
       </c>
-      <c r="C128" s="10" t="s">
+      <c r="E128" s="10" t="s">
         <v>1717</v>
       </c>
-      <c r="D128" s="10" t="s">
+      <c r="F128" s="10" t="s">
         <v>1718</v>
-      </c>
-      <c r="E128" s="10" t="s">
-        <v>1719</v>
-      </c>
-      <c r="F128" s="10" t="s">
-        <v>1720</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28278,16 +28343,20 @@
         <v>526</v>
       </c>
       <c r="B129" s="35" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C129" s="10" t="s">
+        <v>1720</v>
+      </c>
+      <c r="D129" s="10" t="s">
         <v>1721</v>
       </c>
-      <c r="C129" s="10" t="s">
+      <c r="E129" s="10" t="s">
         <v>1722</v>
       </c>
-      <c r="D129" s="10" t="s">
+      <c r="F129" s="10" t="s">
         <v>1723</v>
       </c>
-      <c r="E129" s="10"/>
-      <c r="F129" s="10"/>
     </row>
     <row r="130" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="18" t="s">
@@ -28321,11 +28390,11 @@
       <c r="E131" s="10"/>
       <c r="F131" s="10"/>
     </row>
-    <row r="132" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="18" t="s">
         <v>526</v>
       </c>
-      <c r="B132" s="10" t="s">
+      <c r="B132" s="35" t="s">
         <v>1730</v>
       </c>
       <c r="C132" s="10" t="s">
@@ -28344,10 +28413,10 @@
       <c r="B133" s="10" t="s">
         <v>1733</v>
       </c>
-      <c r="C133" s="11" t="s">
+      <c r="C133" s="10" t="s">
         <v>1734</v>
       </c>
-      <c r="D133" s="11" t="s">
+      <c r="D133" s="10" t="s">
         <v>1735</v>
       </c>
       <c r="E133" s="10"/>
@@ -28385,7 +28454,7 @@
       <c r="E135" s="10"/>
       <c r="F135" s="10"/>
     </row>
-    <row r="136" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="18" t="s">
         <v>526</v>
       </c>
@@ -28405,7 +28474,7 @@
       <c r="A137" s="18" t="s">
         <v>526</v>
       </c>
-      <c r="B137" s="45" t="s">
+      <c r="B137" s="10" t="s">
         <v>1745</v>
       </c>
       <c r="C137" s="11" t="s">
@@ -28521,10 +28590,10 @@
         <v>1766</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>1755</v>
+        <v>1767</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>1756</v>
+        <v>1768</v>
       </c>
       <c r="E144" s="10"/>
       <c r="F144" s="10"/>
@@ -28534,13 +28603,13 @@
         <v>526</v>
       </c>
       <c r="B145" s="45" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>1768</v>
+        <v>1758</v>
       </c>
       <c r="D145" s="11" t="s">
-        <v>1769</v>
+        <v>1759</v>
       </c>
       <c r="E145" s="10"/>
       <c r="F145" s="10"/>
@@ -28681,10 +28750,10 @@
         <v>1794</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>1783</v>
+        <v>1795</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>1784</v>
+        <v>1796</v>
       </c>
       <c r="E154" s="10"/>
       <c r="F154" s="10"/>
@@ -28694,13 +28763,13 @@
         <v>526</v>
       </c>
       <c r="B155" s="45" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>1796</v>
+        <v>1786</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>1797</v>
+        <v>1787</v>
       </c>
       <c r="E155" s="10"/>
       <c r="F155" s="10"/>
@@ -28725,7 +28794,7 @@
       <c r="A157" s="18" t="s">
         <v>526</v>
       </c>
-      <c r="B157" s="10" t="s">
+      <c r="B157" s="45" t="s">
         <v>1801</v>
       </c>
       <c r="C157" s="11" t="s">
@@ -28737,7 +28806,7 @@
       <c r="E157" s="10"/>
       <c r="F157" s="10"/>
     </row>
-    <row r="158" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="18" t="s">
         <v>526</v>
       </c>
@@ -28753,84 +28822,80 @@
       <c r="E158" s="10"/>
       <c r="F158" s="10"/>
     </row>
-    <row r="159" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B159" s="1" t="s">
+    <row r="159" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="18" t="s">
+        <v>526</v>
+      </c>
+      <c r="B159" s="10" t="s">
         <v>1807</v>
       </c>
-      <c r="C159" s="1" t="s">
+      <c r="C159" s="11" t="s">
         <v>1808</v>
       </c>
-      <c r="D159" s="1" t="s">
+      <c r="D159" s="11" t="s">
         <v>1809</v>
       </c>
-      <c r="E159" s="1" t="s">
-        <v>1810</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>1811</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E159" s="10"/>
+      <c r="F159" s="10"/>
+    </row>
+    <row r="160" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
         <v>152</v>
       </c>
       <c r="B160" s="1" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>1812</v>
       </c>
-      <c r="C160" s="1" t="s">
+      <c r="E160" s="1" t="s">
         <v>1813</v>
       </c>
-      <c r="D160" s="1" t="s">
+      <c r="F160" s="1" t="s">
         <v>1814</v>
       </c>
-      <c r="E160" s="1" t="s">
-        <v>1815</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>1816</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="161" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B161" s="92" t="s">
+      <c r="B161" s="1" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>1817</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="E161" s="1" t="s">
         <v>1818</v>
       </c>
-      <c r="D161" s="1" t="s">
+      <c r="F161" s="1" t="s">
         <v>1819</v>
       </c>
-      <c r="E161" s="1" t="s">
-        <v>1820</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>1821</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="162" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
         <v>152</v>
       </c>
       <c r="B162" s="92" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>1822</v>
       </c>
-      <c r="C162" s="1" t="s">
+      <c r="E162" s="1" t="s">
         <v>1823</v>
       </c>
-      <c r="D162" s="1" t="s">
+      <c r="F162" s="1" t="s">
         <v>1824</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>1825</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>1826</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28838,58 +28903,62 @@
         <v>152</v>
       </c>
       <c r="B163" s="92" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>1827</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="E163" s="1" t="s">
         <v>1828</v>
       </c>
-      <c r="D163" s="1" t="s">
+      <c r="F163" s="1" t="s">
         <v>1829</v>
       </c>
-      <c r="E163" s="1" t="s">
+    </row>
+    <row r="164" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B164" s="92" t="s">
         <v>1830</v>
       </c>
-      <c r="F163" s="1" t="s">
+      <c r="C164" s="1" t="s">
         <v>1831</v>
       </c>
-    </row>
-    <row r="164" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="B164" s="93" t="s">
+      <c r="D164" s="1" t="s">
         <v>1832</v>
       </c>
-      <c r="C164" s="65" t="s">
+      <c r="E164" s="1" t="s">
         <v>1833</v>
       </c>
-      <c r="D164" s="28" t="s">
+      <c r="F164" s="1" t="s">
         <v>1834</v>
       </c>
-      <c r="E164" s="10"/>
-      <c r="F164" s="10"/>
     </row>
     <row r="165" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B165" s="10" t="s">
+      <c r="B165" s="93" t="s">
         <v>1835</v>
       </c>
-      <c r="C165" s="10" t="s">
+      <c r="C165" s="65" t="s">
         <v>1836</v>
       </c>
-      <c r="D165" s="10" t="s">
+      <c r="D165" s="28" t="s">
         <v>1837</v>
       </c>
       <c r="E165" s="10"/>
       <c r="F165" s="10"/>
     </row>
-    <row r="166" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B166" s="2" t="s">
+      <c r="B166" s="10" t="s">
         <v>1838</v>
       </c>
       <c r="C166" s="10" t="s">
@@ -28898,31 +28967,27 @@
       <c r="D166" s="10" t="s">
         <v>1840</v>
       </c>
-      <c r="E166" s="10" t="s">
-        <v>1841</v>
-      </c>
-      <c r="F166" s="10" t="s">
-        <v>1842</v>
-      </c>
+      <c r="E166" s="10"/>
+      <c r="F166" s="10"/>
     </row>
     <row r="167" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2" t="s">
         <v>342</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>1841</v>
+      </c>
+      <c r="C167" s="10" t="s">
+        <v>1842</v>
+      </c>
+      <c r="D167" s="10" t="s">
         <v>1843</v>
       </c>
-      <c r="C167" s="10" t="s">
+      <c r="E167" s="10" t="s">
         <v>1844</v>
       </c>
-      <c r="D167" s="10" t="s">
+      <c r="F167" s="10" t="s">
         <v>1845</v>
-      </c>
-      <c r="E167" s="10" t="s">
-        <v>1846</v>
-      </c>
-      <c r="F167" s="10" t="s">
-        <v>1847</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28930,59 +28995,59 @@
         <v>342</v>
       </c>
       <c r="B168" s="2" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C168" s="10" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D168" s="10" t="s">
         <v>1848</v>
       </c>
-      <c r="C168" s="28" t="s">
+      <c r="E168" s="10" t="s">
         <v>1849</v>
       </c>
-      <c r="D168" s="28" t="s">
+      <c r="F168" s="10" t="s">
         <v>1850</v>
       </c>
-      <c r="E168" s="28" t="s">
-        <v>1851</v>
-      </c>
-      <c r="F168" s="28" t="s">
-        <v>1852</v>
-      </c>
-    </row>
-    <row r="169" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="169" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2" t="s">
         <v>342</v>
       </c>
       <c r="B169" s="2" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C169" s="28" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D169" s="28" t="s">
         <v>1853</v>
       </c>
-      <c r="C169" s="28" t="s">
+      <c r="E169" s="28" t="s">
         <v>1854</v>
       </c>
-      <c r="D169" s="28" t="s">
+      <c r="F169" s="28" t="s">
         <v>1855</v>
       </c>
-      <c r="E169" s="28" t="s">
-        <v>1856</v>
-      </c>
-      <c r="F169" s="28" t="s">
-        <v>1857</v>
-      </c>
-    </row>
-    <row r="170" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="170" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="s">
         <v>342</v>
       </c>
       <c r="B170" s="2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C170" s="28" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D170" s="28" t="s">
         <v>1858</v>
       </c>
-      <c r="C170" s="28" t="s">
+      <c r="E170" s="28" t="s">
         <v>1859</v>
       </c>
-      <c r="D170" s="28" t="s">
+      <c r="F170" s="28" t="s">
         <v>1860</v>
-      </c>
-      <c r="E170" s="28" t="s">
-        <v>1861</v>
-      </c>
-      <c r="F170" s="28" t="s">
-        <v>1862</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28990,39 +29055,39 @@
         <v>342</v>
       </c>
       <c r="B171" s="2" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C171" s="28" t="s">
+        <v>1862</v>
+      </c>
+      <c r="D171" s="28" t="s">
         <v>1863</v>
       </c>
-      <c r="C171" s="28" t="s">
+      <c r="E171" s="28" t="s">
         <v>1864</v>
       </c>
-      <c r="D171" s="65" t="s">
+      <c r="F171" s="28" t="s">
         <v>1865</v>
       </c>
-      <c r="E171" s="28" t="s">
-        <v>1866</v>
-      </c>
-      <c r="F171" s="65" t="s">
-        <v>1867</v>
-      </c>
-    </row>
-    <row r="172" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="172" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B172" s="10" t="s">
+      <c r="B172" s="2" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C172" s="28" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D172" s="65" t="s">
         <v>1868</v>
       </c>
-      <c r="C172" s="28" t="s">
+      <c r="E172" s="28" t="s">
         <v>1869</v>
       </c>
-      <c r="D172" s="65" t="s">
+      <c r="F172" s="65" t="s">
         <v>1870</v>
-      </c>
-      <c r="E172" s="28" t="s">
-        <v>1871</v>
-      </c>
-      <c r="F172" s="65" t="s">
-        <v>1872</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29030,18 +29095,22 @@
         <v>342</v>
       </c>
       <c r="B173" s="10" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C173" s="28" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D173" s="65" t="s">
         <v>1873</v>
       </c>
-      <c r="C173" s="28" t="s">
+      <c r="E173" s="28" t="s">
         <v>1874</v>
       </c>
-      <c r="D173" s="65" t="s">
+      <c r="F173" s="65" t="s">
         <v>1875</v>
       </c>
-      <c r="E173" s="28"/>
-      <c r="F173" s="65"/>
-    </row>
-    <row r="174" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="174" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2" t="s">
         <v>342</v>
       </c>
@@ -29051,29 +29120,31 @@
       <c r="C174" s="28" t="s">
         <v>1877</v>
       </c>
-      <c r="D174" s="28" t="s">
+      <c r="D174" s="65" t="s">
         <v>1878</v>
       </c>
       <c r="E174" s="28"/>
       <c r="F174" s="65"/>
     </row>
-    <row r="175" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B175" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B175" s="10" t="s">
         <v>1879</v>
       </c>
-      <c r="C175" s="10" t="s">
+      <c r="C175" s="28" t="s">
         <v>1880</v>
       </c>
-      <c r="D175" s="10" t="s">
+      <c r="D175" s="28" t="s">
         <v>1881</v>
       </c>
+      <c r="E175" s="28"/>
+      <c r="F175" s="65"/>
     </row>
     <row r="176" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="s">
-        <v>526</v>
+        <v>1026</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>1882</v>
@@ -29155,17 +29226,17 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="2" t="s">
         <v>526</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>1900</v>
       </c>
-      <c r="C182" s="2" t="s">
+      <c r="C182" s="10" t="s">
         <v>1901</v>
       </c>
-      <c r="D182" s="2" t="s">
+      <c r="D182" s="10" t="s">
         <v>1902</v>
       </c>
     </row>
@@ -29180,7 +29251,7 @@
         <v>1904</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29188,10 +29259,10 @@
         <v>526</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>1907</v>
@@ -29393,31 +29464,31 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B199" s="29" t="s">
+      <c r="B199" s="2" t="s">
         <v>1950</v>
       </c>
-      <c r="C199" s="65" t="s">
+      <c r="C199" s="2" t="s">
         <v>1951</v>
       </c>
-      <c r="D199" s="35" t="s">
+      <c r="D199" s="2" t="s">
         <v>1952</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B200" s="2" t="s">
+      <c r="B200" s="29" t="s">
         <v>1953</v>
       </c>
-      <c r="C200" s="2" t="s">
+      <c r="C200" s="65" t="s">
         <v>1954</v>
       </c>
-      <c r="D200" s="2" t="s">
+      <c r="D200" s="35" t="s">
         <v>1955</v>
       </c>
     </row>
@@ -29477,17 +29548,17 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2" t="s">
         <v>526</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>1968</v>
       </c>
-      <c r="C205" s="65" t="s">
+      <c r="C205" s="2" t="s">
         <v>1969</v>
       </c>
-      <c r="D205" s="35" t="s">
+      <c r="D205" s="2" t="s">
         <v>1970</v>
       </c>
     </row>
@@ -29495,7 +29566,7 @@
       <c r="A206" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B206" s="29" t="s">
+      <c r="B206" s="2" t="s">
         <v>1971</v>
       </c>
       <c r="C206" s="65" t="s">
@@ -29569,10 +29640,10 @@
         <v>1986</v>
       </c>
       <c r="C211" s="65" t="s">
-        <v>1981</v>
+        <v>1987</v>
       </c>
       <c r="D211" s="35" t="s">
-        <v>1982</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29580,7 +29651,7 @@
         <v>526</v>
       </c>
       <c r="B212" s="29" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="C212" s="65" t="s">
         <v>1984</v>
@@ -29594,13 +29665,13 @@
         <v>526</v>
       </c>
       <c r="B213" s="29" t="s">
+        <v>1990</v>
+      </c>
+      <c r="C213" s="65" t="s">
+        <v>1987</v>
+      </c>
+      <c r="D213" s="35" t="s">
         <v>1988</v>
-      </c>
-      <c r="C213" s="65" t="s">
-        <v>1951</v>
-      </c>
-      <c r="D213" s="35" t="s">
-        <v>1952</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29608,13 +29679,13 @@
         <v>526</v>
       </c>
       <c r="B214" s="29" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="C214" s="65" t="s">
-        <v>1990</v>
+        <v>1954</v>
       </c>
       <c r="D214" s="35" t="s">
-        <v>1991</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29645,14 +29716,14 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B217" s="10" t="s">
+      <c r="B217" s="29" t="s">
         <v>1998</v>
       </c>
-      <c r="C217" s="10" t="s">
+      <c r="C217" s="65" t="s">
         <v>1999</v>
       </c>
       <c r="D217" s="35" t="s">
@@ -29660,116 +29731,116 @@
       </c>
     </row>
     <row r="218" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="21" t="s">
-        <v>719</v>
-      </c>
-      <c r="B218" s="11" t="s">
+      <c r="A218" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B218" s="10" t="s">
         <v>2001</v>
       </c>
       <c r="C218" s="10" t="s">
         <v>2002</v>
       </c>
-      <c r="D218" s="94" t="s">
+      <c r="D218" s="35" t="s">
         <v>2003</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="2" t="s">
+    <row r="219" customFormat="false" ht="30.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="21" t="s">
         <v>719</v>
       </c>
-      <c r="B219" s="2" t="s">
+      <c r="B219" s="11" t="s">
         <v>2004</v>
       </c>
-      <c r="C219" s="21" t="s">
-        <v>1335</v>
-      </c>
-      <c r="D219" s="28" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="220" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C219" s="10" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D219" s="94" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="s">
         <v>719</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>2005</v>
-      </c>
-      <c r="C220" s="65" t="s">
-        <v>2006</v>
+        <v>2007</v>
+      </c>
+      <c r="C220" s="21" t="s">
+        <v>1335</v>
       </c>
       <c r="D220" s="28" t="s">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="221" customFormat="false" ht="268.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="B221" s="22" t="s">
+      <c r="B221" s="2" t="s">
         <v>2008</v>
       </c>
-      <c r="C221" s="11" t="s">
+      <c r="C221" s="65" t="s">
         <v>2009</v>
       </c>
-      <c r="D221" s="11" t="s">
+      <c r="D221" s="28" t="s">
         <v>2010</v>
       </c>
-      <c r="E221" s="11" t="s">
-        <v>2011</v>
-      </c>
-      <c r="F221" s="11" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="222" customFormat="false" ht="223.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="222" customFormat="false" ht="268.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2" t="s">
         <v>719</v>
       </c>
       <c r="B222" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="C222" s="11" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D222" s="11" t="s">
         <v>2013</v>
       </c>
-      <c r="C222" s="11" t="s">
+      <c r="E222" s="11" t="s">
         <v>2014</v>
       </c>
-      <c r="D222" s="11" t="s">
+      <c r="F222" s="11" t="s">
         <v>2015</v>
       </c>
-      <c r="E222" s="11" t="s">
+    </row>
+    <row r="223" customFormat="false" ht="223.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="B223" s="22" t="s">
         <v>2016</v>
       </c>
-      <c r="F222" s="11" t="s">
+      <c r="C223" s="11" t="s">
         <v>2017</v>
       </c>
-    </row>
-    <row r="223" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="B223" s="2" t="s">
+      <c r="D223" s="11" t="s">
         <v>2018</v>
       </c>
-      <c r="C223" s="21" t="s">
-        <v>1335</v>
-      </c>
-      <c r="D223" s="28" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="224" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E223" s="11" t="s">
+        <v>2019</v>
+      </c>
+      <c r="F223" s="11" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2" t="s">
         <v>806</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C224" s="65" t="s">
-        <v>2020</v>
-      </c>
-      <c r="D224" s="10" t="s">
         <v>2021</v>
       </c>
-    </row>
-    <row r="225" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C224" s="21" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D224" s="28" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2" t="s">
         <v>806</v>
       </c>
@@ -29777,51 +29848,51 @@
         <v>2022</v>
       </c>
       <c r="C225" s="65" t="s">
-        <v>1397</v>
+        <v>2023</v>
       </c>
       <c r="D225" s="10" t="s">
-        <v>1398</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2" t="s">
-        <v>1026</v>
+        <v>806</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>2023</v>
-      </c>
-      <c r="C226" s="21" t="s">
-        <v>1335</v>
-      </c>
-      <c r="D226" s="28" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="227" customFormat="false" ht="75.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2025</v>
+      </c>
+      <c r="C226" s="65" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D226" s="10" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2" t="s">
         <v>1026</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>2024</v>
-      </c>
-      <c r="C227" s="65" t="s">
-        <v>2025</v>
+        <v>2026</v>
+      </c>
+      <c r="C227" s="21" t="s">
+        <v>1335</v>
       </c>
       <c r="D227" s="28" t="s">
-        <v>2026</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="75.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="2" t="s">
-        <v>973</v>
-      </c>
-      <c r="B228" s="11" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B228" s="2" t="s">
         <v>2027</v>
       </c>
-      <c r="C228" s="11" t="s">
+      <c r="C228" s="65" t="s">
         <v>2028</v>
       </c>
-      <c r="D228" s="11" t="s">
+      <c r="D228" s="28" t="s">
         <v>2029</v>
       </c>
     </row>
@@ -29837,6 +29908,20 @@
       </c>
       <c r="D229" s="11" t="s">
         <v>2032</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="75.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="B230" s="11" t="s">
+        <v>2033</v>
+      </c>
+      <c r="C230" s="11" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D230" s="11" t="s">
+        <v>2035</v>
       </c>
     </row>
   </sheetData>
@@ -29868,7 +29953,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="95" t="s">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="B1" s="95" t="s">
         <v>1133</v>
@@ -29886,13 +29971,13 @@
         <v>9</v>
       </c>
       <c r="G1" s="95" t="s">
-        <v>2034</v>
+        <v>2037</v>
       </c>
       <c r="H1" s="95" t="s">
         <v>12</v>
       </c>
       <c r="I1" s="29" t="s">
-        <v>2035</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29903,10 +29988,10 @@
         <v>1141</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
@@ -29921,10 +30006,10 @@
         <v>1199</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
@@ -29939,10 +30024,10 @@
         <v>212</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
@@ -29951,7 +30036,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>212</v>
@@ -29969,10 +30054,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>1400</v>
@@ -29993,10 +30078,10 @@
         <v>1145</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
@@ -30055,7 +30140,7 @@
       <c r="E11" s="22"/>
       <c r="F11" s="22"/>
       <c r="G11" s="22" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="H11" s="22"/>
     </row>
@@ -30109,10 +30194,10 @@
         <v>1141</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="D15" s="65" t="s">
-        <v>2047</v>
+        <v>2050</v>
       </c>
       <c r="E15" s="28"/>
       <c r="F15" s="28"/>
@@ -30128,10 +30213,10 @@
         <v>1199</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>2048</v>
+        <v>2051</v>
       </c>
       <c r="D16" s="65" t="s">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="E16" s="28"/>
       <c r="F16" s="28"/>
@@ -30141,16 +30226,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="97" t="s">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>2051</v>
+        <v>2054</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>2052</v>
+        <v>2055</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>2053</v>
+        <v>2056</v>
       </c>
       <c r="E17" s="22"/>
       <c r="F17" s="22"/>
@@ -30159,16 +30244,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="97" t="s">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>2054</v>
+        <v>2057</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>2056</v>
+        <v>2059</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="22"/>
@@ -30177,7 +30262,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="97" t="s">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="B19" s="22"/>
       <c r="C19" s="22"/>
@@ -30194,13 +30279,13 @@
         <v>170</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>2051</v>
+        <v>2054</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>2052</v>
+        <v>2055</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>2057</v>
+        <v>2060</v>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
@@ -30212,13 +30297,13 @@
         <v>170</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>2054</v>
+        <v>2057</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="E21" s="22"/>
       <c r="F21" s="22"/>
@@ -30233,10 +30318,10 @@
         <v>172</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>2059</v>
+        <v>2062</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>2060</v>
+        <v>2063</v>
       </c>
       <c r="E22" s="22"/>
       <c r="F22" s="22"/>
@@ -30262,13 +30347,13 @@
         <v>289</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>2061</v>
+        <v>2064</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>2062</v>
+        <v>2065</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>2063</v>
+        <v>2066</v>
       </c>
       <c r="E24" s="22"/>
       <c r="F24" s="22"/>
@@ -30280,13 +30365,13 @@
         <v>289</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>2064</v>
+        <v>2067</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>2065</v>
+        <v>2068</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>2066</v>
+        <v>2069</v>
       </c>
       <c r="E25" s="22"/>
       <c r="F25" s="22"/>
@@ -30312,13 +30397,13 @@
         <v>282</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>2061</v>
+        <v>2064</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>2067</v>
+        <v>2070</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>2068</v>
+        <v>2071</v>
       </c>
       <c r="E27" s="22"/>
       <c r="F27" s="22"/>
@@ -30330,13 +30415,13 @@
         <v>282</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>2064</v>
+        <v>2067</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>2069</v>
+        <v>2072</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>2070</v>
+        <v>2073</v>
       </c>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
@@ -30365,10 +30450,10 @@
         <v>1165</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>2071</v>
+        <v>2074</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
@@ -30387,10 +30472,10 @@
         <v>1166</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>2073</v>
+        <v>2076</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="E31" s="22"/>
       <c r="F31" s="22"/>
@@ -30409,10 +30494,10 @@
         <v>1167</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>2075</v>
+        <v>2078</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>2076</v>
+        <v>2079</v>
       </c>
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
@@ -30431,10 +30516,10 @@
         <v>1169</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>2077</v>
+        <v>2080</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>2078</v>
+        <v>2081</v>
       </c>
       <c r="E33" s="22"/>
       <c r="F33" s="22"/>
@@ -30453,10 +30538,10 @@
         <v>1170</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>2079</v>
+        <v>2082</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>2080</v>
+        <v>2083</v>
       </c>
       <c r="E34" s="22"/>
       <c r="F34" s="22"/>
@@ -30472,13 +30557,13 @@
         <v>325</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>2081</v>
+        <v>2084</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>2082</v>
+        <v>2085</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>2083</v>
+        <v>2086</v>
       </c>
       <c r="E35" s="22"/>
       <c r="F35" s="22"/>
@@ -30493,13 +30578,13 @@
         <v>325</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>2084</v>
+        <v>2087</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>2085</v>
+        <v>2088</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
@@ -30512,13 +30597,13 @@
         <v>325</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>2087</v>
+        <v>2090</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>2089</v>
+        <v>2092</v>
       </c>
       <c r="E37" s="22"/>
       <c r="F37" s="22"/>
@@ -30531,13 +30616,13 @@
         <v>325</v>
       </c>
       <c r="B38" s="60" t="s">
-        <v>2090</v>
+        <v>2093</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>2091</v>
+        <v>2094</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="E38" s="22"/>
       <c r="F38" s="22"/>
@@ -30550,13 +30635,13 @@
         <v>325</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>2094</v>
+        <v>2097</v>
       </c>
       <c r="D39" s="22" t="s">
-        <v>2095</v>
+        <v>2098</v>
       </c>
       <c r="E39" s="22"/>
       <c r="F39" s="22"/>
@@ -30569,13 +30654,13 @@
         <v>325</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>2096</v>
+        <v>2099</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>2097</v>
+        <v>2100</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>2098</v>
+        <v>2101</v>
       </c>
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
@@ -30593,7 +30678,7 @@
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
       <c r="G41" s="22" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="H41" s="22"/>
       <c r="I41" s="29"/>
@@ -30618,13 +30703,13 @@
         <v>296</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>2099</v>
+        <v>2102</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>2100</v>
+        <v>2103</v>
       </c>
       <c r="D43" s="65" t="s">
-        <v>2101</v>
+        <v>2104</v>
       </c>
       <c r="E43" s="22"/>
       <c r="F43" s="22"/>
@@ -30637,13 +30722,13 @@
         <v>296</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>2102</v>
+        <v>2105</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>2103</v>
+        <v>2106</v>
       </c>
       <c r="D44" s="65" t="s">
-        <v>2104</v>
+        <v>2107</v>
       </c>
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
@@ -30656,13 +30741,13 @@
         <v>296</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>2105</v>
+        <v>2108</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>2106</v>
+        <v>2109</v>
       </c>
       <c r="D45" s="65" t="s">
-        <v>2107</v>
+        <v>2110</v>
       </c>
       <c r="E45" s="22"/>
       <c r="F45" s="22"/>
@@ -30675,13 +30760,13 @@
         <v>296</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>2108</v>
+        <v>2111</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>2109</v>
+        <v>2112</v>
       </c>
       <c r="D46" s="65" t="s">
-        <v>2110</v>
+        <v>2113</v>
       </c>
       <c r="E46" s="22"/>
       <c r="F46" s="22"/>
@@ -30699,7 +30784,7 @@
       <c r="E47" s="22"/>
       <c r="F47" s="22"/>
       <c r="G47" s="22" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="H47" s="22"/>
       <c r="I47" s="22"/>
@@ -30712,10 +30797,10 @@
         <v>1230</v>
       </c>
       <c r="C48" s="28" t="s">
-        <v>2111</v>
+        <v>2114</v>
       </c>
       <c r="D48" s="65" t="s">
-        <v>2112</v>
+        <v>2115</v>
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="22"/>
@@ -30730,13 +30815,13 @@
         <v>203</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>2113</v>
+        <v>2116</v>
       </c>
       <c r="C49" s="28" t="s">
-        <v>2114</v>
+        <v>2117</v>
       </c>
       <c r="D49" s="65" t="s">
-        <v>2115</v>
+        <v>2118</v>
       </c>
       <c r="E49" s="22"/>
       <c r="F49" s="22"/>
@@ -30751,13 +30836,13 @@
         <v>203</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>2116</v>
+        <v>2119</v>
       </c>
       <c r="C50" s="28" t="s">
-        <v>2117</v>
+        <v>2120</v>
       </c>
       <c r="D50" s="65" t="s">
-        <v>2118</v>
+        <v>2121</v>
       </c>
       <c r="E50" s="22"/>
       <c r="F50" s="22"/>
@@ -30773,10 +30858,10 @@
         <v>212</v>
       </c>
       <c r="C51" s="28" t="s">
-        <v>2119</v>
+        <v>2122</v>
       </c>
       <c r="D51" s="65" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
       <c r="E51" s="22"/>
       <c r="F51" s="22"/>
@@ -30794,7 +30879,7 @@
       <c r="E52" s="22"/>
       <c r="F52" s="22"/>
       <c r="G52" s="22" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="H52" s="22"/>
       <c r="I52" s="22"/>
@@ -30804,13 +30889,13 @@
         <v>209</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>2121</v>
+        <v>2124</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>2122</v>
+        <v>2125</v>
       </c>
       <c r="D53" s="65" t="s">
-        <v>2123</v>
+        <v>2126</v>
       </c>
       <c r="E53" s="22"/>
       <c r="F53" s="22"/>
@@ -30823,13 +30908,13 @@
         <v>209</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>2124</v>
+        <v>2127</v>
       </c>
       <c r="C54" s="28" t="s">
-        <v>2125</v>
+        <v>2128</v>
       </c>
       <c r="D54" s="65" t="s">
-        <v>2126</v>
+        <v>2129</v>
       </c>
       <c r="E54" s="22"/>
       <c r="F54" s="22"/>
@@ -30842,13 +30927,13 @@
         <v>209</v>
       </c>
       <c r="B55" s="22" t="s">
-        <v>2127</v>
+        <v>2130</v>
       </c>
       <c r="C55" s="28" t="s">
-        <v>2128</v>
+        <v>2131</v>
       </c>
       <c r="D55" s="65" t="s">
-        <v>2129</v>
+        <v>2132</v>
       </c>
       <c r="E55" s="22"/>
       <c r="F55" s="22"/>
@@ -30861,13 +30946,13 @@
         <v>209</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>2130</v>
+        <v>2133</v>
       </c>
       <c r="C56" s="28" t="s">
-        <v>2131</v>
+        <v>2134</v>
       </c>
       <c r="D56" s="65" t="s">
-        <v>2132</v>
+        <v>2135</v>
       </c>
       <c r="E56" s="22"/>
       <c r="F56" s="22"/>
@@ -30880,13 +30965,13 @@
         <v>209</v>
       </c>
       <c r="B57" s="22" t="s">
-        <v>2133</v>
+        <v>2136</v>
       </c>
       <c r="C57" s="28" t="s">
-        <v>2134</v>
+        <v>2137</v>
       </c>
       <c r="D57" s="65" t="s">
-        <v>2134</v>
+        <v>2137</v>
       </c>
       <c r="E57" s="22"/>
       <c r="F57" s="22"/>
@@ -30899,13 +30984,13 @@
         <v>209</v>
       </c>
       <c r="B58" s="22" t="s">
-        <v>2135</v>
+        <v>2138</v>
       </c>
       <c r="C58" s="28" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="D58" s="65" t="s">
-        <v>2137</v>
+        <v>2140</v>
       </c>
       <c r="E58" s="22"/>
       <c r="F58" s="22"/>
@@ -30918,13 +31003,13 @@
         <v>209</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>2138</v>
+        <v>2141</v>
       </c>
       <c r="C59" s="28" t="s">
-        <v>2139</v>
+        <v>2142</v>
       </c>
       <c r="D59" s="65" t="s">
-        <v>2140</v>
+        <v>2143</v>
       </c>
       <c r="E59" s="22"/>
       <c r="F59" s="22"/>
@@ -30937,13 +31022,13 @@
         <v>209</v>
       </c>
       <c r="B60" s="22" t="s">
-        <v>2141</v>
+        <v>2144</v>
       </c>
       <c r="C60" s="28" t="s">
-        <v>2142</v>
+        <v>2145</v>
       </c>
       <c r="D60" s="65" t="s">
-        <v>2143</v>
+        <v>2146</v>
       </c>
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
@@ -30971,13 +31056,13 @@
         <v>209</v>
       </c>
       <c r="B62" s="22" t="s">
-        <v>2144</v>
+        <v>2147</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>2145</v>
+        <v>2148</v>
       </c>
       <c r="D62" s="65" t="s">
-        <v>2146</v>
+        <v>2149</v>
       </c>
       <c r="E62" s="22"/>
       <c r="F62" s="22"/>
@@ -30995,7 +31080,7 @@
       <c r="E63" s="22"/>
       <c r="F63" s="22"/>
       <c r="G63" s="22" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="H63" s="22"/>
       <c r="I63" s="22"/>
@@ -31008,10 +31093,10 @@
         <v>1141</v>
       </c>
       <c r="C64" s="28" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="D64" s="65" t="s">
-        <v>2148</v>
+        <v>2151</v>
       </c>
       <c r="E64" s="22"/>
       <c r="F64" s="22"/>
@@ -31027,10 +31112,10 @@
         <v>1173</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>2149</v>
+        <v>2152</v>
       </c>
       <c r="D65" s="22" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="E65" s="22"/>
       <c r="F65" s="22"/>
@@ -31046,10 +31131,10 @@
         <v>1174</v>
       </c>
       <c r="C66" s="22" t="s">
-        <v>2151</v>
+        <v>2154</v>
       </c>
       <c r="D66" s="22" t="s">
-        <v>2152</v>
+        <v>2155</v>
       </c>
       <c r="E66" s="22"/>
       <c r="F66" s="22"/>
@@ -31065,10 +31150,10 @@
         <v>1175</v>
       </c>
       <c r="C67" s="22" t="s">
-        <v>2153</v>
+        <v>2156</v>
       </c>
       <c r="D67" s="22" t="s">
-        <v>2154</v>
+        <v>2157</v>
       </c>
       <c r="E67" s="22"/>
       <c r="F67" s="22"/>
@@ -31081,13 +31166,13 @@
         <v>303</v>
       </c>
       <c r="B68" s="22" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>2156</v>
+        <v>2159</v>
       </c>
       <c r="D68" s="22" t="s">
-        <v>2157</v>
+        <v>2160</v>
       </c>
       <c r="E68" s="22"/>
       <c r="F68" s="22"/>
@@ -31103,10 +31188,10 @@
         <v>1187</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>2158</v>
+        <v>2161</v>
       </c>
       <c r="D69" s="22" t="s">
-        <v>2159</v>
+        <v>2162</v>
       </c>
       <c r="E69" s="22"/>
       <c r="F69" s="22"/>
@@ -31119,13 +31204,13 @@
         <v>877</v>
       </c>
       <c r="B70" s="29" t="s">
-        <v>2160</v>
+        <v>2163</v>
       </c>
       <c r="C70" s="29" t="s">
-        <v>2161</v>
+        <v>2164</v>
       </c>
       <c r="D70" s="29" t="s">
-        <v>2162</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31133,13 +31218,13 @@
         <v>877</v>
       </c>
       <c r="B71" s="29" t="s">
-        <v>2163</v>
+        <v>2166</v>
       </c>
       <c r="C71" s="29" t="s">
-        <v>2164</v>
+        <v>2167</v>
       </c>
       <c r="D71" s="29" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31147,13 +31232,13 @@
         <v>877</v>
       </c>
       <c r="B72" s="29" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="C72" s="29" t="s">
-        <v>2167</v>
+        <v>2170</v>
       </c>
       <c r="D72" s="29" t="s">
-        <v>2168</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="73" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31161,13 +31246,13 @@
         <v>877</v>
       </c>
       <c r="B73" s="29" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="C73" s="29" t="s">
-        <v>2170</v>
+        <v>2173</v>
       </c>
       <c r="D73" s="29" t="s">
-        <v>2171</v>
+        <v>2174</v>
       </c>
       <c r="E73" s="29"/>
       <c r="F73" s="29"/>
@@ -31180,13 +31265,13 @@
         <v>1054</v>
       </c>
       <c r="B74" s="29" t="s">
-        <v>2172</v>
+        <v>2175</v>
       </c>
       <c r="C74" s="29" t="s">
-        <v>2173</v>
+        <v>2176</v>
       </c>
       <c r="D74" s="29" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="E74" s="29"/>
       <c r="F74" s="29"/>
@@ -31199,13 +31284,13 @@
         <v>1054</v>
       </c>
       <c r="B75" s="60" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="C75" s="60" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="D75" s="60" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="E75" s="60"/>
       <c r="F75" s="60"/>
@@ -31218,13 +31303,13 @@
         <v>1054</v>
       </c>
       <c r="B76" s="60" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="C76" s="60" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="D76" s="60" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="E76" s="60"/>
       <c r="F76" s="60"/>
@@ -31237,13 +31322,13 @@
         <v>1054</v>
       </c>
       <c r="B77" s="60" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="C77" s="60" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="D77" s="60" t="s">
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="E77" s="60"/>
       <c r="F77" s="60"/>
@@ -31256,13 +31341,13 @@
         <v>1054</v>
       </c>
       <c r="B78" s="60" t="s">
-        <v>2184</v>
+        <v>2187</v>
       </c>
       <c r="C78" s="60" t="s">
-        <v>2185</v>
+        <v>2188</v>
       </c>
       <c r="D78" s="60" t="s">
-        <v>2186</v>
+        <v>2189</v>
       </c>
       <c r="E78" s="60"/>
       <c r="F78" s="60"/>
@@ -31275,13 +31360,13 @@
         <v>1054</v>
       </c>
       <c r="B79" s="60" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="C79" s="60" t="s">
-        <v>2188</v>
+        <v>2191</v>
       </c>
       <c r="D79" s="60" t="s">
-        <v>2189</v>
+        <v>2192</v>
       </c>
       <c r="E79" s="60"/>
       <c r="F79" s="60"/>
@@ -31294,13 +31379,13 @@
         <v>1054</v>
       </c>
       <c r="B80" s="60" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="C80" s="60" t="s">
-        <v>2191</v>
+        <v>2194</v>
       </c>
       <c r="D80" s="60" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="E80" s="60"/>
       <c r="F80" s="60"/>
@@ -31313,13 +31398,13 @@
         <v>1054</v>
       </c>
       <c r="B81" s="60" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="C81" s="60" t="s">
-        <v>2194</v>
+        <v>2197</v>
       </c>
       <c r="D81" s="60" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="E81" s="60"/>
       <c r="F81" s="60"/>
@@ -31332,13 +31417,13 @@
         <v>1054</v>
       </c>
       <c r="B82" s="60" t="s">
-        <v>2196</v>
+        <v>2199</v>
       </c>
       <c r="C82" s="60" t="s">
-        <v>2197</v>
+        <v>2200</v>
       </c>
       <c r="D82" s="60" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="E82" s="60"/>
       <c r="F82" s="60"/>
@@ -31351,13 +31436,13 @@
         <v>1054</v>
       </c>
       <c r="B83" s="60" t="s">
-        <v>2199</v>
+        <v>2202</v>
       </c>
       <c r="C83" s="60" t="s">
-        <v>2200</v>
+        <v>2203</v>
       </c>
       <c r="D83" s="60" t="s">
-        <v>2201</v>
+        <v>2204</v>
       </c>
       <c r="E83" s="60"/>
       <c r="F83" s="60"/>
@@ -31370,13 +31455,13 @@
         <v>1054</v>
       </c>
       <c r="B84" s="60" t="s">
-        <v>2202</v>
+        <v>2205</v>
       </c>
       <c r="C84" s="60" t="s">
-        <v>2203</v>
+        <v>2206</v>
       </c>
       <c r="D84" s="60" t="s">
-        <v>2204</v>
+        <v>2207</v>
       </c>
       <c r="E84" s="60"/>
       <c r="F84" s="60"/>
@@ -31389,13 +31474,13 @@
         <v>1054</v>
       </c>
       <c r="B85" s="60" t="s">
-        <v>2205</v>
+        <v>2208</v>
       </c>
       <c r="C85" s="60" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="D85" s="60" t="s">
-        <v>2207</v>
+        <v>2210</v>
       </c>
       <c r="E85" s="60"/>
       <c r="F85" s="60"/>
@@ -31408,13 +31493,13 @@
         <v>1054</v>
       </c>
       <c r="B86" s="29" t="s">
-        <v>2208</v>
+        <v>2211</v>
       </c>
       <c r="C86" s="29" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="D86" s="29" t="s">
-        <v>2210</v>
+        <v>2213</v>
       </c>
       <c r="E86" s="29"/>
       <c r="F86" s="29"/>
@@ -31427,7 +31512,7 @@
         <v>1054</v>
       </c>
       <c r="B87" s="29" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="C87" s="29" t="s">
         <v>1400</v>
@@ -31446,13 +31531,13 @@
         <v>1054</v>
       </c>
       <c r="B88" s="29" t="s">
-        <v>2211</v>
+        <v>2214</v>
       </c>
       <c r="C88" s="29" t="s">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="D88" s="29" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31460,13 +31545,13 @@
         <v>81</v>
       </c>
       <c r="B89" s="60" t="s">
-        <v>2213</v>
+        <v>2216</v>
       </c>
       <c r="C89" s="29" t="s">
-        <v>2214</v>
+        <v>2217</v>
       </c>
       <c r="D89" s="29" t="s">
-        <v>2215</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31474,13 +31559,13 @@
         <v>81</v>
       </c>
       <c r="B90" s="29" t="s">
-        <v>2216</v>
+        <v>2219</v>
       </c>
       <c r="C90" s="29" t="s">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="D90" s="29" t="s">
-        <v>2218</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31505,10 +31590,10 @@
         <v>1145</v>
       </c>
       <c r="C92" s="60" t="s">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="D92" s="60" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="E92" s="60"/>
       <c r="F92" s="60"/>
@@ -31518,13 +31603,13 @@
         <v>403</v>
       </c>
       <c r="B93" s="22" t="s">
-        <v>2219</v>
+        <v>2222</v>
       </c>
       <c r="C93" s="28" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="D93" s="65" t="s">
-        <v>2221</v>
+        <v>2224</v>
       </c>
       <c r="E93" s="28"/>
       <c r="F93" s="28"/>
@@ -31539,13 +31624,13 @@
         <v>403</v>
       </c>
       <c r="B94" s="22" t="s">
-        <v>2222</v>
+        <v>2225</v>
       </c>
       <c r="C94" s="28" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
       <c r="D94" s="65" t="s">
-        <v>2224</v>
+        <v>2227</v>
       </c>
       <c r="E94" s="28"/>
       <c r="F94" s="28"/>
@@ -31560,13 +31645,13 @@
         <v>403</v>
       </c>
       <c r="B95" s="22" t="s">
-        <v>2225</v>
+        <v>2228</v>
       </c>
       <c r="C95" s="28" t="s">
-        <v>2226</v>
+        <v>2229</v>
       </c>
       <c r="D95" s="65" t="s">
-        <v>2227</v>
+        <v>2230</v>
       </c>
       <c r="E95" s="28"/>
       <c r="F95" s="28"/>
@@ -31579,13 +31664,13 @@
         <v>403</v>
       </c>
       <c r="B96" s="22" t="s">
-        <v>2228</v>
+        <v>2231</v>
       </c>
       <c r="C96" s="28" t="s">
-        <v>2229</v>
+        <v>2232</v>
       </c>
       <c r="D96" s="65" t="s">
-        <v>2230</v>
+        <v>2233</v>
       </c>
       <c r="E96" s="28"/>
       <c r="F96" s="28"/>
@@ -31598,13 +31683,13 @@
         <v>403</v>
       </c>
       <c r="B97" s="22" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="C97" s="28" t="s">
-        <v>2232</v>
+        <v>2235</v>
       </c>
       <c r="D97" s="65" t="s">
-        <v>2233</v>
+        <v>2236</v>
       </c>
       <c r="E97" s="28"/>
       <c r="F97" s="28"/>
@@ -31620,10 +31705,10 @@
         <v>1206</v>
       </c>
       <c r="C98" s="28" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="D98" s="65" t="s">
-        <v>2235</v>
+        <v>2238</v>
       </c>
       <c r="E98" s="28"/>
       <c r="F98" s="28"/>
@@ -31641,10 +31726,10 @@
         <v>1207</v>
       </c>
       <c r="C99" s="28" t="s">
-        <v>2236</v>
+        <v>2239</v>
       </c>
       <c r="D99" s="65" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="E99" s="28"/>
       <c r="F99" s="28"/>
@@ -31657,13 +31742,13 @@
         <v>403</v>
       </c>
       <c r="B100" s="22" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
       <c r="C100" s="28" t="s">
-        <v>2239</v>
+        <v>2242</v>
       </c>
       <c r="D100" s="65" t="s">
-        <v>2240</v>
+        <v>2243</v>
       </c>
       <c r="E100" s="28"/>
       <c r="F100" s="28"/>
@@ -31694,56 +31779,56 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="101" t="s">
-        <v>2241</v>
+        <v>2244</v>
       </c>
       <c r="B102" s="29" t="s">
-        <v>2242</v>
+        <v>2245</v>
       </c>
       <c r="C102" s="60" t="s">
-        <v>1712</v>
+        <v>1715</v>
       </c>
       <c r="D102" s="60" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
       <c r="E102" s="60" t="s">
-        <v>1714</v>
+        <v>1717</v>
       </c>
       <c r="F102" s="60" t="s">
-        <v>1715</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="101" t="s">
-        <v>2241</v>
+        <v>2244</v>
       </c>
       <c r="B103" s="29" t="s">
-        <v>2243</v>
+        <v>2246</v>
       </c>
       <c r="C103" s="60" t="s">
-        <v>1717</v>
+        <v>1720</v>
       </c>
       <c r="D103" s="60" t="s">
-        <v>1718</v>
+        <v>1721</v>
       </c>
       <c r="E103" s="60" t="s">
-        <v>1719</v>
+        <v>1722</v>
       </c>
       <c r="F103" s="60" t="s">
-        <v>1720</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="101" t="s">
-        <v>2241</v>
+        <v>2244</v>
       </c>
       <c r="B104" s="29" t="s">
         <v>1199</v>
       </c>
       <c r="C104" s="29" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="D104" s="29" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31751,13 +31836,13 @@
         <v>734</v>
       </c>
       <c r="B105" s="60" t="s">
-        <v>2244</v>
+        <v>2247</v>
       </c>
       <c r="C105" s="60" t="s">
-        <v>2245</v>
+        <v>2248</v>
       </c>
       <c r="D105" s="60" t="s">
-        <v>2246</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31765,13 +31850,13 @@
         <v>734</v>
       </c>
       <c r="B106" s="60" t="s">
-        <v>2247</v>
+        <v>2250</v>
       </c>
       <c r="C106" s="60" t="s">
-        <v>2248</v>
+        <v>2251</v>
       </c>
       <c r="D106" s="60" t="s">
-        <v>2249</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31779,13 +31864,13 @@
         <v>734</v>
       </c>
       <c r="B107" s="60" t="s">
-        <v>2250</v>
+        <v>2253</v>
       </c>
       <c r="C107" s="60" t="s">
-        <v>2251</v>
+        <v>2254</v>
       </c>
       <c r="D107" s="60" t="s">
-        <v>2252</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31793,13 +31878,13 @@
         <v>734</v>
       </c>
       <c r="B108" s="60" t="s">
-        <v>2253</v>
+        <v>2256</v>
       </c>
       <c r="C108" s="60" t="s">
-        <v>2254</v>
+        <v>2257</v>
       </c>
       <c r="D108" s="60" t="s">
-        <v>2255</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31807,7 +31892,7 @@
         <v>734</v>
       </c>
       <c r="G109" s="22" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31815,7 +31900,7 @@
         <v>734</v>
       </c>
       <c r="G110" s="22" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31823,13 +31908,13 @@
         <v>802</v>
       </c>
       <c r="B111" s="60" t="s">
-        <v>2256</v>
+        <v>2259</v>
       </c>
       <c r="C111" s="60" t="s">
-        <v>2257</v>
+        <v>2260</v>
       </c>
       <c r="D111" s="60" t="s">
-        <v>2258</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31837,13 +31922,13 @@
         <v>802</v>
       </c>
       <c r="B112" s="60" t="s">
-        <v>2259</v>
+        <v>2262</v>
       </c>
       <c r="C112" s="60" t="s">
-        <v>2260</v>
+        <v>2263</v>
       </c>
       <c r="D112" s="60" t="s">
-        <v>2261</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31851,13 +31936,13 @@
         <v>802</v>
       </c>
       <c r="B113" s="60" t="s">
-        <v>2250</v>
+        <v>2253</v>
       </c>
       <c r="C113" s="60" t="s">
-        <v>2251</v>
+        <v>2254</v>
       </c>
       <c r="D113" s="60" t="s">
-        <v>2252</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31865,13 +31950,13 @@
         <v>802</v>
       </c>
       <c r="B114" s="22" t="s">
-        <v>2262</v>
+        <v>2265</v>
       </c>
       <c r="C114" s="28" t="s">
-        <v>2263</v>
+        <v>2266</v>
       </c>
       <c r="D114" s="21" t="s">
-        <v>2264</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31879,7 +31964,7 @@
         <v>802</v>
       </c>
       <c r="G115" s="22" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31887,7 +31972,7 @@
         <v>802</v>
       </c>
       <c r="G116" s="22" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31895,13 +31980,13 @@
         <v>322</v>
       </c>
       <c r="B117" s="60" t="s">
-        <v>2265</v>
+        <v>2268</v>
       </c>
       <c r="C117" s="29" t="s">
-        <v>2266</v>
+        <v>2269</v>
       </c>
       <c r="D117" s="29" t="s">
-        <v>2267</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31909,13 +31994,13 @@
         <v>322</v>
       </c>
       <c r="B118" s="29" t="s">
-        <v>2268</v>
+        <v>2271</v>
       </c>
       <c r="C118" s="29" t="s">
-        <v>2269</v>
+        <v>2272</v>
       </c>
       <c r="D118" s="29" t="s">
-        <v>2270</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31923,13 +32008,13 @@
         <v>322</v>
       </c>
       <c r="B119" s="60" t="s">
-        <v>2271</v>
+        <v>2274</v>
       </c>
       <c r="C119" s="29" t="s">
-        <v>2272</v>
+        <v>2275</v>
       </c>
       <c r="D119" s="29" t="s">
-        <v>2273</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31937,13 +32022,13 @@
         <v>322</v>
       </c>
       <c r="B120" s="60" t="s">
-        <v>2274</v>
+        <v>2277</v>
       </c>
       <c r="C120" s="29" t="s">
-        <v>2275</v>
+        <v>2278</v>
       </c>
       <c r="D120" s="29" t="s">
-        <v>2276</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31951,13 +32036,13 @@
         <v>322</v>
       </c>
       <c r="B121" s="60" t="s">
-        <v>2277</v>
+        <v>2280</v>
       </c>
       <c r="C121" s="29" t="s">
-        <v>2278</v>
+        <v>2281</v>
       </c>
       <c r="D121" s="29" t="s">
-        <v>2279</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31965,13 +32050,13 @@
         <v>322</v>
       </c>
       <c r="B122" s="60" t="s">
-        <v>2280</v>
+        <v>2283</v>
       </c>
       <c r="C122" s="29" t="s">
-        <v>2281</v>
+        <v>2284</v>
       </c>
       <c r="D122" s="29" t="s">
-        <v>2282</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31984,103 +32069,103 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="97" t="s">
-        <v>2283</v>
+        <v>2286</v>
       </c>
       <c r="B124" s="22" t="s">
         <v>1173</v>
       </c>
       <c r="C124" s="22" t="s">
-        <v>1808</v>
+        <v>1811</v>
       </c>
       <c r="D124" s="22" t="s">
-        <v>1809</v>
+        <v>1812</v>
       </c>
       <c r="E124" s="22" t="s">
-        <v>1810</v>
+        <v>1813</v>
       </c>
       <c r="F124" s="22" t="s">
-        <v>1811</v>
+        <v>1814</v>
       </c>
       <c r="G124" s="97"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="97" t="s">
-        <v>2283</v>
+        <v>2286</v>
       </c>
       <c r="B125" s="22" t="s">
         <v>1174</v>
       </c>
       <c r="C125" s="22" t="s">
-        <v>1813</v>
+        <v>1816</v>
       </c>
       <c r="D125" s="22" t="s">
-        <v>1814</v>
+        <v>1817</v>
       </c>
       <c r="E125" s="22" t="s">
-        <v>1815</v>
+        <v>1818</v>
       </c>
       <c r="F125" s="22" t="s">
-        <v>1816</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="97" t="s">
-        <v>2283</v>
+        <v>2286</v>
       </c>
       <c r="B126" s="22" t="s">
         <v>1175</v>
       </c>
       <c r="C126" s="22" t="s">
-        <v>1818</v>
+        <v>1821</v>
       </c>
       <c r="D126" s="22" t="s">
-        <v>1819</v>
+        <v>1822</v>
       </c>
       <c r="E126" s="22" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="F126" s="22" t="s">
-        <v>1821</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="97" t="s">
-        <v>2283</v>
+        <v>2286</v>
       </c>
       <c r="B127" s="22" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="C127" s="22" t="s">
-        <v>1823</v>
+        <v>1826</v>
       </c>
       <c r="D127" s="22" t="s">
-        <v>1824</v>
+        <v>1827</v>
       </c>
       <c r="E127" s="22" t="s">
-        <v>1825</v>
+        <v>1828</v>
       </c>
       <c r="F127" s="22" t="s">
-        <v>1826</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="97" t="s">
-        <v>2283</v>
+        <v>2286</v>
       </c>
       <c r="B128" s="22" t="s">
         <v>1187</v>
       </c>
       <c r="C128" s="22" t="s">
-        <v>1828</v>
+        <v>1831</v>
       </c>
       <c r="D128" s="22" t="s">
-        <v>1829</v>
+        <v>1832</v>
       </c>
       <c r="E128" s="22" t="s">
-        <v>1830</v>
+        <v>1833</v>
       </c>
       <c r="F128" s="22" t="s">
-        <v>1831</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32088,13 +32173,13 @@
         <v>661</v>
       </c>
       <c r="B129" s="29" t="s">
-        <v>2284</v>
+        <v>2287</v>
       </c>
       <c r="C129" s="65" t="s">
-        <v>1981</v>
+        <v>1984</v>
       </c>
       <c r="D129" s="35" t="s">
-        <v>1982</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32105,10 +32190,10 @@
         <v>1211</v>
       </c>
       <c r="C130" s="65" t="s">
-        <v>2285</v>
+        <v>2288</v>
       </c>
       <c r="D130" s="35" t="s">
-        <v>2285</v>
+        <v>2288</v>
       </c>
       <c r="H130" s="103" t="s">
         <v>1209</v>
@@ -32119,16 +32204,16 @@
         <v>661</v>
       </c>
       <c r="B131" s="29" t="s">
-        <v>2286</v>
+        <v>2289</v>
       </c>
       <c r="C131" s="65" t="s">
-        <v>2287</v>
+        <v>2290</v>
       </c>
       <c r="D131" s="35" t="s">
-        <v>2288</v>
+        <v>2291</v>
       </c>
       <c r="H131" s="104" t="s">
-        <v>2289</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32136,13 +32221,13 @@
         <v>661</v>
       </c>
       <c r="B132" s="29" t="s">
-        <v>2290</v>
+        <v>2293</v>
       </c>
       <c r="C132" s="65" t="s">
-        <v>1990</v>
+        <v>1993</v>
       </c>
       <c r="D132" s="35" t="s">
-        <v>1991</v>
+        <v>1994</v>
       </c>
       <c r="H132" s="28" t="s">
         <v>935</v>
@@ -32153,13 +32238,13 @@
         <v>661</v>
       </c>
       <c r="B133" s="29" t="s">
-        <v>2291</v>
+        <v>2294</v>
       </c>
       <c r="C133" s="65" t="s">
-        <v>1993</v>
+        <v>1996</v>
       </c>
       <c r="D133" s="35" t="s">
-        <v>1994</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32177,13 +32262,13 @@
         <v>667</v>
       </c>
       <c r="B135" s="29" t="s">
-        <v>2284</v>
+        <v>2287</v>
       </c>
       <c r="C135" s="65" t="s">
-        <v>1981</v>
+        <v>1984</v>
       </c>
       <c r="D135" s="35" t="s">
-        <v>1982</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32191,13 +32276,13 @@
         <v>667</v>
       </c>
       <c r="B136" s="29" t="s">
-        <v>2292</v>
+        <v>2295</v>
       </c>
       <c r="C136" s="65" t="s">
-        <v>2293</v>
+        <v>2296</v>
       </c>
       <c r="D136" s="35" t="s">
-        <v>2294</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32205,13 +32290,13 @@
         <v>667</v>
       </c>
       <c r="B137" s="29" t="s">
-        <v>2290</v>
+        <v>2293</v>
       </c>
       <c r="C137" s="65" t="s">
-        <v>1990</v>
+        <v>1993</v>
       </c>
       <c r="D137" s="35" t="s">
-        <v>1991</v>
+        <v>1994</v>
       </c>
       <c r="H137" s="28" t="s">
         <v>935</v>
@@ -32222,13 +32307,13 @@
         <v>667</v>
       </c>
       <c r="B138" s="29" t="s">
-        <v>2291</v>
+        <v>2294</v>
       </c>
       <c r="C138" s="65" t="s">
-        <v>1993</v>
+        <v>1996</v>
       </c>
       <c r="D138" s="35" t="s">
-        <v>1994</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32236,13 +32321,13 @@
         <v>667</v>
       </c>
       <c r="B139" s="29" t="s">
-        <v>2295</v>
+        <v>2298</v>
       </c>
       <c r="C139" s="65" t="s">
-        <v>2296</v>
+        <v>2299</v>
       </c>
       <c r="D139" s="35" t="s">
-        <v>2297</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32250,13 +32335,13 @@
         <v>667</v>
       </c>
       <c r="B140" s="29" t="s">
-        <v>2298</v>
+        <v>2301</v>
       </c>
       <c r="C140" s="65" t="s">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="D140" s="35" t="s">
-        <v>1997</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32266,7 +32351,7 @@
       <c r="C141" s="35"/>
       <c r="D141" s="35"/>
       <c r="G141" s="22" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32274,16 +32359,16 @@
         <v>557</v>
       </c>
       <c r="B142" s="29" t="s">
-        <v>2299</v>
+        <v>2302</v>
       </c>
       <c r="C142" s="35" t="s">
-        <v>2300</v>
+        <v>2303</v>
       </c>
       <c r="D142" s="35" t="s">
-        <v>2301</v>
+        <v>2304</v>
       </c>
       <c r="H142" s="11" t="s">
-        <v>2302</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32294,13 +32379,13 @@
         <v>1199</v>
       </c>
       <c r="C143" s="35" t="s">
-        <v>2303</v>
+        <v>2306</v>
       </c>
       <c r="D143" s="35" t="s">
-        <v>2304</v>
+        <v>2307</v>
       </c>
       <c r="H143" s="65" t="s">
-        <v>2305</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32311,10 +32396,10 @@
         <v>1141</v>
       </c>
       <c r="C144" s="35" t="s">
-        <v>2306</v>
+        <v>2309</v>
       </c>
       <c r="D144" s="35" t="s">
-        <v>2307</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32322,13 +32407,13 @@
         <v>557</v>
       </c>
       <c r="B145" s="29" t="s">
-        <v>2308</v>
+        <v>2311</v>
       </c>
       <c r="C145" s="35" t="s">
-        <v>2309</v>
+        <v>2312</v>
       </c>
       <c r="D145" s="35" t="s">
-        <v>2310</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32338,7 +32423,7 @@
       <c r="C146" s="35"/>
       <c r="D146" s="35"/>
       <c r="G146" s="29" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32346,13 +32431,13 @@
         <v>590</v>
       </c>
       <c r="B147" s="29" t="s">
-        <v>2311</v>
+        <v>2314</v>
       </c>
       <c r="C147" s="35" t="s">
-        <v>2312</v>
+        <v>2315</v>
       </c>
       <c r="D147" s="35" t="s">
-        <v>2312</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32360,13 +32445,13 @@
         <v>590</v>
       </c>
       <c r="B148" s="29" t="s">
-        <v>2313</v>
+        <v>2316</v>
       </c>
       <c r="C148" s="35" t="s">
-        <v>2314</v>
+        <v>2317</v>
       </c>
       <c r="D148" s="35" t="s">
-        <v>2315</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32376,7 +32461,7 @@
       <c r="C149" s="35"/>
       <c r="D149" s="35"/>
       <c r="G149" s="29" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32384,13 +32469,13 @@
         <v>614</v>
       </c>
       <c r="B150" s="29" t="s">
-        <v>2316</v>
+        <v>2319</v>
       </c>
       <c r="C150" s="65" t="s">
-        <v>2317</v>
+        <v>2320</v>
       </c>
       <c r="D150" s="35" t="s">
-        <v>2318</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32398,13 +32483,13 @@
         <v>614</v>
       </c>
       <c r="B151" s="29" t="s">
-        <v>2319</v>
+        <v>2322</v>
       </c>
       <c r="C151" s="65" t="s">
-        <v>2320</v>
+        <v>2323</v>
       </c>
       <c r="D151" s="35" t="s">
-        <v>2321</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32414,7 +32499,7 @@
       <c r="C152" s="35"/>
       <c r="D152" s="35"/>
       <c r="G152" s="22" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32424,7 +32509,7 @@
       <c r="C153" s="35"/>
       <c r="D153" s="35"/>
       <c r="G153" s="29" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32432,13 +32517,13 @@
         <v>621</v>
       </c>
       <c r="B154" s="29" t="s">
-        <v>2322</v>
+        <v>2325</v>
       </c>
       <c r="C154" s="65" t="s">
-        <v>2323</v>
+        <v>2326</v>
       </c>
       <c r="D154" s="35" t="s">
-        <v>2324</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32446,13 +32531,13 @@
         <v>621</v>
       </c>
       <c r="B155" s="29" t="s">
-        <v>2325</v>
+        <v>2328</v>
       </c>
       <c r="C155" s="65" t="s">
-        <v>2326</v>
+        <v>2329</v>
       </c>
       <c r="D155" s="35" t="s">
-        <v>2326</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32460,13 +32545,13 @@
         <v>621</v>
       </c>
       <c r="B156" s="29" t="s">
-        <v>2327</v>
+        <v>2330</v>
       </c>
       <c r="C156" s="65" t="s">
-        <v>2328</v>
+        <v>2331</v>
       </c>
       <c r="D156" s="65" t="s">
-        <v>2328</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32474,13 +32559,13 @@
         <v>621</v>
       </c>
       <c r="B157" s="29" t="s">
-        <v>2329</v>
+        <v>2332</v>
       </c>
       <c r="C157" s="65" t="s">
-        <v>2330</v>
+        <v>2333</v>
       </c>
       <c r="D157" s="65" t="s">
-        <v>2330</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32490,7 +32575,7 @@
       <c r="C158" s="35"/>
       <c r="D158" s="35"/>
       <c r="G158" s="22" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32500,7 +32585,7 @@
       <c r="C159" s="35"/>
       <c r="D159" s="35"/>
       <c r="G159" s="29" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32508,13 +32593,13 @@
         <v>626</v>
       </c>
       <c r="B160" s="29" t="s">
-        <v>2331</v>
+        <v>2334</v>
       </c>
       <c r="C160" s="65" t="s">
-        <v>2332</v>
+        <v>2335</v>
       </c>
       <c r="D160" s="35" t="s">
-        <v>2333</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32522,13 +32607,13 @@
         <v>626</v>
       </c>
       <c r="B161" s="29" t="s">
-        <v>2334</v>
+        <v>2337</v>
       </c>
       <c r="C161" s="65" t="s">
-        <v>2335</v>
+        <v>2338</v>
       </c>
       <c r="D161" s="35" t="s">
-        <v>2336</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32536,13 +32621,13 @@
         <v>626</v>
       </c>
       <c r="B162" s="29" t="s">
-        <v>2316</v>
+        <v>2319</v>
       </c>
       <c r="C162" s="65" t="s">
-        <v>2337</v>
+        <v>2340</v>
       </c>
       <c r="D162" s="35" t="s">
-        <v>2338</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32550,13 +32635,13 @@
         <v>626</v>
       </c>
       <c r="B163" s="29" t="s">
-        <v>2339</v>
+        <v>2342</v>
       </c>
       <c r="C163" s="65" t="s">
-        <v>2340</v>
+        <v>2343</v>
       </c>
       <c r="D163" s="65" t="s">
-        <v>2340</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32564,13 +32649,13 @@
         <v>626</v>
       </c>
       <c r="B164" s="29" t="s">
-        <v>2341</v>
+        <v>2344</v>
       </c>
       <c r="C164" s="65" t="s">
-        <v>2342</v>
+        <v>2345</v>
       </c>
       <c r="D164" s="35" t="s">
-        <v>2343</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32580,7 +32665,7 @@
       <c r="C165" s="35"/>
       <c r="D165" s="35"/>
       <c r="G165" s="22" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32590,7 +32675,7 @@
       <c r="C166" s="35"/>
       <c r="D166" s="35"/>
       <c r="G166" s="29" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32598,13 +32683,13 @@
         <v>762</v>
       </c>
       <c r="B167" s="22" t="s">
-        <v>2290</v>
+        <v>2293</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>1931</v>
+        <v>1934</v>
       </c>
       <c r="E167" s="22"/>
       <c r="F167" s="22"/>
@@ -32617,13 +32702,13 @@
         <v>762</v>
       </c>
       <c r="B168" s="22" t="s">
-        <v>2291</v>
+        <v>2294</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>1948</v>
+        <v>1951</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>1949</v>
+        <v>1952</v>
       </c>
       <c r="E168" s="22"/>
       <c r="F168" s="22"/>
@@ -32636,13 +32721,13 @@
         <v>762</v>
       </c>
       <c r="B169" s="22" t="s">
-        <v>2298</v>
+        <v>2301</v>
       </c>
       <c r="C169" s="65" t="s">
-        <v>2344</v>
+        <v>2347</v>
       </c>
       <c r="D169" s="35" t="s">
-        <v>2345</v>
+        <v>2348</v>
       </c>
       <c r="E169" s="22"/>
       <c r="F169" s="22"/>
@@ -32655,13 +32740,13 @@
         <v>762</v>
       </c>
       <c r="B170" s="22" t="s">
-        <v>2284</v>
+        <v>2287</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>1883</v>
+        <v>1886</v>
       </c>
       <c r="D170" s="10" t="s">
-        <v>1884</v>
+        <v>1887</v>
       </c>
       <c r="E170" s="22"/>
       <c r="F170" s="22"/>
@@ -32674,13 +32759,13 @@
         <v>762</v>
       </c>
       <c r="B171" s="22" t="s">
-        <v>2346</v>
+        <v>2349</v>
       </c>
       <c r="C171" s="10" t="s">
-        <v>1886</v>
+        <v>1889</v>
       </c>
       <c r="D171" s="10" t="s">
-        <v>1887</v>
+        <v>1890</v>
       </c>
       <c r="E171" s="22"/>
       <c r="F171" s="22"/>
@@ -32696,10 +32781,10 @@
         <v>212</v>
       </c>
       <c r="C172" s="28" t="s">
-        <v>2347</v>
+        <v>2350</v>
       </c>
       <c r="D172" s="65" t="s">
-        <v>2348</v>
+        <v>2351</v>
       </c>
       <c r="E172" s="22"/>
       <c r="F172" s="22"/>
@@ -32714,13 +32799,13 @@
         <v>762</v>
       </c>
       <c r="B173" s="22" t="s">
-        <v>2349</v>
+        <v>2352</v>
       </c>
       <c r="C173" s="28" t="s">
-        <v>2350</v>
+        <v>2353</v>
       </c>
       <c r="D173" s="65" t="s">
-        <v>2351</v>
+        <v>2354</v>
       </c>
       <c r="E173" s="22"/>
       <c r="F173" s="22"/>
@@ -32735,13 +32820,13 @@
         <v>112</v>
       </c>
       <c r="B174" s="22" t="s">
-        <v>2352</v>
+        <v>2355</v>
       </c>
       <c r="C174" s="28" t="s">
-        <v>2353</v>
+        <v>2356</v>
       </c>
       <c r="D174" s="65" t="s">
-        <v>2354</v>
+        <v>2357</v>
       </c>
       <c r="E174" s="22"/>
       <c r="F174" s="22"/>
@@ -32754,13 +32839,13 @@
         <v>112</v>
       </c>
       <c r="B175" s="22" t="s">
-        <v>2355</v>
+        <v>2358</v>
       </c>
       <c r="C175" s="28" t="s">
-        <v>2356</v>
+        <v>2359</v>
       </c>
       <c r="D175" s="65" t="s">
-        <v>2357</v>
+        <v>2360</v>
       </c>
       <c r="E175" s="22"/>
       <c r="F175" s="22"/>
@@ -32814,10 +32899,10 @@
         <v>2</v>
       </c>
       <c r="C178" s="74" t="s">
-        <v>2358</v>
+        <v>2361</v>
       </c>
       <c r="D178" s="74" t="s">
-        <v>2358</v>
+        <v>2361</v>
       </c>
       <c r="E178" s="22"/>
       <c r="F178" s="22"/>
@@ -32833,10 +32918,10 @@
         <v>1141</v>
       </c>
       <c r="C179" s="28" t="s">
-        <v>2359</v>
+        <v>2362</v>
       </c>
       <c r="D179" s="10" t="s">
-        <v>2360</v>
+        <v>2363</v>
       </c>
       <c r="E179" s="22"/>
       <c r="F179" s="22"/>
@@ -32852,10 +32937,10 @@
         <v>1199</v>
       </c>
       <c r="C180" s="28" t="s">
-        <v>2361</v>
+        <v>2364</v>
       </c>
       <c r="D180" s="10" t="s">
-        <v>2362</v>
+        <v>2365</v>
       </c>
       <c r="E180" s="22"/>
       <c r="F180" s="22"/>
@@ -32873,7 +32958,7 @@
       <c r="E181" s="22"/>
       <c r="F181" s="22"/>
       <c r="G181" s="22" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="H181" s="22"/>
       <c r="I181" s="22"/>
@@ -32883,13 +32968,13 @@
         <v>229</v>
       </c>
       <c r="B182" s="22" t="s">
-        <v>2363</v>
+        <v>2366</v>
       </c>
       <c r="C182" s="21" t="s">
-        <v>2364</v>
+        <v>2367</v>
       </c>
       <c r="D182" s="65" t="s">
-        <v>2365</v>
+        <v>2368</v>
       </c>
       <c r="E182" s="22"/>
       <c r="F182" s="22"/>
@@ -32904,13 +32989,13 @@
         <v>229</v>
       </c>
       <c r="B183" s="22" t="s">
-        <v>2366</v>
+        <v>2369</v>
       </c>
       <c r="C183" s="21" t="s">
-        <v>2367</v>
+        <v>2370</v>
       </c>
       <c r="D183" s="65" t="s">
-        <v>2368</v>
+        <v>2371</v>
       </c>
       <c r="E183" s="22"/>
       <c r="F183" s="22"/>
@@ -32925,13 +33010,13 @@
         <v>229</v>
       </c>
       <c r="B184" s="22" t="s">
-        <v>2369</v>
+        <v>2372</v>
       </c>
       <c r="C184" s="21" t="s">
-        <v>2370</v>
+        <v>2373</v>
       </c>
       <c r="D184" s="65" t="s">
-        <v>2371</v>
+        <v>2374</v>
       </c>
       <c r="E184" s="22"/>
       <c r="F184" s="22"/>
@@ -32946,13 +33031,13 @@
         <v>229</v>
       </c>
       <c r="B185" s="22" t="s">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="C185" s="21" t="s">
-        <v>2373</v>
+        <v>2376</v>
       </c>
       <c r="D185" s="65" t="s">
-        <v>2374</v>
+        <v>2377</v>
       </c>
       <c r="E185" s="22"/>
       <c r="F185" s="22"/>
@@ -32967,13 +33052,13 @@
         <v>229</v>
       </c>
       <c r="B186" s="22" t="s">
-        <v>2375</v>
+        <v>2378</v>
       </c>
       <c r="C186" s="21" t="s">
-        <v>2376</v>
+        <v>2379</v>
       </c>
       <c r="D186" s="65" t="s">
-        <v>2377</v>
+        <v>2380</v>
       </c>
       <c r="E186" s="22"/>
       <c r="F186" s="22"/>
@@ -32988,13 +33073,13 @@
         <v>229</v>
       </c>
       <c r="B187" s="22" t="s">
-        <v>2378</v>
+        <v>2381</v>
       </c>
       <c r="C187" s="21" t="s">
-        <v>2379</v>
+        <v>2382</v>
       </c>
       <c r="D187" s="65" t="s">
-        <v>2380</v>
+        <v>2383</v>
       </c>
       <c r="E187" s="22"/>
       <c r="F187" s="22"/>
@@ -33009,13 +33094,13 @@
         <v>229</v>
       </c>
       <c r="B188" s="22" t="s">
-        <v>2381</v>
+        <v>2384</v>
       </c>
       <c r="C188" s="21" t="s">
-        <v>2382</v>
+        <v>2385</v>
       </c>
       <c r="D188" s="65" t="s">
-        <v>2383</v>
+        <v>2386</v>
       </c>
       <c r="E188" s="22"/>
       <c r="F188" s="22"/>
@@ -33030,13 +33115,13 @@
         <v>229</v>
       </c>
       <c r="B189" s="22" t="s">
-        <v>2384</v>
+        <v>2387</v>
       </c>
       <c r="C189" s="21" t="s">
-        <v>2385</v>
+        <v>2388</v>
       </c>
       <c r="D189" s="65" t="s">
-        <v>2386</v>
+        <v>2389</v>
       </c>
       <c r="E189" s="22"/>
       <c r="F189" s="22"/>
@@ -33051,13 +33136,13 @@
         <v>229</v>
       </c>
       <c r="B190" s="22" t="s">
-        <v>2387</v>
+        <v>2390</v>
       </c>
       <c r="C190" s="21" t="s">
-        <v>2388</v>
+        <v>2391</v>
       </c>
       <c r="D190" s="65" t="s">
-        <v>2389</v>
+        <v>2392</v>
       </c>
       <c r="E190" s="22"/>
       <c r="F190" s="22"/>
@@ -33075,10 +33160,10 @@
         <v>212</v>
       </c>
       <c r="C191" s="21" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="D191" s="65" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="E191" s="22"/>
       <c r="F191" s="22"/>
@@ -33108,13 +33193,13 @@
         <v>241</v>
       </c>
       <c r="B193" s="22" t="s">
-        <v>2390</v>
+        <v>2393</v>
       </c>
       <c r="C193" s="21" t="s">
-        <v>2391</v>
+        <v>2394</v>
       </c>
       <c r="D193" s="65" t="s">
-        <v>2392</v>
+        <v>2395</v>
       </c>
       <c r="E193" s="22"/>
       <c r="F193" s="22"/>
@@ -33129,13 +33214,13 @@
         <v>241</v>
       </c>
       <c r="B194" s="22" t="s">
-        <v>2393</v>
+        <v>2396</v>
       </c>
       <c r="C194" s="21" t="s">
-        <v>2394</v>
+        <v>2397</v>
       </c>
       <c r="D194" s="65" t="s">
-        <v>2395</v>
+        <v>2398</v>
       </c>
       <c r="E194" s="22"/>
       <c r="F194" s="22"/>
@@ -33150,13 +33235,13 @@
         <v>241</v>
       </c>
       <c r="B195" s="22" t="s">
-        <v>2396</v>
+        <v>2399</v>
       </c>
       <c r="C195" s="21" t="s">
-        <v>2397</v>
+        <v>2400</v>
       </c>
       <c r="D195" s="65" t="s">
-        <v>2398</v>
+        <v>2401</v>
       </c>
       <c r="E195" s="22"/>
       <c r="F195" s="22"/>
@@ -33171,13 +33256,13 @@
         <v>241</v>
       </c>
       <c r="B196" s="22" t="s">
-        <v>2399</v>
+        <v>2402</v>
       </c>
       <c r="C196" s="21" t="s">
-        <v>2400</v>
+        <v>2403</v>
       </c>
       <c r="D196" s="65" t="s">
-        <v>2401</v>
+        <v>2404</v>
       </c>
       <c r="E196" s="22"/>
       <c r="F196" s="22"/>
@@ -33192,13 +33277,13 @@
         <v>241</v>
       </c>
       <c r="B197" s="22" t="s">
-        <v>2402</v>
+        <v>2405</v>
       </c>
       <c r="C197" s="21" t="s">
-        <v>2403</v>
+        <v>2406</v>
       </c>
       <c r="D197" s="65" t="s">
-        <v>2404</v>
+        <v>2407</v>
       </c>
       <c r="E197" s="22"/>
       <c r="F197" s="22"/>
@@ -33213,13 +33298,13 @@
         <v>241</v>
       </c>
       <c r="B198" s="22" t="s">
-        <v>2405</v>
+        <v>2408</v>
       </c>
       <c r="C198" s="21" t="s">
-        <v>2406</v>
+        <v>2409</v>
       </c>
       <c r="D198" s="65" t="s">
-        <v>2407</v>
+        <v>2410</v>
       </c>
       <c r="E198" s="22"/>
       <c r="F198" s="22"/>
@@ -33234,13 +33319,13 @@
         <v>241</v>
       </c>
       <c r="B199" s="22" t="s">
-        <v>2408</v>
+        <v>2411</v>
       </c>
       <c r="C199" s="21" t="s">
-        <v>2409</v>
+        <v>2412</v>
       </c>
       <c r="D199" s="65" t="s">
-        <v>2410</v>
+        <v>2413</v>
       </c>
       <c r="E199" s="22"/>
       <c r="F199" s="22"/>
@@ -33258,10 +33343,10 @@
         <v>1181</v>
       </c>
       <c r="C200" s="21" t="s">
-        <v>2411</v>
+        <v>2414</v>
       </c>
       <c r="D200" s="65" t="s">
-        <v>2412</v>
+        <v>2415</v>
       </c>
       <c r="E200" s="22"/>
       <c r="F200" s="22"/>
@@ -33278,10 +33363,10 @@
         <v>212</v>
       </c>
       <c r="C201" s="21" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="D201" s="65" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="E201" s="22"/>
       <c r="F201" s="22"/>
@@ -33299,10 +33384,10 @@
         <v>1145</v>
       </c>
       <c r="C202" s="22" t="s">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="D202" s="22" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="E202" s="22"/>
       <c r="F202" s="22"/>
@@ -33317,13 +33402,13 @@
         <v>270</v>
       </c>
       <c r="B203" s="22" t="s">
-        <v>2413</v>
+        <v>2416</v>
       </c>
       <c r="C203" s="21" t="s">
-        <v>2414</v>
+        <v>2417</v>
       </c>
       <c r="D203" s="65" t="s">
-        <v>2415</v>
+        <v>2418</v>
       </c>
       <c r="E203" s="22"/>
       <c r="F203" s="22"/>
@@ -33336,13 +33421,13 @@
         <v>270</v>
       </c>
       <c r="B204" s="22" t="s">
-        <v>2416</v>
+        <v>2419</v>
       </c>
       <c r="C204" s="21" t="s">
-        <v>2417</v>
+        <v>2420</v>
       </c>
       <c r="D204" s="65" t="s">
-        <v>2418</v>
+        <v>2421</v>
       </c>
       <c r="E204" s="22"/>
       <c r="F204" s="22"/>
@@ -33355,13 +33440,13 @@
         <v>270</v>
       </c>
       <c r="B205" s="22" t="s">
-        <v>2419</v>
+        <v>2422</v>
       </c>
       <c r="C205" s="21" t="s">
-        <v>2420</v>
+        <v>2423</v>
       </c>
       <c r="D205" s="65" t="s">
-        <v>2421</v>
+        <v>2424</v>
       </c>
       <c r="E205" s="22"/>
       <c r="F205" s="22"/>
@@ -33374,13 +33459,13 @@
         <v>270</v>
       </c>
       <c r="B206" s="22" t="s">
-        <v>2422</v>
+        <v>2425</v>
       </c>
       <c r="C206" s="21" t="s">
-        <v>2423</v>
+        <v>2426</v>
       </c>
       <c r="D206" s="65" t="s">
-        <v>2424</v>
+        <v>2427</v>
       </c>
       <c r="E206" s="22"/>
       <c r="F206" s="22"/>
@@ -33393,13 +33478,13 @@
         <v>270</v>
       </c>
       <c r="B207" s="22" t="s">
-        <v>2425</v>
+        <v>2428</v>
       </c>
       <c r="C207" s="21" t="s">
-        <v>2426</v>
+        <v>2429</v>
       </c>
       <c r="D207" s="65" t="s">
-        <v>2427</v>
+        <v>2430</v>
       </c>
       <c r="E207" s="22"/>
       <c r="F207" s="22"/>
@@ -33412,13 +33497,13 @@
         <v>277</v>
       </c>
       <c r="B208" s="22" t="s">
-        <v>2413</v>
+        <v>2416</v>
       </c>
       <c r="C208" s="21" t="s">
-        <v>2414</v>
+        <v>2417</v>
       </c>
       <c r="D208" s="65" t="s">
-        <v>2415</v>
+        <v>2418</v>
       </c>
       <c r="E208" s="22"/>
       <c r="F208" s="22"/>
@@ -33433,13 +33518,13 @@
         <v>277</v>
       </c>
       <c r="B209" s="22" t="s">
-        <v>2416</v>
+        <v>2419</v>
       </c>
       <c r="C209" s="21" t="s">
-        <v>2417</v>
+        <v>2420</v>
       </c>
       <c r="D209" s="65" t="s">
-        <v>2418</v>
+        <v>2421</v>
       </c>
       <c r="E209" s="22"/>
       <c r="F209" s="22"/>
@@ -33452,13 +33537,13 @@
         <v>277</v>
       </c>
       <c r="B210" s="22" t="s">
-        <v>2419</v>
+        <v>2422</v>
       </c>
       <c r="C210" s="21" t="s">
-        <v>2420</v>
+        <v>2423</v>
       </c>
       <c r="D210" s="65" t="s">
-        <v>2421</v>
+        <v>2424</v>
       </c>
       <c r="E210" s="22"/>
       <c r="F210" s="22"/>
@@ -33471,13 +33556,13 @@
         <v>277</v>
       </c>
       <c r="B211" s="22" t="s">
-        <v>2422</v>
+        <v>2425</v>
       </c>
       <c r="C211" s="21" t="s">
-        <v>2423</v>
+        <v>2426</v>
       </c>
       <c r="D211" s="65" t="s">
-        <v>2424</v>
+        <v>2427</v>
       </c>
       <c r="E211" s="22"/>
       <c r="F211" s="22"/>
@@ -33490,13 +33575,13 @@
         <v>277</v>
       </c>
       <c r="B212" s="22" t="s">
-        <v>2425</v>
+        <v>2428</v>
       </c>
       <c r="C212" s="21" t="s">
-        <v>2426</v>
+        <v>2429</v>
       </c>
       <c r="D212" s="65" t="s">
-        <v>2427</v>
+        <v>2430</v>
       </c>
       <c r="E212" s="22"/>
       <c r="F212" s="22"/>
@@ -33509,13 +33594,13 @@
         <v>830</v>
       </c>
       <c r="B213" s="29" t="s">
-        <v>2284</v>
+        <v>2287</v>
       </c>
       <c r="C213" s="29" t="s">
-        <v>1981</v>
+        <v>1984</v>
       </c>
       <c r="D213" s="29" t="s">
-        <v>1982</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33523,13 +33608,13 @@
         <v>830</v>
       </c>
       <c r="B214" s="29" t="s">
-        <v>2292</v>
+        <v>2295</v>
       </c>
       <c r="C214" s="29" t="s">
-        <v>2293</v>
+        <v>2296</v>
       </c>
       <c r="D214" s="29" t="s">
-        <v>2294</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33537,13 +33622,13 @@
         <v>830</v>
       </c>
       <c r="B215" s="29" t="s">
-        <v>2428</v>
+        <v>2431</v>
       </c>
       <c r="C215" s="29" t="s">
-        <v>2429</v>
+        <v>2432</v>
       </c>
       <c r="D215" s="29" t="s">
-        <v>2430</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33551,13 +33636,13 @@
         <v>830</v>
       </c>
       <c r="B216" s="29" t="s">
-        <v>2298</v>
+        <v>2301</v>
       </c>
       <c r="C216" s="29" t="s">
-        <v>2431</v>
+        <v>2434</v>
       </c>
       <c r="D216" s="29" t="s">
-        <v>2432</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33565,7 +33650,7 @@
         <v>830</v>
       </c>
       <c r="G217" s="29" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33573,13 +33658,13 @@
         <v>855</v>
       </c>
       <c r="B218" s="29" t="s">
-        <v>2433</v>
+        <v>2436</v>
       </c>
       <c r="C218" s="29" t="s">
-        <v>2434</v>
+        <v>2437</v>
       </c>
       <c r="D218" s="29" t="s">
-        <v>2435</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33587,13 +33672,13 @@
         <v>855</v>
       </c>
       <c r="B219" s="29" t="s">
-        <v>2436</v>
+        <v>2439</v>
       </c>
       <c r="C219" s="29" t="s">
-        <v>2437</v>
+        <v>2440</v>
       </c>
       <c r="D219" s="29" t="s">
-        <v>2438</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33601,13 +33686,13 @@
         <v>855</v>
       </c>
       <c r="B220" s="29" t="s">
-        <v>2439</v>
+        <v>2442</v>
       </c>
       <c r="C220" s="29" t="s">
-        <v>2440</v>
+        <v>2443</v>
       </c>
       <c r="D220" s="29" t="s">
-        <v>2441</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33615,13 +33700,13 @@
         <v>855</v>
       </c>
       <c r="B221" s="29" t="s">
-        <v>2442</v>
+        <v>2445</v>
       </c>
       <c r="C221" s="29" t="s">
-        <v>2443</v>
+        <v>2446</v>
       </c>
       <c r="D221" s="29" t="s">
-        <v>2444</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33629,13 +33714,13 @@
         <v>855</v>
       </c>
       <c r="B222" s="29" t="s">
-        <v>2445</v>
+        <v>2448</v>
       </c>
       <c r="C222" s="29" t="s">
-        <v>2446</v>
+        <v>2449</v>
       </c>
       <c r="D222" s="29" t="s">
-        <v>2447</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33643,13 +33728,13 @@
         <v>855</v>
       </c>
       <c r="B223" s="29" t="s">
-        <v>2448</v>
+        <v>2451</v>
       </c>
       <c r="C223" s="29" t="s">
-        <v>2449</v>
+        <v>2452</v>
       </c>
       <c r="D223" s="29" t="s">
-        <v>2450</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33660,10 +33745,10 @@
         <v>212</v>
       </c>
       <c r="C224" s="29" t="s">
-        <v>2451</v>
+        <v>2454</v>
       </c>
       <c r="D224" s="29" t="s">
-        <v>2452</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33671,13 +33756,13 @@
         <v>859</v>
       </c>
       <c r="B225" s="29" t="s">
-        <v>2284</v>
+        <v>2287</v>
       </c>
       <c r="C225" s="29" t="s">
-        <v>1981</v>
+        <v>1984</v>
       </c>
       <c r="D225" s="29" t="s">
-        <v>1982</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33685,13 +33770,13 @@
         <v>859</v>
       </c>
       <c r="B226" s="29" t="s">
-        <v>2292</v>
+        <v>2295</v>
       </c>
       <c r="C226" s="29" t="s">
-        <v>2293</v>
+        <v>2296</v>
       </c>
       <c r="D226" s="29" t="s">
-        <v>2294</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33699,41 +33784,46 @@
         <v>859</v>
       </c>
       <c r="B227" s="29" t="s">
-        <v>2290</v>
+        <v>2293</v>
       </c>
       <c r="C227" s="29" t="s">
-        <v>2453</v>
+        <v>2456</v>
       </c>
       <c r="D227" s="29" t="s">
-        <v>2454</v>
-      </c>
-    </row>
-    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="228" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="29" t="s">
         <v>859</v>
       </c>
       <c r="B228" s="29" t="s">
-        <v>2291</v>
+        <v>2294</v>
       </c>
       <c r="C228" s="29" t="s">
-        <v>2455</v>
+        <v>2458</v>
       </c>
       <c r="D228" s="29" t="s">
-        <v>2456</v>
-      </c>
+        <v>2459</v>
+      </c>
+      <c r="E228" s="29"/>
+      <c r="F228" s="29"/>
+      <c r="G228" s="29"/>
+      <c r="H228" s="29"/>
+      <c r="I228" s="29"/>
     </row>
     <row r="229" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="29" t="s">
         <v>859</v>
       </c>
       <c r="B229" s="29" t="s">
-        <v>2298</v>
+        <v>2301</v>
       </c>
       <c r="C229" s="29" t="s">
-        <v>2431</v>
+        <v>2434</v>
       </c>
       <c r="D229" s="29" t="s">
-        <v>2432</v>
+        <v>2435</v>
       </c>
       <c r="E229" s="29"/>
       <c r="F229" s="29"/>
@@ -33749,10 +33839,10 @@
         <v>212</v>
       </c>
       <c r="C230" s="29" t="s">
-        <v>2457</v>
+        <v>2460</v>
       </c>
       <c r="D230" s="29" t="s">
-        <v>2458</v>
+        <v>2461</v>
       </c>
       <c r="E230" s="29"/>
       <c r="F230" s="29"/>
@@ -33768,10 +33858,10 @@
         <v>1232</v>
       </c>
       <c r="C231" s="65" t="s">
-        <v>2459</v>
+        <v>2462</v>
       </c>
       <c r="D231" s="65" t="s">
-        <v>2460</v>
+        <v>2463</v>
       </c>
       <c r="E231" s="29"/>
       <c r="F231" s="29"/>
@@ -33784,13 +33874,13 @@
         <v>1025</v>
       </c>
       <c r="B232" s="29" t="s">
-        <v>2461</v>
+        <v>2464</v>
       </c>
       <c r="C232" s="65" t="s">
-        <v>2462</v>
+        <v>2465</v>
       </c>
       <c r="D232" s="65" t="s">
-        <v>2463</v>
+        <v>2466</v>
       </c>
       <c r="E232" s="29"/>
       <c r="F232" s="29"/>
@@ -33805,13 +33895,13 @@
         <v>1025</v>
       </c>
       <c r="B233" s="29" t="s">
-        <v>2464</v>
+        <v>2467</v>
       </c>
       <c r="C233" s="65" t="s">
-        <v>2465</v>
+        <v>2468</v>
       </c>
       <c r="D233" s="65" t="s">
-        <v>2466</v>
+        <v>2469</v>
       </c>
       <c r="E233" s="29"/>
       <c r="F233" s="29"/>
@@ -33826,13 +33916,13 @@
         <v>1025</v>
       </c>
       <c r="B234" s="29" t="s">
-        <v>2467</v>
+        <v>2470</v>
       </c>
       <c r="C234" s="65" t="s">
-        <v>2468</v>
+        <v>2471</v>
       </c>
       <c r="D234" s="28" t="s">
-        <v>2469</v>
+        <v>2472</v>
       </c>
       <c r="E234" s="29"/>
       <c r="F234" s="29"/>
@@ -33847,13 +33937,13 @@
         <v>1025</v>
       </c>
       <c r="B235" s="29" t="s">
-        <v>2470</v>
+        <v>2473</v>
       </c>
       <c r="C235" s="65" t="s">
-        <v>2471</v>
+        <v>2474</v>
       </c>
       <c r="D235" s="21" t="s">
-        <v>2472</v>
+        <v>2475</v>
       </c>
       <c r="E235" s="29"/>
       <c r="F235" s="29"/>
@@ -33866,13 +33956,13 @@
         <v>1031</v>
       </c>
       <c r="B236" s="29" t="s">
-        <v>2473</v>
+        <v>2476</v>
       </c>
       <c r="C236" s="65" t="s">
-        <v>2474</v>
+        <v>2477</v>
       </c>
       <c r="D236" s="65" t="s">
-        <v>2475</v>
+        <v>2478</v>
       </c>
       <c r="E236" s="29"/>
       <c r="F236" s="29"/>
@@ -33887,13 +33977,13 @@
         <v>1031</v>
       </c>
       <c r="B237" s="29" t="s">
-        <v>2476</v>
+        <v>2479</v>
       </c>
       <c r="C237" s="65" t="s">
-        <v>2477</v>
+        <v>2480</v>
       </c>
       <c r="D237" s="65" t="s">
-        <v>2478</v>
+        <v>2481</v>
       </c>
       <c r="E237" s="29"/>
       <c r="F237" s="29"/>
@@ -33908,13 +33998,13 @@
         <v>1031</v>
       </c>
       <c r="B238" s="29" t="s">
-        <v>2479</v>
+        <v>2482</v>
       </c>
       <c r="C238" s="65" t="s">
-        <v>2480</v>
+        <v>2483</v>
       </c>
       <c r="D238" s="65" t="s">
-        <v>2481</v>
+        <v>2484</v>
       </c>
       <c r="E238" s="29"/>
       <c r="F238" s="29"/>
@@ -33924,16 +34014,16 @@
     </row>
     <row r="239" s="2" customFormat="true" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="11" t="s">
-        <v>2482</v>
+        <v>2485</v>
       </c>
       <c r="B239" s="29" t="s">
         <v>1141</v>
       </c>
       <c r="C239" s="28" t="s">
-        <v>2483</v>
+        <v>2486</v>
       </c>
       <c r="D239" s="65" t="s">
-        <v>2484</v>
+        <v>2487</v>
       </c>
       <c r="E239" s="29"/>
       <c r="F239" s="29"/>
@@ -33943,16 +34033,16 @@
     </row>
     <row r="240" s="2" customFormat="true" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="11" t="s">
-        <v>2482</v>
+        <v>2485</v>
       </c>
       <c r="B240" s="29" t="s">
         <v>1199</v>
       </c>
       <c r="C240" s="28" t="s">
-        <v>2485</v>
+        <v>2488</v>
       </c>
       <c r="D240" s="21" t="s">
-        <v>2486</v>
+        <v>2489</v>
       </c>
       <c r="E240" s="29"/>
       <c r="F240" s="29"/>
@@ -33965,13 +34055,13 @@
         <v>1063</v>
       </c>
       <c r="B241" s="29" t="s">
-        <v>2487</v>
+        <v>2490</v>
       </c>
       <c r="C241" s="65" t="s">
-        <v>2488</v>
+        <v>2491</v>
       </c>
       <c r="D241" s="28" t="s">
-        <v>2489</v>
+        <v>2492</v>
       </c>
       <c r="E241" s="29"/>
       <c r="F241" s="29"/>
@@ -33984,13 +34074,13 @@
         <v>1063</v>
       </c>
       <c r="B242" s="29" t="s">
-        <v>2490</v>
+        <v>2493</v>
       </c>
       <c r="C242" s="65" t="s">
-        <v>2491</v>
+        <v>2494</v>
       </c>
       <c r="D242" s="28" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="E242" s="29"/>
       <c r="F242" s="29"/>
@@ -34003,13 +34093,13 @@
         <v>1063</v>
       </c>
       <c r="B243" s="29" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="C243" s="65" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="D243" s="28" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="E243" s="29"/>
       <c r="F243" s="29"/>
@@ -34022,13 +34112,13 @@
         <v>1063</v>
       </c>
       <c r="B244" s="29" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="C244" s="65" t="s">
-        <v>2497</v>
+        <v>2500</v>
       </c>
       <c r="D244" s="28" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="E244" s="29"/>
       <c r="F244" s="29"/>
@@ -34036,38 +34126,38 @@
       <c r="H244" s="29"/>
       <c r="I244" s="29"/>
     </row>
-    <row r="245" s="2" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="11" t="s">
         <v>1063</v>
       </c>
       <c r="B245" s="29" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="C245" s="65" t="s">
-        <v>2500</v>
+        <v>2503</v>
       </c>
       <c r="D245" s="28" t="s">
-        <v>2501</v>
-      </c>
-      <c r="E245" s="29"/>
-      <c r="F245" s="29"/>
-      <c r="G245" s="29"/>
-      <c r="H245" s="29"/>
-      <c r="I245" s="29"/>
-    </row>
-    <row r="246" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="246" s="2" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="11" t="s">
         <v>1063</v>
       </c>
       <c r="B246" s="29" t="s">
-        <v>2502</v>
+        <v>2505</v>
       </c>
       <c r="C246" s="65" t="s">
-        <v>2503</v>
+        <v>2506</v>
       </c>
       <c r="D246" s="28" t="s">
-        <v>2504</v>
-      </c>
+        <v>2507</v>
+      </c>
+      <c r="E246" s="29"/>
+      <c r="F246" s="29"/>
+      <c r="G246" s="29"/>
+      <c r="H246" s="29"/>
+      <c r="I246" s="29"/>
     </row>
     <row r="247" s="2" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="11" t="s">
@@ -34079,7 +34169,7 @@
       <c r="E247" s="29"/>
       <c r="F247" s="29"/>
       <c r="G247" s="22" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="H247" s="29"/>
       <c r="I247" s="29"/>
@@ -34089,13 +34179,13 @@
         <v>918</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>2505</v>
+        <v>2508</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>2506</v>
+        <v>2509</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>2507</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="249" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34103,13 +34193,13 @@
         <v>918</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>2419</v>
+        <v>2422</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>2508</v>
+        <v>2511</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>2509</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="250" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34117,13 +34207,13 @@
         <v>918</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>2510</v>
+        <v>2513</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>2511</v>
+        <v>2514</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>2512</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="251" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34131,13 +34221,13 @@
         <v>918</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>2513</v>
+        <v>2516</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>2514</v>
+        <v>2517</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>2515</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="252" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34145,13 +34235,13 @@
         <v>918</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>2516</v>
+        <v>2519</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>2517</v>
+        <v>2520</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>2518</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="253" s="2" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34162,10 +34252,10 @@
         <v>-2</v>
       </c>
       <c r="C253" s="35" t="s">
-        <v>2519</v>
+        <v>2522</v>
       </c>
       <c r="D253" s="35" t="s">
-        <v>2520</v>
+        <v>2523</v>
       </c>
       <c r="E253" s="29"/>
       <c r="F253" s="29"/>
@@ -34181,10 +34271,10 @@
         <v>-1</v>
       </c>
       <c r="C254" s="35" t="s">
-        <v>2521</v>
+        <v>2524</v>
       </c>
       <c r="D254" s="35" t="s">
-        <v>2522</v>
+        <v>2525</v>
       </c>
       <c r="E254" s="29"/>
       <c r="F254" s="29"/>
@@ -34200,10 +34290,10 @@
         <v>0</v>
       </c>
       <c r="C255" s="35" t="s">
-        <v>2523</v>
+        <v>2526</v>
       </c>
       <c r="D255" s="35" t="s">
-        <v>2524</v>
+        <v>2527</v>
       </c>
       <c r="E255" s="29"/>
       <c r="F255" s="29"/>
@@ -34219,10 +34309,10 @@
         <v>1</v>
       </c>
       <c r="C256" s="35" t="s">
-        <v>2525</v>
+        <v>2528</v>
       </c>
       <c r="D256" s="35" t="s">
-        <v>2526</v>
+        <v>2529</v>
       </c>
       <c r="E256" s="29"/>
       <c r="F256" s="29"/>
@@ -34238,10 +34328,10 @@
         <v>2</v>
       </c>
       <c r="C257" s="35" t="s">
-        <v>2527</v>
+        <v>2530</v>
       </c>
       <c r="D257" s="35" t="s">
-        <v>2528</v>
+        <v>2531</v>
       </c>
       <c r="E257" s="29"/>
       <c r="F257" s="29"/>
@@ -34257,10 +34347,10 @@
         <v>0</v>
       </c>
       <c r="C258" s="21" t="s">
-        <v>2529</v>
+        <v>2532</v>
       </c>
       <c r="D258" s="35" t="s">
-        <v>2530</v>
+        <v>2533</v>
       </c>
       <c r="E258" s="29"/>
       <c r="F258" s="29"/>
@@ -34276,10 +34366,10 @@
         <v>1</v>
       </c>
       <c r="C259" s="21" t="s">
-        <v>2531</v>
+        <v>2534</v>
       </c>
       <c r="D259" s="28" t="s">
-        <v>2532</v>
+        <v>2535</v>
       </c>
       <c r="E259" s="29"/>
       <c r="F259" s="29"/>
@@ -34295,10 +34385,10 @@
         <v>2</v>
       </c>
       <c r="C260" s="21" t="s">
-        <v>2533</v>
+        <v>2536</v>
       </c>
       <c r="D260" s="28" t="s">
-        <v>2534</v>
+        <v>2537</v>
       </c>
       <c r="E260" s="29"/>
       <c r="F260" s="29"/>
@@ -34314,10 +34404,10 @@
         <v>3</v>
       </c>
       <c r="C261" s="21" t="s">
-        <v>2535</v>
+        <v>2538</v>
       </c>
       <c r="D261" s="28" t="s">
-        <v>2536</v>
+        <v>2539</v>
       </c>
       <c r="E261" s="29"/>
       <c r="F261" s="29"/>
@@ -34325,7 +34415,7 @@
       <c r="H261" s="29"/>
       <c r="I261" s="29"/>
     </row>
-    <row r="262" s="2" customFormat="true" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" customFormat="false" ht="60.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="29" t="s">
         <v>985</v>
       </c>
@@ -34333,16 +34423,11 @@
         <v>4</v>
       </c>
       <c r="C262" s="21" t="s">
-        <v>2537</v>
+        <v>2540</v>
       </c>
       <c r="D262" s="28" t="s">
-        <v>2538</v>
-      </c>
-      <c r="E262" s="29"/>
-      <c r="F262" s="29"/>
-      <c r="G262" s="29"/>
-      <c r="H262" s="29"/>
-      <c r="I262" s="29"/>
+        <v>2541</v>
+      </c>
     </row>
     <row r="263" customFormat="false" ht="75.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="29" t="s">
@@ -34352,10 +34437,10 @@
         <v>-1</v>
       </c>
       <c r="C263" s="21" t="s">
-        <v>2539</v>
+        <v>2542</v>
       </c>
       <c r="D263" s="28" t="s">
-        <v>2540</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Choices" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Labels!$A$1:$F$259</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Labels!$A$1:$F$260</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Widgets!$A$1:$W$1048534</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4892" uniqueCount="2683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4896" uniqueCount="2686">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -2035,10 +2035,29 @@
     <t xml:space="preserve">segmentsIntro</t>
   </si>
   <si>
-    <t xml:space="preserve">Veuillez indiquer tous les modes de transport utilisés pour effectuer ce déplacement (de {{originName}} vers {{destinationName}}), dans l'ordre chronologique:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Please indicate all modes of transport used for this trip (from {{originName}} to {{destinationName}}), in chronological order:</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Veuillez indiquer tous les modes de transport utilisés pour effectuer ce déplacement (de {{originName}} vers {{destinationName}}), dans l'ordre chronologique:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">{{prefilledSegmentNote}}</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Please indicate all modes of transport used for this trip (from {{originName}} to {{destinationName}}), in chronological order:{{prefilledSegmentNote}}</t>
   </si>
   <si>
     <t xml:space="preserve">Mode de transport</t>
@@ -6948,6 +6967,17 @@
     <t xml:space="preserve">The transfer station(s) do not seem coherent for this trip</t>
   </si>
   <si>
+    <t xml:space="preserve">prefilledSegmentNote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+__**Note:** Information pré-remplie en fonction de la déclaration de {{referenceNickname}}. Vérifier que les informations sont correctes et changer au besoin.__</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+__**Note:** Information prefilled from {{referenceNickname}}'s trip diary. Verify if the information is correct and change if needed.__</t>
+  </si>
+  <si>
     <t xml:space="preserve">personHasSchoolPlace_schoolchildcare</t>
   </si>
   <si>
@@ -8708,7 +8738,7 @@
     <numFmt numFmtId="166" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
     <numFmt numFmtId="167" formatCode="@"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8792,6 +8822,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -9149,7 +9186,7 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9185,19 +9222,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9205,7 +9242,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9225,11 +9262,11 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9241,19 +9278,19 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9281,11 +9318,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9293,11 +9330,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9305,43 +9362,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9349,7 +9386,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9357,15 +9394,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9373,27 +9410,27 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -22854,7 +22891,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F264"/>
+  <dimension ref="A1:F265"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="53" width="16.73"/>
@@ -26683,117 +26720,117 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="51" t="s">
-        <v>744</v>
-      </c>
-      <c r="B248" s="57" t="s">
+    <row r="248" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="53" t="s">
+        <v>548</v>
+      </c>
+      <c r="B248" s="8" t="s">
         <v>2111</v>
       </c>
       <c r="C248" s="8" t="s">
         <v>2112</v>
       </c>
-      <c r="D248" s="88" t="s">
+      <c r="D248" s="60" t="s">
         <v>2113</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="53" t="s">
+    <row r="249" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="51" t="s">
         <v>744</v>
       </c>
-      <c r="B249" s="89" t="s">
+      <c r="B249" s="57" t="s">
         <v>2114</v>
       </c>
-      <c r="C249" s="51" t="s">
-        <v>1361</v>
-      </c>
-      <c r="D249" s="54" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="250" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C249" s="8" t="s">
+        <v>2115</v>
+      </c>
+      <c r="D249" s="88" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="53" t="s">
         <v>744</v>
       </c>
       <c r="B250" s="89" t="s">
-        <v>2115</v>
-      </c>
-      <c r="C250" s="8" t="s">
-        <v>2116</v>
+        <v>2117</v>
+      </c>
+      <c r="C250" s="51" t="s">
+        <v>1361</v>
       </c>
       <c r="D250" s="54" t="s">
-        <v>2117</v>
-      </c>
-    </row>
-    <row r="251" customFormat="false" ht="285.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="53" t="s">
         <v>744</v>
       </c>
-      <c r="B251" s="56" t="s">
+      <c r="B251" s="89" t="s">
         <v>2118</v>
       </c>
-      <c r="C251" s="57" t="s">
+      <c r="C251" s="8" t="s">
         <v>2119</v>
       </c>
-      <c r="D251" s="57" t="s">
+      <c r="D251" s="54" t="s">
         <v>2120</v>
       </c>
-      <c r="E251" s="57" t="s">
-        <v>2121</v>
-      </c>
-      <c r="F251" s="57" t="s">
-        <v>2122</v>
-      </c>
-    </row>
-    <row r="252" customFormat="false" ht="225.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="252" customFormat="false" ht="285.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="53" t="s">
         <v>744</v>
       </c>
       <c r="B252" s="56" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C252" s="57" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D252" s="57" t="s">
         <v>2123</v>
       </c>
-      <c r="C252" s="57" t="s">
+      <c r="E252" s="57" t="s">
         <v>2124</v>
       </c>
-      <c r="D252" s="57" t="s">
+      <c r="F252" s="57" t="s">
         <v>2125</v>
       </c>
-      <c r="E252" s="57" t="s">
+    </row>
+    <row r="253" customFormat="false" ht="225.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="53" t="s">
+        <v>744</v>
+      </c>
+      <c r="B253" s="56" t="s">
         <v>2126</v>
       </c>
-      <c r="F252" s="57" t="s">
+      <c r="C253" s="57" t="s">
         <v>2127</v>
       </c>
-    </row>
-    <row r="253" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="53" t="s">
-        <v>823</v>
-      </c>
-      <c r="B253" s="53" t="s">
+      <c r="D253" s="57" t="s">
         <v>2128</v>
       </c>
-      <c r="C253" s="51" t="s">
-        <v>1361</v>
-      </c>
-      <c r="D253" s="54" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="254" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E253" s="57" t="s">
+        <v>2129</v>
+      </c>
+      <c r="F253" s="57" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="53" t="s">
         <v>823</v>
       </c>
       <c r="B254" s="53" t="s">
-        <v>2129</v>
-      </c>
-      <c r="C254" s="8" t="s">
-        <v>2130</v>
-      </c>
-      <c r="D254" s="8" t="s">
         <v>2131</v>
       </c>
-    </row>
-    <row r="255" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C254" s="51" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D254" s="54" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="53" t="s">
         <v>823</v>
       </c>
@@ -26801,51 +26838,51 @@
         <v>2132</v>
       </c>
       <c r="C255" s="8" t="s">
-        <v>1419</v>
+        <v>2133</v>
       </c>
       <c r="D255" s="8" t="s">
-        <v>1420</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="53" t="s">
-        <v>1043</v>
+        <v>823</v>
       </c>
       <c r="B256" s="53" t="s">
-        <v>2133</v>
-      </c>
-      <c r="C256" s="51" t="s">
-        <v>1361</v>
-      </c>
-      <c r="D256" s="54" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="257" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2135</v>
+      </c>
+      <c r="C256" s="8" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D256" s="8" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="53" t="s">
         <v>1043</v>
       </c>
       <c r="B257" s="53" t="s">
-        <v>2134</v>
-      </c>
-      <c r="C257" s="8" t="s">
-        <v>2135</v>
+        <v>2136</v>
+      </c>
+      <c r="C257" s="51" t="s">
+        <v>1361</v>
       </c>
       <c r="D257" s="54" t="s">
-        <v>2136</v>
-      </c>
-    </row>
-    <row r="258" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="53" t="s">
-        <v>991</v>
-      </c>
-      <c r="B258" s="57" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B258" s="53" t="s">
         <v>2137</v>
       </c>
-      <c r="C258" s="57" t="s">
+      <c r="C258" s="8" t="s">
         <v>2138</v>
       </c>
-      <c r="D258" s="57" t="s">
+      <c r="D258" s="54" t="s">
         <v>2139</v>
       </c>
     </row>
@@ -26863,65 +26900,65 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="260" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="53" t="s">
-        <v>48</v>
-      </c>
-      <c r="B260" s="53" t="s">
+        <v>991</v>
+      </c>
+      <c r="B260" s="57" t="s">
         <v>2143</v>
       </c>
-      <c r="C260" s="51" t="s">
+      <c r="C260" s="57" t="s">
         <v>2144</v>
       </c>
-      <c r="D260" s="54" t="s">
+      <c r="D260" s="57" t="s">
         <v>2145</v>
       </c>
     </row>
-    <row r="261" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="53" t="s">
         <v>48</v>
       </c>
       <c r="B261" s="53" t="s">
         <v>2146</v>
       </c>
-      <c r="C261" s="8" t="s">
+      <c r="C261" s="51" t="s">
         <v>2147</v>
       </c>
       <c r="D261" s="54" t="s">
         <v>2148</v>
       </c>
     </row>
-    <row r="262" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="53" t="s">
         <v>48</v>
       </c>
       <c r="B262" s="53" t="s">
         <v>2149</v>
       </c>
-      <c r="C262" s="51" t="s">
-        <v>1361</v>
+      <c r="C262" s="8" t="s">
+        <v>2150</v>
       </c>
       <c r="D262" s="54" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="263" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="53" t="s">
         <v>48</v>
       </c>
       <c r="B263" s="53" t="s">
-        <v>2150</v>
-      </c>
-      <c r="C263" s="8" t="s">
-        <v>2151</v>
+        <v>2152</v>
+      </c>
+      <c r="C263" s="51" t="s">
+        <v>1361</v>
       </c>
       <c r="D263" s="54" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="264" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="53" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B264" s="53" t="s">
         <v>2153</v>
@@ -26929,12 +26966,26 @@
       <c r="C264" s="8" t="s">
         <v>2154</v>
       </c>
-      <c r="D264" s="8" t="s">
+      <c r="D264" s="54" t="s">
         <v>2155</v>
       </c>
     </row>
+    <row r="265" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="B265" s="53" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C265" s="8" t="s">
+        <v>2157</v>
+      </c>
+      <c r="D265" s="8" t="s">
+        <v>2158</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F259"/>
+  <autoFilter ref="A1:F260"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -26964,7 +27015,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="90" t="s">
-        <v>2156</v>
+        <v>2159</v>
       </c>
       <c r="B1" s="90" t="s">
         <v>1149</v>
@@ -26982,13 +27033,13 @@
         <v>9</v>
       </c>
       <c r="G1" s="90" t="s">
-        <v>2157</v>
+        <v>2160</v>
       </c>
       <c r="H1" s="90" t="s">
         <v>12</v>
       </c>
       <c r="I1" s="69" t="s">
-        <v>2158</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26999,10 +27050,10 @@
         <v>1157</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>2159</v>
+        <v>2162</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>2160</v>
+        <v>2163</v>
       </c>
       <c r="E2" s="56"/>
       <c r="F2" s="56"/>
@@ -27017,10 +27068,10 @@
         <v>1215</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>2161</v>
+        <v>2164</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>2162</v>
+        <v>2165</v>
       </c>
       <c r="E3" s="56"/>
       <c r="F3" s="56"/>
@@ -27035,10 +27086,10 @@
         <v>229</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>2163</v>
+        <v>2166</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>2164</v>
+        <v>2167</v>
       </c>
       <c r="E4" s="56"/>
       <c r="F4" s="56"/>
@@ -27047,7 +27098,7 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="56" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
       <c r="B5" s="56" t="s">
         <v>229</v>
@@ -27065,16 +27116,16 @@
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="56" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="C6" s="56" t="s">
-        <v>2167</v>
+        <v>2170</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>2168</v>
+        <v>2171</v>
       </c>
       <c r="E6" s="56"/>
       <c r="F6" s="56"/>
@@ -27089,10 +27140,10 @@
         <v>1161</v>
       </c>
       <c r="C7" s="56" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>2170</v>
+        <v>2173</v>
       </c>
       <c r="E7" s="56"/>
       <c r="F7" s="56"/>
@@ -27151,7 +27202,7 @@
       <c r="E11" s="56"/>
       <c r="F11" s="56"/>
       <c r="G11" s="56" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="H11" s="56"/>
     </row>
@@ -27205,10 +27256,10 @@
         <v>1157</v>
       </c>
       <c r="C15" s="54" t="s">
-        <v>2171</v>
+        <v>2174</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>2172</v>
+        <v>2175</v>
       </c>
       <c r="E15" s="54"/>
       <c r="F15" s="54"/>
@@ -27224,10 +27275,10 @@
         <v>1215</v>
       </c>
       <c r="C16" s="54" t="s">
-        <v>2173</v>
+        <v>2176</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="E16" s="54"/>
       <c r="F16" s="54"/>
@@ -27237,16 +27288,16 @@
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="92" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="B17" s="56" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="C17" s="56" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="D17" s="56" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="E17" s="56"/>
       <c r="F17" s="56"/>
@@ -27255,16 +27306,16 @@
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="92" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="B18" s="56" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="C18" s="56" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="E18" s="56"/>
       <c r="F18" s="56"/>
@@ -27273,7 +27324,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="92" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="B19" s="56"/>
       <c r="C19" s="56"/>
@@ -27290,13 +27341,13 @@
         <v>187</v>
       </c>
       <c r="B20" s="56" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="C20" s="56" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="D20" s="56" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="E20" s="56"/>
       <c r="F20" s="56"/>
@@ -27308,13 +27359,13 @@
         <v>187</v>
       </c>
       <c r="B21" s="56" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="C21" s="56" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="D21" s="56" t="s">
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="E21" s="56"/>
       <c r="F21" s="56"/>
@@ -27329,10 +27380,10 @@
         <v>189</v>
       </c>
       <c r="C22" s="56" t="s">
-        <v>2184</v>
+        <v>2187</v>
       </c>
       <c r="D22" s="56" t="s">
-        <v>2185</v>
+        <v>2188</v>
       </c>
       <c r="E22" s="56"/>
       <c r="F22" s="56"/>
@@ -27358,13 +27409,13 @@
         <v>306</v>
       </c>
       <c r="B24" s="56" t="s">
-        <v>2186</v>
+        <v>2189</v>
       </c>
       <c r="C24" s="56" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="D24" s="56" t="s">
-        <v>2188</v>
+        <v>2191</v>
       </c>
       <c r="E24" s="56"/>
       <c r="F24" s="56"/>
@@ -27376,13 +27427,13 @@
         <v>306</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>2189</v>
+        <v>2192</v>
       </c>
       <c r="C25" s="56" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="D25" s="56" t="s">
-        <v>2191</v>
+        <v>2194</v>
       </c>
       <c r="E25" s="56"/>
       <c r="F25" s="56"/>
@@ -27408,13 +27459,13 @@
         <v>299</v>
       </c>
       <c r="B27" s="56" t="s">
-        <v>2186</v>
+        <v>2189</v>
       </c>
       <c r="C27" s="56" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="D27" s="56" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="E27" s="56"/>
       <c r="F27" s="56"/>
@@ -27426,13 +27477,13 @@
         <v>299</v>
       </c>
       <c r="B28" s="56" t="s">
-        <v>2189</v>
+        <v>2192</v>
       </c>
       <c r="C28" s="56" t="s">
-        <v>2194</v>
+        <v>2197</v>
       </c>
       <c r="D28" s="56" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="E28" s="56"/>
       <c r="F28" s="56"/>
@@ -27461,10 +27512,10 @@
         <v>1181</v>
       </c>
       <c r="C30" s="56" t="s">
-        <v>2196</v>
+        <v>2199</v>
       </c>
       <c r="D30" s="56" t="s">
-        <v>2197</v>
+        <v>2200</v>
       </c>
       <c r="E30" s="56"/>
       <c r="F30" s="56"/>
@@ -27483,10 +27534,10 @@
         <v>1182</v>
       </c>
       <c r="C31" s="56" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="D31" s="56" t="s">
-        <v>2199</v>
+        <v>2202</v>
       </c>
       <c r="E31" s="56"/>
       <c r="F31" s="56"/>
@@ -27505,10 +27556,10 @@
         <v>1183</v>
       </c>
       <c r="C32" s="56" t="s">
-        <v>2200</v>
+        <v>2203</v>
       </c>
       <c r="D32" s="56" t="s">
-        <v>2201</v>
+        <v>2204</v>
       </c>
       <c r="E32" s="56"/>
       <c r="F32" s="56"/>
@@ -27527,10 +27578,10 @@
         <v>1185</v>
       </c>
       <c r="C33" s="56" t="s">
-        <v>2202</v>
+        <v>2205</v>
       </c>
       <c r="D33" s="56" t="s">
-        <v>2203</v>
+        <v>2206</v>
       </c>
       <c r="E33" s="56"/>
       <c r="F33" s="56"/>
@@ -27549,10 +27600,10 @@
         <v>1186</v>
       </c>
       <c r="C34" s="56" t="s">
-        <v>2204</v>
+        <v>2207</v>
       </c>
       <c r="D34" s="56" t="s">
-        <v>2205</v>
+        <v>2208</v>
       </c>
       <c r="E34" s="56"/>
       <c r="F34" s="56"/>
@@ -27568,13 +27619,13 @@
         <v>340</v>
       </c>
       <c r="B35" s="56" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="C35" s="56" t="s">
-        <v>2207</v>
+        <v>2210</v>
       </c>
       <c r="D35" s="56" t="s">
-        <v>2208</v>
+        <v>2211</v>
       </c>
       <c r="E35" s="56"/>
       <c r="F35" s="56"/>
@@ -27589,13 +27640,13 @@
         <v>340</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="C36" s="56" t="s">
-        <v>2210</v>
+        <v>2213</v>
       </c>
       <c r="D36" s="56" t="s">
-        <v>2211</v>
+        <v>2214</v>
       </c>
       <c r="E36" s="56"/>
       <c r="F36" s="56"/>
@@ -27611,10 +27662,10 @@
         <v>1252</v>
       </c>
       <c r="C37" s="56" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="D37" s="56" t="s">
-        <v>2213</v>
+        <v>2216</v>
       </c>
       <c r="E37" s="56"/>
       <c r="F37" s="56"/>
@@ -27630,10 +27681,10 @@
         <v>1253</v>
       </c>
       <c r="C38" s="56" t="s">
-        <v>2214</v>
+        <v>2217</v>
       </c>
       <c r="D38" s="56" t="s">
-        <v>2215</v>
+        <v>2218</v>
       </c>
       <c r="E38" s="56"/>
       <c r="F38" s="56"/>
@@ -27646,13 +27697,13 @@
         <v>340</v>
       </c>
       <c r="B39" s="56" t="s">
-        <v>2216</v>
+        <v>2219</v>
       </c>
       <c r="C39" s="56" t="s">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="D39" s="56" t="s">
-        <v>2218</v>
+        <v>2221</v>
       </c>
       <c r="E39" s="56"/>
       <c r="F39" s="56"/>
@@ -27665,13 +27716,13 @@
         <v>340</v>
       </c>
       <c r="B40" s="56" t="s">
-        <v>2219</v>
+        <v>2222</v>
       </c>
       <c r="C40" s="56" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="D40" s="56" t="s">
-        <v>2221</v>
+        <v>2224</v>
       </c>
       <c r="E40" s="56"/>
       <c r="F40" s="56"/>
@@ -27689,7 +27740,7 @@
       <c r="E41" s="56"/>
       <c r="F41" s="56"/>
       <c r="G41" s="56" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
       <c r="H41" s="56"/>
       <c r="I41" s="69"/>
@@ -27714,13 +27765,13 @@
         <v>315</v>
       </c>
       <c r="B43" s="56" t="s">
-        <v>2222</v>
+        <v>2225</v>
       </c>
       <c r="C43" s="51" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>2224</v>
+        <v>2227</v>
       </c>
       <c r="E43" s="56"/>
       <c r="F43" s="56"/>
@@ -27733,13 +27784,13 @@
         <v>315</v>
       </c>
       <c r="B44" s="56" t="s">
-        <v>2225</v>
+        <v>2228</v>
       </c>
       <c r="C44" s="51" t="s">
-        <v>2226</v>
+        <v>2229</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>2227</v>
+        <v>2230</v>
       </c>
       <c r="E44" s="56"/>
       <c r="F44" s="56"/>
@@ -27752,13 +27803,13 @@
         <v>315</v>
       </c>
       <c r="B45" s="56" t="s">
-        <v>2228</v>
+        <v>2231</v>
       </c>
       <c r="C45" s="51" t="s">
-        <v>2229</v>
+        <v>2232</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>2230</v>
+        <v>2233</v>
       </c>
       <c r="E45" s="56"/>
       <c r="F45" s="56"/>
@@ -27771,13 +27822,13 @@
         <v>315</v>
       </c>
       <c r="B46" s="56" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>2232</v>
+        <v>2235</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>2233</v>
+        <v>2236</v>
       </c>
       <c r="E46" s="56"/>
       <c r="F46" s="56"/>
@@ -27795,7 +27846,7 @@
       <c r="E47" s="56"/>
       <c r="F47" s="56"/>
       <c r="G47" s="56" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="H47" s="56"/>
       <c r="I47" s="56"/>
@@ -27808,10 +27859,10 @@
         <v>1246</v>
       </c>
       <c r="C48" s="54" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>2235</v>
+        <v>2238</v>
       </c>
       <c r="E48" s="56"/>
       <c r="F48" s="56"/>
@@ -27826,13 +27877,13 @@
         <v>220</v>
       </c>
       <c r="B49" s="56" t="s">
-        <v>2236</v>
+        <v>2239</v>
       </c>
       <c r="C49" s="54" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
       <c r="E49" s="56"/>
       <c r="F49" s="56"/>
@@ -27847,13 +27898,13 @@
         <v>220</v>
       </c>
       <c r="B50" s="56" t="s">
-        <v>2239</v>
+        <v>2242</v>
       </c>
       <c r="C50" s="54" t="s">
-        <v>2240</v>
+        <v>2243</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>2241</v>
+        <v>2244</v>
       </c>
       <c r="E50" s="56"/>
       <c r="F50" s="56"/>
@@ -27869,10 +27920,10 @@
         <v>229</v>
       </c>
       <c r="C51" s="54" t="s">
-        <v>2242</v>
+        <v>2245</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>2243</v>
+        <v>2246</v>
       </c>
       <c r="E51" s="56"/>
       <c r="F51" s="56"/>
@@ -27890,7 +27941,7 @@
       <c r="E52" s="56"/>
       <c r="F52" s="56"/>
       <c r="G52" s="56" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="H52" s="56"/>
       <c r="I52" s="56"/>
@@ -27900,13 +27951,13 @@
         <v>226</v>
       </c>
       <c r="B53" s="56" t="s">
-        <v>2244</v>
+        <v>2247</v>
       </c>
       <c r="C53" s="54" t="s">
-        <v>2245</v>
+        <v>2248</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>2246</v>
+        <v>2249</v>
       </c>
       <c r="E53" s="56"/>
       <c r="F53" s="56"/>
@@ -27919,13 +27970,13 @@
         <v>226</v>
       </c>
       <c r="B54" s="56" t="s">
-        <v>2247</v>
+        <v>2250</v>
       </c>
       <c r="C54" s="54" t="s">
-        <v>2248</v>
+        <v>2251</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>2249</v>
+        <v>2252</v>
       </c>
       <c r="E54" s="56"/>
       <c r="F54" s="56"/>
@@ -27938,13 +27989,13 @@
         <v>226</v>
       </c>
       <c r="B55" s="56" t="s">
-        <v>2250</v>
+        <v>2253</v>
       </c>
       <c r="C55" s="54" t="s">
-        <v>2251</v>
+        <v>2254</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>2252</v>
+        <v>2255</v>
       </c>
       <c r="E55" s="56"/>
       <c r="F55" s="56"/>
@@ -27957,13 +28008,13 @@
         <v>226</v>
       </c>
       <c r="B56" s="56" t="s">
-        <v>2253</v>
+        <v>2256</v>
       </c>
       <c r="C56" s="54" t="s">
-        <v>2254</v>
+        <v>2257</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>2255</v>
+        <v>2258</v>
       </c>
       <c r="E56" s="56"/>
       <c r="F56" s="56"/>
@@ -27976,13 +28027,13 @@
         <v>226</v>
       </c>
       <c r="B57" s="56" t="s">
-        <v>2256</v>
+        <v>2259</v>
       </c>
       <c r="C57" s="54" t="s">
-        <v>2257</v>
+        <v>2260</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>2257</v>
+        <v>2260</v>
       </c>
       <c r="E57" s="56"/>
       <c r="F57" s="56"/>
@@ -27995,13 +28046,13 @@
         <v>226</v>
       </c>
       <c r="B58" s="56" t="s">
-        <v>2258</v>
+        <v>2261</v>
       </c>
       <c r="C58" s="54" t="s">
-        <v>2259</v>
+        <v>2262</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>2260</v>
+        <v>2263</v>
       </c>
       <c r="E58" s="56"/>
       <c r="F58" s="56"/>
@@ -28014,13 +28065,13 @@
         <v>226</v>
       </c>
       <c r="B59" s="56" t="s">
-        <v>2261</v>
+        <v>2264</v>
       </c>
       <c r="C59" s="54" t="s">
-        <v>2262</v>
+        <v>2265</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>2263</v>
+        <v>2266</v>
       </c>
       <c r="E59" s="56"/>
       <c r="F59" s="56"/>
@@ -28033,13 +28084,13 @@
         <v>226</v>
       </c>
       <c r="B60" s="56" t="s">
-        <v>2264</v>
+        <v>2267</v>
       </c>
       <c r="C60" s="54" t="s">
-        <v>2265</v>
+        <v>2268</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>2266</v>
+        <v>2269</v>
       </c>
       <c r="E60" s="56"/>
       <c r="F60" s="56"/>
@@ -28067,13 +28118,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="56" t="s">
-        <v>2267</v>
+        <v>2270</v>
       </c>
       <c r="C62" s="54" t="s">
-        <v>2268</v>
+        <v>2271</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>2269</v>
+        <v>2272</v>
       </c>
       <c r="E62" s="56"/>
       <c r="F62" s="56"/>
@@ -28091,7 +28142,7 @@
       <c r="E63" s="56"/>
       <c r="F63" s="56"/>
       <c r="G63" s="56" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="H63" s="56"/>
       <c r="I63" s="56"/>
@@ -28104,10 +28155,10 @@
         <v>1157</v>
       </c>
       <c r="C64" s="54" t="s">
-        <v>2270</v>
+        <v>2273</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>2271</v>
+        <v>2274</v>
       </c>
       <c r="E64" s="56"/>
       <c r="F64" s="56"/>
@@ -28123,14 +28174,14 @@
         <v>1189</v>
       </c>
       <c r="C65" s="56" t="s">
-        <v>2272</v>
+        <v>2275</v>
       </c>
       <c r="D65" s="56" t="s">
-        <v>2273</v>
+        <v>2276</v>
       </c>
       <c r="E65" s="56"/>
       <c r="F65" s="56" t="s">
-        <v>2274</v>
+        <v>2277</v>
       </c>
       <c r="G65" s="56"/>
       <c r="H65" s="56"/>
@@ -28144,14 +28195,14 @@
         <v>1190</v>
       </c>
       <c r="C66" s="56" t="s">
-        <v>2275</v>
+        <v>2278</v>
       </c>
       <c r="D66" s="56" t="s">
-        <v>2276</v>
+        <v>2279</v>
       </c>
       <c r="E66" s="56"/>
       <c r="F66" s="56" t="s">
-        <v>2277</v>
+        <v>2280</v>
       </c>
       <c r="G66" s="56"/>
       <c r="H66" s="56"/>
@@ -28162,17 +28213,17 @@
         <v>322</v>
       </c>
       <c r="B67" s="56" t="s">
-        <v>2278</v>
+        <v>2281</v>
       </c>
       <c r="C67" s="56" t="s">
-        <v>2279</v>
+        <v>2282</v>
       </c>
       <c r="D67" s="56" t="s">
-        <v>2280</v>
+        <v>2283</v>
       </c>
       <c r="E67" s="56"/>
       <c r="F67" s="56" t="s">
-        <v>2281</v>
+        <v>2284</v>
       </c>
       <c r="G67" s="56"/>
       <c r="H67" s="56"/>
@@ -28186,14 +28237,14 @@
         <v>1191</v>
       </c>
       <c r="C68" s="56" t="s">
-        <v>2282</v>
+        <v>2285</v>
       </c>
       <c r="D68" s="56" t="s">
-        <v>2283</v>
+        <v>2286</v>
       </c>
       <c r="E68" s="56"/>
       <c r="F68" s="56" t="s">
-        <v>2284</v>
+        <v>2287</v>
       </c>
       <c r="G68" s="56"/>
       <c r="H68" s="56"/>
@@ -28207,14 +28258,14 @@
         <v>1205</v>
       </c>
       <c r="C69" s="56" t="s">
-        <v>2285</v>
+        <v>2288</v>
       </c>
       <c r="D69" s="56" t="s">
-        <v>2286</v>
+        <v>2289</v>
       </c>
       <c r="E69" s="56"/>
       <c r="F69" s="56" t="s">
-        <v>2287</v>
+        <v>2290</v>
       </c>
       <c r="G69" s="56"/>
       <c r="H69" s="56"/>
@@ -28225,13 +28276,13 @@
         <v>895</v>
       </c>
       <c r="B70" s="69" t="s">
-        <v>2288</v>
+        <v>2291</v>
       </c>
       <c r="C70" s="69" t="s">
-        <v>2289</v>
+        <v>2292</v>
       </c>
       <c r="D70" s="69" t="s">
-        <v>2290</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28239,13 +28290,13 @@
         <v>895</v>
       </c>
       <c r="B71" s="69" t="s">
-        <v>2291</v>
+        <v>2294</v>
       </c>
       <c r="C71" s="69" t="s">
-        <v>2292</v>
+        <v>2295</v>
       </c>
       <c r="D71" s="69" t="s">
-        <v>2293</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28253,13 +28304,13 @@
         <v>895</v>
       </c>
       <c r="B72" s="69" t="s">
-        <v>2294</v>
+        <v>2297</v>
       </c>
       <c r="C72" s="69" t="s">
-        <v>2295</v>
+        <v>2298</v>
       </c>
       <c r="D72" s="69" t="s">
-        <v>2296</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="73" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28267,13 +28318,13 @@
         <v>895</v>
       </c>
       <c r="B73" s="69" t="s">
-        <v>2297</v>
+        <v>2300</v>
       </c>
       <c r="C73" s="69" t="s">
-        <v>2298</v>
+        <v>2301</v>
       </c>
       <c r="D73" s="69" t="s">
-        <v>2299</v>
+        <v>2302</v>
       </c>
       <c r="E73" s="69"/>
       <c r="F73" s="69"/>
@@ -28286,13 +28337,13 @@
         <v>1069</v>
       </c>
       <c r="B74" s="69" t="s">
-        <v>2300</v>
+        <v>2303</v>
       </c>
       <c r="C74" s="69" t="s">
-        <v>2301</v>
+        <v>2304</v>
       </c>
       <c r="D74" s="69" t="s">
-        <v>2302</v>
+        <v>2305</v>
       </c>
       <c r="E74" s="69"/>
       <c r="F74" s="69"/>
@@ -28305,13 +28356,13 @@
         <v>1069</v>
       </c>
       <c r="B75" s="53" t="s">
-        <v>2303</v>
+        <v>2306</v>
       </c>
       <c r="C75" s="53" t="s">
-        <v>2304</v>
+        <v>2307</v>
       </c>
       <c r="D75" s="53" t="s">
-        <v>2305</v>
+        <v>2308</v>
       </c>
       <c r="G75" s="69"/>
       <c r="H75" s="69"/>
@@ -28322,13 +28373,13 @@
         <v>1069</v>
       </c>
       <c r="B76" s="53" t="s">
-        <v>2306</v>
+        <v>2309</v>
       </c>
       <c r="C76" s="53" t="s">
-        <v>2307</v>
+        <v>2310</v>
       </c>
       <c r="D76" s="53" t="s">
-        <v>2308</v>
+        <v>2311</v>
       </c>
       <c r="G76" s="69"/>
       <c r="H76" s="69"/>
@@ -28339,13 +28390,13 @@
         <v>1069</v>
       </c>
       <c r="B77" s="53" t="s">
-        <v>2309</v>
+        <v>2312</v>
       </c>
       <c r="C77" s="53" t="s">
-        <v>2310</v>
+        <v>2313</v>
       </c>
       <c r="D77" s="53" t="s">
-        <v>2311</v>
+        <v>2314</v>
       </c>
       <c r="G77" s="69"/>
       <c r="H77" s="69"/>
@@ -28356,13 +28407,13 @@
         <v>1069</v>
       </c>
       <c r="B78" s="53" t="s">
-        <v>2312</v>
+        <v>2315</v>
       </c>
       <c r="C78" s="53" t="s">
-        <v>2313</v>
+        <v>2316</v>
       </c>
       <c r="D78" s="53" t="s">
-        <v>2314</v>
+        <v>2317</v>
       </c>
       <c r="G78" s="69"/>
       <c r="H78" s="69"/>
@@ -28373,13 +28424,13 @@
         <v>1069</v>
       </c>
       <c r="B79" s="53" t="s">
-        <v>2315</v>
+        <v>2318</v>
       </c>
       <c r="C79" s="53" t="s">
-        <v>2316</v>
+        <v>2319</v>
       </c>
       <c r="D79" s="53" t="s">
-        <v>2317</v>
+        <v>2320</v>
       </c>
       <c r="G79" s="69"/>
       <c r="H79" s="69"/>
@@ -28390,13 +28441,13 @@
         <v>1069</v>
       </c>
       <c r="B80" s="53" t="s">
-        <v>2318</v>
+        <v>2321</v>
       </c>
       <c r="C80" s="53" t="s">
-        <v>2319</v>
+        <v>2322</v>
       </c>
       <c r="D80" s="53" t="s">
-        <v>2320</v>
+        <v>2323</v>
       </c>
       <c r="G80" s="69"/>
       <c r="H80" s="69"/>
@@ -28407,13 +28458,13 @@
         <v>1069</v>
       </c>
       <c r="B81" s="53" t="s">
-        <v>2321</v>
+        <v>2324</v>
       </c>
       <c r="C81" s="53" t="s">
-        <v>2322</v>
+        <v>2325</v>
       </c>
       <c r="D81" s="53" t="s">
-        <v>2323</v>
+        <v>2326</v>
       </c>
       <c r="G81" s="69"/>
       <c r="H81" s="69"/>
@@ -28424,13 +28475,13 @@
         <v>1069</v>
       </c>
       <c r="B82" s="53" t="s">
-        <v>2324</v>
+        <v>2327</v>
       </c>
       <c r="C82" s="53" t="s">
-        <v>2325</v>
+        <v>2328</v>
       </c>
       <c r="D82" s="53" t="s">
-        <v>2326</v>
+        <v>2329</v>
       </c>
       <c r="G82" s="69"/>
       <c r="H82" s="69"/>
@@ -28441,13 +28492,13 @@
         <v>1069</v>
       </c>
       <c r="B83" s="53" t="s">
-        <v>2327</v>
+        <v>2330</v>
       </c>
       <c r="C83" s="53" t="s">
-        <v>2328</v>
+        <v>2331</v>
       </c>
       <c r="D83" s="53" t="s">
-        <v>2329</v>
+        <v>2332</v>
       </c>
       <c r="G83" s="69"/>
       <c r="H83" s="69"/>
@@ -28458,13 +28509,13 @@
         <v>1069</v>
       </c>
       <c r="B84" s="53" t="s">
-        <v>2330</v>
+        <v>2333</v>
       </c>
       <c r="C84" s="53" t="s">
-        <v>2331</v>
+        <v>2334</v>
       </c>
       <c r="D84" s="53" t="s">
-        <v>2332</v>
+        <v>2335</v>
       </c>
       <c r="G84" s="69"/>
       <c r="H84" s="69"/>
@@ -28475,13 +28526,13 @@
         <v>1069</v>
       </c>
       <c r="B85" s="53" t="s">
-        <v>2333</v>
+        <v>2336</v>
       </c>
       <c r="C85" s="53" t="s">
-        <v>2334</v>
+        <v>2337</v>
       </c>
       <c r="D85" s="53" t="s">
-        <v>2335</v>
+        <v>2338</v>
       </c>
       <c r="G85" s="69"/>
       <c r="H85" s="69"/>
@@ -28492,13 +28543,13 @@
         <v>1069</v>
       </c>
       <c r="B86" s="69" t="s">
-        <v>2336</v>
+        <v>2339</v>
       </c>
       <c r="C86" s="69" t="s">
-        <v>2337</v>
+        <v>2340</v>
       </c>
       <c r="D86" s="69" t="s">
-        <v>2338</v>
+        <v>2341</v>
       </c>
       <c r="E86" s="69"/>
       <c r="F86" s="69"/>
@@ -28511,13 +28562,13 @@
         <v>1069</v>
       </c>
       <c r="B87" s="69" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="C87" s="69" t="s">
-        <v>2167</v>
+        <v>2170</v>
       </c>
       <c r="D87" s="69" t="s">
-        <v>2168</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28525,13 +28576,13 @@
         <v>1069</v>
       </c>
       <c r="B88" s="69" t="s">
-        <v>2339</v>
+        <v>2342</v>
       </c>
       <c r="C88" s="69" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="D88" s="69" t="s">
-        <v>2340</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28539,13 +28590,13 @@
         <v>99</v>
       </c>
       <c r="B89" s="69" t="s">
-        <v>2341</v>
+        <v>2344</v>
       </c>
       <c r="C89" s="69" t="s">
-        <v>2342</v>
+        <v>2345</v>
       </c>
       <c r="D89" s="69" t="s">
-        <v>2343</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28553,13 +28604,13 @@
         <v>99</v>
       </c>
       <c r="B90" s="69" t="s">
-        <v>2344</v>
+        <v>2347</v>
       </c>
       <c r="C90" s="69" t="s">
-        <v>2345</v>
+        <v>2348</v>
       </c>
       <c r="D90" s="69" t="s">
-        <v>2346</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28584,10 +28635,10 @@
         <v>1161</v>
       </c>
       <c r="C92" s="69" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="D92" s="69" t="s">
-        <v>2340</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28595,13 +28646,13 @@
         <v>423</v>
       </c>
       <c r="B93" s="56" t="s">
-        <v>2347</v>
+        <v>2350</v>
       </c>
       <c r="C93" s="54" t="s">
-        <v>2348</v>
+        <v>2351</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>2349</v>
+        <v>2352</v>
       </c>
       <c r="E93" s="54"/>
       <c r="F93" s="54"/>
@@ -28616,13 +28667,13 @@
         <v>423</v>
       </c>
       <c r="B94" s="56" t="s">
-        <v>2350</v>
+        <v>2353</v>
       </c>
       <c r="C94" s="54" t="s">
-        <v>2351</v>
+        <v>2354</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>2352</v>
+        <v>2355</v>
       </c>
       <c r="E94" s="54"/>
       <c r="F94" s="54"/>
@@ -28637,13 +28688,13 @@
         <v>423</v>
       </c>
       <c r="B95" s="56" t="s">
-        <v>2353</v>
+        <v>2356</v>
       </c>
       <c r="C95" s="54" t="s">
-        <v>2354</v>
+        <v>2357</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>2355</v>
+        <v>2358</v>
       </c>
       <c r="E95" s="54"/>
       <c r="F95" s="54"/>
@@ -28656,13 +28707,13 @@
         <v>423</v>
       </c>
       <c r="B96" s="56" t="s">
-        <v>2356</v>
+        <v>2359</v>
       </c>
       <c r="C96" s="54" t="s">
-        <v>2357</v>
+        <v>2360</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>2358</v>
+        <v>2361</v>
       </c>
       <c r="E96" s="54"/>
       <c r="F96" s="54"/>
@@ -28675,13 +28726,13 @@
         <v>423</v>
       </c>
       <c r="B97" s="56" t="s">
-        <v>2359</v>
+        <v>2362</v>
       </c>
       <c r="C97" s="54" t="s">
-        <v>2360</v>
+        <v>2363</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>2361</v>
+        <v>2364</v>
       </c>
       <c r="E97" s="54"/>
       <c r="F97" s="54"/>
@@ -28697,10 +28748,10 @@
         <v>1222</v>
       </c>
       <c r="C98" s="54" t="s">
-        <v>2362</v>
+        <v>2365</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>2363</v>
+        <v>2366</v>
       </c>
       <c r="E98" s="54"/>
       <c r="F98" s="54"/>
@@ -28718,10 +28769,10 @@
         <v>1223</v>
       </c>
       <c r="C99" s="54" t="s">
-        <v>2364</v>
+        <v>2367</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>2365</v>
+        <v>2368</v>
       </c>
       <c r="E99" s="54"/>
       <c r="F99" s="54"/>
@@ -28734,13 +28785,13 @@
         <v>423</v>
       </c>
       <c r="B100" s="56" t="s">
-        <v>2366</v>
+        <v>2369</v>
       </c>
       <c r="C100" s="54" t="s">
-        <v>2367</v>
+        <v>2370</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>2368</v>
+        <v>2371</v>
       </c>
       <c r="E100" s="54"/>
       <c r="F100" s="54"/>
@@ -28771,10 +28822,10 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="96" t="s">
-        <v>2369</v>
+        <v>2372</v>
       </c>
       <c r="B102" s="69" t="s">
-        <v>2370</v>
+        <v>2373</v>
       </c>
       <c r="C102" s="69" t="s">
         <v>1742</v>
@@ -28791,10 +28842,10 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="96" t="s">
-        <v>2369</v>
+        <v>2372</v>
       </c>
       <c r="B103" s="69" t="s">
-        <v>2371</v>
+        <v>2374</v>
       </c>
       <c r="C103" s="69" t="s">
         <v>1747</v>
@@ -28811,16 +28862,16 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="96" t="s">
-        <v>2369</v>
+        <v>2372</v>
       </c>
       <c r="B104" s="69" t="s">
         <v>1215</v>
       </c>
       <c r="C104" s="69" t="s">
-        <v>2161</v>
+        <v>2164</v>
       </c>
       <c r="D104" s="69" t="s">
-        <v>2162</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28828,13 +28879,13 @@
         <v>759</v>
       </c>
       <c r="B105" s="69" t="s">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="C105" s="69" t="s">
-        <v>2373</v>
+        <v>2376</v>
       </c>
       <c r="D105" s="69" t="s">
-        <v>2374</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28842,13 +28893,13 @@
         <v>759</v>
       </c>
       <c r="B106" s="69" t="s">
-        <v>2375</v>
+        <v>2378</v>
       </c>
       <c r="C106" s="69" t="s">
-        <v>2376</v>
+        <v>2379</v>
       </c>
       <c r="D106" s="69" t="s">
-        <v>2377</v>
+        <v>2380</v>
       </c>
       <c r="I106" s="93" t="n">
         <f aca="false">TRUE()</f>
@@ -28860,13 +28911,13 @@
         <v>759</v>
       </c>
       <c r="B107" s="69" t="s">
-        <v>2378</v>
+        <v>2381</v>
       </c>
       <c r="C107" s="69" t="s">
-        <v>2379</v>
+        <v>2382</v>
       </c>
       <c r="D107" s="69" t="s">
-        <v>2380</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28874,13 +28925,13 @@
         <v>759</v>
       </c>
       <c r="B108" s="69" t="s">
-        <v>2381</v>
+        <v>2384</v>
       </c>
       <c r="C108" s="69" t="s">
-        <v>2382</v>
+        <v>2385</v>
       </c>
       <c r="D108" s="69" t="s">
-        <v>2383</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28888,7 +28939,7 @@
         <v>759</v>
       </c>
       <c r="G109" s="56" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28896,7 +28947,7 @@
         <v>759</v>
       </c>
       <c r="G110" s="56" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28904,13 +28955,13 @@
         <v>819</v>
       </c>
       <c r="B111" s="69" t="s">
-        <v>2384</v>
+        <v>2387</v>
       </c>
       <c r="C111" s="69" t="s">
-        <v>2385</v>
+        <v>2388</v>
       </c>
       <c r="D111" s="69" t="s">
-        <v>2386</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28918,13 +28969,13 @@
         <v>819</v>
       </c>
       <c r="B112" s="69" t="s">
-        <v>2387</v>
+        <v>2390</v>
       </c>
       <c r="C112" s="69" t="s">
-        <v>2388</v>
+        <v>2391</v>
       </c>
       <c r="D112" s="69" t="s">
-        <v>2389</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28932,13 +28983,13 @@
         <v>819</v>
       </c>
       <c r="B113" s="69" t="s">
-        <v>2378</v>
+        <v>2381</v>
       </c>
       <c r="C113" s="69" t="s">
-        <v>2390</v>
+        <v>2393</v>
       </c>
       <c r="D113" s="69" t="s">
-        <v>2391</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28946,13 +28997,13 @@
         <v>819</v>
       </c>
       <c r="B114" s="56" t="s">
-        <v>2392</v>
+        <v>2395</v>
       </c>
       <c r="C114" s="54" t="s">
-        <v>2393</v>
+        <v>2396</v>
       </c>
       <c r="D114" s="51" t="s">
-        <v>2394</v>
+        <v>2397</v>
       </c>
       <c r="I114" s="93" t="n">
         <f aca="false">TRUE()</f>
@@ -28964,7 +29015,7 @@
         <v>819</v>
       </c>
       <c r="G115" s="56" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28972,7 +29023,7 @@
         <v>819</v>
       </c>
       <c r="G116" s="56" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28980,13 +29031,13 @@
         <v>347</v>
       </c>
       <c r="B117" s="69" t="s">
-        <v>2395</v>
+        <v>2398</v>
       </c>
       <c r="C117" s="69" t="s">
-        <v>2396</v>
+        <v>2399</v>
       </c>
       <c r="D117" s="69" t="s">
-        <v>2397</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28994,13 +29045,13 @@
         <v>347</v>
       </c>
       <c r="B118" s="69" t="s">
-        <v>2398</v>
+        <v>2401</v>
       </c>
       <c r="C118" s="69" t="s">
-        <v>2399</v>
+        <v>2402</v>
       </c>
       <c r="D118" s="69" t="s">
-        <v>2400</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29008,13 +29059,13 @@
         <v>347</v>
       </c>
       <c r="B119" s="69" t="s">
-        <v>2401</v>
+        <v>2404</v>
       </c>
       <c r="C119" s="69" t="s">
-        <v>2402</v>
+        <v>2405</v>
       </c>
       <c r="D119" s="69" t="s">
-        <v>2403</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29027,103 +29078,103 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="92" t="s">
-        <v>2404</v>
+        <v>2407</v>
       </c>
       <c r="B121" s="56" t="s">
         <v>1189</v>
       </c>
       <c r="C121" s="56" t="s">
-        <v>2405</v>
+        <v>2408</v>
       </c>
       <c r="D121" s="56" t="s">
-        <v>2406</v>
+        <v>2409</v>
       </c>
       <c r="E121" s="56" t="s">
-        <v>2407</v>
+        <v>2410</v>
       </c>
       <c r="F121" s="56" t="s">
-        <v>2408</v>
+        <v>2411</v>
       </c>
       <c r="G121" s="92"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="92" t="s">
-        <v>2404</v>
+        <v>2407</v>
       </c>
       <c r="B122" s="56" t="s">
         <v>1190</v>
       </c>
       <c r="C122" s="56" t="s">
-        <v>2409</v>
+        <v>2412</v>
       </c>
       <c r="D122" s="56" t="s">
-        <v>2410</v>
+        <v>2413</v>
       </c>
       <c r="E122" s="56" t="s">
-        <v>2411</v>
+        <v>2414</v>
       </c>
       <c r="F122" s="56" t="s">
-        <v>2412</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="92" t="s">
-        <v>2404</v>
+        <v>2407</v>
       </c>
       <c r="B123" s="56" t="s">
         <v>1191</v>
       </c>
       <c r="C123" s="56" t="s">
-        <v>2413</v>
+        <v>2416</v>
       </c>
       <c r="D123" s="56" t="s">
-        <v>2414</v>
+        <v>2417</v>
       </c>
       <c r="E123" s="56" t="s">
-        <v>2415</v>
+        <v>2418</v>
       </c>
       <c r="F123" s="56" t="s">
-        <v>2416</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="92" t="s">
-        <v>2404</v>
+        <v>2407</v>
       </c>
       <c r="B124" s="56" t="s">
         <v>1205</v>
       </c>
       <c r="C124" s="56" t="s">
-        <v>2417</v>
+        <v>2420</v>
       </c>
       <c r="D124" s="56" t="s">
-        <v>2418</v>
+        <v>2421</v>
       </c>
       <c r="E124" s="56" t="s">
-        <v>2419</v>
+        <v>2422</v>
       </c>
       <c r="F124" s="56" t="s">
-        <v>2420</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="92" t="s">
-        <v>2404</v>
+        <v>2407</v>
       </c>
       <c r="B125" s="56" t="s">
-        <v>2278</v>
+        <v>2281</v>
       </c>
       <c r="C125" s="56" t="s">
-        <v>2421</v>
+        <v>2424</v>
       </c>
       <c r="D125" s="56" t="s">
-        <v>2422</v>
+        <v>2425</v>
       </c>
       <c r="E125" s="56" t="s">
-        <v>2423</v>
+        <v>2426</v>
       </c>
       <c r="F125" s="56" t="s">
-        <v>2424</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29131,7 +29182,7 @@
         <v>686</v>
       </c>
       <c r="B126" s="69" t="s">
-        <v>2425</v>
+        <v>2428</v>
       </c>
       <c r="C126" s="8" t="s">
         <v>2011</v>
@@ -29148,10 +29199,10 @@
         <v>1227</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>2426</v>
+        <v>2429</v>
       </c>
       <c r="D127" s="60" t="s">
-        <v>2426</v>
+        <v>2429</v>
       </c>
       <c r="H127" s="98" t="s">
         <v>1225</v>
@@ -29162,16 +29213,16 @@
         <v>686</v>
       </c>
       <c r="B128" s="69" t="s">
-        <v>2427</v>
+        <v>2430</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>2428</v>
+        <v>2431</v>
       </c>
       <c r="D128" s="60" t="s">
-        <v>2429</v>
+        <v>2432</v>
       </c>
       <c r="H128" s="99" t="s">
-        <v>2430</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29179,7 +29230,7 @@
         <v>686</v>
       </c>
       <c r="B129" s="69" t="s">
-        <v>2431</v>
+        <v>2434</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>2020</v>
@@ -29196,7 +29247,7 @@
         <v>686</v>
       </c>
       <c r="B130" s="69" t="s">
-        <v>2432</v>
+        <v>2435</v>
       </c>
       <c r="C130" s="8" t="s">
         <v>2023</v>
@@ -29220,7 +29271,7 @@
         <v>692</v>
       </c>
       <c r="B132" s="69" t="s">
-        <v>2425</v>
+        <v>2428</v>
       </c>
       <c r="C132" s="8" t="s">
         <v>2011</v>
@@ -29234,7 +29285,7 @@
         <v>692</v>
       </c>
       <c r="B133" s="69" t="s">
-        <v>2433</v>
+        <v>2436</v>
       </c>
       <c r="C133" s="8" t="s">
         <v>2030</v>
@@ -29248,7 +29299,7 @@
         <v>692</v>
       </c>
       <c r="B134" s="69" t="s">
-        <v>2431</v>
+        <v>2434</v>
       </c>
       <c r="C134" s="8" t="s">
         <v>2020</v>
@@ -29265,7 +29316,7 @@
         <v>692</v>
       </c>
       <c r="B135" s="69" t="s">
-        <v>2432</v>
+        <v>2435</v>
       </c>
       <c r="C135" s="8" t="s">
         <v>2023</v>
@@ -29279,13 +29330,13 @@
         <v>692</v>
       </c>
       <c r="B136" s="69" t="s">
-        <v>2434</v>
+        <v>2437</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>2435</v>
+        <v>2438</v>
       </c>
       <c r="D136" s="60" t="s">
-        <v>2436</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29293,7 +29344,7 @@
         <v>692</v>
       </c>
       <c r="B137" s="69" t="s">
-        <v>2437</v>
+        <v>2440</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>2026</v>
@@ -29309,7 +29360,7 @@
       <c r="C138" s="60"/>
       <c r="D138" s="60"/>
       <c r="G138" s="56" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29317,16 +29368,16 @@
         <v>582</v>
       </c>
       <c r="B139" s="69" t="s">
-        <v>2438</v>
+        <v>2441</v>
       </c>
       <c r="C139" s="60" t="s">
-        <v>2439</v>
+        <v>2442</v>
       </c>
       <c r="D139" s="60" t="s">
-        <v>2440</v>
+        <v>2443</v>
       </c>
       <c r="H139" s="57" t="s">
-        <v>2441</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29337,13 +29388,13 @@
         <v>1215</v>
       </c>
       <c r="C140" s="60" t="s">
-        <v>2442</v>
+        <v>2445</v>
       </c>
       <c r="D140" s="60" t="s">
-        <v>2443</v>
+        <v>2446</v>
       </c>
       <c r="H140" s="8" t="s">
-        <v>2444</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29354,10 +29405,10 @@
         <v>1157</v>
       </c>
       <c r="C141" s="60" t="s">
-        <v>2445</v>
+        <v>2448</v>
       </c>
       <c r="D141" s="60" t="s">
-        <v>2446</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29365,13 +29416,13 @@
         <v>582</v>
       </c>
       <c r="B142" s="69" t="s">
-        <v>2447</v>
+        <v>2450</v>
       </c>
       <c r="C142" s="60" t="s">
-        <v>2448</v>
+        <v>2451</v>
       </c>
       <c r="D142" s="60" t="s">
-        <v>2449</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29381,7 +29432,7 @@
       <c r="C143" s="60"/>
       <c r="D143" s="60"/>
       <c r="G143" s="69" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29389,13 +29440,13 @@
         <v>615</v>
       </c>
       <c r="B144" s="69" t="s">
-        <v>2450</v>
+        <v>2453</v>
       </c>
       <c r="C144" s="60" t="s">
-        <v>2451</v>
+        <v>2454</v>
       </c>
       <c r="D144" s="60" t="s">
-        <v>2451</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29403,13 +29454,13 @@
         <v>615</v>
       </c>
       <c r="B145" s="69" t="s">
-        <v>2452</v>
+        <v>2455</v>
       </c>
       <c r="C145" s="60" t="s">
-        <v>2453</v>
+        <v>2456</v>
       </c>
       <c r="D145" s="60" t="s">
-        <v>2454</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29419,7 +29470,7 @@
       <c r="C146" s="60"/>
       <c r="D146" s="60"/>
       <c r="G146" s="69" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29427,13 +29478,13 @@
         <v>639</v>
       </c>
       <c r="B147" s="69" t="s">
-        <v>2455</v>
+        <v>2458</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>2456</v>
+        <v>2459</v>
       </c>
       <c r="D147" s="60" t="s">
-        <v>2457</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29441,13 +29492,13 @@
         <v>639</v>
       </c>
       <c r="B148" s="69" t="s">
-        <v>2458</v>
+        <v>2461</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>2459</v>
+        <v>2462</v>
       </c>
       <c r="D148" s="60" t="s">
-        <v>2460</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29457,7 +29508,7 @@
       <c r="C149" s="60"/>
       <c r="D149" s="60"/>
       <c r="G149" s="56" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29467,7 +29518,7 @@
       <c r="C150" s="60"/>
       <c r="D150" s="60"/>
       <c r="G150" s="69" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29475,13 +29526,13 @@
         <v>646</v>
       </c>
       <c r="B151" s="69" t="s">
-        <v>2461</v>
+        <v>2464</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>2462</v>
+        <v>2465</v>
       </c>
       <c r="D151" s="60" t="s">
-        <v>2463</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29489,13 +29540,13 @@
         <v>646</v>
       </c>
       <c r="B152" s="69" t="s">
-        <v>2464</v>
+        <v>2467</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>2465</v>
+        <v>2468</v>
       </c>
       <c r="D152" s="60" t="s">
-        <v>2465</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29503,13 +29554,13 @@
         <v>646</v>
       </c>
       <c r="B153" s="69" t="s">
-        <v>2466</v>
+        <v>2469</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>2467</v>
+        <v>2470</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>2467</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29517,13 +29568,13 @@
         <v>646</v>
       </c>
       <c r="B154" s="69" t="s">
-        <v>2468</v>
+        <v>2471</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>2469</v>
+        <v>2472</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>2469</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29533,7 +29584,7 @@
       <c r="C155" s="60"/>
       <c r="D155" s="60"/>
       <c r="G155" s="56" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29543,7 +29594,7 @@
       <c r="C156" s="60"/>
       <c r="D156" s="60"/>
       <c r="G156" s="69" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29551,13 +29602,13 @@
         <v>651</v>
       </c>
       <c r="B157" s="69" t="s">
-        <v>2470</v>
+        <v>2473</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>2471</v>
+        <v>2474</v>
       </c>
       <c r="D157" s="60" t="s">
-        <v>2472</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29565,13 +29616,13 @@
         <v>651</v>
       </c>
       <c r="B158" s="69" t="s">
-        <v>2473</v>
+        <v>2476</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>2474</v>
+        <v>2477</v>
       </c>
       <c r="D158" s="60" t="s">
-        <v>2475</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29579,13 +29630,13 @@
         <v>651</v>
       </c>
       <c r="B159" s="69" t="s">
-        <v>2455</v>
+        <v>2458</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>2476</v>
+        <v>2479</v>
       </c>
       <c r="D159" s="60" t="s">
-        <v>2477</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29593,13 +29644,13 @@
         <v>651</v>
       </c>
       <c r="B160" s="69" t="s">
-        <v>2478</v>
+        <v>2481</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>2479</v>
+        <v>2482</v>
       </c>
       <c r="D160" s="8" t="s">
-        <v>2479</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29607,13 +29658,13 @@
         <v>651</v>
       </c>
       <c r="B161" s="69" t="s">
-        <v>2480</v>
+        <v>2483</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>2481</v>
+        <v>2484</v>
       </c>
       <c r="D161" s="60" t="s">
-        <v>2482</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29623,7 +29674,7 @@
       <c r="C162" s="60"/>
       <c r="D162" s="60"/>
       <c r="G162" s="56" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29633,7 +29684,7 @@
       <c r="C163" s="60"/>
       <c r="D163" s="60"/>
       <c r="G163" s="69" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29641,7 +29692,7 @@
         <v>783</v>
       </c>
       <c r="B164" s="56" t="s">
-        <v>2431</v>
+        <v>2434</v>
       </c>
       <c r="C164" s="69" t="s">
         <v>1960</v>
@@ -29660,7 +29711,7 @@
         <v>783</v>
       </c>
       <c r="B165" s="56" t="s">
-        <v>2432</v>
+        <v>2435</v>
       </c>
       <c r="C165" s="69" t="s">
         <v>1978</v>
@@ -29679,13 +29730,13 @@
         <v>783</v>
       </c>
       <c r="B166" s="56" t="s">
-        <v>2437</v>
+        <v>2440</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>2483</v>
+        <v>2486</v>
       </c>
       <c r="D166" s="60" t="s">
-        <v>2484</v>
+        <v>2487</v>
       </c>
       <c r="E166" s="56"/>
       <c r="F166" s="56"/>
@@ -29698,7 +29749,7 @@
         <v>783</v>
       </c>
       <c r="B167" s="56" t="s">
-        <v>2425</v>
+        <v>2428</v>
       </c>
       <c r="C167" s="8" t="s">
         <v>1913</v>
@@ -29717,7 +29768,7 @@
         <v>783</v>
       </c>
       <c r="B168" s="56" t="s">
-        <v>2485</v>
+        <v>2488</v>
       </c>
       <c r="C168" s="8" t="s">
         <v>1916</v>
@@ -29739,10 +29790,10 @@
         <v>229</v>
       </c>
       <c r="C169" s="54" t="s">
-        <v>2486</v>
+        <v>2489</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>2487</v>
+        <v>2490</v>
       </c>
       <c r="E169" s="56"/>
       <c r="F169" s="56"/>
@@ -29757,13 +29808,13 @@
         <v>783</v>
       </c>
       <c r="B170" s="56" t="s">
-        <v>2488</v>
+        <v>2491</v>
       </c>
       <c r="C170" s="54" t="s">
-        <v>2489</v>
+        <v>2492</v>
       </c>
       <c r="D170" s="8" t="s">
-        <v>2490</v>
+        <v>2493</v>
       </c>
       <c r="E170" s="56"/>
       <c r="F170" s="56"/>
@@ -29778,13 +29829,13 @@
         <v>129</v>
       </c>
       <c r="B171" s="56" t="s">
-        <v>2491</v>
+        <v>2494</v>
       </c>
       <c r="C171" s="54" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="D171" s="8" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="E171" s="56"/>
       <c r="F171" s="56"/>
@@ -29797,13 +29848,13 @@
         <v>129</v>
       </c>
       <c r="B172" s="56" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="C172" s="54" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="D172" s="8" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="E172" s="56"/>
       <c r="F172" s="56"/>
@@ -29857,10 +29908,10 @@
         <v>2</v>
       </c>
       <c r="C175" s="55" t="s">
-        <v>2497</v>
+        <v>2500</v>
       </c>
       <c r="D175" s="55" t="s">
-        <v>2497</v>
+        <v>2500</v>
       </c>
       <c r="E175" s="56"/>
       <c r="F175" s="56"/>
@@ -29876,10 +29927,10 @@
         <v>1157</v>
       </c>
       <c r="C176" s="54" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="E176" s="56"/>
       <c r="F176" s="56"/>
@@ -29895,10 +29946,10 @@
         <v>1215</v>
       </c>
       <c r="C177" s="54" t="s">
-        <v>2500</v>
+        <v>2503</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>2501</v>
+        <v>2504</v>
       </c>
       <c r="E177" s="56"/>
       <c r="F177" s="56"/>
@@ -29916,7 +29967,7 @@
       <c r="E178" s="56"/>
       <c r="F178" s="56"/>
       <c r="G178" s="56" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="H178" s="56"/>
       <c r="I178" s="56"/>
@@ -29926,13 +29977,13 @@
         <v>246</v>
       </c>
       <c r="B179" s="56" t="s">
-        <v>2502</v>
+        <v>2505</v>
       </c>
       <c r="C179" s="51" t="s">
-        <v>2503</v>
+        <v>2506</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>2504</v>
+        <v>2507</v>
       </c>
       <c r="E179" s="56"/>
       <c r="F179" s="56"/>
@@ -29947,13 +29998,13 @@
         <v>246</v>
       </c>
       <c r="B180" s="56" t="s">
-        <v>2505</v>
+        <v>2508</v>
       </c>
       <c r="C180" s="51" t="s">
-        <v>2506</v>
+        <v>2509</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>2507</v>
+        <v>2510</v>
       </c>
       <c r="E180" s="56"/>
       <c r="F180" s="56"/>
@@ -29968,13 +30019,13 @@
         <v>246</v>
       </c>
       <c r="B181" s="56" t="s">
-        <v>2508</v>
+        <v>2511</v>
       </c>
       <c r="C181" s="51" t="s">
-        <v>2509</v>
+        <v>2512</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>2510</v>
+        <v>2513</v>
       </c>
       <c r="E181" s="56"/>
       <c r="F181" s="56"/>
@@ -29989,13 +30040,13 @@
         <v>246</v>
       </c>
       <c r="B182" s="56" t="s">
-        <v>2511</v>
+        <v>2514</v>
       </c>
       <c r="C182" s="51" t="s">
-        <v>2512</v>
+        <v>2515</v>
       </c>
       <c r="D182" s="8" t="s">
-        <v>2513</v>
+        <v>2516</v>
       </c>
       <c r="E182" s="56"/>
       <c r="F182" s="56"/>
@@ -30010,13 +30061,13 @@
         <v>246</v>
       </c>
       <c r="B183" s="56" t="s">
-        <v>2514</v>
+        <v>2517</v>
       </c>
       <c r="C183" s="51" t="s">
-        <v>2515</v>
+        <v>2518</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>2516</v>
+        <v>2519</v>
       </c>
       <c r="E183" s="56"/>
       <c r="F183" s="56"/>
@@ -30031,13 +30082,13 @@
         <v>246</v>
       </c>
       <c r="B184" s="56" t="s">
-        <v>2517</v>
+        <v>2520</v>
       </c>
       <c r="C184" s="51" t="s">
-        <v>2518</v>
+        <v>2521</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>2519</v>
+        <v>2522</v>
       </c>
       <c r="E184" s="56"/>
       <c r="F184" s="56"/>
@@ -30052,13 +30103,13 @@
         <v>246</v>
       </c>
       <c r="B185" s="56" t="s">
-        <v>2520</v>
+        <v>2523</v>
       </c>
       <c r="C185" s="51" t="s">
-        <v>2521</v>
+        <v>2524</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>2522</v>
+        <v>2525</v>
       </c>
       <c r="E185" s="56"/>
       <c r="F185" s="56"/>
@@ -30073,13 +30124,13 @@
         <v>246</v>
       </c>
       <c r="B186" s="56" t="s">
-        <v>2523</v>
+        <v>2526</v>
       </c>
       <c r="C186" s="51" t="s">
-        <v>2524</v>
+        <v>2527</v>
       </c>
       <c r="D186" s="8" t="s">
-        <v>2525</v>
+        <v>2528</v>
       </c>
       <c r="E186" s="56"/>
       <c r="F186" s="56"/>
@@ -30094,13 +30145,13 @@
         <v>246</v>
       </c>
       <c r="B187" s="56" t="s">
-        <v>2526</v>
+        <v>2529</v>
       </c>
       <c r="C187" s="51" t="s">
-        <v>2527</v>
+        <v>2530</v>
       </c>
       <c r="D187" s="8" t="s">
-        <v>2528</v>
+        <v>2531</v>
       </c>
       <c r="E187" s="56"/>
       <c r="F187" s="56"/>
@@ -30118,10 +30169,10 @@
         <v>229</v>
       </c>
       <c r="C188" s="51" t="s">
-        <v>2163</v>
+        <v>2166</v>
       </c>
       <c r="D188" s="8" t="s">
-        <v>2164</v>
+        <v>2167</v>
       </c>
       <c r="E188" s="56"/>
       <c r="F188" s="56"/>
@@ -30151,13 +30202,13 @@
         <v>258</v>
       </c>
       <c r="B190" s="56" t="s">
-        <v>2529</v>
+        <v>2532</v>
       </c>
       <c r="C190" s="51" t="s">
-        <v>2530</v>
+        <v>2533</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>2531</v>
+        <v>2534</v>
       </c>
       <c r="E190" s="56"/>
       <c r="F190" s="56"/>
@@ -30172,13 +30223,13 @@
         <v>258</v>
       </c>
       <c r="B191" s="56" t="s">
-        <v>2532</v>
+        <v>2535</v>
       </c>
       <c r="C191" s="51" t="s">
-        <v>2533</v>
+        <v>2536</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>2534</v>
+        <v>2537</v>
       </c>
       <c r="E191" s="56"/>
       <c r="F191" s="56"/>
@@ -30193,13 +30244,13 @@
         <v>258</v>
       </c>
       <c r="B192" s="56" t="s">
-        <v>2535</v>
+        <v>2538</v>
       </c>
       <c r="C192" s="51" t="s">
-        <v>2536</v>
+        <v>2539</v>
       </c>
       <c r="D192" s="8" t="s">
-        <v>2537</v>
+        <v>2540</v>
       </c>
       <c r="E192" s="56"/>
       <c r="F192" s="56"/>
@@ -30214,13 +30265,13 @@
         <v>258</v>
       </c>
       <c r="B193" s="56" t="s">
-        <v>2538</v>
+        <v>2541</v>
       </c>
       <c r="C193" s="51" t="s">
-        <v>2539</v>
+        <v>2542</v>
       </c>
       <c r="D193" s="8" t="s">
-        <v>2540</v>
+        <v>2543</v>
       </c>
       <c r="E193" s="56"/>
       <c r="F193" s="56"/>
@@ -30235,13 +30286,13 @@
         <v>258</v>
       </c>
       <c r="B194" s="56" t="s">
-        <v>2541</v>
+        <v>2544</v>
       </c>
       <c r="C194" s="51" t="s">
-        <v>2542</v>
+        <v>2545</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>2543</v>
+        <v>2546</v>
       </c>
       <c r="E194" s="56"/>
       <c r="F194" s="56"/>
@@ -30256,13 +30307,13 @@
         <v>258</v>
       </c>
       <c r="B195" s="56" t="s">
-        <v>2544</v>
+        <v>2547</v>
       </c>
       <c r="C195" s="51" t="s">
-        <v>2545</v>
+        <v>2548</v>
       </c>
       <c r="D195" s="8" t="s">
-        <v>2546</v>
+        <v>2549</v>
       </c>
       <c r="E195" s="56"/>
       <c r="F195" s="56"/>
@@ -30277,13 +30328,13 @@
         <v>258</v>
       </c>
       <c r="B196" s="56" t="s">
-        <v>2547</v>
+        <v>2550</v>
       </c>
       <c r="C196" s="51" t="s">
-        <v>2548</v>
+        <v>2551</v>
       </c>
       <c r="D196" s="8" t="s">
-        <v>2549</v>
+        <v>2552</v>
       </c>
       <c r="E196" s="56"/>
       <c r="F196" s="56"/>
@@ -30301,10 +30352,10 @@
         <v>1197</v>
       </c>
       <c r="C197" s="51" t="s">
-        <v>2550</v>
+        <v>2553</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>2551</v>
+        <v>2554</v>
       </c>
       <c r="E197" s="56"/>
       <c r="F197" s="56"/>
@@ -30321,10 +30372,10 @@
         <v>229</v>
       </c>
       <c r="C198" s="51" t="s">
-        <v>2163</v>
+        <v>2166</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>2164</v>
+        <v>2167</v>
       </c>
       <c r="E198" s="56"/>
       <c r="F198" s="56"/>
@@ -30342,10 +30393,10 @@
         <v>1161</v>
       </c>
       <c r="C199" s="56" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="D199" s="56" t="s">
-        <v>2170</v>
+        <v>2173</v>
       </c>
       <c r="E199" s="56"/>
       <c r="F199" s="56"/>
@@ -30359,13 +30410,13 @@
         <v>287</v>
       </c>
       <c r="B200" s="56" t="s">
-        <v>2552</v>
+        <v>2555</v>
       </c>
       <c r="C200" s="51" t="s">
-        <v>2553</v>
+        <v>2556</v>
       </c>
       <c r="D200" s="8" t="s">
-        <v>2554</v>
+        <v>2557</v>
       </c>
       <c r="E200" s="56"/>
       <c r="F200" s="56"/>
@@ -30378,13 +30429,13 @@
         <v>287</v>
       </c>
       <c r="B201" s="56" t="s">
-        <v>2555</v>
+        <v>2558</v>
       </c>
       <c r="C201" s="51" t="s">
-        <v>2556</v>
+        <v>2559</v>
       </c>
       <c r="D201" s="8" t="s">
-        <v>2557</v>
+        <v>2560</v>
       </c>
       <c r="E201" s="56"/>
       <c r="F201" s="56"/>
@@ -30397,13 +30448,13 @@
         <v>287</v>
       </c>
       <c r="B202" s="56" t="s">
-        <v>2558</v>
+        <v>2561</v>
       </c>
       <c r="C202" s="51" t="s">
-        <v>2559</v>
+        <v>2562</v>
       </c>
       <c r="D202" s="8" t="s">
-        <v>2560</v>
+        <v>2563</v>
       </c>
       <c r="E202" s="56"/>
       <c r="F202" s="56"/>
@@ -30416,13 +30467,13 @@
         <v>287</v>
       </c>
       <c r="B203" s="56" t="s">
-        <v>2561</v>
+        <v>2564</v>
       </c>
       <c r="C203" s="51" t="s">
-        <v>2562</v>
+        <v>2565</v>
       </c>
       <c r="D203" s="8" t="s">
-        <v>2563</v>
+        <v>2566</v>
       </c>
       <c r="E203" s="56"/>
       <c r="F203" s="56"/>
@@ -30435,13 +30486,13 @@
         <v>287</v>
       </c>
       <c r="B204" s="56" t="s">
-        <v>2564</v>
+        <v>2567</v>
       </c>
       <c r="C204" s="51" t="s">
-        <v>2565</v>
+        <v>2568</v>
       </c>
       <c r="D204" s="8" t="s">
-        <v>2566</v>
+        <v>2569</v>
       </c>
       <c r="E204" s="56"/>
       <c r="F204" s="56"/>
@@ -30454,13 +30505,13 @@
         <v>294</v>
       </c>
       <c r="B205" s="56" t="s">
-        <v>2552</v>
+        <v>2555</v>
       </c>
       <c r="C205" s="51" t="s">
-        <v>2553</v>
+        <v>2556</v>
       </c>
       <c r="D205" s="8" t="s">
-        <v>2554</v>
+        <v>2557</v>
       </c>
       <c r="E205" s="56"/>
       <c r="F205" s="56"/>
@@ -30475,13 +30526,13 @@
         <v>294</v>
       </c>
       <c r="B206" s="56" t="s">
-        <v>2555</v>
+        <v>2558</v>
       </c>
       <c r="C206" s="51" t="s">
-        <v>2556</v>
+        <v>2559</v>
       </c>
       <c r="D206" s="8" t="s">
-        <v>2557</v>
+        <v>2560</v>
       </c>
       <c r="E206" s="56"/>
       <c r="F206" s="56"/>
@@ -30494,13 +30545,13 @@
         <v>294</v>
       </c>
       <c r="B207" s="56" t="s">
-        <v>2558</v>
+        <v>2561</v>
       </c>
       <c r="C207" s="51" t="s">
-        <v>2559</v>
+        <v>2562</v>
       </c>
       <c r="D207" s="8" t="s">
-        <v>2560</v>
+        <v>2563</v>
       </c>
       <c r="E207" s="56"/>
       <c r="F207" s="56"/>
@@ -30513,13 +30564,13 @@
         <v>294</v>
       </c>
       <c r="B208" s="56" t="s">
-        <v>2561</v>
+        <v>2564</v>
       </c>
       <c r="C208" s="51" t="s">
-        <v>2562</v>
+        <v>2565</v>
       </c>
       <c r="D208" s="8" t="s">
-        <v>2563</v>
+        <v>2566</v>
       </c>
       <c r="E208" s="56"/>
       <c r="F208" s="56"/>
@@ -30532,13 +30583,13 @@
         <v>294</v>
       </c>
       <c r="B209" s="56" t="s">
-        <v>2564</v>
+        <v>2567</v>
       </c>
       <c r="C209" s="51" t="s">
-        <v>2565</v>
+        <v>2568</v>
       </c>
       <c r="D209" s="8" t="s">
-        <v>2566</v>
+        <v>2569</v>
       </c>
       <c r="E209" s="56"/>
       <c r="F209" s="56"/>
@@ -30551,7 +30602,7 @@
         <v>847</v>
       </c>
       <c r="B210" s="69" t="s">
-        <v>2425</v>
+        <v>2428</v>
       </c>
       <c r="C210" s="69" t="s">
         <v>2011</v>
@@ -30565,7 +30616,7 @@
         <v>847</v>
       </c>
       <c r="B211" s="69" t="s">
-        <v>2433</v>
+        <v>2436</v>
       </c>
       <c r="C211" s="69" t="s">
         <v>2030</v>
@@ -30579,13 +30630,13 @@
         <v>847</v>
       </c>
       <c r="B212" s="69" t="s">
-        <v>2567</v>
+        <v>2570</v>
       </c>
       <c r="C212" s="69" t="s">
-        <v>2568</v>
+        <v>2571</v>
       </c>
       <c r="D212" s="69" t="s">
-        <v>2569</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30593,13 +30644,13 @@
         <v>847</v>
       </c>
       <c r="B213" s="69" t="s">
-        <v>2437</v>
+        <v>2440</v>
       </c>
       <c r="C213" s="69" t="s">
-        <v>2570</v>
+        <v>2573</v>
       </c>
       <c r="D213" s="69" t="s">
-        <v>2571</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30607,7 +30658,7 @@
         <v>847</v>
       </c>
       <c r="G214" s="69" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30615,13 +30666,13 @@
         <v>872</v>
       </c>
       <c r="B215" s="69" t="s">
-        <v>2572</v>
+        <v>2575</v>
       </c>
       <c r="C215" s="69" t="s">
-        <v>2573</v>
+        <v>2576</v>
       </c>
       <c r="D215" s="69" t="s">
-        <v>2574</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30629,13 +30680,13 @@
         <v>872</v>
       </c>
       <c r="B216" s="69" t="s">
-        <v>2575</v>
+        <v>2578</v>
       </c>
       <c r="C216" s="69" t="s">
-        <v>2576</v>
+        <v>2579</v>
       </c>
       <c r="D216" s="69" t="s">
-        <v>2577</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30643,13 +30694,13 @@
         <v>872</v>
       </c>
       <c r="B217" s="69" t="s">
-        <v>2578</v>
+        <v>2581</v>
       </c>
       <c r="C217" s="69" t="s">
-        <v>2579</v>
+        <v>2582</v>
       </c>
       <c r="D217" s="69" t="s">
-        <v>2580</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30657,13 +30708,13 @@
         <v>872</v>
       </c>
       <c r="B218" s="69" t="s">
-        <v>2581</v>
+        <v>2584</v>
       </c>
       <c r="C218" s="69" t="s">
-        <v>2582</v>
+        <v>2585</v>
       </c>
       <c r="D218" s="69" t="s">
-        <v>2583</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30671,13 +30722,13 @@
         <v>872</v>
       </c>
       <c r="B219" s="69" t="s">
-        <v>2584</v>
+        <v>2587</v>
       </c>
       <c r="C219" s="69" t="s">
-        <v>2585</v>
+        <v>2588</v>
       </c>
       <c r="D219" s="69" t="s">
-        <v>2586</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30685,13 +30736,13 @@
         <v>872</v>
       </c>
       <c r="B220" s="69" t="s">
-        <v>2587</v>
+        <v>2590</v>
       </c>
       <c r="C220" s="69" t="s">
-        <v>2588</v>
+        <v>2591</v>
       </c>
       <c r="D220" s="69" t="s">
-        <v>2589</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30702,10 +30753,10 @@
         <v>229</v>
       </c>
       <c r="C221" s="69" t="s">
-        <v>2590</v>
+        <v>2593</v>
       </c>
       <c r="D221" s="69" t="s">
-        <v>2591</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30713,7 +30764,7 @@
         <v>877</v>
       </c>
       <c r="B222" s="69" t="s">
-        <v>2425</v>
+        <v>2428</v>
       </c>
       <c r="C222" s="69" t="s">
         <v>2011</v>
@@ -30727,7 +30778,7 @@
         <v>877</v>
       </c>
       <c r="B223" s="69" t="s">
-        <v>2433</v>
+        <v>2436</v>
       </c>
       <c r="C223" s="69" t="s">
         <v>2030</v>
@@ -30741,13 +30792,13 @@
         <v>877</v>
       </c>
       <c r="B224" s="69" t="s">
-        <v>2431</v>
+        <v>2434</v>
       </c>
       <c r="C224" s="69" t="s">
-        <v>2592</v>
+        <v>2595</v>
       </c>
       <c r="D224" s="69" t="s">
-        <v>2593</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="225" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30755,13 +30806,13 @@
         <v>877</v>
       </c>
       <c r="B225" s="69" t="s">
-        <v>2432</v>
+        <v>2435</v>
       </c>
       <c r="C225" s="69" t="s">
-        <v>2594</v>
+        <v>2597</v>
       </c>
       <c r="D225" s="69" t="s">
-        <v>2595</v>
+        <v>2598</v>
       </c>
       <c r="E225" s="69"/>
       <c r="F225" s="69"/>
@@ -30774,13 +30825,13 @@
         <v>877</v>
       </c>
       <c r="B226" s="69" t="s">
-        <v>2437</v>
+        <v>2440</v>
       </c>
       <c r="C226" s="69" t="s">
-        <v>2570</v>
+        <v>2573</v>
       </c>
       <c r="D226" s="69" t="s">
-        <v>2571</v>
+        <v>2574</v>
       </c>
       <c r="E226" s="69"/>
       <c r="F226" s="69"/>
@@ -30796,10 +30847,10 @@
         <v>229</v>
       </c>
       <c r="C227" s="69" t="s">
-        <v>2596</v>
+        <v>2599</v>
       </c>
       <c r="D227" s="69" t="s">
-        <v>2597</v>
+        <v>2600</v>
       </c>
       <c r="E227" s="69"/>
       <c r="F227" s="69"/>
@@ -30815,10 +30866,10 @@
         <v>1248</v>
       </c>
       <c r="C228" s="8" t="s">
-        <v>2598</v>
+        <v>2601</v>
       </c>
       <c r="D228" s="8" t="s">
-        <v>2599</v>
+        <v>2602</v>
       </c>
       <c r="E228" s="69"/>
       <c r="F228" s="69"/>
@@ -30831,13 +30882,13 @@
         <v>1042</v>
       </c>
       <c r="B229" s="69" t="s">
-        <v>2600</v>
+        <v>2603</v>
       </c>
       <c r="C229" s="8" t="s">
-        <v>2601</v>
+        <v>2604</v>
       </c>
       <c r="D229" s="8" t="s">
-        <v>2602</v>
+        <v>2605</v>
       </c>
       <c r="E229" s="69"/>
       <c r="F229" s="69"/>
@@ -30852,13 +30903,13 @@
         <v>1042</v>
       </c>
       <c r="B230" s="69" t="s">
-        <v>2603</v>
+        <v>2606</v>
       </c>
       <c r="C230" s="8" t="s">
-        <v>2604</v>
+        <v>2607</v>
       </c>
       <c r="D230" s="8" t="s">
-        <v>2605</v>
+        <v>2608</v>
       </c>
       <c r="E230" s="69"/>
       <c r="F230" s="69"/>
@@ -30873,13 +30924,13 @@
         <v>1042</v>
       </c>
       <c r="B231" s="69" t="s">
-        <v>2606</v>
+        <v>2609</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>2607</v>
+        <v>2610</v>
       </c>
       <c r="D231" s="54" t="s">
-        <v>2608</v>
+        <v>2611</v>
       </c>
       <c r="E231" s="69"/>
       <c r="F231" s="69"/>
@@ -30894,13 +30945,13 @@
         <v>1042</v>
       </c>
       <c r="B232" s="69" t="s">
-        <v>2609</v>
+        <v>2612</v>
       </c>
       <c r="C232" s="8" t="s">
-        <v>2610</v>
+        <v>2613</v>
       </c>
       <c r="D232" s="51" t="s">
-        <v>2611</v>
+        <v>2614</v>
       </c>
       <c r="E232" s="69"/>
       <c r="F232" s="69"/>
@@ -30913,13 +30964,13 @@
         <v>1048</v>
       </c>
       <c r="B233" s="69" t="s">
-        <v>2612</v>
+        <v>2615</v>
       </c>
       <c r="C233" s="8" t="s">
-        <v>2613</v>
+        <v>2616</v>
       </c>
       <c r="D233" s="8" t="s">
-        <v>2614</v>
+        <v>2617</v>
       </c>
       <c r="E233" s="69"/>
       <c r="F233" s="69"/>
@@ -30934,13 +30985,13 @@
         <v>1048</v>
       </c>
       <c r="B234" s="69" t="s">
-        <v>2615</v>
+        <v>2618</v>
       </c>
       <c r="C234" s="8" t="s">
-        <v>2616</v>
+        <v>2619</v>
       </c>
       <c r="D234" s="8" t="s">
-        <v>2617</v>
+        <v>2620</v>
       </c>
       <c r="E234" s="69"/>
       <c r="F234" s="69"/>
@@ -30955,13 +31006,13 @@
         <v>1048</v>
       </c>
       <c r="B235" s="69" t="s">
-        <v>2618</v>
+        <v>2621</v>
       </c>
       <c r="C235" s="8" t="s">
-        <v>2619</v>
+        <v>2622</v>
       </c>
       <c r="D235" s="8" t="s">
-        <v>2620</v>
+        <v>2623</v>
       </c>
       <c r="E235" s="69"/>
       <c r="F235" s="69"/>
@@ -30971,16 +31022,16 @@
     </row>
     <row r="236" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="57" t="s">
-        <v>2621</v>
+        <v>2624</v>
       </c>
       <c r="B236" s="69" t="s">
         <v>1157</v>
       </c>
       <c r="C236" s="54" t="s">
-        <v>2622</v>
+        <v>2625</v>
       </c>
       <c r="D236" s="8" t="s">
-        <v>2623</v>
+        <v>2626</v>
       </c>
       <c r="E236" s="69"/>
       <c r="F236" s="69"/>
@@ -30990,16 +31041,16 @@
     </row>
     <row r="237" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="57" t="s">
-        <v>2621</v>
+        <v>2624</v>
       </c>
       <c r="B237" s="69" t="s">
         <v>1215</v>
       </c>
       <c r="C237" s="54" t="s">
-        <v>2624</v>
+        <v>2627</v>
       </c>
       <c r="D237" s="51" t="s">
-        <v>2625</v>
+        <v>2628</v>
       </c>
       <c r="E237" s="69"/>
       <c r="F237" s="69"/>
@@ -31012,13 +31063,13 @@
         <v>1078</v>
       </c>
       <c r="B238" s="69" t="s">
-        <v>2626</v>
+        <v>2629</v>
       </c>
       <c r="C238" s="8" t="s">
-        <v>2627</v>
+        <v>2630</v>
       </c>
       <c r="D238" s="54" t="s">
-        <v>2628</v>
+        <v>2631</v>
       </c>
       <c r="E238" s="69"/>
       <c r="F238" s="69"/>
@@ -31031,13 +31082,13 @@
         <v>1078</v>
       </c>
       <c r="B239" s="69" t="s">
-        <v>2629</v>
+        <v>2632</v>
       </c>
       <c r="C239" s="8" t="s">
-        <v>2630</v>
+        <v>2633</v>
       </c>
       <c r="D239" s="54" t="s">
-        <v>2631</v>
+        <v>2634</v>
       </c>
       <c r="E239" s="69"/>
       <c r="F239" s="69"/>
@@ -31050,13 +31101,13 @@
         <v>1078</v>
       </c>
       <c r="B240" s="69" t="s">
-        <v>2632</v>
+        <v>2635</v>
       </c>
       <c r="C240" s="8" t="s">
-        <v>2633</v>
+        <v>2636</v>
       </c>
       <c r="D240" s="54" t="s">
-        <v>2634</v>
+        <v>2637</v>
       </c>
       <c r="E240" s="69"/>
       <c r="F240" s="69"/>
@@ -31069,13 +31120,13 @@
         <v>1078</v>
       </c>
       <c r="B241" s="69" t="s">
-        <v>2635</v>
+        <v>2638</v>
       </c>
       <c r="C241" s="8" t="s">
-        <v>2636</v>
+        <v>2639</v>
       </c>
       <c r="D241" s="54" t="s">
-        <v>2637</v>
+        <v>2640</v>
       </c>
       <c r="E241" s="69"/>
       <c r="F241" s="69"/>
@@ -31088,13 +31139,13 @@
         <v>1078</v>
       </c>
       <c r="B242" s="69" t="s">
-        <v>2638</v>
+        <v>2641</v>
       </c>
       <c r="C242" s="8" t="s">
-        <v>2639</v>
+        <v>2642</v>
       </c>
       <c r="D242" s="54" t="s">
-        <v>2640</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="243" s="53" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31102,13 +31153,13 @@
         <v>1078</v>
       </c>
       <c r="B243" s="69" t="s">
-        <v>2641</v>
+        <v>2644</v>
       </c>
       <c r="C243" s="8" t="s">
-        <v>2642</v>
+        <v>2645</v>
       </c>
       <c r="D243" s="54" t="s">
-        <v>2643</v>
+        <v>2646</v>
       </c>
       <c r="E243" s="69"/>
       <c r="F243" s="69"/>
@@ -31126,7 +31177,7 @@
       <c r="E244" s="69"/>
       <c r="F244" s="69"/>
       <c r="G244" s="56" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
       <c r="H244" s="69"/>
       <c r="I244" s="69"/>
@@ -31136,13 +31187,13 @@
         <v>936</v>
       </c>
       <c r="B245" s="53" t="s">
-        <v>2644</v>
+        <v>2647</v>
       </c>
       <c r="C245" s="53" t="s">
-        <v>2645</v>
+        <v>2648</v>
       </c>
       <c r="D245" s="53" t="s">
-        <v>2646</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="246" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31150,13 +31201,13 @@
         <v>936</v>
       </c>
       <c r="B246" s="53" t="s">
-        <v>2558</v>
+        <v>2561</v>
       </c>
       <c r="C246" s="53" t="s">
-        <v>2647</v>
+        <v>2650</v>
       </c>
       <c r="D246" s="53" t="s">
-        <v>2648</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="247" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31164,13 +31215,13 @@
         <v>936</v>
       </c>
       <c r="B247" s="53" t="s">
-        <v>2649</v>
+        <v>2652</v>
       </c>
       <c r="C247" s="53" t="s">
-        <v>2650</v>
+        <v>2653</v>
       </c>
       <c r="D247" s="53" t="s">
-        <v>2651</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="248" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31178,13 +31229,13 @@
         <v>936</v>
       </c>
       <c r="B248" s="53" t="s">
-        <v>2652</v>
+        <v>2655</v>
       </c>
       <c r="C248" s="53" t="s">
-        <v>2653</v>
+        <v>2656</v>
       </c>
       <c r="D248" s="53" t="s">
-        <v>2654</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="249" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31192,13 +31243,13 @@
         <v>936</v>
       </c>
       <c r="B249" s="53" t="s">
-        <v>2655</v>
+        <v>2658</v>
       </c>
       <c r="C249" s="53" t="s">
-        <v>2656</v>
+        <v>2659</v>
       </c>
       <c r="D249" s="53" t="s">
-        <v>2657</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="250" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31209,10 +31260,10 @@
         <v>-2</v>
       </c>
       <c r="C250" s="60" t="s">
-        <v>2658</v>
+        <v>2661</v>
       </c>
       <c r="D250" s="60" t="s">
-        <v>2659</v>
+        <v>2662</v>
       </c>
       <c r="E250" s="69"/>
       <c r="F250" s="69"/>
@@ -31228,10 +31279,10 @@
         <v>-1</v>
       </c>
       <c r="C251" s="60" t="s">
-        <v>2660</v>
+        <v>2663</v>
       </c>
       <c r="D251" s="60" t="s">
-        <v>2661</v>
+        <v>2664</v>
       </c>
       <c r="E251" s="69"/>
       <c r="F251" s="69"/>
@@ -31247,10 +31298,10 @@
         <v>0</v>
       </c>
       <c r="C252" s="60" t="s">
-        <v>2662</v>
+        <v>2665</v>
       </c>
       <c r="D252" s="60" t="s">
-        <v>2663</v>
+        <v>2666</v>
       </c>
       <c r="E252" s="69"/>
       <c r="F252" s="69"/>
@@ -31266,10 +31317,10 @@
         <v>1</v>
       </c>
       <c r="C253" s="60" t="s">
-        <v>2664</v>
+        <v>2667</v>
       </c>
       <c r="D253" s="60" t="s">
-        <v>2665</v>
+        <v>2668</v>
       </c>
       <c r="E253" s="69"/>
       <c r="F253" s="69"/>
@@ -31285,10 +31336,10 @@
         <v>2</v>
       </c>
       <c r="C254" s="60" t="s">
-        <v>2666</v>
+        <v>2669</v>
       </c>
       <c r="D254" s="60" t="s">
-        <v>2667</v>
+        <v>2670</v>
       </c>
       <c r="E254" s="69"/>
       <c r="F254" s="69"/>
@@ -31304,10 +31355,10 @@
         <v>0</v>
       </c>
       <c r="C255" s="51" t="s">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="D255" s="60" t="s">
-        <v>2669</v>
+        <v>2672</v>
       </c>
       <c r="E255" s="69"/>
       <c r="F255" s="69"/>
@@ -31323,10 +31374,10 @@
         <v>1</v>
       </c>
       <c r="C256" s="51" t="s">
-        <v>2670</v>
+        <v>2673</v>
       </c>
       <c r="D256" s="54" t="s">
-        <v>2671</v>
+        <v>2674</v>
       </c>
       <c r="E256" s="69"/>
       <c r="F256" s="69"/>
@@ -31342,10 +31393,10 @@
         <v>2</v>
       </c>
       <c r="C257" s="51" t="s">
-        <v>2672</v>
+        <v>2675</v>
       </c>
       <c r="D257" s="54" t="s">
-        <v>2673</v>
+        <v>2676</v>
       </c>
       <c r="E257" s="69"/>
       <c r="F257" s="69"/>
@@ -31361,10 +31412,10 @@
         <v>3</v>
       </c>
       <c r="C258" s="51" t="s">
-        <v>2674</v>
+        <v>2677</v>
       </c>
       <c r="D258" s="54" t="s">
-        <v>2675</v>
+        <v>2678</v>
       </c>
       <c r="E258" s="69"/>
       <c r="F258" s="69"/>
@@ -31380,10 +31431,10 @@
         <v>4</v>
       </c>
       <c r="C259" s="51" t="s">
-        <v>2676</v>
+        <v>2679</v>
       </c>
       <c r="D259" s="54" t="s">
-        <v>2677</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31394,10 +31445,10 @@
         <v>-1</v>
       </c>
       <c r="C260" s="51" t="s">
-        <v>2678</v>
+        <v>2681</v>
       </c>
       <c r="D260" s="54" t="s">
-        <v>2679</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31405,13 +31456,13 @@
         <v>39</v>
       </c>
       <c r="B261" s="69" t="s">
-        <v>2680</v>
+        <v>2683</v>
       </c>
       <c r="C261" s="69" t="s">
-        <v>2681</v>
+        <v>2684</v>
       </c>
       <c r="D261" s="69" t="s">
-        <v>2682</v>
+        <v>2685</v>
       </c>
     </row>
   </sheetData>

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4896" uniqueCount="2686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4893" uniqueCount="2685">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -452,6 +452,9 @@
 overMaxAllowed</t>
   </si>
   <si>
+    <t xml:space="preserve">join_with=${householdTwoWheelNumber}</t>
+  </si>
+  <si>
     <t xml:space="preserve">carNumberValidation</t>
   </si>
   <si>
@@ -472,10 +475,46 @@
 __Also known as mopeds or motorized scooters__</t>
   </si>
   <si>
-    <t xml:space="preserve">zeroToTwoPlus</t>
+    <t xml:space="preserve">join_with=${householdBicycleNumber}</t>
   </si>
   <si>
     <t xml:space="preserve">twoWheelNumberHelpPopup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">householdBicycleNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">household.bicycleNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Vélo(s)** à la disposition de votre ménage 
+__Indiquer seulement les vélos des ados ou adultes dans un état utilisable, incluant les vélos à assistance électrique. Ne pas inclure les vélos pour enfants.__</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Bicycles** owned by household members
+__Include only bicycles belonging to teenagers or adults that are in usable condition, including electric-assist bicycles. Do not include children’s bicycles.__</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bicycleNumberValidation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">householdElectricBicycleNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">household.electricBicycleNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parmi ces vélos, combien sont des **vélos à assistance électrique**?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Among these bicycles, how many are **electric bicycles** (e-bikes)?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">min=0
+max=household.bicycleNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hasHouseholdBicycleConditional</t>
   </si>
   <si>
     <t xml:space="preserve">homeCarParkingsAvailableVehicleHousehold</t>
@@ -536,47 +575,6 @@
   </si>
   <si>
     <t xml:space="preserve">yesNoDontKnow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">householdBicycleNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">household.bicycleNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Vélo(s)** à la disposition de votre ménage 
-__Indiquer seulement les vélos des ados ou adultes dans un état utilisable, incluant les vélos à assistance électrique. Ne pas inclure les vélos pour enfants.__</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Bicycles** owned by household members
-__Include only bicycles belonging to teenagers or adults that are in usable condition, including electric-assist bicycles. Do not include children’s bicycles.__</t>
-  </si>
-  <si>
-    <t xml:space="preserve">min=0
-Max=2
-overMaxAllowed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bicycleNumberValidation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">householdElectricBicycleNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">household.electricBicycleNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parmi ces vélos, combien sont des **vélo(s) à assistance électrique**?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Among these bicycles, how many are **electric bicycles** (e-bikes)?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">min=0
-max=household.bicycleNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hasHouseholdBicycleConditional</t>
   </si>
   <si>
     <t xml:space="preserve">householdBikesharing</t>
@@ -8168,9 +8166,6 @@
   </si>
   <si>
     <t xml:space="preserve">Residential parking permit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2+</t>
   </si>
   <si>
     <t xml:space="preserve">Oui (mensuel, saison)</t>
@@ -9370,7 +9365,7 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9906,32 +9901,32 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:X227"/>
-  <sheetFormatPr defaultColWidth="9.18359375" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="6.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="6.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="39.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="42.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="31.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="20.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="22.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="19.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="13.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="39.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="42.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="31.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="20.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="22.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="19.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="13.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="13.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="13.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="14.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="14.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="10.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="15.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="11.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="19.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="14.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="14.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="20.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="21.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="17.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="19.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="35"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="25" style="3" width="9.18"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="25" style="3" width="9.16"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10008,7 +10003,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
@@ -10048,7 +10043,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>32</v>
       </c>
@@ -10081,7 +10076,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>40</v>
       </c>
@@ -10112,7 +10107,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="69.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>46</v>
       </c>
@@ -10143,7 +10138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="69.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
         <v>52</v>
       </c>
@@ -10189,7 +10184,7 @@
       <c r="W6" s="9"/>
       <c r="X6" s="9"/>
     </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>55</v>
       </c>
@@ -10220,7 +10215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>60</v>
       </c>
@@ -10254,7 +10249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>64</v>
       </c>
@@ -10285,7 +10280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>68</v>
       </c>
@@ -10313,7 +10308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>72</v>
       </c>
@@ -10341,7 +10336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>76</v>
       </c>
@@ -10409,7 +10404,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" s="14" customFormat="true" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" s="14" customFormat="true" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
         <v>88</v>
       </c>
@@ -10461,7 +10456,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>95</v>
       </c>
@@ -10495,7 +10490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="69.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>101</v>
       </c>
@@ -10561,23 +10556,26 @@
       <c r="K17" s="1" t="s">
         <v>114</v>
       </c>
+      <c r="L17" s="9" t="s">
+        <v>115</v>
+      </c>
       <c r="N17" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S17" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="18" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" s="14" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>47</v>
+        <v>118</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="C18" s="10" t="b">
         <f aca="false">TRUE()</f>
@@ -10588,25 +10586,27 @@
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
+      <c r="K18" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>122</v>
+      </c>
       <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9" t="s">
-        <v>121</v>
-      </c>
+      <c r="N18" s="1"/>
+      <c r="O18" s="9"/>
       <c r="P18" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
@@ -10620,112 +10620,83 @@
       <c r="W18" s="9"/>
       <c r="X18" s="9"/>
     </row>
-    <row r="19" s="14" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B19" s="9" t="s">
+    <row r="19" customFormat="false" ht="80.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="2" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="S19" s="1" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="2" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="S20" s="1" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" s="14" customFormat="true" ht="69.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="C19" s="10" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="9"/>
-      <c r="S19" s="9" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="T19" s="9"/>
-      <c r="U19" s="9"/>
-      <c r="V19" s="9"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="12" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="10" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="T20" s="9"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="9"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
-    </row>
-    <row r="21" s="14" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="C21" s="10" t="b">
         <f aca="false">TRUE()</f>
@@ -10736,23 +10707,25 @@
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="H21" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>139</v>
       </c>
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
+      <c r="K21" s="9" t="s">
+        <v>139</v>
+      </c>
       <c r="L21" s="9"/>
-      <c r="M21" s="1" t="s">
+      <c r="M21" s="9" t="s">
         <v>140</v>
       </c>
       <c r="N21" s="9"/>
-      <c r="O21" s="1" t="s">
+      <c r="O21" s="9" t="s">
         <v>141</v>
       </c>
       <c r="P21" s="9"/>
@@ -10766,57 +10739,74 @@
       <c r="U21" s="9"/>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
-      <c r="X21" s="9"/>
-    </row>
-    <row r="22" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="X21" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C22" s="2" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D22" s="1" t="s">
+    </row>
+    <row r="22" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="10" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>143</v>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="K22" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="N22" s="1" t="s">
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="S22" s="1" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="N22" s="9"/>
+      <c r="O22" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
+      <c r="S22" s="9" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="T22" s="9"/>
+      <c r="U22" s="9"/>
+      <c r="V22" s="9"/>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+    </row>
+    <row r="23" s="14" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C23" s="2" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D23" s="1" t="s">
+      <c r="B23" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="10" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="E23" s="9"/>
+      <c r="F23" s="9" t="s">
         <v>149</v>
       </c>
       <c r="G23" s="9" t="s">
@@ -10825,21 +10815,31 @@
       <c r="H23" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="N23" s="9"/>
+      <c r="O23" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="N23" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="S23" s="1" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+    </row>
+    <row r="24" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
         <v>154</v>
       </c>
@@ -10868,11 +10868,11 @@
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
       <c r="M24" s="1" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="N24" s="9"/>
       <c r="O24" s="1" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="P24" s="9"/>
       <c r="Q24" s="9"/>
@@ -10921,7 +10921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
         <v>164</v>
       </c>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="X26" s="18"/>
     </row>
-    <row r="27" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
         <v>168</v>
       </c>
@@ -11028,7 +11028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>176</v>
       </c>
@@ -11062,7 +11062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>182</v>
       </c>
@@ -11108,7 +11108,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="80.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>191</v>
       </c>
@@ -11138,14 +11138,14 @@
         <v>195</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="S31" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>196</v>
       </c>
@@ -11175,14 +11175,14 @@
         <v>200</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="S32" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="33" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
         <v>201</v>
       </c>
@@ -11217,7 +11217,7 @@
       </c>
       <c r="N33" s="9"/>
       <c r="O33" s="9" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="P33" s="9"/>
       <c r="Q33" s="9"/>
@@ -11232,7 +11232,7 @@
       <c r="W33" s="9"/>
       <c r="X33" s="9"/>
     </row>
-    <row r="34" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
         <v>206</v>
       </c>
@@ -11282,7 +11282,7 @@
       <c r="W34" s="9"/>
       <c r="X34" s="9"/>
     </row>
-    <row r="35" s="14" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" s="14" customFormat="true" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
         <v>211</v>
       </c>
@@ -11317,7 +11317,7 @@
       </c>
       <c r="N35" s="9"/>
       <c r="O35" s="9" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="P35" s="9"/>
       <c r="Q35" s="9"/>
@@ -11332,7 +11332,7 @@
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
     </row>
-    <row r="36" s="14" customFormat="true" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" s="14" customFormat="true" ht="92" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
         <v>215</v>
       </c>
@@ -11382,7 +11382,7 @@
       <c r="W36" s="9"/>
       <c r="X36" s="9"/>
     </row>
-    <row r="37" s="14" customFormat="true" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" s="14" customFormat="true" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
         <v>221</v>
       </c>
@@ -11440,7 +11440,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="126" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>231</v>
       </c>
@@ -11483,7 +11483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" s="14" customFormat="true" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" s="14" customFormat="true" ht="69.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
         <v>238</v>
       </c>
@@ -11537,7 +11537,7 @@
       <c r="W39" s="9"/>
       <c r="X39" s="9"/>
     </row>
-    <row r="40" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
         <v>245</v>
       </c>
@@ -11595,7 +11595,7 @@
       <c r="W40" s="9"/>
       <c r="X40" s="12"/>
     </row>
-    <row r="41" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
         <v>252</v>
       </c>
@@ -11644,7 +11644,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="42" s="14" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" s="14" customFormat="true" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>257</v>
       </c>
@@ -11706,7 +11706,7 @@
       <c r="W42" s="9"/>
       <c r="X42" s="12"/>
     </row>
-    <row r="43" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>265</v>
       </c>
@@ -11755,7 +11755,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="44" s="14" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" s="14" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>267</v>
       </c>
@@ -11809,7 +11809,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="45" s="14" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" s="14" customFormat="true" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
         <v>274</v>
       </c>
@@ -11865,7 +11865,7 @@
       <c r="W45" s="9"/>
       <c r="X45" s="9"/>
     </row>
-    <row r="46" s="14" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" s="14" customFormat="true" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
         <v>280</v>
       </c>
@@ -11921,7 +11921,7 @@
       <c r="W46" s="9"/>
       <c r="X46" s="9"/>
     </row>
-    <row r="47" s="14" customFormat="true" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" s="14" customFormat="true" ht="103.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
         <v>288</v>
       </c>
@@ -11977,7 +11977,7 @@
       <c r="W47" s="9"/>
       <c r="X47" s="9"/>
     </row>
-    <row r="48" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
         <v>295</v>
       </c>
@@ -12029,7 +12029,7 @@
       <c r="W48" s="9"/>
       <c r="X48" s="9"/>
     </row>
-    <row r="49" s="14" customFormat="true" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" s="14" customFormat="true" ht="69.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
         <v>301</v>
       </c>
@@ -12081,7 +12081,7 @@
       <c r="W49" s="9"/>
       <c r="X49" s="9"/>
     </row>
-    <row r="50" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
         <v>308</v>
       </c>
@@ -12135,7 +12135,7 @@
       <c r="W50" s="9"/>
       <c r="X50" s="9"/>
     </row>
-    <row r="51" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" s="14" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
         <v>316</v>
       </c>
@@ -12189,7 +12189,7 @@
       <c r="W51" s="9"/>
       <c r="X51" s="9"/>
     </row>
-    <row r="52" s="14" customFormat="true" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" s="14" customFormat="true" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="s">
         <v>323</v>
       </c>
@@ -12243,7 +12243,7 @@
       <c r="W52" s="9"/>
       <c r="X52" s="9"/>
     </row>
-    <row r="53" s="14" customFormat="true" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" s="14" customFormat="true" ht="80.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="s">
         <v>331</v>
       </c>
@@ -12299,7 +12299,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="s">
         <v>340</v>
       </c>
@@ -12351,7 +12351,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="55" s="14" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" s="14" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="s">
         <v>346</v>
       </c>
@@ -12401,7 +12401,7 @@
       <c r="W55" s="9"/>
       <c r="X55" s="9"/>
     </row>
-    <row r="56" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
         <v>351</v>
       </c>
@@ -12447,7 +12447,7 @@
       <c r="V56" s="4"/>
       <c r="W56" s="4"/>
     </row>
-    <row r="57" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="19" t="s">
         <v>353</v>
       </c>
@@ -12488,7 +12488,7 @@
       <c r="W57" s="25"/>
       <c r="X57" s="19"/>
     </row>
-    <row r="58" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="18" t="s">
         <v>357</v>
       </c>
@@ -12529,7 +12529,7 @@
       <c r="W58" s="17"/>
       <c r="X58" s="18"/>
     </row>
-    <row r="59" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="19" t="s">
         <v>360</v>
       </c>
@@ -12575,7 +12575,7 @@
       <c r="W59" s="25"/>
       <c r="X59" s="19"/>
     </row>
-    <row r="60" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
         <v>365</v>
       </c>
@@ -12615,7 +12615,7 @@
       <c r="V60" s="4"/>
       <c r="W60" s="4"/>
     </row>
-    <row r="61" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="171.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
         <v>368</v>
       </c>
@@ -12661,7 +12661,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
         <v>373</v>
       </c>
@@ -12708,7 +12708,7 @@
       <c r="V62" s="4"/>
       <c r="W62" s="4"/>
     </row>
-    <row r="63" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
         <v>379</v>
       </c>
@@ -12764,7 +12764,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="80.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
         <v>388</v>
       </c>
@@ -12817,7 +12817,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="382.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="375.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>398</v>
       </c>
@@ -12871,7 +12871,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="114.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
         <v>406</v>
       </c>
@@ -12920,7 +12920,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="80.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
         <v>416</v>
       </c>
@@ -12960,7 +12960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" s="14" customFormat="true" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" s="14" customFormat="true" ht="69.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="9" t="s">
         <v>424</v>
       </c>
@@ -13013,7 +13013,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="69" s="14" customFormat="true" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" s="14" customFormat="true" ht="80.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="9" t="s">
         <v>434</v>
       </c>
@@ -13062,7 +13062,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="70" s="31" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" s="31" customFormat="true" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
         <v>442</v>
       </c>
@@ -13103,7 +13103,7 @@
       <c r="W70" s="4"/>
       <c r="X70" s="4"/>
     </row>
-    <row r="71" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="18" t="s">
         <v>446</v>
       </c>
@@ -13147,7 +13147,7 @@
       <c r="W71" s="18"/>
       <c r="X71" s="18"/>
     </row>
-    <row r="72" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="19" t="s">
         <v>360</v>
       </c>
@@ -13193,7 +13193,7 @@
       <c r="W72" s="19"/>
       <c r="X72" s="19"/>
     </row>
-    <row r="73" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>365</v>
       </c>
@@ -13217,14 +13217,14 @@
         <v>367</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
         <v>450</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="C74" s="2" t="n">
+      <c r="C74" s="2" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -13258,7 +13258,7 @@
       <c r="B75" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="C75" s="2" t="n">
+      <c r="C75" s="2" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -13299,7 +13299,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
         <v>463</v>
       </c>
@@ -13353,7 +13353,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
         <v>471</v>
       </c>
@@ -13439,7 +13439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
         <v>484</v>
       </c>
@@ -13466,7 +13466,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
         <v>488</v>
       </c>
@@ -13493,7 +13493,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="80.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
         <v>492</v>
       </c>
@@ -13520,7 +13520,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
         <v>496</v>
       </c>
@@ -13553,7 +13553,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="69.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
         <v>502</v>
       </c>
@@ -13586,7 +13586,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
         <v>508</v>
       </c>
@@ -13619,7 +13619,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
         <v>514</v>
       </c>
@@ -13655,7 +13655,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="114.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
         <v>521</v>
       </c>
@@ -13688,7 +13688,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
         <v>527</v>
       </c>
@@ -13863,7 +13863,7 @@
       <c r="W94" s="17"/>
       <c r="X94" s="17"/>
     </row>
-    <row r="95" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="19" t="s">
         <v>360</v>
       </c>
@@ -13901,7 +13901,7 @@
       <c r="W95" s="19"/>
       <c r="X95" s="19"/>
     </row>
-    <row r="96" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
         <v>365</v>
       </c>
@@ -14019,7 +14019,7 @@
       <c r="K99" s="28"/>
       <c r="S99" s="28"/>
     </row>
-    <row r="100" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
         <v>561</v>
       </c>
@@ -14081,7 +14081,7 @@
       <c r="K101" s="28"/>
       <c r="S101" s="28"/>
     </row>
-    <row r="102" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
         <v>567</v>
       </c>
@@ -14158,7 +14158,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
         <v>576</v>
       </c>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="X105" s="12"/>
     </row>
-    <row r="106" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
         <v>583</v>
       </c>
@@ -14265,7 +14265,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="108" s="14" customFormat="true" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" s="14" customFormat="true" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
         <v>594</v>
       </c>
@@ -14315,7 +14315,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="109" s="14" customFormat="true" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" s="14" customFormat="true" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
         <v>600</v>
       </c>
@@ -14365,7 +14365,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="110" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" s="14" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
         <v>604</v>
       </c>
@@ -14415,7 +14415,7 @@
       <c r="W110" s="1"/>
       <c r="X110" s="38"/>
     </row>
-    <row r="111" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" s="14" customFormat="true" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="9" t="s">
         <v>610</v>
       </c>
@@ -14465,7 +14465,7 @@
       <c r="W111" s="9"/>
       <c r="X111" s="9"/>
     </row>
-    <row r="112" s="14" customFormat="true" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" s="14" customFormat="true" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="9" t="s">
         <v>616</v>
       </c>
@@ -14515,7 +14515,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="113" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" s="14" customFormat="true" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="9" t="s">
         <v>621</v>
       </c>
@@ -14567,7 +14567,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="114" s="14" customFormat="true" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" s="14" customFormat="true" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="9" t="s">
         <v>627</v>
       </c>
@@ -14617,7 +14617,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="115" s="14" customFormat="true" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" s="14" customFormat="true" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="9" t="s">
         <v>631</v>
       </c>
@@ -14667,7 +14667,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="116" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="9" t="s">
         <v>634</v>
       </c>
@@ -14719,7 +14719,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="117" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" s="14" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="9" t="s">
         <v>641</v>
       </c>
@@ -14771,7 +14771,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="118" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" s="14" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="9" t="s">
         <v>648</v>
       </c>
@@ -14823,7 +14823,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="119" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" s="14" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="9" t="s">
         <v>653</v>
       </c>
@@ -14875,7 +14875,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="120" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" s="14" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="9" t="s">
         <v>659</v>
       </c>
@@ -14927,7 +14927,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="121" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" s="14" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="9" t="s">
         <v>665</v>
       </c>
@@ -15015,7 +15015,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
         <v>675</v>
       </c>
@@ -15048,7 +15048,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
         <v>680</v>
       </c>
@@ -15091,7 +15091,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
         <v>688</v>
       </c>
@@ -15134,7 +15134,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="103.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
         <v>694</v>
       </c>
@@ -15179,7 +15179,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
         <v>701</v>
       </c>
@@ -15222,7 +15222,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="128" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="9" t="s">
         <v>706</v>
       </c>
@@ -15274,7 +15274,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="129" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="9" t="s">
         <v>714</v>
       </c>
@@ -15378,7 +15378,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
         <v>726</v>
       </c>
@@ -15405,7 +15405,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="132" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" s="14" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
         <v>730</v>
       </c>
@@ -15545,7 +15545,7 @@
       <c r="W134" s="17"/>
       <c r="X134" s="17"/>
     </row>
-    <row r="135" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="19" t="s">
         <v>360</v>
       </c>
@@ -15583,7 +15583,7 @@
       <c r="W135" s="19"/>
       <c r="X135" s="19"/>
     </row>
-    <row r="136" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
         <v>365</v>
       </c>
@@ -15607,7 +15607,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="80.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
         <v>745</v>
       </c>
@@ -15650,7 +15650,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="80.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
         <v>754</v>
       </c>
@@ -15683,7 +15683,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="139" s="14" customFormat="true" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" s="14" customFormat="true" ht="80.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="9" t="s">
         <v>760</v>
       </c>
@@ -15730,7 +15730,7 @@
       <c r="W139" s="9"/>
       <c r="X139" s="12"/>
     </row>
-    <row r="140" s="14" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" s="14" customFormat="true" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="9" t="s">
         <v>767</v>
       </c>
@@ -15780,7 +15780,7 @@
       <c r="W140" s="9"/>
       <c r="X140" s="12"/>
     </row>
-    <row r="141" s="14" customFormat="true" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" s="14" customFormat="true" ht="80.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="9" t="s">
         <v>773</v>
       </c>
@@ -15828,7 +15828,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="142" s="14" customFormat="true" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" s="14" customFormat="true" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="9" t="s">
         <v>776</v>
       </c>
@@ -15886,7 +15886,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="80.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
         <v>786</v>
       </c>
@@ -15929,7 +15929,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="144" s="14" customFormat="true" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" s="14" customFormat="true" ht="69.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="9" t="s">
         <v>794</v>
       </c>
@@ -15985,7 +15985,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="145" s="14" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" s="14" customFormat="true" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="9" t="s">
         <v>802</v>
       </c>
@@ -16035,7 +16035,7 @@
       <c r="W145" s="9"/>
       <c r="X145" s="9"/>
     </row>
-    <row r="146" s="14" customFormat="true" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" s="14" customFormat="true" ht="80.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="9" t="s">
         <v>809</v>
       </c>
@@ -16083,7 +16083,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="80.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
         <v>812</v>
       </c>
@@ -16125,7 +16125,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="148" s="31" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" s="31" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="17" t="s">
         <v>820</v>
       </c>
@@ -16166,7 +16166,7 @@
       <c r="W148" s="17"/>
       <c r="X148" s="17"/>
     </row>
-    <row r="149" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="69.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="19" t="s">
         <v>822</v>
       </c>
@@ -16378,7 +16378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="171.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
         <v>857</v>
       </c>
@@ -16414,7 +16414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
         <v>863</v>
       </c>
@@ -16444,7 +16444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
         <v>868</v>
       </c>
@@ -16553,7 +16553,7 @@
       <c r="W158" s="4"/>
       <c r="X158" s="4"/>
     </row>
-    <row r="159" s="40" customFormat="true" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" s="40" customFormat="true" ht="80.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="19" t="s">
         <v>879</v>
       </c>
@@ -16588,7 +16588,7 @@
       <c r="M159" s="19"/>
       <c r="N159" s="19"/>
       <c r="O159" s="19" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="P159" s="19"/>
       <c r="Q159" s="19"/>
@@ -16603,7 +16603,7 @@
       <c r="W159" s="19"/>
       <c r="X159" s="19"/>
     </row>
-    <row r="160" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
         <v>886</v>
       </c>
@@ -16631,7 +16631,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
         <v>888</v>
       </c>
@@ -16672,7 +16672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
         <v>896</v>
       </c>
@@ -16713,7 +16713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
         <v>902</v>
       </c>
@@ -16754,7 +16754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
         <v>908</v>
       </c>
@@ -16788,7 +16788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
         <v>912</v>
       </c>
@@ -16822,7 +16822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" s="31" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" s="31" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="4" t="s">
         <v>917</v>
       </c>
@@ -16863,7 +16863,7 @@
       <c r="W166" s="4"/>
       <c r="X166" s="4"/>
     </row>
-    <row r="167" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="69.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="19" t="s">
         <v>918</v>
       </c>
@@ -16907,7 +16907,7 @@
       <c r="W167" s="19"/>
       <c r="X167" s="19"/>
     </row>
-    <row r="168" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
         <v>919</v>
       </c>
@@ -16937,7 +16937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" s="31" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" s="31" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="17" t="s">
         <v>926</v>
       </c>
@@ -16978,7 +16978,7 @@
       <c r="W169" s="17"/>
       <c r="X169" s="17"/>
     </row>
-    <row r="170" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="92" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="19" t="s">
         <v>927</v>
       </c>
@@ -17022,7 +17022,7 @@
       <c r="W170" s="19"/>
       <c r="X170" s="19"/>
     </row>
-    <row r="171" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
         <v>932</v>
       </c>
@@ -17056,7 +17056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
         <v>937</v>
       </c>
@@ -17090,7 +17090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
         <v>941</v>
       </c>
@@ -17124,7 +17124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" s="14" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
         <v>945</v>
       </c>
@@ -17138,6 +17138,7 @@
       <c r="D174" s="1" t="s">
         <v>928</v>
       </c>
+      <c r="E174" s="1"/>
       <c r="F174" s="1" t="s">
         <v>946</v>
       </c>
@@ -17147,18 +17148,31 @@
       <c r="H174" s="1" t="s">
         <v>948</v>
       </c>
+      <c r="I174" s="1"/>
+      <c r="J174" s="1"/>
+      <c r="K174" s="1"/>
+      <c r="L174" s="1"/>
+      <c r="M174" s="1"/>
       <c r="N174" s="1" t="s">
         <v>237</v>
       </c>
       <c r="O174" s="1" t="s">
         <v>936</v>
       </c>
+      <c r="P174" s="1"/>
+      <c r="Q174" s="1"/>
+      <c r="R174" s="1"/>
       <c r="S174" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="175" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T174" s="1"/>
+      <c r="U174" s="1"/>
+      <c r="V174" s="1"/>
+      <c r="W174" s="1"/>
+      <c r="X174" s="1"/>
+    </row>
+    <row r="175" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
         <v>949</v>
       </c>
@@ -17172,6 +17186,7 @@
       <c r="D175" s="1" t="s">
         <v>928</v>
       </c>
+      <c r="E175" s="1"/>
       <c r="F175" s="1" t="s">
         <v>950</v>
       </c>
@@ -17181,6 +17196,10 @@
       <c r="H175" s="1" t="s">
         <v>952</v>
       </c>
+      <c r="I175" s="1"/>
+      <c r="J175" s="1"/>
+      <c r="K175" s="1"/>
+      <c r="L175" s="1"/>
       <c r="M175" s="1" t="s">
         <v>953</v>
       </c>
@@ -17190,12 +17209,20 @@
       <c r="O175" s="1" t="s">
         <v>936</v>
       </c>
+      <c r="P175" s="1"/>
+      <c r="Q175" s="1"/>
+      <c r="R175" s="1"/>
       <c r="S175" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="176" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T175" s="1"/>
+      <c r="U175" s="1"/>
+      <c r="V175" s="1"/>
+      <c r="W175" s="1"/>
+      <c r="X175" s="1"/>
+    </row>
+    <row r="176" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="18" t="s">
         <v>954</v>
       </c>
@@ -17236,7 +17263,7 @@
       <c r="W176" s="18"/>
       <c r="X176" s="18"/>
     </row>
-    <row r="177" s="14" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" s="14" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="43" t="s">
         <v>955</v>
       </c>
@@ -17280,7 +17307,7 @@
       <c r="W177" s="43"/>
       <c r="X177" s="43"/>
     </row>
-    <row r="178" s="14" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" s="14" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="9" t="s">
         <v>960</v>
       </c>
@@ -17328,7 +17355,7 @@
       <c r="W178" s="9"/>
       <c r="X178" s="9"/>
     </row>
-    <row r="179" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" s="14" customFormat="true" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="9" t="s">
         <v>965</v>
       </c>
@@ -17376,7 +17403,7 @@
       <c r="W179" s="9"/>
       <c r="X179" s="9"/>
     </row>
-    <row r="180" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="9" t="s">
         <v>969</v>
       </c>
@@ -17424,7 +17451,7 @@
       <c r="W180" s="9"/>
       <c r="X180" s="9"/>
     </row>
-    <row r="181" s="14" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" s="14" customFormat="true" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="9" t="s">
         <v>973</v>
       </c>
@@ -17472,7 +17499,7 @@
       <c r="W181" s="9"/>
       <c r="X181" s="9"/>
     </row>
-    <row r="182" s="14" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" s="31" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="9" t="s">
         <v>977</v>
       </c>
@@ -17520,7 +17547,7 @@
       <c r="W182" s="9"/>
       <c r="X182" s="9"/>
     </row>
-    <row r="183" s="14" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" s="14" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="9" t="s">
         <v>981</v>
       </c>
@@ -17568,7 +17595,7 @@
       <c r="W183" s="9"/>
       <c r="X183" s="9"/>
     </row>
-    <row r="184" s="14" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" s="14" customFormat="true" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="9" t="s">
         <v>985</v>
       </c>
@@ -17616,7 +17643,7 @@
       <c r="W184" s="9"/>
       <c r="X184" s="9"/>
     </row>
-    <row r="185" s="31" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="17" t="s">
         <v>989</v>
       </c>
@@ -17657,7 +17684,7 @@
       <c r="W185" s="17"/>
       <c r="X185" s="17"/>
     </row>
-    <row r="186" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="43" t="s">
         <v>990</v>
       </c>
@@ -17705,7 +17732,7 @@
       <c r="W186" s="43"/>
       <c r="X186" s="43"/>
     </row>
-    <row r="187" s="14" customFormat="true" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" s="14" customFormat="true" ht="80.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="9" t="s">
         <v>996</v>
       </c>
@@ -17751,7 +17778,7 @@
       <c r="W187" s="9"/>
       <c r="X187" s="9"/>
     </row>
-    <row r="188" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="9" t="s">
         <v>999</v>
       </c>
@@ -17801,7 +17828,7 @@
       <c r="W188" s="9"/>
       <c r="X188" s="9"/>
     </row>
-    <row r="189" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="9" t="s">
         <v>1003</v>
       </c>
@@ -17851,7 +17878,7 @@
       <c r="W189" s="9"/>
       <c r="X189" s="9"/>
     </row>
-    <row r="190" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" s="14" customFormat="true" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="9" t="s">
         <v>1006</v>
       </c>
@@ -17901,7 +17928,7 @@
       <c r="W190" s="9"/>
       <c r="X190" s="9"/>
     </row>
-    <row r="191" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="9" t="s">
         <v>1009</v>
       </c>
@@ -17951,7 +17978,7 @@
       <c r="W191" s="9"/>
       <c r="X191" s="9"/>
     </row>
-    <row r="192" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="9" t="s">
         <v>1012</v>
       </c>
@@ -18001,7 +18028,7 @@
       <c r="W192" s="9"/>
       <c r="X192" s="9"/>
     </row>
-    <row r="193" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="9" t="s">
         <v>1015</v>
       </c>
@@ -18051,7 +18078,7 @@
       <c r="W193" s="9"/>
       <c r="X193" s="9"/>
     </row>
-    <row r="194" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="9" t="s">
         <v>1018</v>
       </c>
@@ -18101,7 +18128,7 @@
       <c r="W194" s="9"/>
       <c r="X194" s="9"/>
     </row>
-    <row r="195" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="9" t="s">
         <v>1021</v>
       </c>
@@ -18145,7 +18172,7 @@
       <c r="W195" s="9"/>
       <c r="X195" s="9"/>
     </row>
-    <row r="196" s="14" customFormat="true" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" s="14" customFormat="true" ht="80.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="9" t="s">
         <v>1024</v>
       </c>
@@ -18192,7 +18219,7 @@
       <c r="W196" s="9"/>
       <c r="X196" s="9"/>
     </row>
-    <row r="197" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="9" t="s">
         <v>1027</v>
       </c>
@@ -18242,7 +18269,7 @@
       <c r="W197" s="9"/>
       <c r="X197" s="9"/>
     </row>
-    <row r="198" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="9" t="s">
         <v>1028</v>
       </c>
@@ -18292,7 +18319,7 @@
       <c r="W198" s="9"/>
       <c r="X198" s="9"/>
     </row>
-    <row r="199" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" s="14" customFormat="true" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="9" t="s">
         <v>1030</v>
       </c>
@@ -18342,7 +18369,7 @@
       <c r="W199" s="9"/>
       <c r="X199" s="9"/>
     </row>
-    <row r="200" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="9" t="s">
         <v>1031</v>
       </c>
@@ -18392,7 +18419,7 @@
       <c r="W200" s="9"/>
       <c r="X200" s="9"/>
     </row>
-    <row r="201" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="9" t="s">
         <v>1032</v>
       </c>
@@ -18442,7 +18469,7 @@
       <c r="W201" s="9"/>
       <c r="X201" s="9"/>
     </row>
-    <row r="202" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="9" t="s">
         <v>1033</v>
       </c>
@@ -18492,7 +18519,7 @@
       <c r="W202" s="9"/>
       <c r="X202" s="9"/>
     </row>
-    <row r="203" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" s="31" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="9" t="s">
         <v>1034</v>
       </c>
@@ -18542,7 +18569,7 @@
       <c r="W203" s="9"/>
       <c r="X203" s="9"/>
     </row>
-    <row r="204" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="9" t="s">
         <v>1037</v>
       </c>
@@ -18592,7 +18619,7 @@
       <c r="W204" s="9"/>
       <c r="X204" s="9"/>
     </row>
-    <row r="205" s="14" customFormat="true" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" s="14" customFormat="true" ht="69.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="9" t="s">
         <v>1038</v>
       </c>
@@ -18642,7 +18669,7 @@
       <c r="W205" s="9"/>
       <c r="X205" s="9"/>
     </row>
-    <row r="206" s="31" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" s="14" customFormat="true" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="17" t="s">
         <v>1041</v>
       </c>
@@ -18683,7 +18710,7 @@
       <c r="W206" s="17"/>
       <c r="X206" s="17"/>
     </row>
-    <row r="207" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" s="14" customFormat="true" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="43" t="s">
         <v>1042</v>
       </c>
@@ -18732,7 +18759,7 @@
       <c r="W207" s="43"/>
       <c r="X207" s="43"/>
     </row>
-    <row r="208" s="14" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" s="14" customFormat="true" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="9" t="s">
         <v>1048</v>
       </c>
@@ -18781,7 +18808,7 @@
       <c r="W208" s="9"/>
       <c r="X208" s="9"/>
     </row>
-    <row r="209" s="14" customFormat="true" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" s="14" customFormat="true" ht="92" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="9" t="s">
         <v>1053</v>
       </c>
@@ -18830,7 +18857,7 @@
       <c r="W209" s="9"/>
       <c r="X209" s="9"/>
     </row>
-    <row r="210" s="14" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" s="14" customFormat="true" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="9" t="s">
         <v>1060</v>
       </c>
@@ -18879,7 +18906,7 @@
       <c r="W210" s="9"/>
       <c r="X210" s="9"/>
     </row>
-    <row r="211" s="14" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="9" t="s">
         <v>1065</v>
       </c>
@@ -18917,7 +18944,6 @@
       <c r="P211" s="9" t="s">
         <v>1070</v>
       </c>
-      <c r="Q211" s="1"/>
       <c r="R211" s="9"/>
       <c r="S211" s="9" t="n">
         <v>1</v>
@@ -18928,7 +18954,7 @@
       <c r="W211" s="9"/>
       <c r="X211" s="9"/>
     </row>
-    <row r="212" s="14" customFormat="true" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="114.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="9" t="s">
         <v>1071</v>
       </c>
@@ -18975,12 +19001,11 @@
         <v>1</v>
       </c>
       <c r="T212" s="9"/>
-      <c r="U212" s="1"/>
       <c r="V212" s="9"/>
       <c r="W212" s="9"/>
       <c r="X212" s="9"/>
     </row>
-    <row r="213" s="14" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="9" t="s">
         <v>1078</v>
       </c>
@@ -19027,12 +19052,11 @@
         <v>1</v>
       </c>
       <c r="T213" s="9"/>
-      <c r="U213" s="1"/>
       <c r="V213" s="9"/>
       <c r="W213" s="9"/>
       <c r="X213" s="9"/>
     </row>
-    <row r="214" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="1" t="s">
         <v>1084</v>
       </c>
@@ -19066,7 +19090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="1" t="s">
         <v>1088</v>
       </c>
@@ -19100,7 +19124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="1" t="s">
         <v>1093</v>
       </c>
@@ -19131,7 +19155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="1" t="s">
         <v>1098</v>
       </c>
@@ -19161,7 +19185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="1" t="s">
         <v>1103</v>
       </c>
@@ -19198,7 +19222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="s">
         <v>1110</v>
       </c>
@@ -19232,7 +19256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="1" t="s">
         <v>1114</v>
       </c>
@@ -19269,7 +19293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="s">
         <v>1119</v>
       </c>
@@ -19306,7 +19330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="46.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="1" t="s">
         <v>1124</v>
       </c>
@@ -19343,7 +19367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
         <v>1129</v>
       </c>
@@ -19373,14 +19397,14 @@
         <v>237</v>
       </c>
       <c r="O223" s="1" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="S223" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="18" t="s">
         <v>1133</v>
       </c>
@@ -19421,7 +19445,7 @@
       <c r="W224" s="18"/>
       <c r="X224" s="18"/>
     </row>
-    <row r="225" customFormat="false" ht="344" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="352.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="1" t="s">
         <v>1136</v>
       </c>
@@ -19449,7 +19473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="s">
         <v>1140</v>
       </c>
@@ -19473,7 +19497,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="69.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="s">
         <v>1143</v>
       </c>
@@ -19513,12 +19537,12 @@
       <formula>NOT(ISERROR(SEARCH("TRUE",C225)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C214:C1048576 C7:C32 C49 C56:C67 C70:C76 C122:C127 C131 C133:C138 C143 C147:C176 C185 C206 C1:C5 C80:C107">
+  <conditionalFormatting sqref="C214:C1048576 C1:C5 C49 C56:C67 C70:C76 C80:C107 C122:C127 C131 C133:C138 C143 C147:C176 C185 C206 C7:C32">
     <cfRule type="containsText" priority="4" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="FALSE" dxfId="9">
       <formula>NOT(ISERROR(SEARCH("FALSE",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C49 C56:C67 C70:C76 C185 C206 C214:C224 C228:C1048576 C1:C32 C80:C107 C111:C131 C133:C176">
+  <conditionalFormatting sqref="C49 C56:C67 C70:C76 C80:C107 C111:C131 C133:C176 C185 C206 C214:C224 C228:C1048576 C1:C32">
     <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>1</formula>
     </cfRule>
@@ -19541,7 +19565,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C6 C128:C130 C139:C142 C144:C146 C111:C121">
+  <conditionalFormatting sqref="C6 C111:C121 C128:C130 C139:C142 C144:C146">
     <cfRule type="containsText" priority="10" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="FALSE" dxfId="15">
       <formula>NOT(ISERROR(SEARCH("FALSE",C6)))</formula>
     </cfRule>
@@ -19572,7 +19596,7 @@
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="X13" r:id="rId1" display="FIXME home_geography : territoryValidation · Issue #8 · chairemobilite/od_mtl"/>
-    <hyperlink ref="X19" r:id="rId2" display="Custom label because of the car number plural&#10;home_carParkingsAvailableVehicleHousehold : label · Issue #7 · chairemobilite/od_mtl"/>
+    <hyperlink ref="X21" r:id="rId2" display="Custom label because of the car number plural&#10;home_carParkingsAvailableVehicleHousehold : label · Issue #7 · chairemobilite/od_mtl"/>
     <hyperlink ref="X37" r:id="rId3" display="personTransitFare : transitFareValidation · Issue #10 · chairemobilite/od_mtl"/>
     <hyperlink ref="X44" r:id="rId4" display="personMostUsedMobilityAssistiveDevice : mostMobilityAssistiveDeviceCustomConditional · Issue #42 · chairemobilite/od_mtl&#10;personMostUsedMobilityAssistiveDevice : mostMobilityAssistiveDeviceCustomChoices · Issue #48 · chairemobilite/od_mtl"/>
     <hyperlink ref="X68" r:id="rId5" display="Custom choices because it has the departure place type in the labels&#10;&#10;FIXME: personOutOfTerritory : implication · Issue #45 · chairemobilite/od_mtl"/>
@@ -19610,20 +19634,20 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H148"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="27.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="15.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="27.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="15.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="46" width="20.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="8" width="19.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="12.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="23.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="13.27"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="8" width="8.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="46" width="20.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="8" width="19.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="12.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="23.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="13.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="8" width="8.5"/>
   </cols>
   <sheetData>
-    <row r="1" s="51" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="51" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="47" t="s">
         <v>1146</v>
       </c>
@@ -19649,7 +19673,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
         <v>1152</v>
       </c>
@@ -19663,7 +19687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
         <v>162</v>
       </c>
@@ -19677,7 +19701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
         <v>1155</v>
       </c>
@@ -19691,7 +19715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
         <v>1156</v>
       </c>
@@ -19705,7 +19729,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
         <v>244</v>
       </c>
@@ -19719,7 +19743,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
         <v>244</v>
       </c>
@@ -19736,12 +19760,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="D8" s="46" t="s">
         <v>1154</v>
@@ -19750,7 +19774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="21.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="21.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="52" t="s">
         <v>1159</v>
       </c>
@@ -19764,7 +19788,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
         <v>1162</v>
       </c>
@@ -19778,7 +19802,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
         <v>1162</v>
       </c>
@@ -19795,7 +19819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
         <v>1166</v>
       </c>
@@ -19809,7 +19833,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
         <v>1166</v>
       </c>
@@ -19826,7 +19850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
         <v>1167</v>
       </c>
@@ -19840,7 +19864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
         <v>1167</v>
       </c>
@@ -19857,7 +19881,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
         <v>1168</v>
       </c>
@@ -19871,7 +19895,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
         <v>186</v>
       </c>
@@ -19885,7 +19909,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
         <v>1169</v>
       </c>
@@ -19899,7 +19923,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
         <v>1170</v>
       </c>
@@ -19913,7 +19937,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
         <v>305</v>
       </c>
@@ -19927,7 +19951,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
         <v>1171</v>
       </c>
@@ -19941,7 +19965,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
         <v>1171</v>
       </c>
@@ -19958,7 +19982,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
         <v>1174</v>
       </c>
@@ -19972,7 +19996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
         <v>195</v>
       </c>
@@ -19986,7 +20010,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
         <v>1175</v>
       </c>
@@ -20000,7 +20024,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
         <v>1175</v>
       </c>
@@ -20017,7 +20041,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="27" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
         <v>1176</v>
       </c>
@@ -20035,7 +20059,7 @@
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
     </row>
-    <row r="28" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="54" t="s">
         <v>1177</v>
       </c>
@@ -20052,7 +20076,7 @@
       <c r="F28" s="54"/>
       <c r="G28" s="8"/>
     </row>
-    <row r="29" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="54" t="s">
         <v>1178</v>
       </c>
@@ -20069,7 +20093,7 @@
       <c r="F29" s="54"/>
       <c r="G29" s="8"/>
     </row>
-    <row r="30" s="53" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
         <v>953</v>
       </c>
@@ -20087,7 +20111,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
         <v>314</v>
       </c>
@@ -20101,7 +20125,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
         <v>314</v>
       </c>
@@ -20118,7 +20142,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
         <v>314</v>
       </c>
@@ -20135,7 +20159,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="34" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
         <v>1184</v>
       </c>
@@ -20153,7 +20177,7 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
     </row>
-    <row r="35" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
         <v>1184</v>
       </c>
@@ -20170,7 +20194,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
         <v>1184</v>
       </c>
@@ -20187,7 +20211,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
         <v>1187</v>
       </c>
@@ -20201,7 +20225,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
         <v>1187</v>
       </c>
@@ -20218,7 +20242,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
         <v>1187</v>
       </c>
@@ -20235,7 +20259,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
         <v>1187</v>
       </c>
@@ -20252,7 +20276,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
         <v>1187</v>
       </c>
@@ -20269,7 +20293,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
         <v>1187</v>
       </c>
@@ -20286,7 +20310,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="56" t="s">
         <v>1193</v>
       </c>
@@ -20300,7 +20324,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="56" t="s">
         <v>1193</v>
       </c>
@@ -20317,7 +20341,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="57" t="s">
         <v>255</v>
       </c>
@@ -20331,7 +20355,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="56" t="s">
         <v>1195</v>
       </c>
@@ -20345,7 +20369,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="56" t="s">
         <v>1195</v>
       </c>
@@ -20365,7 +20389,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="56" t="s">
         <v>1195</v>
       </c>
@@ -20385,7 +20409,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="56" t="s">
         <v>1200</v>
       </c>
@@ -20399,7 +20423,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="56" t="s">
         <v>1200</v>
       </c>
@@ -20416,7 +20440,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="56" t="s">
         <v>1201</v>
       </c>
@@ -20430,7 +20454,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="56" t="s">
         <v>1201</v>
       </c>
@@ -20447,7 +20471,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="57" t="s">
         <v>266</v>
       </c>
@@ -20461,7 +20485,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="54" t="s">
         <v>59</v>
       </c>
@@ -20477,7 +20501,7 @@
       </c>
       <c r="F54" s="54"/>
     </row>
-    <row r="55" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="54" t="s">
         <v>59</v>
       </c>
@@ -20495,7 +20519,7 @@
       </c>
       <c r="F55" s="54"/>
     </row>
-    <row r="56" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="58" t="s">
         <v>1092</v>
       </c>
@@ -20652,7 +20676,7 @@
       <c r="F64" s="54"/>
       <c r="G64" s="8"/>
     </row>
-    <row r="65" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="57" t="s">
         <v>250</v>
       </c>
@@ -20669,7 +20693,7 @@
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
     </row>
-    <row r="66" s="53" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="57" t="s">
         <v>286</v>
       </c>
@@ -20686,7 +20710,7 @@
       <c r="F66" s="8"/>
       <c r="G66" s="8"/>
     </row>
-    <row r="67" s="53" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="57" t="s">
         <v>286</v>
       </c>
@@ -20709,7 +20733,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="68" s="53" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="57" t="s">
         <v>286</v>
       </c>
@@ -20728,7 +20752,7 @@
       <c r="F68" s="8"/>
       <c r="G68" s="8"/>
     </row>
-    <row r="69" s="53" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="57" t="s">
         <v>286</v>
       </c>
@@ -20747,7 +20771,7 @@
       <c r="F69" s="8"/>
       <c r="G69" s="8"/>
     </row>
-    <row r="70" s="53" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="57" t="s">
         <v>286</v>
       </c>
@@ -20768,7 +20792,7 @@
       </c>
       <c r="G70" s="8"/>
     </row>
-    <row r="71" s="53" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
         <v>1213</v>
       </c>
@@ -20785,7 +20809,7 @@
       <c r="F71" s="8"/>
       <c r="G71" s="8"/>
     </row>
-    <row r="72" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="57" t="s">
         <v>916</v>
       </c>
@@ -20813,7 +20837,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
         <v>1216</v>
       </c>
@@ -20827,7 +20851,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
         <v>1216</v>
       </c>
@@ -20844,7 +20868,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="62" t="s">
         <v>405</v>
       </c>
@@ -20858,7 +20882,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="77" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="62" t="s">
         <v>405</v>
       </c>
@@ -20878,7 +20902,7 @@
       <c r="G77" s="8"/>
       <c r="H77" s="8"/>
     </row>
-    <row r="78" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="57" t="s">
         <v>431</v>
       </c>
@@ -20895,7 +20919,7 @@
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
     </row>
-    <row r="79" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="57" t="s">
         <v>431</v>
       </c>
@@ -20914,7 +20938,7 @@
       <c r="F79" s="8"/>
       <c r="G79" s="8"/>
     </row>
-    <row r="80" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="57" t="s">
         <v>438</v>
       </c>
@@ -20931,7 +20955,7 @@
       <c r="F80" s="8"/>
       <c r="G80" s="8"/>
     </row>
-    <row r="81" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="57" t="s">
         <v>438</v>
       </c>
@@ -20950,7 +20974,7 @@
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
     </row>
-    <row r="82" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="57" t="s">
         <v>438</v>
       </c>
@@ -20969,7 +20993,7 @@
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
     </row>
-    <row r="83" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="63" t="s">
         <v>1225</v>
       </c>
@@ -20987,7 +21011,7 @@
       <c r="G83" s="8"/>
       <c r="H83" s="8"/>
     </row>
-    <row r="84" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="8" t="s">
         <v>598</v>
       </c>
@@ -21004,7 +21028,7 @@
       <c r="F84" s="8"/>
       <c r="G84" s="8"/>
     </row>
-    <row r="85" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="s">
         <v>620</v>
       </c>
@@ -21021,7 +21045,7 @@
       <c r="F85" s="8"/>
       <c r="G85" s="8"/>
     </row>
-    <row r="86" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="8" t="s">
         <v>630</v>
       </c>
@@ -21034,9 +21058,8 @@
       <c r="E86" s="60" t="s">
         <v>1230</v>
       </c>
-      <c r="H86" s="53"/>
-    </row>
-    <row r="87" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="8" t="s">
         <v>673</v>
       </c>
@@ -21050,7 +21073,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="8" t="s">
         <v>614</v>
       </c>
@@ -21064,7 +21087,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="8" t="s">
         <v>614</v>
       </c>
@@ -21081,7 +21104,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="8" t="s">
         <v>614</v>
       </c>
@@ -21101,7 +21124,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="8" t="s">
         <v>614</v>
       </c>
@@ -21121,7 +21144,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="s">
         <v>614</v>
       </c>
@@ -21141,7 +21164,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="s">
         <v>614</v>
       </c>
@@ -21161,7 +21184,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="8" t="s">
         <v>614</v>
       </c>
@@ -21181,7 +21204,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="8" t="s">
         <v>614</v>
       </c>
@@ -21201,7 +21224,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="8" t="s">
         <v>614</v>
       </c>
@@ -21221,7 +21244,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="8" t="s">
         <v>614</v>
       </c>
@@ -21241,7 +21264,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="8" t="s">
         <v>614</v>
       </c>
@@ -21261,7 +21284,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="8" t="s">
         <v>614</v>
       </c>
@@ -21281,12 +21304,12 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="8" t="s">
         <v>1237</v>
       </c>
       <c r="C100" s="57" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D100" s="46" t="s">
         <v>1154</v>
@@ -21295,12 +21318,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="8" t="s">
         <v>1238</v>
       </c>
       <c r="C101" s="57" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D101" s="46" t="s">
         <v>1153</v>
@@ -21309,7 +21332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="8" t="s">
         <v>808</v>
       </c>
@@ -21323,9 +21346,9 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="57" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>1240</v>
@@ -21337,9 +21360,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="57" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>1164</v>
@@ -21357,9 +21380,9 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="105" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="57" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B105" s="8" t="s">
         <v>1158</v>
@@ -21377,9 +21400,9 @@
       <c r="G105" s="8"/>
       <c r="H105" s="8"/>
     </row>
-    <row r="106" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="57" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B106" s="8" t="s">
         <v>1158</v>
@@ -21398,9 +21421,9 @@
       </c>
       <c r="G106" s="8"/>
     </row>
-    <row r="107" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="57" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B107" s="8" t="s">
         <v>1164</v>
@@ -21419,15 +21442,15 @@
       </c>
       <c r="G107" s="8"/>
     </row>
-    <row r="108" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="57" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B108" s="8" t="s">
         <v>1158</v>
       </c>
       <c r="C108" s="57" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D108" s="46" t="s">
         <v>1154</v>
@@ -21440,9 +21463,9 @@
       </c>
       <c r="G108" s="8"/>
     </row>
-    <row r="109" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="57" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B109" s="8"/>
       <c r="C109" s="8" t="s">
@@ -21457,9 +21480,9 @@
       <c r="F109" s="8"/>
       <c r="G109" s="8"/>
     </row>
-    <row r="110" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="57" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B110" s="8" t="s">
         <v>1164</v>
@@ -21478,9 +21501,9 @@
       </c>
       <c r="H110" s="8"/>
     </row>
-    <row r="111" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="57" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B111" s="8" t="s">
         <v>1158</v>
@@ -21497,9 +21520,9 @@
       <c r="F111" s="8"/>
       <c r="G111" s="8"/>
     </row>
-    <row r="112" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="57" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B112" s="8" t="s">
         <v>1158</v>
@@ -21518,9 +21541,9 @@
       </c>
       <c r="G112" s="8"/>
     </row>
-    <row r="113" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="57" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B113" s="8" t="s">
         <v>1164</v>
@@ -21537,15 +21560,15 @@
       <c r="F113" s="8"/>
       <c r="G113" s="8"/>
     </row>
-    <row r="114" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="57" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B114" s="8" t="s">
         <v>1164</v>
       </c>
       <c r="C114" s="57" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D114" s="46" t="s">
         <v>1153</v>
@@ -21553,11 +21576,10 @@
       <c r="E114" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="H114" s="53"/>
-    </row>
-    <row r="115" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="115" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="8" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="B115" s="8"/>
       <c r="C115" s="54" t="s">
@@ -21575,9 +21597,9 @@
       </c>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="8" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="B116" s="8" t="s">
         <v>1164</v>
@@ -21594,7 +21616,7 @@
       <c r="F116" s="8"/>
       <c r="G116" s="8"/>
     </row>
-    <row r="117" s="53" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="8" t="s">
         <v>200</v>
       </c>
@@ -21610,7 +21632,7 @@
       <c r="F117" s="8"/>
       <c r="G117" s="8"/>
     </row>
-    <row r="118" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="8" t="s">
         <v>200</v>
       </c>
@@ -21618,7 +21640,7 @@
         <v>1164</v>
       </c>
       <c r="C118" s="57" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D118" s="46" t="s">
         <v>1153</v>
@@ -21629,9 +21651,8 @@
       <c r="F118" s="8" t="s">
         <v>1198</v>
       </c>
-      <c r="H118" s="53"/>
-    </row>
-    <row r="119" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="8" t="s">
         <v>200</v>
       </c>
@@ -21648,7 +21669,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="8" t="s">
         <v>200</v>
       </c>
@@ -21668,7 +21689,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="121" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="8" t="s">
         <v>205</v>
       </c>
@@ -21686,7 +21707,7 @@
       <c r="G121" s="8"/>
       <c r="H121" s="8"/>
     </row>
-    <row r="122" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="8" t="s">
         <v>205</v>
       </c>
@@ -21707,7 +21728,7 @@
       </c>
       <c r="G122" s="8"/>
     </row>
-    <row r="123" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="8" t="s">
         <v>205</v>
       </c>
@@ -21726,7 +21747,7 @@
       <c r="F123" s="8"/>
       <c r="G123" s="8"/>
     </row>
-    <row r="124" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="8" t="s">
         <v>205</v>
       </c>
@@ -21747,7 +21768,7 @@
       </c>
       <c r="G124" s="8"/>
     </row>
-    <row r="125" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="8" t="s">
         <v>210</v>
       </c>
@@ -21764,7 +21785,7 @@
       <c r="F125" s="8"/>
       <c r="G125" s="8"/>
     </row>
-    <row r="126" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="57" t="s">
         <v>219</v>
       </c>
@@ -21777,9 +21798,8 @@
       <c r="E126" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="H126" s="53"/>
-    </row>
-    <row r="127" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="57" t="s">
         <v>219</v>
       </c>
@@ -21796,7 +21816,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="8" t="s">
         <v>225</v>
       </c>
@@ -21810,7 +21830,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="8" t="s">
         <v>840</v>
       </c>
@@ -21824,7 +21844,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="8" t="s">
         <v>862</v>
       </c>
@@ -21838,7 +21858,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="8" t="s">
         <v>867</v>
       </c>
@@ -21852,7 +21872,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="64" t="s">
         <v>1047</v>
       </c>
@@ -21868,7 +21888,7 @@
       </c>
       <c r="F132" s="65"/>
     </row>
-    <row r="133" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="57" t="s">
         <v>1047</v>
       </c>
@@ -21888,7 +21908,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="57" t="s">
         <v>1052</v>
       </c>
@@ -21902,7 +21922,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="64" t="s">
         <v>1076</v>
       </c>
@@ -21921,7 +21941,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="57" t="s">
         <v>1083</v>
       </c>
@@ -21935,7 +21955,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="54" t="s">
         <v>995</v>
       </c>
@@ -21949,7 +21969,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="54" t="s">
         <v>1023</v>
       </c>
@@ -21963,7 +21983,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="54" t="s">
         <v>350</v>
       </c>
@@ -21977,7 +21997,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="54" t="s">
         <v>350</v>
       </c>
@@ -21994,7 +22014,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="54" t="s">
         <v>350</v>
       </c>
@@ -22011,7 +22031,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="54" t="s">
         <v>350</v>
       </c>
@@ -22028,7 +22048,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="54" t="s">
         <v>350</v>
       </c>
@@ -22045,7 +22065,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="8" t="s">
         <v>1102</v>
       </c>
@@ -22059,7 +22079,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="8" t="s">
         <v>37</v>
       </c>
@@ -22073,7 +22093,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="8" t="s">
         <v>29</v>
       </c>
@@ -22087,7 +22107,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="8" t="s">
         <v>29</v>
       </c>
@@ -22104,7 +22124,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="8" t="s">
         <v>67</v>
       </c>
@@ -22135,16 +22155,16 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="10.73046875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="10.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="12.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="13.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="12.54"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="5" style="8" width="10.73"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="10.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="13.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="12.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="5" style="8" width="10.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="15.45"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="8" width="10.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="15.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="8" width="10.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22202,7 +22222,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
         <v>48</v>
       </c>
@@ -22228,7 +22248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
         <v>169</v>
       </c>
@@ -22254,7 +22274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
         <v>1275</v>
       </c>
@@ -22280,7 +22300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
         <v>353</v>
       </c>
@@ -22309,7 +22329,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="74" t="s">
         <v>362</v>
       </c>
@@ -22338,7 +22358,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="74" t="s">
         <v>449</v>
       </c>
@@ -22367,7 +22387,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="74" t="s">
         <v>548</v>
       </c>
@@ -22396,7 +22416,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="74" t="s">
         <v>744</v>
       </c>
@@ -22425,7 +22445,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="74" t="s">
         <v>823</v>
       </c>
@@ -22454,7 +22474,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
         <v>880</v>
       </c>
@@ -22483,7 +22503,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
         <v>919</v>
       </c>
@@ -22512,7 +22532,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
         <v>928</v>
       </c>
@@ -22541,7 +22561,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
         <v>956</v>
       </c>
@@ -22570,7 +22590,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="16" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="53" t="s">
         <v>991</v>
       </c>
@@ -22599,7 +22619,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
         <v>1043</v>
       </c>
@@ -22625,7 +22645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
         <v>1137</v>
       </c>
@@ -22671,21 +22691,21 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="53" width="18.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="53" width="17.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="53" width="13.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="53" width="12.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="53" width="18.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="53" width="17.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="53" width="13.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="53" width="12.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="53" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="53" width="13.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="53" width="14.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="53" width="11.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="53" width="13.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="53" width="14.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="53" width="13.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="53" width="14.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="53" width="11.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="53" width="13.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="53" width="14.5"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="75" t="s">
         <v>1315</v>
       </c>
@@ -22892,17 +22912,17 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F265"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="53" width="16.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="53" width="16.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="53" width="51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="53" width="53.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="53" width="47.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="53" width="25.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="53" width="33.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="53" width="53.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="53" width="47.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="53" width="25.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="53" width="33.5"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="77" t="s">
         <v>1352</v>
       </c>
@@ -22922,7 +22942,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="53" t="s">
         <v>169</v>
       </c>
@@ -22938,7 +22958,7 @@
       <c r="E2" s="79"/>
       <c r="F2" s="79"/>
     </row>
-    <row r="3" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="53" t="s">
         <v>169</v>
       </c>
@@ -22954,7 +22974,7 @@
       <c r="E3" s="79"/>
       <c r="F3" s="79"/>
     </row>
-    <row r="4" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="53" t="s">
         <v>48</v>
       </c>
@@ -22970,7 +22990,7 @@
       <c r="E4" s="79"/>
       <c r="F4" s="79"/>
     </row>
-    <row r="5" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="61.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="53" t="s">
         <v>48</v>
       </c>
@@ -22986,7 +23006,7 @@
       <c r="E5" s="79"/>
       <c r="F5" s="79"/>
     </row>
-    <row r="6" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="53" t="s">
         <v>48</v>
       </c>
@@ -23002,7 +23022,7 @@
       <c r="E6" s="79"/>
       <c r="F6" s="79"/>
     </row>
-    <row r="7" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="73.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="53" t="s">
         <v>48</v>
       </c>
@@ -23018,7 +23038,7 @@
       <c r="E7" s="79"/>
       <c r="F7" s="79"/>
     </row>
-    <row r="8" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="49.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="53" t="s">
         <v>48</v>
       </c>
@@ -23034,7 +23054,7 @@
       <c r="E8" s="79"/>
       <c r="F8" s="79"/>
     </row>
-    <row r="9" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="53" t="s">
         <v>48</v>
       </c>
@@ -23050,7 +23070,7 @@
       <c r="E9" s="79"/>
       <c r="F9" s="79"/>
     </row>
-    <row r="10" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="133.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="53" t="s">
         <v>48</v>
       </c>
@@ -23066,7 +23086,7 @@
       <c r="E10" s="79"/>
       <c r="F10" s="79"/>
     </row>
-    <row r="11" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="53" t="s">
         <v>48</v>
       </c>
@@ -23082,7 +23102,7 @@
       <c r="E11" s="79"/>
       <c r="F11" s="79"/>
     </row>
-    <row r="12" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="73.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="53" t="s">
         <v>48</v>
       </c>
@@ -23098,7 +23118,7 @@
       <c r="E12" s="79"/>
       <c r="F12" s="79"/>
     </row>
-    <row r="13" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="53" t="s">
         <v>169</v>
       </c>
@@ -23114,7 +23134,7 @@
       <c r="E13" s="79"/>
       <c r="F13" s="79"/>
     </row>
-    <row r="14" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="133.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="53" t="s">
         <v>169</v>
       </c>
@@ -23130,7 +23150,7 @@
       <c r="E14" s="79"/>
       <c r="F14" s="79"/>
     </row>
-    <row r="15" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="53" t="s">
         <v>169</v>
       </c>
@@ -23146,7 +23166,7 @@
       <c r="E15" s="79"/>
       <c r="F15" s="79"/>
     </row>
-    <row r="16" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="85.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="53" t="s">
         <v>169</v>
       </c>
@@ -23700,7 +23720,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="56" t="s">
         <v>449</v>
       </c>
@@ -23780,7 +23800,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="56" t="s">
         <v>449</v>
       </c>
@@ -23800,7 +23820,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="56" t="s">
         <v>449</v>
       </c>
@@ -23820,7 +23840,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="49.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="56" t="s">
         <v>449</v>
       </c>
@@ -23840,7 +23860,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="49.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="56" t="s">
         <v>449</v>
       </c>
@@ -23860,7 +23880,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="49.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="56" t="s">
         <v>449</v>
       </c>
@@ -23880,7 +23900,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="56" t="s">
         <v>449</v>
       </c>
@@ -23900,7 +23920,7 @@
         <v>1559</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="56" t="s">
         <v>449</v>
       </c>
@@ -23920,7 +23940,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="56" t="s">
         <v>449</v>
       </c>
@@ -23940,7 +23960,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="56" t="s">
         <v>449</v>
       </c>
@@ -23960,7 +23980,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="56" t="s">
         <v>449</v>
       </c>
@@ -23976,7 +23996,7 @@
       <c r="E68" s="54"/>
       <c r="F68" s="54"/>
     </row>
-    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="53" t="s">
         <v>449</v>
       </c>
@@ -24486,7 +24506,7 @@
       <c r="E100" s="54"/>
       <c r="F100" s="54"/>
     </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="53" t="s">
         <v>449</v>
       </c>
@@ -24500,7 +24520,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="53" t="s">
         <v>449</v>
       </c>
@@ -24514,7 +24534,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="53" t="s">
         <v>449</v>
       </c>
@@ -24528,7 +24548,7 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="53" t="s">
         <v>449</v>
       </c>
@@ -24548,7 +24568,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="61.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="53" t="s">
         <v>449</v>
       </c>
@@ -24562,7 +24582,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="53" t="s">
         <v>169</v>
       </c>
@@ -24576,7 +24596,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="53" t="s">
         <v>169</v>
       </c>
@@ -24590,7 +24610,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="53" t="s">
         <v>169</v>
       </c>
@@ -24604,7 +24624,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="53" t="s">
         <v>169</v>
       </c>
@@ -24618,7 +24638,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="53" t="s">
         <v>169</v>
       </c>
@@ -24632,7 +24652,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="53" t="s">
         <v>169</v>
       </c>
@@ -24646,7 +24666,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="53" t="s">
         <v>169</v>
       </c>
@@ -24660,7 +24680,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="53" t="s">
         <v>169</v>
       </c>
@@ -24674,7 +24694,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="53" t="s">
         <v>169</v>
       </c>
@@ -24694,7 +24714,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="53" t="s">
         <v>169</v>
       </c>
@@ -24708,7 +24728,7 @@
         <v>1713</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="53" t="s">
         <v>169</v>
       </c>
@@ -24722,7 +24742,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="53" t="s">
         <v>169</v>
       </c>
@@ -24736,7 +24756,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="53" t="s">
         <v>169</v>
       </c>
@@ -24750,7 +24770,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="53" t="s">
         <v>169</v>
       </c>
@@ -24764,7 +24784,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="83" t="s">
         <v>449</v>
       </c>
@@ -24780,7 +24800,7 @@
       <c r="E120" s="60"/>
       <c r="F120" s="60"/>
     </row>
-    <row r="121" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="83" t="s">
         <v>449</v>
       </c>
@@ -24796,7 +24816,7 @@
       <c r="E121" s="60"/>
       <c r="F121" s="60"/>
     </row>
-    <row r="122" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="83" t="s">
         <v>449</v>
       </c>
@@ -24812,7 +24832,7 @@
       <c r="E122" s="60"/>
       <c r="F122" s="60"/>
     </row>
-    <row r="123" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="49.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="83" t="s">
         <v>449</v>
       </c>
@@ -24832,7 +24852,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="53" t="s">
         <v>449</v>
       </c>
@@ -24846,7 +24866,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="53" t="s">
         <v>449</v>
       </c>
@@ -24860,7 +24880,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="53" t="s">
         <v>449</v>
       </c>
@@ -24874,7 +24894,7 @@
         <v>1737</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="53" t="s">
         <v>449</v>
       </c>
@@ -24888,7 +24908,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="83" t="s">
         <v>548</v>
       </c>
@@ -24908,7 +24928,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="83" t="s">
         <v>548</v>
       </c>
@@ -24928,7 +24948,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="83" t="s">
         <v>548</v>
       </c>
@@ -24944,7 +24964,7 @@
       <c r="E130" s="8"/>
       <c r="F130" s="8"/>
     </row>
-    <row r="131" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="83" t="s">
         <v>548</v>
       </c>
@@ -24960,7 +24980,7 @@
       <c r="E131" s="8"/>
       <c r="F131" s="8"/>
     </row>
-    <row r="132" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="83" t="s">
         <v>548</v>
       </c>
@@ -24976,7 +24996,7 @@
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
     </row>
-    <row r="133" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="83" t="s">
         <v>548</v>
       </c>
@@ -24992,7 +25012,7 @@
       <c r="E133" s="8"/>
       <c r="F133" s="8"/>
     </row>
-    <row r="134" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="83" t="s">
         <v>548</v>
       </c>
@@ -25008,7 +25028,7 @@
       <c r="E134" s="8"/>
       <c r="F134" s="8"/>
     </row>
-    <row r="135" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="83" t="s">
         <v>548</v>
       </c>
@@ -25024,7 +25044,7 @@
       <c r="E135" s="8"/>
       <c r="F135" s="8"/>
     </row>
-    <row r="136" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="83" t="s">
         <v>548</v>
       </c>
@@ -25040,7 +25060,7 @@
       <c r="E136" s="8"/>
       <c r="F136" s="8"/>
     </row>
-    <row r="137" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="83" t="s">
         <v>548</v>
       </c>
@@ -25056,7 +25076,7 @@
       <c r="E137" s="8"/>
       <c r="F137" s="8"/>
     </row>
-    <row r="138" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="83" t="s">
         <v>548</v>
       </c>
@@ -25072,7 +25092,7 @@
       <c r="E138" s="8"/>
       <c r="F138" s="8"/>
     </row>
-    <row r="139" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="83" t="s">
         <v>548</v>
       </c>
@@ -25088,7 +25108,7 @@
       <c r="E139" s="8"/>
       <c r="F139" s="8"/>
     </row>
-    <row r="140" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="83" t="s">
         <v>548</v>
       </c>
@@ -25104,7 +25124,7 @@
       <c r="E140" s="8"/>
       <c r="F140" s="8"/>
     </row>
-    <row r="141" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="83" t="s">
         <v>548</v>
       </c>
@@ -25120,7 +25140,7 @@
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
     </row>
-    <row r="142" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="83" t="s">
         <v>548</v>
       </c>
@@ -25136,7 +25156,7 @@
       <c r="E142" s="8"/>
       <c r="F142" s="8"/>
     </row>
-    <row r="143" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="83" t="s">
         <v>548</v>
       </c>
@@ -25152,7 +25172,7 @@
       <c r="E143" s="8"/>
       <c r="F143" s="8"/>
     </row>
-    <row r="144" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="83" t="s">
         <v>548</v>
       </c>
@@ -25168,7 +25188,7 @@
       <c r="E144" s="8"/>
       <c r="F144" s="8"/>
     </row>
-    <row r="145" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="83" t="s">
         <v>548</v>
       </c>
@@ -25184,7 +25204,7 @@
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
     </row>
-    <row r="146" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="83" t="s">
         <v>548</v>
       </c>
@@ -25200,7 +25220,7 @@
       <c r="E146" s="8"/>
       <c r="F146" s="8"/>
     </row>
-    <row r="147" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="83" t="s">
         <v>548</v>
       </c>
@@ -25216,7 +25236,7 @@
       <c r="E147" s="8"/>
       <c r="F147" s="8"/>
     </row>
-    <row r="148" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="83" t="s">
         <v>548</v>
       </c>
@@ -25232,7 +25252,7 @@
       <c r="E148" s="8"/>
       <c r="F148" s="8"/>
     </row>
-    <row r="149" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="83" t="s">
         <v>548</v>
       </c>
@@ -25248,7 +25268,7 @@
       <c r="E149" s="8"/>
       <c r="F149" s="8"/>
     </row>
-    <row r="150" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="83" t="s">
         <v>548</v>
       </c>
@@ -25264,7 +25284,7 @@
       <c r="E150" s="8"/>
       <c r="F150" s="8"/>
     </row>
-    <row r="151" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="83" t="s">
         <v>548</v>
       </c>
@@ -25280,7 +25300,7 @@
       <c r="E151" s="8"/>
       <c r="F151" s="8"/>
     </row>
-    <row r="152" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="83" t="s">
         <v>548</v>
       </c>
@@ -25296,7 +25316,7 @@
       <c r="E152" s="8"/>
       <c r="F152" s="8"/>
     </row>
-    <row r="153" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="83" t="s">
         <v>548</v>
       </c>
@@ -25312,7 +25332,7 @@
       <c r="E153" s="8"/>
       <c r="F153" s="8"/>
     </row>
-    <row r="154" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="83" t="s">
         <v>548</v>
       </c>
@@ -25328,7 +25348,7 @@
       <c r="E154" s="8"/>
       <c r="F154" s="8"/>
     </row>
-    <row r="155" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="83" t="s">
         <v>548</v>
       </c>
@@ -25344,7 +25364,7 @@
       <c r="E155" s="8"/>
       <c r="F155" s="8"/>
     </row>
-    <row r="156" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="83" t="s">
         <v>548</v>
       </c>
@@ -25360,7 +25380,7 @@
       <c r="E156" s="8"/>
       <c r="F156" s="8"/>
     </row>
-    <row r="157" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="83" t="s">
         <v>548</v>
       </c>
@@ -25376,7 +25396,7 @@
       <c r="E157" s="8"/>
       <c r="F157" s="8"/>
     </row>
-    <row r="158" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="84" t="s">
         <v>548</v>
       </c>
@@ -25392,7 +25412,7 @@
       <c r="E158" s="8"/>
       <c r="F158" s="8"/>
     </row>
-    <row r="159" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="84" t="s">
         <v>548</v>
       </c>
@@ -25408,7 +25428,7 @@
       <c r="E159" s="8"/>
       <c r="F159" s="8"/>
     </row>
-    <row r="160" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="53" t="s">
         <v>169</v>
       </c>
@@ -25428,7 +25448,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="53" t="s">
         <v>169</v>
       </c>
@@ -25448,7 +25468,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="53" t="s">
         <v>169</v>
       </c>
@@ -25468,7 +25488,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="53" t="s">
         <v>169</v>
       </c>
@@ -25488,7 +25508,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="26" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="53" t="s">
         <v>169</v>
       </c>
@@ -25508,7 +25528,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="53" t="s">
         <v>362</v>
       </c>
@@ -25524,7 +25544,7 @@
       <c r="E165" s="8"/>
       <c r="F165" s="8"/>
     </row>
-    <row r="166" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="53" t="s">
         <v>362</v>
       </c>
@@ -25540,7 +25560,7 @@
       <c r="E166" s="8"/>
       <c r="F166" s="8"/>
     </row>
-    <row r="167" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="53" t="s">
         <v>362</v>
       </c>
@@ -25560,7 +25580,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="53" t="s">
         <v>362</v>
       </c>
@@ -25580,7 +25600,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="53" t="s">
         <v>362</v>
       </c>
@@ -25600,7 +25620,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="49.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="53" t="s">
         <v>362</v>
       </c>
@@ -25620,7 +25640,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="53" t="s">
         <v>362</v>
       </c>
@@ -25640,7 +25660,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="53" t="s">
         <v>362</v>
       </c>
@@ -25660,7 +25680,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="53" t="s">
         <v>362</v>
       </c>
@@ -25680,7 +25700,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="53" t="s">
         <v>362</v>
       </c>
@@ -25696,7 +25716,7 @@
       <c r="E174" s="54"/>
       <c r="F174" s="8"/>
     </row>
-    <row r="175" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="53" t="s">
         <v>362</v>
       </c>
@@ -25712,7 +25732,7 @@
       <c r="E175" s="54"/>
       <c r="F175" s="8"/>
     </row>
-    <row r="176" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="53" t="s">
         <v>1043</v>
       </c>
@@ -25726,7 +25746,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="53" t="s">
         <v>548</v>
       </c>
@@ -25740,7 +25760,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="53" t="s">
         <v>548</v>
       </c>
@@ -25754,7 +25774,7 @@
         <v>1917</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="53" t="s">
         <v>548</v>
       </c>
@@ -25768,7 +25788,7 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="53" t="s">
         <v>548</v>
       </c>
@@ -25782,7 +25802,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="53" t="s">
         <v>548</v>
       </c>
@@ -25796,7 +25816,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="53" t="s">
         <v>548</v>
       </c>
@@ -25810,7 +25830,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="53" t="s">
         <v>548</v>
       </c>
@@ -25824,7 +25844,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="53" t="s">
         <v>548</v>
       </c>
@@ -25838,7 +25858,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="53" t="s">
         <v>548</v>
       </c>
@@ -25852,7 +25872,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="53" t="s">
         <v>548</v>
       </c>
@@ -25866,7 +25886,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="53" t="s">
         <v>548</v>
       </c>
@@ -25880,7 +25900,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="53" t="s">
         <v>548</v>
       </c>
@@ -25894,7 +25914,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="53" t="s">
         <v>548</v>
       </c>
@@ -25908,7 +25928,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="53" t="s">
         <v>548</v>
       </c>
@@ -25922,7 +25942,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="53" t="s">
         <v>548</v>
       </c>
@@ -25936,7 +25956,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="53" t="s">
         <v>548</v>
       </c>
@@ -25950,7 +25970,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="53" t="s">
         <v>548</v>
       </c>
@@ -25964,7 +25984,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="53" t="s">
         <v>548</v>
       </c>
@@ -25978,7 +25998,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="53" t="s">
         <v>548</v>
       </c>
@@ -25992,7 +26012,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="53" t="s">
         <v>548</v>
       </c>
@@ -26006,7 +26026,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="53" t="s">
         <v>548</v>
       </c>
@@ -26020,7 +26040,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="53" t="s">
         <v>548</v>
       </c>
@@ -26034,7 +26054,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="53" t="s">
         <v>548</v>
       </c>
@@ -26048,7 +26068,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="53" t="s">
         <v>548</v>
       </c>
@@ -26062,7 +26082,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="53" t="s">
         <v>548</v>
       </c>
@@ -26076,7 +26096,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="53" t="s">
         <v>548</v>
       </c>
@@ -26090,7 +26110,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="53" t="s">
         <v>548</v>
       </c>
@@ -26104,7 +26124,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="53" t="s">
         <v>548</v>
       </c>
@@ -26118,7 +26138,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="53" t="s">
         <v>548</v>
       </c>
@@ -26132,7 +26152,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="53" t="s">
         <v>548</v>
       </c>
@@ -26146,7 +26166,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="53" t="s">
         <v>548</v>
       </c>
@@ -26160,7 +26180,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="53" t="s">
         <v>548</v>
       </c>
@@ -26174,7 +26194,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="53" t="s">
         <v>548</v>
       </c>
@@ -26188,7 +26208,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="53" t="s">
         <v>548</v>
       </c>
@@ -26202,7 +26222,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="53" t="s">
         <v>548</v>
       </c>
@@ -26216,7 +26236,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="53" t="s">
         <v>548</v>
       </c>
@@ -26230,7 +26250,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="53" t="s">
         <v>548</v>
       </c>
@@ -26244,7 +26264,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="53" t="s">
         <v>548</v>
       </c>
@@ -26258,7 +26278,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="53" t="s">
         <v>548</v>
       </c>
@@ -26272,7 +26292,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="53" t="s">
         <v>548</v>
       </c>
@@ -26286,7 +26306,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="53" t="s">
         <v>548</v>
       </c>
@@ -26300,7 +26320,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="53" t="s">
         <v>548</v>
       </c>
@@ -26314,7 +26334,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="53" t="s">
         <v>548</v>
       </c>
@@ -26328,7 +26348,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="53" t="s">
         <v>548</v>
       </c>
@@ -26342,7 +26362,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="53" t="s">
         <v>548</v>
       </c>
@@ -26356,7 +26376,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="53" t="s">
         <v>548</v>
       </c>
@@ -26370,7 +26390,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="53" t="s">
         <v>548</v>
       </c>
@@ -26384,7 +26404,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="53" t="s">
         <v>548</v>
       </c>
@@ -26398,7 +26418,7 @@
         <v>2046</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="53" t="s">
         <v>548</v>
       </c>
@@ -26412,7 +26432,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="53" t="s">
         <v>548</v>
       </c>
@@ -26426,7 +26446,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="53" t="s">
         <v>548</v>
       </c>
@@ -26440,7 +26460,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="53" t="s">
         <v>548</v>
       </c>
@@ -26454,7 +26474,7 @@
         <v>2057</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="53" t="s">
         <v>548</v>
       </c>
@@ -26468,7 +26488,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="53" t="s">
         <v>548</v>
       </c>
@@ -26482,7 +26502,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="53" t="s">
         <v>548</v>
       </c>
@@ -26496,7 +26516,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="53" t="s">
         <v>548</v>
       </c>
@@ -26510,7 +26530,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="53" t="s">
         <v>548</v>
       </c>
@@ -26524,7 +26544,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="53" t="s">
         <v>548</v>
       </c>
@@ -26538,7 +26558,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="53" t="s">
         <v>548</v>
       </c>
@@ -26552,7 +26572,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="53" t="s">
         <v>548</v>
       </c>
@@ -26566,7 +26586,7 @@
         <v>2081</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="53" t="s">
         <v>548</v>
       </c>
@@ -26580,7 +26600,7 @@
         <v>2084</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="53" t="s">
         <v>548</v>
       </c>
@@ -26594,7 +26614,7 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="53" t="s">
         <v>548</v>
       </c>
@@ -26608,7 +26628,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="53" t="s">
         <v>548</v>
       </c>
@@ -26622,7 +26642,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="53" t="s">
         <v>548</v>
       </c>
@@ -26636,7 +26656,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="53" t="s">
         <v>548</v>
       </c>
@@ -26650,7 +26670,7 @@
         <v>2097</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="53" t="s">
         <v>548</v>
       </c>
@@ -26664,7 +26684,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="53" t="s">
         <v>548</v>
       </c>
@@ -26678,7 +26698,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="53" t="s">
         <v>548</v>
       </c>
@@ -26692,7 +26712,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="53" t="s">
         <v>548</v>
       </c>
@@ -26706,7 +26726,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="53" t="s">
         <v>548</v>
       </c>
@@ -26720,7 +26740,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="49.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="53" t="s">
         <v>548</v>
       </c>
@@ -26734,7 +26754,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="51" t="s">
         <v>744</v>
       </c>
@@ -26748,7 +26768,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="53" t="s">
         <v>744</v>
       </c>
@@ -26762,7 +26782,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="53" t="s">
         <v>744</v>
       </c>
@@ -26776,7 +26796,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="285.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="205.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="53" t="s">
         <v>744</v>
       </c>
@@ -26796,7 +26816,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="225.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="169.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="53" t="s">
         <v>744</v>
       </c>
@@ -26816,7 +26836,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="53" t="s">
         <v>823</v>
       </c>
@@ -26830,7 +26850,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="255" customFormat="false" ht="45.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="53" t="s">
         <v>823</v>
       </c>
@@ -26844,7 +26864,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="53" t="s">
         <v>823</v>
       </c>
@@ -26858,7 +26878,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="53" t="s">
         <v>1043</v>
       </c>
@@ -26872,7 +26892,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="53" t="s">
         <v>1043</v>
       </c>
@@ -26886,7 +26906,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="259" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="49.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="53" t="s">
         <v>991</v>
       </c>
@@ -26900,7 +26920,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="260" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" customFormat="false" ht="49.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="53" t="s">
         <v>991</v>
       </c>
@@ -26914,7 +26934,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="261" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="53" t="s">
         <v>48</v>
       </c>
@@ -26928,7 +26948,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="262" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" customFormat="false" ht="49.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="53" t="s">
         <v>48</v>
       </c>
@@ -26942,7 +26962,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="263" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="53" t="s">
         <v>48</v>
       </c>
@@ -26956,7 +26976,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="61.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="53" t="s">
         <v>48</v>
       </c>
@@ -26970,7 +26990,7 @@
         <v>2155</v>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="53" t="s">
         <v>24</v>
       </c>
@@ -27002,18 +27022,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I261"/>
-  <sheetFormatPr defaultColWidth="9.18359375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I1048576"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="69" width="21.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="69" width="15.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="69" width="97.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="69" width="21.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="69" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="69" width="97.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="69" width="101"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="69" width="24.27"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="69" width="9.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="69" width="24.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="69" width="9.16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="90" t="s">
         <v>2159</v>
       </c>
@@ -27042,7 +27062,7 @@
         <v>2161</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="56" t="s">
         <v>1157</v>
       </c>
@@ -27060,7 +27080,7 @@
       <c r="G2" s="56"/>
       <c r="H2" s="56"/>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="56" t="s">
         <v>1215</v>
       </c>
@@ -27078,7 +27098,7 @@
       <c r="G3" s="56"/>
       <c r="H3" s="56"/>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="56" t="s">
         <v>229</v>
       </c>
@@ -27096,7 +27116,7 @@
       <c r="G4" s="56"/>
       <c r="H4" s="56"/>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="56" t="s">
         <v>2168</v>
       </c>
@@ -27114,7 +27134,7 @@
       <c r="G5" s="56"/>
       <c r="H5" s="56"/>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="56" t="s">
         <v>2169</v>
       </c>
@@ -27132,7 +27152,7 @@
       <c r="G6" s="56"/>
       <c r="H6" s="56"/>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="56" t="s">
         <v>1161</v>
       </c>
@@ -27150,7 +27170,7 @@
       <c r="G7" s="56"/>
       <c r="H7" s="56"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="56" t="s">
         <v>51</v>
       </c>
@@ -27164,7 +27184,7 @@
       </c>
       <c r="H8" s="56"/>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="56" t="s">
         <v>51</v>
       </c>
@@ -27178,9 +27198,9 @@
       </c>
       <c r="H9" s="56"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="56" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="B10" s="56"/>
       <c r="C10" s="56"/>
@@ -27192,9 +27212,9 @@
       </c>
       <c r="H10" s="56"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="56" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="B11" s="56"/>
       <c r="C11" s="56"/>
@@ -27206,7 +27226,7 @@
       </c>
       <c r="H11" s="56"/>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="56" t="s">
         <v>163</v>
       </c>
@@ -27220,7 +27240,7 @@
       </c>
       <c r="H12" s="56"/>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="56" t="s">
         <v>163</v>
       </c>
@@ -27234,7 +27254,7 @@
       </c>
       <c r="H13" s="56"/>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="56" t="s">
         <v>163</v>
       </c>
@@ -27248,7 +27268,7 @@
       </c>
       <c r="H14" s="56"/>
     </row>
-    <row r="15" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="56" t="s">
         <v>88</v>
       </c>
@@ -27267,7 +27287,7 @@
       <c r="H15" s="56"/>
       <c r="I15" s="56"/>
     </row>
-    <row r="16" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="56" t="s">
         <v>88</v>
       </c>
@@ -27286,7 +27306,7 @@
       <c r="H16" s="56"/>
       <c r="I16" s="56"/>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="92" t="s">
         <v>2178</v>
       </c>
@@ -27304,7 +27324,7 @@
       <c r="G17" s="56"/>
       <c r="H17" s="56"/>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="92" t="s">
         <v>2178</v>
       </c>
@@ -27322,7 +27342,7 @@
       <c r="G18" s="56"/>
       <c r="H18" s="56"/>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="92" t="s">
         <v>2178</v>
       </c>
@@ -27336,7 +27356,7 @@
       </c>
       <c r="H19" s="56"/>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="92" t="s">
         <v>187</v>
       </c>
@@ -27354,7 +27374,7 @@
       <c r="G20" s="56"/>
       <c r="H20" s="56"/>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="92" t="s">
         <v>187</v>
       </c>
@@ -27372,7 +27392,7 @@
       <c r="G21" s="56"/>
       <c r="H21" s="56"/>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="92" t="s">
         <v>187</v>
       </c>
@@ -27390,7 +27410,7 @@
       <c r="G22" s="56"/>
       <c r="H22" s="56"/>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="92" t="s">
         <v>187</v>
       </c>
@@ -27404,7 +27424,7 @@
       </c>
       <c r="H23" s="56"/>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="56" t="s">
         <v>306</v>
       </c>
@@ -27422,7 +27442,7 @@
       <c r="G24" s="56"/>
       <c r="H24" s="56"/>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="56" t="s">
         <v>306</v>
       </c>
@@ -27440,7 +27460,7 @@
       <c r="G25" s="56"/>
       <c r="H25" s="56"/>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="56" t="s">
         <v>306</v>
       </c>
@@ -27454,7 +27474,7 @@
       </c>
       <c r="H26" s="56"/>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="56" t="s">
         <v>299</v>
       </c>
@@ -27472,7 +27492,7 @@
       <c r="G27" s="56"/>
       <c r="H27" s="56"/>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="56" t="s">
         <v>299</v>
       </c>
@@ -27490,7 +27510,7 @@
       <c r="G28" s="56"/>
       <c r="H28" s="56"/>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="56" t="s">
         <v>299</v>
       </c>
@@ -27504,7 +27524,7 @@
       </c>
       <c r="H29" s="56"/>
     </row>
-    <row r="30" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="56" t="s">
         <v>340</v>
       </c>
@@ -27526,7 +27546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="56" t="s">
         <v>340</v>
       </c>
@@ -27548,7 +27568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="56" t="s">
         <v>340</v>
       </c>
@@ -27570,7 +27590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="56" t="s">
         <v>340</v>
       </c>
@@ -27592,7 +27612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="56" t="s">
         <v>340</v>
       </c>
@@ -27614,7 +27634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="56" t="s">
         <v>340</v>
       </c>
@@ -27635,7 +27655,7 @@
       </c>
       <c r="I35" s="69"/>
     </row>
-    <row r="36" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="56" t="s">
         <v>340</v>
       </c>
@@ -27654,7 +27674,7 @@
       <c r="H36" s="56"/>
       <c r="I36" s="69"/>
     </row>
-    <row r="37" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="56" t="s">
         <v>340</v>
       </c>
@@ -27673,7 +27693,7 @@
       <c r="H37" s="56"/>
       <c r="I37" s="69"/>
     </row>
-    <row r="38" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="56" t="s">
         <v>340</v>
       </c>
@@ -27692,7 +27712,7 @@
       <c r="H38" s="56"/>
       <c r="I38" s="69"/>
     </row>
-    <row r="39" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="56" t="s">
         <v>340</v>
       </c>
@@ -27711,7 +27731,7 @@
       <c r="H39" s="56"/>
       <c r="I39" s="69"/>
     </row>
-    <row r="40" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="56" t="s">
         <v>340</v>
       </c>
@@ -27730,7 +27750,7 @@
       <c r="H40" s="56"/>
       <c r="I40" s="69"/>
     </row>
-    <row r="41" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="56" t="s">
         <v>340</v>
       </c>
@@ -27745,7 +27765,7 @@
       <c r="H41" s="56"/>
       <c r="I41" s="69"/>
     </row>
-    <row r="42" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="56" t="s">
         <v>340</v>
       </c>
@@ -27760,7 +27780,7 @@
       <c r="H42" s="56"/>
       <c r="I42" s="69"/>
     </row>
-    <row r="43" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="57" t="s">
         <v>315</v>
       </c>
@@ -27779,7 +27799,7 @@
       <c r="H43" s="56"/>
       <c r="I43" s="56"/>
     </row>
-    <row r="44" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="57" t="s">
         <v>315</v>
       </c>
@@ -27798,7 +27818,7 @@
       <c r="H44" s="56"/>
       <c r="I44" s="56"/>
     </row>
-    <row r="45" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="57" t="s">
         <v>315</v>
       </c>
@@ -27817,7 +27837,7 @@
       <c r="H45" s="56"/>
       <c r="I45" s="56"/>
     </row>
-    <row r="46" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="57" t="s">
         <v>315</v>
       </c>
@@ -27836,7 +27856,7 @@
       <c r="H46" s="56"/>
       <c r="I46" s="56"/>
     </row>
-    <row r="47" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="57" t="s">
         <v>315</v>
       </c>
@@ -27851,7 +27871,7 @@
       <c r="H47" s="56"/>
       <c r="I47" s="56"/>
     </row>
-    <row r="48" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="57" t="s">
         <v>220</v>
       </c>
@@ -27872,7 +27892,7 @@
       </c>
       <c r="I48" s="56"/>
     </row>
-    <row r="49" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="57" t="s">
         <v>220</v>
       </c>
@@ -27893,7 +27913,7 @@
       </c>
       <c r="I49" s="56"/>
     </row>
-    <row r="50" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="57" t="s">
         <v>220</v>
       </c>
@@ -27912,7 +27932,7 @@
       <c r="H50" s="56"/>
       <c r="I50" s="56"/>
     </row>
-    <row r="51" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="57" t="s">
         <v>220</v>
       </c>
@@ -27931,7 +27951,7 @@
       <c r="H51" s="56"/>
       <c r="I51" s="56"/>
     </row>
-    <row r="52" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="57" t="s">
         <v>220</v>
       </c>
@@ -27946,7 +27966,7 @@
       <c r="H52" s="56"/>
       <c r="I52" s="56"/>
     </row>
-    <row r="53" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="57" t="s">
         <v>226</v>
       </c>
@@ -27965,7 +27985,7 @@
       <c r="H53" s="56"/>
       <c r="I53" s="56"/>
     </row>
-    <row r="54" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="57" t="s">
         <v>226</v>
       </c>
@@ -27984,7 +28004,7 @@
       <c r="H54" s="56"/>
       <c r="I54" s="56"/>
     </row>
-    <row r="55" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="57" t="s">
         <v>226</v>
       </c>
@@ -28003,7 +28023,7 @@
       <c r="H55" s="56"/>
       <c r="I55" s="56"/>
     </row>
-    <row r="56" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="57" t="s">
         <v>226</v>
       </c>
@@ -28022,7 +28042,7 @@
       <c r="H56" s="56"/>
       <c r="I56" s="56"/>
     </row>
-    <row r="57" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="57" t="s">
         <v>226</v>
       </c>
@@ -28041,7 +28061,7 @@
       <c r="H57" s="56"/>
       <c r="I57" s="56"/>
     </row>
-    <row r="58" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="57" t="s">
         <v>226</v>
       </c>
@@ -28060,7 +28080,7 @@
       <c r="H58" s="56"/>
       <c r="I58" s="56"/>
     </row>
-    <row r="59" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="57" t="s">
         <v>226</v>
       </c>
@@ -28079,7 +28099,7 @@
       <c r="H59" s="56"/>
       <c r="I59" s="56"/>
     </row>
-    <row r="60" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="57" t="s">
         <v>226</v>
       </c>
@@ -28098,7 +28118,7 @@
       <c r="H60" s="56"/>
       <c r="I60" s="56"/>
     </row>
-    <row r="61" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="57" t="s">
         <v>226</v>
       </c>
@@ -28113,7 +28133,7 @@
       <c r="H61" s="56"/>
       <c r="I61" s="56"/>
     </row>
-    <row r="62" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="57" t="s">
         <v>226</v>
       </c>
@@ -28132,7 +28152,7 @@
       <c r="H62" s="56"/>
       <c r="I62" s="56"/>
     </row>
-    <row r="63" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="57" t="s">
         <v>226</v>
       </c>
@@ -28147,7 +28167,7 @@
       <c r="H63" s="56"/>
       <c r="I63" s="56"/>
     </row>
-    <row r="64" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="57" t="s">
         <v>232</v>
       </c>
@@ -28166,7 +28186,7 @@
       <c r="H64" s="56"/>
       <c r="I64" s="56"/>
     </row>
-    <row r="65" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="92" t="s">
         <v>322</v>
       </c>
@@ -28187,7 +28207,7 @@
       <c r="H65" s="56"/>
       <c r="I65" s="69"/>
     </row>
-    <row r="66" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="92" t="s">
         <v>322</v>
       </c>
@@ -28208,7 +28228,7 @@
       <c r="H66" s="56"/>
       <c r="I66" s="69"/>
     </row>
-    <row r="67" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="92" t="s">
         <v>322</v>
       </c>
@@ -28229,7 +28249,7 @@
       <c r="H67" s="56"/>
       <c r="I67" s="69"/>
     </row>
-    <row r="68" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="92" t="s">
         <v>322</v>
       </c>
@@ -28250,7 +28270,7 @@
       <c r="H68" s="56"/>
       <c r="I68" s="69"/>
     </row>
-    <row r="69" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="92" t="s">
         <v>322</v>
       </c>
@@ -28271,7 +28291,7 @@
       <c r="H69" s="56"/>
       <c r="I69" s="69"/>
     </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="92" t="s">
         <v>895</v>
       </c>
@@ -28285,7 +28305,7 @@
         <v>2293</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="92" t="s">
         <v>895</v>
       </c>
@@ -28299,7 +28319,7 @@
         <v>2296</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="92" t="s">
         <v>895</v>
       </c>
@@ -28313,7 +28333,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="73" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="92" t="s">
         <v>895</v>
       </c>
@@ -28641,7 +28661,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="95" t="s">
         <v>423</v>
       </c>
@@ -28662,7 +28682,7 @@
       </c>
       <c r="I93" s="56"/>
     </row>
-    <row r="94" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="95" t="s">
         <v>423</v>
       </c>
@@ -28683,7 +28703,7 @@
       </c>
       <c r="I94" s="56"/>
     </row>
-    <row r="95" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="95" t="s">
         <v>423</v>
       </c>
@@ -28702,7 +28722,7 @@
       <c r="H95" s="56"/>
       <c r="I95" s="56"/>
     </row>
-    <row r="96" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="95" t="s">
         <v>423</v>
       </c>
@@ -28740,7 +28760,7 @@
       <c r="H97" s="56"/>
       <c r="I97" s="56"/>
     </row>
-    <row r="98" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="95" t="s">
         <v>423</v>
       </c>
@@ -28761,7 +28781,7 @@
       </c>
       <c r="I98" s="56"/>
     </row>
-    <row r="99" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="95" t="s">
         <v>423</v>
       </c>
@@ -28780,7 +28800,7 @@
       <c r="H99" s="56"/>
       <c r="I99" s="56"/>
     </row>
-    <row r="100" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="95" t="s">
         <v>423</v>
       </c>
@@ -28801,7 +28821,7 @@
       </c>
       <c r="I100" s="56"/>
     </row>
-    <row r="101" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="95" t="s">
         <v>423</v>
       </c>
@@ -28874,7 +28894,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="96" t="s">
         <v>759</v>
       </c>
@@ -28888,7 +28908,7 @@
         <v>2377</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="96" t="s">
         <v>759</v>
       </c>
@@ -28906,7 +28926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="96" t="s">
         <v>759</v>
       </c>
@@ -28920,7 +28940,7 @@
         <v>2383</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="96" t="s">
         <v>759</v>
       </c>
@@ -28934,7 +28954,7 @@
         <v>2386</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="96" t="s">
         <v>759</v>
       </c>
@@ -28942,7 +28962,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="96" t="s">
         <v>759</v>
       </c>
@@ -28950,7 +28970,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="96" t="s">
         <v>819</v>
       </c>
@@ -28964,7 +28984,7 @@
         <v>2389</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="96" t="s">
         <v>819</v>
       </c>
@@ -28978,7 +28998,7 @@
         <v>2392</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="96" t="s">
         <v>819</v>
       </c>
@@ -28992,7 +29012,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="96" t="s">
         <v>819</v>
       </c>
@@ -29010,7 +29030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="96" t="s">
         <v>819</v>
       </c>
@@ -29018,7 +29038,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="96" t="s">
         <v>819</v>
       </c>
@@ -29177,7 +29197,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="57" t="s">
         <v>686</v>
       </c>
@@ -29191,7 +29211,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="57" t="s">
         <v>686</v>
       </c>
@@ -29208,7 +29228,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="57" t="s">
         <v>686</v>
       </c>
@@ -29225,7 +29245,7 @@
         <v>2433</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="57" t="s">
         <v>686</v>
       </c>
@@ -29242,7 +29262,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="57" t="s">
         <v>686</v>
       </c>
@@ -29256,7 +29276,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="57" t="s">
         <v>686</v>
       </c>
@@ -29266,7 +29286,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="57" t="s">
         <v>692</v>
       </c>
@@ -29280,7 +29300,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="57" t="s">
         <v>692</v>
       </c>
@@ -29294,7 +29314,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="57" t="s">
         <v>692</v>
       </c>
@@ -29311,7 +29331,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="57" t="s">
         <v>692</v>
       </c>
@@ -29325,7 +29345,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="57" t="s">
         <v>692</v>
       </c>
@@ -29339,7 +29359,7 @@
         <v>2439</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="57" t="s">
         <v>692</v>
       </c>
@@ -29353,7 +29373,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="57" t="s">
         <v>692</v>
       </c>
@@ -29363,7 +29383,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="57" t="s">
         <v>582</v>
       </c>
@@ -29380,7 +29400,7 @@
         <v>2444</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="57" t="s">
         <v>582</v>
       </c>
@@ -29397,7 +29417,7 @@
         <v>2447</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="57" t="s">
         <v>582</v>
       </c>
@@ -29411,7 +29431,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="57" t="s">
         <v>582</v>
       </c>
@@ -29425,7 +29445,7 @@
         <v>2452</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="57" t="s">
         <v>582</v>
       </c>
@@ -29435,7 +29455,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="69" t="s">
         <v>615</v>
       </c>
@@ -29449,7 +29469,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="69" t="s">
         <v>615</v>
       </c>
@@ -29463,7 +29483,7 @@
         <v>2457</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="69" t="s">
         <v>615</v>
       </c>
@@ -29473,7 +29493,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="57" t="s">
         <v>639</v>
       </c>
@@ -29487,7 +29507,7 @@
         <v>2460</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="57" t="s">
         <v>639</v>
       </c>
@@ -29501,7 +29521,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="57" t="s">
         <v>639</v>
       </c>
@@ -29511,7 +29531,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="57" t="s">
         <v>639</v>
       </c>
@@ -29521,7 +29541,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="57" t="s">
         <v>646</v>
       </c>
@@ -29535,7 +29555,7 @@
         <v>2466</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="57" t="s">
         <v>646</v>
       </c>
@@ -29549,7 +29569,7 @@
         <v>2468</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="57" t="s">
         <v>646</v>
       </c>
@@ -29563,7 +29583,7 @@
         <v>2470</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="57" t="s">
         <v>646</v>
       </c>
@@ -29577,7 +29597,7 @@
         <v>2472</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="57" t="s">
         <v>646</v>
       </c>
@@ -29587,7 +29607,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="57" t="s">
         <v>646</v>
       </c>
@@ -29597,7 +29617,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="57" t="s">
         <v>651</v>
       </c>
@@ -29611,7 +29631,7 @@
         <v>2475</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="57" t="s">
         <v>651</v>
       </c>
@@ -29625,7 +29645,7 @@
         <v>2478</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="57" t="s">
         <v>651</v>
       </c>
@@ -29639,7 +29659,7 @@
         <v>2480</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="57" t="s">
         <v>651</v>
       </c>
@@ -29653,7 +29673,7 @@
         <v>2482</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="57" t="s">
         <v>651</v>
       </c>
@@ -29667,7 +29687,7 @@
         <v>2485</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="57" t="s">
         <v>651</v>
       </c>
@@ -29677,7 +29697,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="57" t="s">
         <v>651</v>
       </c>
@@ -29687,7 +29707,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="57" t="s">
         <v>783</v>
       </c>
@@ -29706,7 +29726,7 @@
       <c r="H164" s="56"/>
       <c r="I164" s="56"/>
     </row>
-    <row r="165" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="57" t="s">
         <v>783</v>
       </c>
@@ -29725,7 +29745,7 @@
       <c r="H165" s="56"/>
       <c r="I165" s="56"/>
     </row>
-    <row r="166" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="57" t="s">
         <v>783</v>
       </c>
@@ -29744,7 +29764,7 @@
       <c r="H166" s="56"/>
       <c r="I166" s="56"/>
     </row>
-    <row r="167" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="57" t="s">
         <v>783</v>
       </c>
@@ -29763,7 +29783,7 @@
       <c r="H167" s="56"/>
       <c r="I167" s="56"/>
     </row>
-    <row r="168" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="57" t="s">
         <v>783</v>
       </c>
@@ -29782,7 +29802,7 @@
       <c r="H168" s="56"/>
       <c r="I168" s="56"/>
     </row>
-    <row r="169" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="57" t="s">
         <v>783</v>
       </c>
@@ -29803,7 +29823,7 @@
       </c>
       <c r="I169" s="56"/>
     </row>
-    <row r="170" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="57" t="s">
         <v>783</v>
       </c>
@@ -29824,9 +29844,9 @@
       </c>
       <c r="I170" s="56"/>
     </row>
-    <row r="171" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="57" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B171" s="56" t="s">
         <v>2494</v>
@@ -29843,9 +29863,9 @@
       <c r="H171" s="56"/>
       <c r="I171" s="56"/>
     </row>
-    <row r="172" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="57" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B172" s="56" t="s">
         <v>2497</v>
@@ -29862,18 +29882,18 @@
       <c r="H172" s="56"/>
       <c r="I172" s="56"/>
     </row>
-    <row r="173" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="56" t="s">
-        <v>121</v>
-      </c>
-      <c r="B173" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="C173" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D173" s="8" t="n">
-        <v>0</v>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="57" t="s">
+        <v>207</v>
+      </c>
+      <c r="B173" s="56" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C173" s="54" t="s">
+        <v>2500</v>
+      </c>
+      <c r="D173" s="8" t="s">
+        <v>2501</v>
       </c>
       <c r="E173" s="56"/>
       <c r="F173" s="56"/>
@@ -29881,18 +29901,18 @@
       <c r="H173" s="56"/>
       <c r="I173" s="56"/>
     </row>
-    <row r="174" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="56" t="s">
-        <v>121</v>
-      </c>
-      <c r="B174" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C174" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D174" s="8" t="n">
-        <v>1</v>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="57" t="s">
+        <v>207</v>
+      </c>
+      <c r="B174" s="56" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C174" s="54" t="s">
+        <v>2502</v>
+      </c>
+      <c r="D174" s="8" t="s">
+        <v>2503</v>
       </c>
       <c r="E174" s="56"/>
       <c r="F174" s="56"/>
@@ -29900,90 +29920,96 @@
       <c r="H174" s="56"/>
       <c r="I174" s="56"/>
     </row>
-    <row r="175" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="56" t="s">
-        <v>121</v>
-      </c>
-      <c r="B175" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="C175" s="55" t="s">
-        <v>2500</v>
-      </c>
-      <c r="D175" s="55" t="s">
-        <v>2500</v>
-      </c>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="57" t="s">
+        <v>207</v>
+      </c>
+      <c r="B175" s="56"/>
+      <c r="C175" s="54"/>
+      <c r="D175" s="8"/>
       <c r="E175" s="56"/>
       <c r="F175" s="56"/>
-      <c r="G175" s="56"/>
+      <c r="G175" s="56" t="s">
+        <v>2169</v>
+      </c>
       <c r="H175" s="56"/>
       <c r="I175" s="56"/>
     </row>
-    <row r="176" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="57" t="s">
-        <v>207</v>
+        <v>246</v>
       </c>
       <c r="B176" s="56" t="s">
-        <v>1157</v>
-      </c>
-      <c r="C176" s="54" t="s">
-        <v>2501</v>
+        <v>2504</v>
+      </c>
+      <c r="C176" s="51" t="s">
+        <v>2505</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="E176" s="56"/>
       <c r="F176" s="56"/>
       <c r="G176" s="56"/>
-      <c r="H176" s="56"/>
+      <c r="H176" s="56" t="s">
+        <v>1193</v>
+      </c>
       <c r="I176" s="56"/>
     </row>
-    <row r="177" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="57" t="s">
-        <v>207</v>
+        <v>246</v>
       </c>
       <c r="B177" s="56" t="s">
-        <v>1215</v>
-      </c>
-      <c r="C177" s="54" t="s">
-        <v>2503</v>
+        <v>2507</v>
+      </c>
+      <c r="C177" s="51" t="s">
+        <v>2508</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>2504</v>
+        <v>2509</v>
       </c>
       <c r="E177" s="56"/>
       <c r="F177" s="56"/>
       <c r="G177" s="56"/>
-      <c r="H177" s="56"/>
+      <c r="H177" s="56" t="s">
+        <v>1193</v>
+      </c>
       <c r="I177" s="56"/>
     </row>
-    <row r="178" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="57" t="s">
-        <v>207</v>
-      </c>
-      <c r="B178" s="56"/>
-      <c r="C178" s="54"/>
-      <c r="D178" s="8"/>
+        <v>246</v>
+      </c>
+      <c r="B178" s="56" t="s">
+        <v>2510</v>
+      </c>
+      <c r="C178" s="51" t="s">
+        <v>2511</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>2512</v>
+      </c>
       <c r="E178" s="56"/>
       <c r="F178" s="56"/>
-      <c r="G178" s="56" t="s">
-        <v>2169</v>
-      </c>
-      <c r="H178" s="56"/>
+      <c r="G178" s="56"/>
+      <c r="H178" s="56" t="s">
+        <v>1193</v>
+      </c>
       <c r="I178" s="56"/>
     </row>
-    <row r="179" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="57" t="s">
         <v>246</v>
       </c>
       <c r="B179" s="56" t="s">
-        <v>2505</v>
+        <v>2513</v>
       </c>
       <c r="C179" s="51" t="s">
-        <v>2506</v>
+        <v>2514</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>2507</v>
+        <v>2515</v>
       </c>
       <c r="E179" s="56"/>
       <c r="F179" s="56"/>
@@ -29993,18 +30019,18 @@
       </c>
       <c r="I179" s="56"/>
     </row>
-    <row r="180" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="57" t="s">
         <v>246</v>
       </c>
       <c r="B180" s="56" t="s">
-        <v>2508</v>
+        <v>2516</v>
       </c>
       <c r="C180" s="51" t="s">
-        <v>2509</v>
+        <v>2517</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>2510</v>
+        <v>2518</v>
       </c>
       <c r="E180" s="56"/>
       <c r="F180" s="56"/>
@@ -30014,18 +30040,18 @@
       </c>
       <c r="I180" s="56"/>
     </row>
-    <row r="181" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="57" t="s">
         <v>246</v>
       </c>
       <c r="B181" s="56" t="s">
-        <v>2511</v>
+        <v>2519</v>
       </c>
       <c r="C181" s="51" t="s">
-        <v>2512</v>
+        <v>2520</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>2513</v>
+        <v>2521</v>
       </c>
       <c r="E181" s="56"/>
       <c r="F181" s="56"/>
@@ -30035,18 +30061,18 @@
       </c>
       <c r="I181" s="56"/>
     </row>
-    <row r="182" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="57" t="s">
         <v>246</v>
       </c>
       <c r="B182" s="56" t="s">
-        <v>2514</v>
+        <v>2522</v>
       </c>
       <c r="C182" s="51" t="s">
-        <v>2515</v>
+        <v>2523</v>
       </c>
       <c r="D182" s="8" t="s">
-        <v>2516</v>
+        <v>2524</v>
       </c>
       <c r="E182" s="56"/>
       <c r="F182" s="56"/>
@@ -30056,18 +30082,18 @@
       </c>
       <c r="I182" s="56"/>
     </row>
-    <row r="183" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="57" t="s">
         <v>246</v>
       </c>
       <c r="B183" s="56" t="s">
-        <v>2517</v>
+        <v>2525</v>
       </c>
       <c r="C183" s="51" t="s">
-        <v>2518</v>
+        <v>2526</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>2519</v>
+        <v>2527</v>
       </c>
       <c r="E183" s="56"/>
       <c r="F183" s="56"/>
@@ -30077,18 +30103,18 @@
       </c>
       <c r="I183" s="56"/>
     </row>
-    <row r="184" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="57" t="s">
         <v>246</v>
       </c>
       <c r="B184" s="56" t="s">
-        <v>2520</v>
+        <v>2528</v>
       </c>
       <c r="C184" s="51" t="s">
-        <v>2521</v>
+        <v>2529</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>2522</v>
+        <v>2530</v>
       </c>
       <c r="E184" s="56"/>
       <c r="F184" s="56"/>
@@ -30098,18 +30124,18 @@
       </c>
       <c r="I184" s="56"/>
     </row>
-    <row r="185" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="57" t="s">
         <v>246</v>
       </c>
-      <c r="B185" s="56" t="s">
-        <v>2523</v>
+      <c r="B185" s="57" t="s">
+        <v>229</v>
       </c>
       <c r="C185" s="51" t="s">
-        <v>2524</v>
+        <v>2166</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>2525</v>
+        <v>2167</v>
       </c>
       <c r="E185" s="56"/>
       <c r="F185" s="56"/>
@@ -30119,96 +30145,96 @@
       </c>
       <c r="I185" s="56"/>
     </row>
-    <row r="186" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="57" t="s">
         <v>246</v>
       </c>
-      <c r="B186" s="56" t="s">
-        <v>2526</v>
-      </c>
-      <c r="C186" s="51" t="s">
-        <v>2527</v>
-      </c>
-      <c r="D186" s="8" t="s">
-        <v>2528</v>
-      </c>
+      <c r="B186" s="56"/>
+      <c r="C186" s="51"/>
+      <c r="D186" s="60"/>
       <c r="E186" s="56"/>
       <c r="F186" s="56"/>
-      <c r="G186" s="56"/>
-      <c r="H186" s="56" t="s">
-        <v>1193</v>
-      </c>
+      <c r="G186" s="56" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H186" s="56"/>
       <c r="I186" s="56"/>
     </row>
-    <row r="187" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="57" t="s">
-        <v>246</v>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="56" t="s">
+        <v>258</v>
       </c>
       <c r="B187" s="56" t="s">
-        <v>2529</v>
+        <v>2531</v>
       </c>
       <c r="C187" s="51" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
       <c r="D187" s="8" t="s">
-        <v>2531</v>
+        <v>2533</v>
       </c>
       <c r="E187" s="56"/>
       <c r="F187" s="56"/>
       <c r="G187" s="56"/>
       <c r="H187" s="56" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="I187" s="56"/>
     </row>
-    <row r="188" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="57" t="s">
-        <v>246</v>
-      </c>
-      <c r="B188" s="57" t="s">
-        <v>229</v>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="56" t="s">
+        <v>258</v>
+      </c>
+      <c r="B188" s="56" t="s">
+        <v>2534</v>
       </c>
       <c r="C188" s="51" t="s">
-        <v>2166</v>
+        <v>2535</v>
       </c>
       <c r="D188" s="8" t="s">
-        <v>2167</v>
+        <v>2536</v>
       </c>
       <c r="E188" s="56"/>
       <c r="F188" s="56"/>
       <c r="G188" s="56"/>
       <c r="H188" s="56" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="I188" s="56"/>
     </row>
-    <row r="189" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="57" t="s">
-        <v>246</v>
-      </c>
-      <c r="B189" s="56"/>
-      <c r="C189" s="51"/>
-      <c r="D189" s="60"/>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="56" t="s">
+        <v>258</v>
+      </c>
+      <c r="B189" s="56" t="s">
+        <v>2537</v>
+      </c>
+      <c r="C189" s="51" t="s">
+        <v>2538</v>
+      </c>
+      <c r="D189" s="8" t="s">
+        <v>2539</v>
+      </c>
       <c r="E189" s="56"/>
       <c r="F189" s="56"/>
-      <c r="G189" s="56" t="s">
-        <v>1161</v>
-      </c>
-      <c r="H189" s="56"/>
+      <c r="G189" s="56"/>
+      <c r="H189" s="56" t="s">
+        <v>1195</v>
+      </c>
       <c r="I189" s="56"/>
     </row>
-    <row r="190" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="56" t="s">
         <v>258</v>
       </c>
       <c r="B190" s="56" t="s">
-        <v>2532</v>
+        <v>2540</v>
       </c>
       <c r="C190" s="51" t="s">
-        <v>2533</v>
+        <v>2541</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>2534</v>
+        <v>2542</v>
       </c>
       <c r="E190" s="56"/>
       <c r="F190" s="56"/>
@@ -30218,18 +30244,18 @@
       </c>
       <c r="I190" s="56"/>
     </row>
-    <row r="191" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="56" t="s">
         <v>258</v>
       </c>
       <c r="B191" s="56" t="s">
-        <v>2535</v>
+        <v>2543</v>
       </c>
       <c r="C191" s="51" t="s">
-        <v>2536</v>
+        <v>2544</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>2537</v>
+        <v>2545</v>
       </c>
       <c r="E191" s="56"/>
       <c r="F191" s="56"/>
@@ -30239,18 +30265,18 @@
       </c>
       <c r="I191" s="56"/>
     </row>
-    <row r="192" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="56" t="s">
         <v>258</v>
       </c>
       <c r="B192" s="56" t="s">
-        <v>2538</v>
+        <v>2546</v>
       </c>
       <c r="C192" s="51" t="s">
-        <v>2539</v>
+        <v>2547</v>
       </c>
       <c r="D192" s="8" t="s">
-        <v>2540</v>
+        <v>2548</v>
       </c>
       <c r="E192" s="56"/>
       <c r="F192" s="56"/>
@@ -30260,18 +30286,18 @@
       </c>
       <c r="I192" s="56"/>
     </row>
-    <row r="193" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="56" t="s">
         <v>258</v>
       </c>
       <c r="B193" s="56" t="s">
-        <v>2541</v>
+        <v>2549</v>
       </c>
       <c r="C193" s="51" t="s">
-        <v>2542</v>
+        <v>2550</v>
       </c>
       <c r="D193" s="8" t="s">
-        <v>2543</v>
+        <v>2551</v>
       </c>
       <c r="E193" s="56"/>
       <c r="F193" s="56"/>
@@ -30281,39 +30307,38 @@
       </c>
       <c r="I193" s="56"/>
     </row>
-    <row r="194" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="56" t="s">
         <v>258</v>
       </c>
       <c r="B194" s="56" t="s">
-        <v>2544</v>
+        <v>1197</v>
       </c>
       <c r="C194" s="51" t="s">
-        <v>2545</v>
+        <v>2552</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>2546</v>
+        <v>2553</v>
       </c>
       <c r="E194" s="56"/>
       <c r="F194" s="56"/>
-      <c r="G194" s="56"/>
       <c r="H194" s="56" t="s">
-        <v>1195</v>
+        <v>1200</v>
       </c>
       <c r="I194" s="56"/>
     </row>
-    <row r="195" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="56" t="s">
         <v>258</v>
       </c>
-      <c r="B195" s="56" t="s">
-        <v>2547</v>
+      <c r="B195" s="57" t="s">
+        <v>229</v>
       </c>
       <c r="C195" s="51" t="s">
-        <v>2548</v>
+        <v>2166</v>
       </c>
       <c r="D195" s="8" t="s">
-        <v>2549</v>
+        <v>2167</v>
       </c>
       <c r="E195" s="56"/>
       <c r="F195" s="56"/>
@@ -30323,119 +30348,114 @@
       </c>
       <c r="I195" s="56"/>
     </row>
-    <row r="196" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="56" t="s">
         <v>258</v>
       </c>
       <c r="B196" s="56" t="s">
-        <v>2550</v>
-      </c>
-      <c r="C196" s="51" t="s">
-        <v>2551</v>
-      </c>
-      <c r="D196" s="8" t="s">
-        <v>2552</v>
+        <v>1161</v>
+      </c>
+      <c r="C196" s="56" t="s">
+        <v>2172</v>
+      </c>
+      <c r="D196" s="56" t="s">
+        <v>2173</v>
       </c>
       <c r="E196" s="56"/>
       <c r="F196" s="56"/>
-      <c r="G196" s="56"/>
       <c r="H196" s="56" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="I196" s="56"/>
     </row>
-    <row r="197" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="56" t="s">
-        <v>258</v>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="57" t="s">
+        <v>287</v>
       </c>
       <c r="B197" s="56" t="s">
-        <v>1197</v>
+        <v>2554</v>
       </c>
       <c r="C197" s="51" t="s">
-        <v>2553</v>
+        <v>2555</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>2554</v>
+        <v>2556</v>
       </c>
       <c r="E197" s="56"/>
       <c r="F197" s="56"/>
-      <c r="H197" s="56" t="s">
-        <v>1200</v>
-      </c>
+      <c r="G197" s="56"/>
+      <c r="H197" s="100"/>
       <c r="I197" s="56"/>
     </row>
-    <row r="198" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="56" t="s">
-        <v>258</v>
-      </c>
-      <c r="B198" s="57" t="s">
-        <v>229</v>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="57" t="s">
+        <v>287</v>
+      </c>
+      <c r="B198" s="56" t="s">
+        <v>2557</v>
       </c>
       <c r="C198" s="51" t="s">
-        <v>2166</v>
+        <v>2558</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>2167</v>
+        <v>2559</v>
       </c>
       <c r="E198" s="56"/>
       <c r="F198" s="56"/>
       <c r="G198" s="56"/>
-      <c r="H198" s="56" t="s">
-        <v>1195</v>
-      </c>
+      <c r="H198" s="56"/>
       <c r="I198" s="56"/>
     </row>
-    <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="56" t="s">
-        <v>258</v>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="57" t="s">
+        <v>287</v>
       </c>
       <c r="B199" s="56" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C199" s="56" t="s">
-        <v>2172</v>
-      </c>
-      <c r="D199" s="56" t="s">
-        <v>2173</v>
+        <v>2560</v>
+      </c>
+      <c r="C199" s="51" t="s">
+        <v>2561</v>
+      </c>
+      <c r="D199" s="8" t="s">
+        <v>2562</v>
       </c>
       <c r="E199" s="56"/>
       <c r="F199" s="56"/>
-      <c r="H199" s="56" t="s">
-        <v>1201</v>
-      </c>
+      <c r="G199" s="56"/>
+      <c r="H199" s="56"/>
       <c r="I199" s="56"/>
     </row>
-    <row r="200" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="57" t="s">
         <v>287</v>
       </c>
       <c r="B200" s="56" t="s">
-        <v>2555</v>
+        <v>2563</v>
       </c>
       <c r="C200" s="51" t="s">
-        <v>2556</v>
+        <v>2564</v>
       </c>
       <c r="D200" s="8" t="s">
-        <v>2557</v>
+        <v>2565</v>
       </c>
       <c r="E200" s="56"/>
       <c r="F200" s="56"/>
       <c r="G200" s="56"/>
-      <c r="H200" s="100"/>
+      <c r="H200" s="56"/>
       <c r="I200" s="56"/>
     </row>
-    <row r="201" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="57" t="s">
         <v>287</v>
       </c>
       <c r="B201" s="56" t="s">
-        <v>2558</v>
+        <v>2566</v>
       </c>
       <c r="C201" s="51" t="s">
-        <v>2559</v>
+        <v>2567</v>
       </c>
       <c r="D201" s="8" t="s">
-        <v>2560</v>
+        <v>2568</v>
       </c>
       <c r="E201" s="56"/>
       <c r="F201" s="56"/>
@@ -30443,37 +30463,39 @@
       <c r="H201" s="56"/>
       <c r="I201" s="56"/>
     </row>
-    <row r="202" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="57" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B202" s="56" t="s">
-        <v>2561</v>
+        <v>2554</v>
       </c>
       <c r="C202" s="51" t="s">
-        <v>2562</v>
+        <v>2555</v>
       </c>
       <c r="D202" s="8" t="s">
-        <v>2563</v>
+        <v>2556</v>
       </c>
       <c r="E202" s="56"/>
       <c r="F202" s="56"/>
       <c r="G202" s="56"/>
-      <c r="H202" s="56"/>
+      <c r="H202" s="100" t="s">
+        <v>1213</v>
+      </c>
       <c r="I202" s="56"/>
     </row>
-    <row r="203" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="57" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B203" s="56" t="s">
-        <v>2564</v>
+        <v>2557</v>
       </c>
       <c r="C203" s="51" t="s">
-        <v>2565</v>
+        <v>2558</v>
       </c>
       <c r="D203" s="8" t="s">
-        <v>2566</v>
+        <v>2559</v>
       </c>
       <c r="E203" s="56"/>
       <c r="F203" s="56"/>
@@ -30481,18 +30503,18 @@
       <c r="H203" s="56"/>
       <c r="I203" s="56"/>
     </row>
-    <row r="204" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="57" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B204" s="56" t="s">
-        <v>2567</v>
+        <v>2560</v>
       </c>
       <c r="C204" s="51" t="s">
-        <v>2568</v>
+        <v>2561</v>
       </c>
       <c r="D204" s="8" t="s">
-        <v>2569</v>
+        <v>2562</v>
       </c>
       <c r="E204" s="56"/>
       <c r="F204" s="56"/>
@@ -30500,39 +30522,37 @@
       <c r="H204" s="56"/>
       <c r="I204" s="56"/>
     </row>
-    <row r="205" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="57" t="s">
         <v>294</v>
       </c>
       <c r="B205" s="56" t="s">
-        <v>2555</v>
+        <v>2563</v>
       </c>
       <c r="C205" s="51" t="s">
-        <v>2556</v>
+        <v>2564</v>
       </c>
       <c r="D205" s="8" t="s">
-        <v>2557</v>
+        <v>2565</v>
       </c>
       <c r="E205" s="56"/>
       <c r="F205" s="56"/>
       <c r="G205" s="56"/>
-      <c r="H205" s="100" t="s">
-        <v>1213</v>
-      </c>
+      <c r="H205" s="56"/>
       <c r="I205" s="56"/>
     </row>
-    <row r="206" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="57" t="s">
         <v>294</v>
       </c>
       <c r="B206" s="56" t="s">
-        <v>2558</v>
+        <v>2566</v>
       </c>
       <c r="C206" s="51" t="s">
-        <v>2559</v>
+        <v>2567</v>
       </c>
       <c r="D206" s="8" t="s">
-        <v>2560</v>
+        <v>2568</v>
       </c>
       <c r="E206" s="56"/>
       <c r="F206" s="56"/>
@@ -30540,279 +30560,279 @@
       <c r="H206" s="56"/>
       <c r="I206" s="56"/>
     </row>
-    <row r="207" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="57" t="s">
-        <v>294</v>
-      </c>
-      <c r="B207" s="56" t="s">
-        <v>2561</v>
-      </c>
-      <c r="C207" s="51" t="s">
-        <v>2562</v>
-      </c>
-      <c r="D207" s="8" t="s">
-        <v>2563</v>
-      </c>
-      <c r="E207" s="56"/>
-      <c r="F207" s="56"/>
-      <c r="G207" s="56"/>
-      <c r="H207" s="56"/>
-      <c r="I207" s="56"/>
-    </row>
-    <row r="208" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="57" t="s">
-        <v>294</v>
-      </c>
-      <c r="B208" s="56" t="s">
-        <v>2564</v>
-      </c>
-      <c r="C208" s="51" t="s">
-        <v>2565</v>
-      </c>
-      <c r="D208" s="8" t="s">
-        <v>2566</v>
-      </c>
-      <c r="E208" s="56"/>
-      <c r="F208" s="56"/>
-      <c r="G208" s="56"/>
-      <c r="H208" s="56"/>
-      <c r="I208" s="56"/>
-    </row>
-    <row r="209" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="57" t="s">
-        <v>294</v>
-      </c>
-      <c r="B209" s="56" t="s">
-        <v>2567</v>
-      </c>
-      <c r="C209" s="51" t="s">
-        <v>2568</v>
-      </c>
-      <c r="D209" s="8" t="s">
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="69" t="s">
+        <v>847</v>
+      </c>
+      <c r="B207" s="69" t="s">
+        <v>2428</v>
+      </c>
+      <c r="C207" s="69" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D207" s="69" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="69" t="s">
+        <v>847</v>
+      </c>
+      <c r="B208" s="69" t="s">
+        <v>2436</v>
+      </c>
+      <c r="C208" s="69" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D208" s="69" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="69" t="s">
+        <v>847</v>
+      </c>
+      <c r="B209" s="69" t="s">
         <v>2569</v>
       </c>
-      <c r="E209" s="56"/>
-      <c r="F209" s="56"/>
-      <c r="G209" s="56"/>
-      <c r="H209" s="56"/>
-      <c r="I209" s="56"/>
-    </row>
-    <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C209" s="69" t="s">
+        <v>2570</v>
+      </c>
+      <c r="D209" s="69" t="s">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="69" t="s">
         <v>847</v>
       </c>
       <c r="B210" s="69" t="s">
-        <v>2428</v>
+        <v>2440</v>
       </c>
       <c r="C210" s="69" t="s">
-        <v>2011</v>
+        <v>2572</v>
       </c>
       <c r="D210" s="69" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="69" t="s">
         <v>847</v>
       </c>
-      <c r="B211" s="69" t="s">
-        <v>2436</v>
-      </c>
-      <c r="C211" s="69" t="s">
-        <v>2030</v>
-      </c>
-      <c r="D211" s="69" t="s">
-        <v>2031</v>
-      </c>
-    </row>
-    <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G211" s="69" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="69" t="s">
-        <v>847</v>
+        <v>872</v>
       </c>
       <c r="B212" s="69" t="s">
-        <v>2570</v>
+        <v>2574</v>
       </c>
       <c r="C212" s="69" t="s">
-        <v>2571</v>
+        <v>2575</v>
       </c>
       <c r="D212" s="69" t="s">
-        <v>2572</v>
-      </c>
-    </row>
-    <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2576</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="69" t="s">
-        <v>847</v>
+        <v>872</v>
       </c>
       <c r="B213" s="69" t="s">
-        <v>2440</v>
+        <v>2577</v>
       </c>
       <c r="C213" s="69" t="s">
-        <v>2573</v>
+        <v>2578</v>
       </c>
       <c r="D213" s="69" t="s">
-        <v>2574</v>
-      </c>
-    </row>
-    <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="69" t="s">
-        <v>847</v>
-      </c>
-      <c r="G214" s="69" t="s">
-        <v>2168</v>
-      </c>
-    </row>
-    <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>872</v>
+      </c>
+      <c r="B214" s="69" t="s">
+        <v>2580</v>
+      </c>
+      <c r="C214" s="69" t="s">
+        <v>2581</v>
+      </c>
+      <c r="D214" s="69" t="s">
+        <v>2582</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="69" t="s">
         <v>872</v>
       </c>
       <c r="B215" s="69" t="s">
-        <v>2575</v>
+        <v>2583</v>
       </c>
       <c r="C215" s="69" t="s">
-        <v>2576</v>
+        <v>2584</v>
       </c>
       <c r="D215" s="69" t="s">
-        <v>2577</v>
-      </c>
-    </row>
-    <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="69" t="s">
         <v>872</v>
       </c>
       <c r="B216" s="69" t="s">
-        <v>2578</v>
+        <v>2586</v>
       </c>
       <c r="C216" s="69" t="s">
-        <v>2579</v>
+        <v>2587</v>
       </c>
       <c r="D216" s="69" t="s">
-        <v>2580</v>
-      </c>
-    </row>
-    <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2588</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="69" t="s">
         <v>872</v>
       </c>
       <c r="B217" s="69" t="s">
-        <v>2581</v>
+        <v>2589</v>
       </c>
       <c r="C217" s="69" t="s">
-        <v>2582</v>
+        <v>2590</v>
       </c>
       <c r="D217" s="69" t="s">
-        <v>2583</v>
-      </c>
-    </row>
-    <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2591</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="69" t="s">
         <v>872</v>
       </c>
       <c r="B218" s="69" t="s">
-        <v>2584</v>
+        <v>229</v>
       </c>
       <c r="C218" s="69" t="s">
-        <v>2585</v>
+        <v>2592</v>
       </c>
       <c r="D218" s="69" t="s">
-        <v>2586</v>
-      </c>
-    </row>
-    <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2593</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="69" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="B219" s="69" t="s">
-        <v>2587</v>
+        <v>2428</v>
       </c>
       <c r="C219" s="69" t="s">
-        <v>2588</v>
+        <v>2011</v>
       </c>
       <c r="D219" s="69" t="s">
-        <v>2589</v>
-      </c>
-    </row>
-    <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="69" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="B220" s="69" t="s">
-        <v>2590</v>
+        <v>2436</v>
       </c>
       <c r="C220" s="69" t="s">
-        <v>2591</v>
+        <v>2030</v>
       </c>
       <c r="D220" s="69" t="s">
-        <v>2592</v>
-      </c>
-    </row>
-    <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="69" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="B221" s="69" t="s">
-        <v>229</v>
+        <v>2434</v>
       </c>
       <c r="C221" s="69" t="s">
-        <v>2593</v>
+        <v>2594</v>
       </c>
       <c r="D221" s="69" t="s">
-        <v>2594</v>
-      </c>
-    </row>
-    <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2595</v>
+      </c>
+    </row>
+    <row r="222" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="69" t="s">
         <v>877</v>
       </c>
       <c r="B222" s="69" t="s">
-        <v>2428</v>
+        <v>2435</v>
       </c>
       <c r="C222" s="69" t="s">
-        <v>2011</v>
+        <v>2596</v>
       </c>
       <c r="D222" s="69" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2597</v>
+      </c>
+      <c r="E222" s="69"/>
+      <c r="F222" s="69"/>
+      <c r="G222" s="69"/>
+      <c r="H222" s="69"/>
+      <c r="I222" s="69"/>
+    </row>
+    <row r="223" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="69" t="s">
         <v>877</v>
       </c>
       <c r="B223" s="69" t="s">
-        <v>2436</v>
+        <v>2440</v>
       </c>
       <c r="C223" s="69" t="s">
-        <v>2030</v>
+        <v>2572</v>
       </c>
       <c r="D223" s="69" t="s">
-        <v>2031</v>
-      </c>
-    </row>
-    <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2573</v>
+      </c>
+      <c r="E223" s="69"/>
+      <c r="F223" s="69"/>
+      <c r="G223" s="69"/>
+      <c r="H223" s="69"/>
+      <c r="I223" s="69"/>
+    </row>
+    <row r="224" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="69" t="s">
         <v>877</v>
       </c>
       <c r="B224" s="69" t="s">
-        <v>2434</v>
+        <v>229</v>
       </c>
       <c r="C224" s="69" t="s">
-        <v>2595</v>
+        <v>2598</v>
       </c>
       <c r="D224" s="69" t="s">
-        <v>2596</v>
-      </c>
-    </row>
-    <row r="225" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="69" t="s">
-        <v>877</v>
-      </c>
-      <c r="B225" s="69" t="s">
-        <v>2435</v>
-      </c>
-      <c r="C225" s="69" t="s">
-        <v>2597</v>
-      </c>
-      <c r="D225" s="69" t="s">
-        <v>2598</v>
+        <v>2599</v>
+      </c>
+      <c r="E224" s="69"/>
+      <c r="F224" s="69"/>
+      <c r="G224" s="69"/>
+      <c r="H224" s="69"/>
+      <c r="I224" s="69"/>
+    </row>
+    <row r="225" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="57" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B225" s="60" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C225" s="8" t="s">
+        <v>2600</v>
+      </c>
+      <c r="D225" s="8" t="s">
+        <v>2601</v>
       </c>
       <c r="E225" s="69"/>
       <c r="F225" s="69"/>
@@ -30820,96 +30840,100 @@
       <c r="H225" s="69"/>
       <c r="I225" s="69"/>
     </row>
-    <row r="226" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="69" t="s">
-        <v>877</v>
+    <row r="226" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="57" t="s">
+        <v>1042</v>
       </c>
       <c r="B226" s="69" t="s">
-        <v>2440</v>
-      </c>
-      <c r="C226" s="69" t="s">
-        <v>2573</v>
-      </c>
-      <c r="D226" s="69" t="s">
-        <v>2574</v>
+        <v>2602</v>
+      </c>
+      <c r="C226" s="8" t="s">
+        <v>2603</v>
+      </c>
+      <c r="D226" s="8" t="s">
+        <v>2604</v>
       </c>
       <c r="E226" s="69"/>
       <c r="F226" s="69"/>
       <c r="G226" s="69"/>
-      <c r="H226" s="69"/>
+      <c r="H226" s="54" t="s">
+        <v>1156</v>
+      </c>
       <c r="I226" s="69"/>
     </row>
-    <row r="227" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="69" t="s">
-        <v>877</v>
+    <row r="227" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="57" t="s">
+        <v>1042</v>
       </c>
       <c r="B227" s="69" t="s">
-        <v>229</v>
-      </c>
-      <c r="C227" s="69" t="s">
-        <v>2599</v>
-      </c>
-      <c r="D227" s="69" t="s">
-        <v>2600</v>
+        <v>2605</v>
+      </c>
+      <c r="C227" s="8" t="s">
+        <v>2606</v>
+      </c>
+      <c r="D227" s="8" t="s">
+        <v>2607</v>
       </c>
       <c r="E227" s="69"/>
       <c r="F227" s="69"/>
       <c r="G227" s="69"/>
-      <c r="H227" s="69"/>
+      <c r="H227" s="54" t="s">
+        <v>1156</v>
+      </c>
       <c r="I227" s="69"/>
     </row>
-    <row r="228" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="57" t="s">
         <v>1042</v>
       </c>
-      <c r="B228" s="60" t="s">
-        <v>1248</v>
+      <c r="B228" s="69" t="s">
+        <v>2608</v>
       </c>
       <c r="C228" s="8" t="s">
-        <v>2601</v>
-      </c>
-      <c r="D228" s="8" t="s">
-        <v>2602</v>
+        <v>2609</v>
+      </c>
+      <c r="D228" s="54" t="s">
+        <v>2610</v>
       </c>
       <c r="E228" s="69"/>
       <c r="F228" s="69"/>
       <c r="G228" s="69"/>
-      <c r="H228" s="69"/>
+      <c r="H228" s="54" t="s">
+        <v>1156</v>
+      </c>
       <c r="I228" s="69"/>
     </row>
-    <row r="229" s="53" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="57" t="s">
         <v>1042</v>
       </c>
       <c r="B229" s="69" t="s">
-        <v>2603</v>
+        <v>2611</v>
       </c>
       <c r="C229" s="8" t="s">
-        <v>2604</v>
-      </c>
-      <c r="D229" s="8" t="s">
-        <v>2605</v>
+        <v>2612</v>
+      </c>
+      <c r="D229" s="51" t="s">
+        <v>2613</v>
       </c>
       <c r="E229" s="69"/>
       <c r="F229" s="69"/>
       <c r="G229" s="69"/>
-      <c r="H229" s="54" t="s">
-        <v>1156</v>
-      </c>
+      <c r="H229" s="69"/>
       <c r="I229" s="69"/>
     </row>
-    <row r="230" s="53" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="57" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="B230" s="69" t="s">
-        <v>2606</v>
+        <v>2614</v>
       </c>
       <c r="C230" s="8" t="s">
-        <v>2607</v>
+        <v>2615</v>
       </c>
       <c r="D230" s="8" t="s">
-        <v>2608</v>
+        <v>2616</v>
       </c>
       <c r="E230" s="69"/>
       <c r="F230" s="69"/>
@@ -30919,39 +30943,39 @@
       </c>
       <c r="I230" s="69"/>
     </row>
-    <row r="231" s="53" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="57" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="B231" s="69" t="s">
-        <v>2609</v>
+        <v>2617</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>2610</v>
-      </c>
-      <c r="D231" s="54" t="s">
-        <v>2611</v>
+        <v>2618</v>
+      </c>
+      <c r="D231" s="8" t="s">
+        <v>2619</v>
       </c>
       <c r="E231" s="69"/>
       <c r="F231" s="69"/>
       <c r="G231" s="69"/>
       <c r="H231" s="54" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="I231" s="69"/>
     </row>
-    <row r="232" s="53" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="57" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="B232" s="69" t="s">
-        <v>2612</v>
+        <v>2620</v>
       </c>
       <c r="C232" s="8" t="s">
-        <v>2613</v>
-      </c>
-      <c r="D232" s="51" t="s">
-        <v>2614</v>
+        <v>2621</v>
+      </c>
+      <c r="D232" s="8" t="s">
+        <v>2622</v>
       </c>
       <c r="E232" s="69"/>
       <c r="F232" s="69"/>
@@ -30959,60 +30983,56 @@
       <c r="H232" s="69"/>
       <c r="I232" s="69"/>
     </row>
-    <row r="233" s="53" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="57" t="s">
-        <v>1048</v>
+        <v>2623</v>
       </c>
       <c r="B233" s="69" t="s">
-        <v>2615</v>
-      </c>
-      <c r="C233" s="8" t="s">
-        <v>2616</v>
+        <v>1157</v>
+      </c>
+      <c r="C233" s="54" t="s">
+        <v>2624</v>
       </c>
       <c r="D233" s="8" t="s">
-        <v>2617</v>
+        <v>2625</v>
       </c>
       <c r="E233" s="69"/>
       <c r="F233" s="69"/>
       <c r="G233" s="69"/>
-      <c r="H233" s="54" t="s">
-        <v>1156</v>
-      </c>
+      <c r="H233" s="69"/>
       <c r="I233" s="69"/>
     </row>
-    <row r="234" s="53" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="57" t="s">
-        <v>1048</v>
+        <v>2623</v>
       </c>
       <c r="B234" s="69" t="s">
-        <v>2618</v>
-      </c>
-      <c r="C234" s="8" t="s">
-        <v>2619</v>
-      </c>
-      <c r="D234" s="8" t="s">
-        <v>2620</v>
+        <v>1215</v>
+      </c>
+      <c r="C234" s="54" t="s">
+        <v>2626</v>
+      </c>
+      <c r="D234" s="51" t="s">
+        <v>2627</v>
       </c>
       <c r="E234" s="69"/>
       <c r="F234" s="69"/>
       <c r="G234" s="69"/>
-      <c r="H234" s="54" t="s">
-        <v>1155</v>
-      </c>
+      <c r="H234" s="69"/>
       <c r="I234" s="69"/>
     </row>
-    <row r="235" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="57" t="s">
-        <v>1048</v>
+        <v>1078</v>
       </c>
       <c r="B235" s="69" t="s">
-        <v>2621</v>
+        <v>2628</v>
       </c>
       <c r="C235" s="8" t="s">
-        <v>2622</v>
-      </c>
-      <c r="D235" s="8" t="s">
-        <v>2623</v>
+        <v>2629</v>
+      </c>
+      <c r="D235" s="54" t="s">
+        <v>2630</v>
       </c>
       <c r="E235" s="69"/>
       <c r="F235" s="69"/>
@@ -31020,18 +31040,18 @@
       <c r="H235" s="69"/>
       <c r="I235" s="69"/>
     </row>
-    <row r="236" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="57" t="s">
-        <v>2624</v>
+        <v>1078</v>
       </c>
       <c r="B236" s="69" t="s">
-        <v>1157</v>
-      </c>
-      <c r="C236" s="54" t="s">
-        <v>2625</v>
-      </c>
-      <c r="D236" s="8" t="s">
-        <v>2626</v>
+        <v>2631</v>
+      </c>
+      <c r="C236" s="8" t="s">
+        <v>2632</v>
+      </c>
+      <c r="D236" s="54" t="s">
+        <v>2633</v>
       </c>
       <c r="E236" s="69"/>
       <c r="F236" s="69"/>
@@ -31039,18 +31059,18 @@
       <c r="H236" s="69"/>
       <c r="I236" s="69"/>
     </row>
-    <row r="237" s="53" customFormat="true" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="57" t="s">
-        <v>2624</v>
+        <v>1078</v>
       </c>
       <c r="B237" s="69" t="s">
-        <v>1215</v>
-      </c>
-      <c r="C237" s="54" t="s">
-        <v>2627</v>
-      </c>
-      <c r="D237" s="51" t="s">
-        <v>2628</v>
+        <v>2634</v>
+      </c>
+      <c r="C237" s="8" t="s">
+        <v>2635</v>
+      </c>
+      <c r="D237" s="54" t="s">
+        <v>2636</v>
       </c>
       <c r="E237" s="69"/>
       <c r="F237" s="69"/>
@@ -31058,18 +31078,18 @@
       <c r="H237" s="69"/>
       <c r="I237" s="69"/>
     </row>
-    <row r="238" s="53" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="57" t="s">
         <v>1078</v>
       </c>
       <c r="B238" s="69" t="s">
-        <v>2629</v>
+        <v>2637</v>
       </c>
       <c r="C238" s="8" t="s">
-        <v>2630</v>
+        <v>2638</v>
       </c>
       <c r="D238" s="54" t="s">
-        <v>2631</v>
+        <v>2639</v>
       </c>
       <c r="E238" s="69"/>
       <c r="F238" s="69"/>
@@ -31077,37 +31097,32 @@
       <c r="H238" s="69"/>
       <c r="I238" s="69"/>
     </row>
-    <row r="239" s="53" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="57" t="s">
         <v>1078</v>
       </c>
       <c r="B239" s="69" t="s">
-        <v>2632</v>
+        <v>2640</v>
       </c>
       <c r="C239" s="8" t="s">
-        <v>2633</v>
+        <v>2641</v>
       </c>
       <c r="D239" s="54" t="s">
-        <v>2634</v>
-      </c>
-      <c r="E239" s="69"/>
-      <c r="F239" s="69"/>
-      <c r="G239" s="69"/>
-      <c r="H239" s="69"/>
-      <c r="I239" s="69"/>
-    </row>
-    <row r="240" s="53" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2642</v>
+      </c>
+    </row>
+    <row r="240" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="57" t="s">
         <v>1078</v>
       </c>
       <c r="B240" s="69" t="s">
-        <v>2635</v>
+        <v>2643</v>
       </c>
       <c r="C240" s="8" t="s">
-        <v>2636</v>
+        <v>2644</v>
       </c>
       <c r="D240" s="54" t="s">
-        <v>2637</v>
+        <v>2645</v>
       </c>
       <c r="E240" s="69"/>
       <c r="F240" s="69"/>
@@ -31115,155 +31130,160 @@
       <c r="H240" s="69"/>
       <c r="I240" s="69"/>
     </row>
-    <row r="241" s="53" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" s="53" customFormat="true" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="57" t="s">
         <v>1078</v>
       </c>
-      <c r="B241" s="69" t="s">
-        <v>2638</v>
-      </c>
-      <c r="C241" s="8" t="s">
-        <v>2639</v>
-      </c>
-      <c r="D241" s="54" t="s">
-        <v>2640</v>
-      </c>
+      <c r="B241" s="69"/>
+      <c r="C241" s="8"/>
+      <c r="D241" s="8"/>
       <c r="E241" s="69"/>
       <c r="F241" s="69"/>
-      <c r="G241" s="69"/>
+      <c r="G241" s="56" t="s">
+        <v>2168</v>
+      </c>
       <c r="H241" s="69"/>
       <c r="I241" s="69"/>
     </row>
-    <row r="242" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="57" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B242" s="69" t="s">
-        <v>2641</v>
-      </c>
-      <c r="C242" s="8" t="s">
-        <v>2642</v>
-      </c>
-      <c r="D242" s="54" t="s">
-        <v>2643</v>
-      </c>
-    </row>
-    <row r="243" s="53" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="57" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B243" s="69" t="s">
-        <v>2644</v>
-      </c>
-      <c r="C243" s="8" t="s">
-        <v>2645</v>
-      </c>
-      <c r="D243" s="54" t="s">
+    <row r="242" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="53" t="s">
+        <v>936</v>
+      </c>
+      <c r="B242" s="53" t="s">
         <v>2646</v>
       </c>
-      <c r="E243" s="69"/>
-      <c r="F243" s="69"/>
-      <c r="G243" s="69"/>
-      <c r="H243" s="69"/>
-      <c r="I243" s="69"/>
-    </row>
-    <row r="244" s="53" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="57" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B244" s="69"/>
-      <c r="C244" s="8"/>
-      <c r="D244" s="8"/>
-      <c r="E244" s="69"/>
-      <c r="F244" s="69"/>
-      <c r="G244" s="56" t="s">
-        <v>2168</v>
-      </c>
-      <c r="H244" s="69"/>
-      <c r="I244" s="69"/>
-    </row>
-    <row r="245" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C242" s="53" t="s">
+        <v>2647</v>
+      </c>
+      <c r="D242" s="53" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="243" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="53" t="s">
+        <v>936</v>
+      </c>
+      <c r="B243" s="53" t="s">
+        <v>2560</v>
+      </c>
+      <c r="C243" s="53" t="s">
+        <v>2649</v>
+      </c>
+      <c r="D243" s="53" t="s">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="244" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="53" t="s">
+        <v>936</v>
+      </c>
+      <c r="B244" s="53" t="s">
+        <v>2651</v>
+      </c>
+      <c r="C244" s="53" t="s">
+        <v>2652</v>
+      </c>
+      <c r="D244" s="53" t="s">
+        <v>2653</v>
+      </c>
+    </row>
+    <row r="245" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="53" t="s">
         <v>936</v>
       </c>
       <c r="B245" s="53" t="s">
-        <v>2647</v>
+        <v>2654</v>
       </c>
       <c r="C245" s="53" t="s">
-        <v>2648</v>
+        <v>2655</v>
       </c>
       <c r="D245" s="53" t="s">
-        <v>2649</v>
-      </c>
-    </row>
-    <row r="246" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2656</v>
+      </c>
+    </row>
+    <row r="246" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="53" t="s">
         <v>936</v>
       </c>
       <c r="B246" s="53" t="s">
-        <v>2561</v>
+        <v>2657</v>
       </c>
       <c r="C246" s="53" t="s">
-        <v>2650</v>
+        <v>2658</v>
       </c>
       <c r="D246" s="53" t="s">
-        <v>2651</v>
-      </c>
-    </row>
-    <row r="247" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="53" t="s">
-        <v>936</v>
-      </c>
-      <c r="B247" s="53" t="s">
-        <v>2652</v>
-      </c>
-      <c r="C247" s="53" t="s">
-        <v>2653</v>
-      </c>
-      <c r="D247" s="53" t="s">
-        <v>2654</v>
-      </c>
-    </row>
-    <row r="248" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="53" t="s">
-        <v>936</v>
-      </c>
-      <c r="B248" s="53" t="s">
-        <v>2655</v>
-      </c>
-      <c r="C248" s="53" t="s">
-        <v>2656</v>
-      </c>
-      <c r="D248" s="53" t="s">
-        <v>2657</v>
-      </c>
-    </row>
-    <row r="249" s="53" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="53" t="s">
-        <v>936</v>
-      </c>
-      <c r="B249" s="53" t="s">
-        <v>2658</v>
-      </c>
-      <c r="C249" s="53" t="s">
         <v>2659</v>
       </c>
-      <c r="D249" s="53" t="s">
+    </row>
+    <row r="247" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="69" t="s">
+        <v>964</v>
+      </c>
+      <c r="B247" s="69" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C247" s="60" t="s">
         <v>2660</v>
       </c>
-    </row>
-    <row r="250" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D247" s="60" t="s">
+        <v>2661</v>
+      </c>
+      <c r="E247" s="69"/>
+      <c r="F247" s="69"/>
+      <c r="G247" s="69"/>
+      <c r="H247" s="69"/>
+      <c r="I247" s="69"/>
+    </row>
+    <row r="248" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="69" t="s">
+        <v>964</v>
+      </c>
+      <c r="B248" s="69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C248" s="60" t="s">
+        <v>2662</v>
+      </c>
+      <c r="D248" s="60" t="s">
+        <v>2663</v>
+      </c>
+      <c r="E248" s="69"/>
+      <c r="F248" s="69"/>
+      <c r="G248" s="69"/>
+      <c r="H248" s="69"/>
+      <c r="I248" s="69"/>
+    </row>
+    <row r="249" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="69" t="s">
+        <v>964</v>
+      </c>
+      <c r="B249" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="C249" s="60" t="s">
+        <v>2664</v>
+      </c>
+      <c r="D249" s="60" t="s">
+        <v>2665</v>
+      </c>
+      <c r="E249" s="69"/>
+      <c r="F249" s="69"/>
+      <c r="G249" s="69"/>
+      <c r="H249" s="69"/>
+      <c r="I249" s="69"/>
+    </row>
+    <row r="250" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="69" t="s">
         <v>964</v>
       </c>
       <c r="B250" s="69" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="C250" s="60" t="s">
-        <v>2661</v>
+        <v>2666</v>
       </c>
       <c r="D250" s="60" t="s">
-        <v>2662</v>
+        <v>2667</v>
       </c>
       <c r="E250" s="69"/>
       <c r="F250" s="69"/>
@@ -31271,18 +31291,18 @@
       <c r="H250" s="69"/>
       <c r="I250" s="69"/>
     </row>
-    <row r="251" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="69" t="s">
         <v>964</v>
       </c>
       <c r="B251" s="69" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="C251" s="60" t="s">
-        <v>2663</v>
+        <v>2668</v>
       </c>
       <c r="D251" s="60" t="s">
-        <v>2664</v>
+        <v>2669</v>
       </c>
       <c r="E251" s="69"/>
       <c r="F251" s="69"/>
@@ -31290,18 +31310,18 @@
       <c r="H251" s="69"/>
       <c r="I251" s="69"/>
     </row>
-    <row r="252" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="69" t="s">
-        <v>964</v>
+        <v>1002</v>
       </c>
       <c r="B252" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="C252" s="60" t="s">
-        <v>2665</v>
+      <c r="C252" s="51" t="s">
+        <v>2670</v>
       </c>
       <c r="D252" s="60" t="s">
-        <v>2666</v>
+        <v>2671</v>
       </c>
       <c r="E252" s="69"/>
       <c r="F252" s="69"/>
@@ -31309,18 +31329,18 @@
       <c r="H252" s="69"/>
       <c r="I252" s="69"/>
     </row>
-    <row r="253" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="69" t="s">
-        <v>964</v>
+        <v>1002</v>
       </c>
       <c r="B253" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="C253" s="60" t="s">
-        <v>2667</v>
-      </c>
-      <c r="D253" s="60" t="s">
-        <v>2668</v>
+      <c r="C253" s="51" t="s">
+        <v>2672</v>
+      </c>
+      <c r="D253" s="54" t="s">
+        <v>2673</v>
       </c>
       <c r="E253" s="69"/>
       <c r="F253" s="69"/>
@@ -31328,18 +31348,18 @@
       <c r="H253" s="69"/>
       <c r="I253" s="69"/>
     </row>
-    <row r="254" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="69" t="s">
-        <v>964</v>
+        <v>1002</v>
       </c>
       <c r="B254" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="C254" s="60" t="s">
-        <v>2669</v>
-      </c>
-      <c r="D254" s="60" t="s">
-        <v>2670</v>
+      <c r="C254" s="51" t="s">
+        <v>2674</v>
+      </c>
+      <c r="D254" s="54" t="s">
+        <v>2675</v>
       </c>
       <c r="E254" s="69"/>
       <c r="F254" s="69"/>
@@ -31347,18 +31367,18 @@
       <c r="H254" s="69"/>
       <c r="I254" s="69"/>
     </row>
-    <row r="255" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" s="53" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="69" t="s">
         <v>1002</v>
       </c>
       <c r="B255" s="69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C255" s="51" t="s">
-        <v>2671</v>
-      </c>
-      <c r="D255" s="60" t="s">
-        <v>2672</v>
+        <v>2676</v>
+      </c>
+      <c r="D255" s="54" t="s">
+        <v>2677</v>
       </c>
       <c r="E255" s="69"/>
       <c r="F255" s="69"/>
@@ -31366,105 +31386,51 @@
       <c r="H255" s="69"/>
       <c r="I255" s="69"/>
     </row>
-    <row r="256" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="69" t="s">
         <v>1002</v>
       </c>
       <c r="B256" s="69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C256" s="51" t="s">
-        <v>2673</v>
+        <v>2678</v>
       </c>
       <c r="D256" s="54" t="s">
-        <v>2674</v>
-      </c>
-      <c r="E256" s="69"/>
-      <c r="F256" s="69"/>
-      <c r="G256" s="69"/>
-      <c r="H256" s="69"/>
-      <c r="I256" s="69"/>
-    </row>
-    <row r="257" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2679</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="69" t="s">
         <v>1002</v>
       </c>
       <c r="B257" s="69" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="C257" s="51" t="s">
-        <v>2675</v>
+        <v>2680</v>
       </c>
       <c r="D257" s="54" t="s">
-        <v>2676</v>
-      </c>
-      <c r="E257" s="69"/>
-      <c r="F257" s="69"/>
-      <c r="G257" s="69"/>
-      <c r="H257" s="69"/>
-      <c r="I257" s="69"/>
-    </row>
-    <row r="258" s="53" customFormat="true" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="69" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B258" s="69" t="n">
-        <v>3</v>
-      </c>
-      <c r="C258" s="51" t="s">
-        <v>2677</v>
-      </c>
-      <c r="D258" s="54" t="s">
-        <v>2678</v>
-      </c>
-      <c r="E258" s="69"/>
-      <c r="F258" s="69"/>
-      <c r="G258" s="69"/>
-      <c r="H258" s="69"/>
-      <c r="I258" s="69"/>
-    </row>
-    <row r="259" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="69" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B259" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="C259" s="51" t="s">
-        <v>2679</v>
-      </c>
-      <c r="D259" s="54" t="s">
-        <v>2680</v>
-      </c>
-    </row>
-    <row r="260" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="69" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B260" s="69" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C260" s="51" t="s">
-        <v>2681</v>
-      </c>
-      <c r="D260" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="B258" s="69" t="s">
         <v>2682</v>
       </c>
-    </row>
-    <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="69" t="s">
-        <v>39</v>
-      </c>
-      <c r="B261" s="69" t="s">
+      <c r="C258" s="69" t="s">
         <v>2683</v>
       </c>
-      <c r="C261" s="69" t="s">
+      <c r="D258" s="69" t="s">
         <v>2684</v>
       </c>
-      <c r="D261" s="69" t="s">
-        <v>2685</v>
-      </c>
-    </row>
+    </row>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -31717,26 +31683,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ac790928-ed95-48e6-acd0-329fd16a4415">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ed79b9f6-c8ab-4e15-9256-843732862240" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F850EC8E-E579-43A2-927D-000EC4364E71}">
   <ds:schemaRefs>
@@ -31754,23 +31700,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC2AE5FC-62C2-4956-8F1C-8F3F7A4948A7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{693D498A-297B-4FC6-9B07-DBE41CE079B1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac790928-ed95-48e6-acd0-329fd16a4415"/>
-    <ds:schemaRef ds:uri="ed79b9f6-c8ab-4e15-9256-843732862240"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4895" uniqueCount="2683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4899" uniqueCount="2687">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -7173,6 +7173,18 @@
   </si>
   <si>
     <t xml:space="preserve">You must confirm that the access code is correctly typed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CheckMagicEmail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un lien de connexion a été envoyé à l’adresse courriel que vous avez fournie. Si vous ne le trouvez pas dans votre boîte de réception, vérifiez vos pourriels.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A connection link has been sent to the email address you provided. If you do not see it in your inbox, check your spam folder.</t>
   </si>
   <si>
     <t xml:space="preserve">choicesName</t>
@@ -9036,7 +9048,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9383,6 +9395,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -23234,7 +23250,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F265"/>
+  <dimension ref="A1:F1048576"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="50" width="16.66"/>
@@ -27327,6 +27343,22 @@
         <v>2168</v>
       </c>
     </row>
+    <row r="266" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="50" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B266" s="87" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C266" s="87" t="s">
+        <v>2171</v>
+      </c>
+      <c r="D266" s="87" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <autoFilter ref="A1:F260"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -27357,32 +27389,32 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="87" t="s">
-        <v>2169</v>
-      </c>
-      <c r="B1" s="87" t="s">
+      <c r="A1" s="88" t="s">
+        <v>2173</v>
+      </c>
+      <c r="B1" s="88" t="s">
         <v>1159</v>
       </c>
-      <c r="C1" s="87" t="s">
+      <c r="C1" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="87" t="s">
+      <c r="D1" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="88" t="s">
+      <c r="E1" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="88" t="s">
+      <c r="F1" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="87" t="s">
-        <v>2170</v>
-      </c>
-      <c r="H1" s="87" t="s">
+      <c r="G1" s="88" t="s">
+        <v>2174</v>
+      </c>
+      <c r="H1" s="88" t="s">
         <v>12</v>
       </c>
       <c r="I1" s="66" t="s">
-        <v>2171</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27393,10 +27425,10 @@
         <v>1167</v>
       </c>
       <c r="C2" s="53" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="D2" s="53" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="E2" s="53"/>
       <c r="F2" s="53"/>
@@ -27411,10 +27443,10 @@
         <v>1225</v>
       </c>
       <c r="C3" s="53" t="s">
-        <v>2174</v>
+        <v>2178</v>
       </c>
       <c r="D3" s="53" t="s">
-        <v>2175</v>
+        <v>2179</v>
       </c>
       <c r="E3" s="53"/>
       <c r="F3" s="53"/>
@@ -27429,10 +27461,10 @@
         <v>229</v>
       </c>
       <c r="C4" s="53" t="s">
-        <v>2176</v>
+        <v>2180</v>
       </c>
       <c r="D4" s="53" t="s">
-        <v>2177</v>
+        <v>2181</v>
       </c>
       <c r="E4" s="53"/>
       <c r="F4" s="53"/>
@@ -27441,7 +27473,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="53" t="s">
-        <v>2178</v>
+        <v>2182</v>
       </c>
       <c r="B5" s="53" t="s">
         <v>229</v>
@@ -27459,16 +27491,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="53" t="s">
-        <v>2179</v>
+        <v>2183</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>2179</v>
+        <v>2183</v>
       </c>
       <c r="C6" s="53" t="s">
-        <v>2180</v>
+        <v>2184</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>2181</v>
+        <v>2185</v>
       </c>
       <c r="E6" s="53"/>
       <c r="F6" s="53"/>
@@ -27483,10 +27515,10 @@
         <v>1171</v>
       </c>
       <c r="C7" s="53" t="s">
-        <v>2182</v>
+        <v>2186</v>
       </c>
       <c r="D7" s="53" t="s">
-        <v>2183</v>
+        <v>2187</v>
       </c>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
@@ -27545,7 +27577,7 @@
       <c r="E11" s="53"/>
       <c r="F11" s="53"/>
       <c r="G11" s="53" t="s">
-        <v>2179</v>
+        <v>2183</v>
       </c>
       <c r="H11" s="53"/>
     </row>
@@ -27599,10 +27631,10 @@
         <v>1167</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>2184</v>
+        <v>2188</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>2185</v>
+        <v>2189</v>
       </c>
       <c r="E15" s="51"/>
       <c r="F15" s="51"/>
@@ -27618,10 +27650,10 @@
         <v>1225</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>2186</v>
+        <v>2190</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>2187</v>
+        <v>2191</v>
       </c>
       <c r="E16" s="51"/>
       <c r="F16" s="51"/>
@@ -27630,17 +27662,17 @@
       <c r="I16" s="53"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="89" t="s">
-        <v>2188</v>
+      <c r="A17" s="90" t="s">
+        <v>2192</v>
       </c>
       <c r="B17" s="53" t="s">
-        <v>2189</v>
+        <v>2193</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>2190</v>
+        <v>2194</v>
       </c>
       <c r="D17" s="53" t="s">
-        <v>2191</v>
+        <v>2195</v>
       </c>
       <c r="E17" s="53"/>
       <c r="F17" s="53"/>
@@ -27648,17 +27680,17 @@
       <c r="H17" s="53"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="89" t="s">
-        <v>2188</v>
+      <c r="A18" s="90" t="s">
+        <v>2192</v>
       </c>
       <c r="B18" s="53" t="s">
-        <v>2192</v>
+        <v>2196</v>
       </c>
       <c r="C18" s="53" t="s">
-        <v>2193</v>
+        <v>2197</v>
       </c>
       <c r="D18" s="53" t="s">
-        <v>2194</v>
+        <v>2198</v>
       </c>
       <c r="E18" s="53"/>
       <c r="F18" s="53"/>
@@ -27666,8 +27698,8 @@
       <c r="H18" s="53"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="89" t="s">
-        <v>2188</v>
+      <c r="A19" s="90" t="s">
+        <v>2192</v>
       </c>
       <c r="B19" s="53"/>
       <c r="C19" s="53"/>
@@ -27680,17 +27712,17 @@
       <c r="H19" s="53"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="89" t="s">
+      <c r="A20" s="90" t="s">
         <v>187</v>
       </c>
       <c r="B20" s="53" t="s">
-        <v>2189</v>
+        <v>2193</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>2190</v>
+        <v>2194</v>
       </c>
       <c r="D20" s="53" t="s">
-        <v>2195</v>
+        <v>2199</v>
       </c>
       <c r="E20" s="53"/>
       <c r="F20" s="53"/>
@@ -27698,17 +27730,17 @@
       <c r="H20" s="53"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="89" t="s">
+      <c r="A21" s="90" t="s">
         <v>187</v>
       </c>
       <c r="B21" s="53" t="s">
-        <v>2192</v>
+        <v>2196</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>2193</v>
+        <v>2197</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>2196</v>
+        <v>2200</v>
       </c>
       <c r="E21" s="53"/>
       <c r="F21" s="53"/>
@@ -27716,17 +27748,17 @@
       <c r="H21" s="53"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="89" t="s">
+      <c r="A22" s="90" t="s">
         <v>187</v>
       </c>
       <c r="B22" s="53" t="s">
         <v>189</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>2197</v>
+        <v>2201</v>
       </c>
       <c r="D22" s="53" t="s">
-        <v>2198</v>
+        <v>2202</v>
       </c>
       <c r="E22" s="53"/>
       <c r="F22" s="53"/>
@@ -27734,7 +27766,7 @@
       <c r="H22" s="53"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="89" t="s">
+      <c r="A23" s="90" t="s">
         <v>187</v>
       </c>
       <c r="B23" s="53"/>
@@ -27752,13 +27784,13 @@
         <v>306</v>
       </c>
       <c r="B24" s="53" t="s">
-        <v>2199</v>
+        <v>2203</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>2200</v>
+        <v>2204</v>
       </c>
       <c r="D24" s="53" t="s">
-        <v>2201</v>
+        <v>2205</v>
       </c>
       <c r="E24" s="53"/>
       <c r="F24" s="53"/>
@@ -27770,13 +27802,13 @@
         <v>306</v>
       </c>
       <c r="B25" s="53" t="s">
-        <v>2202</v>
+        <v>2206</v>
       </c>
       <c r="C25" s="53" t="s">
-        <v>2203</v>
+        <v>2207</v>
       </c>
       <c r="D25" s="53" t="s">
-        <v>2204</v>
+        <v>2208</v>
       </c>
       <c r="E25" s="53"/>
       <c r="F25" s="53"/>
@@ -27802,13 +27834,13 @@
         <v>299</v>
       </c>
       <c r="B27" s="53" t="s">
-        <v>2199</v>
+        <v>2203</v>
       </c>
       <c r="C27" s="53" t="s">
-        <v>2205</v>
+        <v>2209</v>
       </c>
       <c r="D27" s="53" t="s">
-        <v>2206</v>
+        <v>2210</v>
       </c>
       <c r="E27" s="53"/>
       <c r="F27" s="53"/>
@@ -27820,13 +27852,13 @@
         <v>299</v>
       </c>
       <c r="B28" s="53" t="s">
-        <v>2202</v>
+        <v>2206</v>
       </c>
       <c r="C28" s="53" t="s">
-        <v>2207</v>
+        <v>2211</v>
       </c>
       <c r="D28" s="53" t="s">
-        <v>2208</v>
+        <v>2212</v>
       </c>
       <c r="E28" s="53"/>
       <c r="F28" s="53"/>
@@ -27855,16 +27887,16 @@
         <v>1191</v>
       </c>
       <c r="C30" s="53" t="s">
-        <v>2209</v>
+        <v>2213</v>
       </c>
       <c r="D30" s="53" t="s">
-        <v>2210</v>
+        <v>2214</v>
       </c>
       <c r="E30" s="53"/>
       <c r="F30" s="53"/>
       <c r="G30" s="53"/>
       <c r="H30" s="53"/>
-      <c r="I30" s="90" t="n">
+      <c r="I30" s="91" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -27877,16 +27909,16 @@
         <v>1192</v>
       </c>
       <c r="C31" s="53" t="s">
-        <v>2211</v>
+        <v>2215</v>
       </c>
       <c r="D31" s="53" t="s">
-        <v>2212</v>
+        <v>2216</v>
       </c>
       <c r="E31" s="53"/>
       <c r="F31" s="53"/>
       <c r="G31" s="53"/>
       <c r="H31" s="53"/>
-      <c r="I31" s="90" t="n">
+      <c r="I31" s="91" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -27899,16 +27931,16 @@
         <v>1193</v>
       </c>
       <c r="C32" s="53" t="s">
-        <v>2213</v>
+        <v>2217</v>
       </c>
       <c r="D32" s="53" t="s">
-        <v>2214</v>
+        <v>2218</v>
       </c>
       <c r="E32" s="53"/>
       <c r="F32" s="53"/>
       <c r="G32" s="53"/>
       <c r="H32" s="53"/>
-      <c r="I32" s="90" t="n">
+      <c r="I32" s="91" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -27921,16 +27953,16 @@
         <v>1195</v>
       </c>
       <c r="C33" s="53" t="s">
-        <v>2215</v>
+        <v>2219</v>
       </c>
       <c r="D33" s="53" t="s">
-        <v>2216</v>
+        <v>2220</v>
       </c>
       <c r="E33" s="53"/>
       <c r="F33" s="53"/>
       <c r="G33" s="53"/>
       <c r="H33" s="53"/>
-      <c r="I33" s="90" t="n">
+      <c r="I33" s="91" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -27943,16 +27975,16 @@
         <v>1196</v>
       </c>
       <c r="C34" s="53" t="s">
-        <v>2217</v>
+        <v>2221</v>
       </c>
       <c r="D34" s="53" t="s">
-        <v>2218</v>
+        <v>2222</v>
       </c>
       <c r="E34" s="53"/>
       <c r="F34" s="53"/>
       <c r="G34" s="53"/>
       <c r="H34" s="53"/>
-      <c r="I34" s="90" t="n">
+      <c r="I34" s="91" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -27962,13 +27994,13 @@
         <v>340</v>
       </c>
       <c r="B35" s="53" t="s">
-        <v>2219</v>
+        <v>2223</v>
       </c>
       <c r="C35" s="53" t="s">
-        <v>2220</v>
+        <v>2224</v>
       </c>
       <c r="D35" s="53" t="s">
-        <v>2221</v>
+        <v>2225</v>
       </c>
       <c r="E35" s="53"/>
       <c r="F35" s="53"/>
@@ -27983,13 +28015,13 @@
         <v>340</v>
       </c>
       <c r="B36" s="53" t="s">
-        <v>2222</v>
+        <v>2226</v>
       </c>
       <c r="C36" s="53" t="s">
-        <v>2223</v>
+        <v>2227</v>
       </c>
       <c r="D36" s="53" t="s">
-        <v>2224</v>
+        <v>2228</v>
       </c>
       <c r="E36" s="53"/>
       <c r="F36" s="53"/>
@@ -28005,10 +28037,10 @@
         <v>1262</v>
       </c>
       <c r="C37" s="53" t="s">
-        <v>2225</v>
+        <v>2229</v>
       </c>
       <c r="D37" s="53" t="s">
-        <v>2226</v>
+        <v>2230</v>
       </c>
       <c r="E37" s="53"/>
       <c r="F37" s="53"/>
@@ -28024,10 +28056,10 @@
         <v>1263</v>
       </c>
       <c r="C38" s="53" t="s">
-        <v>2227</v>
+        <v>2231</v>
       </c>
       <c r="D38" s="53" t="s">
-        <v>2228</v>
+        <v>2232</v>
       </c>
       <c r="E38" s="53"/>
       <c r="F38" s="53"/>
@@ -28040,13 +28072,13 @@
         <v>340</v>
       </c>
       <c r="B39" s="53" t="s">
-        <v>2229</v>
+        <v>2233</v>
       </c>
       <c r="C39" s="53" t="s">
-        <v>2230</v>
+        <v>2234</v>
       </c>
       <c r="D39" s="53" t="s">
-        <v>2231</v>
+        <v>2235</v>
       </c>
       <c r="E39" s="53"/>
       <c r="F39" s="53"/>
@@ -28059,13 +28091,13 @@
         <v>340</v>
       </c>
       <c r="B40" s="53" t="s">
-        <v>2232</v>
+        <v>2236</v>
       </c>
       <c r="C40" s="53" t="s">
-        <v>2233</v>
+        <v>2237</v>
       </c>
       <c r="D40" s="53" t="s">
-        <v>2234</v>
+        <v>2238</v>
       </c>
       <c r="E40" s="53"/>
       <c r="F40" s="53"/>
@@ -28083,7 +28115,7 @@
       <c r="E41" s="53"/>
       <c r="F41" s="53"/>
       <c r="G41" s="53" t="s">
-        <v>2178</v>
+        <v>2182</v>
       </c>
       <c r="H41" s="53"/>
       <c r="I41" s="66"/>
@@ -28108,13 +28140,13 @@
         <v>315</v>
       </c>
       <c r="B43" s="53" t="s">
-        <v>2235</v>
+        <v>2239</v>
       </c>
       <c r="C43" s="48" t="s">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="E43" s="53"/>
       <c r="F43" s="53"/>
@@ -28127,13 +28159,13 @@
         <v>315</v>
       </c>
       <c r="B44" s="53" t="s">
-        <v>2238</v>
+        <v>2242</v>
       </c>
       <c r="C44" s="48" t="s">
-        <v>2239</v>
+        <v>2243</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>2240</v>
+        <v>2244</v>
       </c>
       <c r="E44" s="53"/>
       <c r="F44" s="53"/>
@@ -28146,13 +28178,13 @@
         <v>315</v>
       </c>
       <c r="B45" s="53" t="s">
-        <v>2241</v>
+        <v>2245</v>
       </c>
       <c r="C45" s="48" t="s">
-        <v>2242</v>
+        <v>2246</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>2243</v>
+        <v>2247</v>
       </c>
       <c r="E45" s="53"/>
       <c r="F45" s="53"/>
@@ -28165,13 +28197,13 @@
         <v>315</v>
       </c>
       <c r="B46" s="53" t="s">
-        <v>2244</v>
+        <v>2248</v>
       </c>
       <c r="C46" s="48" t="s">
-        <v>2245</v>
+        <v>2249</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>2246</v>
+        <v>2250</v>
       </c>
       <c r="E46" s="53"/>
       <c r="F46" s="53"/>
@@ -28189,7 +28221,7 @@
       <c r="E47" s="53"/>
       <c r="F47" s="53"/>
       <c r="G47" s="53" t="s">
-        <v>2179</v>
+        <v>2183</v>
       </c>
       <c r="H47" s="53"/>
       <c r="I47" s="53"/>
@@ -28202,10 +28234,10 @@
         <v>1256</v>
       </c>
       <c r="C48" s="51" t="s">
-        <v>2247</v>
+        <v>2251</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>2248</v>
+        <v>2252</v>
       </c>
       <c r="E48" s="53"/>
       <c r="F48" s="53"/>
@@ -28220,13 +28252,13 @@
         <v>220</v>
       </c>
       <c r="B49" s="53" t="s">
-        <v>2249</v>
+        <v>2253</v>
       </c>
       <c r="C49" s="51" t="s">
-        <v>2250</v>
+        <v>2254</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>2251</v>
+        <v>2255</v>
       </c>
       <c r="E49" s="53"/>
       <c r="F49" s="53"/>
@@ -28241,13 +28273,13 @@
         <v>220</v>
       </c>
       <c r="B50" s="53" t="s">
-        <v>2252</v>
+        <v>2256</v>
       </c>
       <c r="C50" s="51" t="s">
-        <v>2253</v>
+        <v>2257</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>2254</v>
+        <v>2258</v>
       </c>
       <c r="E50" s="53"/>
       <c r="F50" s="53"/>
@@ -28263,10 +28295,10 @@
         <v>229</v>
       </c>
       <c r="C51" s="51" t="s">
-        <v>2255</v>
+        <v>2259</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>2256</v>
+        <v>2260</v>
       </c>
       <c r="E51" s="53"/>
       <c r="F51" s="53"/>
@@ -28284,7 +28316,7 @@
       <c r="E52" s="53"/>
       <c r="F52" s="53"/>
       <c r="G52" s="53" t="s">
-        <v>2179</v>
+        <v>2183</v>
       </c>
       <c r="H52" s="53"/>
       <c r="I52" s="53"/>
@@ -28294,13 +28326,13 @@
         <v>226</v>
       </c>
       <c r="B53" s="53" t="s">
-        <v>2257</v>
+        <v>2261</v>
       </c>
       <c r="C53" s="51" t="s">
-        <v>2258</v>
+        <v>2262</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>2259</v>
+        <v>2263</v>
       </c>
       <c r="E53" s="53"/>
       <c r="F53" s="53"/>
@@ -28313,13 +28345,13 @@
         <v>226</v>
       </c>
       <c r="B54" s="53" t="s">
-        <v>2260</v>
+        <v>2264</v>
       </c>
       <c r="C54" s="51" t="s">
-        <v>2261</v>
+        <v>2265</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>2262</v>
+        <v>2266</v>
       </c>
       <c r="E54" s="53"/>
       <c r="F54" s="53"/>
@@ -28332,13 +28364,13 @@
         <v>226</v>
       </c>
       <c r="B55" s="53" t="s">
-        <v>2263</v>
+        <v>2267</v>
       </c>
       <c r="C55" s="51" t="s">
-        <v>2264</v>
+        <v>2268</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>2265</v>
+        <v>2269</v>
       </c>
       <c r="E55" s="53"/>
       <c r="F55" s="53"/>
@@ -28351,13 +28383,13 @@
         <v>226</v>
       </c>
       <c r="B56" s="53" t="s">
-        <v>2266</v>
+        <v>2270</v>
       </c>
       <c r="C56" s="51" t="s">
-        <v>2267</v>
+        <v>2271</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>2268</v>
+        <v>2272</v>
       </c>
       <c r="E56" s="53"/>
       <c r="F56" s="53"/>
@@ -28370,13 +28402,13 @@
         <v>226</v>
       </c>
       <c r="B57" s="53" t="s">
-        <v>2269</v>
+        <v>2273</v>
       </c>
       <c r="C57" s="51" t="s">
-        <v>2270</v>
+        <v>2274</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>2270</v>
+        <v>2274</v>
       </c>
       <c r="E57" s="53"/>
       <c r="F57" s="53"/>
@@ -28389,13 +28421,13 @@
         <v>226</v>
       </c>
       <c r="B58" s="53" t="s">
-        <v>2271</v>
+        <v>2275</v>
       </c>
       <c r="C58" s="51" t="s">
-        <v>2272</v>
+        <v>2276</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>2273</v>
+        <v>2277</v>
       </c>
       <c r="E58" s="53"/>
       <c r="F58" s="53"/>
@@ -28408,13 +28440,13 @@
         <v>226</v>
       </c>
       <c r="B59" s="53" t="s">
-        <v>2274</v>
+        <v>2278</v>
       </c>
       <c r="C59" s="51" t="s">
-        <v>2275</v>
+        <v>2279</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>2276</v>
+        <v>2280</v>
       </c>
       <c r="E59" s="53"/>
       <c r="F59" s="53"/>
@@ -28427,13 +28459,13 @@
         <v>226</v>
       </c>
       <c r="B60" s="53" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>2278</v>
+        <v>2282</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>2279</v>
+        <v>2283</v>
       </c>
       <c r="E60" s="53"/>
       <c r="F60" s="53"/>
@@ -28461,13 +28493,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="53" t="s">
-        <v>2280</v>
+        <v>2284</v>
       </c>
       <c r="C62" s="51" t="s">
-        <v>2281</v>
+        <v>2285</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>2282</v>
+        <v>2286</v>
       </c>
       <c r="E62" s="53"/>
       <c r="F62" s="53"/>
@@ -28485,7 +28517,7 @@
       <c r="E63" s="53"/>
       <c r="F63" s="53"/>
       <c r="G63" s="53" t="s">
-        <v>2179</v>
+        <v>2183</v>
       </c>
       <c r="H63" s="53"/>
       <c r="I63" s="53"/>
@@ -28498,10 +28530,10 @@
         <v>1167</v>
       </c>
       <c r="C64" s="51" t="s">
-        <v>2283</v>
+        <v>2287</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>2284</v>
+        <v>2288</v>
       </c>
       <c r="E64" s="53"/>
       <c r="F64" s="53"/>
@@ -28510,164 +28542,164 @@
       <c r="I64" s="53"/>
     </row>
     <row r="65" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="89" t="s">
+      <c r="A65" s="90" t="s">
         <v>322</v>
       </c>
       <c r="B65" s="53" t="s">
         <v>1199</v>
       </c>
       <c r="C65" s="53" t="s">
-        <v>2285</v>
+        <v>2289</v>
       </c>
       <c r="D65" s="53" t="s">
-        <v>2286</v>
+        <v>2290</v>
       </c>
       <c r="E65" s="53"/>
       <c r="F65" s="53" t="s">
-        <v>2287</v>
+        <v>2291</v>
       </c>
       <c r="G65" s="53"/>
       <c r="H65" s="53"/>
       <c r="I65" s="66"/>
     </row>
     <row r="66" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="89" t="s">
+      <c r="A66" s="90" t="s">
         <v>322</v>
       </c>
       <c r="B66" s="53" t="s">
         <v>1200</v>
       </c>
       <c r="C66" s="53" t="s">
-        <v>2288</v>
+        <v>2292</v>
       </c>
       <c r="D66" s="53" t="s">
-        <v>2289</v>
+        <v>2293</v>
       </c>
       <c r="E66" s="53"/>
       <c r="F66" s="53" t="s">
-        <v>2290</v>
+        <v>2294</v>
       </c>
       <c r="G66" s="53"/>
       <c r="H66" s="53"/>
       <c r="I66" s="66"/>
     </row>
     <row r="67" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="89" t="s">
+      <c r="A67" s="90" t="s">
         <v>322</v>
       </c>
       <c r="B67" s="53" t="s">
-        <v>2291</v>
+        <v>2295</v>
       </c>
       <c r="C67" s="53" t="s">
-        <v>2292</v>
+        <v>2296</v>
       </c>
       <c r="D67" s="53" t="s">
-        <v>2293</v>
+        <v>2297</v>
       </c>
       <c r="E67" s="53"/>
       <c r="F67" s="53" t="s">
-        <v>2294</v>
+        <v>2298</v>
       </c>
       <c r="G67" s="53"/>
       <c r="H67" s="53"/>
       <c r="I67" s="66"/>
     </row>
     <row r="68" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="89" t="s">
+      <c r="A68" s="90" t="s">
         <v>322</v>
       </c>
       <c r="B68" s="53" t="s">
         <v>1201</v>
       </c>
       <c r="C68" s="53" t="s">
-        <v>2295</v>
+        <v>2299</v>
       </c>
       <c r="D68" s="53" t="s">
-        <v>2296</v>
+        <v>2300</v>
       </c>
       <c r="E68" s="53"/>
       <c r="F68" s="53" t="s">
-        <v>2297</v>
+        <v>2301</v>
       </c>
       <c r="G68" s="53"/>
       <c r="H68" s="53"/>
       <c r="I68" s="66"/>
     </row>
     <row r="69" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="89" t="s">
+      <c r="A69" s="90" t="s">
         <v>322</v>
       </c>
       <c r="B69" s="53" t="s">
         <v>1215</v>
       </c>
       <c r="C69" s="53" t="s">
-        <v>2298</v>
+        <v>2302</v>
       </c>
       <c r="D69" s="53" t="s">
-        <v>2299</v>
+        <v>2303</v>
       </c>
       <c r="E69" s="53"/>
       <c r="F69" s="53" t="s">
-        <v>2300</v>
+        <v>2304</v>
       </c>
       <c r="G69" s="53"/>
       <c r="H69" s="53"/>
       <c r="I69" s="66"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="89" t="s">
+      <c r="A70" s="90" t="s">
         <v>905</v>
       </c>
       <c r="B70" s="66" t="s">
-        <v>2301</v>
+        <v>2305</v>
       </c>
       <c r="C70" s="66" t="s">
-        <v>2302</v>
+        <v>2306</v>
       </c>
       <c r="D70" s="66" t="s">
-        <v>2303</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="89" t="s">
+      <c r="A71" s="90" t="s">
         <v>905</v>
       </c>
       <c r="B71" s="66" t="s">
-        <v>2304</v>
+        <v>2308</v>
       </c>
       <c r="C71" s="66" t="s">
-        <v>2305</v>
+        <v>2309</v>
       </c>
       <c r="D71" s="66" t="s">
-        <v>2306</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="89" t="s">
+      <c r="A72" s="90" t="s">
         <v>905</v>
       </c>
       <c r="B72" s="66" t="s">
-        <v>2307</v>
+        <v>2311</v>
       </c>
       <c r="C72" s="66" t="s">
-        <v>2308</v>
+        <v>2312</v>
       </c>
       <c r="D72" s="66" t="s">
-        <v>2309</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="73" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="89" t="s">
+      <c r="A73" s="90" t="s">
         <v>905</v>
       </c>
       <c r="B73" s="66" t="s">
-        <v>2310</v>
+        <v>2314</v>
       </c>
       <c r="C73" s="66" t="s">
-        <v>2311</v>
+        <v>2315</v>
       </c>
       <c r="D73" s="66" t="s">
-        <v>2312</v>
+        <v>2316</v>
       </c>
       <c r="E73" s="66"/>
       <c r="F73" s="66"/>
@@ -28680,13 +28712,13 @@
         <v>1079</v>
       </c>
       <c r="B74" s="53" t="s">
-        <v>2313</v>
+        <v>2317</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>2314</v>
+        <v>2318</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>2315</v>
+        <v>2319</v>
       </c>
       <c r="E74" s="51"/>
       <c r="F74" s="51"/>
@@ -28699,13 +28731,13 @@
         <v>1079</v>
       </c>
       <c r="B75" s="53" t="s">
-        <v>2316</v>
+        <v>2320</v>
       </c>
       <c r="C75" s="51" t="s">
-        <v>2317</v>
+        <v>2321</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>2318</v>
+        <v>2322</v>
       </c>
       <c r="E75" s="51"/>
       <c r="F75" s="51"/>
@@ -28718,13 +28750,13 @@
         <v>1079</v>
       </c>
       <c r="B76" s="53" t="s">
-        <v>2319</v>
+        <v>2323</v>
       </c>
       <c r="C76" s="51" t="s">
-        <v>2320</v>
+        <v>2324</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>2321</v>
+        <v>2325</v>
       </c>
       <c r="E76" s="51"/>
       <c r="F76" s="51"/>
@@ -28737,13 +28769,13 @@
         <v>1079</v>
       </c>
       <c r="B77" s="53" t="s">
-        <v>2322</v>
+        <v>2326</v>
       </c>
       <c r="C77" s="51" t="s">
-        <v>2323</v>
+        <v>2327</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>2324</v>
+        <v>2328</v>
       </c>
       <c r="E77" s="51"/>
       <c r="F77" s="51"/>
@@ -28756,13 +28788,13 @@
         <v>1079</v>
       </c>
       <c r="B78" s="53" t="s">
-        <v>2325</v>
+        <v>2329</v>
       </c>
       <c r="C78" s="51" t="s">
-        <v>2326</v>
+        <v>2330</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>2327</v>
+        <v>2331</v>
       </c>
       <c r="E78" s="51"/>
       <c r="F78" s="51"/>
@@ -28775,13 +28807,13 @@
         <v>1079</v>
       </c>
       <c r="B79" s="53" t="s">
-        <v>2328</v>
+        <v>2332</v>
       </c>
       <c r="C79" s="51" t="s">
-        <v>2329</v>
+        <v>2333</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>2330</v>
+        <v>2334</v>
       </c>
       <c r="E79" s="51"/>
       <c r="F79" s="51"/>
@@ -28794,13 +28826,13 @@
         <v>1079</v>
       </c>
       <c r="B80" s="53" t="s">
-        <v>2331</v>
+        <v>2335</v>
       </c>
       <c r="C80" s="51" t="s">
-        <v>2332</v>
+        <v>2336</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>2333</v>
+        <v>2337</v>
       </c>
       <c r="E80" s="51"/>
       <c r="F80" s="51"/>
@@ -28813,13 +28845,13 @@
         <v>1079</v>
       </c>
       <c r="B81" s="53" t="s">
-        <v>2334</v>
+        <v>2338</v>
       </c>
       <c r="C81" s="51" t="s">
-        <v>2335</v>
+        <v>2339</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>2336</v>
+        <v>2340</v>
       </c>
       <c r="E81" s="51"/>
       <c r="F81" s="51"/>
@@ -28832,13 +28864,13 @@
         <v>1079</v>
       </c>
       <c r="B82" s="53" t="s">
-        <v>2337</v>
+        <v>2341</v>
       </c>
       <c r="C82" s="51" t="s">
-        <v>2338</v>
+        <v>2342</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>2339</v>
+        <v>2343</v>
       </c>
       <c r="E82" s="51"/>
       <c r="F82" s="51"/>
@@ -28851,13 +28883,13 @@
         <v>1079</v>
       </c>
       <c r="B83" s="53" t="s">
-        <v>2179</v>
+        <v>2183</v>
       </c>
       <c r="C83" s="51" t="s">
-        <v>2180</v>
+        <v>2184</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>2181</v>
+        <v>2185</v>
       </c>
       <c r="E83" s="51"/>
       <c r="F83" s="51"/>
@@ -28870,13 +28902,13 @@
         <v>1079</v>
       </c>
       <c r="B84" s="53" t="s">
-        <v>2340</v>
+        <v>2344</v>
       </c>
       <c r="C84" s="51" t="s">
-        <v>2182</v>
+        <v>2186</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>2341</v>
+        <v>2345</v>
       </c>
       <c r="E84" s="51"/>
       <c r="F84" s="51"/>
@@ -28885,35 +28917,35 @@
       <c r="I84" s="53"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="91" t="s">
+      <c r="A85" s="92" t="s">
         <v>99</v>
       </c>
       <c r="B85" s="66" t="s">
-        <v>2342</v>
+        <v>2346</v>
       </c>
       <c r="C85" s="66" t="s">
-        <v>2343</v>
+        <v>2347</v>
       </c>
       <c r="D85" s="66" t="s">
-        <v>2344</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="91" t="s">
+      <c r="A86" s="92" t="s">
         <v>99</v>
       </c>
       <c r="B86" s="66" t="s">
-        <v>2345</v>
+        <v>2349</v>
       </c>
       <c r="C86" s="66" t="s">
-        <v>2346</v>
+        <v>2350</v>
       </c>
       <c r="D86" s="66" t="s">
-        <v>2347</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="91" t="s">
+      <c r="A87" s="92" t="s">
         <v>99</v>
       </c>
       <c r="B87" s="66" t="s">
@@ -28927,31 +28959,31 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="91" t="s">
+      <c r="A88" s="92" t="s">
         <v>99</v>
       </c>
       <c r="B88" s="66" t="s">
         <v>1171</v>
       </c>
       <c r="C88" s="66" t="s">
-        <v>2182</v>
+        <v>2186</v>
       </c>
       <c r="D88" s="66" t="s">
-        <v>2341</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="92" t="s">
+      <c r="A89" s="93" t="s">
         <v>423</v>
       </c>
       <c r="B89" s="53" t="s">
-        <v>2348</v>
+        <v>2352</v>
       </c>
       <c r="C89" s="51" t="s">
-        <v>2349</v>
+        <v>2353</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>2350</v>
+        <v>2354</v>
       </c>
       <c r="E89" s="51"/>
       <c r="F89" s="51"/>
@@ -28962,17 +28994,17 @@
       <c r="I89" s="53"/>
     </row>
     <row r="90" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="92" t="s">
+      <c r="A90" s="93" t="s">
         <v>423</v>
       </c>
       <c r="B90" s="53" t="s">
-        <v>2351</v>
+        <v>2355</v>
       </c>
       <c r="C90" s="51" t="s">
-        <v>2352</v>
+        <v>2356</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>2353</v>
+        <v>2357</v>
       </c>
       <c r="E90" s="51"/>
       <c r="F90" s="51"/>
@@ -28983,17 +29015,17 @@
       <c r="I90" s="53"/>
     </row>
     <row r="91" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="92" t="s">
+      <c r="A91" s="93" t="s">
         <v>423</v>
       </c>
       <c r="B91" s="53" t="s">
-        <v>2354</v>
+        <v>2358</v>
       </c>
       <c r="C91" s="51" t="s">
-        <v>2355</v>
+        <v>2359</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>2356</v>
+        <v>2360</v>
       </c>
       <c r="E91" s="51"/>
       <c r="F91" s="51"/>
@@ -29002,17 +29034,17 @@
       <c r="I91" s="53"/>
     </row>
     <row r="92" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="92" t="s">
+      <c r="A92" s="93" t="s">
         <v>423</v>
       </c>
       <c r="B92" s="53" t="s">
-        <v>2357</v>
+        <v>2361</v>
       </c>
       <c r="C92" s="51" t="s">
-        <v>2358</v>
+        <v>2362</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>2359</v>
+        <v>2363</v>
       </c>
       <c r="E92" s="51"/>
       <c r="F92" s="51"/>
@@ -29021,17 +29053,17 @@
       <c r="I92" s="53"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="92" t="s">
+      <c r="A93" s="93" t="s">
         <v>423</v>
       </c>
       <c r="B93" s="53" t="s">
-        <v>2360</v>
+        <v>2364</v>
       </c>
       <c r="C93" s="51" t="s">
-        <v>2361</v>
+        <v>2365</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>2362</v>
+        <v>2366</v>
       </c>
       <c r="E93" s="51"/>
       <c r="F93" s="51"/>
@@ -29040,17 +29072,17 @@
       <c r="I93" s="53"/>
     </row>
     <row r="94" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="92" t="s">
+      <c r="A94" s="93" t="s">
         <v>423</v>
       </c>
       <c r="B94" s="53" t="s">
         <v>1232</v>
       </c>
       <c r="C94" s="51" t="s">
-        <v>2363</v>
+        <v>2367</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>2364</v>
+        <v>2368</v>
       </c>
       <c r="E94" s="51"/>
       <c r="F94" s="51"/>
@@ -29061,17 +29093,17 @@
       <c r="I94" s="53"/>
     </row>
     <row r="95" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="92" t="s">
+      <c r="A95" s="93" t="s">
         <v>423</v>
       </c>
       <c r="B95" s="53" t="s">
         <v>1233</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>2365</v>
+        <v>2369</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>2366</v>
+        <v>2370</v>
       </c>
       <c r="E95" s="51"/>
       <c r="F95" s="51"/>
@@ -29080,17 +29112,17 @@
       <c r="I95" s="53"/>
     </row>
     <row r="96" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="92" t="s">
+      <c r="A96" s="93" t="s">
         <v>423</v>
       </c>
       <c r="B96" s="53" t="s">
-        <v>2367</v>
+        <v>2371</v>
       </c>
       <c r="C96" s="51" t="s">
-        <v>2368</v>
+        <v>2372</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>2369</v>
+        <v>2373</v>
       </c>
       <c r="E96" s="51"/>
       <c r="F96" s="51"/>
@@ -29101,7 +29133,7 @@
       <c r="I96" s="53"/>
     </row>
     <row r="97" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="92" t="s">
+      <c r="A97" s="93" t="s">
         <v>423</v>
       </c>
       <c r="B97" s="53" t="s">
@@ -29120,11 +29152,11 @@
       <c r="I97" s="53"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="93" t="s">
-        <v>2370</v>
+      <c r="A98" s="94" t="s">
+        <v>2374</v>
       </c>
       <c r="B98" s="66" t="s">
-        <v>2371</v>
+        <v>2375</v>
       </c>
       <c r="C98" s="66" t="s">
         <v>1752</v>
@@ -29140,11 +29172,11 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="93" t="s">
-        <v>2370</v>
+      <c r="A99" s="94" t="s">
+        <v>2374</v>
       </c>
       <c r="B99" s="66" t="s">
-        <v>2372</v>
+        <v>2376</v>
       </c>
       <c r="C99" s="66" t="s">
         <v>1757</v>
@@ -29160,215 +29192,215 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="93" t="s">
-        <v>2370</v>
+      <c r="A100" s="94" t="s">
+        <v>2374</v>
       </c>
       <c r="B100" s="66" t="s">
         <v>1225</v>
       </c>
       <c r="C100" s="66" t="s">
-        <v>2174</v>
+        <v>2178</v>
       </c>
       <c r="D100" s="66" t="s">
-        <v>2175</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="93" t="s">
+      <c r="A101" s="94" t="s">
         <v>771</v>
       </c>
       <c r="B101" s="66" t="s">
-        <v>2373</v>
+        <v>2377</v>
       </c>
       <c r="C101" s="66" t="s">
-        <v>2374</v>
+        <v>2378</v>
       </c>
       <c r="D101" s="66" t="s">
-        <v>2375</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="93" t="s">
+      <c r="A102" s="94" t="s">
         <v>771</v>
       </c>
       <c r="B102" s="66" t="s">
-        <v>2376</v>
+        <v>2380</v>
       </c>
       <c r="C102" s="66" t="s">
-        <v>2377</v>
+        <v>2381</v>
       </c>
       <c r="D102" s="66" t="s">
-        <v>2378</v>
-      </c>
-      <c r="I102" s="90" t="n">
+        <v>2382</v>
+      </c>
+      <c r="I102" s="91" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="93" t="s">
+      <c r="A103" s="94" t="s">
         <v>771</v>
       </c>
       <c r="B103" s="66" t="s">
-        <v>2379</v>
+        <v>2383</v>
       </c>
       <c r="C103" s="66" t="s">
-        <v>2380</v>
+        <v>2384</v>
       </c>
       <c r="D103" s="66" t="s">
-        <v>2381</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="93" t="s">
+      <c r="A104" s="94" t="s">
         <v>771</v>
       </c>
       <c r="B104" s="66" t="s">
-        <v>2382</v>
+        <v>2386</v>
       </c>
       <c r="C104" s="66" t="s">
+        <v>2387</v>
+      </c>
+      <c r="D104" s="66" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="94" t="s">
+        <v>771</v>
+      </c>
+      <c r="G105" s="53" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="94" t="s">
+        <v>771</v>
+      </c>
+      <c r="G106" s="53" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="94" t="s">
+        <v>829</v>
+      </c>
+      <c r="B107" s="66" t="s">
+        <v>2389</v>
+      </c>
+      <c r="C107" s="66" t="s">
+        <v>2390</v>
+      </c>
+      <c r="D107" s="66" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="94" t="s">
+        <v>829</v>
+      </c>
+      <c r="B108" s="66" t="s">
+        <v>2392</v>
+      </c>
+      <c r="C108" s="66" t="s">
+        <v>2393</v>
+      </c>
+      <c r="D108" s="66" t="s">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="94" t="s">
+        <v>829</v>
+      </c>
+      <c r="B109" s="66" t="s">
         <v>2383</v>
       </c>
-      <c r="D104" s="66" t="s">
-        <v>2384</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="93" t="s">
-        <v>771</v>
-      </c>
-      <c r="G105" s="53" t="s">
-        <v>2178</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="93" t="s">
-        <v>771</v>
-      </c>
-      <c r="G106" s="53" t="s">
-        <v>2179</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="93" t="s">
+      <c r="C109" s="66" t="s">
+        <v>2395</v>
+      </c>
+      <c r="D109" s="66" t="s">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="94" t="s">
         <v>829</v>
       </c>
-      <c r="B107" s="66" t="s">
-        <v>2385</v>
-      </c>
-      <c r="C107" s="66" t="s">
-        <v>2386</v>
-      </c>
-      <c r="D107" s="66" t="s">
-        <v>2387</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="93" t="s">
+      <c r="B110" s="53" t="s">
+        <v>2397</v>
+      </c>
+      <c r="C110" s="51" t="s">
+        <v>2398</v>
+      </c>
+      <c r="D110" s="48" t="s">
+        <v>2399</v>
+      </c>
+      <c r="I110" s="91" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="94" t="s">
         <v>829</v>
       </c>
-      <c r="B108" s="66" t="s">
-        <v>2388</v>
-      </c>
-      <c r="C108" s="66" t="s">
-        <v>2389</v>
-      </c>
-      <c r="D108" s="66" t="s">
-        <v>2390</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="93" t="s">
+      <c r="G111" s="53" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="94" t="s">
         <v>829</v>
       </c>
-      <c r="B109" s="66" t="s">
-        <v>2379</v>
-      </c>
-      <c r="C109" s="66" t="s">
-        <v>2391</v>
-      </c>
-      <c r="D109" s="66" t="s">
-        <v>2392</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="93" t="s">
-        <v>829</v>
-      </c>
-      <c r="B110" s="53" t="s">
-        <v>2393</v>
-      </c>
-      <c r="C110" s="51" t="s">
-        <v>2394</v>
-      </c>
-      <c r="D110" s="48" t="s">
-        <v>2395</v>
-      </c>
-      <c r="I110" s="90" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="93" t="s">
-        <v>829</v>
-      </c>
-      <c r="G111" s="53" t="s">
-        <v>2178</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="93" t="s">
-        <v>829</v>
-      </c>
       <c r="G112" s="53" t="s">
-        <v>2179</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="94" t="s">
+      <c r="A113" s="95" t="s">
         <v>347</v>
       </c>
       <c r="B113" s="66" t="s">
-        <v>2396</v>
+        <v>2400</v>
       </c>
       <c r="C113" s="66" t="s">
-        <v>2397</v>
+        <v>2401</v>
       </c>
       <c r="D113" s="66" t="s">
-        <v>2398</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="94" t="s">
+      <c r="A114" s="95" t="s">
         <v>347</v>
       </c>
       <c r="B114" s="66" t="s">
-        <v>2399</v>
+        <v>2403</v>
       </c>
       <c r="C114" s="66" t="s">
-        <v>2400</v>
+        <v>2404</v>
       </c>
       <c r="D114" s="66" t="s">
-        <v>2401</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="94" t="s">
+      <c r="A115" s="95" t="s">
         <v>347</v>
       </c>
       <c r="B115" s="66" t="s">
-        <v>2402</v>
+        <v>2406</v>
       </c>
       <c r="C115" s="66" t="s">
-        <v>2403</v>
+        <v>2407</v>
       </c>
       <c r="D115" s="66" t="s">
-        <v>2404</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="94" t="s">
+      <c r="A116" s="95" t="s">
         <v>347</v>
       </c>
       <c r="G116" s="53" t="s">
@@ -29376,104 +29408,104 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="89" t="s">
-        <v>2405</v>
+      <c r="A117" s="90" t="s">
+        <v>2409</v>
       </c>
       <c r="B117" s="53" t="s">
         <v>1199</v>
       </c>
       <c r="C117" s="53" t="s">
-        <v>2406</v>
+        <v>2410</v>
       </c>
       <c r="D117" s="53" t="s">
-        <v>2407</v>
+        <v>2411</v>
       </c>
       <c r="E117" s="53" t="s">
-        <v>2408</v>
+        <v>2412</v>
       </c>
       <c r="F117" s="53" t="s">
+        <v>2413</v>
+      </c>
+      <c r="G117" s="90"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="90" t="s">
         <v>2409</v>
-      </c>
-      <c r="G117" s="89"/>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="89" t="s">
-        <v>2405</v>
       </c>
       <c r="B118" s="53" t="s">
         <v>1200</v>
       </c>
       <c r="C118" s="53" t="s">
-        <v>2410</v>
+        <v>2414</v>
       </c>
       <c r="D118" s="53" t="s">
-        <v>2411</v>
+        <v>2415</v>
       </c>
       <c r="E118" s="53" t="s">
-        <v>2412</v>
+        <v>2416</v>
       </c>
       <c r="F118" s="53" t="s">
-        <v>2413</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="89" t="s">
-        <v>2405</v>
+      <c r="A119" s="90" t="s">
+        <v>2409</v>
       </c>
       <c r="B119" s="53" t="s">
         <v>1201</v>
       </c>
       <c r="C119" s="53" t="s">
-        <v>2414</v>
+        <v>2418</v>
       </c>
       <c r="D119" s="53" t="s">
-        <v>2415</v>
+        <v>2419</v>
       </c>
       <c r="E119" s="53" t="s">
-        <v>2416</v>
+        <v>2420</v>
       </c>
       <c r="F119" s="53" t="s">
-        <v>2417</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="89" t="s">
-        <v>2405</v>
+      <c r="A120" s="90" t="s">
+        <v>2409</v>
       </c>
       <c r="B120" s="53" t="s">
         <v>1215</v>
       </c>
       <c r="C120" s="53" t="s">
-        <v>2418</v>
+        <v>2422</v>
       </c>
       <c r="D120" s="53" t="s">
-        <v>2419</v>
+        <v>2423</v>
       </c>
       <c r="E120" s="53" t="s">
-        <v>2420</v>
+        <v>2424</v>
       </c>
       <c r="F120" s="53" t="s">
-        <v>2421</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="89" t="s">
-        <v>2405</v>
+      <c r="A121" s="90" t="s">
+        <v>2409</v>
       </c>
       <c r="B121" s="53" t="s">
-        <v>2291</v>
+        <v>2295</v>
       </c>
       <c r="C121" s="53" t="s">
-        <v>2422</v>
+        <v>2426</v>
       </c>
       <c r="D121" s="53" t="s">
-        <v>2423</v>
+        <v>2427</v>
       </c>
       <c r="E121" s="53" t="s">
-        <v>2424</v>
+        <v>2428</v>
       </c>
       <c r="F121" s="53" t="s">
-        <v>2425</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29481,7 +29513,7 @@
         <v>698</v>
       </c>
       <c r="B122" s="66" t="s">
-        <v>2426</v>
+        <v>2430</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>2021</v>
@@ -29498,12 +29530,12 @@
         <v>1237</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>2427</v>
+        <v>2431</v>
       </c>
       <c r="D123" s="57" t="s">
-        <v>2427</v>
-      </c>
-      <c r="H123" s="95" t="s">
+        <v>2431</v>
+      </c>
+      <c r="H123" s="96" t="s">
         <v>1235</v>
       </c>
     </row>
@@ -29512,16 +29544,16 @@
         <v>698</v>
       </c>
       <c r="B124" s="66" t="s">
-        <v>2428</v>
+        <v>2432</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>2429</v>
+        <v>2433</v>
       </c>
       <c r="D124" s="57" t="s">
-        <v>2430</v>
-      </c>
-      <c r="H124" s="96" t="s">
-        <v>2431</v>
+        <v>2434</v>
+      </c>
+      <c r="H124" s="97" t="s">
+        <v>2435</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29529,7 +29561,7 @@
         <v>698</v>
       </c>
       <c r="B125" s="66" t="s">
-        <v>2432</v>
+        <v>2436</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>2030</v>
@@ -29546,7 +29578,7 @@
         <v>698</v>
       </c>
       <c r="B126" s="66" t="s">
-        <v>2433</v>
+        <v>2437</v>
       </c>
       <c r="C126" s="8" t="s">
         <v>2033</v>
@@ -29570,7 +29602,7 @@
         <v>704</v>
       </c>
       <c r="B128" s="66" t="s">
-        <v>2426</v>
+        <v>2430</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>2021</v>
@@ -29584,7 +29616,7 @@
         <v>704</v>
       </c>
       <c r="B129" s="66" t="s">
-        <v>2434</v>
+        <v>2438</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>2040</v>
@@ -29598,7 +29630,7 @@
         <v>704</v>
       </c>
       <c r="B130" s="66" t="s">
-        <v>2432</v>
+        <v>2436</v>
       </c>
       <c r="C130" s="8" t="s">
         <v>2030</v>
@@ -29615,7 +29647,7 @@
         <v>704</v>
       </c>
       <c r="B131" s="66" t="s">
-        <v>2433</v>
+        <v>2437</v>
       </c>
       <c r="C131" s="8" t="s">
         <v>2033</v>
@@ -29629,13 +29661,13 @@
         <v>704</v>
       </c>
       <c r="B132" s="66" t="s">
-        <v>2435</v>
+        <v>2439</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>2436</v>
+        <v>2440</v>
       </c>
       <c r="D132" s="57" t="s">
-        <v>2437</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29643,7 +29675,7 @@
         <v>704</v>
       </c>
       <c r="B133" s="66" t="s">
-        <v>2438</v>
+        <v>2442</v>
       </c>
       <c r="C133" s="8" t="s">
         <v>2036</v>
@@ -29659,7 +29691,7 @@
       <c r="C134" s="57"/>
       <c r="D134" s="57"/>
       <c r="G134" s="53" t="s">
-        <v>2178</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29667,16 +29699,16 @@
         <v>594</v>
       </c>
       <c r="B135" s="66" t="s">
-        <v>2439</v>
+        <v>2443</v>
       </c>
       <c r="C135" s="57" t="s">
-        <v>2440</v>
+        <v>2444</v>
       </c>
       <c r="D135" s="57" t="s">
-        <v>2441</v>
+        <v>2445</v>
       </c>
       <c r="H135" s="54" t="s">
-        <v>2442</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29687,13 +29719,13 @@
         <v>1225</v>
       </c>
       <c r="C136" s="57" t="s">
-        <v>2443</v>
+        <v>2447</v>
       </c>
       <c r="D136" s="57" t="s">
-        <v>2444</v>
+        <v>2448</v>
       </c>
       <c r="H136" s="8" t="s">
-        <v>2445</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29704,10 +29736,10 @@
         <v>1167</v>
       </c>
       <c r="C137" s="57" t="s">
-        <v>2446</v>
+        <v>2450</v>
       </c>
       <c r="D137" s="57" t="s">
-        <v>2447</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29715,13 +29747,13 @@
         <v>594</v>
       </c>
       <c r="B138" s="66" t="s">
-        <v>2448</v>
+        <v>2452</v>
       </c>
       <c r="C138" s="57" t="s">
-        <v>2449</v>
+        <v>2453</v>
       </c>
       <c r="D138" s="57" t="s">
-        <v>2450</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29731,7 +29763,7 @@
       <c r="C139" s="57"/>
       <c r="D139" s="57"/>
       <c r="G139" s="66" t="s">
-        <v>2179</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29739,13 +29771,13 @@
         <v>627</v>
       </c>
       <c r="B140" s="66" t="s">
-        <v>2451</v>
+        <v>2455</v>
       </c>
       <c r="C140" s="57" t="s">
-        <v>2452</v>
+        <v>2456</v>
       </c>
       <c r="D140" s="57" t="s">
-        <v>2452</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29753,13 +29785,13 @@
         <v>627</v>
       </c>
       <c r="B141" s="66" t="s">
-        <v>2453</v>
+        <v>2457</v>
       </c>
       <c r="C141" s="57" t="s">
-        <v>2454</v>
+        <v>2458</v>
       </c>
       <c r="D141" s="57" t="s">
-        <v>2455</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29769,7 +29801,7 @@
       <c r="C142" s="57"/>
       <c r="D142" s="57"/>
       <c r="G142" s="66" t="s">
-        <v>2179</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29777,13 +29809,13 @@
         <v>651</v>
       </c>
       <c r="B143" s="66" t="s">
-        <v>2456</v>
+        <v>2460</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>2457</v>
+        <v>2461</v>
       </c>
       <c r="D143" s="57" t="s">
-        <v>2458</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29791,13 +29823,13 @@
         <v>651</v>
       </c>
       <c r="B144" s="66" t="s">
-        <v>2459</v>
+        <v>2463</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>2460</v>
+        <v>2464</v>
       </c>
       <c r="D144" s="57" t="s">
-        <v>2461</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29807,7 +29839,7 @@
       <c r="C145" s="57"/>
       <c r="D145" s="57"/>
       <c r="G145" s="53" t="s">
-        <v>2178</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29817,7 +29849,7 @@
       <c r="C146" s="57"/>
       <c r="D146" s="57"/>
       <c r="G146" s="66" t="s">
-        <v>2179</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29825,13 +29857,13 @@
         <v>658</v>
       </c>
       <c r="B147" s="66" t="s">
-        <v>2462</v>
+        <v>2466</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>2463</v>
+        <v>2467</v>
       </c>
       <c r="D147" s="57" t="s">
-        <v>2464</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29839,13 +29871,13 @@
         <v>658</v>
       </c>
       <c r="B148" s="66" t="s">
-        <v>2465</v>
+        <v>2469</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>2466</v>
+        <v>2470</v>
       </c>
       <c r="D148" s="57" t="s">
-        <v>2466</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29853,13 +29885,13 @@
         <v>658</v>
       </c>
       <c r="B149" s="66" t="s">
-        <v>2467</v>
+        <v>2471</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>2468</v>
+        <v>2472</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>2468</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29867,13 +29899,13 @@
         <v>658</v>
       </c>
       <c r="B150" s="66" t="s">
-        <v>2469</v>
+        <v>2473</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>2470</v>
+        <v>2474</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>2470</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29883,7 +29915,7 @@
       <c r="C151" s="57"/>
       <c r="D151" s="57"/>
       <c r="G151" s="53" t="s">
-        <v>2178</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29893,7 +29925,7 @@
       <c r="C152" s="57"/>
       <c r="D152" s="57"/>
       <c r="G152" s="66" t="s">
-        <v>2179</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29901,13 +29933,13 @@
         <v>663</v>
       </c>
       <c r="B153" s="66" t="s">
-        <v>2471</v>
+        <v>2475</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>2472</v>
+        <v>2476</v>
       </c>
       <c r="D153" s="57" t="s">
-        <v>2473</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29915,13 +29947,13 @@
         <v>663</v>
       </c>
       <c r="B154" s="66" t="s">
-        <v>2474</v>
+        <v>2478</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>2475</v>
+        <v>2479</v>
       </c>
       <c r="D154" s="57" t="s">
-        <v>2476</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29929,13 +29961,13 @@
         <v>663</v>
       </c>
       <c r="B155" s="66" t="s">
-        <v>2456</v>
+        <v>2460</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>2477</v>
+        <v>2481</v>
       </c>
       <c r="D155" s="57" t="s">
-        <v>2478</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29943,13 +29975,13 @@
         <v>663</v>
       </c>
       <c r="B156" s="66" t="s">
-        <v>2479</v>
+        <v>2483</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>2480</v>
+        <v>2484</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>2480</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29957,13 +29989,13 @@
         <v>663</v>
       </c>
       <c r="B157" s="66" t="s">
-        <v>2481</v>
+        <v>2485</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>2482</v>
+        <v>2486</v>
       </c>
       <c r="D157" s="57" t="s">
-        <v>2483</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29973,7 +30005,7 @@
       <c r="C158" s="57"/>
       <c r="D158" s="57"/>
       <c r="G158" s="53" t="s">
-        <v>2178</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29983,7 +30015,7 @@
       <c r="C159" s="57"/>
       <c r="D159" s="57"/>
       <c r="G159" s="66" t="s">
-        <v>2179</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29991,7 +30023,7 @@
         <v>793</v>
       </c>
       <c r="B160" s="53" t="s">
-        <v>2432</v>
+        <v>2436</v>
       </c>
       <c r="C160" s="66" t="s">
         <v>1970</v>
@@ -30010,7 +30042,7 @@
         <v>793</v>
       </c>
       <c r="B161" s="53" t="s">
-        <v>2433</v>
+        <v>2437</v>
       </c>
       <c r="C161" s="66" t="s">
         <v>1988</v>
@@ -30029,13 +30061,13 @@
         <v>793</v>
       </c>
       <c r="B162" s="53" t="s">
-        <v>2438</v>
+        <v>2442</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>2484</v>
+        <v>2488</v>
       </c>
       <c r="D162" s="57" t="s">
-        <v>2485</v>
+        <v>2489</v>
       </c>
       <c r="E162" s="53"/>
       <c r="F162" s="53"/>
@@ -30048,7 +30080,7 @@
         <v>793</v>
       </c>
       <c r="B163" s="53" t="s">
-        <v>2426</v>
+        <v>2430</v>
       </c>
       <c r="C163" s="8" t="s">
         <v>1923</v>
@@ -30067,7 +30099,7 @@
         <v>793</v>
       </c>
       <c r="B164" s="53" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="C164" s="8" t="s">
         <v>1926</v>
@@ -30089,10 +30121,10 @@
         <v>229</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>2487</v>
+        <v>2491</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>2488</v>
+        <v>2492</v>
       </c>
       <c r="E165" s="53"/>
       <c r="F165" s="53"/>
@@ -30107,13 +30139,13 @@
         <v>793</v>
       </c>
       <c r="B166" s="53" t="s">
-        <v>2489</v>
+        <v>2493</v>
       </c>
       <c r="C166" s="51" t="s">
-        <v>2490</v>
+        <v>2494</v>
       </c>
       <c r="D166" s="8" t="s">
-        <v>2491</v>
+        <v>2495</v>
       </c>
       <c r="E166" s="53"/>
       <c r="F166" s="53"/>
@@ -30128,13 +30160,13 @@
         <v>141</v>
       </c>
       <c r="B167" s="53" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
       <c r="C167" s="51" t="s">
-        <v>2493</v>
+        <v>2497</v>
       </c>
       <c r="D167" s="8" t="s">
-        <v>2494</v>
+        <v>2498</v>
       </c>
       <c r="E167" s="53"/>
       <c r="F167" s="53"/>
@@ -30147,13 +30179,13 @@
         <v>141</v>
       </c>
       <c r="B168" s="53" t="s">
-        <v>2495</v>
+        <v>2499</v>
       </c>
       <c r="C168" s="51" t="s">
-        <v>2496</v>
+        <v>2500</v>
       </c>
       <c r="D168" s="8" t="s">
-        <v>2497</v>
+        <v>2501</v>
       </c>
       <c r="E168" s="53"/>
       <c r="F168" s="53"/>
@@ -30169,10 +30201,10 @@
         <v>1167</v>
       </c>
       <c r="C169" s="51" t="s">
-        <v>2498</v>
+        <v>2502</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>2499</v>
+        <v>2503</v>
       </c>
       <c r="E169" s="53"/>
       <c r="F169" s="53"/>
@@ -30188,10 +30220,10 @@
         <v>1225</v>
       </c>
       <c r="C170" s="51" t="s">
-        <v>2500</v>
+        <v>2504</v>
       </c>
       <c r="D170" s="8" t="s">
-        <v>2501</v>
+        <v>2505</v>
       </c>
       <c r="E170" s="53"/>
       <c r="F170" s="53"/>
@@ -30209,7 +30241,7 @@
       <c r="E171" s="53"/>
       <c r="F171" s="53"/>
       <c r="G171" s="53" t="s">
-        <v>2179</v>
+        <v>2183</v>
       </c>
       <c r="H171" s="53"/>
       <c r="I171" s="53"/>
@@ -30219,13 +30251,13 @@
         <v>246</v>
       </c>
       <c r="B172" s="53" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="C172" s="48" t="s">
-        <v>2503</v>
+        <v>2507</v>
       </c>
       <c r="D172" s="8" t="s">
-        <v>2504</v>
+        <v>2508</v>
       </c>
       <c r="E172" s="53"/>
       <c r="F172" s="53"/>
@@ -30240,13 +30272,13 @@
         <v>246</v>
       </c>
       <c r="B173" s="53" t="s">
-        <v>2505</v>
+        <v>2509</v>
       </c>
       <c r="C173" s="48" t="s">
-        <v>2506</v>
+        <v>2510</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>2507</v>
+        <v>2511</v>
       </c>
       <c r="E173" s="53"/>
       <c r="F173" s="53"/>
@@ -30261,13 +30293,13 @@
         <v>246</v>
       </c>
       <c r="B174" s="53" t="s">
-        <v>2508</v>
+        <v>2512</v>
       </c>
       <c r="C174" s="48" t="s">
-        <v>2509</v>
+        <v>2513</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>2510</v>
+        <v>2514</v>
       </c>
       <c r="E174" s="53"/>
       <c r="F174" s="53"/>
@@ -30282,13 +30314,13 @@
         <v>246</v>
       </c>
       <c r="B175" s="53" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="C175" s="48" t="s">
-        <v>2512</v>
+        <v>2516</v>
       </c>
       <c r="D175" s="8" t="s">
-        <v>2513</v>
+        <v>2517</v>
       </c>
       <c r="E175" s="53"/>
       <c r="F175" s="53"/>
@@ -30303,13 +30335,13 @@
         <v>246</v>
       </c>
       <c r="B176" s="53" t="s">
-        <v>2514</v>
+        <v>2518</v>
       </c>
       <c r="C176" s="48" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>2516</v>
+        <v>2520</v>
       </c>
       <c r="E176" s="53"/>
       <c r="F176" s="53"/>
@@ -30324,13 +30356,13 @@
         <v>246</v>
       </c>
       <c r="B177" s="53" t="s">
-        <v>2517</v>
+        <v>2521</v>
       </c>
       <c r="C177" s="48" t="s">
-        <v>2518</v>
+        <v>2522</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>2519</v>
+        <v>2523</v>
       </c>
       <c r="E177" s="53"/>
       <c r="F177" s="53"/>
@@ -30345,13 +30377,13 @@
         <v>246</v>
       </c>
       <c r="B178" s="53" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="C178" s="48" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="D178" s="8" t="s">
-        <v>2522</v>
+        <v>2526</v>
       </c>
       <c r="E178" s="53"/>
       <c r="F178" s="53"/>
@@ -30366,13 +30398,13 @@
         <v>246</v>
       </c>
       <c r="B179" s="53" t="s">
-        <v>2523</v>
+        <v>2527</v>
       </c>
       <c r="C179" s="48" t="s">
-        <v>2524</v>
+        <v>2528</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="E179" s="53"/>
       <c r="F179" s="53"/>
@@ -30387,13 +30419,13 @@
         <v>246</v>
       </c>
       <c r="B180" s="53" t="s">
-        <v>2526</v>
+        <v>2530</v>
       </c>
       <c r="C180" s="48" t="s">
-        <v>2527</v>
+        <v>2531</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>2528</v>
+        <v>2532</v>
       </c>
       <c r="E180" s="53"/>
       <c r="F180" s="53"/>
@@ -30411,10 +30443,10 @@
         <v>229</v>
       </c>
       <c r="C181" s="48" t="s">
-        <v>2176</v>
+        <v>2180</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>2177</v>
+        <v>2181</v>
       </c>
       <c r="E181" s="53"/>
       <c r="F181" s="53"/>
@@ -30444,13 +30476,13 @@
         <v>258</v>
       </c>
       <c r="B183" s="53" t="s">
-        <v>2529</v>
+        <v>2533</v>
       </c>
       <c r="C183" s="48" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>2531</v>
+        <v>2535</v>
       </c>
       <c r="E183" s="53"/>
       <c r="F183" s="53"/>
@@ -30465,13 +30497,13 @@
         <v>258</v>
       </c>
       <c r="B184" s="53" t="s">
-        <v>2532</v>
+        <v>2536</v>
       </c>
       <c r="C184" s="48" t="s">
-        <v>2533</v>
+        <v>2537</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>2534</v>
+        <v>2538</v>
       </c>
       <c r="E184" s="53"/>
       <c r="F184" s="53"/>
@@ -30486,13 +30518,13 @@
         <v>258</v>
       </c>
       <c r="B185" s="53" t="s">
-        <v>2535</v>
+        <v>2539</v>
       </c>
       <c r="C185" s="48" t="s">
-        <v>2536</v>
+        <v>2540</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>2537</v>
+        <v>2541</v>
       </c>
       <c r="E185" s="53"/>
       <c r="F185" s="53"/>
@@ -30507,13 +30539,13 @@
         <v>258</v>
       </c>
       <c r="B186" s="53" t="s">
-        <v>2538</v>
+        <v>2542</v>
       </c>
       <c r="C186" s="48" t="s">
-        <v>2539</v>
+        <v>2543</v>
       </c>
       <c r="D186" s="8" t="s">
-        <v>2540</v>
+        <v>2544</v>
       </c>
       <c r="E186" s="53"/>
       <c r="F186" s="53"/>
@@ -30528,13 +30560,13 @@
         <v>258</v>
       </c>
       <c r="B187" s="53" t="s">
-        <v>2541</v>
+        <v>2545</v>
       </c>
       <c r="C187" s="48" t="s">
-        <v>2542</v>
+        <v>2546</v>
       </c>
       <c r="D187" s="8" t="s">
-        <v>2543</v>
+        <v>2547</v>
       </c>
       <c r="E187" s="53"/>
       <c r="F187" s="53"/>
@@ -30549,13 +30581,13 @@
         <v>258</v>
       </c>
       <c r="B188" s="53" t="s">
-        <v>2544</v>
+        <v>2548</v>
       </c>
       <c r="C188" s="48" t="s">
-        <v>2545</v>
+        <v>2549</v>
       </c>
       <c r="D188" s="8" t="s">
-        <v>2546</v>
+        <v>2550</v>
       </c>
       <c r="E188" s="53"/>
       <c r="F188" s="53"/>
@@ -30570,13 +30602,13 @@
         <v>258</v>
       </c>
       <c r="B189" s="53" t="s">
-        <v>2547</v>
+        <v>2551</v>
       </c>
       <c r="C189" s="48" t="s">
-        <v>2548</v>
+        <v>2552</v>
       </c>
       <c r="D189" s="8" t="s">
-        <v>2549</v>
+        <v>2553</v>
       </c>
       <c r="E189" s="53"/>
       <c r="F189" s="53"/>
@@ -30594,10 +30626,10 @@
         <v>1207</v>
       </c>
       <c r="C190" s="48" t="s">
-        <v>2550</v>
+        <v>2554</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>2551</v>
+        <v>2555</v>
       </c>
       <c r="E190" s="53"/>
       <c r="F190" s="53"/>
@@ -30614,10 +30646,10 @@
         <v>229</v>
       </c>
       <c r="C191" s="48" t="s">
-        <v>2176</v>
+        <v>2180</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>2177</v>
+        <v>2181</v>
       </c>
       <c r="E191" s="53"/>
       <c r="F191" s="53"/>
@@ -30635,10 +30667,10 @@
         <v>1171</v>
       </c>
       <c r="C192" s="53" t="s">
-        <v>2182</v>
+        <v>2186</v>
       </c>
       <c r="D192" s="53" t="s">
-        <v>2183</v>
+        <v>2187</v>
       </c>
       <c r="E192" s="53"/>
       <c r="F192" s="53"/>
@@ -30652,18 +30684,18 @@
         <v>287</v>
       </c>
       <c r="B193" s="53" t="s">
-        <v>2552</v>
+        <v>2556</v>
       </c>
       <c r="C193" s="48" t="s">
-        <v>2553</v>
+        <v>2557</v>
       </c>
       <c r="D193" s="8" t="s">
-        <v>2554</v>
+        <v>2558</v>
       </c>
       <c r="E193" s="53"/>
       <c r="F193" s="53"/>
       <c r="G193" s="53"/>
-      <c r="H193" s="97"/>
+      <c r="H193" s="98"/>
       <c r="I193" s="53"/>
     </row>
     <row r="194" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30671,13 +30703,13 @@
         <v>287</v>
       </c>
       <c r="B194" s="53" t="s">
-        <v>2555</v>
+        <v>2559</v>
       </c>
       <c r="C194" s="48" t="s">
-        <v>2556</v>
+        <v>2560</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>2557</v>
+        <v>2561</v>
       </c>
       <c r="E194" s="53"/>
       <c r="F194" s="53"/>
@@ -30690,13 +30722,13 @@
         <v>287</v>
       </c>
       <c r="B195" s="53" t="s">
-        <v>2558</v>
+        <v>2562</v>
       </c>
       <c r="C195" s="48" t="s">
-        <v>2559</v>
+        <v>2563</v>
       </c>
       <c r="D195" s="8" t="s">
-        <v>2560</v>
+        <v>2564</v>
       </c>
       <c r="E195" s="53"/>
       <c r="F195" s="53"/>
@@ -30709,13 +30741,13 @@
         <v>287</v>
       </c>
       <c r="B196" s="53" t="s">
-        <v>2561</v>
+        <v>2565</v>
       </c>
       <c r="C196" s="48" t="s">
-        <v>2562</v>
+        <v>2566</v>
       </c>
       <c r="D196" s="8" t="s">
-        <v>2563</v>
+        <v>2567</v>
       </c>
       <c r="E196" s="53"/>
       <c r="F196" s="53"/>
@@ -30728,13 +30760,13 @@
         <v>287</v>
       </c>
       <c r="B197" s="53" t="s">
-        <v>2564</v>
+        <v>2568</v>
       </c>
       <c r="C197" s="48" t="s">
-        <v>2565</v>
+        <v>2569</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>2566</v>
+        <v>2570</v>
       </c>
       <c r="E197" s="53"/>
       <c r="F197" s="53"/>
@@ -30747,18 +30779,18 @@
         <v>294</v>
       </c>
       <c r="B198" s="53" t="s">
-        <v>2552</v>
+        <v>2556</v>
       </c>
       <c r="C198" s="48" t="s">
-        <v>2553</v>
+        <v>2557</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>2554</v>
+        <v>2558</v>
       </c>
       <c r="E198" s="53"/>
       <c r="F198" s="53"/>
       <c r="G198" s="53"/>
-      <c r="H198" s="97" t="s">
+      <c r="H198" s="98" t="s">
         <v>1223</v>
       </c>
       <c r="I198" s="53"/>
@@ -30768,13 +30800,13 @@
         <v>294</v>
       </c>
       <c r="B199" s="53" t="s">
-        <v>2555</v>
+        <v>2559</v>
       </c>
       <c r="C199" s="48" t="s">
-        <v>2556</v>
+        <v>2560</v>
       </c>
       <c r="D199" s="8" t="s">
-        <v>2557</v>
+        <v>2561</v>
       </c>
       <c r="E199" s="53"/>
       <c r="F199" s="53"/>
@@ -30787,13 +30819,13 @@
         <v>294</v>
       </c>
       <c r="B200" s="53" t="s">
-        <v>2558</v>
+        <v>2562</v>
       </c>
       <c r="C200" s="48" t="s">
-        <v>2559</v>
+        <v>2563</v>
       </c>
       <c r="D200" s="8" t="s">
-        <v>2560</v>
+        <v>2564</v>
       </c>
       <c r="E200" s="53"/>
       <c r="F200" s="53"/>
@@ -30806,13 +30838,13 @@
         <v>294</v>
       </c>
       <c r="B201" s="53" t="s">
-        <v>2561</v>
+        <v>2565</v>
       </c>
       <c r="C201" s="48" t="s">
-        <v>2562</v>
+        <v>2566</v>
       </c>
       <c r="D201" s="8" t="s">
-        <v>2563</v>
+        <v>2567</v>
       </c>
       <c r="E201" s="53"/>
       <c r="F201" s="53"/>
@@ -30825,13 +30857,13 @@
         <v>294</v>
       </c>
       <c r="B202" s="53" t="s">
-        <v>2564</v>
+        <v>2568</v>
       </c>
       <c r="C202" s="48" t="s">
-        <v>2565</v>
+        <v>2569</v>
       </c>
       <c r="D202" s="8" t="s">
-        <v>2566</v>
+        <v>2570</v>
       </c>
       <c r="E202" s="53"/>
       <c r="F202" s="53"/>
@@ -30844,7 +30876,7 @@
         <v>857</v>
       </c>
       <c r="B203" s="66" t="s">
-        <v>2426</v>
+        <v>2430</v>
       </c>
       <c r="C203" s="66" t="s">
         <v>2021</v>
@@ -30858,7 +30890,7 @@
         <v>857</v>
       </c>
       <c r="B204" s="66" t="s">
-        <v>2434</v>
+        <v>2438</v>
       </c>
       <c r="C204" s="66" t="s">
         <v>2040</v>
@@ -30872,13 +30904,13 @@
         <v>857</v>
       </c>
       <c r="B205" s="66" t="s">
-        <v>2567</v>
+        <v>2571</v>
       </c>
       <c r="C205" s="66" t="s">
-        <v>2568</v>
+        <v>2572</v>
       </c>
       <c r="D205" s="66" t="s">
-        <v>2569</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30886,13 +30918,13 @@
         <v>857</v>
       </c>
       <c r="B206" s="66" t="s">
-        <v>2438</v>
+        <v>2442</v>
       </c>
       <c r="C206" s="66" t="s">
-        <v>2570</v>
+        <v>2574</v>
       </c>
       <c r="D206" s="66" t="s">
-        <v>2571</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30900,7 +30932,7 @@
         <v>857</v>
       </c>
       <c r="G207" s="66" t="s">
-        <v>2178</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30908,13 +30940,13 @@
         <v>882</v>
       </c>
       <c r="B208" s="66" t="s">
-        <v>2572</v>
+        <v>2576</v>
       </c>
       <c r="C208" s="66" t="s">
-        <v>2573</v>
+        <v>2577</v>
       </c>
       <c r="D208" s="66" t="s">
-        <v>2574</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30922,13 +30954,13 @@
         <v>882</v>
       </c>
       <c r="B209" s="66" t="s">
-        <v>2575</v>
+        <v>2579</v>
       </c>
       <c r="C209" s="66" t="s">
-        <v>2576</v>
+        <v>2580</v>
       </c>
       <c r="D209" s="66" t="s">
-        <v>2577</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30936,13 +30968,13 @@
         <v>882</v>
       </c>
       <c r="B210" s="66" t="s">
-        <v>2578</v>
+        <v>2582</v>
       </c>
       <c r="C210" s="66" t="s">
-        <v>2579</v>
+        <v>2583</v>
       </c>
       <c r="D210" s="66" t="s">
-        <v>2580</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30950,13 +30982,13 @@
         <v>882</v>
       </c>
       <c r="B211" s="66" t="s">
-        <v>2581</v>
+        <v>2585</v>
       </c>
       <c r="C211" s="66" t="s">
-        <v>2582</v>
+        <v>2586</v>
       </c>
       <c r="D211" s="66" t="s">
-        <v>2583</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30964,13 +30996,13 @@
         <v>882</v>
       </c>
       <c r="B212" s="66" t="s">
-        <v>2584</v>
+        <v>2588</v>
       </c>
       <c r="C212" s="66" t="s">
-        <v>2585</v>
+        <v>2589</v>
       </c>
       <c r="D212" s="66" t="s">
-        <v>2586</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30978,13 +31010,13 @@
         <v>882</v>
       </c>
       <c r="B213" s="66" t="s">
-        <v>2587</v>
+        <v>2591</v>
       </c>
       <c r="C213" s="66" t="s">
-        <v>2588</v>
+        <v>2592</v>
       </c>
       <c r="D213" s="66" t="s">
-        <v>2589</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30995,10 +31027,10 @@
         <v>229</v>
       </c>
       <c r="C214" s="66" t="s">
-        <v>2590</v>
+        <v>2594</v>
       </c>
       <c r="D214" s="66" t="s">
-        <v>2591</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31006,7 +31038,7 @@
         <v>887</v>
       </c>
       <c r="B215" s="66" t="s">
-        <v>2426</v>
+        <v>2430</v>
       </c>
       <c r="C215" s="66" t="s">
         <v>2021</v>
@@ -31020,7 +31052,7 @@
         <v>887</v>
       </c>
       <c r="B216" s="66" t="s">
-        <v>2434</v>
+        <v>2438</v>
       </c>
       <c r="C216" s="66" t="s">
         <v>2040</v>
@@ -31034,13 +31066,13 @@
         <v>887</v>
       </c>
       <c r="B217" s="66" t="s">
-        <v>2432</v>
+        <v>2436</v>
       </c>
       <c r="C217" s="66" t="s">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="D217" s="66" t="s">
-        <v>2593</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="218" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31048,13 +31080,13 @@
         <v>887</v>
       </c>
       <c r="B218" s="66" t="s">
-        <v>2433</v>
+        <v>2437</v>
       </c>
       <c r="C218" s="66" t="s">
-        <v>2594</v>
+        <v>2598</v>
       </c>
       <c r="D218" s="66" t="s">
-        <v>2595</v>
+        <v>2599</v>
       </c>
       <c r="E218" s="66"/>
       <c r="F218" s="66"/>
@@ -31067,13 +31099,13 @@
         <v>887</v>
       </c>
       <c r="B219" s="66" t="s">
-        <v>2438</v>
+        <v>2442</v>
       </c>
       <c r="C219" s="66" t="s">
-        <v>2570</v>
+        <v>2574</v>
       </c>
       <c r="D219" s="66" t="s">
-        <v>2571</v>
+        <v>2575</v>
       </c>
       <c r="E219" s="66"/>
       <c r="F219" s="66"/>
@@ -31089,10 +31121,10 @@
         <v>229</v>
       </c>
       <c r="C220" s="66" t="s">
-        <v>2596</v>
+        <v>2600</v>
       </c>
       <c r="D220" s="66" t="s">
-        <v>2597</v>
+        <v>2601</v>
       </c>
       <c r="E220" s="66"/>
       <c r="F220" s="66"/>
@@ -31108,10 +31140,10 @@
         <v>1258</v>
       </c>
       <c r="C221" s="8" t="s">
-        <v>2598</v>
+        <v>2602</v>
       </c>
       <c r="D221" s="8" t="s">
-        <v>2599</v>
+        <v>2603</v>
       </c>
       <c r="E221" s="66"/>
       <c r="F221" s="66"/>
@@ -31124,13 +31156,13 @@
         <v>1052</v>
       </c>
       <c r="B222" s="66" t="s">
-        <v>2600</v>
+        <v>2604</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>2601</v>
+        <v>2605</v>
       </c>
       <c r="D222" s="8" t="s">
-        <v>2602</v>
+        <v>2606</v>
       </c>
       <c r="E222" s="66"/>
       <c r="F222" s="66"/>
@@ -31145,13 +31177,13 @@
         <v>1052</v>
       </c>
       <c r="B223" s="66" t="s">
-        <v>2603</v>
+        <v>2607</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>2604</v>
+        <v>2608</v>
       </c>
       <c r="D223" s="8" t="s">
-        <v>2605</v>
+        <v>2609</v>
       </c>
       <c r="E223" s="66"/>
       <c r="F223" s="66"/>
@@ -31166,13 +31198,13 @@
         <v>1052</v>
       </c>
       <c r="B224" s="66" t="s">
-        <v>2606</v>
+        <v>2610</v>
       </c>
       <c r="C224" s="8" t="s">
-        <v>2607</v>
+        <v>2611</v>
       </c>
       <c r="D224" s="51" t="s">
-        <v>2608</v>
+        <v>2612</v>
       </c>
       <c r="E224" s="66"/>
       <c r="F224" s="66"/>
@@ -31187,13 +31219,13 @@
         <v>1052</v>
       </c>
       <c r="B225" s="66" t="s">
-        <v>2609</v>
+        <v>2613</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>2610</v>
+        <v>2614</v>
       </c>
       <c r="D225" s="48" t="s">
-        <v>2611</v>
+        <v>2615</v>
       </c>
       <c r="E225" s="66"/>
       <c r="F225" s="66"/>
@@ -31206,13 +31238,13 @@
         <v>1058</v>
       </c>
       <c r="B226" s="66" t="s">
-        <v>2612</v>
+        <v>2616</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>2613</v>
+        <v>2617</v>
       </c>
       <c r="D226" s="8" t="s">
-        <v>2614</v>
+        <v>2618</v>
       </c>
       <c r="E226" s="66"/>
       <c r="F226" s="66"/>
@@ -31227,13 +31259,13 @@
         <v>1058</v>
       </c>
       <c r="B227" s="66" t="s">
-        <v>2615</v>
+        <v>2619</v>
       </c>
       <c r="C227" s="8" t="s">
-        <v>2616</v>
+        <v>2620</v>
       </c>
       <c r="D227" s="8" t="s">
-        <v>2617</v>
+        <v>2621</v>
       </c>
       <c r="E227" s="66"/>
       <c r="F227" s="66"/>
@@ -31248,13 +31280,13 @@
         <v>1058</v>
       </c>
       <c r="B228" s="66" t="s">
-        <v>2618</v>
+        <v>2622</v>
       </c>
       <c r="C228" s="8" t="s">
-        <v>2619</v>
+        <v>2623</v>
       </c>
       <c r="D228" s="8" t="s">
-        <v>2620</v>
+        <v>2624</v>
       </c>
       <c r="E228" s="66"/>
       <c r="F228" s="66"/>
@@ -31264,16 +31296,16 @@
     </row>
     <row r="229" s="50" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="54" t="s">
-        <v>2621</v>
+        <v>2625</v>
       </c>
       <c r="B229" s="66" t="s">
         <v>1167</v>
       </c>
       <c r="C229" s="51" t="s">
-        <v>2622</v>
+        <v>2626</v>
       </c>
       <c r="D229" s="8" t="s">
-        <v>2623</v>
+        <v>2627</v>
       </c>
       <c r="E229" s="66"/>
       <c r="F229" s="66"/>
@@ -31283,16 +31315,16 @@
     </row>
     <row r="230" s="50" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="54" t="s">
-        <v>2621</v>
+        <v>2625</v>
       </c>
       <c r="B230" s="66" t="s">
         <v>1225</v>
       </c>
       <c r="C230" s="51" t="s">
-        <v>2624</v>
+        <v>2628</v>
       </c>
       <c r="D230" s="48" t="s">
-        <v>2625</v>
+        <v>2629</v>
       </c>
       <c r="E230" s="66"/>
       <c r="F230" s="66"/>
@@ -31305,13 +31337,13 @@
         <v>1088</v>
       </c>
       <c r="B231" s="66" t="s">
-        <v>2626</v>
+        <v>2630</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>2627</v>
+        <v>2631</v>
       </c>
       <c r="D231" s="51" t="s">
-        <v>2628</v>
+        <v>2632</v>
       </c>
       <c r="E231" s="66"/>
       <c r="F231" s="66"/>
@@ -31324,13 +31356,13 @@
         <v>1088</v>
       </c>
       <c r="B232" s="66" t="s">
-        <v>2629</v>
+        <v>2633</v>
       </c>
       <c r="C232" s="8" t="s">
-        <v>2630</v>
+        <v>2634</v>
       </c>
       <c r="D232" s="51" t="s">
-        <v>2631</v>
+        <v>2635</v>
       </c>
       <c r="E232" s="66"/>
       <c r="F232" s="66"/>
@@ -31343,13 +31375,13 @@
         <v>1088</v>
       </c>
       <c r="B233" s="66" t="s">
-        <v>2632</v>
+        <v>2636</v>
       </c>
       <c r="C233" s="8" t="s">
-        <v>2633</v>
+        <v>2637</v>
       </c>
       <c r="D233" s="51" t="s">
-        <v>2634</v>
+        <v>2638</v>
       </c>
       <c r="E233" s="66"/>
       <c r="F233" s="66"/>
@@ -31362,13 +31394,13 @@
         <v>1088</v>
       </c>
       <c r="B234" s="66" t="s">
-        <v>2635</v>
+        <v>2639</v>
       </c>
       <c r="C234" s="8" t="s">
-        <v>2636</v>
+        <v>2640</v>
       </c>
       <c r="D234" s="51" t="s">
-        <v>2637</v>
+        <v>2641</v>
       </c>
       <c r="E234" s="66"/>
       <c r="F234" s="66"/>
@@ -31381,13 +31413,13 @@
         <v>1088</v>
       </c>
       <c r="B235" s="66" t="s">
-        <v>2638</v>
+        <v>2642</v>
       </c>
       <c r="C235" s="8" t="s">
-        <v>2639</v>
+        <v>2643</v>
       </c>
       <c r="D235" s="51" t="s">
-        <v>2640</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="236" s="50" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31395,13 +31427,13 @@
         <v>1088</v>
       </c>
       <c r="B236" s="66" t="s">
-        <v>2641</v>
+        <v>2645</v>
       </c>
       <c r="C236" s="8" t="s">
-        <v>2642</v>
+        <v>2646</v>
       </c>
       <c r="D236" s="51" t="s">
-        <v>2643</v>
+        <v>2647</v>
       </c>
       <c r="E236" s="66"/>
       <c r="F236" s="66"/>
@@ -31419,7 +31451,7 @@
       <c r="E237" s="66"/>
       <c r="F237" s="66"/>
       <c r="G237" s="53" t="s">
-        <v>2178</v>
+        <v>2182</v>
       </c>
       <c r="H237" s="66"/>
       <c r="I237" s="66"/>
@@ -31429,13 +31461,13 @@
         <v>946</v>
       </c>
       <c r="B238" s="50" t="s">
-        <v>2644</v>
+        <v>2648</v>
       </c>
       <c r="C238" s="50" t="s">
-        <v>2645</v>
+        <v>2649</v>
       </c>
       <c r="D238" s="50" t="s">
-        <v>2646</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="239" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31443,13 +31475,13 @@
         <v>946</v>
       </c>
       <c r="B239" s="50" t="s">
-        <v>2558</v>
+        <v>2562</v>
       </c>
       <c r="C239" s="50" t="s">
-        <v>2647</v>
+        <v>2651</v>
       </c>
       <c r="D239" s="50" t="s">
-        <v>2648</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="240" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31457,13 +31489,13 @@
         <v>946</v>
       </c>
       <c r="B240" s="50" t="s">
-        <v>2649</v>
+        <v>2653</v>
       </c>
       <c r="C240" s="50" t="s">
-        <v>2650</v>
+        <v>2654</v>
       </c>
       <c r="D240" s="50" t="s">
-        <v>2651</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="241" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31471,13 +31503,13 @@
         <v>946</v>
       </c>
       <c r="B241" s="50" t="s">
-        <v>2652</v>
+        <v>2656</v>
       </c>
       <c r="C241" s="50" t="s">
-        <v>2653</v>
+        <v>2657</v>
       </c>
       <c r="D241" s="50" t="s">
-        <v>2654</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="242" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31485,13 +31517,13 @@
         <v>946</v>
       </c>
       <c r="B242" s="50" t="s">
-        <v>2655</v>
+        <v>2659</v>
       </c>
       <c r="C242" s="50" t="s">
-        <v>2656</v>
+        <v>2660</v>
       </c>
       <c r="D242" s="50" t="s">
-        <v>2657</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="243" s="50" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31502,10 +31534,10 @@
         <v>-2</v>
       </c>
       <c r="C243" s="57" t="s">
-        <v>2658</v>
+        <v>2662</v>
       </c>
       <c r="D243" s="57" t="s">
-        <v>2659</v>
+        <v>2663</v>
       </c>
       <c r="E243" s="66"/>
       <c r="F243" s="66"/>
@@ -31521,10 +31553,10 @@
         <v>-1</v>
       </c>
       <c r="C244" s="57" t="s">
-        <v>2660</v>
+        <v>2664</v>
       </c>
       <c r="D244" s="57" t="s">
-        <v>2661</v>
+        <v>2665</v>
       </c>
       <c r="E244" s="66"/>
       <c r="F244" s="66"/>
@@ -31540,10 +31572,10 @@
         <v>0</v>
       </c>
       <c r="C245" s="57" t="s">
-        <v>2662</v>
+        <v>2666</v>
       </c>
       <c r="D245" s="57" t="s">
-        <v>2663</v>
+        <v>2667</v>
       </c>
       <c r="E245" s="66"/>
       <c r="F245" s="66"/>
@@ -31559,10 +31591,10 @@
         <v>1</v>
       </c>
       <c r="C246" s="57" t="s">
-        <v>2664</v>
+        <v>2668</v>
       </c>
       <c r="D246" s="57" t="s">
-        <v>2665</v>
+        <v>2669</v>
       </c>
       <c r="E246" s="66"/>
       <c r="F246" s="66"/>
@@ -31578,10 +31610,10 @@
         <v>2</v>
       </c>
       <c r="C247" s="57" t="s">
-        <v>2666</v>
+        <v>2670</v>
       </c>
       <c r="D247" s="57" t="s">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="E247" s="66"/>
       <c r="F247" s="66"/>
@@ -31597,10 +31629,10 @@
         <v>0</v>
       </c>
       <c r="C248" s="48" t="s">
-        <v>2668</v>
+        <v>2672</v>
       </c>
       <c r="D248" s="57" t="s">
-        <v>2669</v>
+        <v>2673</v>
       </c>
       <c r="E248" s="66"/>
       <c r="F248" s="66"/>
@@ -31616,10 +31648,10 @@
         <v>1</v>
       </c>
       <c r="C249" s="48" t="s">
-        <v>2670</v>
+        <v>2674</v>
       </c>
       <c r="D249" s="51" t="s">
-        <v>2671</v>
+        <v>2675</v>
       </c>
       <c r="E249" s="66"/>
       <c r="F249" s="66"/>
@@ -31635,10 +31667,10 @@
         <v>2</v>
       </c>
       <c r="C250" s="48" t="s">
-        <v>2672</v>
+        <v>2676</v>
       </c>
       <c r="D250" s="51" t="s">
-        <v>2673</v>
+        <v>2677</v>
       </c>
       <c r="E250" s="66"/>
       <c r="F250" s="66"/>
@@ -31654,10 +31686,10 @@
         <v>3</v>
       </c>
       <c r="C251" s="48" t="s">
-        <v>2674</v>
+        <v>2678</v>
       </c>
       <c r="D251" s="51" t="s">
-        <v>2675</v>
+        <v>2679</v>
       </c>
       <c r="E251" s="66"/>
       <c r="F251" s="66"/>
@@ -31673,10 +31705,10 @@
         <v>4</v>
       </c>
       <c r="C252" s="48" t="s">
-        <v>2676</v>
+        <v>2680</v>
       </c>
       <c r="D252" s="51" t="s">
-        <v>2677</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31687,10 +31719,10 @@
         <v>-1</v>
       </c>
       <c r="C253" s="48" t="s">
-        <v>2678</v>
+        <v>2682</v>
       </c>
       <c r="D253" s="51" t="s">
-        <v>2679</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31698,13 +31730,13 @@
         <v>39</v>
       </c>
       <c r="B254" s="66" t="s">
-        <v>2680</v>
+        <v>2684</v>
       </c>
       <c r="C254" s="66" t="s">
-        <v>2681</v>
+        <v>2685</v>
       </c>
       <c r="D254" s="66" t="s">
-        <v>2682</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -1549,10 +1549,10 @@
     <t xml:space="preserve">departurePlaceOtherChoices</t>
   </si>
   <si>
-    <t xml:space="preserve">personOutOfTerritory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">household.persons.{_activePersonId}.journeys.{_activeJourneyId}.outOfTerritory</t>
+    <t xml:space="preserve">personReturnedHome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">household.persons.{_activePersonId}.journeys.{_activeJourneyId}.returnedHome</t>
   </si>
   <si>
     <t xml:space="preserve">Est-ce que {{nickname}} est retourn{{gender:é/ée/é(e)}} au domicile ({{address}}) la journée du {{journeyDate}}?</t>
@@ -1621,13 +1621,13 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">customLabels={{personOutOfTerritoryCustomLabel}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">outOfTerritoryConditional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">outOfTerritoryCustomChoices</t>
+    <t xml:space="preserve">customLabels={{personReturnedHomeCustomLabel}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">returnedHomeConditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">returnedHomeCustomChoices</t>
   </si>
   <si>
     <t xml:space="preserve">Custom choices because it has the departure place type in the labels
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">hotelForVacation</t>
   </si>
   <si>
-    <t xml:space="preserve">${currentJourney}.outOfTerritory</t>
+    <t xml:space="preserve">${currentJourney}.returnedHome</t>
   </si>
   <si>
     <t xml:space="preserve">isCurrentSegmentNotTransitBusConditional</t>
@@ -6304,7 +6304,7 @@
     <t xml:space="preserve">I did make at least one trip on {{journeyDate}}</t>
   </si>
   <si>
-    <t xml:space="preserve">outOfTerritoryChoiceNo</t>
+    <t xml:space="preserve">returnedHomeChoiceNo</t>
   </si>
   <si>
     <t xml:space="preserve">Non, {{nickname}} est rest{{gender:é/ée/é(e)}} à cet endroit jusqu’au lendemain</t>
@@ -6319,7 +6319,7 @@
     <t xml:space="preserve">No, I stayed at this place until the next day</t>
   </si>
   <si>
-    <t xml:space="preserve">outOfTerritoryChoiceNo_hotelForWork</t>
+    <t xml:space="preserve">returnedHomeChoiceNo_hotelForWork</t>
   </si>
   <si>
     <t xml:space="preserve">Non, {{nickname}} est rest{{gender:é/ée/é(e)}} en voyage pour le travail jusqu’au lendemain</t>
@@ -6334,7 +6334,7 @@
     <t xml:space="preserve">No, I stayed away for work until the next day</t>
   </si>
   <si>
-    <t xml:space="preserve">outOfTerritoryChoiceNo_hotelForVacation</t>
+    <t xml:space="preserve">returnedHomeChoiceNo_hotelForVacation</t>
   </si>
   <si>
     <t xml:space="preserve">Non, {{nickname}} est rest{{gender:é/ée/é(e)}} en vacances jusqu’au lendemain</t>
@@ -6349,7 +6349,7 @@
     <t xml:space="preserve">No, I stayed on vacation until the next day</t>
   </si>
   <si>
-    <t xml:space="preserve">outOfTerritoryChoiceYes</t>
+    <t xml:space="preserve">returnedHomeChoiceYes</t>
   </si>
   <si>
     <t xml:space="preserve">Oui, {{nickname}} est reven{{gender:u/ue/u(e)}} au domicile avant le lendemain</t>
@@ -9397,8 +9397,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -21315,7 +21315,7 @@
         <v>1163</v>
       </c>
       <c r="E82" s="57" t="s">
-        <v>1167</v>
+        <v>1225</v>
       </c>
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
@@ -23250,7 +23250,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1048576"/>
+  <dimension ref="A1:F266"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="50" width="16.66"/>
@@ -27343,8 +27343,8 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="50" t="s">
+    <row r="266" s="87" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="87" t="s">
         <v>2169</v>
       </c>
       <c r="B266" s="87" t="s">
@@ -27357,8 +27357,6 @@
         <v>2172</v>
       </c>
     </row>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <autoFilter ref="A1:F260"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -4250,7 +4250,7 @@
     <t xml:space="preserve">${currentPerson}.hasSchoolPlace</t>
   </si>
   <si>
-    <t xml:space="preserve">home.RA</t>
+    <t xml:space="preserve">home.geography.properties.RA</t>
   </si>
   <si>
     <t xml:space="preserve">freqAttitudinal</t>
@@ -9048,7 +9048,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="98">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9394,10 +9394,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -27343,17 +27339,17 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="266" s="87" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="87" t="s">
+    <row r="266" s="74" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="74" t="s">
         <v>2169</v>
       </c>
-      <c r="B266" s="87" t="s">
+      <c r="B266" s="74" t="s">
         <v>2170</v>
       </c>
-      <c r="C266" s="87" t="s">
+      <c r="C266" s="74" t="s">
         <v>2171</v>
       </c>
-      <c r="D266" s="87" t="s">
+      <c r="D266" s="74" t="s">
         <v>2172</v>
       </c>
     </row>
@@ -27387,28 +27383,28 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="87" t="s">
         <v>2173</v>
       </c>
-      <c r="B1" s="88" t="s">
+      <c r="B1" s="87" t="s">
         <v>1159</v>
       </c>
-      <c r="C1" s="88" t="s">
+      <c r="C1" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="88" t="s">
+      <c r="D1" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="89" t="s">
+      <c r="E1" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="89" t="s">
+      <c r="F1" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="88" t="s">
+      <c r="G1" s="87" t="s">
         <v>2174</v>
       </c>
-      <c r="H1" s="88" t="s">
+      <c r="H1" s="87" t="s">
         <v>12</v>
       </c>
       <c r="I1" s="66" t="s">
@@ -27660,7 +27656,7 @@
       <c r="I16" s="53"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="90" t="s">
+      <c r="A17" s="89" t="s">
         <v>2192</v>
       </c>
       <c r="B17" s="53" t="s">
@@ -27678,7 +27674,7 @@
       <c r="H17" s="53"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="90" t="s">
+      <c r="A18" s="89" t="s">
         <v>2192</v>
       </c>
       <c r="B18" s="53" t="s">
@@ -27696,7 +27692,7 @@
       <c r="H18" s="53"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="90" t="s">
+      <c r="A19" s="89" t="s">
         <v>2192</v>
       </c>
       <c r="B19" s="53"/>
@@ -27710,7 +27706,7 @@
       <c r="H19" s="53"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="90" t="s">
+      <c r="A20" s="89" t="s">
         <v>187</v>
       </c>
       <c r="B20" s="53" t="s">
@@ -27728,7 +27724,7 @@
       <c r="H20" s="53"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="89" t="s">
         <v>187</v>
       </c>
       <c r="B21" s="53" t="s">
@@ -27746,7 +27742,7 @@
       <c r="H21" s="53"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="89" t="s">
         <v>187</v>
       </c>
       <c r="B22" s="53" t="s">
@@ -27764,7 +27760,7 @@
       <c r="H22" s="53"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="90" t="s">
+      <c r="A23" s="89" t="s">
         <v>187</v>
       </c>
       <c r="B23" s="53"/>
@@ -27894,7 +27890,7 @@
       <c r="F30" s="53"/>
       <c r="G30" s="53"/>
       <c r="H30" s="53"/>
-      <c r="I30" s="91" t="n">
+      <c r="I30" s="90" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -27916,7 +27912,7 @@
       <c r="F31" s="53"/>
       <c r="G31" s="53"/>
       <c r="H31" s="53"/>
-      <c r="I31" s="91" t="n">
+      <c r="I31" s="90" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -27938,7 +27934,7 @@
       <c r="F32" s="53"/>
       <c r="G32" s="53"/>
       <c r="H32" s="53"/>
-      <c r="I32" s="91" t="n">
+      <c r="I32" s="90" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -27960,7 +27956,7 @@
       <c r="F33" s="53"/>
       <c r="G33" s="53"/>
       <c r="H33" s="53"/>
-      <c r="I33" s="91" t="n">
+      <c r="I33" s="90" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -27982,7 +27978,7 @@
       <c r="F34" s="53"/>
       <c r="G34" s="53"/>
       <c r="H34" s="53"/>
-      <c r="I34" s="91" t="n">
+      <c r="I34" s="90" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -28540,7 +28536,7 @@
       <c r="I64" s="53"/>
     </row>
     <row r="65" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="90" t="s">
+      <c r="A65" s="89" t="s">
         <v>322</v>
       </c>
       <c r="B65" s="53" t="s">
@@ -28561,7 +28557,7 @@
       <c r="I65" s="66"/>
     </row>
     <row r="66" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="90" t="s">
+      <c r="A66" s="89" t="s">
         <v>322</v>
       </c>
       <c r="B66" s="53" t="s">
@@ -28582,7 +28578,7 @@
       <c r="I66" s="66"/>
     </row>
     <row r="67" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="90" t="s">
+      <c r="A67" s="89" t="s">
         <v>322</v>
       </c>
       <c r="B67" s="53" t="s">
@@ -28603,7 +28599,7 @@
       <c r="I67" s="66"/>
     </row>
     <row r="68" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="90" t="s">
+      <c r="A68" s="89" t="s">
         <v>322</v>
       </c>
       <c r="B68" s="53" t="s">
@@ -28624,7 +28620,7 @@
       <c r="I68" s="66"/>
     </row>
     <row r="69" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="90" t="s">
+      <c r="A69" s="89" t="s">
         <v>322</v>
       </c>
       <c r="B69" s="53" t="s">
@@ -28645,7 +28641,7 @@
       <c r="I69" s="66"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="90" t="s">
+      <c r="A70" s="89" t="s">
         <v>905</v>
       </c>
       <c r="B70" s="66" t="s">
@@ -28659,7 +28655,7 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="90" t="s">
+      <c r="A71" s="89" t="s">
         <v>905</v>
       </c>
       <c r="B71" s="66" t="s">
@@ -28673,7 +28669,7 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="90" t="s">
+      <c r="A72" s="89" t="s">
         <v>905</v>
       </c>
       <c r="B72" s="66" t="s">
@@ -28687,7 +28683,7 @@
       </c>
     </row>
     <row r="73" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="90" t="s">
+      <c r="A73" s="89" t="s">
         <v>905</v>
       </c>
       <c r="B73" s="66" t="s">
@@ -28915,7 +28911,7 @@
       <c r="I84" s="53"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="92" t="s">
+      <c r="A85" s="91" t="s">
         <v>99</v>
       </c>
       <c r="B85" s="66" t="s">
@@ -28929,7 +28925,7 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="92" t="s">
+      <c r="A86" s="91" t="s">
         <v>99</v>
       </c>
       <c r="B86" s="66" t="s">
@@ -28943,7 +28939,7 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="92" t="s">
+      <c r="A87" s="91" t="s">
         <v>99</v>
       </c>
       <c r="B87" s="66" t="s">
@@ -28957,7 +28953,7 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="92" t="s">
+      <c r="A88" s="91" t="s">
         <v>99</v>
       </c>
       <c r="B88" s="66" t="s">
@@ -28971,7 +28967,7 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="93" t="s">
+      <c r="A89" s="92" t="s">
         <v>423</v>
       </c>
       <c r="B89" s="53" t="s">
@@ -28992,7 +28988,7 @@
       <c r="I89" s="53"/>
     </row>
     <row r="90" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="93" t="s">
+      <c r="A90" s="92" t="s">
         <v>423</v>
       </c>
       <c r="B90" s="53" t="s">
@@ -29013,7 +29009,7 @@
       <c r="I90" s="53"/>
     </row>
     <row r="91" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="93" t="s">
+      <c r="A91" s="92" t="s">
         <v>423</v>
       </c>
       <c r="B91" s="53" t="s">
@@ -29032,7 +29028,7 @@
       <c r="I91" s="53"/>
     </row>
     <row r="92" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="93" t="s">
+      <c r="A92" s="92" t="s">
         <v>423</v>
       </c>
       <c r="B92" s="53" t="s">
@@ -29051,7 +29047,7 @@
       <c r="I92" s="53"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="93" t="s">
+      <c r="A93" s="92" t="s">
         <v>423</v>
       </c>
       <c r="B93" s="53" t="s">
@@ -29070,7 +29066,7 @@
       <c r="I93" s="53"/>
     </row>
     <row r="94" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="93" t="s">
+      <c r="A94" s="92" t="s">
         <v>423</v>
       </c>
       <c r="B94" s="53" t="s">
@@ -29091,7 +29087,7 @@
       <c r="I94" s="53"/>
     </row>
     <row r="95" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="93" t="s">
+      <c r="A95" s="92" t="s">
         <v>423</v>
       </c>
       <c r="B95" s="53" t="s">
@@ -29110,7 +29106,7 @@
       <c r="I95" s="53"/>
     </row>
     <row r="96" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="93" t="s">
+      <c r="A96" s="92" t="s">
         <v>423</v>
       </c>
       <c r="B96" s="53" t="s">
@@ -29131,7 +29127,7 @@
       <c r="I96" s="53"/>
     </row>
     <row r="97" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="93" t="s">
+      <c r="A97" s="92" t="s">
         <v>423</v>
       </c>
       <c r="B97" s="53" t="s">
@@ -29150,7 +29146,7 @@
       <c r="I97" s="53"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="94" t="s">
+      <c r="A98" s="93" t="s">
         <v>2374</v>
       </c>
       <c r="B98" s="66" t="s">
@@ -29170,7 +29166,7 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="94" t="s">
+      <c r="A99" s="93" t="s">
         <v>2374</v>
       </c>
       <c r="B99" s="66" t="s">
@@ -29190,7 +29186,7 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="94" t="s">
+      <c r="A100" s="93" t="s">
         <v>2374</v>
       </c>
       <c r="B100" s="66" t="s">
@@ -29204,7 +29200,7 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="94" t="s">
+      <c r="A101" s="93" t="s">
         <v>771</v>
       </c>
       <c r="B101" s="66" t="s">
@@ -29218,7 +29214,7 @@
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="94" t="s">
+      <c r="A102" s="93" t="s">
         <v>771</v>
       </c>
       <c r="B102" s="66" t="s">
@@ -29230,13 +29226,13 @@
       <c r="D102" s="66" t="s">
         <v>2382</v>
       </c>
-      <c r="I102" s="91" t="n">
+      <c r="I102" s="90" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="94" t="s">
+      <c r="A103" s="93" t="s">
         <v>771</v>
       </c>
       <c r="B103" s="66" t="s">
@@ -29250,7 +29246,7 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="94" t="s">
+      <c r="A104" s="93" t="s">
         <v>771</v>
       </c>
       <c r="B104" s="66" t="s">
@@ -29264,7 +29260,7 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="94" t="s">
+      <c r="A105" s="93" t="s">
         <v>771</v>
       </c>
       <c r="G105" s="53" t="s">
@@ -29272,7 +29268,7 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="94" t="s">
+      <c r="A106" s="93" t="s">
         <v>771</v>
       </c>
       <c r="G106" s="53" t="s">
@@ -29280,7 +29276,7 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="94" t="s">
+      <c r="A107" s="93" t="s">
         <v>829</v>
       </c>
       <c r="B107" s="66" t="s">
@@ -29294,7 +29290,7 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="94" t="s">
+      <c r="A108" s="93" t="s">
         <v>829</v>
       </c>
       <c r="B108" s="66" t="s">
@@ -29308,7 +29304,7 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="94" t="s">
+      <c r="A109" s="93" t="s">
         <v>829</v>
       </c>
       <c r="B109" s="66" t="s">
@@ -29322,7 +29318,7 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="94" t="s">
+      <c r="A110" s="93" t="s">
         <v>829</v>
       </c>
       <c r="B110" s="53" t="s">
@@ -29334,13 +29330,13 @@
       <c r="D110" s="48" t="s">
         <v>2399</v>
       </c>
-      <c r="I110" s="91" t="n">
+      <c r="I110" s="90" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="94" t="s">
+      <c r="A111" s="93" t="s">
         <v>829</v>
       </c>
       <c r="G111" s="53" t="s">
@@ -29348,7 +29344,7 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="94" t="s">
+      <c r="A112" s="93" t="s">
         <v>829</v>
       </c>
       <c r="G112" s="53" t="s">
@@ -29356,7 +29352,7 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="95" t="s">
+      <c r="A113" s="94" t="s">
         <v>347</v>
       </c>
       <c r="B113" s="66" t="s">
@@ -29370,7 +29366,7 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="95" t="s">
+      <c r="A114" s="94" t="s">
         <v>347</v>
       </c>
       <c r="B114" s="66" t="s">
@@ -29384,7 +29380,7 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="95" t="s">
+      <c r="A115" s="94" t="s">
         <v>347</v>
       </c>
       <c r="B115" s="66" t="s">
@@ -29398,7 +29394,7 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="95" t="s">
+      <c r="A116" s="94" t="s">
         <v>347</v>
       </c>
       <c r="G116" s="53" t="s">
@@ -29406,7 +29402,7 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="90" t="s">
+      <c r="A117" s="89" t="s">
         <v>2409</v>
       </c>
       <c r="B117" s="53" t="s">
@@ -29424,10 +29420,10 @@
       <c r="F117" s="53" t="s">
         <v>2413</v>
       </c>
-      <c r="G117" s="90"/>
+      <c r="G117" s="89"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="90" t="s">
+      <c r="A118" s="89" t="s">
         <v>2409</v>
       </c>
       <c r="B118" s="53" t="s">
@@ -29447,7 +29443,7 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="90" t="s">
+      <c r="A119" s="89" t="s">
         <v>2409</v>
       </c>
       <c r="B119" s="53" t="s">
@@ -29467,7 +29463,7 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="90" t="s">
+      <c r="A120" s="89" t="s">
         <v>2409</v>
       </c>
       <c r="B120" s="53" t="s">
@@ -29487,7 +29483,7 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="90" t="s">
+      <c r="A121" s="89" t="s">
         <v>2409</v>
       </c>
       <c r="B121" s="53" t="s">
@@ -29533,7 +29529,7 @@
       <c r="D123" s="57" t="s">
         <v>2431</v>
       </c>
-      <c r="H123" s="96" t="s">
+      <c r="H123" s="95" t="s">
         <v>1235</v>
       </c>
     </row>
@@ -29550,7 +29546,7 @@
       <c r="D124" s="57" t="s">
         <v>2434</v>
       </c>
-      <c r="H124" s="97" t="s">
+      <c r="H124" s="96" t="s">
         <v>2435</v>
       </c>
     </row>
@@ -30693,7 +30689,7 @@
       <c r="E193" s="53"/>
       <c r="F193" s="53"/>
       <c r="G193" s="53"/>
-      <c r="H193" s="98"/>
+      <c r="H193" s="97"/>
       <c r="I193" s="53"/>
     </row>
     <row r="194" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30788,7 +30784,7 @@
       <c r="E198" s="53"/>
       <c r="F198" s="53"/>
       <c r="G198" s="53"/>
-      <c r="H198" s="98" t="s">
+      <c r="H198" s="97" t="s">
         <v>1223</v>
       </c>
       <c r="I198" s="53"/>

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -16,7 +16,7 @@
     <sheet name="Choices" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Labels!$A$1:$F$260</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Labels!$A$1:$F$269</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Widgets!$A$1:$W$1048536</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4899" uniqueCount="2687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4935" uniqueCount="2702">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -6406,6 +6406,78 @@
     <t xml:space="preserve">Make sure your slider button is inside the range.</t>
   </si>
   <si>
+    <t xml:space="preserve">modePre.Walk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">modePre.Bicycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vélo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bicycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">modePre.Bus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">modePre.TransitHeavy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Métro, Train ou REM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metro, REM or Train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">modePre.SchoolBus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobus scolaire (jaune)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">School bus (yellow)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">modePre.CarPassenger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto en tant que passager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passenger in a car</t>
+  </si>
+  <si>
+    <t xml:space="preserve">modePre.CarDriver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto en tant que conducteur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Car as driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">modePre.Intercity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avion, train ou bus interurbain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plane, intercity train or bus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">modePre.Other</t>
+  </si>
+  <si>
     <t xml:space="preserve">mode.Walk</t>
   </si>
   <si>
@@ -6703,12 +6775,6 @@
     <t xml:space="preserve">mode.Walk_workOnTheRoad</t>
   </si>
   <si>
-    <t xml:space="preserve">Marche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walking</t>
-  </si>
-  <si>
     <t xml:space="preserve">mode.Bicycle_workOnTheRoad</t>
   </si>
   <si>
@@ -6730,18 +6796,9 @@
     <t xml:space="preserve">mode.CarDriver_leisureStroll</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto en tant que conducteur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Car as driver</t>
-  </si>
-  <si>
     <t xml:space="preserve">mode.CarPassenger_leisureStroll</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto en tant que passager</t>
-  </si>
-  <si>
     <t xml:space="preserve">Car as passenger</t>
   </si>
   <si>
@@ -6760,12 +6817,6 @@
     <t xml:space="preserve">mode.short.Bicycle</t>
   </si>
   <si>
-    <t xml:space="preserve">Vélo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bicycle</t>
-  </si>
-  <si>
     <t xml:space="preserve">mode.short.BicycleElectric</t>
   </si>
   <si>
@@ -6863,12 +6914,6 @@
   </si>
   <si>
     <t xml:space="preserve">mode.short.SchoolBus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobus scolaire (jaune)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">School bus (yellow)</t>
   </si>
   <si>
     <t xml:space="preserve">mode.short.OtherBus</t>
@@ -23246,7 +23291,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F266"/>
+  <dimension ref="A1:F275"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="50" width="16.66"/>
@@ -26081,115 +26126,115 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B177" s="50" t="s">
+      <c r="B177" s="0" t="s">
         <v>1922</v>
       </c>
-      <c r="C177" s="8" t="s">
+      <c r="C177" s="0" t="s">
         <v>1923</v>
       </c>
-      <c r="D177" s="8" t="s">
+      <c r="D177" s="0" t="s">
         <v>1924</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B178" s="50" t="s">
+      <c r="B178" s="0" t="s">
         <v>1925</v>
       </c>
-      <c r="C178" s="8" t="s">
+      <c r="C178" s="0" t="s">
         <v>1926</v>
       </c>
-      <c r="D178" s="8" t="s">
+      <c r="D178" s="0" t="s">
         <v>1927</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B179" s="50" t="s">
+      <c r="B179" s="0" t="s">
         <v>1928</v>
       </c>
-      <c r="C179" s="8" t="s">
+      <c r="C179" s="0" t="s">
         <v>1929</v>
       </c>
-      <c r="D179" s="8" t="s">
-        <v>1930</v>
-      </c>
-    </row>
-    <row r="180" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D179" s="0" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B180" s="50" t="s">
+      <c r="B180" s="0" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C180" s="0" t="s">
         <v>1931</v>
       </c>
-      <c r="C180" s="8" t="s">
+      <c r="D180" s="0" t="s">
         <v>1932</v>
       </c>
-      <c r="D180" s="8" t="s">
-        <v>1933</v>
-      </c>
-    </row>
-    <row r="181" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B181" s="50" t="s">
+      <c r="B181" s="0" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C181" s="0" t="s">
         <v>1934</v>
       </c>
-      <c r="C181" s="8" t="s">
+      <c r="D181" s="0" t="s">
         <v>1935</v>
       </c>
-      <c r="D181" s="8" t="s">
-        <v>1936</v>
-      </c>
-    </row>
-    <row r="182" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B182" s="50" t="s">
+      <c r="B182" s="0" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C182" s="0" t="s">
         <v>1937</v>
       </c>
-      <c r="C182" s="8" t="s">
+      <c r="D182" s="0" t="s">
         <v>1938</v>
-      </c>
-      <c r="D182" s="8" t="s">
-        <v>1939</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B183" s="50" t="s">
+      <c r="B183" s="0" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C183" s="0" t="s">
         <v>1940</v>
       </c>
-      <c r="C183" s="50" t="s">
+      <c r="D183" s="0" t="s">
         <v>1941</v>
-      </c>
-      <c r="D183" s="50" t="s">
-        <v>1942</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B184" s="50" t="s">
+      <c r="B184" s="0" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C184" s="0" t="s">
         <v>1943</v>
       </c>
-      <c r="C184" s="50" t="s">
-        <v>1944</v>
-      </c>
-      <c r="D184" s="50" t="s">
+      <c r="D184" s="0" t="s">
         <v>1944</v>
       </c>
     </row>
@@ -26197,98 +26242,98 @@
       <c r="A185" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B185" s="50" t="s">
+      <c r="B185" s="0" t="s">
         <v>1945</v>
       </c>
-      <c r="C185" s="50" t="s">
-        <v>1946</v>
-      </c>
-      <c r="D185" s="50" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C185" s="0" t="s">
+        <v>1601</v>
+      </c>
+      <c r="D185" s="0" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="50" t="s">
         <v>560</v>
       </c>
       <c r="B186" s="50" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C186" s="8" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D186" s="8" t="s">
         <v>1948</v>
       </c>
-      <c r="C186" s="50" t="s">
-        <v>1949</v>
-      </c>
-      <c r="D186" s="50" t="s">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="187" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="50" t="s">
         <v>560</v>
       </c>
       <c r="B187" s="50" t="s">
+        <v>1949</v>
+      </c>
+      <c r="C187" s="8" t="s">
+        <v>1950</v>
+      </c>
+      <c r="D187" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="C187" s="50" t="s">
-        <v>1952</v>
-      </c>
-      <c r="D187" s="50" t="s">
-        <v>1953</v>
-      </c>
-    </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="188" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="50" t="s">
         <v>560</v>
       </c>
       <c r="B188" s="50" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C188" s="8" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D188" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="C188" s="50" t="s">
-        <v>1955</v>
-      </c>
-      <c r="D188" s="50" t="s">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="189" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="50" t="s">
         <v>560</v>
       </c>
       <c r="B189" s="50" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C189" s="8" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D189" s="8" t="s">
         <v>1957</v>
       </c>
-      <c r="C189" s="50" t="s">
-        <v>1958</v>
-      </c>
-      <c r="D189" s="50" t="s">
-        <v>1959</v>
-      </c>
-    </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="190" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="50" t="s">
         <v>560</v>
       </c>
       <c r="B190" s="50" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C190" s="8" t="s">
+        <v>1959</v>
+      </c>
+      <c r="D190" s="8" t="s">
         <v>1960</v>
       </c>
-      <c r="C190" s="50" t="s">
-        <v>1961</v>
-      </c>
-      <c r="D190" s="50" t="s">
-        <v>1962</v>
-      </c>
-    </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="191" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="50" t="s">
         <v>560</v>
       </c>
       <c r="B191" s="50" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C191" s="8" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D191" s="8" t="s">
         <v>1963</v>
-      </c>
-      <c r="C191" s="50" t="s">
-        <v>1964</v>
-      </c>
-      <c r="D191" s="50" t="s">
-        <v>1965</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26296,13 +26341,13 @@
         <v>560</v>
       </c>
       <c r="B192" s="50" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C192" s="50" t="s">
+        <v>1965</v>
+      </c>
+      <c r="D192" s="50" t="s">
         <v>1966</v>
-      </c>
-      <c r="C192" s="50" t="s">
-        <v>1967</v>
-      </c>
-      <c r="D192" s="50" t="s">
-        <v>1968</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26310,13 +26355,13 @@
         <v>560</v>
       </c>
       <c r="B193" s="50" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="C193" s="50" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="D193" s="50" t="s">
-        <v>1971</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26324,13 +26369,13 @@
         <v>560</v>
       </c>
       <c r="B194" s="50" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="C194" s="50" t="s">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="D194" s="50" t="s">
-        <v>1974</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26338,13 +26383,13 @@
         <v>560</v>
       </c>
       <c r="B195" s="50" t="s">
-        <v>1975</v>
+        <v>1972</v>
       </c>
       <c r="C195" s="50" t="s">
-        <v>1976</v>
+        <v>1973</v>
       </c>
       <c r="D195" s="50" t="s">
-        <v>1977</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26352,13 +26397,13 @@
         <v>560</v>
       </c>
       <c r="B196" s="50" t="s">
-        <v>1978</v>
+        <v>1975</v>
       </c>
       <c r="C196" s="50" t="s">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="D196" s="50" t="s">
-        <v>1980</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26366,13 +26411,13 @@
         <v>560</v>
       </c>
       <c r="B197" s="50" t="s">
-        <v>1981</v>
+        <v>1978</v>
       </c>
       <c r="C197" s="50" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
       <c r="D197" s="50" t="s">
-        <v>1983</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26380,13 +26425,13 @@
         <v>560</v>
       </c>
       <c r="B198" s="50" t="s">
-        <v>1984</v>
+        <v>1981</v>
       </c>
       <c r="C198" s="50" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="D198" s="50" t="s">
-        <v>1986</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26394,27 +26439,27 @@
         <v>560</v>
       </c>
       <c r="B199" s="50" t="s">
-        <v>1987</v>
+        <v>1984</v>
       </c>
       <c r="C199" s="50" t="s">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="D199" s="50" t="s">
-        <v>1989</v>
-      </c>
-    </row>
-    <row r="200" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B200" s="66" t="s">
-        <v>1990</v>
-      </c>
-      <c r="C200" s="8" t="s">
-        <v>1991</v>
-      </c>
-      <c r="D200" s="57" t="s">
-        <v>1992</v>
+      <c r="B200" s="50" t="s">
+        <v>1987</v>
+      </c>
+      <c r="C200" s="50" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D200" s="50" t="s">
+        <v>1989</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26422,13 +26467,13 @@
         <v>560</v>
       </c>
       <c r="B201" s="50" t="s">
-        <v>1993</v>
+        <v>1990</v>
       </c>
       <c r="C201" s="50" t="s">
-        <v>1994</v>
+        <v>1991</v>
       </c>
       <c r="D201" s="50" t="s">
-        <v>1995</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26436,13 +26481,13 @@
         <v>560</v>
       </c>
       <c r="B202" s="50" t="s">
-        <v>1996</v>
+        <v>1993</v>
       </c>
       <c r="C202" s="50" t="s">
-        <v>1997</v>
+        <v>1994</v>
       </c>
       <c r="D202" s="50" t="s">
-        <v>1998</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26450,13 +26495,13 @@
         <v>560</v>
       </c>
       <c r="B203" s="50" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="C203" s="50" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="D203" s="50" t="s">
-        <v>2001</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26464,13 +26509,13 @@
         <v>560</v>
       </c>
       <c r="B204" s="50" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="C204" s="50" t="s">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="D204" s="50" t="s">
-        <v>2004</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26478,153 +26523,153 @@
         <v>560</v>
       </c>
       <c r="B205" s="50" t="s">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="C205" s="50" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="D205" s="50" t="s">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="206" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="50" t="s">
         <v>560</v>
       </c>
       <c r="B206" s="50" t="s">
-        <v>2008</v>
-      </c>
-      <c r="C206" s="8" t="s">
-        <v>2009</v>
-      </c>
-      <c r="D206" s="57" t="s">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="207" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2005</v>
+      </c>
+      <c r="C206" s="50" t="s">
+        <v>2006</v>
+      </c>
+      <c r="D206" s="50" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B207" s="66" t="s">
-        <v>2011</v>
-      </c>
-      <c r="C207" s="8" t="s">
-        <v>2012</v>
-      </c>
-      <c r="D207" s="57" t="s">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="208" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B207" s="50" t="s">
+        <v>2008</v>
+      </c>
+      <c r="C207" s="50" t="s">
+        <v>2009</v>
+      </c>
+      <c r="D207" s="50" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B208" s="66" t="s">
-        <v>2014</v>
-      </c>
-      <c r="C208" s="8" t="s">
-        <v>2015</v>
-      </c>
-      <c r="D208" s="57" t="s">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="209" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B208" s="50" t="s">
+        <v>2011</v>
+      </c>
+      <c r="C208" s="50" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D208" s="50" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="50" t="s">
         <v>560</v>
       </c>
       <c r="B209" s="66" t="s">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C209" s="8" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="D209" s="57" t="s">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="210" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B210" s="66" t="s">
-        <v>2020</v>
-      </c>
-      <c r="C210" s="8" t="s">
-        <v>2021</v>
-      </c>
-      <c r="D210" s="57" t="s">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="211" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B210" s="50" t="s">
+        <v>2017</v>
+      </c>
+      <c r="C210" s="50" t="s">
+        <v>2018</v>
+      </c>
+      <c r="D210" s="50" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B211" s="66" t="s">
-        <v>2023</v>
-      </c>
-      <c r="C211" s="8" t="s">
-        <v>2024</v>
-      </c>
-      <c r="D211" s="57" t="s">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="212" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B211" s="50" t="s">
+        <v>2020</v>
+      </c>
+      <c r="C211" s="50" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D211" s="50" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B212" s="66" t="s">
-        <v>2026</v>
-      </c>
-      <c r="C212" s="8" t="s">
-        <v>2021</v>
-      </c>
-      <c r="D212" s="57" t="s">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="213" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B212" s="50" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C212" s="50" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D212" s="50" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B213" s="66" t="s">
+      <c r="B213" s="50" t="s">
+        <v>2026</v>
+      </c>
+      <c r="C213" s="50" t="s">
         <v>2027</v>
       </c>
-      <c r="C213" s="8" t="s">
-        <v>2024</v>
-      </c>
-      <c r="D213" s="57" t="s">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="214" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D213" s="50" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B214" s="66" t="s">
-        <v>2028</v>
-      </c>
-      <c r="C214" s="8" t="s">
-        <v>1991</v>
-      </c>
-      <c r="D214" s="57" t="s">
-        <v>1992</v>
+      <c r="B214" s="50" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C214" s="50" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D214" s="50" t="s">
+        <v>2031</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B215" s="66" t="s">
-        <v>2029</v>
+      <c r="B215" s="50" t="s">
+        <v>2032</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="D215" s="57" t="s">
-        <v>2031</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26632,13 +26677,13 @@
         <v>560</v>
       </c>
       <c r="B216" s="66" t="s">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="D216" s="57" t="s">
-        <v>2034</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26646,139 +26691,139 @@
         <v>560</v>
       </c>
       <c r="B217" s="66" t="s">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="C217" s="8" t="s">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="D217" s="57" t="s">
-        <v>2037</v>
-      </c>
-    </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B218" s="50" t="s">
-        <v>2038</v>
-      </c>
-      <c r="C218" s="50" t="s">
-        <v>2021</v>
-      </c>
-      <c r="D218" s="50" t="s">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B218" s="66" t="s">
+        <v>2041</v>
+      </c>
+      <c r="C218" s="8" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D218" s="57" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B219" s="50" t="s">
-        <v>2039</v>
-      </c>
-      <c r="C219" s="50" t="s">
-        <v>2040</v>
-      </c>
-      <c r="D219" s="50" t="s">
-        <v>2041</v>
-      </c>
-    </row>
-    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B219" s="66" t="s">
+        <v>2044</v>
+      </c>
+      <c r="C219" s="8" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D219" s="57" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B220" s="50" t="s">
-        <v>2042</v>
-      </c>
-      <c r="C220" s="50" t="s">
-        <v>2043</v>
-      </c>
-      <c r="D220" s="50" t="s">
-        <v>2044</v>
-      </c>
-    </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B220" s="66" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C220" s="8" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D220" s="57" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B221" s="50" t="s">
-        <v>2045</v>
-      </c>
-      <c r="C221" s="50" t="s">
-        <v>2046</v>
-      </c>
-      <c r="D221" s="50" t="s">
-        <v>2047</v>
-      </c>
-    </row>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B221" s="66" t="s">
+        <v>2048</v>
+      </c>
+      <c r="C221" s="8" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D221" s="57" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B222" s="50" t="s">
-        <v>2048</v>
-      </c>
-      <c r="C222" s="50" t="s">
+      <c r="B222" s="66" t="s">
         <v>2049</v>
       </c>
-      <c r="D222" s="50" t="s">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C222" s="8" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D222" s="57" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B223" s="50" t="s">
-        <v>2051</v>
-      </c>
-      <c r="C223" s="50" t="s">
-        <v>2052</v>
-      </c>
-      <c r="D223" s="50" t="s">
-        <v>2053</v>
-      </c>
-    </row>
-    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B223" s="66" t="s">
+        <v>2050</v>
+      </c>
+      <c r="C223" s="8" t="s">
+        <v>2015</v>
+      </c>
+      <c r="D223" s="57" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B224" s="50" t="s">
-        <v>2054</v>
-      </c>
-      <c r="C224" s="50" t="s">
-        <v>2055</v>
-      </c>
-      <c r="D224" s="50" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B224" s="66" t="s">
+        <v>2051</v>
+      </c>
+      <c r="C224" s="8" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D224" s="57" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B225" s="50" t="s">
-        <v>2057</v>
-      </c>
-      <c r="C225" s="50" t="s">
-        <v>2058</v>
-      </c>
-      <c r="D225" s="50" t="s">
-        <v>2058</v>
-      </c>
-    </row>
-    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B225" s="66" t="s">
+        <v>2052</v>
+      </c>
+      <c r="C225" s="8" t="s">
+        <v>1937</v>
+      </c>
+      <c r="D225" s="57" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B226" s="50" t="s">
-        <v>2059</v>
-      </c>
-      <c r="C226" s="50" t="s">
-        <v>2060</v>
-      </c>
-      <c r="D226" s="50" t="s">
-        <v>2061</v>
+      <c r="B226" s="66" t="s">
+        <v>2054</v>
+      </c>
+      <c r="C226" s="8" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D226" s="57" t="s">
+        <v>2056</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26786,13 +26831,13 @@
         <v>560</v>
       </c>
       <c r="B227" s="50" t="s">
-        <v>2062</v>
+        <v>2057</v>
       </c>
       <c r="C227" s="50" t="s">
-        <v>2063</v>
+        <v>1923</v>
       </c>
       <c r="D227" s="50" t="s">
-        <v>2064</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26800,13 +26845,13 @@
         <v>560</v>
       </c>
       <c r="B228" s="50" t="s">
-        <v>2065</v>
+        <v>2058</v>
       </c>
       <c r="C228" s="50" t="s">
-        <v>2066</v>
+        <v>1926</v>
       </c>
       <c r="D228" s="50" t="s">
-        <v>2067</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26814,13 +26859,13 @@
         <v>560</v>
       </c>
       <c r="B229" s="50" t="s">
-        <v>2068</v>
+        <v>2059</v>
       </c>
       <c r="C229" s="50" t="s">
-        <v>2069</v>
+        <v>2060</v>
       </c>
       <c r="D229" s="50" t="s">
-        <v>2070</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26828,13 +26873,13 @@
         <v>560</v>
       </c>
       <c r="B230" s="50" t="s">
-        <v>2071</v>
+        <v>2062</v>
       </c>
       <c r="C230" s="50" t="s">
-        <v>2072</v>
+        <v>2063</v>
       </c>
       <c r="D230" s="50" t="s">
-        <v>2073</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26842,13 +26887,13 @@
         <v>560</v>
       </c>
       <c r="B231" s="50" t="s">
-        <v>2074</v>
+        <v>2065</v>
       </c>
       <c r="C231" s="50" t="s">
-        <v>2075</v>
+        <v>2066</v>
       </c>
       <c r="D231" s="50" t="s">
-        <v>2076</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26856,13 +26901,13 @@
         <v>560</v>
       </c>
       <c r="B232" s="50" t="s">
-        <v>2077</v>
+        <v>2068</v>
       </c>
       <c r="C232" s="50" t="s">
-        <v>2078</v>
+        <v>2069</v>
       </c>
       <c r="D232" s="50" t="s">
-        <v>2079</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26870,13 +26915,13 @@
         <v>560</v>
       </c>
       <c r="B233" s="50" t="s">
-        <v>2080</v>
+        <v>2071</v>
       </c>
       <c r="C233" s="50" t="s">
-        <v>2081</v>
+        <v>2072</v>
       </c>
       <c r="D233" s="50" t="s">
-        <v>2082</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26884,13 +26929,13 @@
         <v>560</v>
       </c>
       <c r="B234" s="50" t="s">
-        <v>2083</v>
+        <v>2074</v>
       </c>
       <c r="C234" s="50" t="s">
-        <v>2084</v>
+        <v>2075</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>2085</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26898,13 +26943,13 @@
         <v>560</v>
       </c>
       <c r="B235" s="50" t="s">
-        <v>2086</v>
+        <v>2076</v>
       </c>
       <c r="C235" s="50" t="s">
-        <v>2087</v>
+        <v>2077</v>
       </c>
       <c r="D235" s="50" t="s">
-        <v>2088</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26912,13 +26957,13 @@
         <v>560</v>
       </c>
       <c r="B236" s="50" t="s">
-        <v>2089</v>
+        <v>2079</v>
       </c>
       <c r="C236" s="50" t="s">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="D236" s="50" t="s">
-        <v>2091</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26926,13 +26971,13 @@
         <v>560</v>
       </c>
       <c r="B237" s="50" t="s">
-        <v>2092</v>
+        <v>2082</v>
       </c>
       <c r="C237" s="50" t="s">
-        <v>2093</v>
+        <v>2083</v>
       </c>
       <c r="D237" s="50" t="s">
-        <v>2094</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26940,13 +26985,13 @@
         <v>560</v>
       </c>
       <c r="B238" s="50" t="s">
-        <v>2095</v>
+        <v>2085</v>
       </c>
       <c r="C238" s="50" t="s">
-        <v>2096</v>
+        <v>2086</v>
       </c>
       <c r="D238" s="50" t="s">
-        <v>2097</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26954,13 +26999,13 @@
         <v>560</v>
       </c>
       <c r="B239" s="50" t="s">
-        <v>2098</v>
+        <v>2088</v>
       </c>
       <c r="C239" s="50" t="s">
-        <v>2099</v>
+        <v>2089</v>
       </c>
       <c r="D239" s="50" t="s">
-        <v>2100</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26968,13 +27013,13 @@
         <v>560</v>
       </c>
       <c r="B240" s="50" t="s">
-        <v>2101</v>
+        <v>2091</v>
       </c>
       <c r="C240" s="50" t="s">
-        <v>2102</v>
+        <v>1934</v>
       </c>
       <c r="D240" s="50" t="s">
-        <v>2103</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26982,13 +27027,13 @@
         <v>560</v>
       </c>
       <c r="B241" s="50" t="s">
-        <v>2104</v>
+        <v>2092</v>
       </c>
       <c r="C241" s="50" t="s">
-        <v>1991</v>
+        <v>2093</v>
       </c>
       <c r="D241" s="50" t="s">
-        <v>1992</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26996,13 +27041,13 @@
         <v>560</v>
       </c>
       <c r="B242" s="50" t="s">
-        <v>2105</v>
+        <v>2095</v>
       </c>
       <c r="C242" s="50" t="s">
-        <v>2106</v>
+        <v>2096</v>
       </c>
       <c r="D242" s="50" t="s">
-        <v>2107</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27010,13 +27055,13 @@
         <v>560</v>
       </c>
       <c r="B243" s="50" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
       <c r="C243" s="50" t="s">
-        <v>2109</v>
+        <v>2099</v>
       </c>
       <c r="D243" s="50" t="s">
-        <v>2110</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27024,13 +27069,13 @@
         <v>560</v>
       </c>
       <c r="B244" s="50" t="s">
-        <v>2111</v>
+        <v>2101</v>
       </c>
       <c r="C244" s="50" t="s">
-        <v>1601</v>
+        <v>2102</v>
       </c>
       <c r="D244" s="50" t="s">
-        <v>1602</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27038,13 +27083,13 @@
         <v>560</v>
       </c>
       <c r="B245" s="50" t="s">
-        <v>2112</v>
+        <v>2104</v>
       </c>
       <c r="C245" s="50" t="s">
-        <v>2113</v>
+        <v>2105</v>
       </c>
       <c r="D245" s="50" t="s">
-        <v>2114</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27052,257 +27097,257 @@
         <v>560</v>
       </c>
       <c r="B246" s="50" t="s">
-        <v>2115</v>
+        <v>2107</v>
       </c>
       <c r="C246" s="50" t="s">
-        <v>2116</v>
+        <v>2108</v>
       </c>
       <c r="D246" s="50" t="s">
-        <v>2117</v>
-      </c>
-    </row>
-    <row r="247" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B247" s="8" t="s">
-        <v>2118</v>
-      </c>
-      <c r="C247" s="8" t="s">
-        <v>2119</v>
-      </c>
-      <c r="D247" s="57" t="s">
-        <v>2120</v>
-      </c>
-    </row>
-    <row r="248" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B247" s="50" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C247" s="50" t="s">
+        <v>2111</v>
+      </c>
+      <c r="D247" s="50" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B248" s="8" t="s">
+      <c r="B248" s="50" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C248" s="50" t="s">
+        <v>2114</v>
+      </c>
+      <c r="D248" s="50" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="50" t="s">
+        <v>560</v>
+      </c>
+      <c r="B249" s="50" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C249" s="50" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D249" s="50" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="50" t="s">
+        <v>560</v>
+      </c>
+      <c r="B250" s="50" t="s">
+        <v>2119</v>
+      </c>
+      <c r="C250" s="50" t="s">
+        <v>2015</v>
+      </c>
+      <c r="D250" s="50" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="50" t="s">
+        <v>560</v>
+      </c>
+      <c r="B251" s="50" t="s">
+        <v>2120</v>
+      </c>
+      <c r="C251" s="50" t="s">
         <v>2121</v>
       </c>
-      <c r="C248" s="8" t="s">
+      <c r="D251" s="50" t="s">
         <v>2122</v>
       </c>
-      <c r="D248" s="57" t="s">
+    </row>
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="50" t="s">
+        <v>560</v>
+      </c>
+      <c r="B252" s="50" t="s">
         <v>2123</v>
       </c>
-    </row>
-    <row r="249" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="48" t="s">
+      <c r="C252" s="50" t="s">
+        <v>2124</v>
+      </c>
+      <c r="D252" s="50" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="50" t="s">
+        <v>560</v>
+      </c>
+      <c r="B253" s="50" t="s">
+        <v>2126</v>
+      </c>
+      <c r="C253" s="50" t="s">
+        <v>1601</v>
+      </c>
+      <c r="D253" s="50" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="50" t="s">
+        <v>560</v>
+      </c>
+      <c r="B254" s="50" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C254" s="50" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D254" s="50" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="50" t="s">
+        <v>560</v>
+      </c>
+      <c r="B255" s="50" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C255" s="50" t="s">
+        <v>2131</v>
+      </c>
+      <c r="D255" s="50" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="50" t="s">
+        <v>560</v>
+      </c>
+      <c r="B256" s="8" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C256" s="8" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D256" s="57" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="50" t="s">
+        <v>560</v>
+      </c>
+      <c r="B257" s="8" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C257" s="8" t="s">
+        <v>2137</v>
+      </c>
+      <c r="D257" s="57" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="48" t="s">
         <v>756</v>
       </c>
-      <c r="B249" s="54" t="s">
-        <v>2124</v>
-      </c>
-      <c r="C249" s="8" t="s">
-        <v>2125</v>
-      </c>
-      <c r="D249" s="85" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="250" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="50" t="s">
+      <c r="B258" s="54" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C258" s="8" t="s">
+        <v>2140</v>
+      </c>
+      <c r="D258" s="85" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="50" t="s">
         <v>756</v>
       </c>
-      <c r="B250" s="86" t="s">
-        <v>2127</v>
-      </c>
-      <c r="C250" s="48" t="s">
+      <c r="B259" s="86" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C259" s="48" t="s">
         <v>1371</v>
       </c>
-      <c r="D250" s="51" t="s">
+      <c r="D259" s="51" t="s">
         <v>1372</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="50" t="s">
+    <row r="260" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="50" t="s">
         <v>756</v>
       </c>
-      <c r="B251" s="86" t="s">
-        <v>2128</v>
-      </c>
-      <c r="C251" s="8" t="s">
-        <v>2129</v>
-      </c>
-      <c r="D251" s="51" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="252" customFormat="false" ht="285.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="50" t="s">
+      <c r="B260" s="86" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C260" s="8" t="s">
+        <v>2144</v>
+      </c>
+      <c r="D260" s="51" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="285.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="50" t="s">
         <v>756</v>
       </c>
-      <c r="B252" s="53" t="s">
-        <v>2131</v>
-      </c>
-      <c r="C252" s="54" t="s">
-        <v>2132</v>
-      </c>
-      <c r="D252" s="54" t="s">
-        <v>2133</v>
-      </c>
-      <c r="E252" s="54" t="s">
-        <v>2134</v>
-      </c>
-      <c r="F252" s="54" t="s">
-        <v>2135</v>
-      </c>
-    </row>
-    <row r="253" customFormat="false" ht="225.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="50" t="s">
+      <c r="B261" s="53" t="s">
+        <v>2146</v>
+      </c>
+      <c r="C261" s="54" t="s">
+        <v>2147</v>
+      </c>
+      <c r="D261" s="54" t="s">
+        <v>2148</v>
+      </c>
+      <c r="E261" s="54" t="s">
+        <v>2149</v>
+      </c>
+      <c r="F261" s="54" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="225.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="50" t="s">
         <v>756</v>
       </c>
-      <c r="B253" s="53" t="s">
-        <v>2136</v>
-      </c>
-      <c r="C253" s="54" t="s">
-        <v>2137</v>
-      </c>
-      <c r="D253" s="54" t="s">
-        <v>2138</v>
-      </c>
-      <c r="E253" s="54" t="s">
-        <v>2139</v>
-      </c>
-      <c r="F253" s="54" t="s">
-        <v>2140</v>
-      </c>
-    </row>
-    <row r="254" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="50" t="s">
-        <v>833</v>
-      </c>
-      <c r="B254" s="50" t="s">
-        <v>2141</v>
-      </c>
-      <c r="C254" s="48" t="s">
-        <v>1371</v>
-      </c>
-      <c r="D254" s="51" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="255" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="50" t="s">
-        <v>833</v>
-      </c>
-      <c r="B255" s="50" t="s">
-        <v>2142</v>
-      </c>
-      <c r="C255" s="8" t="s">
-        <v>2143</v>
-      </c>
-      <c r="D255" s="8" t="s">
-        <v>2144</v>
-      </c>
-    </row>
-    <row r="256" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="50" t="s">
-        <v>833</v>
-      </c>
-      <c r="B256" s="50" t="s">
-        <v>2145</v>
-      </c>
-      <c r="C256" s="8" t="s">
-        <v>1429</v>
-      </c>
-      <c r="D256" s="8" t="s">
-        <v>1430</v>
-      </c>
-    </row>
-    <row r="257" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="50" t="s">
-        <v>1053</v>
-      </c>
-      <c r="B257" s="50" t="s">
-        <v>2146</v>
-      </c>
-      <c r="C257" s="48" t="s">
-        <v>1371</v>
-      </c>
-      <c r="D257" s="51" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="258" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="50" t="s">
-        <v>1053</v>
-      </c>
-      <c r="B258" s="50" t="s">
-        <v>2147</v>
-      </c>
-      <c r="C258" s="8" t="s">
-        <v>2148</v>
-      </c>
-      <c r="D258" s="51" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="259" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="50" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B259" s="54" t="s">
-        <v>2150</v>
-      </c>
-      <c r="C259" s="54" t="s">
+      <c r="B262" s="53" t="s">
         <v>2151</v>
       </c>
-      <c r="D259" s="54" t="s">
+      <c r="C262" s="54" t="s">
         <v>2152</v>
       </c>
-    </row>
-    <row r="260" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="50" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B260" s="54" t="s">
+      <c r="D262" s="54" t="s">
         <v>2153</v>
       </c>
-      <c r="C260" s="54" t="s">
+      <c r="E262" s="54" t="s">
         <v>2154</v>
       </c>
-      <c r="D260" s="54" t="s">
+      <c r="F262" s="54" t="s">
         <v>2155</v>
-      </c>
-    </row>
-    <row r="261" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="50" t="s">
-        <v>48</v>
-      </c>
-      <c r="B261" s="50" t="s">
-        <v>2156</v>
-      </c>
-      <c r="C261" s="48" t="s">
-        <v>2157</v>
-      </c>
-      <c r="D261" s="51" t="s">
-        <v>2158</v>
-      </c>
-    </row>
-    <row r="262" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="50" t="s">
-        <v>48</v>
-      </c>
-      <c r="B262" s="50" t="s">
-        <v>2159</v>
-      </c>
-      <c r="C262" s="8" t="s">
-        <v>2160</v>
-      </c>
-      <c r="D262" s="51" t="s">
-        <v>2161</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="50" t="s">
-        <v>48</v>
+        <v>833</v>
       </c>
       <c r="B263" s="50" t="s">
-        <v>2162</v>
+        <v>2156</v>
       </c>
       <c r="C263" s="48" t="s">
         <v>1371</v>
@@ -27311,50 +27356,176 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="50" t="s">
+        <v>833</v>
+      </c>
+      <c r="B264" s="50" t="s">
+        <v>2157</v>
+      </c>
+      <c r="C264" s="8" t="s">
+        <v>2158</v>
+      </c>
+      <c r="D264" s="8" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="265" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="50" t="s">
+        <v>833</v>
+      </c>
+      <c r="B265" s="50" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C265" s="8" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D265" s="8" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="50" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B266" s="50" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C266" s="48" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D266" s="51" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A267" s="50" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B267" s="50" t="s">
+        <v>2162</v>
+      </c>
+      <c r="C267" s="8" t="s">
+        <v>2163</v>
+      </c>
+      <c r="D267" s="51" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A268" s="50" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B268" s="54" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C268" s="54" t="s">
+        <v>2166</v>
+      </c>
+      <c r="D268" s="54" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="269" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="50" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B269" s="54" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C269" s="54" t="s">
+        <v>2169</v>
+      </c>
+      <c r="D269" s="54" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="270" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A270" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="B264" s="50" t="s">
-        <v>2163</v>
-      </c>
-      <c r="C264" s="8" t="s">
-        <v>2164</v>
-      </c>
-      <c r="D264" s="51" t="s">
-        <v>2165</v>
-      </c>
-    </row>
-    <row r="265" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="50" t="s">
+      <c r="B270" s="50" t="s">
+        <v>2171</v>
+      </c>
+      <c r="C270" s="48" t="s">
+        <v>2172</v>
+      </c>
+      <c r="D270" s="51" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="271" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="B271" s="50" t="s">
+        <v>2174</v>
+      </c>
+      <c r="C271" s="8" t="s">
+        <v>2175</v>
+      </c>
+      <c r="D271" s="51" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A272" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="B272" s="50" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C272" s="48" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D272" s="51" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="273" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A273" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="B273" s="50" t="s">
+        <v>2178</v>
+      </c>
+      <c r="C273" s="8" t="s">
+        <v>2179</v>
+      </c>
+      <c r="D273" s="51" t="s">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="274" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B265" s="50" t="s">
-        <v>2166</v>
-      </c>
-      <c r="C265" s="8" t="s">
-        <v>2167</v>
-      </c>
-      <c r="D265" s="8" t="s">
-        <v>2168</v>
-      </c>
-    </row>
-    <row r="266" s="74" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="74" t="s">
-        <v>2169</v>
-      </c>
-      <c r="B266" s="74" t="s">
-        <v>2170</v>
-      </c>
-      <c r="C266" s="74" t="s">
-        <v>2171</v>
-      </c>
-      <c r="D266" s="74" t="s">
-        <v>2172</v>
+      <c r="B274" s="50" t="s">
+        <v>2181</v>
+      </c>
+      <c r="C274" s="8" t="s">
+        <v>2182</v>
+      </c>
+      <c r="D274" s="8" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="275" s="74" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="74" t="s">
+        <v>2184</v>
+      </c>
+      <c r="B275" s="74" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C275" s="74" t="s">
+        <v>2186</v>
+      </c>
+      <c r="D275" s="74" t="s">
+        <v>2187</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F260"/>
+  <autoFilter ref="A1:F269"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -27384,7 +27555,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="87" t="s">
-        <v>2173</v>
+        <v>2188</v>
       </c>
       <c r="B1" s="87" t="s">
         <v>1159</v>
@@ -27402,13 +27573,13 @@
         <v>9</v>
       </c>
       <c r="G1" s="87" t="s">
-        <v>2174</v>
+        <v>2189</v>
       </c>
       <c r="H1" s="87" t="s">
         <v>12</v>
       </c>
       <c r="I1" s="66" t="s">
-        <v>2175</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27419,10 +27590,10 @@
         <v>1167</v>
       </c>
       <c r="C2" s="53" t="s">
-        <v>2176</v>
+        <v>2191</v>
       </c>
       <c r="D2" s="53" t="s">
-        <v>2177</v>
+        <v>2192</v>
       </c>
       <c r="E2" s="53"/>
       <c r="F2" s="53"/>
@@ -27437,10 +27608,10 @@
         <v>1225</v>
       </c>
       <c r="C3" s="53" t="s">
-        <v>2178</v>
+        <v>2193</v>
       </c>
       <c r="D3" s="53" t="s">
-        <v>2179</v>
+        <v>2194</v>
       </c>
       <c r="E3" s="53"/>
       <c r="F3" s="53"/>
@@ -27455,10 +27626,10 @@
         <v>229</v>
       </c>
       <c r="C4" s="53" t="s">
-        <v>2180</v>
+        <v>2195</v>
       </c>
       <c r="D4" s="53" t="s">
-        <v>2181</v>
+        <v>2196</v>
       </c>
       <c r="E4" s="53"/>
       <c r="F4" s="53"/>
@@ -27467,7 +27638,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="53" t="s">
-        <v>2182</v>
+        <v>2197</v>
       </c>
       <c r="B5" s="53" t="s">
         <v>229</v>
@@ -27485,16 +27656,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="53" t="s">
-        <v>2183</v>
+        <v>2198</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>2183</v>
+        <v>2198</v>
       </c>
       <c r="C6" s="53" t="s">
-        <v>2184</v>
+        <v>2199</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>2185</v>
+        <v>2200</v>
       </c>
       <c r="E6" s="53"/>
       <c r="F6" s="53"/>
@@ -27509,10 +27680,10 @@
         <v>1171</v>
       </c>
       <c r="C7" s="53" t="s">
-        <v>2186</v>
+        <v>2201</v>
       </c>
       <c r="D7" s="53" t="s">
-        <v>2187</v>
+        <v>2202</v>
       </c>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
@@ -27571,7 +27742,7 @@
       <c r="E11" s="53"/>
       <c r="F11" s="53"/>
       <c r="G11" s="53" t="s">
-        <v>2183</v>
+        <v>2198</v>
       </c>
       <c r="H11" s="53"/>
     </row>
@@ -27625,10 +27796,10 @@
         <v>1167</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>2188</v>
+        <v>2203</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>2189</v>
+        <v>2204</v>
       </c>
       <c r="E15" s="51"/>
       <c r="F15" s="51"/>
@@ -27644,10 +27815,10 @@
         <v>1225</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>2190</v>
+        <v>2205</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>2191</v>
+        <v>2206</v>
       </c>
       <c r="E16" s="51"/>
       <c r="F16" s="51"/>
@@ -27657,16 +27828,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="89" t="s">
-        <v>2192</v>
+        <v>2207</v>
       </c>
       <c r="B17" s="53" t="s">
-        <v>2193</v>
+        <v>2208</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>2194</v>
+        <v>2209</v>
       </c>
       <c r="D17" s="53" t="s">
-        <v>2195</v>
+        <v>2210</v>
       </c>
       <c r="E17" s="53"/>
       <c r="F17" s="53"/>
@@ -27675,16 +27846,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="89" t="s">
-        <v>2192</v>
+        <v>2207</v>
       </c>
       <c r="B18" s="53" t="s">
-        <v>2196</v>
+        <v>2211</v>
       </c>
       <c r="C18" s="53" t="s">
-        <v>2197</v>
+        <v>2212</v>
       </c>
       <c r="D18" s="53" t="s">
-        <v>2198</v>
+        <v>2213</v>
       </c>
       <c r="E18" s="53"/>
       <c r="F18" s="53"/>
@@ -27693,7 +27864,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="89" t="s">
-        <v>2192</v>
+        <v>2207</v>
       </c>
       <c r="B19" s="53"/>
       <c r="C19" s="53"/>
@@ -27710,13 +27881,13 @@
         <v>187</v>
       </c>
       <c r="B20" s="53" t="s">
-        <v>2193</v>
+        <v>2208</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>2194</v>
+        <v>2209</v>
       </c>
       <c r="D20" s="53" t="s">
-        <v>2199</v>
+        <v>2214</v>
       </c>
       <c r="E20" s="53"/>
       <c r="F20" s="53"/>
@@ -27728,13 +27899,13 @@
         <v>187</v>
       </c>
       <c r="B21" s="53" t="s">
-        <v>2196</v>
+        <v>2211</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>2197</v>
+        <v>2212</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>2200</v>
+        <v>2215</v>
       </c>
       <c r="E21" s="53"/>
       <c r="F21" s="53"/>
@@ -27749,10 +27920,10 @@
         <v>189</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>2201</v>
+        <v>2216</v>
       </c>
       <c r="D22" s="53" t="s">
-        <v>2202</v>
+        <v>2217</v>
       </c>
       <c r="E22" s="53"/>
       <c r="F22" s="53"/>
@@ -27778,13 +27949,13 @@
         <v>306</v>
       </c>
       <c r="B24" s="53" t="s">
-        <v>2203</v>
+        <v>2218</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>2204</v>
+        <v>2219</v>
       </c>
       <c r="D24" s="53" t="s">
-        <v>2205</v>
+        <v>2220</v>
       </c>
       <c r="E24" s="53"/>
       <c r="F24" s="53"/>
@@ -27796,13 +27967,13 @@
         <v>306</v>
       </c>
       <c r="B25" s="53" t="s">
-        <v>2206</v>
+        <v>2221</v>
       </c>
       <c r="C25" s="53" t="s">
-        <v>2207</v>
+        <v>2222</v>
       </c>
       <c r="D25" s="53" t="s">
-        <v>2208</v>
+        <v>2223</v>
       </c>
       <c r="E25" s="53"/>
       <c r="F25" s="53"/>
@@ -27828,13 +27999,13 @@
         <v>299</v>
       </c>
       <c r="B27" s="53" t="s">
-        <v>2203</v>
+        <v>2218</v>
       </c>
       <c r="C27" s="53" t="s">
-        <v>2209</v>
+        <v>2224</v>
       </c>
       <c r="D27" s="53" t="s">
-        <v>2210</v>
+        <v>2225</v>
       </c>
       <c r="E27" s="53"/>
       <c r="F27" s="53"/>
@@ -27846,13 +28017,13 @@
         <v>299</v>
       </c>
       <c r="B28" s="53" t="s">
-        <v>2206</v>
+        <v>2221</v>
       </c>
       <c r="C28" s="53" t="s">
-        <v>2211</v>
+        <v>2226</v>
       </c>
       <c r="D28" s="53" t="s">
-        <v>2212</v>
+        <v>2227</v>
       </c>
       <c r="E28" s="53"/>
       <c r="F28" s="53"/>
@@ -27881,10 +28052,10 @@
         <v>1191</v>
       </c>
       <c r="C30" s="53" t="s">
-        <v>2213</v>
+        <v>2228</v>
       </c>
       <c r="D30" s="53" t="s">
-        <v>2214</v>
+        <v>2229</v>
       </c>
       <c r="E30" s="53"/>
       <c r="F30" s="53"/>
@@ -27903,10 +28074,10 @@
         <v>1192</v>
       </c>
       <c r="C31" s="53" t="s">
-        <v>2215</v>
+        <v>2230</v>
       </c>
       <c r="D31" s="53" t="s">
-        <v>2216</v>
+        <v>2231</v>
       </c>
       <c r="E31" s="53"/>
       <c r="F31" s="53"/>
@@ -27925,10 +28096,10 @@
         <v>1193</v>
       </c>
       <c r="C32" s="53" t="s">
-        <v>2217</v>
+        <v>2232</v>
       </c>
       <c r="D32" s="53" t="s">
-        <v>2218</v>
+        <v>2233</v>
       </c>
       <c r="E32" s="53"/>
       <c r="F32" s="53"/>
@@ -27947,10 +28118,10 @@
         <v>1195</v>
       </c>
       <c r="C33" s="53" t="s">
-        <v>2219</v>
+        <v>2234</v>
       </c>
       <c r="D33" s="53" t="s">
-        <v>2220</v>
+        <v>2235</v>
       </c>
       <c r="E33" s="53"/>
       <c r="F33" s="53"/>
@@ -27969,10 +28140,10 @@
         <v>1196</v>
       </c>
       <c r="C34" s="53" t="s">
-        <v>2221</v>
+        <v>2236</v>
       </c>
       <c r="D34" s="53" t="s">
-        <v>2222</v>
+        <v>2237</v>
       </c>
       <c r="E34" s="53"/>
       <c r="F34" s="53"/>
@@ -27988,13 +28159,13 @@
         <v>340</v>
       </c>
       <c r="B35" s="53" t="s">
-        <v>2223</v>
+        <v>2238</v>
       </c>
       <c r="C35" s="53" t="s">
-        <v>2224</v>
+        <v>2239</v>
       </c>
       <c r="D35" s="53" t="s">
-        <v>2225</v>
+        <v>2240</v>
       </c>
       <c r="E35" s="53"/>
       <c r="F35" s="53"/>
@@ -28009,13 +28180,13 @@
         <v>340</v>
       </c>
       <c r="B36" s="53" t="s">
-        <v>2226</v>
+        <v>2241</v>
       </c>
       <c r="C36" s="53" t="s">
-        <v>2227</v>
+        <v>2242</v>
       </c>
       <c r="D36" s="53" t="s">
-        <v>2228</v>
+        <v>2243</v>
       </c>
       <c r="E36" s="53"/>
       <c r="F36" s="53"/>
@@ -28031,10 +28202,10 @@
         <v>1262</v>
       </c>
       <c r="C37" s="53" t="s">
-        <v>2229</v>
+        <v>2244</v>
       </c>
       <c r="D37" s="53" t="s">
-        <v>2230</v>
+        <v>2245</v>
       </c>
       <c r="E37" s="53"/>
       <c r="F37" s="53"/>
@@ -28050,10 +28221,10 @@
         <v>1263</v>
       </c>
       <c r="C38" s="53" t="s">
-        <v>2231</v>
+        <v>2246</v>
       </c>
       <c r="D38" s="53" t="s">
-        <v>2232</v>
+        <v>2247</v>
       </c>
       <c r="E38" s="53"/>
       <c r="F38" s="53"/>
@@ -28066,13 +28237,13 @@
         <v>340</v>
       </c>
       <c r="B39" s="53" t="s">
-        <v>2233</v>
+        <v>2248</v>
       </c>
       <c r="C39" s="53" t="s">
-        <v>2234</v>
+        <v>2249</v>
       </c>
       <c r="D39" s="53" t="s">
-        <v>2235</v>
+        <v>2250</v>
       </c>
       <c r="E39" s="53"/>
       <c r="F39" s="53"/>
@@ -28085,13 +28256,13 @@
         <v>340</v>
       </c>
       <c r="B40" s="53" t="s">
-        <v>2236</v>
+        <v>2251</v>
       </c>
       <c r="C40" s="53" t="s">
-        <v>2237</v>
+        <v>2252</v>
       </c>
       <c r="D40" s="53" t="s">
-        <v>2238</v>
+        <v>2253</v>
       </c>
       <c r="E40" s="53"/>
       <c r="F40" s="53"/>
@@ -28109,7 +28280,7 @@
       <c r="E41" s="53"/>
       <c r="F41" s="53"/>
       <c r="G41" s="53" t="s">
-        <v>2182</v>
+        <v>2197</v>
       </c>
       <c r="H41" s="53"/>
       <c r="I41" s="66"/>
@@ -28134,13 +28305,13 @@
         <v>315</v>
       </c>
       <c r="B43" s="53" t="s">
-        <v>2239</v>
+        <v>2254</v>
       </c>
       <c r="C43" s="48" t="s">
-        <v>2240</v>
+        <v>2255</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>2241</v>
+        <v>2256</v>
       </c>
       <c r="E43" s="53"/>
       <c r="F43" s="53"/>
@@ -28153,13 +28324,13 @@
         <v>315</v>
       </c>
       <c r="B44" s="53" t="s">
-        <v>2242</v>
+        <v>2257</v>
       </c>
       <c r="C44" s="48" t="s">
-        <v>2243</v>
+        <v>2258</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>2244</v>
+        <v>2259</v>
       </c>
       <c r="E44" s="53"/>
       <c r="F44" s="53"/>
@@ -28172,13 +28343,13 @@
         <v>315</v>
       </c>
       <c r="B45" s="53" t="s">
-        <v>2245</v>
+        <v>2260</v>
       </c>
       <c r="C45" s="48" t="s">
-        <v>2246</v>
+        <v>2261</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>2247</v>
+        <v>2262</v>
       </c>
       <c r="E45" s="53"/>
       <c r="F45" s="53"/>
@@ -28191,13 +28362,13 @@
         <v>315</v>
       </c>
       <c r="B46" s="53" t="s">
-        <v>2248</v>
+        <v>2263</v>
       </c>
       <c r="C46" s="48" t="s">
-        <v>2249</v>
+        <v>2264</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>2250</v>
+        <v>2265</v>
       </c>
       <c r="E46" s="53"/>
       <c r="F46" s="53"/>
@@ -28215,7 +28386,7 @@
       <c r="E47" s="53"/>
       <c r="F47" s="53"/>
       <c r="G47" s="53" t="s">
-        <v>2183</v>
+        <v>2198</v>
       </c>
       <c r="H47" s="53"/>
       <c r="I47" s="53"/>
@@ -28228,10 +28399,10 @@
         <v>1256</v>
       </c>
       <c r="C48" s="51" t="s">
-        <v>2251</v>
+        <v>2266</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>2252</v>
+        <v>2267</v>
       </c>
       <c r="E48" s="53"/>
       <c r="F48" s="53"/>
@@ -28246,13 +28417,13 @@
         <v>220</v>
       </c>
       <c r="B49" s="53" t="s">
-        <v>2253</v>
+        <v>2268</v>
       </c>
       <c r="C49" s="51" t="s">
-        <v>2254</v>
+        <v>2269</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>2255</v>
+        <v>2270</v>
       </c>
       <c r="E49" s="53"/>
       <c r="F49" s="53"/>
@@ -28267,13 +28438,13 @@
         <v>220</v>
       </c>
       <c r="B50" s="53" t="s">
-        <v>2256</v>
+        <v>2271</v>
       </c>
       <c r="C50" s="51" t="s">
-        <v>2257</v>
+        <v>2272</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>2258</v>
+        <v>2273</v>
       </c>
       <c r="E50" s="53"/>
       <c r="F50" s="53"/>
@@ -28289,10 +28460,10 @@
         <v>229</v>
       </c>
       <c r="C51" s="51" t="s">
-        <v>2259</v>
+        <v>2274</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>2260</v>
+        <v>2275</v>
       </c>
       <c r="E51" s="53"/>
       <c r="F51" s="53"/>
@@ -28310,7 +28481,7 @@
       <c r="E52" s="53"/>
       <c r="F52" s="53"/>
       <c r="G52" s="53" t="s">
-        <v>2183</v>
+        <v>2198</v>
       </c>
       <c r="H52" s="53"/>
       <c r="I52" s="53"/>
@@ -28320,13 +28491,13 @@
         <v>226</v>
       </c>
       <c r="B53" s="53" t="s">
-        <v>2261</v>
+        <v>2276</v>
       </c>
       <c r="C53" s="51" t="s">
-        <v>2262</v>
+        <v>2277</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>2263</v>
+        <v>2278</v>
       </c>
       <c r="E53" s="53"/>
       <c r="F53" s="53"/>
@@ -28339,13 +28510,13 @@
         <v>226</v>
       </c>
       <c r="B54" s="53" t="s">
-        <v>2264</v>
+        <v>2279</v>
       </c>
       <c r="C54" s="51" t="s">
-        <v>2265</v>
+        <v>2280</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>2266</v>
+        <v>2281</v>
       </c>
       <c r="E54" s="53"/>
       <c r="F54" s="53"/>
@@ -28358,13 +28529,13 @@
         <v>226</v>
       </c>
       <c r="B55" s="53" t="s">
-        <v>2267</v>
+        <v>2282</v>
       </c>
       <c r="C55" s="51" t="s">
-        <v>2268</v>
+        <v>2283</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>2269</v>
+        <v>2284</v>
       </c>
       <c r="E55" s="53"/>
       <c r="F55" s="53"/>
@@ -28377,13 +28548,13 @@
         <v>226</v>
       </c>
       <c r="B56" s="53" t="s">
-        <v>2270</v>
+        <v>2285</v>
       </c>
       <c r="C56" s="51" t="s">
-        <v>2271</v>
+        <v>2286</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>2272</v>
+        <v>2287</v>
       </c>
       <c r="E56" s="53"/>
       <c r="F56" s="53"/>
@@ -28396,13 +28567,13 @@
         <v>226</v>
       </c>
       <c r="B57" s="53" t="s">
-        <v>2273</v>
+        <v>2288</v>
       </c>
       <c r="C57" s="51" t="s">
-        <v>2274</v>
+        <v>2289</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>2274</v>
+        <v>2289</v>
       </c>
       <c r="E57" s="53"/>
       <c r="F57" s="53"/>
@@ -28415,13 +28586,13 @@
         <v>226</v>
       </c>
       <c r="B58" s="53" t="s">
-        <v>2275</v>
+        <v>2290</v>
       </c>
       <c r="C58" s="51" t="s">
-        <v>2276</v>
+        <v>2291</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>2277</v>
+        <v>2292</v>
       </c>
       <c r="E58" s="53"/>
       <c r="F58" s="53"/>
@@ -28434,13 +28605,13 @@
         <v>226</v>
       </c>
       <c r="B59" s="53" t="s">
-        <v>2278</v>
+        <v>2293</v>
       </c>
       <c r="C59" s="51" t="s">
-        <v>2279</v>
+        <v>2294</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>2280</v>
+        <v>2295</v>
       </c>
       <c r="E59" s="53"/>
       <c r="F59" s="53"/>
@@ -28453,13 +28624,13 @@
         <v>226</v>
       </c>
       <c r="B60" s="53" t="s">
-        <v>2281</v>
+        <v>2296</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>2282</v>
+        <v>2297</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>2283</v>
+        <v>2298</v>
       </c>
       <c r="E60" s="53"/>
       <c r="F60" s="53"/>
@@ -28487,13 +28658,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="53" t="s">
-        <v>2284</v>
+        <v>2299</v>
       </c>
       <c r="C62" s="51" t="s">
-        <v>2285</v>
+        <v>2300</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>2286</v>
+        <v>2301</v>
       </c>
       <c r="E62" s="53"/>
       <c r="F62" s="53"/>
@@ -28511,7 +28682,7 @@
       <c r="E63" s="53"/>
       <c r="F63" s="53"/>
       <c r="G63" s="53" t="s">
-        <v>2183</v>
+        <v>2198</v>
       </c>
       <c r="H63" s="53"/>
       <c r="I63" s="53"/>
@@ -28524,10 +28695,10 @@
         <v>1167</v>
       </c>
       <c r="C64" s="51" t="s">
-        <v>2287</v>
+        <v>2302</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>2288</v>
+        <v>2303</v>
       </c>
       <c r="E64" s="53"/>
       <c r="F64" s="53"/>
@@ -28543,14 +28714,14 @@
         <v>1199</v>
       </c>
       <c r="C65" s="53" t="s">
-        <v>2289</v>
+        <v>2304</v>
       </c>
       <c r="D65" s="53" t="s">
-        <v>2290</v>
+        <v>2305</v>
       </c>
       <c r="E65" s="53"/>
       <c r="F65" s="53" t="s">
-        <v>2291</v>
+        <v>2306</v>
       </c>
       <c r="G65" s="53"/>
       <c r="H65" s="53"/>
@@ -28564,14 +28735,14 @@
         <v>1200</v>
       </c>
       <c r="C66" s="53" t="s">
-        <v>2292</v>
+        <v>2307</v>
       </c>
       <c r="D66" s="53" t="s">
-        <v>2293</v>
+        <v>2308</v>
       </c>
       <c r="E66" s="53"/>
       <c r="F66" s="53" t="s">
-        <v>2294</v>
+        <v>2309</v>
       </c>
       <c r="G66" s="53"/>
       <c r="H66" s="53"/>
@@ -28582,17 +28753,17 @@
         <v>322</v>
       </c>
       <c r="B67" s="53" t="s">
-        <v>2295</v>
+        <v>2310</v>
       </c>
       <c r="C67" s="53" t="s">
-        <v>2296</v>
+        <v>2311</v>
       </c>
       <c r="D67" s="53" t="s">
-        <v>2297</v>
+        <v>2312</v>
       </c>
       <c r="E67" s="53"/>
       <c r="F67" s="53" t="s">
-        <v>2298</v>
+        <v>2313</v>
       </c>
       <c r="G67" s="53"/>
       <c r="H67" s="53"/>
@@ -28606,14 +28777,14 @@
         <v>1201</v>
       </c>
       <c r="C68" s="53" t="s">
-        <v>2299</v>
+        <v>2314</v>
       </c>
       <c r="D68" s="53" t="s">
-        <v>2300</v>
+        <v>2315</v>
       </c>
       <c r="E68" s="53"/>
       <c r="F68" s="53" t="s">
-        <v>2301</v>
+        <v>2316</v>
       </c>
       <c r="G68" s="53"/>
       <c r="H68" s="53"/>
@@ -28627,14 +28798,14 @@
         <v>1215</v>
       </c>
       <c r="C69" s="53" t="s">
-        <v>2302</v>
+        <v>2317</v>
       </c>
       <c r="D69" s="53" t="s">
-        <v>2303</v>
+        <v>2318</v>
       </c>
       <c r="E69" s="53"/>
       <c r="F69" s="53" t="s">
-        <v>2304</v>
+        <v>2319</v>
       </c>
       <c r="G69" s="53"/>
       <c r="H69" s="53"/>
@@ -28645,13 +28816,13 @@
         <v>905</v>
       </c>
       <c r="B70" s="66" t="s">
-        <v>2305</v>
+        <v>2320</v>
       </c>
       <c r="C70" s="66" t="s">
-        <v>2306</v>
+        <v>2321</v>
       </c>
       <c r="D70" s="66" t="s">
-        <v>2307</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28659,13 +28830,13 @@
         <v>905</v>
       </c>
       <c r="B71" s="66" t="s">
-        <v>2308</v>
+        <v>2323</v>
       </c>
       <c r="C71" s="66" t="s">
-        <v>2309</v>
+        <v>2324</v>
       </c>
       <c r="D71" s="66" t="s">
-        <v>2310</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28673,13 +28844,13 @@
         <v>905</v>
       </c>
       <c r="B72" s="66" t="s">
-        <v>2311</v>
+        <v>2326</v>
       </c>
       <c r="C72" s="66" t="s">
-        <v>2312</v>
+        <v>2327</v>
       </c>
       <c r="D72" s="66" t="s">
-        <v>2313</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="73" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28687,13 +28858,13 @@
         <v>905</v>
       </c>
       <c r="B73" s="66" t="s">
-        <v>2314</v>
+        <v>2329</v>
       </c>
       <c r="C73" s="66" t="s">
-        <v>2315</v>
+        <v>2330</v>
       </c>
       <c r="D73" s="66" t="s">
-        <v>2316</v>
+        <v>2331</v>
       </c>
       <c r="E73" s="66"/>
       <c r="F73" s="66"/>
@@ -28706,13 +28877,13 @@
         <v>1079</v>
       </c>
       <c r="B74" s="53" t="s">
-        <v>2317</v>
+        <v>2332</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>2318</v>
+        <v>2333</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>2319</v>
+        <v>2334</v>
       </c>
       <c r="E74" s="51"/>
       <c r="F74" s="51"/>
@@ -28725,13 +28896,13 @@
         <v>1079</v>
       </c>
       <c r="B75" s="53" t="s">
-        <v>2320</v>
+        <v>2335</v>
       </c>
       <c r="C75" s="51" t="s">
-        <v>2321</v>
+        <v>2336</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>2322</v>
+        <v>2337</v>
       </c>
       <c r="E75" s="51"/>
       <c r="F75" s="51"/>
@@ -28744,13 +28915,13 @@
         <v>1079</v>
       </c>
       <c r="B76" s="53" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
       <c r="C76" s="51" t="s">
-        <v>2324</v>
+        <v>2339</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
       <c r="E76" s="51"/>
       <c r="F76" s="51"/>
@@ -28763,13 +28934,13 @@
         <v>1079</v>
       </c>
       <c r="B77" s="53" t="s">
-        <v>2326</v>
+        <v>2341</v>
       </c>
       <c r="C77" s="51" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
       <c r="E77" s="51"/>
       <c r="F77" s="51"/>
@@ -28782,13 +28953,13 @@
         <v>1079</v>
       </c>
       <c r="B78" s="53" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
       <c r="C78" s="51" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>2331</v>
+        <v>2346</v>
       </c>
       <c r="E78" s="51"/>
       <c r="F78" s="51"/>
@@ -28801,13 +28972,13 @@
         <v>1079</v>
       </c>
       <c r="B79" s="53" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
       <c r="C79" s="51" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
       <c r="E79" s="51"/>
       <c r="F79" s="51"/>
@@ -28820,13 +28991,13 @@
         <v>1079</v>
       </c>
       <c r="B80" s="53" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
       <c r="C80" s="51" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
       <c r="E80" s="51"/>
       <c r="F80" s="51"/>
@@ -28839,13 +29010,13 @@
         <v>1079</v>
       </c>
       <c r="B81" s="53" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
       <c r="C81" s="51" t="s">
-        <v>2339</v>
+        <v>2354</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>2340</v>
+        <v>2355</v>
       </c>
       <c r="E81" s="51"/>
       <c r="F81" s="51"/>
@@ -28858,13 +29029,13 @@
         <v>1079</v>
       </c>
       <c r="B82" s="53" t="s">
-        <v>2341</v>
+        <v>2356</v>
       </c>
       <c r="C82" s="51" t="s">
-        <v>2342</v>
+        <v>2357</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>2343</v>
+        <v>2358</v>
       </c>
       <c r="E82" s="51"/>
       <c r="F82" s="51"/>
@@ -28877,13 +29048,13 @@
         <v>1079</v>
       </c>
       <c r="B83" s="53" t="s">
-        <v>2183</v>
+        <v>2198</v>
       </c>
       <c r="C83" s="51" t="s">
-        <v>2184</v>
+        <v>2199</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>2185</v>
+        <v>2200</v>
       </c>
       <c r="E83" s="51"/>
       <c r="F83" s="51"/>
@@ -28896,13 +29067,13 @@
         <v>1079</v>
       </c>
       <c r="B84" s="53" t="s">
-        <v>2344</v>
+        <v>2359</v>
       </c>
       <c r="C84" s="51" t="s">
-        <v>2186</v>
+        <v>2201</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>2345</v>
+        <v>2360</v>
       </c>
       <c r="E84" s="51"/>
       <c r="F84" s="51"/>
@@ -28915,13 +29086,13 @@
         <v>99</v>
       </c>
       <c r="B85" s="66" t="s">
-        <v>2346</v>
+        <v>2361</v>
       </c>
       <c r="C85" s="66" t="s">
-        <v>2347</v>
+        <v>2362</v>
       </c>
       <c r="D85" s="66" t="s">
-        <v>2348</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28929,13 +29100,13 @@
         <v>99</v>
       </c>
       <c r="B86" s="66" t="s">
-        <v>2349</v>
+        <v>2364</v>
       </c>
       <c r="C86" s="66" t="s">
-        <v>2350</v>
+        <v>2365</v>
       </c>
       <c r="D86" s="66" t="s">
-        <v>2351</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28960,10 +29131,10 @@
         <v>1171</v>
       </c>
       <c r="C88" s="66" t="s">
-        <v>2186</v>
+        <v>2201</v>
       </c>
       <c r="D88" s="66" t="s">
-        <v>2345</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28971,13 +29142,13 @@
         <v>423</v>
       </c>
       <c r="B89" s="53" t="s">
-        <v>2352</v>
+        <v>2367</v>
       </c>
       <c r="C89" s="51" t="s">
-        <v>2353</v>
+        <v>2368</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>2354</v>
+        <v>2369</v>
       </c>
       <c r="E89" s="51"/>
       <c r="F89" s="51"/>
@@ -28992,13 +29163,13 @@
         <v>423</v>
       </c>
       <c r="B90" s="53" t="s">
-        <v>2355</v>
+        <v>2370</v>
       </c>
       <c r="C90" s="51" t="s">
-        <v>2356</v>
+        <v>2371</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>2357</v>
+        <v>2372</v>
       </c>
       <c r="E90" s="51"/>
       <c r="F90" s="51"/>
@@ -29013,13 +29184,13 @@
         <v>423</v>
       </c>
       <c r="B91" s="53" t="s">
-        <v>2358</v>
+        <v>2373</v>
       </c>
       <c r="C91" s="51" t="s">
-        <v>2359</v>
+        <v>2374</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>2360</v>
+        <v>2375</v>
       </c>
       <c r="E91" s="51"/>
       <c r="F91" s="51"/>
@@ -29032,13 +29203,13 @@
         <v>423</v>
       </c>
       <c r="B92" s="53" t="s">
-        <v>2361</v>
+        <v>2376</v>
       </c>
       <c r="C92" s="51" t="s">
-        <v>2362</v>
+        <v>2377</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>2363</v>
+        <v>2378</v>
       </c>
       <c r="E92" s="51"/>
       <c r="F92" s="51"/>
@@ -29051,13 +29222,13 @@
         <v>423</v>
       </c>
       <c r="B93" s="53" t="s">
-        <v>2364</v>
+        <v>2379</v>
       </c>
       <c r="C93" s="51" t="s">
-        <v>2365</v>
+        <v>2380</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>2366</v>
+        <v>2381</v>
       </c>
       <c r="E93" s="51"/>
       <c r="F93" s="51"/>
@@ -29073,10 +29244,10 @@
         <v>1232</v>
       </c>
       <c r="C94" s="51" t="s">
-        <v>2367</v>
+        <v>2382</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>2368</v>
+        <v>2383</v>
       </c>
       <c r="E94" s="51"/>
       <c r="F94" s="51"/>
@@ -29094,10 +29265,10 @@
         <v>1233</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>2369</v>
+        <v>2384</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>2370</v>
+        <v>2385</v>
       </c>
       <c r="E95" s="51"/>
       <c r="F95" s="51"/>
@@ -29110,13 +29281,13 @@
         <v>423</v>
       </c>
       <c r="B96" s="53" t="s">
-        <v>2371</v>
+        <v>2386</v>
       </c>
       <c r="C96" s="51" t="s">
-        <v>2372</v>
+        <v>2387</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>2373</v>
+        <v>2388</v>
       </c>
       <c r="E96" s="51"/>
       <c r="F96" s="51"/>
@@ -29147,10 +29318,10 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="93" t="s">
-        <v>2374</v>
+        <v>2389</v>
       </c>
       <c r="B98" s="66" t="s">
-        <v>2375</v>
+        <v>2390</v>
       </c>
       <c r="C98" s="66" t="s">
         <v>1752</v>
@@ -29167,10 +29338,10 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="93" t="s">
-        <v>2374</v>
+        <v>2389</v>
       </c>
       <c r="B99" s="66" t="s">
-        <v>2376</v>
+        <v>2391</v>
       </c>
       <c r="C99" s="66" t="s">
         <v>1757</v>
@@ -29187,16 +29358,16 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="93" t="s">
-        <v>2374</v>
+        <v>2389</v>
       </c>
       <c r="B100" s="66" t="s">
         <v>1225</v>
       </c>
       <c r="C100" s="66" t="s">
-        <v>2178</v>
+        <v>2193</v>
       </c>
       <c r="D100" s="66" t="s">
-        <v>2179</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29204,13 +29375,13 @@
         <v>771</v>
       </c>
       <c r="B101" s="66" t="s">
-        <v>2377</v>
+        <v>2392</v>
       </c>
       <c r="C101" s="66" t="s">
-        <v>2378</v>
+        <v>2393</v>
       </c>
       <c r="D101" s="66" t="s">
-        <v>2379</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29218,13 +29389,13 @@
         <v>771</v>
       </c>
       <c r="B102" s="66" t="s">
-        <v>2380</v>
+        <v>2395</v>
       </c>
       <c r="C102" s="66" t="s">
-        <v>2381</v>
+        <v>2396</v>
       </c>
       <c r="D102" s="66" t="s">
-        <v>2382</v>
+        <v>2397</v>
       </c>
       <c r="I102" s="90" t="n">
         <f aca="false">TRUE()</f>
@@ -29236,13 +29407,13 @@
         <v>771</v>
       </c>
       <c r="B103" s="66" t="s">
-        <v>2383</v>
+        <v>2398</v>
       </c>
       <c r="C103" s="66" t="s">
-        <v>2384</v>
+        <v>2399</v>
       </c>
       <c r="D103" s="66" t="s">
-        <v>2385</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29250,13 +29421,13 @@
         <v>771</v>
       </c>
       <c r="B104" s="66" t="s">
-        <v>2386</v>
+        <v>2401</v>
       </c>
       <c r="C104" s="66" t="s">
-        <v>2387</v>
+        <v>2402</v>
       </c>
       <c r="D104" s="66" t="s">
-        <v>2388</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29264,7 +29435,7 @@
         <v>771</v>
       </c>
       <c r="G105" s="53" t="s">
-        <v>2182</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29272,7 +29443,7 @@
         <v>771</v>
       </c>
       <c r="G106" s="53" t="s">
-        <v>2183</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29280,13 +29451,13 @@
         <v>829</v>
       </c>
       <c r="B107" s="66" t="s">
-        <v>2389</v>
+        <v>2404</v>
       </c>
       <c r="C107" s="66" t="s">
-        <v>2390</v>
+        <v>2405</v>
       </c>
       <c r="D107" s="66" t="s">
-        <v>2391</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29294,13 +29465,13 @@
         <v>829</v>
       </c>
       <c r="B108" s="66" t="s">
-        <v>2392</v>
+        <v>2407</v>
       </c>
       <c r="C108" s="66" t="s">
-        <v>2393</v>
+        <v>2408</v>
       </c>
       <c r="D108" s="66" t="s">
-        <v>2394</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29308,13 +29479,13 @@
         <v>829</v>
       </c>
       <c r="B109" s="66" t="s">
-        <v>2383</v>
+        <v>2398</v>
       </c>
       <c r="C109" s="66" t="s">
-        <v>2395</v>
+        <v>2410</v>
       </c>
       <c r="D109" s="66" t="s">
-        <v>2396</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29322,13 +29493,13 @@
         <v>829</v>
       </c>
       <c r="B110" s="53" t="s">
-        <v>2397</v>
+        <v>2412</v>
       </c>
       <c r="C110" s="51" t="s">
-        <v>2398</v>
+        <v>2413</v>
       </c>
       <c r="D110" s="48" t="s">
-        <v>2399</v>
+        <v>2414</v>
       </c>
       <c r="I110" s="90" t="n">
         <f aca="false">TRUE()</f>
@@ -29340,7 +29511,7 @@
         <v>829</v>
       </c>
       <c r="G111" s="53" t="s">
-        <v>2182</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29348,7 +29519,7 @@
         <v>829</v>
       </c>
       <c r="G112" s="53" t="s">
-        <v>2183</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29356,13 +29527,13 @@
         <v>347</v>
       </c>
       <c r="B113" s="66" t="s">
-        <v>2400</v>
+        <v>2415</v>
       </c>
       <c r="C113" s="66" t="s">
-        <v>2401</v>
+        <v>2416</v>
       </c>
       <c r="D113" s="66" t="s">
-        <v>2402</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29370,13 +29541,13 @@
         <v>347</v>
       </c>
       <c r="B114" s="66" t="s">
-        <v>2403</v>
+        <v>2418</v>
       </c>
       <c r="C114" s="66" t="s">
-        <v>2404</v>
+        <v>2419</v>
       </c>
       <c r="D114" s="66" t="s">
-        <v>2405</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29384,13 +29555,13 @@
         <v>347</v>
       </c>
       <c r="B115" s="66" t="s">
-        <v>2406</v>
+        <v>2421</v>
       </c>
       <c r="C115" s="66" t="s">
-        <v>2407</v>
+        <v>2422</v>
       </c>
       <c r="D115" s="66" t="s">
-        <v>2408</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29403,103 +29574,103 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="89" t="s">
-        <v>2409</v>
+        <v>2424</v>
       </c>
       <c r="B117" s="53" t="s">
         <v>1199</v>
       </c>
       <c r="C117" s="53" t="s">
-        <v>2410</v>
+        <v>2425</v>
       </c>
       <c r="D117" s="53" t="s">
-        <v>2411</v>
+        <v>2426</v>
       </c>
       <c r="E117" s="53" t="s">
-        <v>2412</v>
+        <v>2427</v>
       </c>
       <c r="F117" s="53" t="s">
-        <v>2413</v>
+        <v>2428</v>
       </c>
       <c r="G117" s="89"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="89" t="s">
-        <v>2409</v>
+        <v>2424</v>
       </c>
       <c r="B118" s="53" t="s">
         <v>1200</v>
       </c>
       <c r="C118" s="53" t="s">
-        <v>2414</v>
+        <v>2429</v>
       </c>
       <c r="D118" s="53" t="s">
-        <v>2415</v>
+        <v>2430</v>
       </c>
       <c r="E118" s="53" t="s">
-        <v>2416</v>
+        <v>2431</v>
       </c>
       <c r="F118" s="53" t="s">
-        <v>2417</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="89" t="s">
-        <v>2409</v>
+        <v>2424</v>
       </c>
       <c r="B119" s="53" t="s">
         <v>1201</v>
       </c>
       <c r="C119" s="53" t="s">
-        <v>2418</v>
+        <v>2433</v>
       </c>
       <c r="D119" s="53" t="s">
-        <v>2419</v>
+        <v>2434</v>
       </c>
       <c r="E119" s="53" t="s">
-        <v>2420</v>
+        <v>2435</v>
       </c>
       <c r="F119" s="53" t="s">
-        <v>2421</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="89" t="s">
-        <v>2409</v>
+        <v>2424</v>
       </c>
       <c r="B120" s="53" t="s">
         <v>1215</v>
       </c>
       <c r="C120" s="53" t="s">
-        <v>2422</v>
+        <v>2437</v>
       </c>
       <c r="D120" s="53" t="s">
-        <v>2423</v>
+        <v>2438</v>
       </c>
       <c r="E120" s="53" t="s">
-        <v>2424</v>
+        <v>2439</v>
       </c>
       <c r="F120" s="53" t="s">
-        <v>2425</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="89" t="s">
-        <v>2409</v>
+        <v>2424</v>
       </c>
       <c r="B121" s="53" t="s">
-        <v>2295</v>
+        <v>2310</v>
       </c>
       <c r="C121" s="53" t="s">
-        <v>2426</v>
+        <v>2441</v>
       </c>
       <c r="D121" s="53" t="s">
-        <v>2427</v>
+        <v>2442</v>
       </c>
       <c r="E121" s="53" t="s">
-        <v>2428</v>
+        <v>2443</v>
       </c>
       <c r="F121" s="53" t="s">
-        <v>2429</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29507,13 +29678,13 @@
         <v>698</v>
       </c>
       <c r="B122" s="66" t="s">
-        <v>2430</v>
+        <v>2445</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>2021</v>
+        <v>1923</v>
       </c>
       <c r="D122" s="57" t="s">
-        <v>2022</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29524,10 +29695,10 @@
         <v>1237</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>2431</v>
+        <v>2446</v>
       </c>
       <c r="D123" s="57" t="s">
-        <v>2431</v>
+        <v>2446</v>
       </c>
       <c r="H123" s="95" t="s">
         <v>1235</v>
@@ -29538,16 +29709,16 @@
         <v>698</v>
       </c>
       <c r="B124" s="66" t="s">
-        <v>2432</v>
+        <v>2447</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>2433</v>
+        <v>2448</v>
       </c>
       <c r="D124" s="57" t="s">
-        <v>2434</v>
+        <v>2449</v>
       </c>
       <c r="H124" s="96" t="s">
-        <v>2435</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29555,13 +29726,13 @@
         <v>698</v>
       </c>
       <c r="B125" s="66" t="s">
-        <v>2436</v>
+        <v>2451</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>2030</v>
+        <v>1940</v>
       </c>
       <c r="D125" s="57" t="s">
-        <v>2031</v>
+        <v>1941</v>
       </c>
       <c r="H125" s="51" t="s">
         <v>963</v>
@@ -29572,13 +29743,13 @@
         <v>698</v>
       </c>
       <c r="B126" s="66" t="s">
-        <v>2437</v>
+        <v>2452</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>2033</v>
+        <v>1937</v>
       </c>
       <c r="D126" s="57" t="s">
-        <v>2034</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29596,13 +29767,13 @@
         <v>704</v>
       </c>
       <c r="B128" s="66" t="s">
-        <v>2430</v>
+        <v>2445</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>2021</v>
+        <v>1923</v>
       </c>
       <c r="D128" s="57" t="s">
-        <v>2022</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29610,13 +29781,13 @@
         <v>704</v>
       </c>
       <c r="B129" s="66" t="s">
-        <v>2438</v>
+        <v>2453</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>2040</v>
+        <v>1926</v>
       </c>
       <c r="D129" s="57" t="s">
-        <v>2041</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29624,13 +29795,13 @@
         <v>704</v>
       </c>
       <c r="B130" s="66" t="s">
-        <v>2436</v>
+        <v>2451</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>2030</v>
+        <v>1940</v>
       </c>
       <c r="D130" s="57" t="s">
-        <v>2031</v>
+        <v>1941</v>
       </c>
       <c r="H130" s="51" t="s">
         <v>963</v>
@@ -29641,13 +29812,13 @@
         <v>704</v>
       </c>
       <c r="B131" s="66" t="s">
-        <v>2437</v>
+        <v>2452</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>2033</v>
+        <v>1937</v>
       </c>
       <c r="D131" s="57" t="s">
-        <v>2034</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29655,13 +29826,13 @@
         <v>704</v>
       </c>
       <c r="B132" s="66" t="s">
-        <v>2439</v>
+        <v>2454</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>2440</v>
+        <v>2455</v>
       </c>
       <c r="D132" s="57" t="s">
-        <v>2441</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29669,13 +29840,13 @@
         <v>704</v>
       </c>
       <c r="B133" s="66" t="s">
-        <v>2442</v>
+        <v>2457</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>2036</v>
+        <v>2055</v>
       </c>
       <c r="D133" s="57" t="s">
-        <v>2037</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29685,7 +29856,7 @@
       <c r="C134" s="57"/>
       <c r="D134" s="57"/>
       <c r="G134" s="53" t="s">
-        <v>2182</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29693,16 +29864,16 @@
         <v>594</v>
       </c>
       <c r="B135" s="66" t="s">
-        <v>2443</v>
+        <v>2458</v>
       </c>
       <c r="C135" s="57" t="s">
-        <v>2444</v>
+        <v>2459</v>
       </c>
       <c r="D135" s="57" t="s">
-        <v>2445</v>
+        <v>2460</v>
       </c>
       <c r="H135" s="54" t="s">
-        <v>2446</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29713,13 +29884,13 @@
         <v>1225</v>
       </c>
       <c r="C136" s="57" t="s">
-        <v>2447</v>
+        <v>2462</v>
       </c>
       <c r="D136" s="57" t="s">
-        <v>2448</v>
+        <v>2463</v>
       </c>
       <c r="H136" s="8" t="s">
-        <v>2449</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29730,10 +29901,10 @@
         <v>1167</v>
       </c>
       <c r="C137" s="57" t="s">
-        <v>2450</v>
+        <v>2465</v>
       </c>
       <c r="D137" s="57" t="s">
-        <v>2451</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29741,13 +29912,13 @@
         <v>594</v>
       </c>
       <c r="B138" s="66" t="s">
-        <v>2452</v>
+        <v>2467</v>
       </c>
       <c r="C138" s="57" t="s">
-        <v>2453</v>
+        <v>2468</v>
       </c>
       <c r="D138" s="57" t="s">
-        <v>2454</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29757,7 +29928,7 @@
       <c r="C139" s="57"/>
       <c r="D139" s="57"/>
       <c r="G139" s="66" t="s">
-        <v>2183</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29765,13 +29936,13 @@
         <v>627</v>
       </c>
       <c r="B140" s="66" t="s">
-        <v>2455</v>
+        <v>2470</v>
       </c>
       <c r="C140" s="57" t="s">
-        <v>2456</v>
+        <v>2471</v>
       </c>
       <c r="D140" s="57" t="s">
-        <v>2456</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29779,13 +29950,13 @@
         <v>627</v>
       </c>
       <c r="B141" s="66" t="s">
-        <v>2457</v>
+        <v>2472</v>
       </c>
       <c r="C141" s="57" t="s">
-        <v>2458</v>
+        <v>2473</v>
       </c>
       <c r="D141" s="57" t="s">
-        <v>2459</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29795,7 +29966,7 @@
       <c r="C142" s="57"/>
       <c r="D142" s="57"/>
       <c r="G142" s="66" t="s">
-        <v>2183</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29803,13 +29974,13 @@
         <v>651</v>
       </c>
       <c r="B143" s="66" t="s">
-        <v>2460</v>
+        <v>2475</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>2461</v>
+        <v>2476</v>
       </c>
       <c r="D143" s="57" t="s">
-        <v>2462</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29817,13 +29988,13 @@
         <v>651</v>
       </c>
       <c r="B144" s="66" t="s">
-        <v>2463</v>
+        <v>2478</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>2464</v>
+        <v>2479</v>
       </c>
       <c r="D144" s="57" t="s">
-        <v>2465</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29833,7 +30004,7 @@
       <c r="C145" s="57"/>
       <c r="D145" s="57"/>
       <c r="G145" s="53" t="s">
-        <v>2182</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29843,7 +30014,7 @@
       <c r="C146" s="57"/>
       <c r="D146" s="57"/>
       <c r="G146" s="66" t="s">
-        <v>2183</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29851,13 +30022,13 @@
         <v>658</v>
       </c>
       <c r="B147" s="66" t="s">
-        <v>2466</v>
+        <v>2481</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>2467</v>
+        <v>2482</v>
       </c>
       <c r="D147" s="57" t="s">
-        <v>2468</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29865,13 +30036,13 @@
         <v>658</v>
       </c>
       <c r="B148" s="66" t="s">
-        <v>2469</v>
+        <v>2484</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>2470</v>
+        <v>2485</v>
       </c>
       <c r="D148" s="57" t="s">
-        <v>2470</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29879,13 +30050,13 @@
         <v>658</v>
       </c>
       <c r="B149" s="66" t="s">
-        <v>2471</v>
+        <v>2486</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>2472</v>
+        <v>2487</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>2472</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29893,13 +30064,13 @@
         <v>658</v>
       </c>
       <c r="B150" s="66" t="s">
-        <v>2473</v>
+        <v>2488</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>2474</v>
+        <v>2489</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>2474</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29909,7 +30080,7 @@
       <c r="C151" s="57"/>
       <c r="D151" s="57"/>
       <c r="G151" s="53" t="s">
-        <v>2182</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29919,7 +30090,7 @@
       <c r="C152" s="57"/>
       <c r="D152" s="57"/>
       <c r="G152" s="66" t="s">
-        <v>2183</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29927,13 +30098,13 @@
         <v>663</v>
       </c>
       <c r="B153" s="66" t="s">
-        <v>2475</v>
+        <v>2490</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>2476</v>
+        <v>2491</v>
       </c>
       <c r="D153" s="57" t="s">
-        <v>2477</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29941,13 +30112,13 @@
         <v>663</v>
       </c>
       <c r="B154" s="66" t="s">
-        <v>2478</v>
+        <v>2493</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>2479</v>
+        <v>2494</v>
       </c>
       <c r="D154" s="57" t="s">
-        <v>2480</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29955,13 +30126,13 @@
         <v>663</v>
       </c>
       <c r="B155" s="66" t="s">
-        <v>2460</v>
+        <v>2475</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>2481</v>
+        <v>2496</v>
       </c>
       <c r="D155" s="57" t="s">
-        <v>2482</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29969,13 +30140,13 @@
         <v>663</v>
       </c>
       <c r="B156" s="66" t="s">
-        <v>2483</v>
+        <v>2498</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>2484</v>
+        <v>2499</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>2484</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29983,13 +30154,13 @@
         <v>663</v>
       </c>
       <c r="B157" s="66" t="s">
-        <v>2485</v>
+        <v>2500</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>2486</v>
+        <v>2501</v>
       </c>
       <c r="D157" s="57" t="s">
-        <v>2487</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29999,7 +30170,7 @@
       <c r="C158" s="57"/>
       <c r="D158" s="57"/>
       <c r="G158" s="53" t="s">
-        <v>2182</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30009,7 +30180,7 @@
       <c r="C159" s="57"/>
       <c r="D159" s="57"/>
       <c r="G159" s="66" t="s">
-        <v>2183</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30017,13 +30188,13 @@
         <v>793</v>
       </c>
       <c r="B160" s="53" t="s">
-        <v>2436</v>
+        <v>2451</v>
       </c>
       <c r="C160" s="66" t="s">
-        <v>1970</v>
+        <v>1994</v>
       </c>
       <c r="D160" s="66" t="s">
-        <v>1971</v>
+        <v>1995</v>
       </c>
       <c r="E160" s="53"/>
       <c r="F160" s="53"/>
@@ -30036,13 +30207,13 @@
         <v>793</v>
       </c>
       <c r="B161" s="53" t="s">
-        <v>2437</v>
+        <v>2452</v>
       </c>
       <c r="C161" s="66" t="s">
-        <v>1988</v>
+        <v>2012</v>
       </c>
       <c r="D161" s="66" t="s">
-        <v>1989</v>
+        <v>2013</v>
       </c>
       <c r="E161" s="53"/>
       <c r="F161" s="53"/>
@@ -30055,13 +30226,13 @@
         <v>793</v>
       </c>
       <c r="B162" s="53" t="s">
-        <v>2442</v>
+        <v>2457</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>2488</v>
+        <v>2503</v>
       </c>
       <c r="D162" s="57" t="s">
-        <v>2489</v>
+        <v>2504</v>
       </c>
       <c r="E162" s="53"/>
       <c r="F162" s="53"/>
@@ -30074,13 +30245,13 @@
         <v>793</v>
       </c>
       <c r="B163" s="53" t="s">
-        <v>2430</v>
+        <v>2445</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>1923</v>
+        <v>1947</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>1924</v>
+        <v>1948</v>
       </c>
       <c r="E163" s="53"/>
       <c r="F163" s="53"/>
@@ -30093,13 +30264,13 @@
         <v>793</v>
       </c>
       <c r="B164" s="53" t="s">
-        <v>2490</v>
+        <v>2505</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>1926</v>
+        <v>1950</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>1927</v>
+        <v>1951</v>
       </c>
       <c r="E164" s="53"/>
       <c r="F164" s="53"/>
@@ -30115,10 +30286,10 @@
         <v>229</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>2491</v>
+        <v>2506</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>2492</v>
+        <v>2507</v>
       </c>
       <c r="E165" s="53"/>
       <c r="F165" s="53"/>
@@ -30133,13 +30304,13 @@
         <v>793</v>
       </c>
       <c r="B166" s="53" t="s">
-        <v>2493</v>
+        <v>2508</v>
       </c>
       <c r="C166" s="51" t="s">
-        <v>2494</v>
+        <v>2509</v>
       </c>
       <c r="D166" s="8" t="s">
-        <v>2495</v>
+        <v>2510</v>
       </c>
       <c r="E166" s="53"/>
       <c r="F166" s="53"/>
@@ -30154,13 +30325,13 @@
         <v>141</v>
       </c>
       <c r="B167" s="53" t="s">
-        <v>2496</v>
+        <v>2511</v>
       </c>
       <c r="C167" s="51" t="s">
-        <v>2497</v>
+        <v>2512</v>
       </c>
       <c r="D167" s="8" t="s">
-        <v>2498</v>
+        <v>2513</v>
       </c>
       <c r="E167" s="53"/>
       <c r="F167" s="53"/>
@@ -30173,13 +30344,13 @@
         <v>141</v>
       </c>
       <c r="B168" s="53" t="s">
-        <v>2499</v>
+        <v>2514</v>
       </c>
       <c r="C168" s="51" t="s">
-        <v>2500</v>
+        <v>2515</v>
       </c>
       <c r="D168" s="8" t="s">
-        <v>2501</v>
+        <v>2516</v>
       </c>
       <c r="E168" s="53"/>
       <c r="F168" s="53"/>
@@ -30195,10 +30366,10 @@
         <v>1167</v>
       </c>
       <c r="C169" s="51" t="s">
-        <v>2502</v>
+        <v>2517</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>2503</v>
+        <v>2518</v>
       </c>
       <c r="E169" s="53"/>
       <c r="F169" s="53"/>
@@ -30214,10 +30385,10 @@
         <v>1225</v>
       </c>
       <c r="C170" s="51" t="s">
-        <v>2504</v>
+        <v>2519</v>
       </c>
       <c r="D170" s="8" t="s">
-        <v>2505</v>
+        <v>2520</v>
       </c>
       <c r="E170" s="53"/>
       <c r="F170" s="53"/>
@@ -30235,7 +30406,7 @@
       <c r="E171" s="53"/>
       <c r="F171" s="53"/>
       <c r="G171" s="53" t="s">
-        <v>2183</v>
+        <v>2198</v>
       </c>
       <c r="H171" s="53"/>
       <c r="I171" s="53"/>
@@ -30245,13 +30416,13 @@
         <v>246</v>
       </c>
       <c r="B172" s="53" t="s">
-        <v>2506</v>
+        <v>2521</v>
       </c>
       <c r="C172" s="48" t="s">
-        <v>2507</v>
+        <v>2522</v>
       </c>
       <c r="D172" s="8" t="s">
-        <v>2508</v>
+        <v>2523</v>
       </c>
       <c r="E172" s="53"/>
       <c r="F172" s="53"/>
@@ -30266,13 +30437,13 @@
         <v>246</v>
       </c>
       <c r="B173" s="53" t="s">
-        <v>2509</v>
+        <v>2524</v>
       </c>
       <c r="C173" s="48" t="s">
-        <v>2510</v>
+        <v>2525</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>2511</v>
+        <v>2526</v>
       </c>
       <c r="E173" s="53"/>
       <c r="F173" s="53"/>
@@ -30287,13 +30458,13 @@
         <v>246</v>
       </c>
       <c r="B174" s="53" t="s">
-        <v>2512</v>
+        <v>2527</v>
       </c>
       <c r="C174" s="48" t="s">
-        <v>2513</v>
+        <v>2528</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>2514</v>
+        <v>2529</v>
       </c>
       <c r="E174" s="53"/>
       <c r="F174" s="53"/>
@@ -30308,13 +30479,13 @@
         <v>246</v>
       </c>
       <c r="B175" s="53" t="s">
-        <v>2515</v>
+        <v>2530</v>
       </c>
       <c r="C175" s="48" t="s">
-        <v>2516</v>
+        <v>2531</v>
       </c>
       <c r="D175" s="8" t="s">
-        <v>2517</v>
+        <v>2532</v>
       </c>
       <c r="E175" s="53"/>
       <c r="F175" s="53"/>
@@ -30329,13 +30500,13 @@
         <v>246</v>
       </c>
       <c r="B176" s="53" t="s">
-        <v>2518</v>
+        <v>2533</v>
       </c>
       <c r="C176" s="48" t="s">
-        <v>2519</v>
+        <v>2534</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>2520</v>
+        <v>2535</v>
       </c>
       <c r="E176" s="53"/>
       <c r="F176" s="53"/>
@@ -30350,13 +30521,13 @@
         <v>246</v>
       </c>
       <c r="B177" s="53" t="s">
-        <v>2521</v>
+        <v>2536</v>
       </c>
       <c r="C177" s="48" t="s">
-        <v>2522</v>
+        <v>2537</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>2523</v>
+        <v>2538</v>
       </c>
       <c r="E177" s="53"/>
       <c r="F177" s="53"/>
@@ -30371,13 +30542,13 @@
         <v>246</v>
       </c>
       <c r="B178" s="53" t="s">
-        <v>2524</v>
+        <v>2539</v>
       </c>
       <c r="C178" s="48" t="s">
-        <v>2525</v>
+        <v>2540</v>
       </c>
       <c r="D178" s="8" t="s">
-        <v>2526</v>
+        <v>2541</v>
       </c>
       <c r="E178" s="53"/>
       <c r="F178" s="53"/>
@@ -30392,13 +30563,13 @@
         <v>246</v>
       </c>
       <c r="B179" s="53" t="s">
-        <v>2527</v>
+        <v>2542</v>
       </c>
       <c r="C179" s="48" t="s">
-        <v>2528</v>
+        <v>2543</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>2529</v>
+        <v>2544</v>
       </c>
       <c r="E179" s="53"/>
       <c r="F179" s="53"/>
@@ -30413,13 +30584,13 @@
         <v>246</v>
       </c>
       <c r="B180" s="53" t="s">
-        <v>2530</v>
+        <v>2545</v>
       </c>
       <c r="C180" s="48" t="s">
-        <v>2531</v>
+        <v>2546</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>2532</v>
+        <v>2547</v>
       </c>
       <c r="E180" s="53"/>
       <c r="F180" s="53"/>
@@ -30437,10 +30608,10 @@
         <v>229</v>
       </c>
       <c r="C181" s="48" t="s">
-        <v>2180</v>
+        <v>2195</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>2181</v>
+        <v>2196</v>
       </c>
       <c r="E181" s="53"/>
       <c r="F181" s="53"/>
@@ -30470,13 +30641,13 @@
         <v>258</v>
       </c>
       <c r="B183" s="53" t="s">
-        <v>2533</v>
+        <v>2548</v>
       </c>
       <c r="C183" s="48" t="s">
-        <v>2534</v>
+        <v>2549</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>2535</v>
+        <v>2550</v>
       </c>
       <c r="E183" s="53"/>
       <c r="F183" s="53"/>
@@ -30491,13 +30662,13 @@
         <v>258</v>
       </c>
       <c r="B184" s="53" t="s">
-        <v>2536</v>
+        <v>2551</v>
       </c>
       <c r="C184" s="48" t="s">
-        <v>2537</v>
+        <v>2552</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>2538</v>
+        <v>2553</v>
       </c>
       <c r="E184" s="53"/>
       <c r="F184" s="53"/>
@@ -30512,13 +30683,13 @@
         <v>258</v>
       </c>
       <c r="B185" s="53" t="s">
-        <v>2539</v>
+        <v>2554</v>
       </c>
       <c r="C185" s="48" t="s">
-        <v>2540</v>
+        <v>2555</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>2541</v>
+        <v>2556</v>
       </c>
       <c r="E185" s="53"/>
       <c r="F185" s="53"/>
@@ -30533,13 +30704,13 @@
         <v>258</v>
       </c>
       <c r="B186" s="53" t="s">
-        <v>2542</v>
+        <v>2557</v>
       </c>
       <c r="C186" s="48" t="s">
-        <v>2543</v>
+        <v>2558</v>
       </c>
       <c r="D186" s="8" t="s">
-        <v>2544</v>
+        <v>2559</v>
       </c>
       <c r="E186" s="53"/>
       <c r="F186" s="53"/>
@@ -30554,13 +30725,13 @@
         <v>258</v>
       </c>
       <c r="B187" s="53" t="s">
-        <v>2545</v>
+        <v>2560</v>
       </c>
       <c r="C187" s="48" t="s">
-        <v>2546</v>
+        <v>2561</v>
       </c>
       <c r="D187" s="8" t="s">
-        <v>2547</v>
+        <v>2562</v>
       </c>
       <c r="E187" s="53"/>
       <c r="F187" s="53"/>
@@ -30575,13 +30746,13 @@
         <v>258</v>
       </c>
       <c r="B188" s="53" t="s">
-        <v>2548</v>
+        <v>2563</v>
       </c>
       <c r="C188" s="48" t="s">
-        <v>2549</v>
+        <v>2564</v>
       </c>
       <c r="D188" s="8" t="s">
-        <v>2550</v>
+        <v>2565</v>
       </c>
       <c r="E188" s="53"/>
       <c r="F188" s="53"/>
@@ -30596,13 +30767,13 @@
         <v>258</v>
       </c>
       <c r="B189" s="53" t="s">
-        <v>2551</v>
+        <v>2566</v>
       </c>
       <c r="C189" s="48" t="s">
-        <v>2552</v>
+        <v>2567</v>
       </c>
       <c r="D189" s="8" t="s">
-        <v>2553</v>
+        <v>2568</v>
       </c>
       <c r="E189" s="53"/>
       <c r="F189" s="53"/>
@@ -30620,10 +30791,10 @@
         <v>1207</v>
       </c>
       <c r="C190" s="48" t="s">
-        <v>2554</v>
+        <v>2569</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>2555</v>
+        <v>2570</v>
       </c>
       <c r="E190" s="53"/>
       <c r="F190" s="53"/>
@@ -30640,10 +30811,10 @@
         <v>229</v>
       </c>
       <c r="C191" s="48" t="s">
-        <v>2180</v>
+        <v>2195</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>2181</v>
+        <v>2196</v>
       </c>
       <c r="E191" s="53"/>
       <c r="F191" s="53"/>
@@ -30661,10 +30832,10 @@
         <v>1171</v>
       </c>
       <c r="C192" s="53" t="s">
-        <v>2186</v>
+        <v>2201</v>
       </c>
       <c r="D192" s="53" t="s">
-        <v>2187</v>
+        <v>2202</v>
       </c>
       <c r="E192" s="53"/>
       <c r="F192" s="53"/>
@@ -30678,13 +30849,13 @@
         <v>287</v>
       </c>
       <c r="B193" s="53" t="s">
-        <v>2556</v>
+        <v>2571</v>
       </c>
       <c r="C193" s="48" t="s">
-        <v>2557</v>
+        <v>2572</v>
       </c>
       <c r="D193" s="8" t="s">
-        <v>2558</v>
+        <v>2573</v>
       </c>
       <c r="E193" s="53"/>
       <c r="F193" s="53"/>
@@ -30697,13 +30868,13 @@
         <v>287</v>
       </c>
       <c r="B194" s="53" t="s">
-        <v>2559</v>
+        <v>2574</v>
       </c>
       <c r="C194" s="48" t="s">
-        <v>2560</v>
+        <v>2575</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>2561</v>
+        <v>2576</v>
       </c>
       <c r="E194" s="53"/>
       <c r="F194" s="53"/>
@@ -30716,13 +30887,13 @@
         <v>287</v>
       </c>
       <c r="B195" s="53" t="s">
-        <v>2562</v>
+        <v>2577</v>
       </c>
       <c r="C195" s="48" t="s">
-        <v>2563</v>
+        <v>2578</v>
       </c>
       <c r="D195" s="8" t="s">
-        <v>2564</v>
+        <v>2579</v>
       </c>
       <c r="E195" s="53"/>
       <c r="F195" s="53"/>
@@ -30735,13 +30906,13 @@
         <v>287</v>
       </c>
       <c r="B196" s="53" t="s">
-        <v>2565</v>
+        <v>2580</v>
       </c>
       <c r="C196" s="48" t="s">
-        <v>2566</v>
+        <v>2581</v>
       </c>
       <c r="D196" s="8" t="s">
-        <v>2567</v>
+        <v>2582</v>
       </c>
       <c r="E196" s="53"/>
       <c r="F196" s="53"/>
@@ -30754,13 +30925,13 @@
         <v>287</v>
       </c>
       <c r="B197" s="53" t="s">
-        <v>2568</v>
+        <v>2583</v>
       </c>
       <c r="C197" s="48" t="s">
-        <v>2569</v>
+        <v>2584</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>2570</v>
+        <v>2585</v>
       </c>
       <c r="E197" s="53"/>
       <c r="F197" s="53"/>
@@ -30773,13 +30944,13 @@
         <v>294</v>
       </c>
       <c r="B198" s="53" t="s">
-        <v>2556</v>
+        <v>2571</v>
       </c>
       <c r="C198" s="48" t="s">
-        <v>2557</v>
+        <v>2572</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>2558</v>
+        <v>2573</v>
       </c>
       <c r="E198" s="53"/>
       <c r="F198" s="53"/>
@@ -30794,13 +30965,13 @@
         <v>294</v>
       </c>
       <c r="B199" s="53" t="s">
-        <v>2559</v>
+        <v>2574</v>
       </c>
       <c r="C199" s="48" t="s">
-        <v>2560</v>
+        <v>2575</v>
       </c>
       <c r="D199" s="8" t="s">
-        <v>2561</v>
+        <v>2576</v>
       </c>
       <c r="E199" s="53"/>
       <c r="F199" s="53"/>
@@ -30813,13 +30984,13 @@
         <v>294</v>
       </c>
       <c r="B200" s="53" t="s">
-        <v>2562</v>
+        <v>2577</v>
       </c>
       <c r="C200" s="48" t="s">
-        <v>2563</v>
+        <v>2578</v>
       </c>
       <c r="D200" s="8" t="s">
-        <v>2564</v>
+        <v>2579</v>
       </c>
       <c r="E200" s="53"/>
       <c r="F200" s="53"/>
@@ -30832,13 +31003,13 @@
         <v>294</v>
       </c>
       <c r="B201" s="53" t="s">
-        <v>2565</v>
+        <v>2580</v>
       </c>
       <c r="C201" s="48" t="s">
-        <v>2566</v>
+        <v>2581</v>
       </c>
       <c r="D201" s="8" t="s">
-        <v>2567</v>
+        <v>2582</v>
       </c>
       <c r="E201" s="53"/>
       <c r="F201" s="53"/>
@@ -30851,13 +31022,13 @@
         <v>294</v>
       </c>
       <c r="B202" s="53" t="s">
-        <v>2568</v>
+        <v>2583</v>
       </c>
       <c r="C202" s="48" t="s">
-        <v>2569</v>
+        <v>2584</v>
       </c>
       <c r="D202" s="8" t="s">
-        <v>2570</v>
+        <v>2585</v>
       </c>
       <c r="E202" s="53"/>
       <c r="F202" s="53"/>
@@ -30870,13 +31041,13 @@
         <v>857</v>
       </c>
       <c r="B203" s="66" t="s">
-        <v>2430</v>
+        <v>2445</v>
       </c>
       <c r="C203" s="66" t="s">
-        <v>2021</v>
+        <v>1923</v>
       </c>
       <c r="D203" s="66" t="s">
-        <v>2022</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30884,13 +31055,13 @@
         <v>857</v>
       </c>
       <c r="B204" s="66" t="s">
-        <v>2438</v>
+        <v>2453</v>
       </c>
       <c r="C204" s="66" t="s">
-        <v>2040</v>
+        <v>1926</v>
       </c>
       <c r="D204" s="66" t="s">
-        <v>2041</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30898,13 +31069,13 @@
         <v>857</v>
       </c>
       <c r="B205" s="66" t="s">
-        <v>2571</v>
+        <v>2586</v>
       </c>
       <c r="C205" s="66" t="s">
-        <v>2572</v>
+        <v>2587</v>
       </c>
       <c r="D205" s="66" t="s">
-        <v>2573</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30912,13 +31083,13 @@
         <v>857</v>
       </c>
       <c r="B206" s="66" t="s">
-        <v>2442</v>
+        <v>2457</v>
       </c>
       <c r="C206" s="66" t="s">
-        <v>2574</v>
+        <v>2589</v>
       </c>
       <c r="D206" s="66" t="s">
-        <v>2575</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30926,7 +31097,7 @@
         <v>857</v>
       </c>
       <c r="G207" s="66" t="s">
-        <v>2182</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30934,13 +31105,13 @@
         <v>882</v>
       </c>
       <c r="B208" s="66" t="s">
-        <v>2576</v>
+        <v>2591</v>
       </c>
       <c r="C208" s="66" t="s">
-        <v>2577</v>
+        <v>2592</v>
       </c>
       <c r="D208" s="66" t="s">
-        <v>2578</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30948,13 +31119,13 @@
         <v>882</v>
       </c>
       <c r="B209" s="66" t="s">
-        <v>2579</v>
+        <v>2594</v>
       </c>
       <c r="C209" s="66" t="s">
-        <v>2580</v>
+        <v>2595</v>
       </c>
       <c r="D209" s="66" t="s">
-        <v>2581</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30962,13 +31133,13 @@
         <v>882</v>
       </c>
       <c r="B210" s="66" t="s">
-        <v>2582</v>
+        <v>2597</v>
       </c>
       <c r="C210" s="66" t="s">
-        <v>2583</v>
+        <v>2598</v>
       </c>
       <c r="D210" s="66" t="s">
-        <v>2584</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30976,13 +31147,13 @@
         <v>882</v>
       </c>
       <c r="B211" s="66" t="s">
-        <v>2585</v>
+        <v>2600</v>
       </c>
       <c r="C211" s="66" t="s">
-        <v>2586</v>
+        <v>2601</v>
       </c>
       <c r="D211" s="66" t="s">
-        <v>2587</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30990,13 +31161,13 @@
         <v>882</v>
       </c>
       <c r="B212" s="66" t="s">
-        <v>2588</v>
+        <v>2603</v>
       </c>
       <c r="C212" s="66" t="s">
-        <v>2589</v>
+        <v>2604</v>
       </c>
       <c r="D212" s="66" t="s">
-        <v>2590</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31004,13 +31175,13 @@
         <v>882</v>
       </c>
       <c r="B213" s="66" t="s">
-        <v>2591</v>
+        <v>2606</v>
       </c>
       <c r="C213" s="66" t="s">
-        <v>2592</v>
+        <v>2607</v>
       </c>
       <c r="D213" s="66" t="s">
-        <v>2593</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31021,10 +31192,10 @@
         <v>229</v>
       </c>
       <c r="C214" s="66" t="s">
-        <v>2594</v>
+        <v>2609</v>
       </c>
       <c r="D214" s="66" t="s">
-        <v>2595</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31032,13 +31203,13 @@
         <v>887</v>
       </c>
       <c r="B215" s="66" t="s">
-        <v>2430</v>
+        <v>2445</v>
       </c>
       <c r="C215" s="66" t="s">
-        <v>2021</v>
+        <v>1923</v>
       </c>
       <c r="D215" s="66" t="s">
-        <v>2022</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31046,13 +31217,13 @@
         <v>887</v>
       </c>
       <c r="B216" s="66" t="s">
-        <v>2438</v>
+        <v>2453</v>
       </c>
       <c r="C216" s="66" t="s">
-        <v>2040</v>
+        <v>1926</v>
       </c>
       <c r="D216" s="66" t="s">
-        <v>2041</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31060,13 +31231,13 @@
         <v>887</v>
       </c>
       <c r="B217" s="66" t="s">
-        <v>2436</v>
+        <v>2451</v>
       </c>
       <c r="C217" s="66" t="s">
-        <v>2596</v>
+        <v>2611</v>
       </c>
       <c r="D217" s="66" t="s">
-        <v>2597</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="218" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31074,13 +31245,13 @@
         <v>887</v>
       </c>
       <c r="B218" s="66" t="s">
-        <v>2437</v>
+        <v>2452</v>
       </c>
       <c r="C218" s="66" t="s">
-        <v>2598</v>
+        <v>2613</v>
       </c>
       <c r="D218" s="66" t="s">
-        <v>2599</v>
+        <v>2614</v>
       </c>
       <c r="E218" s="66"/>
       <c r="F218" s="66"/>
@@ -31093,13 +31264,13 @@
         <v>887</v>
       </c>
       <c r="B219" s="66" t="s">
-        <v>2442</v>
+        <v>2457</v>
       </c>
       <c r="C219" s="66" t="s">
-        <v>2574</v>
+        <v>2589</v>
       </c>
       <c r="D219" s="66" t="s">
-        <v>2575</v>
+        <v>2590</v>
       </c>
       <c r="E219" s="66"/>
       <c r="F219" s="66"/>
@@ -31115,10 +31286,10 @@
         <v>229</v>
       </c>
       <c r="C220" s="66" t="s">
-        <v>2600</v>
+        <v>2615</v>
       </c>
       <c r="D220" s="66" t="s">
-        <v>2601</v>
+        <v>2616</v>
       </c>
       <c r="E220" s="66"/>
       <c r="F220" s="66"/>
@@ -31134,10 +31305,10 @@
         <v>1258</v>
       </c>
       <c r="C221" s="8" t="s">
-        <v>2602</v>
+        <v>2617</v>
       </c>
       <c r="D221" s="8" t="s">
-        <v>2603</v>
+        <v>2618</v>
       </c>
       <c r="E221" s="66"/>
       <c r="F221" s="66"/>
@@ -31150,13 +31321,13 @@
         <v>1052</v>
       </c>
       <c r="B222" s="66" t="s">
-        <v>2604</v>
+        <v>2619</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>2605</v>
+        <v>2620</v>
       </c>
       <c r="D222" s="8" t="s">
-        <v>2606</v>
+        <v>2621</v>
       </c>
       <c r="E222" s="66"/>
       <c r="F222" s="66"/>
@@ -31171,13 +31342,13 @@
         <v>1052</v>
       </c>
       <c r="B223" s="66" t="s">
-        <v>2607</v>
+        <v>2622</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>2608</v>
+        <v>2623</v>
       </c>
       <c r="D223" s="8" t="s">
-        <v>2609</v>
+        <v>2624</v>
       </c>
       <c r="E223" s="66"/>
       <c r="F223" s="66"/>
@@ -31192,13 +31363,13 @@
         <v>1052</v>
       </c>
       <c r="B224" s="66" t="s">
-        <v>2610</v>
+        <v>2625</v>
       </c>
       <c r="C224" s="8" t="s">
-        <v>2611</v>
+        <v>2626</v>
       </c>
       <c r="D224" s="51" t="s">
-        <v>2612</v>
+        <v>2627</v>
       </c>
       <c r="E224" s="66"/>
       <c r="F224" s="66"/>
@@ -31213,13 +31384,13 @@
         <v>1052</v>
       </c>
       <c r="B225" s="66" t="s">
-        <v>2613</v>
+        <v>2628</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>2614</v>
+        <v>2629</v>
       </c>
       <c r="D225" s="48" t="s">
-        <v>2615</v>
+        <v>2630</v>
       </c>
       <c r="E225" s="66"/>
       <c r="F225" s="66"/>
@@ -31232,13 +31403,13 @@
         <v>1058</v>
       </c>
       <c r="B226" s="66" t="s">
-        <v>2616</v>
+        <v>2631</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>2617</v>
+        <v>2632</v>
       </c>
       <c r="D226" s="8" t="s">
-        <v>2618</v>
+        <v>2633</v>
       </c>
       <c r="E226" s="66"/>
       <c r="F226" s="66"/>
@@ -31253,13 +31424,13 @@
         <v>1058</v>
       </c>
       <c r="B227" s="66" t="s">
-        <v>2619</v>
+        <v>2634</v>
       </c>
       <c r="C227" s="8" t="s">
-        <v>2620</v>
+        <v>2635</v>
       </c>
       <c r="D227" s="8" t="s">
-        <v>2621</v>
+        <v>2636</v>
       </c>
       <c r="E227" s="66"/>
       <c r="F227" s="66"/>
@@ -31274,13 +31445,13 @@
         <v>1058</v>
       </c>
       <c r="B228" s="66" t="s">
-        <v>2622</v>
+        <v>2637</v>
       </c>
       <c r="C228" s="8" t="s">
-        <v>2623</v>
+        <v>2638</v>
       </c>
       <c r="D228" s="8" t="s">
-        <v>2624</v>
+        <v>2639</v>
       </c>
       <c r="E228" s="66"/>
       <c r="F228" s="66"/>
@@ -31290,16 +31461,16 @@
     </row>
     <row r="229" s="50" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="54" t="s">
-        <v>2625</v>
+        <v>2640</v>
       </c>
       <c r="B229" s="66" t="s">
         <v>1167</v>
       </c>
       <c r="C229" s="51" t="s">
-        <v>2626</v>
+        <v>2641</v>
       </c>
       <c r="D229" s="8" t="s">
-        <v>2627</v>
+        <v>2642</v>
       </c>
       <c r="E229" s="66"/>
       <c r="F229" s="66"/>
@@ -31309,16 +31480,16 @@
     </row>
     <row r="230" s="50" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="54" t="s">
-        <v>2625</v>
+        <v>2640</v>
       </c>
       <c r="B230" s="66" t="s">
         <v>1225</v>
       </c>
       <c r="C230" s="51" t="s">
-        <v>2628</v>
+        <v>2643</v>
       </c>
       <c r="D230" s="48" t="s">
-        <v>2629</v>
+        <v>2644</v>
       </c>
       <c r="E230" s="66"/>
       <c r="F230" s="66"/>
@@ -31331,13 +31502,13 @@
         <v>1088</v>
       </c>
       <c r="B231" s="66" t="s">
-        <v>2630</v>
+        <v>2645</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>2631</v>
+        <v>2646</v>
       </c>
       <c r="D231" s="51" t="s">
-        <v>2632</v>
+        <v>2647</v>
       </c>
       <c r="E231" s="66"/>
       <c r="F231" s="66"/>
@@ -31350,13 +31521,13 @@
         <v>1088</v>
       </c>
       <c r="B232" s="66" t="s">
-        <v>2633</v>
+        <v>2648</v>
       </c>
       <c r="C232" s="8" t="s">
-        <v>2634</v>
+        <v>2649</v>
       </c>
       <c r="D232" s="51" t="s">
-        <v>2635</v>
+        <v>2650</v>
       </c>
       <c r="E232" s="66"/>
       <c r="F232" s="66"/>
@@ -31369,13 +31540,13 @@
         <v>1088</v>
       </c>
       <c r="B233" s="66" t="s">
-        <v>2636</v>
+        <v>2651</v>
       </c>
       <c r="C233" s="8" t="s">
-        <v>2637</v>
+        <v>2652</v>
       </c>
       <c r="D233" s="51" t="s">
-        <v>2638</v>
+        <v>2653</v>
       </c>
       <c r="E233" s="66"/>
       <c r="F233" s="66"/>
@@ -31388,13 +31559,13 @@
         <v>1088</v>
       </c>
       <c r="B234" s="66" t="s">
-        <v>2639</v>
+        <v>2654</v>
       </c>
       <c r="C234" s="8" t="s">
-        <v>2640</v>
+        <v>2655</v>
       </c>
       <c r="D234" s="51" t="s">
-        <v>2641</v>
+        <v>2656</v>
       </c>
       <c r="E234" s="66"/>
       <c r="F234" s="66"/>
@@ -31407,13 +31578,13 @@
         <v>1088</v>
       </c>
       <c r="B235" s="66" t="s">
-        <v>2642</v>
+        <v>2657</v>
       </c>
       <c r="C235" s="8" t="s">
-        <v>2643</v>
+        <v>2658</v>
       </c>
       <c r="D235" s="51" t="s">
-        <v>2644</v>
+        <v>2659</v>
       </c>
     </row>
     <row r="236" s="50" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31421,13 +31592,13 @@
         <v>1088</v>
       </c>
       <c r="B236" s="66" t="s">
-        <v>2645</v>
+        <v>2660</v>
       </c>
       <c r="C236" s="8" t="s">
-        <v>2646</v>
+        <v>2661</v>
       </c>
       <c r="D236" s="51" t="s">
-        <v>2647</v>
+        <v>2662</v>
       </c>
       <c r="E236" s="66"/>
       <c r="F236" s="66"/>
@@ -31445,7 +31616,7 @@
       <c r="E237" s="66"/>
       <c r="F237" s="66"/>
       <c r="G237" s="53" t="s">
-        <v>2182</v>
+        <v>2197</v>
       </c>
       <c r="H237" s="66"/>
       <c r="I237" s="66"/>
@@ -31455,13 +31626,13 @@
         <v>946</v>
       </c>
       <c r="B238" s="50" t="s">
-        <v>2648</v>
+        <v>2663</v>
       </c>
       <c r="C238" s="50" t="s">
-        <v>2649</v>
+        <v>2664</v>
       </c>
       <c r="D238" s="50" t="s">
-        <v>2650</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="239" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31469,13 +31640,13 @@
         <v>946</v>
       </c>
       <c r="B239" s="50" t="s">
-        <v>2562</v>
+        <v>2577</v>
       </c>
       <c r="C239" s="50" t="s">
-        <v>2651</v>
+        <v>2666</v>
       </c>
       <c r="D239" s="50" t="s">
-        <v>2652</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="240" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31483,13 +31654,13 @@
         <v>946</v>
       </c>
       <c r="B240" s="50" t="s">
-        <v>2653</v>
+        <v>2668</v>
       </c>
       <c r="C240" s="50" t="s">
-        <v>2654</v>
+        <v>2669</v>
       </c>
       <c r="D240" s="50" t="s">
-        <v>2655</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="241" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31497,13 +31668,13 @@
         <v>946</v>
       </c>
       <c r="B241" s="50" t="s">
-        <v>2656</v>
+        <v>2671</v>
       </c>
       <c r="C241" s="50" t="s">
-        <v>2657</v>
+        <v>2672</v>
       </c>
       <c r="D241" s="50" t="s">
-        <v>2658</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="242" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31511,13 +31682,13 @@
         <v>946</v>
       </c>
       <c r="B242" s="50" t="s">
-        <v>2659</v>
+        <v>2674</v>
       </c>
       <c r="C242" s="50" t="s">
-        <v>2660</v>
+        <v>2675</v>
       </c>
       <c r="D242" s="50" t="s">
-        <v>2661</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="243" s="50" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31528,10 +31699,10 @@
         <v>-2</v>
       </c>
       <c r="C243" s="57" t="s">
-        <v>2662</v>
+        <v>2677</v>
       </c>
       <c r="D243" s="57" t="s">
-        <v>2663</v>
+        <v>2678</v>
       </c>
       <c r="E243" s="66"/>
       <c r="F243" s="66"/>
@@ -31547,10 +31718,10 @@
         <v>-1</v>
       </c>
       <c r="C244" s="57" t="s">
-        <v>2664</v>
+        <v>2679</v>
       </c>
       <c r="D244" s="57" t="s">
-        <v>2665</v>
+        <v>2680</v>
       </c>
       <c r="E244" s="66"/>
       <c r="F244" s="66"/>
@@ -31566,10 +31737,10 @@
         <v>0</v>
       </c>
       <c r="C245" s="57" t="s">
-        <v>2666</v>
+        <v>2681</v>
       </c>
       <c r="D245" s="57" t="s">
-        <v>2667</v>
+        <v>2682</v>
       </c>
       <c r="E245" s="66"/>
       <c r="F245" s="66"/>
@@ -31585,10 +31756,10 @@
         <v>1</v>
       </c>
       <c r="C246" s="57" t="s">
-        <v>2668</v>
+        <v>2683</v>
       </c>
       <c r="D246" s="57" t="s">
-        <v>2669</v>
+        <v>2684</v>
       </c>
       <c r="E246" s="66"/>
       <c r="F246" s="66"/>
@@ -31604,10 +31775,10 @@
         <v>2</v>
       </c>
       <c r="C247" s="57" t="s">
-        <v>2670</v>
+        <v>2685</v>
       </c>
       <c r="D247" s="57" t="s">
-        <v>2671</v>
+        <v>2686</v>
       </c>
       <c r="E247" s="66"/>
       <c r="F247" s="66"/>
@@ -31623,10 +31794,10 @@
         <v>0</v>
       </c>
       <c r="C248" s="48" t="s">
-        <v>2672</v>
+        <v>2687</v>
       </c>
       <c r="D248" s="57" t="s">
-        <v>2673</v>
+        <v>2688</v>
       </c>
       <c r="E248" s="66"/>
       <c r="F248" s="66"/>
@@ -31642,10 +31813,10 @@
         <v>1</v>
       </c>
       <c r="C249" s="48" t="s">
-        <v>2674</v>
+        <v>2689</v>
       </c>
       <c r="D249" s="51" t="s">
-        <v>2675</v>
+        <v>2690</v>
       </c>
       <c r="E249" s="66"/>
       <c r="F249" s="66"/>
@@ -31661,10 +31832,10 @@
         <v>2</v>
       </c>
       <c r="C250" s="48" t="s">
-        <v>2676</v>
+        <v>2691</v>
       </c>
       <c r="D250" s="51" t="s">
-        <v>2677</v>
+        <v>2692</v>
       </c>
       <c r="E250" s="66"/>
       <c r="F250" s="66"/>
@@ -31680,10 +31851,10 @@
         <v>3</v>
       </c>
       <c r="C251" s="48" t="s">
-        <v>2678</v>
+        <v>2693</v>
       </c>
       <c r="D251" s="51" t="s">
-        <v>2679</v>
+        <v>2694</v>
       </c>
       <c r="E251" s="66"/>
       <c r="F251" s="66"/>
@@ -31699,10 +31870,10 @@
         <v>4</v>
       </c>
       <c r="C252" s="48" t="s">
-        <v>2680</v>
+        <v>2695</v>
       </c>
       <c r="D252" s="51" t="s">
-        <v>2681</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31713,10 +31884,10 @@
         <v>-1</v>
       </c>
       <c r="C253" s="48" t="s">
-        <v>2682</v>
+        <v>2697</v>
       </c>
       <c r="D253" s="51" t="s">
-        <v>2683</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31724,13 +31895,13 @@
         <v>39</v>
       </c>
       <c r="B254" s="66" t="s">
-        <v>2684</v>
+        <v>2699</v>
       </c>
       <c r="C254" s="66" t="s">
-        <v>2685</v>
+        <v>2700</v>
       </c>
       <c r="D254" s="66" t="s">
-        <v>2686</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -194,35 +194,8 @@
     <t xml:space="preserve">wantToParticipateToDraw</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Je souhaite participer au **tirage au sort**
-__Seuls les gagnants seront contactés. Il est nécessaire de terminer le questionnaire pour être retenu (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[Voir règlement](lien)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">).__</t>
-    </r>
+    <t xml:space="preserve">Je souhaite participer au **tirage au sort**
+__Seuls les gagnants seront contactés. Il est nécessaire de terminer le questionnaire pour être retenu (&lt;a href="https://www.artm.quebec/wp-content/uploads/2026/07/Reglement-concours_Enquete-2026-Pm_FR.pdf" target="_blank"&gt;Voir règlement&lt;/a&gt;).__</t>
   </si>
   <si>
     <r>
@@ -243,7 +216,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">[View rules](lien)</t>
+      <t xml:space="preserve">&lt;a href="https://www.artm.quebec/wp-content/uploads/2026/08/Contest-Rules_2026-Pm_EN.pdf" target="_blank"&gt;View rules&lt;/a&gt;</t>
     </r>
     <r>
       <rPr>
@@ -10191,7 +10164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
         <v>52</v>
       </c>
@@ -26130,13 +26103,13 @@
       <c r="A177" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B177" s="0" t="s">
+      <c r="B177" s="50" t="s">
         <v>1922</v>
       </c>
-      <c r="C177" s="0" t="s">
+      <c r="C177" s="50" t="s">
         <v>1923</v>
       </c>
-      <c r="D177" s="0" t="s">
+      <c r="D177" s="50" t="s">
         <v>1924</v>
       </c>
     </row>
@@ -26144,13 +26117,13 @@
       <c r="A178" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B178" s="0" t="s">
+      <c r="B178" s="50" t="s">
         <v>1925</v>
       </c>
-      <c r="C178" s="0" t="s">
+      <c r="C178" s="50" t="s">
         <v>1926</v>
       </c>
-      <c r="D178" s="0" t="s">
+      <c r="D178" s="50" t="s">
         <v>1927</v>
       </c>
     </row>
@@ -26158,13 +26131,13 @@
       <c r="A179" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B179" s="0" t="s">
+      <c r="B179" s="50" t="s">
         <v>1928</v>
       </c>
-      <c r="C179" s="0" t="s">
+      <c r="C179" s="50" t="s">
         <v>1929</v>
       </c>
-      <c r="D179" s="0" t="s">
+      <c r="D179" s="50" t="s">
         <v>1929</v>
       </c>
     </row>
@@ -26172,13 +26145,13 @@
       <c r="A180" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B180" s="0" t="s">
+      <c r="B180" s="50" t="s">
         <v>1930</v>
       </c>
-      <c r="C180" s="0" t="s">
+      <c r="C180" s="50" t="s">
         <v>1931</v>
       </c>
-      <c r="D180" s="0" t="s">
+      <c r="D180" s="50" t="s">
         <v>1932</v>
       </c>
     </row>
@@ -26186,13 +26159,13 @@
       <c r="A181" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B181" s="0" t="s">
+      <c r="B181" s="50" t="s">
         <v>1933</v>
       </c>
-      <c r="C181" s="0" t="s">
+      <c r="C181" s="50" t="s">
         <v>1934</v>
       </c>
-      <c r="D181" s="0" t="s">
+      <c r="D181" s="50" t="s">
         <v>1935</v>
       </c>
     </row>
@@ -26200,13 +26173,13 @@
       <c r="A182" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B182" s="0" t="s">
+      <c r="B182" s="50" t="s">
         <v>1936</v>
       </c>
-      <c r="C182" s="0" t="s">
+      <c r="C182" s="50" t="s">
         <v>1937</v>
       </c>
-      <c r="D182" s="0" t="s">
+      <c r="D182" s="50" t="s">
         <v>1938</v>
       </c>
     </row>
@@ -26214,13 +26187,13 @@
       <c r="A183" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B183" s="0" t="s">
+      <c r="B183" s="50" t="s">
         <v>1939</v>
       </c>
-      <c r="C183" s="0" t="s">
+      <c r="C183" s="50" t="s">
         <v>1940</v>
       </c>
-      <c r="D183" s="0" t="s">
+      <c r="D183" s="50" t="s">
         <v>1941</v>
       </c>
     </row>
@@ -26228,13 +26201,13 @@
       <c r="A184" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B184" s="0" t="s">
+      <c r="B184" s="50" t="s">
         <v>1942</v>
       </c>
-      <c r="C184" s="0" t="s">
+      <c r="C184" s="50" t="s">
         <v>1943</v>
       </c>
-      <c r="D184" s="0" t="s">
+      <c r="D184" s="50" t="s">
         <v>1944</v>
       </c>
     </row>
@@ -26242,13 +26215,13 @@
       <c r="A185" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="B185" s="0" t="s">
+      <c r="B185" s="50" t="s">
         <v>1945</v>
       </c>
-      <c r="C185" s="0" t="s">
+      <c r="C185" s="50" t="s">
         <v>1601</v>
       </c>
-      <c r="D185" s="0" t="s">
+      <c r="D185" s="50" t="s">
         <v>1602</v>
       </c>
     </row>

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -16,7 +16,7 @@
     <sheet name="Choices" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Labels!$A$1:$F$269</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Labels!$A$1:$F$271</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Widgets!$A$1:$W$1048536</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4935" uniqueCount="2702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4943" uniqueCount="2704">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -7030,6 +7030,12 @@
   <si>
     <t xml:space="preserve">
 __**Note:** Information prefilled from {{referenceNickname}}'s trip diary. Verify if the information is correct and change if needed.__</t>
+  </si>
+  <si>
+    <t xml:space="preserve">featureSelect.other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">featureSelect.dontKnow</t>
   </si>
   <si>
     <t xml:space="preserve">personHasSchoolPlace_schoolchildcare</t>
@@ -23264,7 +23270,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F275"/>
+  <dimension ref="A1:F277"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="50" width="16.66"/>
@@ -27233,114 +27239,114 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="48" t="s">
+    <row r="258" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="50" t="s">
+        <v>560</v>
+      </c>
+      <c r="B258" s="8" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C258" s="8" t="s">
+        <v>1601</v>
+      </c>
+      <c r="D258" s="57" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="50" t="s">
+        <v>560</v>
+      </c>
+      <c r="B259" s="8" t="s">
+        <v>2140</v>
+      </c>
+      <c r="C259" s="8" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D259" s="57" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="48" t="s">
         <v>756</v>
       </c>
-      <c r="B258" s="54" t="s">
-        <v>2139</v>
-      </c>
-      <c r="C258" s="8" t="s">
-        <v>2140</v>
-      </c>
-      <c r="D258" s="85" t="s">
+      <c r="B260" s="54" t="s">
         <v>2141</v>
       </c>
-    </row>
-    <row r="259" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="50" t="s">
-        <v>756</v>
-      </c>
-      <c r="B259" s="86" t="s">
+      <c r="C260" s="8" t="s">
         <v>2142</v>
       </c>
-      <c r="C259" s="48" t="s">
-        <v>1371</v>
-      </c>
-      <c r="D259" s="51" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="260" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="50" t="s">
-        <v>756</v>
-      </c>
-      <c r="B260" s="86" t="s">
+      <c r="D260" s="85" t="s">
         <v>2143</v>
       </c>
-      <c r="C260" s="8" t="s">
-        <v>2144</v>
-      </c>
-      <c r="D260" s="51" t="s">
-        <v>2145</v>
-      </c>
-    </row>
-    <row r="261" customFormat="false" ht="285.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="261" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="50" t="s">
         <v>756</v>
       </c>
-      <c r="B261" s="53" t="s">
-        <v>2146</v>
-      </c>
-      <c r="C261" s="54" t="s">
-        <v>2147</v>
-      </c>
-      <c r="D261" s="54" t="s">
-        <v>2148</v>
-      </c>
-      <c r="E261" s="54" t="s">
-        <v>2149</v>
-      </c>
-      <c r="F261" s="54" t="s">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="262" customFormat="false" ht="225.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B261" s="86" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C261" s="48" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D261" s="51" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="50" t="s">
         <v>756</v>
       </c>
-      <c r="B262" s="53" t="s">
+      <c r="B262" s="86" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C262" s="8" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D262" s="51" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="285.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="50" t="s">
+        <v>756</v>
+      </c>
+      <c r="B263" s="53" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C263" s="54" t="s">
+        <v>2149</v>
+      </c>
+      <c r="D263" s="54" t="s">
+        <v>2150</v>
+      </c>
+      <c r="E263" s="54" t="s">
         <v>2151</v>
       </c>
-      <c r="C262" s="54" t="s">
+      <c r="F263" s="54" t="s">
         <v>2152</v>
       </c>
-      <c r="D262" s="54" t="s">
+    </row>
+    <row r="264" customFormat="false" ht="225.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="50" t="s">
+        <v>756</v>
+      </c>
+      <c r="B264" s="53" t="s">
         <v>2153</v>
       </c>
-      <c r="E262" s="54" t="s">
+      <c r="C264" s="54" t="s">
         <v>2154</v>
       </c>
-      <c r="F262" s="54" t="s">
+      <c r="D264" s="54" t="s">
         <v>2155</v>
       </c>
-    </row>
-    <row r="263" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="50" t="s">
-        <v>833</v>
-      </c>
-      <c r="B263" s="50" t="s">
+      <c r="E264" s="54" t="s">
         <v>2156</v>
       </c>
-      <c r="C263" s="48" t="s">
-        <v>1371</v>
-      </c>
-      <c r="D263" s="51" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="264" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="50" t="s">
-        <v>833</v>
-      </c>
-      <c r="B264" s="50" t="s">
+      <c r="F264" s="54" t="s">
         <v>2157</v>
-      </c>
-      <c r="C264" s="8" t="s">
-        <v>2158</v>
-      </c>
-      <c r="D264" s="8" t="s">
-        <v>2159</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27348,97 +27354,97 @@
         <v>833</v>
       </c>
       <c r="B265" s="50" t="s">
+        <v>2158</v>
+      </c>
+      <c r="C265" s="48" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D265" s="51" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="50" t="s">
+        <v>833</v>
+      </c>
+      <c r="B266" s="50" t="s">
+        <v>2159</v>
+      </c>
+      <c r="C266" s="8" t="s">
         <v>2160</v>
       </c>
-      <c r="C265" s="8" t="s">
-        <v>1429</v>
-      </c>
-      <c r="D265" s="8" t="s">
-        <v>1430</v>
-      </c>
-    </row>
-    <row r="266" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="50" t="s">
-        <v>1053</v>
-      </c>
-      <c r="B266" s="50" t="s">
+      <c r="D266" s="8" t="s">
         <v>2161</v>
       </c>
-      <c r="C266" s="48" t="s">
-        <v>1371</v>
-      </c>
-      <c r="D266" s="51" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="267" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="267" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="50" t="s">
-        <v>1053</v>
+        <v>833</v>
       </c>
       <c r="B267" s="50" t="s">
         <v>2162</v>
       </c>
       <c r="C267" s="8" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D267" s="8" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A268" s="50" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B268" s="50" t="s">
         <v>2163</v>
       </c>
-      <c r="D267" s="51" t="s">
+      <c r="C268" s="48" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D268" s="51" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="269" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="50" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B269" s="50" t="s">
         <v>2164</v>
       </c>
-    </row>
-    <row r="268" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="50" t="s">
+      <c r="C269" s="8" t="s">
+        <v>2165</v>
+      </c>
+      <c r="D269" s="51" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="270" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A270" s="50" t="s">
         <v>1001</v>
       </c>
-      <c r="B268" s="54" t="s">
-        <v>2165</v>
-      </c>
-      <c r="C268" s="54" t="s">
-        <v>2166</v>
-      </c>
-      <c r="D268" s="54" t="s">
+      <c r="B270" s="54" t="s">
         <v>2167</v>
       </c>
-    </row>
-    <row r="269" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="50" t="s">
+      <c r="C270" s="54" t="s">
+        <v>2168</v>
+      </c>
+      <c r="D270" s="54" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="271" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="50" t="s">
         <v>1001</v>
       </c>
-      <c r="B269" s="54" t="s">
-        <v>2168</v>
-      </c>
-      <c r="C269" s="54" t="s">
-        <v>2169</v>
-      </c>
-      <c r="D269" s="54" t="s">
+      <c r="B271" s="54" t="s">
         <v>2170</v>
       </c>
-    </row>
-    <row r="270" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="50" t="s">
-        <v>48</v>
-      </c>
-      <c r="B270" s="50" t="s">
+      <c r="C271" s="54" t="s">
         <v>2171</v>
       </c>
-      <c r="C270" s="48" t="s">
+      <c r="D271" s="54" t="s">
         <v>2172</v>
-      </c>
-      <c r="D270" s="51" t="s">
-        <v>2173</v>
-      </c>
-    </row>
-    <row r="271" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="50" t="s">
-        <v>48</v>
-      </c>
-      <c r="B271" s="50" t="s">
-        <v>2174</v>
-      </c>
-      <c r="C271" s="8" t="s">
-        <v>2175</v>
-      </c>
-      <c r="D271" s="51" t="s">
-        <v>2176</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27446,59 +27452,87 @@
         <v>48</v>
       </c>
       <c r="B272" s="50" t="s">
-        <v>2177</v>
+        <v>2173</v>
       </c>
       <c r="C272" s="48" t="s">
-        <v>1371</v>
+        <v>2174</v>
       </c>
       <c r="D272" s="51" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="273" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="273" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="50" t="s">
         <v>48</v>
       </c>
       <c r="B273" s="50" t="s">
+        <v>2176</v>
+      </c>
+      <c r="C273" s="8" t="s">
+        <v>2177</v>
+      </c>
+      <c r="D273" s="51" t="s">
         <v>2178</v>
       </c>
-      <c r="C273" s="8" t="s">
+    </row>
+    <row r="274" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="B274" s="50" t="s">
         <v>2179</v>
       </c>
-      <c r="D273" s="51" t="s">
+      <c r="C274" s="48" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D274" s="51" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="275" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="B275" s="50" t="s">
         <v>2180</v>
       </c>
-    </row>
-    <row r="274" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="50" t="s">
+      <c r="C275" s="8" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D275" s="51" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="276" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A276" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B274" s="50" t="s">
-        <v>2181</v>
-      </c>
-      <c r="C274" s="8" t="s">
-        <v>2182</v>
-      </c>
-      <c r="D274" s="8" t="s">
+      <c r="B276" s="50" t="s">
         <v>2183</v>
       </c>
-    </row>
-    <row r="275" s="74" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="74" t="s">
+      <c r="C276" s="8" t="s">
         <v>2184</v>
       </c>
-      <c r="B275" s="74" t="s">
+      <c r="D276" s="8" t="s">
         <v>2185</v>
       </c>
-      <c r="C275" s="74" t="s">
+    </row>
+    <row r="277" s="74" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A277" s="74" t="s">
         <v>2186</v>
       </c>
-      <c r="D275" s="74" t="s">
+      <c r="B277" s="74" t="s">
         <v>2187</v>
       </c>
+      <c r="C277" s="74" t="s">
+        <v>2188</v>
+      </c>
+      <c r="D277" s="74" t="s">
+        <v>2189</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F269"/>
+  <autoFilter ref="A1:F271"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -27528,7 +27562,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="87" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="B1" s="87" t="s">
         <v>1159</v>
@@ -27546,13 +27580,13 @@
         <v>9</v>
       </c>
       <c r="G1" s="87" t="s">
-        <v>2189</v>
+        <v>2191</v>
       </c>
       <c r="H1" s="87" t="s">
         <v>12</v>
       </c>
       <c r="I1" s="66" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27563,10 +27597,10 @@
         <v>1167</v>
       </c>
       <c r="C2" s="53" t="s">
-        <v>2191</v>
+        <v>2193</v>
       </c>
       <c r="D2" s="53" t="s">
-        <v>2192</v>
+        <v>2194</v>
       </c>
       <c r="E2" s="53"/>
       <c r="F2" s="53"/>
@@ -27581,10 +27615,10 @@
         <v>1225</v>
       </c>
       <c r="C3" s="53" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="D3" s="53" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="E3" s="53"/>
       <c r="F3" s="53"/>
@@ -27599,10 +27633,10 @@
         <v>229</v>
       </c>
       <c r="C4" s="53" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="D4" s="53" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="E4" s="53"/>
       <c r="F4" s="53"/>
@@ -27611,7 +27645,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="53" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
       <c r="B5" s="53" t="s">
         <v>229</v>
@@ -27629,16 +27663,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="53" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="C6" s="53" t="s">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="E6" s="53"/>
       <c r="F6" s="53"/>
@@ -27653,10 +27687,10 @@
         <v>1171</v>
       </c>
       <c r="C7" s="53" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="D7" s="53" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
@@ -27715,7 +27749,7 @@
       <c r="E11" s="53"/>
       <c r="F11" s="53"/>
       <c r="G11" s="53" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="H11" s="53"/>
     </row>
@@ -27769,10 +27803,10 @@
         <v>1167</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="E15" s="51"/>
       <c r="F15" s="51"/>
@@ -27788,10 +27822,10 @@
         <v>1225</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>2206</v>
+        <v>2208</v>
       </c>
       <c r="E16" s="51"/>
       <c r="F16" s="51"/>
@@ -27801,16 +27835,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="89" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="B17" s="53" t="s">
-        <v>2208</v>
+        <v>2210</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="D17" s="53" t="s">
-        <v>2210</v>
+        <v>2212</v>
       </c>
       <c r="E17" s="53"/>
       <c r="F17" s="53"/>
@@ -27819,16 +27853,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="89" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="B18" s="53" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="C18" s="53" t="s">
-        <v>2212</v>
+        <v>2214</v>
       </c>
       <c r="D18" s="53" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="E18" s="53"/>
       <c r="F18" s="53"/>
@@ -27837,7 +27871,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="89" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="B19" s="53"/>
       <c r="C19" s="53"/>
@@ -27854,13 +27888,13 @@
         <v>187</v>
       </c>
       <c r="B20" s="53" t="s">
-        <v>2208</v>
+        <v>2210</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="D20" s="53" t="s">
-        <v>2214</v>
+        <v>2216</v>
       </c>
       <c r="E20" s="53"/>
       <c r="F20" s="53"/>
@@ -27872,13 +27906,13 @@
         <v>187</v>
       </c>
       <c r="B21" s="53" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>2212</v>
+        <v>2214</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="E21" s="53"/>
       <c r="F21" s="53"/>
@@ -27893,10 +27927,10 @@
         <v>189</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>2216</v>
+        <v>2218</v>
       </c>
       <c r="D22" s="53" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
       <c r="E22" s="53"/>
       <c r="F22" s="53"/>
@@ -27922,13 +27956,13 @@
         <v>306</v>
       </c>
       <c r="B24" s="53" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="D24" s="53" t="s">
-        <v>2220</v>
+        <v>2222</v>
       </c>
       <c r="E24" s="53"/>
       <c r="F24" s="53"/>
@@ -27940,13 +27974,13 @@
         <v>306</v>
       </c>
       <c r="B25" s="53" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="C25" s="53" t="s">
-        <v>2222</v>
+        <v>2224</v>
       </c>
       <c r="D25" s="53" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="E25" s="53"/>
       <c r="F25" s="53"/>
@@ -27972,13 +28006,13 @@
         <v>299</v>
       </c>
       <c r="B27" s="53" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="C27" s="53" t="s">
-        <v>2224</v>
+        <v>2226</v>
       </c>
       <c r="D27" s="53" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="E27" s="53"/>
       <c r="F27" s="53"/>
@@ -27990,13 +28024,13 @@
         <v>299</v>
       </c>
       <c r="B28" s="53" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="C28" s="53" t="s">
-        <v>2226</v>
+        <v>2228</v>
       </c>
       <c r="D28" s="53" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="E28" s="53"/>
       <c r="F28" s="53"/>
@@ -28025,10 +28059,10 @@
         <v>1191</v>
       </c>
       <c r="C30" s="53" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="D30" s="53" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="E30" s="53"/>
       <c r="F30" s="53"/>
@@ -28047,10 +28081,10 @@
         <v>1192</v>
       </c>
       <c r="C31" s="53" t="s">
-        <v>2230</v>
+        <v>2232</v>
       </c>
       <c r="D31" s="53" t="s">
-        <v>2231</v>
+        <v>2233</v>
       </c>
       <c r="E31" s="53"/>
       <c r="F31" s="53"/>
@@ -28069,10 +28103,10 @@
         <v>1193</v>
       </c>
       <c r="C32" s="53" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="D32" s="53" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
       <c r="E32" s="53"/>
       <c r="F32" s="53"/>
@@ -28091,10 +28125,10 @@
         <v>1195</v>
       </c>
       <c r="C33" s="53" t="s">
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="D33" s="53" t="s">
-        <v>2235</v>
+        <v>2237</v>
       </c>
       <c r="E33" s="53"/>
       <c r="F33" s="53"/>
@@ -28113,10 +28147,10 @@
         <v>1196</v>
       </c>
       <c r="C34" s="53" t="s">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="D34" s="53" t="s">
-        <v>2237</v>
+        <v>2239</v>
       </c>
       <c r="E34" s="53"/>
       <c r="F34" s="53"/>
@@ -28132,13 +28166,13 @@
         <v>340</v>
       </c>
       <c r="B35" s="53" t="s">
-        <v>2238</v>
+        <v>2240</v>
       </c>
       <c r="C35" s="53" t="s">
-        <v>2239</v>
+        <v>2241</v>
       </c>
       <c r="D35" s="53" t="s">
-        <v>2240</v>
+        <v>2242</v>
       </c>
       <c r="E35" s="53"/>
       <c r="F35" s="53"/>
@@ -28153,13 +28187,13 @@
         <v>340</v>
       </c>
       <c r="B36" s="53" t="s">
-        <v>2241</v>
+        <v>2243</v>
       </c>
       <c r="C36" s="53" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="D36" s="53" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="E36" s="53"/>
       <c r="F36" s="53"/>
@@ -28175,10 +28209,10 @@
         <v>1262</v>
       </c>
       <c r="C37" s="53" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="D37" s="53" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="E37" s="53"/>
       <c r="F37" s="53"/>
@@ -28194,10 +28228,10 @@
         <v>1263</v>
       </c>
       <c r="C38" s="53" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="D38" s="53" t="s">
-        <v>2247</v>
+        <v>2249</v>
       </c>
       <c r="E38" s="53"/>
       <c r="F38" s="53"/>
@@ -28210,13 +28244,13 @@
         <v>340</v>
       </c>
       <c r="B39" s="53" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="C39" s="53" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="D39" s="53" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="E39" s="53"/>
       <c r="F39" s="53"/>
@@ -28229,13 +28263,13 @@
         <v>340</v>
       </c>
       <c r="B40" s="53" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
       <c r="C40" s="53" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="D40" s="53" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="E40" s="53"/>
       <c r="F40" s="53"/>
@@ -28253,7 +28287,7 @@
       <c r="E41" s="53"/>
       <c r="F41" s="53"/>
       <c r="G41" s="53" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
       <c r="H41" s="53"/>
       <c r="I41" s="66"/>
@@ -28278,13 +28312,13 @@
         <v>315</v>
       </c>
       <c r="B43" s="53" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="C43" s="48" t="s">
-        <v>2255</v>
+        <v>2257</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
       <c r="E43" s="53"/>
       <c r="F43" s="53"/>
@@ -28297,13 +28331,13 @@
         <v>315</v>
       </c>
       <c r="B44" s="53" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
       <c r="C44" s="48" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
       <c r="E44" s="53"/>
       <c r="F44" s="53"/>
@@ -28316,13 +28350,13 @@
         <v>315</v>
       </c>
       <c r="B45" s="53" t="s">
-        <v>2260</v>
+        <v>2262</v>
       </c>
       <c r="C45" s="48" t="s">
-        <v>2261</v>
+        <v>2263</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
       <c r="E45" s="53"/>
       <c r="F45" s="53"/>
@@ -28335,13 +28369,13 @@
         <v>315</v>
       </c>
       <c r="B46" s="53" t="s">
-        <v>2263</v>
+        <v>2265</v>
       </c>
       <c r="C46" s="48" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
       <c r="E46" s="53"/>
       <c r="F46" s="53"/>
@@ -28359,7 +28393,7 @@
       <c r="E47" s="53"/>
       <c r="F47" s="53"/>
       <c r="G47" s="53" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="H47" s="53"/>
       <c r="I47" s="53"/>
@@ -28372,10 +28406,10 @@
         <v>1256</v>
       </c>
       <c r="C48" s="51" t="s">
-        <v>2266</v>
+        <v>2268</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
       <c r="E48" s="53"/>
       <c r="F48" s="53"/>
@@ -28390,13 +28424,13 @@
         <v>220</v>
       </c>
       <c r="B49" s="53" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="C49" s="51" t="s">
-        <v>2269</v>
+        <v>2271</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>2270</v>
+        <v>2272</v>
       </c>
       <c r="E49" s="53"/>
       <c r="F49" s="53"/>
@@ -28411,13 +28445,13 @@
         <v>220</v>
       </c>
       <c r="B50" s="53" t="s">
-        <v>2271</v>
+        <v>2273</v>
       </c>
       <c r="C50" s="51" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>2273</v>
+        <v>2275</v>
       </c>
       <c r="E50" s="53"/>
       <c r="F50" s="53"/>
@@ -28433,10 +28467,10 @@
         <v>229</v>
       </c>
       <c r="C51" s="51" t="s">
-        <v>2274</v>
+        <v>2276</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>2275</v>
+        <v>2277</v>
       </c>
       <c r="E51" s="53"/>
       <c r="F51" s="53"/>
@@ -28454,7 +28488,7 @@
       <c r="E52" s="53"/>
       <c r="F52" s="53"/>
       <c r="G52" s="53" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="H52" s="53"/>
       <c r="I52" s="53"/>
@@ -28464,13 +28498,13 @@
         <v>226</v>
       </c>
       <c r="B53" s="53" t="s">
-        <v>2276</v>
+        <v>2278</v>
       </c>
       <c r="C53" s="51" t="s">
-        <v>2277</v>
+        <v>2279</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>2278</v>
+        <v>2280</v>
       </c>
       <c r="E53" s="53"/>
       <c r="F53" s="53"/>
@@ -28483,13 +28517,13 @@
         <v>226</v>
       </c>
       <c r="B54" s="53" t="s">
-        <v>2279</v>
+        <v>2281</v>
       </c>
       <c r="C54" s="51" t="s">
-        <v>2280</v>
+        <v>2282</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="E54" s="53"/>
       <c r="F54" s="53"/>
@@ -28502,13 +28536,13 @@
         <v>226</v>
       </c>
       <c r="B55" s="53" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
       <c r="C55" s="51" t="s">
-        <v>2283</v>
+        <v>2285</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>2284</v>
+        <v>2286</v>
       </c>
       <c r="E55" s="53"/>
       <c r="F55" s="53"/>
@@ -28521,13 +28555,13 @@
         <v>226</v>
       </c>
       <c r="B56" s="53" t="s">
-        <v>2285</v>
+        <v>2287</v>
       </c>
       <c r="C56" s="51" t="s">
-        <v>2286</v>
+        <v>2288</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>2287</v>
+        <v>2289</v>
       </c>
       <c r="E56" s="53"/>
       <c r="F56" s="53"/>
@@ -28540,13 +28574,13 @@
         <v>226</v>
       </c>
       <c r="B57" s="53" t="s">
-        <v>2288</v>
+        <v>2290</v>
       </c>
       <c r="C57" s="51" t="s">
-        <v>2289</v>
+        <v>2291</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>2289</v>
+        <v>2291</v>
       </c>
       <c r="E57" s="53"/>
       <c r="F57" s="53"/>
@@ -28559,13 +28593,13 @@
         <v>226</v>
       </c>
       <c r="B58" s="53" t="s">
-        <v>2290</v>
+        <v>2292</v>
       </c>
       <c r="C58" s="51" t="s">
-        <v>2291</v>
+        <v>2293</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>2292</v>
+        <v>2294</v>
       </c>
       <c r="E58" s="53"/>
       <c r="F58" s="53"/>
@@ -28578,13 +28612,13 @@
         <v>226</v>
       </c>
       <c r="B59" s="53" t="s">
-        <v>2293</v>
+        <v>2295</v>
       </c>
       <c r="C59" s="51" t="s">
-        <v>2294</v>
+        <v>2296</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="E59" s="53"/>
       <c r="F59" s="53"/>
@@ -28597,13 +28631,13 @@
         <v>226</v>
       </c>
       <c r="B60" s="53" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>2297</v>
+        <v>2299</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>2298</v>
+        <v>2300</v>
       </c>
       <c r="E60" s="53"/>
       <c r="F60" s="53"/>
@@ -28631,13 +28665,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="53" t="s">
-        <v>2299</v>
+        <v>2301</v>
       </c>
       <c r="C62" s="51" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>2301</v>
+        <v>2303</v>
       </c>
       <c r="E62" s="53"/>
       <c r="F62" s="53"/>
@@ -28655,7 +28689,7 @@
       <c r="E63" s="53"/>
       <c r="F63" s="53"/>
       <c r="G63" s="53" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="H63" s="53"/>
       <c r="I63" s="53"/>
@@ -28668,10 +28702,10 @@
         <v>1167</v>
       </c>
       <c r="C64" s="51" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>2303</v>
+        <v>2305</v>
       </c>
       <c r="E64" s="53"/>
       <c r="F64" s="53"/>
@@ -28687,14 +28721,14 @@
         <v>1199</v>
       </c>
       <c r="C65" s="53" t="s">
-        <v>2304</v>
+        <v>2306</v>
       </c>
       <c r="D65" s="53" t="s">
-        <v>2305</v>
+        <v>2307</v>
       </c>
       <c r="E65" s="53"/>
       <c r="F65" s="53" t="s">
-        <v>2306</v>
+        <v>2308</v>
       </c>
       <c r="G65" s="53"/>
       <c r="H65" s="53"/>
@@ -28708,14 +28742,14 @@
         <v>1200</v>
       </c>
       <c r="C66" s="53" t="s">
-        <v>2307</v>
+        <v>2309</v>
       </c>
       <c r="D66" s="53" t="s">
-        <v>2308</v>
+        <v>2310</v>
       </c>
       <c r="E66" s="53"/>
       <c r="F66" s="53" t="s">
-        <v>2309</v>
+        <v>2311</v>
       </c>
       <c r="G66" s="53"/>
       <c r="H66" s="53"/>
@@ -28726,17 +28760,17 @@
         <v>322</v>
       </c>
       <c r="B67" s="53" t="s">
-        <v>2310</v>
+        <v>2312</v>
       </c>
       <c r="C67" s="53" t="s">
-        <v>2311</v>
+        <v>2313</v>
       </c>
       <c r="D67" s="53" t="s">
-        <v>2312</v>
+        <v>2314</v>
       </c>
       <c r="E67" s="53"/>
       <c r="F67" s="53" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
       <c r="G67" s="53"/>
       <c r="H67" s="53"/>
@@ -28750,14 +28784,14 @@
         <v>1201</v>
       </c>
       <c r="C68" s="53" t="s">
-        <v>2314</v>
+        <v>2316</v>
       </c>
       <c r="D68" s="53" t="s">
-        <v>2315</v>
+        <v>2317</v>
       </c>
       <c r="E68" s="53"/>
       <c r="F68" s="53" t="s">
-        <v>2316</v>
+        <v>2318</v>
       </c>
       <c r="G68" s="53"/>
       <c r="H68" s="53"/>
@@ -28771,14 +28805,14 @@
         <v>1215</v>
       </c>
       <c r="C69" s="53" t="s">
-        <v>2317</v>
+        <v>2319</v>
       </c>
       <c r="D69" s="53" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="E69" s="53"/>
       <c r="F69" s="53" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
       <c r="G69" s="53"/>
       <c r="H69" s="53"/>
@@ -28789,13 +28823,13 @@
         <v>905</v>
       </c>
       <c r="B70" s="66" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="C70" s="66" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
       <c r="D70" s="66" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28803,13 +28837,13 @@
         <v>905</v>
       </c>
       <c r="B71" s="66" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
       <c r="C71" s="66" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="D71" s="66" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28817,13 +28851,13 @@
         <v>905</v>
       </c>
       <c r="B72" s="66" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="C72" s="66" t="s">
-        <v>2327</v>
+        <v>2329</v>
       </c>
       <c r="D72" s="66" t="s">
-        <v>2328</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="73" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28831,13 +28865,13 @@
         <v>905</v>
       </c>
       <c r="B73" s="66" t="s">
-        <v>2329</v>
+        <v>2331</v>
       </c>
       <c r="C73" s="66" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
       <c r="D73" s="66" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
       <c r="E73" s="66"/>
       <c r="F73" s="66"/>
@@ -28850,13 +28884,13 @@
         <v>1079</v>
       </c>
       <c r="B74" s="53" t="s">
-        <v>2332</v>
+        <v>2334</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>2333</v>
+        <v>2335</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="E74" s="51"/>
       <c r="F74" s="51"/>
@@ -28869,13 +28903,13 @@
         <v>1079</v>
       </c>
       <c r="B75" s="53" t="s">
-        <v>2335</v>
+        <v>2337</v>
       </c>
       <c r="C75" s="51" t="s">
-        <v>2336</v>
+        <v>2338</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>2337</v>
+        <v>2339</v>
       </c>
       <c r="E75" s="51"/>
       <c r="F75" s="51"/>
@@ -28888,13 +28922,13 @@
         <v>1079</v>
       </c>
       <c r="B76" s="53" t="s">
-        <v>2338</v>
+        <v>2340</v>
       </c>
       <c r="C76" s="51" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>2340</v>
+        <v>2342</v>
       </c>
       <c r="E76" s="51"/>
       <c r="F76" s="51"/>
@@ -28907,13 +28941,13 @@
         <v>1079</v>
       </c>
       <c r="B77" s="53" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="C77" s="51" t="s">
-        <v>2342</v>
+        <v>2344</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="E77" s="51"/>
       <c r="F77" s="51"/>
@@ -28926,13 +28960,13 @@
         <v>1079</v>
       </c>
       <c r="B78" s="53" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
       <c r="C78" s="51" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>2346</v>
+        <v>2348</v>
       </c>
       <c r="E78" s="51"/>
       <c r="F78" s="51"/>
@@ -28945,13 +28979,13 @@
         <v>1079</v>
       </c>
       <c r="B79" s="53" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="C79" s="51" t="s">
-        <v>2348</v>
+        <v>2350</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="E79" s="51"/>
       <c r="F79" s="51"/>
@@ -28964,13 +28998,13 @@
         <v>1079</v>
       </c>
       <c r="B80" s="53" t="s">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="C80" s="51" t="s">
-        <v>2351</v>
+        <v>2353</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="E80" s="51"/>
       <c r="F80" s="51"/>
@@ -28983,13 +29017,13 @@
         <v>1079</v>
       </c>
       <c r="B81" s="53" t="s">
-        <v>2353</v>
+        <v>2355</v>
       </c>
       <c r="C81" s="51" t="s">
-        <v>2354</v>
+        <v>2356</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>2355</v>
+        <v>2357</v>
       </c>
       <c r="E81" s="51"/>
       <c r="F81" s="51"/>
@@ -29002,13 +29036,13 @@
         <v>1079</v>
       </c>
       <c r="B82" s="53" t="s">
-        <v>2356</v>
+        <v>2358</v>
       </c>
       <c r="C82" s="51" t="s">
-        <v>2357</v>
+        <v>2359</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="E82" s="51"/>
       <c r="F82" s="51"/>
@@ -29021,13 +29055,13 @@
         <v>1079</v>
       </c>
       <c r="B83" s="53" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="C83" s="51" t="s">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="E83" s="51"/>
       <c r="F83" s="51"/>
@@ -29040,13 +29074,13 @@
         <v>1079</v>
       </c>
       <c r="B84" s="53" t="s">
-        <v>2359</v>
+        <v>2361</v>
       </c>
       <c r="C84" s="51" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>2360</v>
+        <v>2362</v>
       </c>
       <c r="E84" s="51"/>
       <c r="F84" s="51"/>
@@ -29059,13 +29093,13 @@
         <v>99</v>
       </c>
       <c r="B85" s="66" t="s">
-        <v>2361</v>
+        <v>2363</v>
       </c>
       <c r="C85" s="66" t="s">
-        <v>2362</v>
+        <v>2364</v>
       </c>
       <c r="D85" s="66" t="s">
-        <v>2363</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29073,13 +29107,13 @@
         <v>99</v>
       </c>
       <c r="B86" s="66" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
       <c r="C86" s="66" t="s">
-        <v>2365</v>
+        <v>2367</v>
       </c>
       <c r="D86" s="66" t="s">
-        <v>2366</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29104,10 +29138,10 @@
         <v>1171</v>
       </c>
       <c r="C88" s="66" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="D88" s="66" t="s">
-        <v>2360</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29115,13 +29149,13 @@
         <v>423</v>
       </c>
       <c r="B89" s="53" t="s">
-        <v>2367</v>
+        <v>2369</v>
       </c>
       <c r="C89" s="51" t="s">
-        <v>2368</v>
+        <v>2370</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>2369</v>
+        <v>2371</v>
       </c>
       <c r="E89" s="51"/>
       <c r="F89" s="51"/>
@@ -29136,13 +29170,13 @@
         <v>423</v>
       </c>
       <c r="B90" s="53" t="s">
-        <v>2370</v>
+        <v>2372</v>
       </c>
       <c r="C90" s="51" t="s">
-        <v>2371</v>
+        <v>2373</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>2372</v>
+        <v>2374</v>
       </c>
       <c r="E90" s="51"/>
       <c r="F90" s="51"/>
@@ -29157,13 +29191,13 @@
         <v>423</v>
       </c>
       <c r="B91" s="53" t="s">
-        <v>2373</v>
+        <v>2375</v>
       </c>
       <c r="C91" s="51" t="s">
-        <v>2374</v>
+        <v>2376</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>2375</v>
+        <v>2377</v>
       </c>
       <c r="E91" s="51"/>
       <c r="F91" s="51"/>
@@ -29176,13 +29210,13 @@
         <v>423</v>
       </c>
       <c r="B92" s="53" t="s">
-        <v>2376</v>
+        <v>2378</v>
       </c>
       <c r="C92" s="51" t="s">
-        <v>2377</v>
+        <v>2379</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>2378</v>
+        <v>2380</v>
       </c>
       <c r="E92" s="51"/>
       <c r="F92" s="51"/>
@@ -29195,13 +29229,13 @@
         <v>423</v>
       </c>
       <c r="B93" s="53" t="s">
-        <v>2379</v>
+        <v>2381</v>
       </c>
       <c r="C93" s="51" t="s">
-        <v>2380</v>
+        <v>2382</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>2381</v>
+        <v>2383</v>
       </c>
       <c r="E93" s="51"/>
       <c r="F93" s="51"/>
@@ -29217,10 +29251,10 @@
         <v>1232</v>
       </c>
       <c r="C94" s="51" t="s">
-        <v>2382</v>
+        <v>2384</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>2383</v>
+        <v>2385</v>
       </c>
       <c r="E94" s="51"/>
       <c r="F94" s="51"/>
@@ -29238,10 +29272,10 @@
         <v>1233</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>2385</v>
+        <v>2387</v>
       </c>
       <c r="E95" s="51"/>
       <c r="F95" s="51"/>
@@ -29254,13 +29288,13 @@
         <v>423</v>
       </c>
       <c r="B96" s="53" t="s">
-        <v>2386</v>
+        <v>2388</v>
       </c>
       <c r="C96" s="51" t="s">
-        <v>2387</v>
+        <v>2389</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>2388</v>
+        <v>2390</v>
       </c>
       <c r="E96" s="51"/>
       <c r="F96" s="51"/>
@@ -29291,10 +29325,10 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="93" t="s">
-        <v>2389</v>
+        <v>2391</v>
       </c>
       <c r="B98" s="66" t="s">
-        <v>2390</v>
+        <v>2392</v>
       </c>
       <c r="C98" s="66" t="s">
         <v>1752</v>
@@ -29311,10 +29345,10 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="93" t="s">
-        <v>2389</v>
+        <v>2391</v>
       </c>
       <c r="B99" s="66" t="s">
-        <v>2391</v>
+        <v>2393</v>
       </c>
       <c r="C99" s="66" t="s">
         <v>1757</v>
@@ -29331,16 +29365,16 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="93" t="s">
-        <v>2389</v>
+        <v>2391</v>
       </c>
       <c r="B100" s="66" t="s">
         <v>1225</v>
       </c>
       <c r="C100" s="66" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="D100" s="66" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29348,13 +29382,13 @@
         <v>771</v>
       </c>
       <c r="B101" s="66" t="s">
-        <v>2392</v>
+        <v>2394</v>
       </c>
       <c r="C101" s="66" t="s">
-        <v>2393</v>
+        <v>2395</v>
       </c>
       <c r="D101" s="66" t="s">
-        <v>2394</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29362,13 +29396,13 @@
         <v>771</v>
       </c>
       <c r="B102" s="66" t="s">
-        <v>2395</v>
+        <v>2397</v>
       </c>
       <c r="C102" s="66" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="D102" s="66" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
       <c r="I102" s="90" t="n">
         <f aca="false">TRUE()</f>
@@ -29380,13 +29414,13 @@
         <v>771</v>
       </c>
       <c r="B103" s="66" t="s">
-        <v>2398</v>
+        <v>2400</v>
       </c>
       <c r="C103" s="66" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="D103" s="66" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29394,13 +29428,13 @@
         <v>771</v>
       </c>
       <c r="B104" s="66" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
       <c r="C104" s="66" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
       <c r="D104" s="66" t="s">
-        <v>2403</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29408,7 +29442,7 @@
         <v>771</v>
       </c>
       <c r="G105" s="53" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29416,7 +29450,7 @@
         <v>771</v>
       </c>
       <c r="G106" s="53" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29424,13 +29458,13 @@
         <v>829</v>
       </c>
       <c r="B107" s="66" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
       <c r="C107" s="66" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
       <c r="D107" s="66" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29438,13 +29472,13 @@
         <v>829</v>
       </c>
       <c r="B108" s="66" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
       <c r="C108" s="66" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="D108" s="66" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29452,13 +29486,13 @@
         <v>829</v>
       </c>
       <c r="B109" s="66" t="s">
-        <v>2398</v>
+        <v>2400</v>
       </c>
       <c r="C109" s="66" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="D109" s="66" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29466,13 +29500,13 @@
         <v>829</v>
       </c>
       <c r="B110" s="53" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="C110" s="51" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
       <c r="D110" s="48" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
       <c r="I110" s="90" t="n">
         <f aca="false">TRUE()</f>
@@ -29484,7 +29518,7 @@
         <v>829</v>
       </c>
       <c r="G111" s="53" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29492,7 +29526,7 @@
         <v>829</v>
       </c>
       <c r="G112" s="53" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29500,13 +29534,13 @@
         <v>347</v>
       </c>
       <c r="B113" s="66" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="C113" s="66" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
       <c r="D113" s="66" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29514,13 +29548,13 @@
         <v>347</v>
       </c>
       <c r="B114" s="66" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="C114" s="66" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="D114" s="66" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29528,13 +29562,13 @@
         <v>347</v>
       </c>
       <c r="B115" s="66" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="C115" s="66" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="D115" s="66" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29547,103 +29581,103 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="89" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="B117" s="53" t="s">
         <v>1199</v>
       </c>
       <c r="C117" s="53" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="D117" s="53" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="E117" s="53" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="F117" s="53" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="G117" s="89"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="89" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="B118" s="53" t="s">
         <v>1200</v>
       </c>
       <c r="C118" s="53" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="D118" s="53" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="E118" s="53" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="F118" s="53" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="89" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="B119" s="53" t="s">
         <v>1201</v>
       </c>
       <c r="C119" s="53" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="D119" s="53" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="E119" s="53" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="F119" s="53" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="89" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="B120" s="53" t="s">
         <v>1215</v>
       </c>
       <c r="C120" s="53" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
       <c r="D120" s="53" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
       <c r="E120" s="53" t="s">
-        <v>2439</v>
+        <v>2441</v>
       </c>
       <c r="F120" s="53" t="s">
-        <v>2440</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="89" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="B121" s="53" t="s">
-        <v>2310</v>
+        <v>2312</v>
       </c>
       <c r="C121" s="53" t="s">
-        <v>2441</v>
+        <v>2443</v>
       </c>
       <c r="D121" s="53" t="s">
-        <v>2442</v>
+        <v>2444</v>
       </c>
       <c r="E121" s="53" t="s">
-        <v>2443</v>
+        <v>2445</v>
       </c>
       <c r="F121" s="53" t="s">
-        <v>2444</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29651,7 +29685,7 @@
         <v>698</v>
       </c>
       <c r="B122" s="66" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>1923</v>
@@ -29668,10 +29702,10 @@
         <v>1237</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
       <c r="D123" s="57" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
       <c r="H123" s="95" t="s">
         <v>1235</v>
@@ -29682,16 +29716,16 @@
         <v>698</v>
       </c>
       <c r="B124" s="66" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
       <c r="D124" s="57" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="H124" s="96" t="s">
-        <v>2450</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29699,7 +29733,7 @@
         <v>698</v>
       </c>
       <c r="B125" s="66" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>1940</v>
@@ -29716,7 +29750,7 @@
         <v>698</v>
       </c>
       <c r="B126" s="66" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="C126" s="8" t="s">
         <v>1937</v>
@@ -29740,7 +29774,7 @@
         <v>704</v>
       </c>
       <c r="B128" s="66" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>1923</v>
@@ -29754,7 +29788,7 @@
         <v>704</v>
       </c>
       <c r="B129" s="66" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>1926</v>
@@ -29768,7 +29802,7 @@
         <v>704</v>
       </c>
       <c r="B130" s="66" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="C130" s="8" t="s">
         <v>1940</v>
@@ -29785,7 +29819,7 @@
         <v>704</v>
       </c>
       <c r="B131" s="66" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="C131" s="8" t="s">
         <v>1937</v>
@@ -29799,13 +29833,13 @@
         <v>704</v>
       </c>
       <c r="B132" s="66" t="s">
-        <v>2454</v>
+        <v>2456</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>2455</v>
+        <v>2457</v>
       </c>
       <c r="D132" s="57" t="s">
-        <v>2456</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29813,7 +29847,7 @@
         <v>704</v>
       </c>
       <c r="B133" s="66" t="s">
-        <v>2457</v>
+        <v>2459</v>
       </c>
       <c r="C133" s="8" t="s">
         <v>2055</v>
@@ -29829,7 +29863,7 @@
       <c r="C134" s="57"/>
       <c r="D134" s="57"/>
       <c r="G134" s="53" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29837,16 +29871,16 @@
         <v>594</v>
       </c>
       <c r="B135" s="66" t="s">
-        <v>2458</v>
+        <v>2460</v>
       </c>
       <c r="C135" s="57" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="D135" s="57" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
       <c r="H135" s="54" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29857,13 +29891,13 @@
         <v>1225</v>
       </c>
       <c r="C136" s="57" t="s">
-        <v>2462</v>
+        <v>2464</v>
       </c>
       <c r="D136" s="57" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="H136" s="8" t="s">
-        <v>2464</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29874,10 +29908,10 @@
         <v>1167</v>
       </c>
       <c r="C137" s="57" t="s">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="D137" s="57" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29885,13 +29919,13 @@
         <v>594</v>
       </c>
       <c r="B138" s="66" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="C138" s="57" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="D138" s="57" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29901,7 +29935,7 @@
       <c r="C139" s="57"/>
       <c r="D139" s="57"/>
       <c r="G139" s="66" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29909,13 +29943,13 @@
         <v>627</v>
       </c>
       <c r="B140" s="66" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="C140" s="57" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
       <c r="D140" s="57" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29923,13 +29957,13 @@
         <v>627</v>
       </c>
       <c r="B141" s="66" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="C141" s="57" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="D141" s="57" t="s">
-        <v>2474</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29939,7 +29973,7 @@
       <c r="C142" s="57"/>
       <c r="D142" s="57"/>
       <c r="G142" s="66" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29947,13 +29981,13 @@
         <v>651</v>
       </c>
       <c r="B143" s="66" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>2476</v>
+        <v>2478</v>
       </c>
       <c r="D143" s="57" t="s">
-        <v>2477</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29961,13 +29995,13 @@
         <v>651</v>
       </c>
       <c r="B144" s="66" t="s">
-        <v>2478</v>
+        <v>2480</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>2479</v>
+        <v>2481</v>
       </c>
       <c r="D144" s="57" t="s">
-        <v>2480</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29977,7 +30011,7 @@
       <c r="C145" s="57"/>
       <c r="D145" s="57"/>
       <c r="G145" s="53" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29987,7 +30021,7 @@
       <c r="C146" s="57"/>
       <c r="D146" s="57"/>
       <c r="G146" s="66" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29995,13 +30029,13 @@
         <v>658</v>
       </c>
       <c r="B147" s="66" t="s">
-        <v>2481</v>
+        <v>2483</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>2482</v>
+        <v>2484</v>
       </c>
       <c r="D147" s="57" t="s">
-        <v>2483</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30009,13 +30043,13 @@
         <v>658</v>
       </c>
       <c r="B148" s="66" t="s">
-        <v>2484</v>
+        <v>2486</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>2485</v>
+        <v>2487</v>
       </c>
       <c r="D148" s="57" t="s">
-        <v>2485</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30023,13 +30057,13 @@
         <v>658</v>
       </c>
       <c r="B149" s="66" t="s">
-        <v>2486</v>
+        <v>2488</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>2487</v>
+        <v>2489</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>2487</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30037,13 +30071,13 @@
         <v>658</v>
       </c>
       <c r="B150" s="66" t="s">
-        <v>2488</v>
+        <v>2490</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30053,7 +30087,7 @@
       <c r="C151" s="57"/>
       <c r="D151" s="57"/>
       <c r="G151" s="53" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30063,7 +30097,7 @@
       <c r="C152" s="57"/>
       <c r="D152" s="57"/>
       <c r="G152" s="66" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30071,13 +30105,13 @@
         <v>663</v>
       </c>
       <c r="B153" s="66" t="s">
-        <v>2490</v>
+        <v>2492</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="D153" s="57" t="s">
-        <v>2492</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30085,13 +30119,13 @@
         <v>663</v>
       </c>
       <c r="B154" s="66" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>2494</v>
+        <v>2496</v>
       </c>
       <c r="D154" s="57" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30099,13 +30133,13 @@
         <v>663</v>
       </c>
       <c r="B155" s="66" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="D155" s="57" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30113,13 +30147,13 @@
         <v>663</v>
       </c>
       <c r="B156" s="66" t="s">
-        <v>2498</v>
+        <v>2500</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30127,13 +30161,13 @@
         <v>663</v>
       </c>
       <c r="B157" s="66" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>2501</v>
+        <v>2503</v>
       </c>
       <c r="D157" s="57" t="s">
-        <v>2502</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30143,7 +30177,7 @@
       <c r="C158" s="57"/>
       <c r="D158" s="57"/>
       <c r="G158" s="53" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30153,7 +30187,7 @@
       <c r="C159" s="57"/>
       <c r="D159" s="57"/>
       <c r="G159" s="66" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30161,7 +30195,7 @@
         <v>793</v>
       </c>
       <c r="B160" s="53" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="C160" s="66" t="s">
         <v>1994</v>
@@ -30180,7 +30214,7 @@
         <v>793</v>
       </c>
       <c r="B161" s="53" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="C161" s="66" t="s">
         <v>2012</v>
@@ -30199,13 +30233,13 @@
         <v>793</v>
       </c>
       <c r="B162" s="53" t="s">
-        <v>2457</v>
+        <v>2459</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D162" s="57" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="E162" s="53"/>
       <c r="F162" s="53"/>
@@ -30218,7 +30252,7 @@
         <v>793</v>
       </c>
       <c r="B163" s="53" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="C163" s="8" t="s">
         <v>1947</v>
@@ -30237,7 +30271,7 @@
         <v>793</v>
       </c>
       <c r="B164" s="53" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="C164" s="8" t="s">
         <v>1950</v>
@@ -30259,10 +30293,10 @@
         <v>229</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="E165" s="53"/>
       <c r="F165" s="53"/>
@@ -30277,13 +30311,13 @@
         <v>793</v>
       </c>
       <c r="B166" s="53" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="C166" s="51" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="D166" s="8" t="s">
-        <v>2510</v>
+        <v>2512</v>
       </c>
       <c r="E166" s="53"/>
       <c r="F166" s="53"/>
@@ -30298,13 +30332,13 @@
         <v>141</v>
       </c>
       <c r="B167" s="53" t="s">
-        <v>2511</v>
+        <v>2513</v>
       </c>
       <c r="C167" s="51" t="s">
-        <v>2512</v>
+        <v>2514</v>
       </c>
       <c r="D167" s="8" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
       <c r="E167" s="53"/>
       <c r="F167" s="53"/>
@@ -30317,13 +30351,13 @@
         <v>141</v>
       </c>
       <c r="B168" s="53" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
       <c r="C168" s="51" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
       <c r="D168" s="8" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="E168" s="53"/>
       <c r="F168" s="53"/>
@@ -30339,10 +30373,10 @@
         <v>1167</v>
       </c>
       <c r="C169" s="51" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="E169" s="53"/>
       <c r="F169" s="53"/>
@@ -30358,10 +30392,10 @@
         <v>1225</v>
       </c>
       <c r="C170" s="51" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="D170" s="8" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
       <c r="E170" s="53"/>
       <c r="F170" s="53"/>
@@ -30379,7 +30413,7 @@
       <c r="E171" s="53"/>
       <c r="F171" s="53"/>
       <c r="G171" s="53" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="H171" s="53"/>
       <c r="I171" s="53"/>
@@ -30389,13 +30423,13 @@
         <v>246</v>
       </c>
       <c r="B172" s="53" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="C172" s="48" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="D172" s="8" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="E172" s="53"/>
       <c r="F172" s="53"/>
@@ -30410,13 +30444,13 @@
         <v>246</v>
       </c>
       <c r="B173" s="53" t="s">
-        <v>2524</v>
+        <v>2526</v>
       </c>
       <c r="C173" s="48" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
       <c r="E173" s="53"/>
       <c r="F173" s="53"/>
@@ -30431,13 +30465,13 @@
         <v>246</v>
       </c>
       <c r="B174" s="53" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
       <c r="C174" s="48" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>2529</v>
+        <v>2531</v>
       </c>
       <c r="E174" s="53"/>
       <c r="F174" s="53"/>
@@ -30452,13 +30486,13 @@
         <v>246</v>
       </c>
       <c r="B175" s="53" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
       <c r="C175" s="48" t="s">
-        <v>2531</v>
+        <v>2533</v>
       </c>
       <c r="D175" s="8" t="s">
-        <v>2532</v>
+        <v>2534</v>
       </c>
       <c r="E175" s="53"/>
       <c r="F175" s="53"/>
@@ -30473,13 +30507,13 @@
         <v>246</v>
       </c>
       <c r="B176" s="53" t="s">
-        <v>2533</v>
+        <v>2535</v>
       </c>
       <c r="C176" s="48" t="s">
-        <v>2534</v>
+        <v>2536</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>2535</v>
+        <v>2537</v>
       </c>
       <c r="E176" s="53"/>
       <c r="F176" s="53"/>
@@ -30494,13 +30528,13 @@
         <v>246</v>
       </c>
       <c r="B177" s="53" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
       <c r="C177" s="48" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
       <c r="E177" s="53"/>
       <c r="F177" s="53"/>
@@ -30515,13 +30549,13 @@
         <v>246</v>
       </c>
       <c r="B178" s="53" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
       <c r="C178" s="48" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="D178" s="8" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
       <c r="E178" s="53"/>
       <c r="F178" s="53"/>
@@ -30536,13 +30570,13 @@
         <v>246</v>
       </c>
       <c r="B179" s="53" t="s">
-        <v>2542</v>
+        <v>2544</v>
       </c>
       <c r="C179" s="48" t="s">
-        <v>2543</v>
+        <v>2545</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
       <c r="E179" s="53"/>
       <c r="F179" s="53"/>
@@ -30557,13 +30591,13 @@
         <v>246</v>
       </c>
       <c r="B180" s="53" t="s">
-        <v>2545</v>
+        <v>2547</v>
       </c>
       <c r="C180" s="48" t="s">
-        <v>2546</v>
+        <v>2548</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>2547</v>
+        <v>2549</v>
       </c>
       <c r="E180" s="53"/>
       <c r="F180" s="53"/>
@@ -30581,10 +30615,10 @@
         <v>229</v>
       </c>
       <c r="C181" s="48" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="E181" s="53"/>
       <c r="F181" s="53"/>
@@ -30614,13 +30648,13 @@
         <v>258</v>
       </c>
       <c r="B183" s="53" t="s">
-        <v>2548</v>
+        <v>2550</v>
       </c>
       <c r="C183" s="48" t="s">
-        <v>2549</v>
+        <v>2551</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>2550</v>
+        <v>2552</v>
       </c>
       <c r="E183" s="53"/>
       <c r="F183" s="53"/>
@@ -30635,13 +30669,13 @@
         <v>258</v>
       </c>
       <c r="B184" s="53" t="s">
-        <v>2551</v>
+        <v>2553</v>
       </c>
       <c r="C184" s="48" t="s">
-        <v>2552</v>
+        <v>2554</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>2553</v>
+        <v>2555</v>
       </c>
       <c r="E184" s="53"/>
       <c r="F184" s="53"/>
@@ -30656,13 +30690,13 @@
         <v>258</v>
       </c>
       <c r="B185" s="53" t="s">
-        <v>2554</v>
+        <v>2556</v>
       </c>
       <c r="C185" s="48" t="s">
-        <v>2555</v>
+        <v>2557</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>2556</v>
+        <v>2558</v>
       </c>
       <c r="E185" s="53"/>
       <c r="F185" s="53"/>
@@ -30677,13 +30711,13 @@
         <v>258</v>
       </c>
       <c r="B186" s="53" t="s">
-        <v>2557</v>
+        <v>2559</v>
       </c>
       <c r="C186" s="48" t="s">
-        <v>2558</v>
+        <v>2560</v>
       </c>
       <c r="D186" s="8" t="s">
-        <v>2559</v>
+        <v>2561</v>
       </c>
       <c r="E186" s="53"/>
       <c r="F186" s="53"/>
@@ -30698,13 +30732,13 @@
         <v>258</v>
       </c>
       <c r="B187" s="53" t="s">
-        <v>2560</v>
+        <v>2562</v>
       </c>
       <c r="C187" s="48" t="s">
-        <v>2561</v>
+        <v>2563</v>
       </c>
       <c r="D187" s="8" t="s">
-        <v>2562</v>
+        <v>2564</v>
       </c>
       <c r="E187" s="53"/>
       <c r="F187" s="53"/>
@@ -30719,13 +30753,13 @@
         <v>258</v>
       </c>
       <c r="B188" s="53" t="s">
-        <v>2563</v>
+        <v>2565</v>
       </c>
       <c r="C188" s="48" t="s">
-        <v>2564</v>
+        <v>2566</v>
       </c>
       <c r="D188" s="8" t="s">
-        <v>2565</v>
+        <v>2567</v>
       </c>
       <c r="E188" s="53"/>
       <c r="F188" s="53"/>
@@ -30740,13 +30774,13 @@
         <v>258</v>
       </c>
       <c r="B189" s="53" t="s">
-        <v>2566</v>
+        <v>2568</v>
       </c>
       <c r="C189" s="48" t="s">
-        <v>2567</v>
+        <v>2569</v>
       </c>
       <c r="D189" s="8" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="E189" s="53"/>
       <c r="F189" s="53"/>
@@ -30764,10 +30798,10 @@
         <v>1207</v>
       </c>
       <c r="C190" s="48" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="E190" s="53"/>
       <c r="F190" s="53"/>
@@ -30784,10 +30818,10 @@
         <v>229</v>
       </c>
       <c r="C191" s="48" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="E191" s="53"/>
       <c r="F191" s="53"/>
@@ -30805,10 +30839,10 @@
         <v>1171</v>
       </c>
       <c r="C192" s="53" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="D192" s="53" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="E192" s="53"/>
       <c r="F192" s="53"/>
@@ -30822,13 +30856,13 @@
         <v>287</v>
       </c>
       <c r="B193" s="53" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="C193" s="48" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="D193" s="8" t="s">
-        <v>2573</v>
+        <v>2575</v>
       </c>
       <c r="E193" s="53"/>
       <c r="F193" s="53"/>
@@ -30841,13 +30875,13 @@
         <v>287</v>
       </c>
       <c r="B194" s="53" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="C194" s="48" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>2576</v>
+        <v>2578</v>
       </c>
       <c r="E194" s="53"/>
       <c r="F194" s="53"/>
@@ -30860,13 +30894,13 @@
         <v>287</v>
       </c>
       <c r="B195" s="53" t="s">
-        <v>2577</v>
+        <v>2579</v>
       </c>
       <c r="C195" s="48" t="s">
-        <v>2578</v>
+        <v>2580</v>
       </c>
       <c r="D195" s="8" t="s">
-        <v>2579</v>
+        <v>2581</v>
       </c>
       <c r="E195" s="53"/>
       <c r="F195" s="53"/>
@@ -30879,13 +30913,13 @@
         <v>287</v>
       </c>
       <c r="B196" s="53" t="s">
-        <v>2580</v>
+        <v>2582</v>
       </c>
       <c r="C196" s="48" t="s">
-        <v>2581</v>
+        <v>2583</v>
       </c>
       <c r="D196" s="8" t="s">
-        <v>2582</v>
+        <v>2584</v>
       </c>
       <c r="E196" s="53"/>
       <c r="F196" s="53"/>
@@ -30898,13 +30932,13 @@
         <v>287</v>
       </c>
       <c r="B197" s="53" t="s">
-        <v>2583</v>
+        <v>2585</v>
       </c>
       <c r="C197" s="48" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
       <c r="E197" s="53"/>
       <c r="F197" s="53"/>
@@ -30917,13 +30951,13 @@
         <v>294</v>
       </c>
       <c r="B198" s="53" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="C198" s="48" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>2573</v>
+        <v>2575</v>
       </c>
       <c r="E198" s="53"/>
       <c r="F198" s="53"/>
@@ -30938,13 +30972,13 @@
         <v>294</v>
       </c>
       <c r="B199" s="53" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="C199" s="48" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="D199" s="8" t="s">
-        <v>2576</v>
+        <v>2578</v>
       </c>
       <c r="E199" s="53"/>
       <c r="F199" s="53"/>
@@ -30957,13 +30991,13 @@
         <v>294</v>
       </c>
       <c r="B200" s="53" t="s">
-        <v>2577</v>
+        <v>2579</v>
       </c>
       <c r="C200" s="48" t="s">
-        <v>2578</v>
+        <v>2580</v>
       </c>
       <c r="D200" s="8" t="s">
-        <v>2579</v>
+        <v>2581</v>
       </c>
       <c r="E200" s="53"/>
       <c r="F200" s="53"/>
@@ -30976,13 +31010,13 @@
         <v>294</v>
       </c>
       <c r="B201" s="53" t="s">
-        <v>2580</v>
+        <v>2582</v>
       </c>
       <c r="C201" s="48" t="s">
-        <v>2581</v>
+        <v>2583</v>
       </c>
       <c r="D201" s="8" t="s">
-        <v>2582</v>
+        <v>2584</v>
       </c>
       <c r="E201" s="53"/>
       <c r="F201" s="53"/>
@@ -30995,13 +31029,13 @@
         <v>294</v>
       </c>
       <c r="B202" s="53" t="s">
-        <v>2583</v>
+        <v>2585</v>
       </c>
       <c r="C202" s="48" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
       <c r="D202" s="8" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
       <c r="E202" s="53"/>
       <c r="F202" s="53"/>
@@ -31014,7 +31048,7 @@
         <v>857</v>
       </c>
       <c r="B203" s="66" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="C203" s="66" t="s">
         <v>1923</v>
@@ -31028,7 +31062,7 @@
         <v>857</v>
       </c>
       <c r="B204" s="66" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
       <c r="C204" s="66" t="s">
         <v>1926</v>
@@ -31042,13 +31076,13 @@
         <v>857</v>
       </c>
       <c r="B205" s="66" t="s">
-        <v>2586</v>
+        <v>2588</v>
       </c>
       <c r="C205" s="66" t="s">
-        <v>2587</v>
+        <v>2589</v>
       </c>
       <c r="D205" s="66" t="s">
-        <v>2588</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31056,13 +31090,13 @@
         <v>857</v>
       </c>
       <c r="B206" s="66" t="s">
-        <v>2457</v>
+        <v>2459</v>
       </c>
       <c r="C206" s="66" t="s">
-        <v>2589</v>
+        <v>2591</v>
       </c>
       <c r="D206" s="66" t="s">
-        <v>2590</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31070,7 +31104,7 @@
         <v>857</v>
       </c>
       <c r="G207" s="66" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31078,13 +31112,13 @@
         <v>882</v>
       </c>
       <c r="B208" s="66" t="s">
-        <v>2591</v>
+        <v>2593</v>
       </c>
       <c r="C208" s="66" t="s">
-        <v>2592</v>
+        <v>2594</v>
       </c>
       <c r="D208" s="66" t="s">
-        <v>2593</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31092,13 +31126,13 @@
         <v>882</v>
       </c>
       <c r="B209" s="66" t="s">
-        <v>2594</v>
+        <v>2596</v>
       </c>
       <c r="C209" s="66" t="s">
-        <v>2595</v>
+        <v>2597</v>
       </c>
       <c r="D209" s="66" t="s">
-        <v>2596</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31106,13 +31140,13 @@
         <v>882</v>
       </c>
       <c r="B210" s="66" t="s">
-        <v>2597</v>
+        <v>2599</v>
       </c>
       <c r="C210" s="66" t="s">
-        <v>2598</v>
+        <v>2600</v>
       </c>
       <c r="D210" s="66" t="s">
-        <v>2599</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31120,13 +31154,13 @@
         <v>882</v>
       </c>
       <c r="B211" s="66" t="s">
-        <v>2600</v>
+        <v>2602</v>
       </c>
       <c r="C211" s="66" t="s">
-        <v>2601</v>
+        <v>2603</v>
       </c>
       <c r="D211" s="66" t="s">
-        <v>2602</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31134,13 +31168,13 @@
         <v>882</v>
       </c>
       <c r="B212" s="66" t="s">
-        <v>2603</v>
+        <v>2605</v>
       </c>
       <c r="C212" s="66" t="s">
-        <v>2604</v>
+        <v>2606</v>
       </c>
       <c r="D212" s="66" t="s">
-        <v>2605</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31148,13 +31182,13 @@
         <v>882</v>
       </c>
       <c r="B213" s="66" t="s">
-        <v>2606</v>
+        <v>2608</v>
       </c>
       <c r="C213" s="66" t="s">
-        <v>2607</v>
+        <v>2609</v>
       </c>
       <c r="D213" s="66" t="s">
-        <v>2608</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31165,10 +31199,10 @@
         <v>229</v>
       </c>
       <c r="C214" s="66" t="s">
-        <v>2609</v>
+        <v>2611</v>
       </c>
       <c r="D214" s="66" t="s">
-        <v>2610</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31176,7 +31210,7 @@
         <v>887</v>
       </c>
       <c r="B215" s="66" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="C215" s="66" t="s">
         <v>1923</v>
@@ -31190,7 +31224,7 @@
         <v>887</v>
       </c>
       <c r="B216" s="66" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
       <c r="C216" s="66" t="s">
         <v>1926</v>
@@ -31204,13 +31238,13 @@
         <v>887</v>
       </c>
       <c r="B217" s="66" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="C217" s="66" t="s">
-        <v>2611</v>
+        <v>2613</v>
       </c>
       <c r="D217" s="66" t="s">
-        <v>2612</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="218" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31218,13 +31252,13 @@
         <v>887</v>
       </c>
       <c r="B218" s="66" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="C218" s="66" t="s">
-        <v>2613</v>
+        <v>2615</v>
       </c>
       <c r="D218" s="66" t="s">
-        <v>2614</v>
+        <v>2616</v>
       </c>
       <c r="E218" s="66"/>
       <c r="F218" s="66"/>
@@ -31237,13 +31271,13 @@
         <v>887</v>
       </c>
       <c r="B219" s="66" t="s">
-        <v>2457</v>
+        <v>2459</v>
       </c>
       <c r="C219" s="66" t="s">
-        <v>2589</v>
+        <v>2591</v>
       </c>
       <c r="D219" s="66" t="s">
-        <v>2590</v>
+        <v>2592</v>
       </c>
       <c r="E219" s="66"/>
       <c r="F219" s="66"/>
@@ -31259,10 +31293,10 @@
         <v>229</v>
       </c>
       <c r="C220" s="66" t="s">
-        <v>2615</v>
+        <v>2617</v>
       </c>
       <c r="D220" s="66" t="s">
-        <v>2616</v>
+        <v>2618</v>
       </c>
       <c r="E220" s="66"/>
       <c r="F220" s="66"/>
@@ -31278,10 +31312,10 @@
         <v>1258</v>
       </c>
       <c r="C221" s="8" t="s">
-        <v>2617</v>
+        <v>2619</v>
       </c>
       <c r="D221" s="8" t="s">
-        <v>2618</v>
+        <v>2620</v>
       </c>
       <c r="E221" s="66"/>
       <c r="F221" s="66"/>
@@ -31294,13 +31328,13 @@
         <v>1052</v>
       </c>
       <c r="B222" s="66" t="s">
-        <v>2619</v>
+        <v>2621</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>2620</v>
+        <v>2622</v>
       </c>
       <c r="D222" s="8" t="s">
-        <v>2621</v>
+        <v>2623</v>
       </c>
       <c r="E222" s="66"/>
       <c r="F222" s="66"/>
@@ -31315,13 +31349,13 @@
         <v>1052</v>
       </c>
       <c r="B223" s="66" t="s">
-        <v>2622</v>
+        <v>2624</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>2623</v>
+        <v>2625</v>
       </c>
       <c r="D223" s="8" t="s">
-        <v>2624</v>
+        <v>2626</v>
       </c>
       <c r="E223" s="66"/>
       <c r="F223" s="66"/>
@@ -31336,13 +31370,13 @@
         <v>1052</v>
       </c>
       <c r="B224" s="66" t="s">
-        <v>2625</v>
+        <v>2627</v>
       </c>
       <c r="C224" s="8" t="s">
-        <v>2626</v>
+        <v>2628</v>
       </c>
       <c r="D224" s="51" t="s">
-        <v>2627</v>
+        <v>2629</v>
       </c>
       <c r="E224" s="66"/>
       <c r="F224" s="66"/>
@@ -31357,13 +31391,13 @@
         <v>1052</v>
       </c>
       <c r="B225" s="66" t="s">
-        <v>2628</v>
+        <v>2630</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>2629</v>
+        <v>2631</v>
       </c>
       <c r="D225" s="48" t="s">
-        <v>2630</v>
+        <v>2632</v>
       </c>
       <c r="E225" s="66"/>
       <c r="F225" s="66"/>
@@ -31376,13 +31410,13 @@
         <v>1058</v>
       </c>
       <c r="B226" s="66" t="s">
-        <v>2631</v>
+        <v>2633</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>2632</v>
+        <v>2634</v>
       </c>
       <c r="D226" s="8" t="s">
-        <v>2633</v>
+        <v>2635</v>
       </c>
       <c r="E226" s="66"/>
       <c r="F226" s="66"/>
@@ -31397,13 +31431,13 @@
         <v>1058</v>
       </c>
       <c r="B227" s="66" t="s">
-        <v>2634</v>
+        <v>2636</v>
       </c>
       <c r="C227" s="8" t="s">
-        <v>2635</v>
+        <v>2637</v>
       </c>
       <c r="D227" s="8" t="s">
-        <v>2636</v>
+        <v>2638</v>
       </c>
       <c r="E227" s="66"/>
       <c r="F227" s="66"/>
@@ -31418,13 +31452,13 @@
         <v>1058</v>
       </c>
       <c r="B228" s="66" t="s">
-        <v>2637</v>
+        <v>2639</v>
       </c>
       <c r="C228" s="8" t="s">
-        <v>2638</v>
+        <v>2640</v>
       </c>
       <c r="D228" s="8" t="s">
-        <v>2639</v>
+        <v>2641</v>
       </c>
       <c r="E228" s="66"/>
       <c r="F228" s="66"/>
@@ -31434,16 +31468,16 @@
     </row>
     <row r="229" s="50" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="54" t="s">
-        <v>2640</v>
+        <v>2642</v>
       </c>
       <c r="B229" s="66" t="s">
         <v>1167</v>
       </c>
       <c r="C229" s="51" t="s">
-        <v>2641</v>
+        <v>2643</v>
       </c>
       <c r="D229" s="8" t="s">
-        <v>2642</v>
+        <v>2644</v>
       </c>
       <c r="E229" s="66"/>
       <c r="F229" s="66"/>
@@ -31453,16 +31487,16 @@
     </row>
     <row r="230" s="50" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="54" t="s">
-        <v>2640</v>
+        <v>2642</v>
       </c>
       <c r="B230" s="66" t="s">
         <v>1225</v>
       </c>
       <c r="C230" s="51" t="s">
-        <v>2643</v>
+        <v>2645</v>
       </c>
       <c r="D230" s="48" t="s">
-        <v>2644</v>
+        <v>2646</v>
       </c>
       <c r="E230" s="66"/>
       <c r="F230" s="66"/>
@@ -31475,13 +31509,13 @@
         <v>1088</v>
       </c>
       <c r="B231" s="66" t="s">
-        <v>2645</v>
+        <v>2647</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>2646</v>
+        <v>2648</v>
       </c>
       <c r="D231" s="51" t="s">
-        <v>2647</v>
+        <v>2649</v>
       </c>
       <c r="E231" s="66"/>
       <c r="F231" s="66"/>
@@ -31494,13 +31528,13 @@
         <v>1088</v>
       </c>
       <c r="B232" s="66" t="s">
-        <v>2648</v>
+        <v>2650</v>
       </c>
       <c r="C232" s="8" t="s">
-        <v>2649</v>
+        <v>2651</v>
       </c>
       <c r="D232" s="51" t="s">
-        <v>2650</v>
+        <v>2652</v>
       </c>
       <c r="E232" s="66"/>
       <c r="F232" s="66"/>
@@ -31513,13 +31547,13 @@
         <v>1088</v>
       </c>
       <c r="B233" s="66" t="s">
-        <v>2651</v>
+        <v>2653</v>
       </c>
       <c r="C233" s="8" t="s">
-        <v>2652</v>
+        <v>2654</v>
       </c>
       <c r="D233" s="51" t="s">
-        <v>2653</v>
+        <v>2655</v>
       </c>
       <c r="E233" s="66"/>
       <c r="F233" s="66"/>
@@ -31532,13 +31566,13 @@
         <v>1088</v>
       </c>
       <c r="B234" s="66" t="s">
-        <v>2654</v>
+        <v>2656</v>
       </c>
       <c r="C234" s="8" t="s">
-        <v>2655</v>
+        <v>2657</v>
       </c>
       <c r="D234" s="51" t="s">
-        <v>2656</v>
+        <v>2658</v>
       </c>
       <c r="E234" s="66"/>
       <c r="F234" s="66"/>
@@ -31551,13 +31585,13 @@
         <v>1088</v>
       </c>
       <c r="B235" s="66" t="s">
-        <v>2657</v>
+        <v>2659</v>
       </c>
       <c r="C235" s="8" t="s">
-        <v>2658</v>
+        <v>2660</v>
       </c>
       <c r="D235" s="51" t="s">
-        <v>2659</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="236" s="50" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31565,13 +31599,13 @@
         <v>1088</v>
       </c>
       <c r="B236" s="66" t="s">
-        <v>2660</v>
+        <v>2662</v>
       </c>
       <c r="C236" s="8" t="s">
-        <v>2661</v>
+        <v>2663</v>
       </c>
       <c r="D236" s="51" t="s">
-        <v>2662</v>
+        <v>2664</v>
       </c>
       <c r="E236" s="66"/>
       <c r="F236" s="66"/>
@@ -31589,7 +31623,7 @@
       <c r="E237" s="66"/>
       <c r="F237" s="66"/>
       <c r="G237" s="53" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
       <c r="H237" s="66"/>
       <c r="I237" s="66"/>
@@ -31599,13 +31633,13 @@
         <v>946</v>
       </c>
       <c r="B238" s="50" t="s">
-        <v>2663</v>
+        <v>2665</v>
       </c>
       <c r="C238" s="50" t="s">
-        <v>2664</v>
+        <v>2666</v>
       </c>
       <c r="D238" s="50" t="s">
-        <v>2665</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="239" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31613,13 +31647,13 @@
         <v>946</v>
       </c>
       <c r="B239" s="50" t="s">
-        <v>2577</v>
+        <v>2579</v>
       </c>
       <c r="C239" s="50" t="s">
-        <v>2666</v>
+        <v>2668</v>
       </c>
       <c r="D239" s="50" t="s">
-        <v>2667</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="240" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31627,13 +31661,13 @@
         <v>946</v>
       </c>
       <c r="B240" s="50" t="s">
-        <v>2668</v>
+        <v>2670</v>
       </c>
       <c r="C240" s="50" t="s">
-        <v>2669</v>
+        <v>2671</v>
       </c>
       <c r="D240" s="50" t="s">
-        <v>2670</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="241" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31641,13 +31675,13 @@
         <v>946</v>
       </c>
       <c r="B241" s="50" t="s">
-        <v>2671</v>
+        <v>2673</v>
       </c>
       <c r="C241" s="50" t="s">
-        <v>2672</v>
+        <v>2674</v>
       </c>
       <c r="D241" s="50" t="s">
-        <v>2673</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="242" s="50" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31655,13 +31689,13 @@
         <v>946</v>
       </c>
       <c r="B242" s="50" t="s">
-        <v>2674</v>
+        <v>2676</v>
       </c>
       <c r="C242" s="50" t="s">
-        <v>2675</v>
+        <v>2677</v>
       </c>
       <c r="D242" s="50" t="s">
-        <v>2676</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="243" s="50" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31672,10 +31706,10 @@
         <v>-2</v>
       </c>
       <c r="C243" s="57" t="s">
-        <v>2677</v>
+        <v>2679</v>
       </c>
       <c r="D243" s="57" t="s">
-        <v>2678</v>
+        <v>2680</v>
       </c>
       <c r="E243" s="66"/>
       <c r="F243" s="66"/>
@@ -31691,10 +31725,10 @@
         <v>-1</v>
       </c>
       <c r="C244" s="57" t="s">
-        <v>2679</v>
+        <v>2681</v>
       </c>
       <c r="D244" s="57" t="s">
-        <v>2680</v>
+        <v>2682</v>
       </c>
       <c r="E244" s="66"/>
       <c r="F244" s="66"/>
@@ -31710,10 +31744,10 @@
         <v>0</v>
       </c>
       <c r="C245" s="57" t="s">
-        <v>2681</v>
+        <v>2683</v>
       </c>
       <c r="D245" s="57" t="s">
-        <v>2682</v>
+        <v>2684</v>
       </c>
       <c r="E245" s="66"/>
       <c r="F245" s="66"/>
@@ -31729,10 +31763,10 @@
         <v>1</v>
       </c>
       <c r="C246" s="57" t="s">
-        <v>2683</v>
+        <v>2685</v>
       </c>
       <c r="D246" s="57" t="s">
-        <v>2684</v>
+        <v>2686</v>
       </c>
       <c r="E246" s="66"/>
       <c r="F246" s="66"/>
@@ -31748,10 +31782,10 @@
         <v>2</v>
       </c>
       <c r="C247" s="57" t="s">
-        <v>2685</v>
+        <v>2687</v>
       </c>
       <c r="D247" s="57" t="s">
-        <v>2686</v>
+        <v>2688</v>
       </c>
       <c r="E247" s="66"/>
       <c r="F247" s="66"/>
@@ -31767,10 +31801,10 @@
         <v>0</v>
       </c>
       <c r="C248" s="48" t="s">
-        <v>2687</v>
+        <v>2689</v>
       </c>
       <c r="D248" s="57" t="s">
-        <v>2688</v>
+        <v>2690</v>
       </c>
       <c r="E248" s="66"/>
       <c r="F248" s="66"/>
@@ -31786,10 +31820,10 @@
         <v>1</v>
       </c>
       <c r="C249" s="48" t="s">
-        <v>2689</v>
+        <v>2691</v>
       </c>
       <c r="D249" s="51" t="s">
-        <v>2690</v>
+        <v>2692</v>
       </c>
       <c r="E249" s="66"/>
       <c r="F249" s="66"/>
@@ -31805,10 +31839,10 @@
         <v>2</v>
       </c>
       <c r="C250" s="48" t="s">
-        <v>2691</v>
+        <v>2693</v>
       </c>
       <c r="D250" s="51" t="s">
-        <v>2692</v>
+        <v>2694</v>
       </c>
       <c r="E250" s="66"/>
       <c r="F250" s="66"/>
@@ -31824,10 +31858,10 @@
         <v>3</v>
       </c>
       <c r="C251" s="48" t="s">
-        <v>2693</v>
+        <v>2695</v>
       </c>
       <c r="D251" s="51" t="s">
-        <v>2694</v>
+        <v>2696</v>
       </c>
       <c r="E251" s="66"/>
       <c r="F251" s="66"/>
@@ -31843,10 +31877,10 @@
         <v>4</v>
       </c>
       <c r="C252" s="48" t="s">
-        <v>2695</v>
+        <v>2697</v>
       </c>
       <c r="D252" s="51" t="s">
-        <v>2696</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31857,10 +31891,10 @@
         <v>-1</v>
       </c>
       <c r="C253" s="48" t="s">
-        <v>2697</v>
+        <v>2699</v>
       </c>
       <c r="D253" s="51" t="s">
-        <v>2698</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31868,13 +31902,13 @@
         <v>39</v>
       </c>
       <c r="B254" s="66" t="s">
-        <v>2699</v>
+        <v>2701</v>
       </c>
       <c r="C254" s="66" t="s">
-        <v>2700</v>
+        <v>2702</v>
       </c>
       <c r="D254" s="66" t="s">
-        <v>2701</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -1658,19 +1658,19 @@
     <t xml:space="preserve">personVisitedPlacesTitle</t>
   </si>
   <si>
-    <t xml:space="preserve">Lieux où {{nickname}} est allé{{gender:/e/(e)/(e)}} le {{journeyDate}} :
+    <t xml:space="preserve">Lieux où {{nickname}} est allé{{gender:/e/(e)/(e)}} le {{journeyDates}} :
 L'ordre chronologique doit être respecté.</t>
   </si>
   <si>
-    <t xml:space="preserve">Places {{nickname}} went on {{journeyDate}}:
+    <t xml:space="preserve">Places {{nickname}} went on {{journeyDates}}:
 Chronological order must be respected (i.e. sequence matters).</t>
   </si>
   <si>
-    <t xml:space="preserve">Lieux où vous êtes allé{{gender:/e/(e)/(e)}} le {{journeyDate}} :
+    <t xml:space="preserve">Lieux où vous êtes allé{{gender:/e/(e)/(e)}} le {{journeyDates}} :
 L'ordre chronologique doit être respecté.</t>
   </si>
   <si>
-    <t xml:space="preserve">Places you went on {{journeyDate}}:
+    <t xml:space="preserve">Places you went on {{journeyDates}}:
 Chronological order must be respected (i.e. sequence matters).</t>
   </si>
   <si>

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5000" uniqueCount="2732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5000" uniqueCount="2736">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -2696,22 +2696,22 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Quel moyen de transport utilise habituellement {{nickname}} pour** se rendre à son lieu de travail?** 
+    <t xml:space="preserve">Quel moyen de transport utilise habituellement {{nickname}} pour** se rendre à son lieu de travail**, en automne?
 __Si plusieurs modes sont utilisés, indiquer le mode qui représente la plus grande partie de la distance parcourue.
 Si {{nickname}} fréquente plusieurs lieux, répondre en fonction du lieu déclaré ci-dessus.__</t>
   </si>
   <si>
-    <t xml:space="preserve">What mode of transportation does {{nickname}} usually use **to travel to their workplace?**
+    <t xml:space="preserve">What mode of transportation does {{nickname}} usually use **to travel to their workplace**, in automn?
 __If multiple modes are used, indicate the one that represents the largest share of distance traveled.
 If {{nickname}} works at multiple locations, respond based on the location identified above.__</t>
   </si>
   <si>
-    <t xml:space="preserve">Quel moyen de transport utilisez-vous habituellement pour** vous rendre à votre lieu de travail?** 
+    <t xml:space="preserve">Quel moyen de transport utilisez-vous habituellement pour** vous rendre à votre lieu de travail**, en automne? 
 __Si plusieurs modes sont utilisés, indiquer le mode qui représente la plus grande partie de la distance parcourue.
 Si vous fréquentez plusieurs lieux, répondre en fonction du lieu déclaré ci-dessus.__</t>
   </si>
   <si>
-    <t xml:space="preserve">What mode of transportation do you usually use **to travel to your workplace?**
+    <t xml:space="preserve">What mode of transportation do you usually use **to travel to your workplace**, in automn?
 __If multiple modes are used, indicate the one that represents the largest share of distance traveled.
 If you work at multiple locations, respond based on the location identified above.__</t>
   </si>
@@ -8122,6 +8122,18 @@
   </si>
   <si>
     <t xml:space="preserve">Longueuil Intermodal Terminal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto en tant que **conducteur**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Car as **driver**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto en tant que **passager**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Car as **passenger**</t>
   </si>
   <si>
     <t xml:space="preserve">**Transport en commun**</t>
@@ -16288,7 +16300,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="9" t="s">
         <v>786</v>
       </c>
@@ -30492,10 +30504,10 @@
         <v>2481</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>2024</v>
+        <v>2533</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>2025</v>
+        <v>2534</v>
       </c>
       <c r="G161" s="56"/>
       <c r="H161" s="56"/>
@@ -30509,10 +30521,10 @@
         <v>2482</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>2042</v>
+        <v>2535</v>
       </c>
       <c r="D162" s="11" t="s">
-        <v>2043</v>
+        <v>2536</v>
       </c>
       <c r="G162" s="56"/>
       <c r="H162" s="56"/>
@@ -30526,10 +30538,10 @@
         <v>2487</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>2533</v>
+        <v>2537</v>
       </c>
       <c r="D163" s="11" t="s">
-        <v>2534</v>
+        <v>2538</v>
       </c>
       <c r="G163" s="56"/>
       <c r="H163" s="56"/>
@@ -30557,7 +30569,7 @@
         <v>793</v>
       </c>
       <c r="B165" s="56" t="s">
-        <v>2535</v>
+        <v>2539</v>
       </c>
       <c r="C165" s="11" t="s">
         <v>1980</v>
@@ -30577,10 +30589,10 @@
         <v>232</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>2536</v>
+        <v>2540</v>
       </c>
       <c r="D166" s="11" t="s">
-        <v>2537</v>
+        <v>2541</v>
       </c>
       <c r="G166" s="56"/>
       <c r="H166" s="52" t="s">
@@ -30593,13 +30605,13 @@
         <v>793</v>
       </c>
       <c r="B167" s="56" t="s">
-        <v>2538</v>
+        <v>2542</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>2539</v>
+        <v>2543</v>
       </c>
       <c r="D167" s="11" t="s">
-        <v>2540</v>
+        <v>2544</v>
       </c>
       <c r="G167" s="56"/>
       <c r="H167" s="52" t="s">
@@ -30612,13 +30624,13 @@
         <v>141</v>
       </c>
       <c r="B168" s="56" t="s">
-        <v>2541</v>
+        <v>2545</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>2542</v>
+        <v>2546</v>
       </c>
       <c r="D168" s="11" t="s">
-        <v>2543</v>
+        <v>2547</v>
       </c>
       <c r="G168" s="56"/>
       <c r="H168" s="56"/>
@@ -30629,13 +30641,13 @@
         <v>141</v>
       </c>
       <c r="B169" s="56" t="s">
-        <v>2544</v>
+        <v>2548</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>2545</v>
+        <v>2549</v>
       </c>
       <c r="D169" s="11" t="s">
-        <v>2546</v>
+        <v>2550</v>
       </c>
       <c r="G169" s="56"/>
       <c r="H169" s="56"/>
@@ -30649,10 +30661,10 @@
         <v>1212</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>2547</v>
+        <v>2551</v>
       </c>
       <c r="D170" s="11" t="s">
-        <v>2548</v>
+        <v>2552</v>
       </c>
       <c r="G170" s="56"/>
       <c r="H170" s="56"/>
@@ -30666,10 +30678,10 @@
         <v>1248</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>2549</v>
+        <v>2553</v>
       </c>
       <c r="D171" s="11" t="s">
-        <v>2550</v>
+        <v>2554</v>
       </c>
       <c r="G171" s="56"/>
       <c r="H171" s="56"/>
@@ -30691,13 +30703,13 @@
         <v>248</v>
       </c>
       <c r="B173" s="56" t="s">
-        <v>2551</v>
+        <v>2555</v>
       </c>
       <c r="C173" s="11" t="s">
-        <v>2552</v>
+        <v>2556</v>
       </c>
       <c r="D173" s="11" t="s">
-        <v>2553</v>
+        <v>2557</v>
       </c>
       <c r="G173" s="56"/>
       <c r="H173" s="56" t="s">
@@ -30710,13 +30722,13 @@
         <v>248</v>
       </c>
       <c r="B174" s="56" t="s">
-        <v>2554</v>
+        <v>2558</v>
       </c>
       <c r="C174" s="11" t="s">
-        <v>2555</v>
+        <v>2559</v>
       </c>
       <c r="D174" s="11" t="s">
-        <v>2556</v>
+        <v>2560</v>
       </c>
       <c r="G174" s="56"/>
       <c r="H174" s="56" t="s">
@@ -30729,13 +30741,13 @@
         <v>248</v>
       </c>
       <c r="B175" s="56" t="s">
-        <v>2557</v>
+        <v>2561</v>
       </c>
       <c r="C175" s="11" t="s">
-        <v>2558</v>
+        <v>2562</v>
       </c>
       <c r="D175" s="11" t="s">
-        <v>2559</v>
+        <v>2563</v>
       </c>
       <c r="G175" s="56"/>
       <c r="H175" s="56" t="s">
@@ -30748,13 +30760,13 @@
         <v>248</v>
       </c>
       <c r="B176" s="56" t="s">
-        <v>2560</v>
+        <v>2564</v>
       </c>
       <c r="C176" s="11" t="s">
-        <v>2561</v>
+        <v>2565</v>
       </c>
       <c r="D176" s="11" t="s">
-        <v>2562</v>
+        <v>2566</v>
       </c>
       <c r="G176" s="56"/>
       <c r="H176" s="56" t="s">
@@ -30767,13 +30779,13 @@
         <v>248</v>
       </c>
       <c r="B177" s="56" t="s">
-        <v>2563</v>
+        <v>2567</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>2564</v>
+        <v>2568</v>
       </c>
       <c r="D177" s="11" t="s">
-        <v>2565</v>
+        <v>2569</v>
       </c>
       <c r="G177" s="56"/>
       <c r="H177" s="56" t="s">
@@ -30786,13 +30798,13 @@
         <v>248</v>
       </c>
       <c r="B178" s="56" t="s">
-        <v>2566</v>
+        <v>2570</v>
       </c>
       <c r="C178" s="11" t="s">
-        <v>2567</v>
+        <v>2571</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>2568</v>
+        <v>2572</v>
       </c>
       <c r="G178" s="56"/>
       <c r="H178" s="56" t="s">
@@ -30805,13 +30817,13 @@
         <v>248</v>
       </c>
       <c r="B179" s="56" t="s">
-        <v>2569</v>
+        <v>2573</v>
       </c>
       <c r="C179" s="11" t="s">
-        <v>2570</v>
+        <v>2574</v>
       </c>
       <c r="D179" s="11" t="s">
-        <v>2571</v>
+        <v>2575</v>
       </c>
       <c r="G179" s="56"/>
       <c r="H179" s="56" t="s">
@@ -30824,13 +30836,13 @@
         <v>248</v>
       </c>
       <c r="B180" s="56" t="s">
-        <v>2572</v>
+        <v>2576</v>
       </c>
       <c r="C180" s="11" t="s">
-        <v>2573</v>
+        <v>2577</v>
       </c>
       <c r="D180" s="11" t="s">
-        <v>2574</v>
+        <v>2578</v>
       </c>
       <c r="G180" s="56"/>
       <c r="H180" s="56" t="s">
@@ -30843,13 +30855,13 @@
         <v>248</v>
       </c>
       <c r="B181" s="56" t="s">
-        <v>2575</v>
+        <v>2579</v>
       </c>
       <c r="C181" s="11" t="s">
-        <v>2576</v>
+        <v>2580</v>
       </c>
       <c r="D181" s="11" t="s">
-        <v>2577</v>
+        <v>2581</v>
       </c>
       <c r="G181" s="56"/>
       <c r="H181" s="56" t="s">
@@ -30892,13 +30904,13 @@
         <v>260</v>
       </c>
       <c r="B184" s="56" t="s">
-        <v>2578</v>
+        <v>2582</v>
       </c>
       <c r="C184" s="11" t="s">
-        <v>2579</v>
+        <v>2583</v>
       </c>
       <c r="D184" s="11" t="s">
-        <v>2580</v>
+        <v>2584</v>
       </c>
       <c r="G184" s="56"/>
       <c r="H184" s="56" t="s">
@@ -30911,13 +30923,13 @@
         <v>260</v>
       </c>
       <c r="B185" s="56" t="s">
-        <v>2581</v>
+        <v>2585</v>
       </c>
       <c r="C185" s="11" t="s">
-        <v>2582</v>
+        <v>2586</v>
       </c>
       <c r="D185" s="11" t="s">
-        <v>2583</v>
+        <v>2587</v>
       </c>
       <c r="G185" s="56"/>
       <c r="H185" s="56" t="s">
@@ -30930,13 +30942,13 @@
         <v>260</v>
       </c>
       <c r="B186" s="56" t="s">
-        <v>2584</v>
+        <v>2588</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>2585</v>
+        <v>2589</v>
       </c>
       <c r="D186" s="11" t="s">
-        <v>2586</v>
+        <v>2590</v>
       </c>
       <c r="G186" s="56"/>
       <c r="H186" s="56" t="s">
@@ -30949,13 +30961,13 @@
         <v>260</v>
       </c>
       <c r="B187" s="56" t="s">
-        <v>2587</v>
+        <v>2591</v>
       </c>
       <c r="C187" s="11" t="s">
-        <v>2588</v>
+        <v>2592</v>
       </c>
       <c r="D187" s="11" t="s">
-        <v>2589</v>
+        <v>2593</v>
       </c>
       <c r="G187" s="56"/>
       <c r="H187" s="56" t="s">
@@ -30968,13 +30980,13 @@
         <v>260</v>
       </c>
       <c r="B188" s="56" t="s">
-        <v>2590</v>
+        <v>2594</v>
       </c>
       <c r="C188" s="11" t="s">
-        <v>2591</v>
+        <v>2595</v>
       </c>
       <c r="D188" s="11" t="s">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="G188" s="56"/>
       <c r="H188" s="56" t="s">
@@ -30987,13 +30999,13 @@
         <v>260</v>
       </c>
       <c r="B189" s="56" t="s">
-        <v>2593</v>
+        <v>2597</v>
       </c>
       <c r="C189" s="11" t="s">
-        <v>2594</v>
+        <v>2598</v>
       </c>
       <c r="D189" s="11" t="s">
-        <v>2595</v>
+        <v>2599</v>
       </c>
       <c r="G189" s="56"/>
       <c r="H189" s="56" t="s">
@@ -31006,13 +31018,13 @@
         <v>260</v>
       </c>
       <c r="B190" s="56" t="s">
-        <v>2596</v>
+        <v>2600</v>
       </c>
       <c r="C190" s="11" t="s">
-        <v>2597</v>
+        <v>2601</v>
       </c>
       <c r="D190" s="11" t="s">
-        <v>2598</v>
+        <v>2602</v>
       </c>
       <c r="G190" s="56"/>
       <c r="H190" s="56" t="s">
@@ -31028,10 +31040,10 @@
         <v>1230</v>
       </c>
       <c r="C191" s="11" t="s">
-        <v>2599</v>
+        <v>2603</v>
       </c>
       <c r="D191" s="11" t="s">
-        <v>2600</v>
+        <v>2604</v>
       </c>
       <c r="G191" s="70"/>
       <c r="H191" s="56" t="s">
@@ -31082,13 +31094,13 @@
         <v>288</v>
       </c>
       <c r="B194" s="56" t="s">
-        <v>2601</v>
+        <v>2605</v>
       </c>
       <c r="C194" s="11" t="s">
-        <v>2602</v>
+        <v>2606</v>
       </c>
       <c r="D194" s="11" t="s">
-        <v>2603</v>
+        <v>2607</v>
       </c>
       <c r="G194" s="56"/>
       <c r="H194" s="95"/>
@@ -31099,13 +31111,13 @@
         <v>288</v>
       </c>
       <c r="B195" s="56" t="s">
-        <v>2604</v>
+        <v>2608</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>2605</v>
+        <v>2609</v>
       </c>
       <c r="D195" s="11" t="s">
-        <v>2606</v>
+        <v>2610</v>
       </c>
       <c r="G195" s="56"/>
       <c r="H195" s="56"/>
@@ -31116,13 +31128,13 @@
         <v>288</v>
       </c>
       <c r="B196" s="56" t="s">
-        <v>2607</v>
+        <v>2611</v>
       </c>
       <c r="C196" s="11" t="s">
-        <v>2608</v>
+        <v>2612</v>
       </c>
       <c r="D196" s="11" t="s">
-        <v>2609</v>
+        <v>2613</v>
       </c>
       <c r="G196" s="56"/>
       <c r="H196" s="56"/>
@@ -31133,13 +31145,13 @@
         <v>288</v>
       </c>
       <c r="B197" s="56" t="s">
-        <v>2610</v>
+        <v>2614</v>
       </c>
       <c r="C197" s="11" t="s">
-        <v>2611</v>
+        <v>2615</v>
       </c>
       <c r="D197" s="11" t="s">
-        <v>2612</v>
+        <v>2616</v>
       </c>
       <c r="G197" s="56"/>
       <c r="H197" s="56"/>
@@ -31150,13 +31162,13 @@
         <v>288</v>
       </c>
       <c r="B198" s="56" t="s">
-        <v>2613</v>
+        <v>2617</v>
       </c>
       <c r="C198" s="11" t="s">
-        <v>2614</v>
+        <v>2618</v>
       </c>
       <c r="D198" s="11" t="s">
-        <v>2615</v>
+        <v>2619</v>
       </c>
       <c r="G198" s="56"/>
       <c r="H198" s="56"/>
@@ -31167,13 +31179,13 @@
         <v>295</v>
       </c>
       <c r="B199" s="56" t="s">
-        <v>2601</v>
+        <v>2605</v>
       </c>
       <c r="C199" s="11" t="s">
-        <v>2602</v>
+        <v>2606</v>
       </c>
       <c r="D199" s="11" t="s">
-        <v>2603</v>
+        <v>2607</v>
       </c>
       <c r="G199" s="56"/>
       <c r="H199" s="95" t="s">
@@ -31186,13 +31198,13 @@
         <v>295</v>
       </c>
       <c r="B200" s="56" t="s">
-        <v>2604</v>
+        <v>2608</v>
       </c>
       <c r="C200" s="11" t="s">
-        <v>2605</v>
+        <v>2609</v>
       </c>
       <c r="D200" s="11" t="s">
-        <v>2606</v>
+        <v>2610</v>
       </c>
       <c r="G200" s="56"/>
       <c r="H200" s="56"/>
@@ -31203,13 +31215,13 @@
         <v>295</v>
       </c>
       <c r="B201" s="56" t="s">
-        <v>2607</v>
+        <v>2611</v>
       </c>
       <c r="C201" s="11" t="s">
-        <v>2608</v>
+        <v>2612</v>
       </c>
       <c r="D201" s="11" t="s">
-        <v>2609</v>
+        <v>2613</v>
       </c>
       <c r="G201" s="56"/>
       <c r="H201" s="56"/>
@@ -31220,13 +31232,13 @@
         <v>295</v>
       </c>
       <c r="B202" s="56" t="s">
-        <v>2610</v>
+        <v>2614</v>
       </c>
       <c r="C202" s="11" t="s">
-        <v>2611</v>
+        <v>2615</v>
       </c>
       <c r="D202" s="11" t="s">
-        <v>2612</v>
+        <v>2616</v>
       </c>
       <c r="G202" s="56"/>
       <c r="H202" s="56"/>
@@ -31237,13 +31249,13 @@
         <v>295</v>
       </c>
       <c r="B203" s="56" t="s">
-        <v>2613</v>
+        <v>2617</v>
       </c>
       <c r="C203" s="11" t="s">
-        <v>2614</v>
+        <v>2618</v>
       </c>
       <c r="D203" s="11" t="s">
-        <v>2615</v>
+        <v>2619</v>
       </c>
       <c r="G203" s="56"/>
       <c r="H203" s="56"/>
@@ -31282,13 +31294,13 @@
         <v>857</v>
       </c>
       <c r="B206" s="70" t="s">
-        <v>2616</v>
+        <v>2620</v>
       </c>
       <c r="C206" s="11" t="s">
-        <v>2617</v>
+        <v>2621</v>
       </c>
       <c r="D206" s="11" t="s">
-        <v>2618</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31299,10 +31311,10 @@
         <v>2487</v>
       </c>
       <c r="C207" s="11" t="s">
-        <v>2619</v>
+        <v>2623</v>
       </c>
       <c r="D207" s="11" t="s">
-        <v>2620</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31318,13 +31330,13 @@
         <v>882</v>
       </c>
       <c r="B209" s="70" t="s">
-        <v>2621</v>
+        <v>2625</v>
       </c>
       <c r="C209" s="11" t="s">
-        <v>2622</v>
+        <v>2626</v>
       </c>
       <c r="D209" s="11" t="s">
-        <v>2623</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31332,13 +31344,13 @@
         <v>882</v>
       </c>
       <c r="B210" s="70" t="s">
-        <v>2624</v>
+        <v>2628</v>
       </c>
       <c r="C210" s="11" t="s">
-        <v>2625</v>
+        <v>2629</v>
       </c>
       <c r="D210" s="11" t="s">
-        <v>2626</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31346,13 +31358,13 @@
         <v>882</v>
       </c>
       <c r="B211" s="70" t="s">
-        <v>2627</v>
+        <v>2631</v>
       </c>
       <c r="C211" s="11" t="s">
-        <v>2628</v>
+        <v>2632</v>
       </c>
       <c r="D211" s="11" t="s">
-        <v>2629</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31360,13 +31372,13 @@
         <v>882</v>
       </c>
       <c r="B212" s="70" t="s">
-        <v>2630</v>
+        <v>2634</v>
       </c>
       <c r="C212" s="11" t="s">
-        <v>2631</v>
+        <v>2635</v>
       </c>
       <c r="D212" s="11" t="s">
-        <v>2632</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31374,13 +31386,13 @@
         <v>882</v>
       </c>
       <c r="B213" s="70" t="s">
-        <v>2633</v>
+        <v>2637</v>
       </c>
       <c r="C213" s="11" t="s">
-        <v>2634</v>
+        <v>2638</v>
       </c>
       <c r="D213" s="11" t="s">
-        <v>2635</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31388,13 +31400,13 @@
         <v>882</v>
       </c>
       <c r="B214" s="70" t="s">
-        <v>2636</v>
+        <v>2640</v>
       </c>
       <c r="C214" s="11" t="s">
-        <v>2637</v>
+        <v>2641</v>
       </c>
       <c r="D214" s="11" t="s">
-        <v>2638</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31405,10 +31417,10 @@
         <v>232</v>
       </c>
       <c r="C215" s="11" t="s">
-        <v>2639</v>
+        <v>2643</v>
       </c>
       <c r="D215" s="11" t="s">
-        <v>2640</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31447,10 +31459,10 @@
         <v>2481</v>
       </c>
       <c r="C218" s="11" t="s">
-        <v>2641</v>
+        <v>2645</v>
       </c>
       <c r="D218" s="11" t="s">
-        <v>2642</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31461,10 +31473,10 @@
         <v>2482</v>
       </c>
       <c r="C219" s="11" t="s">
-        <v>2643</v>
+        <v>2647</v>
       </c>
       <c r="D219" s="11" t="s">
-        <v>2644</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31475,10 +31487,10 @@
         <v>2487</v>
       </c>
       <c r="C220" s="11" t="s">
-        <v>2619</v>
+        <v>2623</v>
       </c>
       <c r="D220" s="11" t="s">
-        <v>2620</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31489,10 +31501,10 @@
         <v>232</v>
       </c>
       <c r="C221" s="11" t="s">
-        <v>2645</v>
+        <v>2649</v>
       </c>
       <c r="D221" s="11" t="s">
-        <v>2646</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31503,10 +31515,10 @@
         <v>1282</v>
       </c>
       <c r="C222" s="11" t="s">
-        <v>2647</v>
+        <v>2651</v>
       </c>
       <c r="D222" s="11" t="s">
-        <v>2648</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31514,13 +31526,13 @@
         <v>1075</v>
       </c>
       <c r="B223" s="70" t="s">
-        <v>2649</v>
+        <v>2653</v>
       </c>
       <c r="C223" s="11" t="s">
-        <v>2650</v>
+        <v>2654</v>
       </c>
       <c r="D223" s="11" t="s">
-        <v>2651</v>
+        <v>2655</v>
       </c>
       <c r="H223" s="54" t="s">
         <v>1189</v>
@@ -31531,13 +31543,13 @@
         <v>1075</v>
       </c>
       <c r="B224" s="70" t="s">
-        <v>2652</v>
+        <v>2656</v>
       </c>
       <c r="C224" s="11" t="s">
-        <v>2653</v>
+        <v>2657</v>
       </c>
       <c r="D224" s="11" t="s">
-        <v>2654</v>
+        <v>2658</v>
       </c>
       <c r="H224" s="54" t="s">
         <v>1189</v>
@@ -31548,13 +31560,13 @@
         <v>1075</v>
       </c>
       <c r="B225" s="70" t="s">
-        <v>2655</v>
+        <v>2659</v>
       </c>
       <c r="C225" s="11" t="s">
-        <v>2656</v>
+        <v>2660</v>
       </c>
       <c r="D225" s="11" t="s">
-        <v>2657</v>
+        <v>2661</v>
       </c>
       <c r="H225" s="54" t="s">
         <v>1189</v>
@@ -31565,13 +31577,13 @@
         <v>1075</v>
       </c>
       <c r="B226" s="70" t="s">
-        <v>2658</v>
+        <v>2662</v>
       </c>
       <c r="C226" s="11" t="s">
-        <v>2659</v>
+        <v>2663</v>
       </c>
       <c r="D226" s="11" t="s">
-        <v>2660</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31579,13 +31591,13 @@
         <v>1081</v>
       </c>
       <c r="B227" s="70" t="s">
-        <v>2661</v>
+        <v>2665</v>
       </c>
       <c r="C227" s="11" t="s">
-        <v>2662</v>
+        <v>2666</v>
       </c>
       <c r="D227" s="11" t="s">
-        <v>2663</v>
+        <v>2667</v>
       </c>
       <c r="H227" s="54" t="s">
         <v>1189</v>
@@ -31596,13 +31608,13 @@
         <v>1081</v>
       </c>
       <c r="B228" s="70" t="s">
-        <v>2664</v>
+        <v>2668</v>
       </c>
       <c r="C228" s="11" t="s">
-        <v>2665</v>
+        <v>2669</v>
       </c>
       <c r="D228" s="11" t="s">
-        <v>2666</v>
+        <v>2670</v>
       </c>
       <c r="H228" s="54" t="s">
         <v>1188</v>
@@ -31613,41 +31625,41 @@
         <v>1081</v>
       </c>
       <c r="B229" s="70" t="s">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="C229" s="11" t="s">
-        <v>2668</v>
+        <v>2672</v>
       </c>
       <c r="D229" s="11" t="s">
-        <v>2669</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="57" t="s">
-        <v>2670</v>
+        <v>2674</v>
       </c>
       <c r="B230" s="70" t="s">
         <v>1212</v>
       </c>
       <c r="C230" s="11" t="s">
-        <v>2671</v>
+        <v>2675</v>
       </c>
       <c r="D230" s="11" t="s">
-        <v>2672</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="57" t="s">
-        <v>2670</v>
+        <v>2674</v>
       </c>
       <c r="B231" s="70" t="s">
         <v>1248</v>
       </c>
       <c r="C231" s="11" t="s">
-        <v>2673</v>
+        <v>2677</v>
       </c>
       <c r="D231" s="11" t="s">
-        <v>2674</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31655,13 +31667,13 @@
         <v>1111</v>
       </c>
       <c r="B232" s="70" t="s">
-        <v>2675</v>
+        <v>2679</v>
       </c>
       <c r="C232" s="11" t="s">
-        <v>2676</v>
+        <v>2680</v>
       </c>
       <c r="D232" s="11" t="s">
-        <v>2677</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31669,13 +31681,13 @@
         <v>1111</v>
       </c>
       <c r="B233" s="70" t="s">
-        <v>2678</v>
+        <v>2682</v>
       </c>
       <c r="C233" s="11" t="s">
-        <v>2679</v>
+        <v>2683</v>
       </c>
       <c r="D233" s="11" t="s">
-        <v>2680</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31683,13 +31695,13 @@
         <v>1111</v>
       </c>
       <c r="B234" s="70" t="s">
-        <v>2681</v>
+        <v>2685</v>
       </c>
       <c r="C234" s="11" t="s">
-        <v>2682</v>
+        <v>2686</v>
       </c>
       <c r="D234" s="11" t="s">
-        <v>2683</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31697,13 +31709,13 @@
         <v>1111</v>
       </c>
       <c r="B235" s="70" t="s">
-        <v>2684</v>
+        <v>2688</v>
       </c>
       <c r="C235" s="11" t="s">
-        <v>2685</v>
+        <v>2689</v>
       </c>
       <c r="D235" s="11" t="s">
-        <v>2686</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31711,13 +31723,13 @@
         <v>1111</v>
       </c>
       <c r="B236" s="70" t="s">
-        <v>2687</v>
+        <v>2691</v>
       </c>
       <c r="C236" s="11" t="s">
-        <v>2688</v>
+        <v>2692</v>
       </c>
       <c r="D236" s="11" t="s">
-        <v>2689</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31725,13 +31737,13 @@
         <v>1111</v>
       </c>
       <c r="B237" s="70" t="s">
-        <v>2690</v>
+        <v>2694</v>
       </c>
       <c r="C237" s="11" t="s">
-        <v>2691</v>
+        <v>2695</v>
       </c>
       <c r="D237" s="11" t="s">
-        <v>2692</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31747,13 +31759,13 @@
         <v>999</v>
       </c>
       <c r="B239" s="11" t="s">
-        <v>2693</v>
+        <v>2697</v>
       </c>
       <c r="C239" s="11" t="s">
-        <v>2694</v>
+        <v>2698</v>
       </c>
       <c r="D239" s="11" t="s">
-        <v>2695</v>
+        <v>2699</v>
       </c>
       <c r="G239" s="11"/>
       <c r="H239" s="11"/>
@@ -31764,13 +31776,13 @@
         <v>999</v>
       </c>
       <c r="B240" s="11" t="s">
-        <v>2607</v>
+        <v>2611</v>
       </c>
       <c r="C240" s="11" t="s">
-        <v>2696</v>
+        <v>2700</v>
       </c>
       <c r="D240" s="11" t="s">
-        <v>2697</v>
+        <v>2701</v>
       </c>
       <c r="G240" s="11"/>
       <c r="H240" s="11"/>
@@ -31781,13 +31793,13 @@
         <v>999</v>
       </c>
       <c r="B241" s="11" t="s">
-        <v>2698</v>
+        <v>2702</v>
       </c>
       <c r="C241" s="11" t="s">
-        <v>2699</v>
+        <v>2703</v>
       </c>
       <c r="D241" s="11" t="s">
-        <v>2700</v>
+        <v>2704</v>
       </c>
       <c r="G241" s="11"/>
       <c r="H241" s="11"/>
@@ -31798,13 +31810,13 @@
         <v>999</v>
       </c>
       <c r="B242" s="11" t="s">
-        <v>2701</v>
+        <v>2705</v>
       </c>
       <c r="C242" s="11" t="s">
-        <v>2702</v>
+        <v>2706</v>
       </c>
       <c r="D242" s="11" t="s">
-        <v>2703</v>
+        <v>2707</v>
       </c>
       <c r="G242" s="11"/>
       <c r="H242" s="11"/>
@@ -31815,13 +31827,13 @@
         <v>999</v>
       </c>
       <c r="B243" s="11" t="s">
-        <v>2704</v>
+        <v>2708</v>
       </c>
       <c r="C243" s="11" t="s">
-        <v>2705</v>
+        <v>2709</v>
       </c>
       <c r="D243" s="11" t="s">
-        <v>2706</v>
+        <v>2710</v>
       </c>
       <c r="G243" s="11"/>
       <c r="H243" s="11"/>
@@ -31835,10 +31847,10 @@
         <v>-2</v>
       </c>
       <c r="C244" s="11" t="s">
-        <v>2707</v>
+        <v>2711</v>
       </c>
       <c r="D244" s="11" t="s">
-        <v>2708</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31849,10 +31861,10 @@
         <v>-1</v>
       </c>
       <c r="C245" s="11" t="s">
-        <v>2709</v>
+        <v>2713</v>
       </c>
       <c r="D245" s="11" t="s">
-        <v>2710</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31863,10 +31875,10 @@
         <v>0</v>
       </c>
       <c r="C246" s="11" t="s">
-        <v>2711</v>
+        <v>2715</v>
       </c>
       <c r="D246" s="11" t="s">
-        <v>2712</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31877,10 +31889,10 @@
         <v>1</v>
       </c>
       <c r="C247" s="11" t="s">
-        <v>2713</v>
+        <v>2717</v>
       </c>
       <c r="D247" s="11" t="s">
-        <v>2714</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31891,10 +31903,10 @@
         <v>2</v>
       </c>
       <c r="C248" s="11" t="s">
-        <v>2715</v>
+        <v>2719</v>
       </c>
       <c r="D248" s="11" t="s">
-        <v>2716</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31905,10 +31917,10 @@
         <v>0</v>
       </c>
       <c r="C249" s="11" t="s">
-        <v>2717</v>
+        <v>2721</v>
       </c>
       <c r="D249" s="11" t="s">
-        <v>2718</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31919,10 +31931,10 @@
         <v>1</v>
       </c>
       <c r="C250" s="11" t="s">
-        <v>2719</v>
+        <v>2723</v>
       </c>
       <c r="D250" s="11" t="s">
-        <v>2720</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31933,10 +31945,10 @@
         <v>2</v>
       </c>
       <c r="C251" s="11" t="s">
-        <v>2721</v>
+        <v>2725</v>
       </c>
       <c r="D251" s="11" t="s">
-        <v>2722</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31947,10 +31959,10 @@
         <v>3</v>
       </c>
       <c r="C252" s="11" t="s">
-        <v>2723</v>
+        <v>2727</v>
       </c>
       <c r="D252" s="11" t="s">
-        <v>2724</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31961,10 +31973,10 @@
         <v>4</v>
       </c>
       <c r="C253" s="11" t="s">
-        <v>2725</v>
+        <v>2729</v>
       </c>
       <c r="D253" s="11" t="s">
-        <v>2726</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31975,10 +31987,10 @@
         <v>-1</v>
       </c>
       <c r="C254" s="11" t="s">
-        <v>2727</v>
+        <v>2731</v>
       </c>
       <c r="D254" s="11" t="s">
-        <v>2728</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31986,13 +31998,13 @@
         <v>39</v>
       </c>
       <c r="B255" s="70" t="s">
-        <v>2729</v>
+        <v>2733</v>
       </c>
       <c r="C255" s="11" t="s">
-        <v>2730</v>
+        <v>2734</v>
       </c>
       <c r="D255" s="11" t="s">
-        <v>2731</v>
+        <v>2735</v>
       </c>
     </row>
   </sheetData>

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -7884,7 +7884,7 @@
     <t xml:space="preserve">bachelorOrHigher</t>
   </si>
   <si>
-    <t xml:space="preserve">Certificat ou diplôme universitaire niveau baccalauréat ou supérieur</t>
+    <t xml:space="preserve">Baccalauréat ou supérieur</t>
   </si>
   <si>
     <t xml:space="preserve">Bachelor's degree or higher</t>

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -2108,7 +2108,7 @@
     <t xml:space="preserve">**Station d'embarquement** (au départ) : </t>
   </si>
   <si>
-    <t xml:space="preserve">**Boarding station**(when entering the metro):</t>
+    <t xml:space="preserve">**Boarding station** (when entering the metro):</t>
   </si>
   <si>
     <t xml:space="preserve">subwayConditional</t>

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -1571,10 +1571,10 @@
     <t xml:space="preserve">household.persons.{_activePersonId}.journeys.{_activeJourneyId}.outOfTerritoryMembers</t>
   </si>
   <si>
-    <t xml:space="preserve">D’autres membres du ménage étaient aussi en dehors du domicile toute la journée?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Were other household members also outside home all day?</t>
+    <t xml:space="preserve">Quels autres membres du ménage étaient eux-aussi absents du domicile toute la journée ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which other household members were also away from home all day?</t>
   </si>
   <si>
     <t xml:space="preserve">outOfTerritoryMembersConditional</t>
@@ -9159,6 +9159,10 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9193,10 +9197,6 @@
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -13250,10 +13250,10 @@
       <c r="F70" s="9" t="s">
         <v>441</v>
       </c>
-      <c r="G70" s="9" t="s">
+      <c r="G70" s="30" t="s">
         <v>442</v>
       </c>
-      <c r="H70" s="9" t="s">
+      <c r="H70" s="30" t="s">
         <v>443</v>
       </c>
       <c r="I70" s="9"/>
@@ -13338,10 +13338,10 @@
       <c r="F72" s="18" t="s">
         <v>452</v>
       </c>
-      <c r="G72" s="30" t="s">
+      <c r="G72" s="31" t="s">
         <v>453</v>
       </c>
-      <c r="H72" s="30" t="s">
+      <c r="H72" s="31" t="s">
         <v>454</v>
       </c>
       <c r="I72" s="18"/>
@@ -13451,16 +13451,16 @@
       <c r="F75" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="G75" s="31" t="s">
+      <c r="G75" s="32" t="s">
         <v>457</v>
       </c>
-      <c r="H75" s="31" t="s">
+      <c r="H75" s="32" t="s">
         <v>458</v>
       </c>
-      <c r="I75" s="31" t="s">
+      <c r="I75" s="32" t="s">
         <v>459</v>
       </c>
-      <c r="J75" s="31" t="s">
+      <c r="J75" s="32" t="s">
         <v>460</v>
       </c>
       <c r="S75" s="1" t="b">
@@ -13577,7 +13577,7 @@
       <c r="B80" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="C80" s="32" t="n">
+      <c r="C80" s="33" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -13633,16 +13633,16 @@
       <c r="F81" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="G81" s="33" t="s">
+      <c r="G81" s="34" t="s">
         <v>485</v>
       </c>
-      <c r="H81" s="33" t="s">
+      <c r="H81" s="34" t="s">
         <v>486</v>
       </c>
-      <c r="I81" s="33" t="s">
+      <c r="I81" s="34" t="s">
         <v>487</v>
       </c>
-      <c r="J81" s="33" t="s">
+      <c r="J81" s="34" t="s">
         <v>488</v>
       </c>
       <c r="K81" s="9"/>
@@ -13676,16 +13676,16 @@
       <c r="F82" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="G82" s="33" t="s">
+      <c r="G82" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="H82" s="33" t="s">
+      <c r="H82" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="I82" s="33" t="s">
+      <c r="I82" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="J82" s="33" t="s">
+      <c r="J82" s="34" t="s">
         <v>494</v>
       </c>
       <c r="K82" s="9"/>
@@ -14143,7 +14143,7 @@
       <c r="B97" s="17" t="s">
         <v>367</v>
       </c>
-      <c r="C97" s="34" t="n">
+      <c r="C97" s="35" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -14183,23 +14183,23 @@
       <c r="A98" s="19" t="s">
         <v>366</v>
       </c>
-      <c r="B98" s="35" t="s">
+      <c r="B98" s="36" t="s">
         <v>367</v>
       </c>
-      <c r="C98" s="36" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D98" s="35" t="s">
+      <c r="C98" s="37" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D98" s="36" t="s">
         <v>566</v>
       </c>
       <c r="E98" s="19"/>
       <c r="F98" s="19"/>
       <c r="G98" s="19"/>
       <c r="H98" s="19"/>
-      <c r="I98" s="35"/>
-      <c r="J98" s="35"/>
-      <c r="K98" s="35"/>
+      <c r="I98" s="36"/>
+      <c r="J98" s="36"/>
+      <c r="K98" s="36"/>
       <c r="L98" s="19"/>
       <c r="M98" s="19"/>
       <c r="N98" s="19"/>
@@ -14207,7 +14207,7 @@
       <c r="P98" s="19"/>
       <c r="Q98" s="19"/>
       <c r="R98" s="19"/>
-      <c r="S98" s="35" t="b">
+      <c r="S98" s="36" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -14221,42 +14221,42 @@
       <c r="A99" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B99" s="31" t="s">
+      <c r="B99" s="32" t="s">
         <v>367</v>
       </c>
-      <c r="C99" s="37" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D99" s="31" t="s">
+      <c r="C99" s="38" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D99" s="32" t="s">
         <v>566</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="G99" s="31" t="s">
+      <c r="G99" s="32" t="s">
         <v>372</v>
       </c>
-      <c r="H99" s="31" t="s">
+      <c r="H99" s="32" t="s">
         <v>373</v>
       </c>
-      <c r="I99" s="31"/>
-      <c r="J99" s="31"/>
-      <c r="K99" s="31"/>
-      <c r="S99" s="31"/>
+      <c r="I99" s="32"/>
+      <c r="J99" s="32"/>
+      <c r="K99" s="32"/>
+      <c r="S99" s="32"/>
     </row>
     <row r="100" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="B100" s="31" t="s">
+      <c r="B100" s="32" t="s">
         <v>367</v>
       </c>
-      <c r="C100" s="37" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D100" s="31" t="s">
+      <c r="C100" s="38" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D100" s="32" t="s">
         <v>566</v>
       </c>
       <c r="F100" s="1" t="s">
@@ -14274,8 +14274,8 @@
       <c r="J100" s="9" t="s">
         <v>571</v>
       </c>
-      <c r="K100" s="31"/>
-      <c r="S100" s="31" t="b">
+      <c r="K100" s="32"/>
+      <c r="S100" s="32" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -14284,14 +14284,14 @@
       <c r="A101" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B101" s="31" t="s">
+      <c r="B101" s="32" t="s">
         <v>367</v>
       </c>
-      <c r="C101" s="37" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D101" s="31" t="s">
+      <c r="C101" s="38" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D101" s="32" t="s">
         <v>566</v>
       </c>
       <c r="F101" s="1" t="s">
@@ -14309,44 +14309,44 @@
       <c r="J101" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="K101" s="31"/>
-      <c r="S101" s="31"/>
+      <c r="K101" s="32"/>
+      <c r="S101" s="32"/>
     </row>
     <row r="102" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="B102" s="31" t="s">
+      <c r="B102" s="32" t="s">
         <v>367</v>
       </c>
-      <c r="C102" s="37" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D102" s="31" t="s">
+      <c r="C102" s="38" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D102" s="32" t="s">
         <v>566</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="H102" s="31"/>
-      <c r="I102" s="31"/>
-      <c r="J102" s="31"/>
-      <c r="K102" s="31"/>
-      <c r="S102" s="31"/>
+      <c r="H102" s="32"/>
+      <c r="I102" s="32"/>
+      <c r="J102" s="32"/>
+      <c r="K102" s="32"/>
+      <c r="S102" s="32"/>
     </row>
     <row r="103" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B103" s="31" t="s">
+      <c r="B103" s="32" t="s">
         <v>367</v>
       </c>
-      <c r="C103" s="37" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D103" s="31" t="s">
+      <c r="C103" s="38" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D103" s="32" t="s">
         <v>566</v>
       </c>
       <c r="E103" s="1" t="s">
@@ -14363,21 +14363,21 @@
       </c>
       <c r="I103" s="11"/>
       <c r="J103" s="11"/>
-      <c r="K103" s="31"/>
-      <c r="S103" s="31"/>
+      <c r="K103" s="32"/>
+      <c r="S103" s="32"/>
     </row>
     <row r="104" s="12" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B104" s="31" t="s">
+      <c r="B104" s="32" t="s">
         <v>367</v>
       </c>
-      <c r="C104" s="37" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D104" s="31" t="s">
+      <c r="C104" s="38" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D104" s="32" t="s">
         <v>566</v>
       </c>
       <c r="E104" s="1" t="s">
@@ -14389,12 +14389,12 @@
       <c r="G104" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="H104" s="31" t="s">
+      <c r="H104" s="32" t="s">
         <v>584</v>
       </c>
-      <c r="I104" s="31"/>
-      <c r="J104" s="31"/>
-      <c r="K104" s="31"/>
+      <c r="I104" s="32"/>
+      <c r="J104" s="32"/>
+      <c r="K104" s="32"/>
       <c r="L104" s="1"/>
       <c r="M104" s="1"/>
       <c r="N104" s="1"/>
@@ -14402,7 +14402,7 @@
       <c r="P104" s="1"/>
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
-      <c r="S104" s="31"/>
+      <c r="S104" s="32"/>
       <c r="T104" s="1"/>
       <c r="U104" s="1"/>
       <c r="V104" s="1"/>
@@ -14413,14 +14413,14 @@
       <c r="A105" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="B105" s="31" t="s">
+      <c r="B105" s="32" t="s">
         <v>367</v>
       </c>
-      <c r="C105" s="37" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D105" s="31" t="s">
+      <c r="C105" s="38" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D105" s="32" t="s">
         <v>566</v>
       </c>
       <c r="E105" s="1" t="s">
@@ -14435,9 +14435,9 @@
       <c r="H105" s="9" t="s">
         <v>588</v>
       </c>
-      <c r="I105" s="31"/>
-      <c r="J105" s="31"/>
-      <c r="K105" s="31"/>
+      <c r="I105" s="32"/>
+      <c r="J105" s="32"/>
+      <c r="K105" s="32"/>
       <c r="L105" s="1"/>
       <c r="M105" s="1"/>
       <c r="N105" s="1"/>
@@ -14445,7 +14445,7 @@
       <c r="P105" s="1"/>
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
-      <c r="S105" s="31"/>
+      <c r="S105" s="32"/>
       <c r="T105" s="1"/>
       <c r="U105" s="1"/>
       <c r="V105" s="1"/>
@@ -14720,7 +14720,7 @@
       <c r="U111" s="1"/>
       <c r="V111" s="1"/>
       <c r="W111" s="1"/>
-      <c r="X111" s="38" t="s">
+      <c r="X111" s="39" t="s">
         <v>615</v>
       </c>
     </row>
@@ -14770,7 +14770,7 @@
       <c r="U112" s="1"/>
       <c r="V112" s="1"/>
       <c r="W112" s="1"/>
-      <c r="X112" s="38" t="s">
+      <c r="X112" s="39" t="s">
         <v>615</v>
       </c>
     </row>
@@ -14822,7 +14822,7 @@
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
       <c r="W113" s="1"/>
-      <c r="X113" s="38"/>
+      <c r="X113" s="39"/>
     </row>
     <row r="114" s="12" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="9" t="s">
@@ -14920,7 +14920,7 @@
       <c r="U115" s="9"/>
       <c r="V115" s="9"/>
       <c r="W115" s="9"/>
-      <c r="X115" s="38" t="s">
+      <c r="X115" s="39" t="s">
         <v>615</v>
       </c>
     </row>
@@ -14972,7 +14972,7 @@
       <c r="U116" s="9"/>
       <c r="V116" s="9"/>
       <c r="W116" s="9"/>
-      <c r="X116" s="38" t="s">
+      <c r="X116" s="39" t="s">
         <v>642</v>
       </c>
     </row>
@@ -15022,7 +15022,7 @@
       <c r="U117" s="9"/>
       <c r="V117" s="9"/>
       <c r="W117" s="9"/>
-      <c r="X117" s="38" t="s">
+      <c r="X117" s="39" t="s">
         <v>615</v>
       </c>
     </row>
@@ -15072,7 +15072,7 @@
       <c r="U118" s="9"/>
       <c r="V118" s="9"/>
       <c r="W118" s="9"/>
-      <c r="X118" s="38" t="s">
+      <c r="X118" s="39" t="s">
         <v>615</v>
       </c>
     </row>
@@ -15957,7 +15957,7 @@
       <c r="B137" s="17" t="s">
         <v>367</v>
       </c>
-      <c r="C137" s="34" t="n">
+      <c r="C137" s="35" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -15971,7 +15971,7 @@
       <c r="G137" s="17" t="s">
         <v>754</v>
       </c>
-      <c r="H137" s="39" t="s">
+      <c r="H137" s="8" t="s">
         <v>755</v>
       </c>
       <c r="I137" s="17"/>
@@ -16600,7 +16600,7 @@
       <c r="B151" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="C151" s="34" t="n">
+      <c r="C151" s="35" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -17154,13 +17154,13 @@
       <c r="G164" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="H164" s="31" t="s">
+      <c r="H164" s="32" t="s">
         <v>901</v>
       </c>
-      <c r="I164" s="31" t="s">
+      <c r="I164" s="32" t="s">
         <v>902</v>
       </c>
-      <c r="J164" s="31" t="s">
+      <c r="J164" s="32" t="s">
         <v>903</v>
       </c>
       <c r="M164" s="1" t="s">
@@ -17195,13 +17195,13 @@
       <c r="G165" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="H165" s="31" t="s">
+      <c r="H165" s="32" t="s">
         <v>909</v>
       </c>
-      <c r="I165" s="31" t="s">
+      <c r="I165" s="32" t="s">
         <v>910</v>
       </c>
-      <c r="J165" s="31" t="s">
+      <c r="J165" s="32" t="s">
         <v>911</v>
       </c>
       <c r="K165" s="1"/>
@@ -17250,7 +17250,7 @@
       <c r="H166" s="1" t="s">
         <v>915</v>
       </c>
-      <c r="I166" s="31" t="s">
+      <c r="I166" s="32" t="s">
         <v>916</v>
       </c>
       <c r="J166" s="1" t="s">
@@ -18066,7 +18066,7 @@
       <c r="B184" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="C184" s="34" t="n">
+      <c r="C184" s="35" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -18197,7 +18197,7 @@
       <c r="B187" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="C187" s="34" t="n">
+      <c r="C187" s="35" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -18957,7 +18957,7 @@
       <c r="B203" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="C203" s="34" t="n">
+      <c r="C203" s="35" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -19444,7 +19444,7 @@
       <c r="B213" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="C213" s="34" t="n">
+      <c r="C213" s="35" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -19906,7 +19906,7 @@
       <c r="F223" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="G223" s="31" t="s">
+      <c r="G223" s="32" t="s">
         <v>1129</v>
       </c>
       <c r="H223" s="1" t="s">
@@ -19934,7 +19934,7 @@
       <c r="D224" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="F224" s="31" t="s">
+      <c r="F224" s="32" t="s">
         <v>1132</v>
       </c>
       <c r="G224" s="1" t="s">
@@ -19967,7 +19967,7 @@
       <c r="F225" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="G225" s="31" t="s">
+      <c r="G225" s="32" t="s">
         <v>1139</v>
       </c>
       <c r="H225" s="1" t="s">
@@ -20004,7 +20004,7 @@
       <c r="F226" s="1" t="s">
         <v>1144</v>
       </c>
-      <c r="G226" s="31" t="s">
+      <c r="G226" s="32" t="s">
         <v>1145</v>
       </c>
       <c r="H226" s="1" t="s">
@@ -20038,7 +20038,7 @@
       <c r="F227" s="1" t="s">
         <v>1148</v>
       </c>
-      <c r="G227" s="31" t="s">
+      <c r="G227" s="32" t="s">
         <v>1149</v>
       </c>
       <c r="H227" s="1" t="s">
@@ -20075,7 +20075,7 @@
       <c r="F228" s="1" t="s">
         <v>1153</v>
       </c>
-      <c r="G228" s="31" t="s">
+      <c r="G228" s="32" t="s">
         <v>1154</v>
       </c>
       <c r="H228" s="1" t="s">
@@ -20112,7 +20112,7 @@
       <c r="F229" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="G229" s="31" t="s">
+      <c r="G229" s="32" t="s">
         <v>1159</v>
       </c>
       <c r="H229" s="1" t="s">
@@ -20149,7 +20149,7 @@
       <c r="F230" s="1" t="s">
         <v>1163</v>
       </c>
-      <c r="G230" s="31" t="s">
+      <c r="G230" s="32" t="s">
         <v>1164</v>
       </c>
       <c r="H230" s="1" t="s">
@@ -20217,7 +20217,7 @@
       <c r="B232" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C232" s="32" t="n">
+      <c r="C232" s="33" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -20247,7 +20247,7 @@
       <c r="B233" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C233" s="32" t="n">
+      <c r="C233" s="33" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -20273,7 +20273,7 @@
       <c r="B234" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C234" s="32" t="n">
+      <c r="C234" s="33" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4984" uniqueCount="2721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4986" uniqueCount="2721">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -15455,6 +15455,9 @@
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
+      <c r="U126" s="1" t="s">
+        <v>232</v>
+      </c>
       <c r="X126" s="1" t="s">
         <v>690</v>
       </c>
@@ -15793,6 +15796,9 @@
       <c r="S133" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+      <c r="U133" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="X133" s="1" t="s">
         <v>690</v>

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -8728,8 +8728,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
-    <numFmt numFmtId="166" formatCode="&quot;VRAI&quot;;&quot;VRAI&quot;;&quot;FAUX&quot;"/>
+    <numFmt numFmtId="165" formatCode="&quot;VRAI&quot;;&quot;VRAI&quot;;&quot;FAUX&quot;"/>
+    <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -8994,7 +8994,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9075,6 +9075,10 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9103,7 +9107,7 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9111,7 +9115,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9131,7 +9135,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9143,7 +9147,7 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9163,7 +9167,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9175,7 +9179,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9187,7 +9191,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9259,7 +9263,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -12600,9 +12604,8 @@
       <c r="B68" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C68" s="2" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="C68" s="20" t="b">
+        <v>0</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>361</v>
@@ -12642,9 +12645,8 @@
       <c r="B69" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C69" s="2" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="C69" s="20" t="b">
+        <v>0</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>361</v>
@@ -13015,16 +13017,16 @@
       <c r="F80" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="G80" s="20" t="s">
+      <c r="G80" s="21" t="s">
         <v>478</v>
       </c>
-      <c r="H80" s="20" t="s">
+      <c r="H80" s="21" t="s">
         <v>479</v>
       </c>
-      <c r="I80" s="20" t="s">
+      <c r="I80" s="21" t="s">
         <v>480</v>
       </c>
-      <c r="J80" s="20" t="s">
+      <c r="J80" s="21" t="s">
         <v>481</v>
       </c>
     </row>
@@ -13048,16 +13050,16 @@
       <c r="F81" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="G81" s="20" t="s">
+      <c r="G81" s="21" t="s">
         <v>484</v>
       </c>
-      <c r="H81" s="20" t="s">
+      <c r="H81" s="21" t="s">
         <v>485</v>
       </c>
-      <c r="I81" s="20" t="s">
+      <c r="I81" s="21" t="s">
         <v>486</v>
       </c>
-      <c r="J81" s="20" t="s">
+      <c r="J81" s="21" t="s">
         <v>487</v>
       </c>
     </row>
@@ -13492,7 +13494,7 @@
       <c r="B96" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="C96" s="21" t="b">
+      <c r="C96" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -13935,7 +13937,7 @@
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X110" s="22" t="s">
+      <c r="X110" s="23" t="s">
         <v>608</v>
       </c>
     </row>
@@ -13972,7 +13974,7 @@
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X111" s="22" t="s">
+      <c r="X111" s="23" t="s">
         <v>608</v>
       </c>
     </row>
@@ -14014,7 +14016,7 @@
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X112" s="22"/>
+      <c r="X112" s="23"/>
     </row>
     <row r="113" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
@@ -14086,7 +14088,7 @@
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X114" s="22" t="s">
+      <c r="X114" s="23" t="s">
         <v>608</v>
       </c>
     </row>
@@ -14126,7 +14128,7 @@
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X115" s="22" t="s">
+      <c r="X115" s="23" t="s">
         <v>635</v>
       </c>
     </row>
@@ -14163,7 +14165,7 @@
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X116" s="22" t="s">
+      <c r="X116" s="23" t="s">
         <v>608</v>
       </c>
     </row>
@@ -14200,7 +14202,7 @@
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X117" s="22" t="s">
+      <c r="X117" s="23" t="s">
         <v>608</v>
       </c>
     </row>
@@ -14618,7 +14620,7 @@
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X128" s="22" t="s">
+      <c r="X128" s="23" t="s">
         <v>608</v>
       </c>
     </row>
@@ -14655,7 +14657,7 @@
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X129" s="22" t="s">
+      <c r="X129" s="23" t="s">
         <v>608</v>
       </c>
     </row>
@@ -14911,7 +14913,7 @@
       <c r="B136" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="C136" s="21" t="b">
+      <c r="C136" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -15163,7 +15165,7 @@
       <c r="D143" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="F143" s="23" t="s">
+      <c r="F143" s="24" t="s">
         <v>772</v>
       </c>
       <c r="G143" s="1" t="s">
@@ -15201,7 +15203,7 @@
       <c r="D144" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="F144" s="23" t="s">
+      <c r="F144" s="24" t="s">
         <v>776</v>
       </c>
       <c r="G144" s="8" t="s">
@@ -15235,7 +15237,7 @@
       <c r="D145" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="F145" s="23" t="s">
+      <c r="F145" s="24" t="s">
         <v>779</v>
       </c>
       <c r="G145" s="7" t="s">
@@ -15479,7 +15481,7 @@
       <c r="B151" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="C151" s="21" t="b">
+      <c r="C151" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -15984,12 +15986,12 @@
       <c r="D163" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="E163" s="24"/>
+      <c r="E163" s="25"/>
       <c r="F163" s="1" t="str">
         <f aca="false">A163</f>
         <v>householdLongDistanceIntroMap</v>
       </c>
-      <c r="I163" s="25"/>
+      <c r="I163" s="26"/>
       <c r="S163" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
@@ -16012,7 +16014,7 @@
       <c r="D164" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="E164" s="24"/>
+      <c r="E164" s="25"/>
       <c r="F164" s="1" t="s">
         <v>892</v>
       </c>
@@ -16064,7 +16066,7 @@
       <c r="D165" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="E165" s="24"/>
+      <c r="E165" s="25"/>
       <c r="F165" s="1" t="s">
         <v>900</v>
       </c>
@@ -16116,7 +16118,7 @@
       <c r="D166" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="E166" s="24"/>
+      <c r="E166" s="25"/>
       <c r="F166" s="1" t="s">
         <v>906</v>
       </c>
@@ -16295,13 +16297,13 @@
       <c r="F170" s="3" t="s">
         <v>921</v>
       </c>
-      <c r="G170" s="26" t="s">
+      <c r="G170" s="27" t="s">
         <v>923</v>
       </c>
       <c r="H170" s="14" t="s">
         <v>924</v>
       </c>
-      <c r="I170" s="26"/>
+      <c r="I170" s="27"/>
       <c r="J170" s="14"/>
       <c r="K170" s="1"/>
       <c r="L170" s="3"/>
@@ -16339,13 +16341,13 @@
       <c r="F171" s="3" t="s">
         <v>925</v>
       </c>
-      <c r="G171" s="26" t="s">
+      <c r="G171" s="27" t="s">
         <v>926</v>
       </c>
       <c r="H171" s="14" t="s">
         <v>927</v>
       </c>
-      <c r="I171" s="26"/>
+      <c r="I171" s="27"/>
       <c r="J171" s="14"/>
       <c r="K171" s="1"/>
       <c r="L171" s="3"/>
@@ -16385,13 +16387,13 @@
       <c r="F172" s="3" t="s">
         <v>929</v>
       </c>
-      <c r="G172" s="26" t="s">
+      <c r="G172" s="27" t="s">
         <v>930</v>
       </c>
       <c r="H172" s="14" t="s">
         <v>931</v>
       </c>
-      <c r="I172" s="26"/>
+      <c r="I172" s="27"/>
       <c r="J172" s="14"/>
       <c r="K172" s="1" t="s">
         <v>932</v>
@@ -16479,14 +16481,14 @@
       <c r="D174" s="7" t="s">
         <v>922</v>
       </c>
-      <c r="E174" s="24"/>
+      <c r="E174" s="25"/>
       <c r="F174" s="1" t="str">
         <f aca="false">A174</f>
         <v>barriersDisabilityTripMap</v>
       </c>
       <c r="G174" s="1"/>
       <c r="H174" s="1"/>
-      <c r="I174" s="25"/>
+      <c r="I174" s="26"/>
       <c r="J174" s="1"/>
       <c r="K174" s="1"/>
       <c r="L174" s="1"/>
@@ -16882,7 +16884,7 @@
       <c r="B185" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="C185" s="21" t="b">
+      <c r="C185" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -16998,7 +17000,7 @@
       <c r="B188" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="C188" s="21" t="b">
+      <c r="C188" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -17591,7 +17593,7 @@
       <c r="B204" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="C204" s="21" t="b">
+      <c r="C204" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -17691,12 +17693,12 @@
       <c r="D206" s="14" t="s">
         <v>1052</v>
       </c>
-      <c r="E206" s="24"/>
+      <c r="E206" s="25"/>
       <c r="F206" s="1" t="str">
         <f aca="false">A206</f>
         <v>barriersTripMap</v>
       </c>
-      <c r="I206" s="25"/>
+      <c r="I206" s="26"/>
       <c r="M206" s="14" t="s">
         <v>1057</v>
       </c>
@@ -18005,7 +18007,7 @@
       <c r="B215" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="C215" s="21" t="b">
+      <c r="C215" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -18899,7 +18901,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="27.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="15.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="27" width="20.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="28" width="20.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="19.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="12.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="7" width="23.5"/>
@@ -18907,29 +18909,29 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="7" width="8.5"/>
   </cols>
   <sheetData>
-    <row r="1" s="32" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="28" t="s">
+    <row r="1" s="33" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="29" t="s">
         <v>1175</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="29" t="s">
         <v>1176</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="30" t="s">
         <v>1177</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="29" t="s">
         <v>1178</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="29" t="s">
         <v>1179</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="31" t="s">
         <v>1180</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="32" t="s">
         <v>23</v>
       </c>
     </row>
@@ -18940,7 +18942,7 @@
       <c r="C2" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E2" s="7" t="n">
@@ -18954,7 +18956,7 @@
       <c r="C3" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="28" t="s">
         <v>1183</v>
       </c>
       <c r="E3" s="7" t="n">
@@ -18968,7 +18970,7 @@
       <c r="C4" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E4" s="7" t="n">
@@ -18982,7 +18984,7 @@
       <c r="C5" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="28" t="s">
         <v>1183</v>
       </c>
       <c r="E5" s="7" t="n">
@@ -18996,7 +18998,7 @@
       <c r="C6" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="28" t="s">
         <v>1183</v>
       </c>
       <c r="E6" s="7" t="n">
@@ -19004,13 +19006,13 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="34" t="s">
         <v>1186</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>1187</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E7" s="7" t="s">
@@ -19024,7 +19026,7 @@
       <c r="C8" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="28" t="s">
         <v>1183</v>
       </c>
       <c r="E8" s="7" t="n">
@@ -19041,7 +19043,7 @@
       <c r="C9" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="28" t="s">
         <v>1192</v>
       </c>
       <c r="E9" s="7" t="n">
@@ -19055,7 +19057,7 @@
       <c r="C10" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="28" t="s">
         <v>1183</v>
       </c>
       <c r="E10" s="7" t="n">
@@ -19072,7 +19074,7 @@
       <c r="C11" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="28" t="s">
         <v>1192</v>
       </c>
       <c r="E11" s="7" t="n">
@@ -19086,7 +19088,7 @@
       <c r="C12" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="28" t="s">
         <v>1183</v>
       </c>
       <c r="E12" s="7" t="n">
@@ -19103,7 +19105,7 @@
       <c r="C13" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="28" t="s">
         <v>1192</v>
       </c>
       <c r="E13" s="7" t="n">
@@ -19117,7 +19119,7 @@
       <c r="C14" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="28" t="s">
         <v>1192</v>
       </c>
       <c r="E14" s="7" t="n">
@@ -19131,7 +19133,7 @@
       <c r="C15" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="28" t="s">
         <v>1183</v>
       </c>
       <c r="E15" s="7" t="n">
@@ -19145,7 +19147,7 @@
       <c r="C16" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="28" t="s">
         <v>1183</v>
       </c>
       <c r="E16" s="7" t="n">
@@ -19159,7 +19161,7 @@
       <c r="C17" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="28" t="s">
         <v>1183</v>
       </c>
       <c r="E17" s="7" t="n">
@@ -19173,7 +19175,7 @@
       <c r="C18" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="28" t="s">
         <v>1183</v>
       </c>
       <c r="E18" s="7" t="n">
@@ -19187,7 +19189,7 @@
       <c r="C19" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="28" t="s">
         <v>1192</v>
       </c>
       <c r="E19" s="7" t="n">
@@ -19204,7 +19206,7 @@
       <c r="C20" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="28" t="s">
         <v>1199</v>
       </c>
       <c r="E20" s="7" t="s">
@@ -19218,7 +19220,7 @@
       <c r="C21" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="28" t="s">
         <v>1183</v>
       </c>
       <c r="E21" s="7" t="n">
@@ -19232,7 +19234,7 @@
       <c r="C22" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="28" t="s">
         <v>1183</v>
       </c>
       <c r="E22" s="7" t="n">
@@ -19246,7 +19248,7 @@
       <c r="C23" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D23" s="27" t="s">
+      <c r="D23" s="28" t="s">
         <v>1192</v>
       </c>
       <c r="E23" s="7" t="n">
@@ -19263,7 +19265,7 @@
       <c r="C24" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D24" s="27" t="s">
+      <c r="D24" s="28" t="s">
         <v>1199</v>
       </c>
       <c r="E24" s="7" t="s">
@@ -19278,7 +19280,7 @@
       <c r="C25" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D25" s="27" t="s">
+      <c r="D25" s="28" t="s">
         <v>1183</v>
       </c>
       <c r="E25" s="7" t="n">
@@ -19289,37 +19291,37 @@
       <c r="H25" s="7"/>
     </row>
     <row r="26" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="23" t="s">
         <v>1204</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22" t="s">
+      <c r="B26" s="23"/>
+      <c r="C26" s="23" t="s">
         <v>1190</v>
       </c>
-      <c r="D26" s="34" t="s">
+      <c r="D26" s="35" t="s">
         <v>1192</v>
       </c>
-      <c r="E26" s="22" t="n">
+      <c r="E26" s="23" t="n">
         <v>64</v>
       </c>
-      <c r="F26" s="22"/>
+      <c r="F26" s="23"/>
       <c r="G26" s="7"/>
     </row>
     <row r="27" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="23" t="s">
         <v>1205</v>
       </c>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22" t="s">
+      <c r="B27" s="23"/>
+      <c r="C27" s="23" t="s">
         <v>1190</v>
       </c>
-      <c r="D27" s="34" t="s">
+      <c r="D27" s="35" t="s">
         <v>1183</v>
       </c>
-      <c r="E27" s="22" t="n">
+      <c r="E27" s="23" t="n">
         <v>65</v>
       </c>
-      <c r="F27" s="22"/>
+      <c r="F27" s="23"/>
       <c r="G27" s="7"/>
     </row>
     <row r="28" s="9" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19330,32 +19332,32 @@
       <c r="C28" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="D28" s="27" t="s">
+      <c r="D28" s="28" t="s">
         <v>1183</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F28" s="22"/>
+      <c r="F28" s="23"/>
       <c r="G28" s="7"/>
     </row>
     <row r="29" s="9" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="23" t="s">
         <v>1206</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="C29" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="D29" s="34" t="s">
+      <c r="D29" s="35" t="s">
         <v>1182</v>
       </c>
-      <c r="E29" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="22"/>
+      <c r="E29" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="23"/>
       <c r="G29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19365,7 +19367,7 @@
       <c r="C30" s="7" t="s">
         <v>1207</v>
       </c>
-      <c r="D30" s="27" t="s">
+      <c r="D30" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E30" s="7" t="s">
@@ -19379,10 +19381,10 @@
       <c r="C31" s="7" t="s">
         <v>1209</v>
       </c>
-      <c r="D31" s="27" t="s">
+      <c r="D31" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E31" s="27" t="s">
+      <c r="E31" s="28" t="s">
         <v>1210</v>
       </c>
     </row>
@@ -19396,10 +19398,10 @@
       <c r="C32" s="7" t="s">
         <v>1209</v>
       </c>
-      <c r="D32" s="27" t="s">
+      <c r="D32" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E32" s="27" t="s">
+      <c r="E32" s="28" t="s">
         <v>1211</v>
       </c>
     </row>
@@ -19413,10 +19415,10 @@
       <c r="C33" s="7" t="s">
         <v>1209</v>
       </c>
-      <c r="D33" s="27" t="s">
+      <c r="D33" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E33" s="27" t="s">
+      <c r="E33" s="28" t="s">
         <v>1212</v>
       </c>
       <c r="F33" s="7"/>
@@ -19430,10 +19432,10 @@
       <c r="C34" s="7" t="s">
         <v>1209</v>
       </c>
-      <c r="D34" s="27" t="s">
+      <c r="D34" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E34" s="27" t="s">
+      <c r="E34" s="28" t="s">
         <v>1214</v>
       </c>
     </row>
@@ -19447,10 +19449,10 @@
       <c r="C35" s="7" t="s">
         <v>1209</v>
       </c>
-      <c r="D35" s="27" t="s">
+      <c r="D35" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E35" s="27" t="s">
+      <c r="E35" s="28" t="s">
         <v>1215</v>
       </c>
     </row>
@@ -19464,10 +19466,10 @@
       <c r="C36" s="7" t="s">
         <v>1209</v>
       </c>
-      <c r="D36" s="27" t="s">
+      <c r="D36" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E36" s="27" t="s">
+      <c r="E36" s="28" t="s">
         <v>1212</v>
       </c>
     </row>
@@ -19478,7 +19480,7 @@
       <c r="C37" s="7" t="s">
         <v>1217</v>
       </c>
-      <c r="D37" s="27" t="s">
+      <c r="D37" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E37" s="7" t="s">
@@ -19495,7 +19497,7 @@
       <c r="C38" s="7" t="s">
         <v>1217</v>
       </c>
-      <c r="D38" s="27" t="s">
+      <c r="D38" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E38" s="7" t="s">
@@ -19512,7 +19514,7 @@
       <c r="C39" s="7" t="s">
         <v>1217</v>
       </c>
-      <c r="D39" s="27" t="s">
+      <c r="D39" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E39" s="7" t="s">
@@ -19529,7 +19531,7 @@
       <c r="C40" s="7" t="s">
         <v>1221</v>
       </c>
-      <c r="D40" s="27" t="s">
+      <c r="D40" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E40" s="7" t="s">
@@ -19546,7 +19548,7 @@
       <c r="C41" s="7" t="s">
         <v>1221</v>
       </c>
-      <c r="D41" s="27" t="s">
+      <c r="D41" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E41" s="7" t="s">
@@ -19563,7 +19565,7 @@
       <c r="C42" s="7" t="s">
         <v>1221</v>
       </c>
-      <c r="D42" s="27" t="s">
+      <c r="D42" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E42" s="7" t="s">
@@ -19571,13 +19573,13 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="35" t="s">
+      <c r="A43" s="36" t="s">
         <v>1222</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>1223</v>
       </c>
-      <c r="D43" s="27" t="s">
+      <c r="D43" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E43" s="7" t="s">
@@ -19585,7 +19587,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="35" t="s">
+      <c r="A44" s="36" t="s">
         <v>1222</v>
       </c>
       <c r="B44" s="7" t="s">
@@ -19594,7 +19596,7 @@
       <c r="C44" s="7" t="s">
         <v>1223</v>
       </c>
-      <c r="D44" s="27" t="s">
+      <c r="D44" s="28" t="s">
         <v>1199</v>
       </c>
       <c r="E44" s="7" t="s">
@@ -19602,13 +19604,13 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="22" t="s">
+      <c r="A45" s="23" t="s">
         <v>257</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>1223</v>
       </c>
-      <c r="D45" s="27" t="s">
+      <c r="D45" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E45" s="7" t="s">
@@ -19616,13 +19618,13 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="35" t="s">
+      <c r="A46" s="36" t="s">
         <v>1224</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>1225</v>
       </c>
-      <c r="D46" s="27" t="s">
+      <c r="D46" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E46" s="7" t="s">
@@ -19630,7 +19632,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="35" t="s">
+      <c r="A47" s="36" t="s">
         <v>1224</v>
       </c>
       <c r="B47" s="7" t="s">
@@ -19639,10 +19641,10 @@
       <c r="C47" s="7" t="s">
         <v>1225</v>
       </c>
-      <c r="D47" s="27" t="s">
+      <c r="D47" s="28" t="s">
         <v>1199</v>
       </c>
-      <c r="E47" s="35" t="s">
+      <c r="E47" s="36" t="s">
         <v>1226</v>
       </c>
       <c r="F47" s="7" t="s">
@@ -19650,7 +19652,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="35" t="s">
+      <c r="A48" s="36" t="s">
         <v>1224</v>
       </c>
       <c r="B48" s="7" t="s">
@@ -19659,7 +19661,7 @@
       <c r="C48" s="7" t="s">
         <v>1225</v>
       </c>
-      <c r="D48" s="27" t="s">
+      <c r="D48" s="28" t="s">
         <v>1199</v>
       </c>
       <c r="E48" s="7" t="s">
@@ -19670,13 +19672,13 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="35" t="s">
+      <c r="A49" s="36" t="s">
         <v>1229</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>1225</v>
       </c>
-      <c r="D49" s="27" t="s">
+      <c r="D49" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E49" s="7" t="s">
@@ -19684,7 +19686,7 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="35" t="s">
+      <c r="A50" s="36" t="s">
         <v>1229</v>
       </c>
       <c r="B50" s="7" t="s">
@@ -19693,7 +19695,7 @@
       <c r="C50" s="7" t="s">
         <v>1225</v>
       </c>
-      <c r="D50" s="27" t="s">
+      <c r="D50" s="28" t="s">
         <v>1199</v>
       </c>
       <c r="E50" s="7" t="s">
@@ -19701,13 +19703,13 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="35" t="s">
+      <c r="A51" s="36" t="s">
         <v>1230</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>1225</v>
       </c>
-      <c r="D51" s="27" t="s">
+      <c r="D51" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E51" s="7" t="s">
@@ -19715,7 +19717,7 @@
       </c>
     </row>
     <row r="52" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="35" t="s">
+      <c r="A52" s="36" t="s">
         <v>1230</v>
       </c>
       <c r="B52" s="7" t="s">
@@ -19724,10 +19726,10 @@
       <c r="C52" s="7" t="s">
         <v>1225</v>
       </c>
-      <c r="D52" s="27" t="s">
+      <c r="D52" s="28" t="s">
         <v>1199</v>
       </c>
-      <c r="E52" s="35" t="s">
+      <c r="E52" s="36" t="s">
         <v>1226</v>
       </c>
       <c r="F52" s="7"/>
@@ -19735,14 +19737,14 @@
       <c r="H52" s="7"/>
     </row>
     <row r="53" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="22" t="s">
+      <c r="A53" s="23" t="s">
         <v>268</v>
       </c>
       <c r="B53" s="7"/>
       <c r="C53" s="7" t="s">
         <v>1225</v>
       </c>
-      <c r="D53" s="27" t="s">
+      <c r="D53" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E53" s="7" t="s">
@@ -19753,55 +19755,55 @@
       <c r="H53" s="7"/>
     </row>
     <row r="54" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="22" t="s">
+      <c r="A54" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="B54" s="22"/>
-      <c r="C54" s="22" t="s">
+      <c r="B54" s="23"/>
+      <c r="C54" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D54" s="34" t="s">
+      <c r="D54" s="35" t="s">
         <v>1182</v>
       </c>
-      <c r="E54" s="22" t="s">
+      <c r="E54" s="23" t="s">
         <v>1208</v>
       </c>
-      <c r="F54" s="22"/>
+      <c r="F54" s="23"/>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
     </row>
     <row r="55" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="22" t="s">
+      <c r="A55" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="22" t="s">
+      <c r="B55" s="23" t="s">
         <v>1206</v>
       </c>
-      <c r="C55" s="22" t="s">
+      <c r="C55" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D55" s="34" t="s">
+      <c r="D55" s="35" t="s">
         <v>1182</v>
       </c>
-      <c r="E55" s="22" t="s">
+      <c r="E55" s="23" t="s">
         <v>1208</v>
       </c>
-      <c r="F55" s="22"/>
+      <c r="F55" s="23"/>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
     </row>
     <row r="56" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="36" t="s">
+      <c r="A56" s="37" t="s">
         <v>1121</v>
       </c>
       <c r="B56" s="7"/>
       <c r="C56" s="7" t="s">
         <v>1114</v>
       </c>
-      <c r="D56" s="37" t="s">
+      <c r="D56" s="38" t="s">
         <v>1182</v>
       </c>
-      <c r="E56" s="32" t="s">
+      <c r="E56" s="33" t="s">
         <v>1208</v>
       </c>
       <c r="F56" s="7"/>
@@ -19809,14 +19811,14 @@
       <c r="H56" s="7"/>
     </row>
     <row r="57" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="36" t="s">
+      <c r="A57" s="37" t="s">
         <v>1087</v>
       </c>
       <c r="B57" s="7"/>
       <c r="C57" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D57" s="27" t="s">
+      <c r="D57" s="28" t="s">
         <v>1183</v>
       </c>
       <c r="E57" s="7" t="n">
@@ -19827,14 +19829,14 @@
       <c r="H57" s="7"/>
     </row>
     <row r="58" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="38" t="s">
+      <c r="A58" s="39" t="s">
         <v>1231</v>
       </c>
       <c r="B58" s="7"/>
       <c r="C58" s="7" t="s">
         <v>1217</v>
       </c>
-      <c r="D58" s="27" t="s">
+      <c r="D58" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E58" s="7" t="s">
@@ -19845,14 +19847,14 @@
       <c r="H58" s="7"/>
     </row>
     <row r="59" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="39" t="s">
+      <c r="A59" s="40" t="s">
         <v>329</v>
       </c>
       <c r="B59" s="7"/>
       <c r="C59" s="7" t="s">
         <v>1217</v>
       </c>
-      <c r="D59" s="27" t="s">
+      <c r="D59" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E59" s="7" t="s">
@@ -19863,146 +19865,146 @@
       <c r="H59" s="7"/>
     </row>
     <row r="60" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="22" t="s">
+      <c r="A60" s="23" t="s">
         <v>337</v>
       </c>
-      <c r="B60" s="22"/>
-      <c r="C60" s="22" t="s">
+      <c r="B60" s="23"/>
+      <c r="C60" s="23" t="s">
         <v>1217</v>
       </c>
-      <c r="D60" s="34" t="s">
+      <c r="D60" s="35" t="s">
         <v>1182</v>
       </c>
-      <c r="E60" s="22" t="s">
+      <c r="E60" s="23" t="s">
         <v>1219</v>
       </c>
-      <c r="F60" s="22" t="s">
+      <c r="F60" s="23" t="s">
         <v>1227</v>
       </c>
       <c r="G60" s="7"/>
     </row>
     <row r="61" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="22" t="s">
+      <c r="A61" s="23" t="s">
         <v>337</v>
       </c>
-      <c r="B61" s="22" t="s">
+      <c r="B61" s="23" t="s">
         <v>1191</v>
       </c>
-      <c r="C61" s="22" t="s">
+      <c r="C61" s="23" t="s">
         <v>1232</v>
       </c>
-      <c r="D61" s="34" t="s">
+      <c r="D61" s="35" t="s">
         <v>1233</v>
       </c>
-      <c r="E61" s="22" t="n">
+      <c r="E61" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="F61" s="22" t="s">
+      <c r="F61" s="23" t="s">
         <v>1228</v>
       </c>
       <c r="G61" s="7"/>
     </row>
     <row r="62" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="22" t="s">
+      <c r="A62" s="23" t="s">
         <v>337</v>
       </c>
-      <c r="B62" s="22" t="s">
+      <c r="B62" s="23" t="s">
         <v>1206</v>
       </c>
-      <c r="C62" s="22" t="s">
+      <c r="C62" s="23" t="s">
         <v>1217</v>
       </c>
-      <c r="D62" s="34" t="s">
+      <c r="D62" s="35" t="s">
         <v>1182</v>
       </c>
-      <c r="E62" s="22" t="s">
+      <c r="E62" s="23" t="s">
         <v>1218</v>
       </c>
-      <c r="F62" s="22"/>
+      <c r="F62" s="23"/>
       <c r="G62" s="7"/>
     </row>
     <row r="63" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="22" t="s">
+      <c r="A63" s="23" t="s">
         <v>337</v>
       </c>
-      <c r="B63" s="22" t="s">
+      <c r="B63" s="23" t="s">
         <v>1206</v>
       </c>
-      <c r="C63" s="22" t="s">
+      <c r="C63" s="23" t="s">
         <v>1217</v>
       </c>
-      <c r="D63" s="34" t="s">
+      <c r="D63" s="35" t="s">
         <v>1182</v>
       </c>
-      <c r="E63" s="35" t="s">
+      <c r="E63" s="36" t="s">
         <v>1220</v>
       </c>
-      <c r="F63" s="22"/>
+      <c r="F63" s="23"/>
       <c r="G63" s="7"/>
     </row>
     <row r="64" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="22" t="s">
+      <c r="A64" s="23" t="s">
         <v>337</v>
       </c>
-      <c r="B64" s="22" t="s">
+      <c r="B64" s="23" t="s">
         <v>1206</v>
       </c>
-      <c r="C64" s="22" t="s">
+      <c r="C64" s="23" t="s">
         <v>1217</v>
       </c>
-      <c r="D64" s="34" t="s">
+      <c r="D64" s="35" t="s">
         <v>1182</v>
       </c>
-      <c r="E64" s="35" t="s">
+      <c r="E64" s="36" t="s">
         <v>1234</v>
       </c>
-      <c r="F64" s="22"/>
+      <c r="F64" s="23"/>
       <c r="G64" s="7"/>
     </row>
     <row r="65" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="22" t="s">
+      <c r="A65" s="23" t="s">
         <v>252</v>
       </c>
-      <c r="C65" s="22" t="s">
+      <c r="C65" s="23" t="s">
         <v>1235</v>
       </c>
-      <c r="D65" s="27" t="s">
+      <c r="D65" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E65" s="38" t="s">
+      <c r="E65" s="39" t="s">
         <v>1208</v>
       </c>
       <c r="H65" s="9"/>
     </row>
     <row r="66" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="22" t="s">
+      <c r="A66" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="C66" s="22" t="s">
+      <c r="C66" s="23" t="s">
         <v>1236</v>
       </c>
-      <c r="D66" s="27" t="s">
+      <c r="D66" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E66" s="38" t="s">
+      <c r="E66" s="39" t="s">
         <v>1208</v>
       </c>
       <c r="H66" s="9"/>
     </row>
     <row r="67" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="22" t="s">
+      <c r="A67" s="23" t="s">
         <v>287</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="C67" s="22" t="s">
+      <c r="C67" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="D67" s="27" t="s">
+      <c r="D67" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E67" s="38" t="s">
+      <c r="E67" s="39" t="s">
         <v>1071</v>
       </c>
       <c r="F67" s="7" t="s">
@@ -20014,55 +20016,55 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="22" t="s">
+      <c r="A68" s="23" t="s">
         <v>287</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>1206</v>
       </c>
-      <c r="C68" s="22" t="s">
+      <c r="C68" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="D68" s="27" t="s">
+      <c r="D68" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E68" s="38" t="s">
+      <c r="E68" s="39" t="s">
         <v>1239</v>
       </c>
       <c r="H68" s="9"/>
     </row>
     <row r="69" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="22" t="s">
+      <c r="A69" s="23" t="s">
         <v>287</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>1206</v>
       </c>
-      <c r="C69" s="22" t="s">
+      <c r="C69" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="D69" s="27" t="s">
+      <c r="D69" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E69" s="38" t="s">
+      <c r="E69" s="39" t="s">
         <v>1240</v>
       </c>
       <c r="H69" s="9"/>
     </row>
     <row r="70" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="22" t="s">
+      <c r="A70" s="23" t="s">
         <v>287</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>1206</v>
       </c>
-      <c r="C70" s="22" t="s">
+      <c r="C70" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="D70" s="27" t="s">
+      <c r="D70" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E70" s="38" t="s">
+      <c r="E70" s="39" t="s">
         <v>1241</v>
       </c>
       <c r="F70" s="7" t="s">
@@ -20078,27 +20080,27 @@
       <c r="C71" s="7" t="s">
         <v>1243</v>
       </c>
-      <c r="D71" s="27" t="s">
+      <c r="D71" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E71" s="38" t="s">
+      <c r="E71" s="39" t="s">
         <v>1244</v>
       </c>
       <c r="F71" s="7"/>
       <c r="G71" s="7"/>
     </row>
     <row r="72" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="22" t="s">
+      <c r="A72" s="23" t="s">
         <v>919</v>
       </c>
       <c r="B72" s="7"/>
-      <c r="C72" s="22" t="s">
+      <c r="C72" s="23" t="s">
         <v>912</v>
       </c>
-      <c r="D72" s="27" t="s">
+      <c r="D72" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E72" s="38" t="s">
+      <c r="E72" s="39" t="s">
         <v>1208</v>
       </c>
       <c r="F72" s="7"/>
@@ -20106,14 +20108,14 @@
       <c r="H72" s="7"/>
     </row>
     <row r="73" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="22" t="s">
+      <c r="A73" s="23" t="s">
         <v>897</v>
       </c>
       <c r="B73" s="7"/>
       <c r="C73" s="7" t="s">
         <v>884</v>
       </c>
-      <c r="D73" s="27" t="s">
+      <c r="D73" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E73" s="7" t="s">
@@ -20131,10 +20133,10 @@
       <c r="C74" s="7" t="s">
         <v>1246</v>
       </c>
-      <c r="D74" s="27" t="s">
+      <c r="D74" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E74" s="38" t="s">
+      <c r="E74" s="39" t="s">
         <v>1247</v>
       </c>
       <c r="F74" s="7"/>
@@ -20148,13 +20150,13 @@
       <c r="B75" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="C75" s="22" t="s">
+      <c r="C75" s="23" t="s">
         <v>1217</v>
       </c>
-      <c r="D75" s="27" t="s">
+      <c r="D75" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E75" s="35" t="s">
+      <c r="E75" s="36" t="s">
         <v>1220</v>
       </c>
       <c r="F75" s="7"/>
@@ -20162,14 +20164,14 @@
       <c r="H75" s="7"/>
     </row>
     <row r="76" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="40" t="s">
+      <c r="A76" s="41" t="s">
         <v>404</v>
       </c>
       <c r="B76" s="7"/>
       <c r="C76" s="7" t="s">
         <v>1248</v>
       </c>
-      <c r="D76" s="27" t="s">
+      <c r="D76" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E76" s="7" t="s">
@@ -20180,7 +20182,7 @@
       <c r="H76" s="7"/>
     </row>
     <row r="77" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="40" t="s">
+      <c r="A77" s="41" t="s">
         <v>404</v>
       </c>
       <c r="B77" s="7" t="s">
@@ -20189,7 +20191,7 @@
       <c r="C77" s="7" t="s">
         <v>1249</v>
       </c>
-      <c r="D77" s="27" t="s">
+      <c r="D77" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E77" s="7" t="s">
@@ -20200,85 +20202,85 @@
       <c r="H77" s="7"/>
     </row>
     <row r="78" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="22" t="s">
+      <c r="A78" s="23" t="s">
         <v>430</v>
       </c>
-      <c r="C78" s="22" t="s">
+      <c r="C78" s="23" t="s">
         <v>1250</v>
       </c>
-      <c r="D78" s="27" t="s">
+      <c r="D78" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E78" s="35" t="s">
+      <c r="E78" s="36" t="s">
         <v>1251</v>
       </c>
       <c r="H78" s="9"/>
     </row>
     <row r="79" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="22" t="s">
+      <c r="A79" s="23" t="s">
         <v>430</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>1206</v>
       </c>
-      <c r="C79" s="22" t="s">
+      <c r="C79" s="23" t="s">
         <v>1250</v>
       </c>
-      <c r="D79" s="27" t="s">
+      <c r="D79" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E79" s="35" t="s">
+      <c r="E79" s="36" t="s">
         <v>1252</v>
       </c>
       <c r="H79" s="9"/>
     </row>
     <row r="80" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="22" t="s">
+      <c r="A80" s="23" t="s">
         <v>437</v>
       </c>
-      <c r="C80" s="22" t="s">
+      <c r="C80" s="23" t="s">
         <v>1250</v>
       </c>
-      <c r="D80" s="27" t="s">
+      <c r="D80" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E80" s="35" t="s">
+      <c r="E80" s="36" t="s">
         <v>1252</v>
       </c>
       <c r="H80" s="9"/>
     </row>
     <row r="81" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="22" t="s">
+      <c r="A81" s="23" t="s">
         <v>437</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="C81" s="22" t="s">
+      <c r="C81" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="D81" s="34" t="s">
+      <c r="D81" s="35" t="s">
         <v>1183</v>
       </c>
-      <c r="E81" s="22" t="n">
+      <c r="E81" s="23" t="n">
         <v>2</v>
       </c>
       <c r="H81" s="9"/>
     </row>
     <row r="82" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="22" t="s">
+      <c r="A82" s="23" t="s">
         <v>437</v>
       </c>
-      <c r="B82" s="22" t="s">
+      <c r="B82" s="23" t="s">
         <v>1191</v>
       </c>
-      <c r="C82" s="22" t="s">
+      <c r="C82" s="23" t="s">
         <v>1253</v>
       </c>
-      <c r="D82" s="27" t="s">
+      <c r="D82" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E82" s="38" t="s">
+      <c r="E82" s="39" t="s">
         <v>1244</v>
       </c>
       <c r="H82" s="9"/>
@@ -20290,10 +20292,10 @@
       <c r="C83" s="7" t="s">
         <v>1254</v>
       </c>
-      <c r="D83" s="27" t="s">
+      <c r="D83" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E83" s="38" t="s">
+      <c r="E83" s="39" t="s">
         <v>1255</v>
       </c>
       <c r="H83" s="9"/>
@@ -20305,10 +20307,10 @@
       <c r="C84" s="7" t="s">
         <v>1254</v>
       </c>
-      <c r="D84" s="27" t="s">
+      <c r="D84" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E84" s="38" t="s">
+      <c r="E84" s="39" t="s">
         <v>1256</v>
       </c>
       <c r="H84" s="9"/>
@@ -20320,10 +20322,10 @@
       <c r="C85" s="7" t="s">
         <v>1254</v>
       </c>
-      <c r="D85" s="27" t="s">
+      <c r="D85" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E85" s="38" t="s">
+      <c r="E85" s="39" t="s">
         <v>1257</v>
       </c>
     </row>
@@ -20334,10 +20336,10 @@
       <c r="C86" s="7" t="s">
         <v>1254</v>
       </c>
-      <c r="D86" s="27" t="s">
+      <c r="D86" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E86" s="38" t="s">
+      <c r="E86" s="39" t="s">
         <v>1258</v>
       </c>
     </row>
@@ -20348,10 +20350,10 @@
       <c r="C87" s="7" t="s">
         <v>1259</v>
       </c>
-      <c r="D87" s="27" t="s">
+      <c r="D87" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E87" s="38" t="s">
+      <c r="E87" s="39" t="s">
         <v>1260</v>
       </c>
     </row>
@@ -20365,10 +20367,10 @@
       <c r="C88" s="7" t="s">
         <v>1261</v>
       </c>
-      <c r="D88" s="27" t="s">
+      <c r="D88" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E88" s="38" t="s">
+      <c r="E88" s="39" t="s">
         <v>1262</v>
       </c>
     </row>
@@ -20382,10 +20384,10 @@
       <c r="C89" s="7" t="s">
         <v>1259</v>
       </c>
-      <c r="D89" s="27" t="s">
+      <c r="D89" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E89" s="38" t="s">
+      <c r="E89" s="39" t="s">
         <v>1262</v>
       </c>
       <c r="F89" s="7" t="s">
@@ -20402,10 +20404,10 @@
       <c r="C90" s="7" t="s">
         <v>1261</v>
       </c>
-      <c r="D90" s="27" t="s">
+      <c r="D90" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E90" s="38" t="s">
+      <c r="E90" s="39" t="s">
         <v>1260</v>
       </c>
       <c r="F90" s="7" t="s">
@@ -20422,10 +20424,10 @@
       <c r="C91" s="7" t="s">
         <v>1259</v>
       </c>
-      <c r="D91" s="27" t="s">
+      <c r="D91" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E91" s="38" t="s">
+      <c r="E91" s="39" t="s">
         <v>1263</v>
       </c>
       <c r="F91" s="7" t="s">
@@ -20442,10 +20444,10 @@
       <c r="C92" s="7" t="s">
         <v>1261</v>
       </c>
-      <c r="D92" s="27" t="s">
+      <c r="D92" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E92" s="38" t="s">
+      <c r="E92" s="39" t="s">
         <v>1262</v>
       </c>
       <c r="F92" s="7" t="s">
@@ -20462,10 +20464,10 @@
       <c r="C93" s="7" t="s">
         <v>1259</v>
       </c>
-      <c r="D93" s="27" t="s">
+      <c r="D93" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E93" s="38" t="s">
+      <c r="E93" s="39" t="s">
         <v>1262</v>
       </c>
       <c r="F93" s="7" t="s">
@@ -20484,10 +20486,10 @@
       <c r="C94" s="7" t="s">
         <v>1261</v>
       </c>
-      <c r="D94" s="27" t="s">
+      <c r="D94" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E94" s="38" t="s">
+      <c r="E94" s="39" t="s">
         <v>1263</v>
       </c>
       <c r="F94" s="7" t="s">
@@ -20506,10 +20508,10 @@
       <c r="C95" s="7" t="s">
         <v>1259</v>
       </c>
-      <c r="D95" s="27" t="s">
+      <c r="D95" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E95" s="38" t="s">
+      <c r="E95" s="39" t="s">
         <v>1264</v>
       </c>
       <c r="F95" s="7" t="s">
@@ -20528,10 +20530,10 @@
       <c r="C96" s="7" t="s">
         <v>1261</v>
       </c>
-      <c r="D96" s="27" t="s">
+      <c r="D96" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E96" s="38" t="s">
+      <c r="E96" s="39" t="s">
         <v>1262</v>
       </c>
       <c r="F96" s="7" t="s">
@@ -20550,10 +20552,10 @@
       <c r="C97" s="7" t="s">
         <v>1259</v>
       </c>
-      <c r="D97" s="27" t="s">
+      <c r="D97" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E97" s="38" t="s">
+      <c r="E97" s="39" t="s">
         <v>1262</v>
       </c>
       <c r="F97" s="7" t="s">
@@ -20572,10 +20574,10 @@
       <c r="C98" s="7" t="s">
         <v>1261</v>
       </c>
-      <c r="D98" s="27" t="s">
+      <c r="D98" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E98" s="38" t="s">
+      <c r="E98" s="39" t="s">
         <v>1264</v>
       </c>
       <c r="F98" s="7" t="s">
@@ -20589,13 +20591,13 @@
         <v>1265</v>
       </c>
       <c r="B99" s="7"/>
-      <c r="C99" s="22" t="s">
+      <c r="C99" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="D99" s="27" t="s">
+      <c r="D99" s="28" t="s">
         <v>1183</v>
       </c>
-      <c r="E99" s="38" t="n">
+      <c r="E99" s="39" t="n">
         <v>1</v>
       </c>
       <c r="F99" s="7"/>
@@ -20607,13 +20609,13 @@
         <v>1266</v>
       </c>
       <c r="B100" s="7"/>
-      <c r="C100" s="22" t="s">
+      <c r="C100" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="D100" s="27" t="s">
+      <c r="D100" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E100" s="38" t="n">
+      <c r="E100" s="39" t="n">
         <v>0</v>
       </c>
       <c r="F100" s="7"/>
@@ -20625,13 +20627,13 @@
         <v>810</v>
       </c>
       <c r="B101" s="7"/>
-      <c r="C101" s="22" t="s">
+      <c r="C101" s="23" t="s">
         <v>1267</v>
       </c>
-      <c r="D101" s="27" t="s">
+      <c r="D101" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E101" s="38" t="s">
+      <c r="E101" s="39" t="s">
         <v>1208</v>
       </c>
       <c r="F101" s="7"/>
@@ -20639,33 +20641,33 @@
       <c r="H101" s="7"/>
     </row>
     <row r="102" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="22" t="s">
+      <c r="A102" s="23" t="s">
         <v>140</v>
       </c>
       <c r="C102" s="7" t="s">
         <v>1268</v>
       </c>
-      <c r="D102" s="27" t="s">
+      <c r="D102" s="28" t="s">
         <v>1192</v>
       </c>
-      <c r="E102" s="38" t="n">
+      <c r="E102" s="39" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="103" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="22" t="s">
+      <c r="A103" s="23" t="s">
         <v>140</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="C103" s="22" t="s">
+      <c r="C103" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="D103" s="27" t="s">
+      <c r="D103" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E103" s="38" t="s">
+      <c r="E103" s="39" t="s">
         <v>1269</v>
       </c>
       <c r="F103" s="7" t="s">
@@ -20675,19 +20677,19 @@
       <c r="H103" s="7"/>
     </row>
     <row r="104" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="22" t="s">
+      <c r="A104" s="23" t="s">
         <v>140</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>1206</v>
       </c>
-      <c r="C104" s="22" t="s">
+      <c r="C104" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="D104" s="27" t="s">
+      <c r="D104" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E104" s="38" t="s">
+      <c r="E104" s="39" t="s">
         <v>1270</v>
       </c>
       <c r="F104" s="7"/>
@@ -20695,19 +20697,19 @@
       <c r="H104" s="7"/>
     </row>
     <row r="105" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="22" t="s">
+      <c r="A105" s="23" t="s">
         <v>140</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>1206</v>
       </c>
-      <c r="C105" s="22" t="s">
+      <c r="C105" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="D105" s="27" t="s">
+      <c r="D105" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E105" s="38" t="s">
+      <c r="E105" s="39" t="s">
         <v>1271</v>
       </c>
       <c r="F105" s="7" t="s">
@@ -20716,19 +20718,19 @@
       <c r="G105" s="7"/>
     </row>
     <row r="106" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="22" t="s">
+      <c r="A106" s="23" t="s">
         <v>140</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="C106" s="22" t="s">
+      <c r="C106" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="D106" s="27" t="s">
+      <c r="D106" s="28" t="s">
         <v>1183</v>
       </c>
-      <c r="E106" s="38" t="n">
+      <c r="E106" s="39" t="n">
         <v>1</v>
       </c>
       <c r="F106" s="7" t="s">
@@ -20737,19 +20739,19 @@
       <c r="H106" s="9"/>
     </row>
     <row r="107" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="22" t="s">
+      <c r="A107" s="23" t="s">
         <v>140</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>1206</v>
       </c>
-      <c r="C107" s="22" t="s">
+      <c r="C107" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="D107" s="27" t="s">
+      <c r="D107" s="28" t="s">
         <v>1183</v>
       </c>
-      <c r="E107" s="38" t="n">
+      <c r="E107" s="39" t="n">
         <v>1</v>
       </c>
       <c r="F107" s="7" t="s">
@@ -20758,34 +20760,34 @@
       <c r="H107" s="9"/>
     </row>
     <row r="108" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="22" t="s">
+      <c r="A108" s="23" t="s">
         <v>147</v>
       </c>
       <c r="C108" s="7" t="s">
         <v>1268</v>
       </c>
-      <c r="D108" s="27" t="s">
+      <c r="D108" s="28" t="s">
         <v>1192</v>
       </c>
-      <c r="E108" s="38" t="n">
+      <c r="E108" s="39" t="n">
         <v>2</v>
       </c>
       <c r="H108" s="9"/>
     </row>
     <row r="109" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="22" t="s">
+      <c r="A109" s="23" t="s">
         <v>147</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="C109" s="22" t="s">
+      <c r="C109" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="D109" s="27" t="s">
+      <c r="D109" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E109" s="38" t="s">
+      <c r="E109" s="39" t="s">
         <v>1269</v>
       </c>
       <c r="F109" s="7" t="s">
@@ -20794,38 +20796,38 @@
       <c r="H109" s="7"/>
     </row>
     <row r="110" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="22" t="s">
+      <c r="A110" s="23" t="s">
         <v>147</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>1206</v>
       </c>
-      <c r="C110" s="22" t="s">
+      <c r="C110" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="D110" s="27" t="s">
+      <c r="D110" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E110" s="38" t="s">
+      <c r="E110" s="39" t="s">
         <v>1270</v>
       </c>
       <c r="F110" s="7"/>
       <c r="G110" s="7"/>
     </row>
     <row r="111" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="22" t="s">
+      <c r="A111" s="23" t="s">
         <v>147</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>1206</v>
       </c>
-      <c r="C111" s="22" t="s">
+      <c r="C111" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="D111" s="27" t="s">
+      <c r="D111" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E111" s="38" t="s">
+      <c r="E111" s="39" t="s">
         <v>1271</v>
       </c>
       <c r="F111" s="7" t="s">
@@ -20834,38 +20836,38 @@
       <c r="G111" s="7"/>
     </row>
     <row r="112" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="22" t="s">
+      <c r="A112" s="23" t="s">
         <v>147</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="C112" s="22" t="s">
+      <c r="C112" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="D112" s="27" t="s">
+      <c r="D112" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E112" s="38" t="n">
+      <c r="E112" s="39" t="n">
         <v>0</v>
       </c>
       <c r="F112" s="7"/>
       <c r="G112" s="7"/>
     </row>
     <row r="113" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="22" t="s">
+      <c r="A113" s="23" t="s">
         <v>147</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="C113" s="22" t="s">
+      <c r="C113" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="D113" s="27" t="s">
+      <c r="D113" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E113" s="38" t="n">
+      <c r="E113" s="39" t="n">
         <v>0</v>
       </c>
       <c r="F113" s="7"/>
@@ -20876,13 +20878,13 @@
       <c r="A114" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C114" s="22" t="s">
+      <c r="C114" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="D114" s="34" t="s">
+      <c r="D114" s="35" t="s">
         <v>1183</v>
       </c>
-      <c r="E114" s="22" t="n">
+      <c r="E114" s="23" t="n">
         <v>2</v>
       </c>
       <c r="G114" s="7" t="s">
@@ -20899,25 +20901,25 @@
       <c r="C115" s="7" t="s">
         <v>1268</v>
       </c>
-      <c r="D115" s="27" t="s">
+      <c r="D115" s="28" t="s">
         <v>1192</v>
       </c>
-      <c r="E115" s="38" t="n">
+      <c r="E115" s="39" t="n">
         <v>6</v>
       </c>
       <c r="H115" s="9"/>
     </row>
-    <row r="116" s="41" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" s="42" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="C116" s="22" t="s">
+      <c r="C116" s="23" t="s">
         <v>1190</v>
       </c>
-      <c r="D116" s="34" t="s">
+      <c r="D116" s="35" t="s">
         <v>1183</v>
       </c>
-      <c r="E116" s="22" t="n">
+      <c r="E116" s="23" t="n">
         <v>19</v>
       </c>
       <c r="F116" s="7"/>
@@ -20930,13 +20932,13 @@
       <c r="B117" s="9" t="s">
         <v>1191</v>
       </c>
-      <c r="C117" s="22" t="s">
+      <c r="C117" s="23" t="s">
         <v>1207</v>
       </c>
-      <c r="D117" s="34" t="s">
+      <c r="D117" s="35" t="s">
         <v>1182</v>
       </c>
-      <c r="E117" s="22" t="s">
+      <c r="E117" s="23" t="s">
         <v>1208</v>
       </c>
       <c r="H117" s="9"/>
@@ -20948,13 +20950,13 @@
       <c r="B118" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="C118" s="22" t="s">
+      <c r="C118" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="D118" s="27" t="s">
+      <c r="D118" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E118" s="38" t="s">
+      <c r="E118" s="39" t="s">
         <v>1208</v>
       </c>
       <c r="F118" s="7" t="s">
@@ -20971,10 +20973,10 @@
       <c r="C119" s="7" t="s">
         <v>1268</v>
       </c>
-      <c r="D119" s="27" t="s">
+      <c r="D119" s="28" t="s">
         <v>1192</v>
       </c>
-      <c r="E119" s="38" t="n">
+      <c r="E119" s="39" t="n">
         <v>6</v>
       </c>
     </row>
@@ -20985,13 +20987,13 @@
       <c r="B120" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="C120" s="22" t="s">
+      <c r="C120" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="D120" s="34" t="s">
+      <c r="D120" s="35" t="s">
         <v>1182</v>
       </c>
-      <c r="E120" s="22" t="n">
+      <c r="E120" s="23" t="n">
         <v>1</v>
       </c>
       <c r="F120" s="7" t="s">
@@ -21002,13 +21004,13 @@
       <c r="A121" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="C121" s="22" t="s">
+      <c r="C121" s="23" t="s">
         <v>1190</v>
       </c>
-      <c r="D121" s="34" t="s">
+      <c r="D121" s="35" t="s">
         <v>1183</v>
       </c>
-      <c r="E121" s="22" t="n">
+      <c r="E121" s="23" t="n">
         <v>14</v>
       </c>
     </row>
@@ -21019,13 +21021,13 @@
       <c r="B122" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="C122" s="22" t="s">
+      <c r="C122" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="D122" s="27" t="s">
+      <c r="D122" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E122" s="38" t="s">
+      <c r="E122" s="39" t="s">
         <v>1208</v>
       </c>
       <c r="F122" s="7" t="s">
@@ -21043,10 +21045,10 @@
       <c r="C123" s="7" t="s">
         <v>1268</v>
       </c>
-      <c r="D123" s="27" t="s">
+      <c r="D123" s="28" t="s">
         <v>1192</v>
       </c>
-      <c r="E123" s="38" t="n">
+      <c r="E123" s="39" t="n">
         <v>6</v>
       </c>
       <c r="H123" s="9"/>
@@ -21058,13 +21060,13 @@
       <c r="B124" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="C124" s="22" t="s">
+      <c r="C124" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="D124" s="34" t="s">
+      <c r="D124" s="35" t="s">
         <v>1182</v>
       </c>
-      <c r="E124" s="22" t="n">
+      <c r="E124" s="23" t="n">
         <v>1</v>
       </c>
       <c r="F124" s="7" t="s">
@@ -21076,33 +21078,33 @@
       <c r="A125" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="C125" s="22" t="s">
+      <c r="C125" s="23" t="s">
         <v>1272</v>
       </c>
-      <c r="D125" s="27" t="s">
+      <c r="D125" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E125" s="38" t="s">
+      <c r="E125" s="39" t="s">
         <v>1208</v>
       </c>
       <c r="H125" s="9"/>
     </row>
     <row r="126" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="22" t="s">
+      <c r="A126" s="23" t="s">
         <v>222</v>
       </c>
-      <c r="C126" s="22" t="s">
+      <c r="C126" s="23" t="s">
         <v>1190</v>
       </c>
-      <c r="D126" s="34" t="s">
+      <c r="D126" s="35" t="s">
         <v>1183</v>
       </c>
-      <c r="E126" s="22" t="n">
+      <c r="E126" s="23" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="22" t="s">
+      <c r="A127" s="23" t="s">
         <v>222</v>
       </c>
       <c r="B127" s="7" t="s">
@@ -21111,10 +21113,10 @@
       <c r="C127" s="7" t="s">
         <v>1243</v>
       </c>
-      <c r="D127" s="27" t="s">
+      <c r="D127" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E127" s="38" t="s">
+      <c r="E127" s="39" t="s">
         <v>1208</v>
       </c>
     </row>
@@ -21122,13 +21124,13 @@
       <c r="A128" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="C128" s="22" t="s">
+      <c r="C128" s="23" t="s">
         <v>1273</v>
       </c>
-      <c r="D128" s="27" t="s">
+      <c r="D128" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E128" s="38" t="s">
+      <c r="E128" s="39" t="s">
         <v>1274</v>
       </c>
     </row>
@@ -21142,7 +21144,7 @@
       <c r="C129" s="9" t="s">
         <v>1273</v>
       </c>
-      <c r="D129" s="42" t="s">
+      <c r="D129" s="43" t="s">
         <v>1182</v>
       </c>
       <c r="E129" s="9" t="s">
@@ -21159,7 +21161,7 @@
       <c r="C130" s="7" t="s">
         <v>827</v>
       </c>
-      <c r="D130" s="27" t="s">
+      <c r="D130" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E130" s="7" t="s">
@@ -21173,7 +21175,7 @@
       <c r="C131" s="7" t="s">
         <v>1237</v>
       </c>
-      <c r="D131" s="27" t="s">
+      <c r="D131" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E131" s="7" t="s">
@@ -21187,7 +21189,7 @@
       <c r="C132" s="7" t="s">
         <v>861</v>
       </c>
-      <c r="D132" s="27" t="s">
+      <c r="D132" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E132" s="7" t="s">
@@ -21195,96 +21197,96 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="43" t="s">
+      <c r="A133" s="44" t="s">
         <v>1076</v>
       </c>
-      <c r="B133" s="44"/>
-      <c r="C133" s="43" t="s">
+      <c r="B133" s="45"/>
+      <c r="C133" s="44" t="s">
         <v>1237</v>
       </c>
-      <c r="D133" s="45" t="s">
+      <c r="D133" s="46" t="s">
         <v>1182</v>
       </c>
-      <c r="E133" s="46" t="s">
+      <c r="E133" s="47" t="s">
         <v>1071</v>
       </c>
-      <c r="F133" s="44"/>
+      <c r="F133" s="45"/>
     </row>
     <row r="134" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="22" t="s">
+      <c r="A134" s="23" t="s">
         <v>1076</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="C134" s="22" t="s">
+      <c r="C134" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="D134" s="34" t="s">
+      <c r="D134" s="35" t="s">
         <v>1183</v>
       </c>
-      <c r="E134" s="22" t="n">
+      <c r="E134" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H134" s="44" t="s">
+      <c r="H134" s="45" t="s">
         <v>1276</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="22" t="s">
+      <c r="A135" s="23" t="s">
         <v>1081</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>1073</v>
       </c>
-      <c r="D135" s="27" t="s">
+      <c r="D135" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E135" s="38" t="s">
+      <c r="E135" s="39" t="s">
         <v>1277</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="43" t="s">
+      <c r="A136" s="44" t="s">
         <v>1105</v>
       </c>
-      <c r="B136" s="44"/>
-      <c r="C136" s="43" t="s">
+      <c r="B136" s="45"/>
+      <c r="C136" s="44" t="s">
         <v>1237</v>
       </c>
-      <c r="D136" s="45" t="s">
+      <c r="D136" s="46" t="s">
         <v>1182</v>
       </c>
-      <c r="E136" s="46" t="s">
+      <c r="E136" s="47" t="s">
         <v>1241</v>
       </c>
-      <c r="F136" s="44"/>
-      <c r="H136" s="44" t="s">
+      <c r="F136" s="45"/>
+      <c r="H136" s="45" t="s">
         <v>1278</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="22" t="s">
+      <c r="A137" s="23" t="s">
         <v>1112</v>
       </c>
-      <c r="C137" s="22" t="s">
+      <c r="C137" s="23" t="s">
         <v>1101</v>
       </c>
-      <c r="D137" s="47" t="s">
+      <c r="D137" s="48" t="s">
         <v>1182</v>
       </c>
-      <c r="E137" s="38" t="s">
+      <c r="E137" s="39" t="s">
         <v>1244</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="22" t="s">
+      <c r="A138" s="23" t="s">
         <v>1057</v>
       </c>
       <c r="C138" s="7" t="s">
         <v>1279</v>
       </c>
-      <c r="D138" s="27" t="s">
+      <c r="D138" s="28" t="s">
         <v>1199</v>
       </c>
       <c r="E138" s="7" t="s">
@@ -21298,7 +21300,7 @@
       <c r="C139" s="3" t="s">
         <v>929</v>
       </c>
-      <c r="D139" s="27" t="s">
+      <c r="D139" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E139" s="7" t="s">
@@ -21306,21 +21308,21 @@
       </c>
     </row>
     <row r="140" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="22" t="s">
+      <c r="A140" s="23" t="s">
         <v>349</v>
       </c>
       <c r="C140" s="7" t="s">
         <v>1209</v>
       </c>
-      <c r="D140" s="27" t="s">
+      <c r="D140" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E140" s="27" t="s">
+      <c r="E140" s="28" t="s">
         <v>1210</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="22" t="s">
+      <c r="A141" s="23" t="s">
         <v>349</v>
       </c>
       <c r="B141" s="7" t="s">
@@ -21329,15 +21331,15 @@
       <c r="C141" s="7" t="s">
         <v>1209</v>
       </c>
-      <c r="D141" s="27" t="s">
+      <c r="D141" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E141" s="27" t="s">
+      <c r="E141" s="28" t="s">
         <v>1211</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="22" t="s">
+      <c r="A142" s="23" t="s">
         <v>349</v>
       </c>
       <c r="B142" s="7" t="s">
@@ -21346,15 +21348,15 @@
       <c r="C142" s="7" t="s">
         <v>1209</v>
       </c>
-      <c r="D142" s="27" t="s">
+      <c r="D142" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E142" s="27" t="s">
+      <c r="E142" s="28" t="s">
         <v>1212</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="22" t="s">
+      <c r="A143" s="23" t="s">
         <v>349</v>
       </c>
       <c r="B143" s="7" t="s">
@@ -21363,15 +21365,15 @@
       <c r="C143" s="7" t="s">
         <v>1209</v>
       </c>
-      <c r="D143" s="27" t="s">
+      <c r="D143" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E143" s="35" t="s">
+      <c r="E143" s="36" t="s">
         <v>1280</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="22" t="s">
+      <c r="A144" s="23" t="s">
         <v>349</v>
       </c>
       <c r="B144" s="7" t="s">
@@ -21380,7 +21382,7 @@
       <c r="C144" s="7" t="s">
         <v>1209</v>
       </c>
-      <c r="D144" s="27" t="s">
+      <c r="D144" s="28" t="s">
         <v>1182</v>
       </c>
       <c r="E144" s="7" t="s">
@@ -21391,13 +21393,13 @@
       <c r="A145" s="7" t="s">
         <v>1131</v>
       </c>
-      <c r="C145" s="22" t="s">
+      <c r="C145" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="D145" s="27" t="s">
+      <c r="D145" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E145" s="38" t="s">
+      <c r="E145" s="39" t="s">
         <v>1282</v>
       </c>
     </row>
@@ -21408,10 +21410,10 @@
       <c r="C146" s="7" t="s">
         <v>1283</v>
       </c>
-      <c r="D146" s="42" t="s">
+      <c r="D146" s="43" t="s">
         <v>1182</v>
       </c>
-      <c r="E146" s="42" t="s">
+      <c r="E146" s="43" t="s">
         <v>1284</v>
       </c>
     </row>
@@ -21422,10 +21424,10 @@
       <c r="C147" s="7" t="s">
         <v>1283</v>
       </c>
-      <c r="D147" s="42" t="s">
+      <c r="D147" s="43" t="s">
         <v>1182</v>
       </c>
-      <c r="E147" s="42" t="s">
+      <c r="E147" s="43" t="s">
         <v>1284</v>
       </c>
     </row>
@@ -21439,7 +21441,7 @@
       <c r="C148" s="7" t="s">
         <v>1283</v>
       </c>
-      <c r="D148" s="42" t="s">
+      <c r="D148" s="43" t="s">
         <v>1182</v>
       </c>
       <c r="E148" s="7" t="s">
@@ -21453,14 +21455,14 @@
       <c r="C149" s="7" t="s">
         <v>1285</v>
       </c>
-      <c r="D149" s="27" t="s">
+      <c r="D149" s="28" t="s">
         <v>1182</v>
       </c>
-      <c r="E149" s="42" t="s">
+      <c r="E149" s="43" t="s">
         <v>1286</v>
       </c>
     </row>
-    <row r="150" s="41" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" s="42" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="7" t="s">
         <v>763</v>
       </c>
@@ -21468,7 +21470,7 @@
       <c r="C150" s="7" t="s">
         <v>1287</v>
       </c>
-      <c r="D150" s="48" t="s">
+      <c r="D150" s="49" t="s">
         <v>1182</v>
       </c>
       <c r="E150" s="7" t="s">
@@ -21509,57 +21511,57 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="50" t="s">
         <v>1288</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="50" t="s">
         <v>1289</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="50" t="s">
         <v>1290</v>
       </c>
-      <c r="E1" s="49" t="s">
+      <c r="E1" s="50" t="s">
         <v>1291</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="50" t="s">
         <v>1292</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="51" t="s">
         <v>1293</v>
       </c>
-      <c r="H1" s="49" t="s">
+      <c r="H1" s="50" t="s">
         <v>1294</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="50" t="s">
         <v>1295</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="50" t="s">
         <v>1296</v>
       </c>
-      <c r="D2" s="49" t="s">
+      <c r="D2" s="50" t="s">
         <v>1297</v>
       </c>
-      <c r="E2" s="51" t="b">
+      <c r="E2" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F2" s="51" t="b">
+      <c r="F2" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G2" s="51" t="b">
+      <c r="G2" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="50" t="s">
         <v>48</v>
       </c>
     </row>
@@ -21576,15 +21578,15 @@
       <c r="D3" s="7" t="s">
         <v>1300</v>
       </c>
-      <c r="E3" s="51" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F3" s="51" t="b">
+      <c r="E3" s="52" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="F3" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G3" s="51" t="b">
+      <c r="G3" s="52" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -21602,15 +21604,15 @@
       <c r="D4" s="7" t="s">
         <v>1303</v>
       </c>
-      <c r="E4" s="51" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F4" s="51" t="b">
+      <c r="E4" s="52" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="F4" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G4" s="51" t="b">
+      <c r="G4" s="52" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -21628,15 +21630,15 @@
       <c r="D5" s="7" t="s">
         <v>1307</v>
       </c>
-      <c r="E5" s="51" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F5" s="51" t="b">
+      <c r="E5" s="52" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="F5" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G5" s="51" t="b">
+      <c r="G5" s="52" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -21654,15 +21656,15 @@
       <c r="D6" s="7" t="s">
         <v>1310</v>
       </c>
-      <c r="E6" s="51" t="b">
+      <c r="E6" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F6" s="51" t="b">
+      <c r="F6" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G6" s="51" t="b">
+      <c r="G6" s="52" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -21671,7 +21673,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="53" t="s">
         <v>361</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -21683,15 +21685,15 @@
       <c r="D7" s="7" t="s">
         <v>1307</v>
       </c>
-      <c r="E7" s="51" t="b">
+      <c r="E7" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F7" s="51" t="b">
+      <c r="F7" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G7" s="51" t="b">
+      <c r="G7" s="52" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -21700,7 +21702,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="53" t="s">
         <v>448</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -21712,15 +21714,15 @@
       <c r="D8" s="7" t="s">
         <v>1306</v>
       </c>
-      <c r="E8" s="51" t="b">
+      <c r="E8" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F8" s="51" t="b">
+      <c r="F8" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G8" s="51" t="b">
+      <c r="G8" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -21729,7 +21731,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="53" t="s">
         <v>559</v>
       </c>
       <c r="B9" s="7" t="s">
@@ -21741,15 +21743,15 @@
       <c r="D9" s="7" t="s">
         <v>1316</v>
       </c>
-      <c r="E9" s="51" t="b">
+      <c r="E9" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F9" s="51" t="b">
+      <c r="F9" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G9" s="51" t="b">
+      <c r="G9" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -21758,7 +21760,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="53" t="s">
         <v>743</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -21770,15 +21772,15 @@
       <c r="D10" s="7" t="s">
         <v>1319</v>
       </c>
-      <c r="E10" s="51" t="b">
+      <c r="E10" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F10" s="51" t="b">
+      <c r="F10" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G10" s="51" t="b">
+      <c r="G10" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -21787,7 +21789,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="53" t="s">
         <v>826</v>
       </c>
       <c r="B11" s="7" t="s">
@@ -21799,15 +21801,15 @@
       <c r="D11" s="7" t="s">
         <v>1322</v>
       </c>
-      <c r="E11" s="51" t="b">
+      <c r="E11" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F11" s="51" t="b">
+      <c r="F11" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G11" s="51" t="b">
+      <c r="G11" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -21828,15 +21830,15 @@
       <c r="D12" s="7" t="s">
         <v>1325</v>
       </c>
-      <c r="E12" s="51" t="b">
+      <c r="E12" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F12" s="51" t="b">
+      <c r="F12" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G12" s="51" t="b">
+      <c r="G12" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -21857,15 +21859,15 @@
       <c r="D13" s="7" t="s">
         <v>1328</v>
       </c>
-      <c r="E13" s="51" t="b">
+      <c r="E13" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F13" s="51" t="b">
+      <c r="F13" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G13" s="51" t="b">
+      <c r="G13" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -21886,15 +21888,15 @@
       <c r="D14" s="7" t="s">
         <v>1331</v>
       </c>
-      <c r="E14" s="51" t="b">
+      <c r="E14" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F14" s="51" t="b">
+      <c r="F14" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G14" s="51" t="b">
+      <c r="G14" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -21915,15 +21917,15 @@
       <c r="D15" s="7" t="s">
         <v>1334</v>
       </c>
-      <c r="E15" s="51" t="b">
+      <c r="E15" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F15" s="51" t="b">
+      <c r="F15" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G15" s="51" t="b">
+      <c r="G15" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -21944,15 +21946,15 @@
       <c r="D16" s="7" t="s">
         <v>1337</v>
       </c>
-      <c r="E16" s="51" t="b">
+      <c r="E16" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F16" s="51" t="b">
+      <c r="F16" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G16" s="51" t="b">
+      <c r="G16" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -21973,15 +21975,15 @@
       <c r="D17" s="9" t="s">
         <v>1328</v>
       </c>
-      <c r="E17" s="51" t="b">
+      <c r="E17" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F17" s="51" t="b">
+      <c r="F17" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G17" s="51" t="b">
+      <c r="G17" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -22002,15 +22004,15 @@
       <c r="D18" s="7" t="s">
         <v>1341</v>
       </c>
-      <c r="E18" s="51" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F18" s="51" t="b">
+      <c r="E18" s="52" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="F18" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G18" s="51" t="b">
+      <c r="G18" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -22028,15 +22030,15 @@
       <c r="D19" s="7" t="s">
         <v>1344</v>
       </c>
-      <c r="E19" s="51" t="b">
+      <c r="E19" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F19" s="51" t="b">
+      <c r="F19" s="52" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G19" s="51" t="b">
+      <c r="G19" s="52" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -22076,192 +22078,192 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="54" t="s">
         <v>1345</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="54" t="s">
         <v>1346</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="54" t="s">
         <v>1347</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="54" t="s">
         <v>1348</v>
       </c>
-      <c r="E1" s="53" t="s">
+      <c r="E1" s="54" t="s">
         <v>1349</v>
       </c>
-      <c r="F1" s="53" t="s">
+      <c r="F1" s="54" t="s">
         <v>1350</v>
       </c>
-      <c r="G1" s="53" t="s">
+      <c r="G1" s="54" t="s">
         <v>1351</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="54" t="s">
         <v>1352</v>
       </c>
-      <c r="I1" s="53" t="s">
+      <c r="I1" s="54" t="s">
         <v>1353</v>
       </c>
-      <c r="J1" s="53" t="s">
+      <c r="J1" s="54" t="s">
         <v>1354</v>
       </c>
-      <c r="K1" s="53" t="s">
+      <c r="K1" s="54" t="s">
         <v>1355</v>
       </c>
-      <c r="L1" s="53" t="s">
+      <c r="L1" s="54" t="s">
         <v>1356</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="23" t="s">
         <v>1147</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="23" t="s">
         <v>1357</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="23" t="s">
         <v>1358</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="23" t="s">
         <v>1359</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="23" t="s">
         <v>1360</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="23" t="s">
         <v>1361</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="23" t="s">
         <v>1362</v>
       </c>
-      <c r="H2" s="22" t="n">
+      <c r="H2" s="23" t="n">
         <v>-10</v>
       </c>
-      <c r="I2" s="22" t="n">
+      <c r="I2" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="J2" s="23" t="s">
         <v>1363</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="K2" s="23" t="s">
         <v>1363</v>
       </c>
-      <c r="L2" s="22" t="s">
+      <c r="L2" s="23" t="s">
         <v>1364</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="23" t="s">
         <v>1138</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="23" t="s">
         <v>1365</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="23" t="s">
         <v>1366</v>
       </c>
-      <c r="D3" s="54" t="s">
+      <c r="D3" s="55" t="s">
         <v>1367</v>
       </c>
-      <c r="E3" s="54" t="s">
+      <c r="E3" s="55" t="s">
         <v>1368</v>
       </c>
-      <c r="F3" s="54" t="s">
+      <c r="F3" s="55" t="s">
         <v>1369</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="23" t="s">
         <v>1370</v>
       </c>
-      <c r="H3" s="22" t="n">
+      <c r="H3" s="23" t="n">
         <v>-10</v>
       </c>
-      <c r="I3" s="22" t="n">
+      <c r="I3" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="J3" s="23" t="s">
         <v>1363</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="23" t="s">
         <v>1363</v>
       </c>
-      <c r="L3" s="22" t="s">
+      <c r="L3" s="23" t="s">
         <v>1371</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="23" t="s">
         <v>1152</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="23" t="s">
         <v>1372</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="23" t="s">
         <v>1373</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="23" t="s">
         <v>1374</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="23" t="s">
         <v>1375</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="23" t="s">
         <v>1376</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="23" t="s">
         <v>1377</v>
       </c>
-      <c r="H4" s="22" t="n">
+      <c r="H4" s="23" t="n">
         <v>-10</v>
       </c>
-      <c r="I4" s="22" t="n">
+      <c r="I4" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="J4" s="22" t="s">
+      <c r="J4" s="23" t="s">
         <v>1363</v>
       </c>
-      <c r="K4" s="22" t="s">
+      <c r="K4" s="23" t="s">
         <v>1363</v>
       </c>
-      <c r="L4" s="22" t="s">
+      <c r="L4" s="23" t="s">
         <v>1364</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="23" t="s">
         <v>1157</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="23" t="s">
         <v>1365</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="23" t="s">
         <v>1378</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="23" t="s">
         <v>1379</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="23" t="s">
         <v>1368</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="23" t="s">
         <v>1380</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="23" t="s">
         <v>1381</v>
       </c>
-      <c r="H5" s="22" t="n">
+      <c r="H5" s="23" t="n">
         <v>-10</v>
       </c>
-      <c r="I5" s="22" t="n">
+      <c r="I5" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="J5" s="23" t="s">
         <v>1363</v>
       </c>
-      <c r="K5" s="22" t="s">
+      <c r="K5" s="23" t="s">
         <v>1363</v>
       </c>
-      <c r="L5" s="22" t="s">
+      <c r="L5" s="23" t="s">
         <v>1364</v>
       </c>
     </row>
@@ -22305,10 +22307,10 @@
       <c r="D1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="55" t="s">
+      <c r="E1" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="55" t="s">
+      <c r="F1" s="56" t="s">
         <v>9</v>
       </c>
     </row>
@@ -22325,8 +22327,8 @@
       <c r="D2" s="9" t="s">
         <v>1386</v>
       </c>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
@@ -22341,8 +22343,8 @@
       <c r="D3" s="9" t="s">
         <v>1389</v>
       </c>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
@@ -22357,8 +22359,8 @@
       <c r="D4" s="9" t="s">
         <v>1392</v>
       </c>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
@@ -22373,8 +22375,8 @@
       <c r="D5" s="9" t="s">
         <v>1395</v>
       </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
@@ -22389,8 +22391,8 @@
       <c r="D6" s="9" t="s">
         <v>1398</v>
       </c>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
     </row>
     <row r="7" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
@@ -22405,14 +22407,14 @@
       <c r="D7" s="7" t="s">
         <v>1401</v>
       </c>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
     </row>
     <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="23" t="s">
         <v>1402</v>
       </c>
       <c r="C8" s="7" t="s">
@@ -22421,8 +22423,8 @@
       <c r="D8" s="7" t="s">
         <v>1404</v>
       </c>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
@@ -22437,14 +22439,14 @@
       <c r="D9" s="9" t="s">
         <v>1407</v>
       </c>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
     </row>
     <row r="10" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="23" t="s">
         <v>1408</v>
       </c>
       <c r="C10" s="7" t="s">
@@ -22453,14 +22455,14 @@
       <c r="D10" s="7" t="s">
         <v>1410</v>
       </c>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="23" t="s">
         <v>1411</v>
       </c>
       <c r="C11" s="9" t="s">
@@ -22469,14 +22471,14 @@
       <c r="D11" s="9" t="s">
         <v>1407</v>
       </c>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
     </row>
     <row r="12" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="23" t="s">
         <v>1412</v>
       </c>
       <c r="C12" s="7" t="s">
@@ -22485,14 +22487,14 @@
       <c r="D12" s="7" t="s">
         <v>1414</v>
       </c>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="23" t="s">
         <v>1415</v>
       </c>
       <c r="C13" s="9" t="s">
@@ -22501,14 +22503,14 @@
       <c r="D13" s="9" t="s">
         <v>1417</v>
       </c>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
     </row>
     <row r="14" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="23" t="s">
         <v>1418</v>
       </c>
       <c r="C14" s="7" t="s">
@@ -22517,14 +22519,14 @@
       <c r="D14" s="7" t="s">
         <v>1420</v>
       </c>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="23" t="s">
         <v>1421</v>
       </c>
       <c r="C15" s="9" t="s">
@@ -22533,14 +22535,14 @@
       <c r="D15" s="9" t="s">
         <v>1423</v>
       </c>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
     </row>
     <row r="16" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="23" t="s">
         <v>1424</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -22549,8 +22551,8 @@
       <c r="D16" s="7" t="s">
         <v>1426</v>
       </c>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
@@ -23091,10 +23093,10 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="35" t="s">
+      <c r="A55" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="B55" s="56" t="s">
+      <c r="B55" s="57" t="s">
         <v>1540</v>
       </c>
       <c r="C55" s="9" t="s">
@@ -23103,18 +23105,18 @@
       <c r="D55" s="9" t="s">
         <v>1542</v>
       </c>
-      <c r="E55" s="22" t="s">
+      <c r="E55" s="23" t="s">
         <v>1543</v>
       </c>
-      <c r="F55" s="22" t="s">
+      <c r="F55" s="23" t="s">
         <v>1544</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="35" t="s">
+      <c r="A56" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="B56" s="56" t="s">
+      <c r="B56" s="57" t="s">
         <v>1545</v>
       </c>
       <c r="C56" s="9" t="s">
@@ -23123,15 +23125,15 @@
       <c r="D56" s="9" t="s">
         <v>1547</v>
       </c>
-      <c r="E56" s="22" t="s">
+      <c r="E56" s="23" t="s">
         <v>1548</v>
       </c>
-      <c r="F56" s="56" t="s">
+      <c r="F56" s="57" t="s">
         <v>1549</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="35" t="s">
+      <c r="A57" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B57" s="7" t="s">
@@ -23143,15 +23145,15 @@
       <c r="D57" s="9" t="s">
         <v>1552</v>
       </c>
-      <c r="E57" s="22" t="s">
+      <c r="E57" s="23" t="s">
         <v>1553</v>
       </c>
-      <c r="F57" s="22" t="s">
+      <c r="F57" s="23" t="s">
         <v>1554</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="156.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="35" t="s">
+      <c r="A58" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B58" s="7" t="s">
@@ -23163,18 +23165,18 @@
       <c r="D58" s="9" t="s">
         <v>1557</v>
       </c>
-      <c r="E58" s="22" t="s">
+      <c r="E58" s="23" t="s">
         <v>1558</v>
       </c>
-      <c r="F58" s="22" t="s">
+      <c r="F58" s="23" t="s">
         <v>1559</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="35" t="s">
+      <c r="A59" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="B59" s="22" t="s">
+      <c r="B59" s="23" t="s">
         <v>1560</v>
       </c>
       <c r="C59" s="9" t="s">
@@ -23183,18 +23185,18 @@
       <c r="D59" s="9" t="s">
         <v>1562</v>
       </c>
-      <c r="E59" s="22" t="s">
+      <c r="E59" s="23" t="s">
         <v>1563</v>
       </c>
-      <c r="F59" s="22" t="s">
+      <c r="F59" s="23" t="s">
         <v>1564</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="35" t="s">
+      <c r="A60" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="B60" s="22" t="s">
+      <c r="B60" s="23" t="s">
         <v>1565</v>
       </c>
       <c r="C60" s="9" t="s">
@@ -23203,18 +23205,18 @@
       <c r="D60" s="9" t="s">
         <v>1567</v>
       </c>
-      <c r="E60" s="22" t="s">
+      <c r="E60" s="23" t="s">
         <v>1568</v>
       </c>
-      <c r="F60" s="22" t="s">
+      <c r="F60" s="23" t="s">
         <v>1569</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="35" t="s">
+      <c r="A61" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="B61" s="22" t="s">
+      <c r="B61" s="23" t="s">
         <v>1570</v>
       </c>
       <c r="C61" s="9" t="s">
@@ -23223,18 +23225,18 @@
       <c r="D61" s="9" t="s">
         <v>1572</v>
       </c>
-      <c r="E61" s="22" t="s">
+      <c r="E61" s="23" t="s">
         <v>1573</v>
       </c>
-      <c r="F61" s="22" t="s">
+      <c r="F61" s="23" t="s">
         <v>1574</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="35" t="s">
+      <c r="A62" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="B62" s="22" t="s">
+      <c r="B62" s="23" t="s">
         <v>1575</v>
       </c>
       <c r="C62" s="9" t="s">
@@ -23243,18 +23245,18 @@
       <c r="D62" s="9" t="s">
         <v>1577</v>
       </c>
-      <c r="E62" s="22" t="s">
+      <c r="E62" s="23" t="s">
         <v>1578</v>
       </c>
-      <c r="F62" s="22" t="s">
+      <c r="F62" s="23" t="s">
         <v>1579</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="35" t="s">
+      <c r="A63" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="B63" s="22" t="s">
+      <c r="B63" s="23" t="s">
         <v>1580</v>
       </c>
       <c r="C63" s="9" t="s">
@@ -23263,15 +23265,15 @@
       <c r="D63" s="9" t="s">
         <v>1582</v>
       </c>
-      <c r="E63" s="22" t="s">
+      <c r="E63" s="23" t="s">
         <v>1583</v>
       </c>
-      <c r="F63" s="22" t="s">
+      <c r="F63" s="23" t="s">
         <v>1584</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="35" t="s">
+      <c r="A64" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B64" s="7" t="s">
@@ -23283,18 +23285,18 @@
       <c r="D64" s="9" t="s">
         <v>1587</v>
       </c>
-      <c r="E64" s="22" t="s">
+      <c r="E64" s="23" t="s">
         <v>1588</v>
       </c>
-      <c r="F64" s="22" t="s">
+      <c r="F64" s="23" t="s">
         <v>1589</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="35" t="s">
+      <c r="A65" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="B65" s="22" t="s">
+      <c r="B65" s="23" t="s">
         <v>1590</v>
       </c>
       <c r="C65" s="9" t="s">
@@ -23303,15 +23305,15 @@
       <c r="D65" s="9" t="s">
         <v>1592</v>
       </c>
-      <c r="E65" s="22" t="s">
+      <c r="E65" s="23" t="s">
         <v>1593</v>
       </c>
-      <c r="F65" s="22" t="s">
+      <c r="F65" s="23" t="s">
         <v>1594</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="35" t="s">
+      <c r="A66" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B66" s="7" t="s">
@@ -23323,15 +23325,15 @@
       <c r="D66" s="9" t="s">
         <v>1597</v>
       </c>
-      <c r="E66" s="22" t="s">
+      <c r="E66" s="23" t="s">
         <v>1598</v>
       </c>
-      <c r="F66" s="22" t="s">
+      <c r="F66" s="23" t="s">
         <v>1599</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="35" t="s">
+      <c r="A67" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B67" s="7" t="s">
@@ -23343,15 +23345,15 @@
       <c r="D67" s="9" t="s">
         <v>1602</v>
       </c>
-      <c r="E67" s="22" t="s">
+      <c r="E67" s="23" t="s">
         <v>1603</v>
       </c>
-      <c r="F67" s="22" t="s">
+      <c r="F67" s="23" t="s">
         <v>1604</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="35" t="s">
+      <c r="A68" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B68" s="7" t="s">
@@ -23363,8 +23365,8 @@
       <c r="D68" s="9" t="s">
         <v>1607</v>
       </c>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
+      <c r="E68" s="23"/>
+      <c r="F68" s="23"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="9" t="s">
@@ -23381,7 +23383,7 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="35" t="s">
+      <c r="A70" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B70" s="7" t="s">
@@ -23393,11 +23395,11 @@
       <c r="D70" s="9" t="s">
         <v>1613</v>
       </c>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
+      <c r="E70" s="23"/>
+      <c r="F70" s="23"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="35" t="s">
+      <c r="A71" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B71" s="7" t="s">
@@ -23409,11 +23411,11 @@
       <c r="D71" s="9" t="s">
         <v>1616</v>
       </c>
-      <c r="E71" s="22"/>
-      <c r="F71" s="22"/>
+      <c r="E71" s="23"/>
+      <c r="F71" s="23"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="35" t="s">
+      <c r="A72" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B72" s="7" t="s">
@@ -23425,11 +23427,11 @@
       <c r="D72" s="9" t="s">
         <v>1619</v>
       </c>
-      <c r="E72" s="22"/>
-      <c r="F72" s="22"/>
+      <c r="E72" s="23"/>
+      <c r="F72" s="23"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="35" t="s">
+      <c r="A73" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B73" s="7" t="s">
@@ -23441,11 +23443,11 @@
       <c r="D73" s="9" t="s">
         <v>1622</v>
       </c>
-      <c r="E73" s="22"/>
-      <c r="F73" s="22"/>
+      <c r="E73" s="23"/>
+      <c r="F73" s="23"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="35" t="s">
+      <c r="A74" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B74" s="7" t="s">
@@ -23457,11 +23459,11 @@
       <c r="D74" s="9" t="s">
         <v>1625</v>
       </c>
-      <c r="E74" s="22"/>
-      <c r="F74" s="22"/>
+      <c r="E74" s="23"/>
+      <c r="F74" s="23"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="35" t="s">
+      <c r="A75" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B75" s="7" t="s">
@@ -23473,11 +23475,11 @@
       <c r="D75" s="9" t="s">
         <v>1300</v>
       </c>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
+      <c r="E75" s="23"/>
+      <c r="F75" s="23"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="35" t="s">
+      <c r="A76" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B76" s="7" t="s">
@@ -23489,11 +23491,11 @@
       <c r="D76" s="9" t="s">
         <v>1629</v>
       </c>
-      <c r="E76" s="22"/>
-      <c r="F76" s="22"/>
+      <c r="E76" s="23"/>
+      <c r="F76" s="23"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="35" t="s">
+      <c r="A77" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B77" s="7" t="s">
@@ -23505,11 +23507,11 @@
       <c r="D77" s="9" t="s">
         <v>1632</v>
       </c>
-      <c r="E77" s="22"/>
-      <c r="F77" s="22"/>
+      <c r="E77" s="23"/>
+      <c r="F77" s="23"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="35" t="s">
+      <c r="A78" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B78" s="7" t="s">
@@ -23521,11 +23523,11 @@
       <c r="D78" s="9" t="s">
         <v>1635</v>
       </c>
-      <c r="E78" s="22"/>
-      <c r="F78" s="22"/>
+      <c r="E78" s="23"/>
+      <c r="F78" s="23"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="35" t="s">
+      <c r="A79" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B79" s="7" t="s">
@@ -23537,11 +23539,11 @@
       <c r="D79" s="9" t="s">
         <v>1638</v>
       </c>
-      <c r="E79" s="22"/>
-      <c r="F79" s="22"/>
+      <c r="E79" s="23"/>
+      <c r="F79" s="23"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="35" t="s">
+      <c r="A80" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B80" s="7" t="s">
@@ -23553,11 +23555,11 @@
       <c r="D80" s="9" t="s">
         <v>1641</v>
       </c>
-      <c r="E80" s="22"/>
-      <c r="F80" s="22"/>
+      <c r="E80" s="23"/>
+      <c r="F80" s="23"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="35" t="s">
+      <c r="A81" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B81" s="7" t="s">
@@ -23569,11 +23571,11 @@
       <c r="D81" s="9" t="s">
         <v>1644</v>
       </c>
-      <c r="E81" s="22"/>
-      <c r="F81" s="22"/>
+      <c r="E81" s="23"/>
+      <c r="F81" s="23"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="35" t="s">
+      <c r="A82" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B82" s="7" t="s">
@@ -23585,11 +23587,11 @@
       <c r="D82" s="9" t="s">
         <v>1647</v>
       </c>
-      <c r="E82" s="22"/>
-      <c r="F82" s="22"/>
+      <c r="E82" s="23"/>
+      <c r="F82" s="23"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="35" t="s">
+      <c r="A83" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B83" s="7" t="s">
@@ -23601,11 +23603,11 @@
       <c r="D83" s="9" t="s">
         <v>1650</v>
       </c>
-      <c r="E83" s="22"/>
-      <c r="F83" s="22"/>
+      <c r="E83" s="23"/>
+      <c r="F83" s="23"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="35" t="s">
+      <c r="A84" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B84" s="7" t="s">
@@ -23617,11 +23619,11 @@
       <c r="D84" s="9" t="s">
         <v>1653</v>
       </c>
-      <c r="E84" s="22"/>
-      <c r="F84" s="22"/>
+      <c r="E84" s="23"/>
+      <c r="F84" s="23"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="35" t="s">
+      <c r="A85" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B85" s="7" t="s">
@@ -23633,11 +23635,11 @@
       <c r="D85" s="9" t="s">
         <v>1656</v>
       </c>
-      <c r="E85" s="22"/>
-      <c r="F85" s="22"/>
+      <c r="E85" s="23"/>
+      <c r="F85" s="23"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="35" t="s">
+      <c r="A86" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B86" s="7" t="s">
@@ -23649,11 +23651,11 @@
       <c r="D86" s="9" t="s">
         <v>1659</v>
       </c>
-      <c r="E86" s="22"/>
-      <c r="F86" s="22"/>
+      <c r="E86" s="23"/>
+      <c r="F86" s="23"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="35" t="s">
+      <c r="A87" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B87" s="7" t="s">
@@ -23665,11 +23667,11 @@
       <c r="D87" s="9" t="s">
         <v>1662</v>
       </c>
-      <c r="E87" s="22"/>
-      <c r="F87" s="22"/>
+      <c r="E87" s="23"/>
+      <c r="F87" s="23"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="35" t="s">
+      <c r="A88" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B88" s="7" t="s">
@@ -23681,11 +23683,11 @@
       <c r="D88" s="9" t="s">
         <v>1665</v>
       </c>
-      <c r="E88" s="22"/>
-      <c r="F88" s="22"/>
+      <c r="E88" s="23"/>
+      <c r="F88" s="23"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="35" t="s">
+      <c r="A89" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B89" s="7" t="s">
@@ -23697,11 +23699,11 @@
       <c r="D89" s="9" t="s">
         <v>1622</v>
       </c>
-      <c r="E89" s="22"/>
-      <c r="F89" s="22"/>
+      <c r="E89" s="23"/>
+      <c r="F89" s="23"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="35" t="s">
+      <c r="A90" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B90" s="7" t="s">
@@ -23713,11 +23715,11 @@
       <c r="D90" s="9" t="s">
         <v>1669</v>
       </c>
-      <c r="E90" s="22"/>
-      <c r="F90" s="22"/>
+      <c r="E90" s="23"/>
+      <c r="F90" s="23"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="35" t="s">
+      <c r="A91" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B91" s="7" t="s">
@@ -23729,11 +23731,11 @@
       <c r="D91" s="9" t="s">
         <v>1672</v>
       </c>
-      <c r="E91" s="22"/>
-      <c r="F91" s="22"/>
+      <c r="E91" s="23"/>
+      <c r="F91" s="23"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="35" t="s">
+      <c r="A92" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B92" s="7" t="s">
@@ -23745,11 +23747,11 @@
       <c r="D92" s="9" t="s">
         <v>1675</v>
       </c>
-      <c r="E92" s="22"/>
-      <c r="F92" s="22"/>
+      <c r="E92" s="23"/>
+      <c r="F92" s="23"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="35" t="s">
+      <c r="A93" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B93" s="7" t="s">
@@ -23761,11 +23763,11 @@
       <c r="D93" s="9" t="s">
         <v>1678</v>
       </c>
-      <c r="E93" s="22"/>
-      <c r="F93" s="22"/>
+      <c r="E93" s="23"/>
+      <c r="F93" s="23"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="35" t="s">
+      <c r="A94" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B94" s="7" t="s">
@@ -23777,27 +23779,27 @@
       <c r="D94" s="9" t="s">
         <v>1681</v>
       </c>
-      <c r="E94" s="22"/>
-      <c r="F94" s="22"/>
-    </row>
-    <row r="95" s="41" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="35" t="s">
+      <c r="E94" s="23"/>
+      <c r="F94" s="23"/>
+    </row>
+    <row r="95" s="42" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>1682</v>
       </c>
-      <c r="C95" s="41" t="s">
+      <c r="C95" s="42" t="s">
         <v>1683</v>
       </c>
-      <c r="D95" s="41" t="s">
+      <c r="D95" s="42" t="s">
         <v>1684</v>
       </c>
-      <c r="E95" s="22"/>
-      <c r="F95" s="22"/>
+      <c r="E95" s="23"/>
+      <c r="F95" s="23"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="35" t="s">
+      <c r="A96" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B96" s="7" t="s">
@@ -23809,11 +23811,11 @@
       <c r="D96" s="9" t="s">
         <v>1687</v>
       </c>
-      <c r="E96" s="22"/>
-      <c r="F96" s="22"/>
+      <c r="E96" s="23"/>
+      <c r="F96" s="23"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="35" t="s">
+      <c r="A97" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B97" s="7" t="s">
@@ -23825,11 +23827,11 @@
       <c r="D97" s="9" t="s">
         <v>1690</v>
       </c>
-      <c r="E97" s="22"/>
-      <c r="F97" s="22"/>
+      <c r="E97" s="23"/>
+      <c r="F97" s="23"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="35" t="s">
+      <c r="A98" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B98" s="7" t="s">
@@ -23841,11 +23843,11 @@
       <c r="D98" s="9" t="s">
         <v>1638</v>
       </c>
-      <c r="E98" s="22"/>
-      <c r="F98" s="22"/>
+      <c r="E98" s="23"/>
+      <c r="F98" s="23"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="35" t="s">
+      <c r="A99" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B99" s="7" t="s">
@@ -23857,11 +23859,11 @@
       <c r="D99" s="9" t="s">
         <v>1693</v>
       </c>
-      <c r="E99" s="22"/>
-      <c r="F99" s="22"/>
+      <c r="E99" s="23"/>
+      <c r="F99" s="23"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="35" t="s">
+      <c r="A100" s="36" t="s">
         <v>448</v>
       </c>
       <c r="B100" s="7" t="s">
@@ -23873,8 +23875,8 @@
       <c r="D100" s="9" t="s">
         <v>1696</v>
       </c>
-      <c r="E100" s="22"/>
-      <c r="F100" s="22"/>
+      <c r="E100" s="23"/>
+      <c r="F100" s="23"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="9" t="s">
@@ -24026,7 +24028,7 @@
       <c r="A111" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B111" s="57" t="s">
+      <c r="B111" s="58" t="s">
         <v>1727</v>
       </c>
       <c r="C111" s="9" t="s">
@@ -24088,7 +24090,7 @@
       <c r="A115" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B115" s="52" t="s">
+      <c r="B115" s="53" t="s">
         <v>1741</v>
       </c>
       <c r="C115" s="9" t="s">
@@ -24102,7 +24104,7 @@
       <c r="A116" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B116" s="52" t="s">
+      <c r="B116" s="53" t="s">
         <v>1744</v>
       </c>
       <c r="C116" s="9" t="s">
@@ -24169,10 +24171,10 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="58" t="s">
+      <c r="A121" s="59" t="s">
         <v>448</v>
       </c>
-      <c r="B121" s="38" t="s">
+      <c r="B121" s="39" t="s">
         <v>1759</v>
       </c>
       <c r="C121" s="9" t="s">
@@ -24181,14 +24183,14 @@
       <c r="D121" s="9" t="s">
         <v>1300</v>
       </c>
-      <c r="E121" s="38"/>
-      <c r="F121" s="38"/>
+      <c r="E121" s="39"/>
+      <c r="F121" s="39"/>
     </row>
     <row r="122" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="58" t="s">
+      <c r="A122" s="59" t="s">
         <v>448</v>
       </c>
-      <c r="B122" s="38" t="s">
+      <c r="B122" s="39" t="s">
         <v>1760</v>
       </c>
       <c r="C122" s="9" t="s">
@@ -24197,14 +24199,14 @@
       <c r="D122" s="9" t="s">
         <v>1700</v>
       </c>
-      <c r="E122" s="38"/>
-      <c r="F122" s="38"/>
+      <c r="E122" s="39"/>
+      <c r="F122" s="39"/>
     </row>
     <row r="123" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="58" t="s">
+      <c r="A123" s="59" t="s">
         <v>448</v>
       </c>
-      <c r="B123" s="38" t="s">
+      <c r="B123" s="39" t="s">
         <v>1761</v>
       </c>
       <c r="C123" s="9" t="s">
@@ -24213,11 +24215,11 @@
       <c r="D123" s="9" t="s">
         <v>1703</v>
       </c>
-      <c r="E123" s="38"/>
-      <c r="F123" s="38"/>
+      <c r="E123" s="39"/>
+      <c r="F123" s="39"/>
     </row>
     <row r="124" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="58" t="s">
+      <c r="A124" s="59" t="s">
         <v>448</v>
       </c>
       <c r="B124" s="7" t="s">
@@ -24293,10 +24295,10 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="58" t="s">
+      <c r="A129" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B129" s="38" t="s">
+      <c r="B129" s="39" t="s">
         <v>1775</v>
       </c>
       <c r="C129" s="9" t="s">
@@ -24313,10 +24315,10 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="58" t="s">
+      <c r="A130" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B130" s="38" t="s">
+      <c r="B130" s="39" t="s">
         <v>1780</v>
       </c>
       <c r="C130" s="9" t="s">
@@ -24333,10 +24335,10 @@
       </c>
     </row>
     <row r="131" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="58" t="s">
+      <c r="A131" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B131" s="38" t="s">
+      <c r="B131" s="39" t="s">
         <v>1785</v>
       </c>
       <c r="C131" s="9" t="s">
@@ -24349,10 +24351,10 @@
       <c r="F131" s="7"/>
     </row>
     <row r="132" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="58" t="s">
+      <c r="A132" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B132" s="38" t="s">
+      <c r="B132" s="39" t="s">
         <v>1788</v>
       </c>
       <c r="C132" s="9" t="s">
@@ -24365,7 +24367,7 @@
       <c r="F132" s="7"/>
     </row>
     <row r="133" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="58" t="s">
+      <c r="A133" s="59" t="s">
         <v>559</v>
       </c>
       <c r="B133" s="7" t="s">
@@ -24381,7 +24383,7 @@
       <c r="F133" s="7"/>
     </row>
     <row r="134" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="58" t="s">
+      <c r="A134" s="59" t="s">
         <v>559</v>
       </c>
       <c r="B134" s="7" t="s">
@@ -24397,10 +24399,10 @@
       <c r="F134" s="7"/>
     </row>
     <row r="135" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="58" t="s">
+      <c r="A135" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B135" s="38" t="s">
+      <c r="B135" s="39" t="s">
         <v>1797</v>
       </c>
       <c r="C135" s="9" t="s">
@@ -24413,7 +24415,7 @@
       <c r="F135" s="7"/>
     </row>
     <row r="136" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="58" t="s">
+      <c r="A136" s="59" t="s">
         <v>559</v>
       </c>
       <c r="B136" s="7" t="s">
@@ -24429,7 +24431,7 @@
       <c r="F136" s="7"/>
     </row>
     <row r="137" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="58" t="s">
+      <c r="A137" s="59" t="s">
         <v>559</v>
       </c>
       <c r="B137" s="7" t="s">
@@ -24445,7 +24447,7 @@
       <c r="F137" s="7"/>
     </row>
     <row r="138" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="58" t="s">
+      <c r="A138" s="59" t="s">
         <v>559</v>
       </c>
       <c r="B138" s="7" t="s">
@@ -24461,7 +24463,7 @@
       <c r="F138" s="7"/>
     </row>
     <row r="139" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="58" t="s">
+      <c r="A139" s="59" t="s">
         <v>559</v>
       </c>
       <c r="B139" s="7" t="s">
@@ -24477,7 +24479,7 @@
       <c r="F139" s="7"/>
     </row>
     <row r="140" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="58" t="s">
+      <c r="A140" s="59" t="s">
         <v>559</v>
       </c>
       <c r="B140" s="7" t="s">
@@ -24493,10 +24495,10 @@
       <c r="F140" s="7"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="58" t="s">
+      <c r="A141" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B141" s="52" t="s">
+      <c r="B141" s="53" t="s">
         <v>1815</v>
       </c>
       <c r="C141" s="9" t="s">
@@ -24509,10 +24511,10 @@
       <c r="F141" s="7"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="58" t="s">
+      <c r="A142" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B142" s="52" t="s">
+      <c r="B142" s="53" t="s">
         <v>1818</v>
       </c>
       <c r="C142" s="9" t="s">
@@ -24525,10 +24527,10 @@
       <c r="F142" s="7"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="58" t="s">
+      <c r="A143" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B143" s="52" t="s">
+      <c r="B143" s="53" t="s">
         <v>1821</v>
       </c>
       <c r="C143" s="9" t="s">
@@ -24541,10 +24543,10 @@
       <c r="F143" s="7"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="58" t="s">
+      <c r="A144" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B144" s="52" t="s">
+      <c r="B144" s="53" t="s">
         <v>1824</v>
       </c>
       <c r="C144" s="9" t="s">
@@ -24557,10 +24559,10 @@
       <c r="F144" s="7"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="58" t="s">
+      <c r="A145" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B145" s="52" t="s">
+      <c r="B145" s="53" t="s">
         <v>1827</v>
       </c>
       <c r="C145" s="9" t="s">
@@ -24573,10 +24575,10 @@
       <c r="F145" s="7"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="58" t="s">
+      <c r="A146" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B146" s="52" t="s">
+      <c r="B146" s="53" t="s">
         <v>1830</v>
       </c>
       <c r="C146" s="9" t="s">
@@ -24589,10 +24591,10 @@
       <c r="F146" s="7"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="58" t="s">
+      <c r="A147" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B147" s="52" t="s">
+      <c r="B147" s="53" t="s">
         <v>1833</v>
       </c>
       <c r="C147" s="9" t="s">
@@ -24605,10 +24607,10 @@
       <c r="F147" s="7"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="58" t="s">
+      <c r="A148" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B148" s="52" t="s">
+      <c r="B148" s="53" t="s">
         <v>1836</v>
       </c>
       <c r="C148" s="9" t="s">
@@ -24621,10 +24623,10 @@
       <c r="F148" s="7"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="58" t="s">
+      <c r="A149" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B149" s="52" t="s">
+      <c r="B149" s="53" t="s">
         <v>1837</v>
       </c>
       <c r="C149" s="9" t="s">
@@ -24637,10 +24639,10 @@
       <c r="F149" s="7"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="58" t="s">
+      <c r="A150" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B150" s="52" t="s">
+      <c r="B150" s="53" t="s">
         <v>1840</v>
       </c>
       <c r="C150" s="9" t="s">
@@ -24653,10 +24655,10 @@
       <c r="F150" s="7"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="58" t="s">
+      <c r="A151" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B151" s="52" t="s">
+      <c r="B151" s="53" t="s">
         <v>1843</v>
       </c>
       <c r="C151" s="9" t="s">
@@ -24669,10 +24671,10 @@
       <c r="F151" s="7"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="58" t="s">
+      <c r="A152" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B152" s="52" t="s">
+      <c r="B152" s="53" t="s">
         <v>1846</v>
       </c>
       <c r="C152" s="9" t="s">
@@ -24685,10 +24687,10 @@
       <c r="F152" s="7"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="58" t="s">
+      <c r="A153" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B153" s="52" t="s">
+      <c r="B153" s="53" t="s">
         <v>1849</v>
       </c>
       <c r="C153" s="9" t="s">
@@ -24701,10 +24703,10 @@
       <c r="F153" s="7"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="58" t="s">
+      <c r="A154" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B154" s="52" t="s">
+      <c r="B154" s="53" t="s">
         <v>1852</v>
       </c>
       <c r="C154" s="9" t="s">
@@ -24717,10 +24719,10 @@
       <c r="F154" s="7"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="58" t="s">
+      <c r="A155" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B155" s="52" t="s">
+      <c r="B155" s="53" t="s">
         <v>1855</v>
       </c>
       <c r="C155" s="9" t="s">
@@ -24733,10 +24735,10 @@
       <c r="F155" s="7"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="58" t="s">
+      <c r="A156" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B156" s="52" t="s">
+      <c r="B156" s="53" t="s">
         <v>1858</v>
       </c>
       <c r="C156" s="9" t="s">
@@ -24749,10 +24751,10 @@
       <c r="F156" s="7"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="58" t="s">
+      <c r="A157" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B157" s="52" t="s">
+      <c r="B157" s="53" t="s">
         <v>1861</v>
       </c>
       <c r="C157" s="9" t="s">
@@ -24765,10 +24767,10 @@
       <c r="F157" s="7"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="58" t="s">
+      <c r="A158" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B158" s="52" t="s">
+      <c r="B158" s="53" t="s">
         <v>1864</v>
       </c>
       <c r="C158" s="9" t="s">
@@ -24781,10 +24783,10 @@
       <c r="F158" s="7"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="58" t="s">
+      <c r="A159" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B159" s="52" t="s">
+      <c r="B159" s="53" t="s">
         <v>1865</v>
       </c>
       <c r="C159" s="9" t="s">
@@ -24797,10 +24799,10 @@
       <c r="F159" s="7"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="58" t="s">
+      <c r="A160" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="B160" s="52" t="s">
+      <c r="B160" s="53" t="s">
         <v>1868</v>
       </c>
       <c r="C160" s="9" t="s">
@@ -24813,10 +24815,10 @@
       <c r="F160" s="7"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="59" t="s">
+      <c r="A161" s="60" t="s">
         <v>559</v>
       </c>
-      <c r="B161" s="52" t="s">
+      <c r="B161" s="53" t="s">
         <v>1871</v>
       </c>
       <c r="C161" s="9" t="s">
@@ -24829,10 +24831,10 @@
       <c r="F161" s="7"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="59" t="s">
+      <c r="A162" s="60" t="s">
         <v>559</v>
       </c>
-      <c r="B162" s="52" t="s">
+      <c r="B162" s="53" t="s">
         <v>1874</v>
       </c>
       <c r="C162" s="9" t="s">
@@ -24848,7 +24850,7 @@
       <c r="A163" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B163" s="22" t="s">
+      <c r="B163" s="23" t="s">
         <v>1877</v>
       </c>
       <c r="C163" s="9" t="s">
@@ -24857,10 +24859,10 @@
       <c r="D163" s="9" t="s">
         <v>1879</v>
       </c>
-      <c r="E163" s="35" t="s">
+      <c r="E163" s="36" t="s">
         <v>1880</v>
       </c>
-      <c r="F163" s="35" t="s">
+      <c r="F163" s="36" t="s">
         <v>1881</v>
       </c>
     </row>
@@ -24868,7 +24870,7 @@
       <c r="A164" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B164" s="22" t="s">
+      <c r="B164" s="23" t="s">
         <v>1882</v>
       </c>
       <c r="C164" s="9" t="s">
@@ -24877,10 +24879,10 @@
       <c r="D164" s="9" t="s">
         <v>1884</v>
       </c>
-      <c r="E164" s="35" t="s">
+      <c r="E164" s="36" t="s">
         <v>1885</v>
       </c>
-      <c r="F164" s="35" t="s">
+      <c r="F164" s="36" t="s">
         <v>1886</v>
       </c>
     </row>
@@ -24888,7 +24890,7 @@
       <c r="A165" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B165" s="39" t="s">
+      <c r="B165" s="40" t="s">
         <v>1887</v>
       </c>
       <c r="C165" s="9" t="s">
@@ -24897,10 +24899,10 @@
       <c r="D165" s="9" t="s">
         <v>1889</v>
       </c>
-      <c r="E165" s="35" t="s">
+      <c r="E165" s="36" t="s">
         <v>1890</v>
       </c>
-      <c r="F165" s="35" t="s">
+      <c r="F165" s="36" t="s">
         <v>1891</v>
       </c>
     </row>
@@ -24908,7 +24910,7 @@
       <c r="A166" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B166" s="60" t="s">
+      <c r="B166" s="61" t="s">
         <v>1892</v>
       </c>
       <c r="C166" s="9" t="s">
@@ -24917,10 +24919,10 @@
       <c r="D166" s="9" t="s">
         <v>1894</v>
       </c>
-      <c r="E166" s="35" t="s">
+      <c r="E166" s="36" t="s">
         <v>1895</v>
       </c>
-      <c r="F166" s="35" t="s">
+      <c r="F166" s="36" t="s">
         <v>1896</v>
       </c>
     </row>
@@ -24928,7 +24930,7 @@
       <c r="A167" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B167" s="60" t="s">
+      <c r="B167" s="61" t="s">
         <v>1897</v>
       </c>
       <c r="C167" s="9" t="s">
@@ -24937,10 +24939,10 @@
       <c r="D167" s="9" t="s">
         <v>1899</v>
       </c>
-      <c r="E167" s="35" t="s">
+      <c r="E167" s="36" t="s">
         <v>1900</v>
       </c>
-      <c r="F167" s="35" t="s">
+      <c r="F167" s="36" t="s">
         <v>1901</v>
       </c>
     </row>
@@ -24948,7 +24950,7 @@
       <c r="A168" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="B168" s="61" t="s">
+      <c r="B168" s="62" t="s">
         <v>1902</v>
       </c>
       <c r="C168" s="9" t="s">
@@ -25029,10 +25031,10 @@
       <c r="D172" s="9" t="s">
         <v>1920</v>
       </c>
-      <c r="E172" s="22" t="s">
+      <c r="E172" s="23" t="s">
         <v>1921</v>
       </c>
-      <c r="F172" s="22" t="s">
+      <c r="F172" s="23" t="s">
         <v>1922</v>
       </c>
     </row>
@@ -25049,10 +25051,10 @@
       <c r="D173" s="9" t="s">
         <v>1925</v>
       </c>
-      <c r="E173" s="22" t="s">
+      <c r="E173" s="23" t="s">
         <v>1926</v>
       </c>
-      <c r="F173" s="22" t="s">
+      <c r="F173" s="23" t="s">
         <v>1927</v>
       </c>
     </row>
@@ -25069,10 +25071,10 @@
       <c r="D174" s="9" t="s">
         <v>1930</v>
       </c>
-      <c r="E174" s="22" t="s">
+      <c r="E174" s="23" t="s">
         <v>1931</v>
       </c>
-      <c r="F174" s="22" t="s">
+      <c r="F174" s="23" t="s">
         <v>1932</v>
       </c>
     </row>
@@ -25089,7 +25091,7 @@
       <c r="D175" s="9" t="s">
         <v>1935</v>
       </c>
-      <c r="E175" s="22" t="s">
+      <c r="E175" s="23" t="s">
         <v>1936</v>
       </c>
       <c r="F175" s="7" t="s">
@@ -25109,7 +25111,7 @@
       <c r="D176" s="9" t="s">
         <v>1940</v>
       </c>
-      <c r="E176" s="22" t="s">
+      <c r="E176" s="23" t="s">
         <v>1941</v>
       </c>
       <c r="F176" s="7" t="s">
@@ -25129,7 +25131,7 @@
       <c r="D177" s="9" t="s">
         <v>1945</v>
       </c>
-      <c r="E177" s="22"/>
+      <c r="E177" s="23"/>
       <c r="F177" s="7"/>
     </row>
     <row r="178" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25145,7 +25147,7 @@
       <c r="D178" s="9" t="s">
         <v>1948</v>
       </c>
-      <c r="E178" s="22"/>
+      <c r="E178" s="23"/>
       <c r="F178" s="7"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25614,7 +25616,7 @@
       <c r="A212" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="B212" s="47" t="s">
+      <c r="B212" s="48" t="s">
         <v>2044</v>
       </c>
       <c r="C212" s="9" t="s">
@@ -25712,7 +25714,7 @@
       <c r="A219" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="B219" s="47" t="s">
+      <c r="B219" s="48" t="s">
         <v>2065</v>
       </c>
       <c r="C219" s="9" t="s">
@@ -25726,7 +25728,7 @@
       <c r="A220" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="B220" s="47" t="s">
+      <c r="B220" s="48" t="s">
         <v>2068</v>
       </c>
       <c r="C220" s="9" t="s">
@@ -25740,7 +25742,7 @@
       <c r="A221" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="B221" s="47" t="s">
+      <c r="B221" s="48" t="s">
         <v>2071</v>
       </c>
       <c r="C221" s="9" t="s">
@@ -25754,7 +25756,7 @@
       <c r="A222" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="B222" s="47" t="s">
+      <c r="B222" s="48" t="s">
         <v>2074</v>
       </c>
       <c r="C222" s="9" t="s">
@@ -25768,7 +25770,7 @@
       <c r="A223" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="B223" s="47" t="s">
+      <c r="B223" s="48" t="s">
         <v>2075</v>
       </c>
       <c r="C223" s="9" t="s">
@@ -25782,7 +25784,7 @@
       <c r="A224" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="B224" s="47" t="s">
+      <c r="B224" s="48" t="s">
         <v>2078</v>
       </c>
       <c r="C224" s="9" t="s">
@@ -25796,7 +25798,7 @@
       <c r="A225" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="B225" s="47" t="s">
+      <c r="B225" s="48" t="s">
         <v>2079</v>
       </c>
       <c r="C225" s="9" t="s">
@@ -25810,7 +25812,7 @@
       <c r="A226" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="B226" s="47" t="s">
+      <c r="B226" s="48" t="s">
         <v>2080</v>
       </c>
       <c r="C226" s="9" t="s">
@@ -25824,7 +25826,7 @@
       <c r="A227" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="B227" s="47" t="s">
+      <c r="B227" s="48" t="s">
         <v>2081</v>
       </c>
       <c r="C227" s="9" t="s">
@@ -25838,7 +25840,7 @@
       <c r="A228" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="B228" s="47" t="s">
+      <c r="B228" s="48" t="s">
         <v>2082</v>
       </c>
       <c r="C228" s="9" t="s">
@@ -25852,7 +25854,7 @@
       <c r="A229" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="B229" s="47" t="s">
+      <c r="B229" s="48" t="s">
         <v>2084</v>
       </c>
       <c r="C229" s="9" t="s">
@@ -26325,10 +26327,10 @@
       </c>
     </row>
     <row r="263" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="32" t="s">
+      <c r="A263" s="33" t="s">
         <v>743</v>
       </c>
-      <c r="B263" s="22" t="s">
+      <c r="B263" s="23" t="s">
         <v>2171</v>
       </c>
       <c r="C263" s="9" t="s">
@@ -26370,7 +26372,7 @@
       <c r="A266" s="9" t="s">
         <v>743</v>
       </c>
-      <c r="B266" s="35" t="s">
+      <c r="B266" s="36" t="s">
         <v>2178</v>
       </c>
       <c r="C266" s="7" t="s">
@@ -26379,10 +26381,10 @@
       <c r="D266" s="7" t="s">
         <v>2180</v>
       </c>
-      <c r="E266" s="62" t="s">
+      <c r="E266" s="63" t="s">
         <v>2181</v>
       </c>
-      <c r="F266" s="62" t="s">
+      <c r="F266" s="63" t="s">
         <v>2182</v>
       </c>
     </row>
@@ -26390,7 +26392,7 @@
       <c r="A267" s="9" t="s">
         <v>743</v>
       </c>
-      <c r="B267" s="35" t="s">
+      <c r="B267" s="36" t="s">
         <v>2183</v>
       </c>
       <c r="C267" s="7" t="s">
@@ -26399,10 +26401,10 @@
       <c r="D267" s="7" t="s">
         <v>2185</v>
       </c>
-      <c r="E267" s="62" t="s">
+      <c r="E267" s="63" t="s">
         <v>2186</v>
       </c>
-      <c r="F267" s="62" t="s">
+      <c r="F267" s="63" t="s">
         <v>2187</v>
       </c>
     </row>
@@ -26480,7 +26482,7 @@
       <c r="A273" s="9" t="s">
         <v>1052</v>
       </c>
-      <c r="B273" s="22" t="s">
+      <c r="B273" s="23" t="s">
         <v>2197</v>
       </c>
       <c r="C273" s="9" t="s">
@@ -26494,7 +26496,7 @@
       <c r="A274" s="9" t="s">
         <v>1052</v>
       </c>
-      <c r="B274" s="22" t="s">
+      <c r="B274" s="23" t="s">
         <v>2200</v>
       </c>
       <c r="C274" s="9" t="s">
@@ -26609,21 +26611,21 @@
   <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="47" width="21.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="47" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="48" width="21.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="48" width="15.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="78.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="9" width="81.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="9" width="71.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="9" width="72.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="47" width="24.33"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="47" width="9.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="48" width="24.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="48" width="9.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="64" t="s">
         <v>2220</v>
       </c>
-      <c r="B1" s="63" t="s">
+      <c r="B1" s="64" t="s">
         <v>1178</v>
       </c>
       <c r="C1" s="9" t="s">
@@ -26638,21 +26640,21 @@
       <c r="F1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="63" t="s">
+      <c r="G1" s="64" t="s">
         <v>2221</v>
       </c>
-      <c r="H1" s="63" t="s">
+      <c r="H1" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="47" t="s">
+      <c r="I1" s="48" t="s">
         <v>2222</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="36" t="s">
         <v>1208</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="36" t="s">
         <v>1208</v>
       </c>
       <c r="C2" s="9" t="s">
@@ -26661,14 +26663,14 @@
       <c r="D2" s="9" t="s">
         <v>2224</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="36" t="s">
         <v>1244</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="36" t="s">
         <v>1244</v>
       </c>
       <c r="C3" s="9" t="s">
@@ -26677,14 +26679,14 @@
       <c r="D3" s="9" t="s">
         <v>2226</v>
       </c>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>232</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="36" t="s">
         <v>232</v>
       </c>
       <c r="C4" s="9" t="s">
@@ -26693,14 +26695,14 @@
       <c r="D4" s="9" t="s">
         <v>2228</v>
       </c>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="36" t="s">
         <v>2229</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="36" t="s">
         <v>232</v>
       </c>
       <c r="C5" s="9" t="s">
@@ -26709,14 +26711,14 @@
       <c r="D5" s="9" t="s">
         <v>1622</v>
       </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="36" t="s">
         <v>2230</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="36" t="s">
         <v>2230</v>
       </c>
       <c r="C6" s="9" t="s">
@@ -26725,14 +26727,14 @@
       <c r="D6" s="9" t="s">
         <v>2232</v>
       </c>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="36" t="s">
         <v>1188</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="36" t="s">
         <v>1188</v>
       </c>
       <c r="C7" s="9" t="s">
@@ -26741,86 +26743,86 @@
       <c r="D7" s="9" t="s">
         <v>2234</v>
       </c>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="G8" s="35" t="s">
+      <c r="B8" s="36"/>
+      <c r="G8" s="36" t="s">
         <v>1208</v>
       </c>
-      <c r="H8" s="35"/>
+      <c r="H8" s="36"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="G9" s="35" t="s">
+      <c r="B9" s="36"/>
+      <c r="G9" s="36" t="s">
         <v>1244</v>
       </c>
-      <c r="H9" s="35"/>
+      <c r="H9" s="36"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="B10" s="35"/>
-      <c r="G10" s="35" t="s">
+      <c r="B10" s="36"/>
+      <c r="G10" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="H10" s="35"/>
+      <c r="H10" s="36"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="G11" s="35" t="s">
+      <c r="B11" s="36"/>
+      <c r="G11" s="36" t="s">
         <v>2230</v>
       </c>
-      <c r="H11" s="35"/>
+      <c r="H11" s="36"/>
     </row>
     <row r="12" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="G12" s="35" t="s">
+      <c r="B12" s="36"/>
+      <c r="G12" s="36" t="s">
         <v>1208</v>
       </c>
-      <c r="H12" s="35"/>
-      <c r="I12" s="47"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="48"/>
     </row>
     <row r="13" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="B13" s="35"/>
-      <c r="G13" s="35" t="s">
+      <c r="B13" s="36"/>
+      <c r="G13" s="36" t="s">
         <v>1244</v>
       </c>
-      <c r="H13" s="35"/>
-      <c r="I13" s="47"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="48"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="35" t="s">
+      <c r="A14" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="G14" s="35" t="s">
+      <c r="B14" s="36"/>
+      <c r="G14" s="36" t="s">
         <v>1188</v>
       </c>
-      <c r="H14" s="35"/>
+      <c r="H14" s="36"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="35" t="s">
+      <c r="A15" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="36" t="s">
         <v>1208</v>
       </c>
       <c r="C15" s="9" t="s">
@@ -26829,15 +26831,15 @@
       <c r="D15" s="9" t="s">
         <v>2236</v>
       </c>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="35" t="s">
+      <c r="A16" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="36" t="s">
         <v>1244</v>
       </c>
       <c r="C16" s="9" t="s">
@@ -26846,15 +26848,15 @@
       <c r="D16" s="9" t="s">
         <v>2238</v>
       </c>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="65" t="s">
         <v>2239</v>
       </c>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="36" t="s">
         <v>2240</v>
       </c>
       <c r="C17" s="9" t="s">
@@ -26863,14 +26865,14 @@
       <c r="D17" s="9" t="s">
         <v>2242</v>
       </c>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="64" t="s">
+      <c r="A18" s="65" t="s">
         <v>2239</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="36" t="s">
         <v>2243</v>
       </c>
       <c r="C18" s="9" t="s">
@@ -26879,24 +26881,24 @@
       <c r="D18" s="9" t="s">
         <v>2245</v>
       </c>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="65" t="s">
         <v>2239</v>
       </c>
-      <c r="B19" s="35"/>
-      <c r="G19" s="35" t="s">
+      <c r="B19" s="36"/>
+      <c r="G19" s="36" t="s">
         <v>1188</v>
       </c>
-      <c r="H19" s="35"/>
+      <c r="H19" s="36"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="64" t="s">
+      <c r="A20" s="65" t="s">
         <v>189</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="36" t="s">
         <v>2240</v>
       </c>
       <c r="C20" s="9" t="s">
@@ -26905,14 +26907,14 @@
       <c r="D20" s="9" t="s">
         <v>2242</v>
       </c>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="64" t="s">
+      <c r="A21" s="65" t="s">
         <v>189</v>
       </c>
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="36" t="s">
         <v>2243</v>
       </c>
       <c r="C21" s="9" t="s">
@@ -26921,14 +26923,14 @@
       <c r="D21" s="9" t="s">
         <v>2245</v>
       </c>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="64" t="s">
+      <c r="A22" s="65" t="s">
         <v>189</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="B22" s="36" t="s">
         <v>191</v>
       </c>
       <c r="C22" s="9" t="s">
@@ -26937,24 +26939,24 @@
       <c r="D22" s="9" t="s">
         <v>2247</v>
       </c>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="64" t="s">
+      <c r="A23" s="65" t="s">
         <v>189</v>
       </c>
-      <c r="B23" s="35"/>
-      <c r="G23" s="35" t="s">
+      <c r="B23" s="36"/>
+      <c r="G23" s="36" t="s">
         <v>1188</v>
       </c>
-      <c r="H23" s="35"/>
+      <c r="H23" s="36"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="35" t="s">
+      <c r="A24" s="36" t="s">
         <v>307</v>
       </c>
-      <c r="B24" s="35" t="s">
+      <c r="B24" s="36" t="s">
         <v>2248</v>
       </c>
       <c r="C24" s="9" t="s">
@@ -26963,14 +26965,14 @@
       <c r="D24" s="9" t="s">
         <v>2250</v>
       </c>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="35" t="s">
+      <c r="A25" s="36" t="s">
         <v>307</v>
       </c>
-      <c r="B25" s="35" t="s">
+      <c r="B25" s="36" t="s">
         <v>2251</v>
       </c>
       <c r="C25" s="9" t="s">
@@ -26979,24 +26981,24 @@
       <c r="D25" s="9" t="s">
         <v>2253</v>
       </c>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="35" t="s">
+      <c r="A26" s="36" t="s">
         <v>307</v>
       </c>
-      <c r="B26" s="35"/>
-      <c r="G26" s="35" t="s">
+      <c r="B26" s="36"/>
+      <c r="G26" s="36" t="s">
         <v>1244</v>
       </c>
-      <c r="H26" s="35"/>
+      <c r="H26" s="36"/>
     </row>
     <row r="27" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="35" t="s">
+      <c r="A27" s="36" t="s">
         <v>300</v>
       </c>
-      <c r="B27" s="35" t="s">
+      <c r="B27" s="36" t="s">
         <v>2248</v>
       </c>
       <c r="C27" s="9" t="s">
@@ -27005,15 +27007,15 @@
       <c r="D27" s="9" t="s">
         <v>2255</v>
       </c>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="47"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="48"/>
     </row>
     <row r="28" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>300</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="36" t="s">
         <v>2251</v>
       </c>
       <c r="C28" s="9" t="s">
@@ -27022,26 +27024,26 @@
       <c r="D28" s="9" t="s">
         <v>2257</v>
       </c>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="47"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="48"/>
     </row>
     <row r="29" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="35" t="s">
+      <c r="A29" s="36" t="s">
         <v>300</v>
       </c>
-      <c r="B29" s="35"/>
-      <c r="G29" s="35" t="s">
+      <c r="B29" s="36"/>
+      <c r="G29" s="36" t="s">
         <v>1244</v>
       </c>
-      <c r="H29" s="35"/>
-      <c r="I29" s="47"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="48"/>
     </row>
     <row r="30" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="35" t="s">
+      <c r="A30" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="B30" s="35" t="s">
+      <c r="B30" s="36" t="s">
         <v>1210</v>
       </c>
       <c r="C30" s="9" t="s">
@@ -27050,18 +27052,18 @@
       <c r="D30" s="9" t="s">
         <v>2259</v>
       </c>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="65" t="b">
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="66" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="31" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="35" t="s">
+      <c r="A31" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="B31" s="35" t="s">
+      <c r="B31" s="36" t="s">
         <v>1211</v>
       </c>
       <c r="C31" s="9" t="s">
@@ -27070,18 +27072,18 @@
       <c r="D31" s="9" t="s">
         <v>2261</v>
       </c>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="65" t="b">
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="66" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="32" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="35" t="s">
+      <c r="A32" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="B32" s="35" t="s">
+      <c r="B32" s="36" t="s">
         <v>1212</v>
       </c>
       <c r="C32" s="9" t="s">
@@ -27090,18 +27092,18 @@
       <c r="D32" s="9" t="s">
         <v>2263</v>
       </c>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="65" t="b">
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="66" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="33" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="35" t="s">
+      <c r="A33" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="B33" s="35" t="s">
+      <c r="B33" s="36" t="s">
         <v>1214</v>
       </c>
       <c r="C33" s="9" t="s">
@@ -27110,18 +27112,18 @@
       <c r="D33" s="9" t="s">
         <v>2265</v>
       </c>
-      <c r="G33" s="35"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="65" t="b">
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="66" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="34" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="35" t="s">
+      <c r="A34" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="B34" s="35" t="s">
+      <c r="B34" s="36" t="s">
         <v>1215</v>
       </c>
       <c r="C34" s="9" t="s">
@@ -27130,18 +27132,18 @@
       <c r="D34" s="9" t="s">
         <v>2267</v>
       </c>
-      <c r="G34" s="35"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="65" t="b">
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="66" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="35" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="35" t="s">
+      <c r="A35" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="B35" s="35" t="s">
+      <c r="B35" s="36" t="s">
         <v>2268</v>
       </c>
       <c r="C35" s="9" t="s">
@@ -27150,17 +27152,17 @@
       <c r="D35" s="9" t="s">
         <v>2270</v>
       </c>
-      <c r="G35" s="35"/>
-      <c r="H35" s="35" t="s">
+      <c r="G35" s="36"/>
+      <c r="H35" s="36" t="s">
         <v>1203</v>
       </c>
-      <c r="I35" s="47"/>
+      <c r="I35" s="48"/>
     </row>
     <row r="36" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="35" t="s">
+      <c r="A36" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="B36" s="35" t="s">
+      <c r="B36" s="36" t="s">
         <v>2271</v>
       </c>
       <c r="C36" s="9" t="s">
@@ -27169,15 +27171,15 @@
       <c r="D36" s="9" t="s">
         <v>2273</v>
       </c>
-      <c r="G36" s="35"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="47"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="48"/>
     </row>
     <row r="37" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="35" t="s">
+      <c r="A37" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="B37" s="35" t="s">
+      <c r="B37" s="36" t="s">
         <v>1280</v>
       </c>
       <c r="C37" s="9" t="s">
@@ -27186,12 +27188,12 @@
       <c r="D37" s="9" t="s">
         <v>2275</v>
       </c>
-      <c r="G37" s="35"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="47"/>
+      <c r="G37" s="36"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="48"/>
     </row>
     <row r="38" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="35" t="s">
+      <c r="A38" s="36" t="s">
         <v>339</v>
       </c>
       <c r="B38" s="9" t="s">
@@ -27203,15 +27205,15 @@
       <c r="D38" s="9" t="s">
         <v>2277</v>
       </c>
-      <c r="G38" s="35"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="47"/>
+      <c r="G38" s="36"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="48"/>
     </row>
     <row r="39" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="35" t="s">
+      <c r="A39" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="B39" s="35" t="s">
+      <c r="B39" s="36" t="s">
         <v>2278</v>
       </c>
       <c r="C39" s="9" t="s">
@@ -27220,15 +27222,15 @@
       <c r="D39" s="9" t="s">
         <v>2280</v>
       </c>
-      <c r="G39" s="35"/>
-      <c r="H39" s="35"/>
-      <c r="I39" s="47"/>
+      <c r="G39" s="36"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="48"/>
     </row>
     <row r="40" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="35" t="s">
+      <c r="A40" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="B40" s="35" t="s">
+      <c r="B40" s="36" t="s">
         <v>2281</v>
       </c>
       <c r="C40" s="9" t="s">
@@ -27237,37 +27239,37 @@
       <c r="D40" s="9" t="s">
         <v>2283</v>
       </c>
-      <c r="G40" s="35"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="47"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="48"/>
     </row>
     <row r="41" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="35" t="s">
+      <c r="A41" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="B41" s="35"/>
-      <c r="G41" s="35" t="s">
+      <c r="B41" s="36"/>
+      <c r="G41" s="36" t="s">
         <v>2229</v>
       </c>
-      <c r="H41" s="35"/>
-      <c r="I41" s="47"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="48"/>
     </row>
     <row r="42" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="35" t="s">
+      <c r="A42" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="B42" s="35"/>
-      <c r="G42" s="35" t="s">
+      <c r="B42" s="36"/>
+      <c r="G42" s="36" t="s">
         <v>1188</v>
       </c>
-      <c r="H42" s="35"/>
-      <c r="I42" s="47"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="48"/>
     </row>
     <row r="43" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="22" t="s">
+      <c r="A43" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="B43" s="35" t="s">
+      <c r="B43" s="36" t="s">
         <v>1274</v>
       </c>
       <c r="C43" s="9" t="s">
@@ -27276,17 +27278,17 @@
       <c r="D43" s="9" t="s">
         <v>2285</v>
       </c>
-      <c r="G43" s="35"/>
-      <c r="H43" s="22" t="s">
+      <c r="G43" s="36"/>
+      <c r="H43" s="23" t="s">
         <v>1204</v>
       </c>
-      <c r="I43" s="35"/>
+      <c r="I43" s="36"/>
     </row>
     <row r="44" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="22" t="s">
+      <c r="A44" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="B44" s="35" t="s">
+      <c r="B44" s="36" t="s">
         <v>1275</v>
       </c>
       <c r="C44" s="9" t="s">
@@ -27295,17 +27297,17 @@
       <c r="D44" s="9" t="s">
         <v>2287</v>
       </c>
-      <c r="G44" s="35"/>
-      <c r="H44" s="22" t="s">
+      <c r="G44" s="36"/>
+      <c r="H44" s="23" t="s">
         <v>1205</v>
       </c>
-      <c r="I44" s="35"/>
+      <c r="I44" s="36"/>
     </row>
     <row r="45" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="22" t="s">
+      <c r="A45" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="B45" s="35" t="s">
+      <c r="B45" s="36" t="s">
         <v>2288</v>
       </c>
       <c r="C45" s="9" t="s">
@@ -27314,32 +27316,32 @@
       <c r="D45" s="9" t="s">
         <v>2290</v>
       </c>
-      <c r="G45" s="35"/>
-      <c r="H45" s="35"/>
-      <c r="I45" s="35"/>
-    </row>
-    <row r="46" s="41" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="62" t="s">
+      <c r="G45" s="36"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="36"/>
+    </row>
+    <row r="46" s="42" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="63" t="s">
         <v>223</v>
       </c>
-      <c r="B46" s="35" t="s">
+      <c r="B46" s="36" t="s">
         <v>2291</v>
       </c>
-      <c r="C46" s="41" t="s">
+      <c r="C46" s="42" t="s">
         <v>2292</v>
       </c>
-      <c r="D46" s="41" t="s">
+      <c r="D46" s="42" t="s">
         <v>2293</v>
       </c>
-      <c r="G46" s="35"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="35"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
     </row>
     <row r="47" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="22" t="s">
+      <c r="A47" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="B47" s="35" t="s">
+      <c r="B47" s="36" t="s">
         <v>232</v>
       </c>
       <c r="C47" s="9" t="s">
@@ -27348,26 +27350,26 @@
       <c r="D47" s="9" t="s">
         <v>2294</v>
       </c>
-      <c r="G47" s="35"/>
-      <c r="H47" s="35"/>
-      <c r="I47" s="35"/>
+      <c r="G47" s="36"/>
+      <c r="H47" s="36"/>
+      <c r="I47" s="36"/>
     </row>
     <row r="48" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="22" t="s">
+      <c r="A48" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="B48" s="35"/>
-      <c r="G48" s="35" t="s">
+      <c r="B48" s="36"/>
+      <c r="G48" s="36" t="s">
         <v>2230</v>
       </c>
-      <c r="H48" s="35"/>
-      <c r="I48" s="35"/>
+      <c r="H48" s="36"/>
+      <c r="I48" s="36"/>
     </row>
     <row r="49" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="22" t="s">
+      <c r="A49" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="B49" s="35" t="s">
+      <c r="B49" s="36" t="s">
         <v>2295</v>
       </c>
       <c r="C49" s="9" t="s">
@@ -27376,15 +27378,15 @@
       <c r="D49" s="9" t="s">
         <v>2297</v>
       </c>
-      <c r="G49" s="35"/>
-      <c r="H49" s="35"/>
-      <c r="I49" s="35"/>
+      <c r="G49" s="36"/>
+      <c r="H49" s="36"/>
+      <c r="I49" s="36"/>
     </row>
     <row r="50" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="22" t="s">
+      <c r="A50" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="B50" s="35" t="s">
+      <c r="B50" s="36" t="s">
         <v>2298</v>
       </c>
       <c r="C50" s="9" t="s">
@@ -27393,15 +27395,15 @@
       <c r="D50" s="9" t="s">
         <v>2300</v>
       </c>
-      <c r="G50" s="35"/>
-      <c r="H50" s="35"/>
-      <c r="I50" s="35"/>
+      <c r="G50" s="36"/>
+      <c r="H50" s="36"/>
+      <c r="I50" s="36"/>
     </row>
     <row r="51" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="22" t="s">
+      <c r="A51" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="B51" s="35" t="s">
+      <c r="B51" s="36" t="s">
         <v>2301</v>
       </c>
       <c r="C51" s="9" t="s">
@@ -27410,15 +27412,15 @@
       <c r="D51" s="9" t="s">
         <v>2303</v>
       </c>
-      <c r="G51" s="35"/>
-      <c r="H51" s="35"/>
-      <c r="I51" s="35"/>
+      <c r="G51" s="36"/>
+      <c r="H51" s="36"/>
+      <c r="I51" s="36"/>
     </row>
     <row r="52" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="22" t="s">
+      <c r="A52" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="B52" s="35" t="s">
+      <c r="B52" s="36" t="s">
         <v>2304</v>
       </c>
       <c r="C52" s="9" t="s">
@@ -27427,15 +27429,15 @@
       <c r="D52" s="9" t="s">
         <v>2306</v>
       </c>
-      <c r="G52" s="35"/>
-      <c r="H52" s="35"/>
-      <c r="I52" s="35"/>
+      <c r="G52" s="36"/>
+      <c r="H52" s="36"/>
+      <c r="I52" s="36"/>
     </row>
     <row r="53" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="22" t="s">
+      <c r="A53" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="B53" s="35" t="s">
+      <c r="B53" s="36" t="s">
         <v>2307</v>
       </c>
       <c r="C53" s="9" t="s">
@@ -27444,15 +27446,15 @@
       <c r="D53" s="9" t="s">
         <v>2308</v>
       </c>
-      <c r="G53" s="35"/>
-      <c r="H53" s="35"/>
-      <c r="I53" s="35"/>
+      <c r="G53" s="36"/>
+      <c r="H53" s="36"/>
+      <c r="I53" s="36"/>
     </row>
     <row r="54" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="22" t="s">
+      <c r="A54" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="B54" s="35" t="s">
+      <c r="B54" s="36" t="s">
         <v>2309</v>
       </c>
       <c r="C54" s="9" t="s">
@@ -27461,15 +27463,15 @@
       <c r="D54" s="9" t="s">
         <v>2311</v>
       </c>
-      <c r="G54" s="35"/>
-      <c r="H54" s="35"/>
-      <c r="I54" s="35"/>
+      <c r="G54" s="36"/>
+      <c r="H54" s="36"/>
+      <c r="I54" s="36"/>
     </row>
     <row r="55" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="22" t="s">
+      <c r="A55" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="B55" s="35" t="s">
+      <c r="B55" s="36" t="s">
         <v>2312</v>
       </c>
       <c r="C55" s="9" t="s">
@@ -27478,15 +27480,15 @@
       <c r="D55" s="9" t="s">
         <v>2314</v>
       </c>
-      <c r="G55" s="35"/>
-      <c r="H55" s="35"/>
-      <c r="I55" s="35"/>
+      <c r="G55" s="36"/>
+      <c r="H55" s="36"/>
+      <c r="I55" s="36"/>
     </row>
     <row r="56" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="22" t="s">
+      <c r="A56" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="B56" s="35" t="s">
+      <c r="B56" s="36" t="s">
         <v>2315</v>
       </c>
       <c r="C56" s="9" t="s">
@@ -27495,26 +27497,26 @@
       <c r="D56" s="9" t="s">
         <v>2317</v>
       </c>
-      <c r="G56" s="35"/>
-      <c r="H56" s="35"/>
-      <c r="I56" s="35"/>
+      <c r="G56" s="36"/>
+      <c r="H56" s="36"/>
+      <c r="I56" s="36"/>
     </row>
     <row r="57" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="22" t="s">
+      <c r="A57" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="B57" s="35"/>
-      <c r="G57" s="35" t="s">
+      <c r="B57" s="36"/>
+      <c r="G57" s="36" t="s">
         <v>232</v>
       </c>
-      <c r="H57" s="35"/>
-      <c r="I57" s="35"/>
+      <c r="H57" s="36"/>
+      <c r="I57" s="36"/>
     </row>
     <row r="58" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="22" t="s">
+      <c r="A58" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="B58" s="35" t="s">
+      <c r="B58" s="36" t="s">
         <v>2318</v>
       </c>
       <c r="C58" s="9" t="s">
@@ -27523,26 +27525,26 @@
       <c r="D58" s="9" t="s">
         <v>2320</v>
       </c>
-      <c r="G58" s="35"/>
-      <c r="H58" s="35"/>
-      <c r="I58" s="35"/>
+      <c r="G58" s="36"/>
+      <c r="H58" s="36"/>
+      <c r="I58" s="36"/>
     </row>
     <row r="59" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="22" t="s">
+      <c r="A59" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="B59" s="35"/>
-      <c r="G59" s="35" t="s">
+      <c r="B59" s="36"/>
+      <c r="G59" s="36" t="s">
         <v>2230</v>
       </c>
-      <c r="H59" s="35"/>
-      <c r="I59" s="35"/>
+      <c r="H59" s="36"/>
+      <c r="I59" s="36"/>
     </row>
     <row r="60" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="22" t="s">
+      <c r="A60" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="B60" s="35" t="s">
+      <c r="B60" s="36" t="s">
         <v>1208</v>
       </c>
       <c r="C60" s="9" t="s">
@@ -27551,15 +27553,15 @@
       <c r="D60" s="9" t="s">
         <v>2322</v>
       </c>
-      <c r="G60" s="35"/>
-      <c r="H60" s="35"/>
-      <c r="I60" s="35"/>
+      <c r="G60" s="36"/>
+      <c r="H60" s="36"/>
+      <c r="I60" s="36"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="64" t="s">
+      <c r="A61" s="65" t="s">
         <v>321</v>
       </c>
-      <c r="B61" s="35" t="s">
+      <c r="B61" s="36" t="s">
         <v>1218</v>
       </c>
       <c r="C61" s="9" t="s">
@@ -27568,18 +27570,18 @@
       <c r="D61" s="9" t="s">
         <v>2324</v>
       </c>
-      <c r="E61" s="66"/>
+      <c r="E61" s="67"/>
       <c r="F61" s="9" t="s">
         <v>2325</v>
       </c>
-      <c r="G61" s="35"/>
-      <c r="H61" s="35"/>
+      <c r="G61" s="36"/>
+      <c r="H61" s="36"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="64" t="s">
+      <c r="A62" s="65" t="s">
         <v>321</v>
       </c>
-      <c r="B62" s="35" t="s">
+      <c r="B62" s="36" t="s">
         <v>1219</v>
       </c>
       <c r="C62" s="9" t="s">
@@ -27591,14 +27593,14 @@
       <c r="F62" s="9" t="s">
         <v>2328</v>
       </c>
-      <c r="G62" s="35"/>
-      <c r="H62" s="35"/>
+      <c r="G62" s="36"/>
+      <c r="H62" s="36"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="64" t="s">
+      <c r="A63" s="65" t="s">
         <v>321</v>
       </c>
-      <c r="B63" s="35" t="s">
+      <c r="B63" s="36" t="s">
         <v>2329</v>
       </c>
       <c r="C63" s="9" t="s">
@@ -27610,14 +27612,14 @@
       <c r="F63" s="9" t="s">
         <v>2332</v>
       </c>
-      <c r="G63" s="35"/>
-      <c r="H63" s="35"/>
+      <c r="G63" s="36"/>
+      <c r="H63" s="36"/>
     </row>
     <row r="64" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="64" t="s">
+      <c r="A64" s="65" t="s">
         <v>321</v>
       </c>
-      <c r="B64" s="35" t="s">
+      <c r="B64" s="36" t="s">
         <v>1220</v>
       </c>
       <c r="C64" s="9" t="s">
@@ -27629,15 +27631,15 @@
       <c r="F64" s="9" t="s">
         <v>2335</v>
       </c>
-      <c r="G64" s="35"/>
-      <c r="H64" s="35"/>
-      <c r="I64" s="47"/>
+      <c r="G64" s="36"/>
+      <c r="H64" s="36"/>
+      <c r="I64" s="48"/>
     </row>
     <row r="65" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="64" t="s">
+      <c r="A65" s="65" t="s">
         <v>321</v>
       </c>
-      <c r="B65" s="35" t="s">
+      <c r="B65" s="36" t="s">
         <v>1234</v>
       </c>
       <c r="C65" s="9" t="s">
@@ -27649,15 +27651,15 @@
       <c r="F65" s="9" t="s">
         <v>2338</v>
       </c>
-      <c r="G65" s="35"/>
-      <c r="H65" s="35"/>
-      <c r="I65" s="47"/>
+      <c r="G65" s="36"/>
+      <c r="H65" s="36"/>
+      <c r="I65" s="48"/>
     </row>
     <row r="66" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="64" t="s">
+      <c r="A66" s="65" t="s">
         <v>898</v>
       </c>
-      <c r="B66" s="47" t="s">
+      <c r="B66" s="48" t="s">
         <v>2339</v>
       </c>
       <c r="C66" s="9" t="s">
@@ -27666,15 +27668,15 @@
       <c r="D66" s="9" t="s">
         <v>2341</v>
       </c>
-      <c r="G66" s="47"/>
-      <c r="H66" s="47"/>
-      <c r="I66" s="47"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
     </row>
     <row r="67" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="64" t="s">
+      <c r="A67" s="65" t="s">
         <v>898</v>
       </c>
-      <c r="B67" s="47" t="s">
+      <c r="B67" s="48" t="s">
         <v>2342</v>
       </c>
       <c r="C67" s="9" t="s">
@@ -27683,15 +27685,15 @@
       <c r="D67" s="9" t="s">
         <v>2344</v>
       </c>
-      <c r="G67" s="47"/>
-      <c r="H67" s="47"/>
-      <c r="I67" s="47"/>
+      <c r="G67" s="48"/>
+      <c r="H67" s="48"/>
+      <c r="I67" s="48"/>
     </row>
     <row r="68" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="64" t="s">
+      <c r="A68" s="65" t="s">
         <v>898</v>
       </c>
-      <c r="B68" s="47" t="s">
+      <c r="B68" s="48" t="s">
         <v>2345</v>
       </c>
       <c r="C68" s="9" t="s">
@@ -27700,15 +27702,15 @@
       <c r="D68" s="9" t="s">
         <v>2347</v>
       </c>
-      <c r="G68" s="47"/>
-      <c r="H68" s="47"/>
-      <c r="I68" s="47"/>
+      <c r="G68" s="48"/>
+      <c r="H68" s="48"/>
+      <c r="I68" s="48"/>
     </row>
     <row r="69" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="64" t="s">
+      <c r="A69" s="65" t="s">
         <v>898</v>
       </c>
-      <c r="B69" s="47" t="s">
+      <c r="B69" s="48" t="s">
         <v>2348</v>
       </c>
       <c r="C69" s="9" t="s">
@@ -27717,15 +27719,15 @@
       <c r="D69" s="9" t="s">
         <v>2350</v>
       </c>
-      <c r="G69" s="47"/>
-      <c r="H69" s="47"/>
-      <c r="I69" s="47"/>
+      <c r="G69" s="48"/>
+      <c r="H69" s="48"/>
+      <c r="I69" s="48"/>
     </row>
     <row r="70" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="35" t="s">
+      <c r="A70" s="36" t="s">
         <v>1098</v>
       </c>
-      <c r="B70" s="35" t="s">
+      <c r="B70" s="36" t="s">
         <v>2351</v>
       </c>
       <c r="C70" s="9" t="s">
@@ -27734,15 +27736,15 @@
       <c r="D70" s="9" t="s">
         <v>2353</v>
       </c>
-      <c r="G70" s="35"/>
-      <c r="H70" s="35"/>
-      <c r="I70" s="35"/>
+      <c r="G70" s="36"/>
+      <c r="H70" s="36"/>
+      <c r="I70" s="36"/>
     </row>
     <row r="71" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="35" t="s">
+      <c r="A71" s="36" t="s">
         <v>1098</v>
       </c>
-      <c r="B71" s="35" t="s">
+      <c r="B71" s="36" t="s">
         <v>2354</v>
       </c>
       <c r="C71" s="9" t="s">
@@ -27751,15 +27753,15 @@
       <c r="D71" s="9" t="s">
         <v>2356</v>
       </c>
-      <c r="G71" s="35"/>
-      <c r="H71" s="35"/>
-      <c r="I71" s="35"/>
+      <c r="G71" s="36"/>
+      <c r="H71" s="36"/>
+      <c r="I71" s="36"/>
     </row>
     <row r="72" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="35" t="s">
+      <c r="A72" s="36" t="s">
         <v>1098</v>
       </c>
-      <c r="B72" s="35" t="s">
+      <c r="B72" s="36" t="s">
         <v>2357</v>
       </c>
       <c r="C72" s="9" t="s">
@@ -27768,15 +27770,15 @@
       <c r="D72" s="9" t="s">
         <v>2359</v>
       </c>
-      <c r="G72" s="35"/>
-      <c r="H72" s="35"/>
-      <c r="I72" s="35"/>
+      <c r="G72" s="36"/>
+      <c r="H72" s="36"/>
+      <c r="I72" s="36"/>
     </row>
     <row r="73" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="35" t="s">
+      <c r="A73" s="36" t="s">
         <v>1098</v>
       </c>
-      <c r="B73" s="35" t="s">
+      <c r="B73" s="36" t="s">
         <v>2360</v>
       </c>
       <c r="C73" s="9" t="s">
@@ -27785,15 +27787,15 @@
       <c r="D73" s="9" t="s">
         <v>2362</v>
       </c>
-      <c r="G73" s="35"/>
-      <c r="H73" s="35"/>
-      <c r="I73" s="35"/>
+      <c r="G73" s="36"/>
+      <c r="H73" s="36"/>
+      <c r="I73" s="36"/>
     </row>
     <row r="74" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="35" t="s">
+      <c r="A74" s="36" t="s">
         <v>1098</v>
       </c>
-      <c r="B74" s="35" t="s">
+      <c r="B74" s="36" t="s">
         <v>2363</v>
       </c>
       <c r="C74" s="9" t="s">
@@ -27802,15 +27804,15 @@
       <c r="D74" s="9" t="s">
         <v>2365</v>
       </c>
-      <c r="G74" s="35"/>
-      <c r="H74" s="35"/>
-      <c r="I74" s="35"/>
+      <c r="G74" s="36"/>
+      <c r="H74" s="36"/>
+      <c r="I74" s="36"/>
     </row>
     <row r="75" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="35" t="s">
+      <c r="A75" s="36" t="s">
         <v>1098</v>
       </c>
-      <c r="B75" s="35" t="s">
+      <c r="B75" s="36" t="s">
         <v>2366</v>
       </c>
       <c r="C75" s="9" t="s">
@@ -27819,15 +27821,15 @@
       <c r="D75" s="9" t="s">
         <v>2368</v>
       </c>
-      <c r="G75" s="35"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
+      <c r="G75" s="36"/>
+      <c r="H75" s="36"/>
+      <c r="I75" s="36"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="35" t="s">
+      <c r="A76" s="36" t="s">
         <v>1098</v>
       </c>
-      <c r="B76" s="35" t="s">
+      <c r="B76" s="36" t="s">
         <v>2369</v>
       </c>
       <c r="C76" s="9" t="s">
@@ -27836,15 +27838,15 @@
       <c r="D76" s="9" t="s">
         <v>2371</v>
       </c>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
+      <c r="G76" s="36"/>
+      <c r="H76" s="36"/>
+      <c r="I76" s="36"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="35" t="s">
+      <c r="A77" s="36" t="s">
         <v>1098</v>
       </c>
-      <c r="B77" s="35" t="s">
+      <c r="B77" s="36" t="s">
         <v>2372</v>
       </c>
       <c r="C77" s="9" t="s">
@@ -27853,15 +27855,15 @@
       <c r="D77" s="9" t="s">
         <v>2374</v>
       </c>
-      <c r="G77" s="35"/>
-      <c r="H77" s="35"/>
-      <c r="I77" s="35"/>
+      <c r="G77" s="36"/>
+      <c r="H77" s="36"/>
+      <c r="I77" s="36"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="35" t="s">
+      <c r="A78" s="36" t="s">
         <v>1098</v>
       </c>
-      <c r="B78" s="35" t="s">
+      <c r="B78" s="36" t="s">
         <v>2375</v>
       </c>
       <c r="C78" s="9" t="s">
@@ -27870,15 +27872,15 @@
       <c r="D78" s="9" t="s">
         <v>2377</v>
       </c>
-      <c r="G78" s="35"/>
-      <c r="H78" s="35"/>
-      <c r="I78" s="35"/>
+      <c r="G78" s="36"/>
+      <c r="H78" s="36"/>
+      <c r="I78" s="36"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="35" t="s">
+      <c r="A79" s="36" t="s">
         <v>1098</v>
       </c>
-      <c r="B79" s="35" t="s">
+      <c r="B79" s="36" t="s">
         <v>2230</v>
       </c>
       <c r="C79" s="9" t="s">
@@ -27887,15 +27889,15 @@
       <c r="D79" s="9" t="s">
         <v>2232</v>
       </c>
-      <c r="G79" s="35"/>
-      <c r="H79" s="35"/>
-      <c r="I79" s="35"/>
+      <c r="G79" s="36"/>
+      <c r="H79" s="36"/>
+      <c r="I79" s="36"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="35" t="s">
+      <c r="A80" s="36" t="s">
         <v>1098</v>
       </c>
-      <c r="B80" s="35" t="s">
+      <c r="B80" s="36" t="s">
         <v>2378</v>
       </c>
       <c r="C80" s="9" t="s">
@@ -27904,15 +27906,15 @@
       <c r="D80" s="9" t="s">
         <v>2379</v>
       </c>
-      <c r="G80" s="35"/>
-      <c r="H80" s="35"/>
-      <c r="I80" s="35"/>
+      <c r="G80" s="36"/>
+      <c r="H80" s="36"/>
+      <c r="I80" s="36"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="67" t="s">
+      <c r="A81" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="B81" s="47" t="s">
+      <c r="B81" s="48" t="s">
         <v>2380</v>
       </c>
       <c r="C81" s="9" t="s">
@@ -27923,10 +27925,10 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="67" t="s">
+      <c r="A82" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="B82" s="47" t="s">
+      <c r="B82" s="48" t="s">
         <v>2383</v>
       </c>
       <c r="C82" s="9" t="s">
@@ -27937,10 +27939,10 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="67" t="s">
+      <c r="A83" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="B83" s="47" t="s">
+      <c r="B83" s="48" t="s">
         <v>232</v>
       </c>
       <c r="C83" s="9" t="s">
@@ -27951,10 +27953,10 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="67" t="s">
+      <c r="A84" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="B84" s="47" t="s">
+      <c r="B84" s="48" t="s">
         <v>1188</v>
       </c>
       <c r="C84" s="9" t="s">
@@ -27965,10 +27967,10 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="68" t="s">
+      <c r="A85" s="69" t="s">
         <v>422</v>
       </c>
-      <c r="B85" s="35" t="s">
+      <c r="B85" s="36" t="s">
         <v>2386</v>
       </c>
       <c r="C85" s="9" t="s">
@@ -27977,17 +27979,17 @@
       <c r="D85" s="9" t="s">
         <v>2388</v>
       </c>
-      <c r="G85" s="35"/>
-      <c r="H85" s="35" t="s">
+      <c r="G85" s="36"/>
+      <c r="H85" s="36" t="s">
         <v>1202</v>
       </c>
-      <c r="I85" s="35"/>
+      <c r="I85" s="36"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="68" t="s">
+      <c r="A86" s="69" t="s">
         <v>422</v>
       </c>
-      <c r="B86" s="35" t="s">
+      <c r="B86" s="36" t="s">
         <v>2389</v>
       </c>
       <c r="C86" s="9" t="s">
@@ -27996,17 +27998,17 @@
       <c r="D86" s="9" t="s">
         <v>2391</v>
       </c>
-      <c r="G86" s="35"/>
-      <c r="H86" s="35" t="s">
+      <c r="G86" s="36"/>
+      <c r="H86" s="36" t="s">
         <v>314</v>
       </c>
-      <c r="I86" s="35"/>
+      <c r="I86" s="36"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="68" t="s">
+      <c r="A87" s="69" t="s">
         <v>422</v>
       </c>
-      <c r="B87" s="35" t="s">
+      <c r="B87" s="36" t="s">
         <v>2392</v>
       </c>
       <c r="C87" s="9" t="s">
@@ -28015,15 +28017,15 @@
       <c r="D87" s="9" t="s">
         <v>2394</v>
       </c>
-      <c r="G87" s="35"/>
-      <c r="H87" s="35"/>
-      <c r="I87" s="35"/>
+      <c r="G87" s="36"/>
+      <c r="H87" s="36"/>
+      <c r="I87" s="36"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="68" t="s">
+      <c r="A88" s="69" t="s">
         <v>422</v>
       </c>
-      <c r="B88" s="35" t="s">
+      <c r="B88" s="36" t="s">
         <v>2395</v>
       </c>
       <c r="C88" s="9" t="s">
@@ -28032,15 +28034,15 @@
       <c r="D88" s="9" t="s">
         <v>2397</v>
       </c>
-      <c r="G88" s="35"/>
-      <c r="H88" s="35"/>
-      <c r="I88" s="35"/>
+      <c r="G88" s="36"/>
+      <c r="H88" s="36"/>
+      <c r="I88" s="36"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="68" t="s">
+      <c r="A89" s="69" t="s">
         <v>422</v>
       </c>
-      <c r="B89" s="35" t="s">
+      <c r="B89" s="36" t="s">
         <v>2398</v>
       </c>
       <c r="C89" s="9" t="s">
@@ -28049,15 +28051,15 @@
       <c r="D89" s="9" t="s">
         <v>2400</v>
       </c>
-      <c r="G89" s="35"/>
-      <c r="H89" s="35"/>
-      <c r="I89" s="35"/>
+      <c r="G89" s="36"/>
+      <c r="H89" s="36"/>
+      <c r="I89" s="36"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="68" t="s">
+      <c r="A90" s="69" t="s">
         <v>422</v>
       </c>
-      <c r="B90" s="35" t="s">
+      <c r="B90" s="36" t="s">
         <v>1251</v>
       </c>
       <c r="C90" s="9" t="s">
@@ -28066,17 +28068,17 @@
       <c r="D90" s="9" t="s">
         <v>2402</v>
       </c>
-      <c r="G90" s="35"/>
-      <c r="H90" s="35" t="s">
+      <c r="G90" s="36"/>
+      <c r="H90" s="36" t="s">
         <v>314</v>
       </c>
-      <c r="I90" s="35"/>
+      <c r="I90" s="36"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="68" t="s">
+      <c r="A91" s="69" t="s">
         <v>422</v>
       </c>
-      <c r="B91" s="35" t="s">
+      <c r="B91" s="36" t="s">
         <v>1252</v>
       </c>
       <c r="C91" s="9" t="s">
@@ -28085,15 +28087,15 @@
       <c r="D91" s="9" t="s">
         <v>2404</v>
       </c>
-      <c r="G91" s="35"/>
-      <c r="H91" s="35"/>
-      <c r="I91" s="35"/>
+      <c r="G91" s="36"/>
+      <c r="H91" s="36"/>
+      <c r="I91" s="36"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="68" t="s">
+      <c r="A92" s="69" t="s">
         <v>422</v>
       </c>
-      <c r="B92" s="35" t="s">
+      <c r="B92" s="36" t="s">
         <v>2405</v>
       </c>
       <c r="C92" s="9" t="s">
@@ -28102,17 +28104,17 @@
       <c r="D92" s="9" t="s">
         <v>2407</v>
       </c>
-      <c r="G92" s="35"/>
-      <c r="H92" s="35" t="s">
+      <c r="G92" s="36"/>
+      <c r="H92" s="36" t="s">
         <v>1213</v>
       </c>
-      <c r="I92" s="35"/>
+      <c r="I92" s="36"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="68" t="s">
+      <c r="A93" s="69" t="s">
         <v>422</v>
       </c>
-      <c r="B93" s="35" t="s">
+      <c r="B93" s="36" t="s">
         <v>232</v>
       </c>
       <c r="C93" s="9" t="s">
@@ -28121,15 +28123,15 @@
       <c r="D93" s="9" t="s">
         <v>1622</v>
       </c>
-      <c r="G93" s="35"/>
-      <c r="H93" s="35"/>
-      <c r="I93" s="35"/>
+      <c r="G93" s="36"/>
+      <c r="H93" s="36"/>
+      <c r="I93" s="36"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="69" t="s">
+      <c r="A94" s="70" t="s">
         <v>2408</v>
       </c>
-      <c r="B94" s="47" t="s">
+      <c r="B94" s="48" t="s">
         <v>2409</v>
       </c>
       <c r="C94" s="9" t="s">
@@ -28146,10 +28148,10 @@
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="69" t="s">
+      <c r="A95" s="70" t="s">
         <v>2408</v>
       </c>
-      <c r="B95" s="47" t="s">
+      <c r="B95" s="48" t="s">
         <v>2410</v>
       </c>
       <c r="C95" s="9" t="s">
@@ -28166,10 +28168,10 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="69" t="s">
+      <c r="A96" s="70" t="s">
         <v>2408</v>
       </c>
-      <c r="B96" s="47" t="s">
+      <c r="B96" s="48" t="s">
         <v>1244</v>
       </c>
       <c r="C96" s="9" t="s">
@@ -28180,10 +28182,10 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="69" t="s">
+      <c r="A97" s="70" t="s">
         <v>758</v>
       </c>
-      <c r="B97" s="47" t="s">
+      <c r="B97" s="48" t="s">
         <v>2411</v>
       </c>
       <c r="C97" s="9" t="s">
@@ -28194,10 +28196,10 @@
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="69" t="s">
+      <c r="A98" s="70" t="s">
         <v>758</v>
       </c>
-      <c r="B98" s="47" t="s">
+      <c r="B98" s="48" t="s">
         <v>2414</v>
       </c>
       <c r="C98" s="9" t="s">
@@ -28206,16 +28208,16 @@
       <c r="D98" s="9" t="s">
         <v>2416</v>
       </c>
-      <c r="I98" s="65" t="b">
+      <c r="I98" s="66" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="69" t="s">
+      <c r="A99" s="70" t="s">
         <v>758</v>
       </c>
-      <c r="B99" s="47" t="s">
+      <c r="B99" s="48" t="s">
         <v>2417</v>
       </c>
       <c r="C99" s="9" t="s">
@@ -28226,10 +28228,10 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="69" t="s">
+      <c r="A100" s="70" t="s">
         <v>758</v>
       </c>
-      <c r="B100" s="47" t="s">
+      <c r="B100" s="48" t="s">
         <v>2420</v>
       </c>
       <c r="C100" s="9" t="s">
@@ -28240,26 +28242,26 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="69" t="s">
+      <c r="A101" s="70" t="s">
         <v>758</v>
       </c>
-      <c r="G101" s="35" t="s">
+      <c r="G101" s="36" t="s">
         <v>2229</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="69" t="s">
+      <c r="A102" s="70" t="s">
         <v>758</v>
       </c>
-      <c r="G102" s="35" t="s">
+      <c r="G102" s="36" t="s">
         <v>2230</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="69" t="s">
+      <c r="A103" s="70" t="s">
         <v>822</v>
       </c>
-      <c r="B103" s="47" t="s">
+      <c r="B103" s="48" t="s">
         <v>2423</v>
       </c>
       <c r="C103" s="9" t="s">
@@ -28270,10 +28272,10 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="69" t="s">
+      <c r="A104" s="70" t="s">
         <v>822</v>
       </c>
-      <c r="B104" s="47" t="s">
+      <c r="B104" s="48" t="s">
         <v>2426</v>
       </c>
       <c r="C104" s="9" t="s">
@@ -28284,10 +28286,10 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="69" t="s">
+      <c r="A105" s="70" t="s">
         <v>822</v>
       </c>
-      <c r="B105" s="47" t="s">
+      <c r="B105" s="48" t="s">
         <v>2417</v>
       </c>
       <c r="C105" s="9" t="s">
@@ -28298,10 +28300,10 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="69" t="s">
+      <c r="A106" s="70" t="s">
         <v>822</v>
       </c>
-      <c r="B106" s="35" t="s">
+      <c r="B106" s="36" t="s">
         <v>2431</v>
       </c>
       <c r="C106" s="9" t="s">
@@ -28310,32 +28312,32 @@
       <c r="D106" s="9" t="s">
         <v>2433</v>
       </c>
-      <c r="I106" s="65" t="b">
+      <c r="I106" s="66" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="69" t="s">
+      <c r="A107" s="70" t="s">
         <v>822</v>
       </c>
-      <c r="G107" s="35" t="s">
+      <c r="G107" s="36" t="s">
         <v>2229</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="69" t="s">
+      <c r="A108" s="70" t="s">
         <v>822</v>
       </c>
-      <c r="G108" s="35" t="s">
+      <c r="G108" s="36" t="s">
         <v>2230</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="70" t="s">
+      <c r="A109" s="71" t="s">
         <v>346</v>
       </c>
-      <c r="B109" s="47" t="s">
+      <c r="B109" s="48" t="s">
         <v>2434</v>
       </c>
       <c r="C109" s="9" t="s">
@@ -28346,10 +28348,10 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="70" t="s">
+      <c r="A110" s="71" t="s">
         <v>346</v>
       </c>
-      <c r="B110" s="47" t="s">
+      <c r="B110" s="48" t="s">
         <v>2437</v>
       </c>
       <c r="C110" s="9" t="s">
@@ -28360,10 +28362,10 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="70" t="s">
+      <c r="A111" s="71" t="s">
         <v>346</v>
       </c>
-      <c r="B111" s="47" t="s">
+      <c r="B111" s="48" t="s">
         <v>2440</v>
       </c>
       <c r="C111" s="9" t="s">
@@ -28374,18 +28376,18 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="70" t="s">
+      <c r="A112" s="71" t="s">
         <v>346</v>
       </c>
-      <c r="G112" s="35" t="s">
+      <c r="G112" s="36" t="s">
         <v>1188</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="64" t="s">
+      <c r="A113" s="65" t="s">
         <v>2443</v>
       </c>
-      <c r="B113" s="35" t="s">
+      <c r="B113" s="36" t="s">
         <v>1218</v>
       </c>
       <c r="C113" s="9" t="s">
@@ -28400,13 +28402,13 @@
       <c r="F113" s="9" t="s">
         <v>2447</v>
       </c>
-      <c r="G113" s="64"/>
+      <c r="G113" s="65"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="64" t="s">
+      <c r="A114" s="65" t="s">
         <v>2443</v>
       </c>
-      <c r="B114" s="35" t="s">
+      <c r="B114" s="36" t="s">
         <v>1219</v>
       </c>
       <c r="C114" s="9" t="s">
@@ -28423,10 +28425,10 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="64" t="s">
+      <c r="A115" s="65" t="s">
         <v>2443</v>
       </c>
-      <c r="B115" s="35" t="s">
+      <c r="B115" s="36" t="s">
         <v>1220</v>
       </c>
       <c r="C115" s="9" t="s">
@@ -28443,10 +28445,10 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="64" t="s">
+      <c r="A116" s="65" t="s">
         <v>2443</v>
       </c>
-      <c r="B116" s="35" t="s">
+      <c r="B116" s="36" t="s">
         <v>1234</v>
       </c>
       <c r="C116" s="9" t="s">
@@ -28463,10 +28465,10 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="64" t="s">
+      <c r="A117" s="65" t="s">
         <v>2443</v>
       </c>
-      <c r="B117" s="35" t="s">
+      <c r="B117" s="36" t="s">
         <v>2329</v>
       </c>
       <c r="C117" s="9" t="s">
@@ -28483,10 +28485,10 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="22" t="s">
+      <c r="A118" s="23" t="s">
         <v>689</v>
       </c>
-      <c r="B118" s="47" t="s">
+      <c r="B118" s="48" t="s">
         <v>2464</v>
       </c>
       <c r="C118" s="9" t="s">
@@ -28497,10 +28499,10 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="22" t="s">
+      <c r="A119" s="23" t="s">
         <v>689</v>
       </c>
-      <c r="B119" s="47" t="s">
+      <c r="B119" s="48" t="s">
         <v>1258</v>
       </c>
       <c r="C119" s="9" t="s">
@@ -28509,15 +28511,15 @@
       <c r="D119" s="9" t="s">
         <v>2465</v>
       </c>
-      <c r="H119" s="71" t="s">
+      <c r="H119" s="72" t="s">
         <v>2466</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="22" t="s">
+      <c r="A120" s="23" t="s">
         <v>689</v>
       </c>
-      <c r="B120" s="47" t="s">
+      <c r="B120" s="48" t="s">
         <v>2467</v>
       </c>
       <c r="C120" s="9" t="s">
@@ -28526,15 +28528,15 @@
       <c r="D120" s="9" t="s">
         <v>2468</v>
       </c>
-      <c r="H120" s="71" t="s">
+      <c r="H120" s="72" t="s">
         <v>2469</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="22" t="s">
+      <c r="A121" s="23" t="s">
         <v>689</v>
       </c>
-      <c r="B121" s="47" t="s">
+      <c r="B121" s="48" t="s">
         <v>2470</v>
       </c>
       <c r="C121" s="9" t="s">
@@ -28543,15 +28545,15 @@
       <c r="D121" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="H121" s="22" t="s">
+      <c r="H121" s="23" t="s">
         <v>1011</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="22" t="s">
+      <c r="A122" s="23" t="s">
         <v>689</v>
       </c>
-      <c r="B122" s="47" t="s">
+      <c r="B122" s="48" t="s">
         <v>2471</v>
       </c>
       <c r="C122" s="9" t="s">
@@ -28562,18 +28564,18 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="22" t="s">
+      <c r="A123" s="23" t="s">
         <v>689</v>
       </c>
-      <c r="G123" s="47" t="s">
+      <c r="G123" s="48" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="22" t="s">
+      <c r="A124" s="23" t="s">
         <v>695</v>
       </c>
-      <c r="B124" s="47" t="s">
+      <c r="B124" s="48" t="s">
         <v>2464</v>
       </c>
       <c r="C124" s="9" t="s">
@@ -28584,10 +28586,10 @@
       </c>
     </row>
     <row r="125" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="22" t="s">
+      <c r="A125" s="23" t="s">
         <v>695</v>
       </c>
-      <c r="B125" s="47" t="s">
+      <c r="B125" s="48" t="s">
         <v>2472</v>
       </c>
       <c r="C125" s="9" t="s">
@@ -28598,10 +28600,10 @@
       </c>
     </row>
     <row r="126" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="22" t="s">
+      <c r="A126" s="23" t="s">
         <v>695</v>
       </c>
-      <c r="B126" s="47" t="s">
+      <c r="B126" s="48" t="s">
         <v>2470</v>
       </c>
       <c r="C126" s="9" t="s">
@@ -28610,15 +28612,15 @@
       <c r="D126" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="H126" s="22" t="s">
+      <c r="H126" s="23" t="s">
         <v>1011</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="22" t="s">
+      <c r="A127" s="23" t="s">
         <v>695</v>
       </c>
-      <c r="B127" s="47" t="s">
+      <c r="B127" s="48" t="s">
         <v>2471</v>
       </c>
       <c r="C127" s="9" t="s">
@@ -28629,10 +28631,10 @@
       </c>
     </row>
     <row r="128" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="22" t="s">
+      <c r="A128" s="23" t="s">
         <v>695</v>
       </c>
-      <c r="B128" s="47" t="s">
+      <c r="B128" s="48" t="s">
         <v>2473</v>
       </c>
       <c r="C128" s="9" t="s">
@@ -28643,10 +28645,10 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="22" t="s">
+      <c r="A129" s="23" t="s">
         <v>695</v>
       </c>
-      <c r="B129" s="47" t="s">
+      <c r="B129" s="48" t="s">
         <v>2476</v>
       </c>
       <c r="C129" s="9" t="s">
@@ -28657,18 +28659,18 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="22" t="s">
+      <c r="A130" s="23" t="s">
         <v>695</v>
       </c>
-      <c r="G130" s="35" t="s">
+      <c r="G130" s="36" t="s">
         <v>2229</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="22" t="s">
+      <c r="A131" s="23" t="s">
         <v>592</v>
       </c>
-      <c r="B131" s="47" t="s">
+      <c r="B131" s="48" t="s">
         <v>2477</v>
       </c>
       <c r="C131" s="9" t="s">
@@ -28677,15 +28679,15 @@
       <c r="D131" s="9" t="s">
         <v>2479</v>
       </c>
-      <c r="H131" s="22" t="s">
+      <c r="H131" s="23" t="s">
         <v>2480</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="22" t="s">
+      <c r="A132" s="23" t="s">
         <v>592</v>
       </c>
-      <c r="B132" s="47" t="s">
+      <c r="B132" s="48" t="s">
         <v>1244</v>
       </c>
       <c r="C132" s="9" t="s">
@@ -28699,10 +28701,10 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="22" t="s">
+      <c r="A133" s="23" t="s">
         <v>592</v>
       </c>
-      <c r="B133" s="47" t="s">
+      <c r="B133" s="48" t="s">
         <v>1208</v>
       </c>
       <c r="C133" s="9" t="s">
@@ -28713,10 +28715,10 @@
       </c>
     </row>
     <row r="134" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="22" t="s">
+      <c r="A134" s="23" t="s">
         <v>592</v>
       </c>
-      <c r="B134" s="47" t="s">
+      <c r="B134" s="48" t="s">
         <v>2486</v>
       </c>
       <c r="C134" s="9" t="s">
@@ -28727,18 +28729,18 @@
       </c>
     </row>
     <row r="135" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="22" t="s">
+      <c r="A135" s="23" t="s">
         <v>592</v>
       </c>
-      <c r="G135" s="47" t="s">
+      <c r="G135" s="48" t="s">
         <v>2230</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="47" t="s">
+      <c r="A136" s="48" t="s">
         <v>624</v>
       </c>
-      <c r="B136" s="47" t="s">
+      <c r="B136" s="48" t="s">
         <v>2489</v>
       </c>
       <c r="C136" s="9" t="s">
@@ -28749,10 +28751,10 @@
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="47" t="s">
+      <c r="A137" s="48" t="s">
         <v>624</v>
       </c>
-      <c r="B137" s="47" t="s">
+      <c r="B137" s="48" t="s">
         <v>2491</v>
       </c>
       <c r="C137" s="9" t="s">
@@ -28763,18 +28765,18 @@
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="47" t="s">
+      <c r="A138" s="48" t="s">
         <v>624</v>
       </c>
-      <c r="G138" s="47" t="s">
+      <c r="G138" s="48" t="s">
         <v>2230</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="22" t="s">
+      <c r="A139" s="23" t="s">
         <v>648</v>
       </c>
-      <c r="B139" s="47" t="s">
+      <c r="B139" s="48" t="s">
         <v>2494</v>
       </c>
       <c r="C139" s="9" t="s">
@@ -28785,10 +28787,10 @@
       </c>
     </row>
     <row r="140" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="22" t="s">
+      <c r="A140" s="23" t="s">
         <v>648</v>
       </c>
-      <c r="B140" s="47" t="s">
+      <c r="B140" s="48" t="s">
         <v>2497</v>
       </c>
       <c r="C140" s="9" t="s">
@@ -28799,26 +28801,26 @@
       </c>
     </row>
     <row r="141" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="22" t="s">
+      <c r="A141" s="23" t="s">
         <v>648</v>
       </c>
-      <c r="G141" s="35" t="s">
+      <c r="G141" s="36" t="s">
         <v>2229</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="22" t="s">
+      <c r="A142" s="23" t="s">
         <v>648</v>
       </c>
-      <c r="G142" s="47" t="s">
+      <c r="G142" s="48" t="s">
         <v>2230</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="22" t="s">
+      <c r="A143" s="23" t="s">
         <v>654</v>
       </c>
-      <c r="B143" s="47" t="s">
+      <c r="B143" s="48" t="s">
         <v>2500</v>
       </c>
       <c r="C143" s="9" t="s">
@@ -28829,10 +28831,10 @@
       </c>
     </row>
     <row r="144" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="22" t="s">
+      <c r="A144" s="23" t="s">
         <v>654</v>
       </c>
-      <c r="B144" s="47" t="s">
+      <c r="B144" s="48" t="s">
         <v>2503</v>
       </c>
       <c r="C144" s="9" t="s">
@@ -28843,10 +28845,10 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="22" t="s">
+      <c r="A145" s="23" t="s">
         <v>654</v>
       </c>
-      <c r="B145" s="47" t="s">
+      <c r="B145" s="48" t="s">
         <v>2505</v>
       </c>
       <c r="C145" s="9" t="s">
@@ -28857,10 +28859,10 @@
       </c>
     </row>
     <row r="146" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="22" t="s">
+      <c r="A146" s="23" t="s">
         <v>654</v>
       </c>
-      <c r="B146" s="47" t="s">
+      <c r="B146" s="48" t="s">
         <v>2507</v>
       </c>
       <c r="C146" s="9" t="s">
@@ -28871,26 +28873,26 @@
       </c>
     </row>
     <row r="147" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="22" t="s">
+      <c r="A147" s="23" t="s">
         <v>654</v>
       </c>
-      <c r="G147" s="35" t="s">
+      <c r="G147" s="36" t="s">
         <v>2229</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="22" t="s">
+      <c r="A148" s="23" t="s">
         <v>654</v>
       </c>
-      <c r="G148" s="47" t="s">
+      <c r="G148" s="48" t="s">
         <v>2230</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="22" t="s">
+      <c r="A149" s="23" t="s">
         <v>658</v>
       </c>
-      <c r="B149" s="47" t="s">
+      <c r="B149" s="48" t="s">
         <v>2509</v>
       </c>
       <c r="C149" s="9" t="s">
@@ -28901,10 +28903,10 @@
       </c>
     </row>
     <row r="150" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="22" t="s">
+      <c r="A150" s="23" t="s">
         <v>658</v>
       </c>
-      <c r="B150" s="47" t="s">
+      <c r="B150" s="48" t="s">
         <v>2512</v>
       </c>
       <c r="C150" s="9" t="s">
@@ -28915,10 +28917,10 @@
       </c>
     </row>
     <row r="151" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="22" t="s">
+      <c r="A151" s="23" t="s">
         <v>658</v>
       </c>
-      <c r="B151" s="47" t="s">
+      <c r="B151" s="48" t="s">
         <v>2494</v>
       </c>
       <c r="C151" s="9" t="s">
@@ -28929,10 +28931,10 @@
       </c>
     </row>
     <row r="152" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="22" t="s">
+      <c r="A152" s="23" t="s">
         <v>658</v>
       </c>
-      <c r="B152" s="47" t="s">
+      <c r="B152" s="48" t="s">
         <v>2517</v>
       </c>
       <c r="C152" s="9" t="s">
@@ -28943,10 +28945,10 @@
       </c>
     </row>
     <row r="153" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="22" t="s">
+      <c r="A153" s="23" t="s">
         <v>658</v>
       </c>
-      <c r="B153" s="47" t="s">
+      <c r="B153" s="48" t="s">
         <v>2519</v>
       </c>
       <c r="C153" s="9" t="s">
@@ -28957,26 +28959,26 @@
       </c>
     </row>
     <row r="154" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="22" t="s">
+      <c r="A154" s="23" t="s">
         <v>658</v>
       </c>
-      <c r="G154" s="35" t="s">
+      <c r="G154" s="36" t="s">
         <v>2229</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="22" t="s">
+      <c r="A155" s="23" t="s">
         <v>658</v>
       </c>
-      <c r="G155" s="47" t="s">
+      <c r="G155" s="48" t="s">
         <v>2230</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="22" t="s">
+      <c r="A156" s="23" t="s">
         <v>785</v>
       </c>
-      <c r="B156" s="35" t="s">
+      <c r="B156" s="36" t="s">
         <v>2470</v>
       </c>
       <c r="C156" s="9" t="s">
@@ -28985,15 +28987,15 @@
       <c r="D156" s="9" t="s">
         <v>2523</v>
       </c>
-      <c r="G156" s="35"/>
-      <c r="H156" s="35"/>
-      <c r="I156" s="35"/>
+      <c r="G156" s="36"/>
+      <c r="H156" s="36"/>
+      <c r="I156" s="36"/>
     </row>
     <row r="157" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="22" t="s">
+      <c r="A157" s="23" t="s">
         <v>785</v>
       </c>
-      <c r="B157" s="35" t="s">
+      <c r="B157" s="36" t="s">
         <v>2471</v>
       </c>
       <c r="C157" s="9" t="s">
@@ -29002,15 +29004,15 @@
       <c r="D157" s="9" t="s">
         <v>2525</v>
       </c>
-      <c r="G157" s="35"/>
-      <c r="H157" s="35"/>
-      <c r="I157" s="35"/>
+      <c r="G157" s="36"/>
+      <c r="H157" s="36"/>
+      <c r="I157" s="36"/>
     </row>
     <row r="158" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="22" t="s">
+      <c r="A158" s="23" t="s">
         <v>785</v>
       </c>
-      <c r="B158" s="35" t="s">
+      <c r="B158" s="36" t="s">
         <v>2476</v>
       </c>
       <c r="C158" s="9" t="s">
@@ -29019,15 +29021,15 @@
       <c r="D158" s="9" t="s">
         <v>2527</v>
       </c>
-      <c r="G158" s="35"/>
-      <c r="H158" s="35"/>
-      <c r="I158" s="35"/>
+      <c r="G158" s="36"/>
+      <c r="H158" s="36"/>
+      <c r="I158" s="36"/>
     </row>
     <row r="159" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="22" t="s">
+      <c r="A159" s="23" t="s">
         <v>785</v>
       </c>
-      <c r="B159" s="35" t="s">
+      <c r="B159" s="36" t="s">
         <v>2464</v>
       </c>
       <c r="C159" s="9" t="s">
@@ -29036,15 +29038,15 @@
       <c r="D159" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G159" s="35"/>
-      <c r="H159" s="35"/>
-      <c r="I159" s="35"/>
+      <c r="G159" s="36"/>
+      <c r="H159" s="36"/>
+      <c r="I159" s="36"/>
     </row>
     <row r="160" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="22" t="s">
+      <c r="A160" s="23" t="s">
         <v>785</v>
       </c>
-      <c r="B160" s="35" t="s">
+      <c r="B160" s="36" t="s">
         <v>2528</v>
       </c>
       <c r="C160" s="9" t="s">
@@ -29053,15 +29055,15 @@
       <c r="D160" s="9" t="s">
         <v>1981</v>
       </c>
-      <c r="G160" s="35"/>
-      <c r="H160" s="35"/>
-      <c r="I160" s="35"/>
+      <c r="G160" s="36"/>
+      <c r="H160" s="36"/>
+      <c r="I160" s="36"/>
     </row>
     <row r="161" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="22" t="s">
+      <c r="A161" s="23" t="s">
         <v>785</v>
       </c>
-      <c r="B161" s="35" t="s">
+      <c r="B161" s="36" t="s">
         <v>232</v>
       </c>
       <c r="C161" s="9" t="s">
@@ -29070,17 +29072,17 @@
       <c r="D161" s="9" t="s">
         <v>2530</v>
       </c>
-      <c r="G161" s="35"/>
-      <c r="H161" s="32" t="s">
+      <c r="G161" s="36"/>
+      <c r="H161" s="33" t="s">
         <v>1266</v>
       </c>
-      <c r="I161" s="35"/>
+      <c r="I161" s="36"/>
     </row>
     <row r="162" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="22" t="s">
+      <c r="A162" s="23" t="s">
         <v>785</v>
       </c>
-      <c r="B162" s="35" t="s">
+      <c r="B162" s="36" t="s">
         <v>2531</v>
       </c>
       <c r="C162" s="9" t="s">
@@ -29089,17 +29091,17 @@
       <c r="D162" s="9" t="s">
         <v>2533</v>
       </c>
-      <c r="G162" s="35"/>
-      <c r="H162" s="32" t="s">
+      <c r="G162" s="36"/>
+      <c r="H162" s="33" t="s">
         <v>1265</v>
       </c>
-      <c r="I162" s="35"/>
+      <c r="I162" s="36"/>
     </row>
     <row r="163" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="22" t="s">
+      <c r="A163" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="B163" s="35" t="s">
+      <c r="B163" s="36" t="s">
         <v>2534</v>
       </c>
       <c r="C163" s="9" t="s">
@@ -29108,15 +29110,15 @@
       <c r="D163" s="9" t="s">
         <v>2536</v>
       </c>
-      <c r="G163" s="35"/>
-      <c r="H163" s="35"/>
-      <c r="I163" s="35"/>
+      <c r="G163" s="36"/>
+      <c r="H163" s="36"/>
+      <c r="I163" s="36"/>
     </row>
     <row r="164" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="22" t="s">
+      <c r="A164" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="B164" s="35" t="s">
+      <c r="B164" s="36" t="s">
         <v>2537</v>
       </c>
       <c r="C164" s="9" t="s">
@@ -29125,15 +29127,15 @@
       <c r="D164" s="9" t="s">
         <v>2539</v>
       </c>
-      <c r="G164" s="35"/>
-      <c r="H164" s="35"/>
-      <c r="I164" s="35"/>
+      <c r="G164" s="36"/>
+      <c r="H164" s="36"/>
+      <c r="I164" s="36"/>
     </row>
     <row r="165" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="22" t="s">
+      <c r="A165" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="B165" s="35" t="s">
+      <c r="B165" s="36" t="s">
         <v>1208</v>
       </c>
       <c r="C165" s="9" t="s">
@@ -29142,15 +29144,15 @@
       <c r="D165" s="9" t="s">
         <v>2541</v>
       </c>
-      <c r="G165" s="35"/>
-      <c r="H165" s="35"/>
-      <c r="I165" s="35"/>
+      <c r="G165" s="36"/>
+      <c r="H165" s="36"/>
+      <c r="I165" s="36"/>
     </row>
     <row r="166" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="22" t="s">
+      <c r="A166" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="B166" s="35" t="s">
+      <c r="B166" s="36" t="s">
         <v>1244</v>
       </c>
       <c r="C166" s="9" t="s">
@@ -29159,26 +29161,26 @@
       <c r="D166" s="9" t="s">
         <v>2543</v>
       </c>
-      <c r="G166" s="35"/>
-      <c r="H166" s="35"/>
-      <c r="I166" s="35"/>
+      <c r="G166" s="36"/>
+      <c r="H166" s="36"/>
+      <c r="I166" s="36"/>
     </row>
     <row r="167" s="9" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="22" t="s">
+      <c r="A167" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="B167" s="35"/>
-      <c r="G167" s="35" t="s">
+      <c r="B167" s="36"/>
+      <c r="G167" s="36" t="s">
         <v>2230</v>
       </c>
-      <c r="H167" s="35"/>
-      <c r="I167" s="35"/>
+      <c r="H167" s="36"/>
+      <c r="I167" s="36"/>
     </row>
     <row r="168" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="22" t="s">
+      <c r="A168" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="B168" s="35" t="s">
+      <c r="B168" s="36" t="s">
         <v>2544</v>
       </c>
       <c r="C168" s="9" t="s">
@@ -29187,17 +29189,17 @@
       <c r="D168" s="9" t="s">
         <v>2546</v>
       </c>
-      <c r="G168" s="35"/>
-      <c r="H168" s="35" t="s">
+      <c r="G168" s="36"/>
+      <c r="H168" s="36" t="s">
         <v>1222</v>
       </c>
-      <c r="I168" s="35"/>
+      <c r="I168" s="36"/>
     </row>
     <row r="169" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="22" t="s">
+      <c r="A169" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="B169" s="35" t="s">
+      <c r="B169" s="36" t="s">
         <v>2547</v>
       </c>
       <c r="C169" s="9" t="s">
@@ -29206,17 +29208,17 @@
       <c r="D169" s="9" t="s">
         <v>2549</v>
       </c>
-      <c r="G169" s="35"/>
-      <c r="H169" s="35" t="s">
+      <c r="G169" s="36"/>
+      <c r="H169" s="36" t="s">
         <v>1222</v>
       </c>
-      <c r="I169" s="35"/>
+      <c r="I169" s="36"/>
     </row>
     <row r="170" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="22" t="s">
+      <c r="A170" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="B170" s="35" t="s">
+      <c r="B170" s="36" t="s">
         <v>2550</v>
       </c>
       <c r="C170" s="9" t="s">
@@ -29225,17 +29227,17 @@
       <c r="D170" s="9" t="s">
         <v>2552</v>
       </c>
-      <c r="G170" s="35"/>
-      <c r="H170" s="35" t="s">
+      <c r="G170" s="36"/>
+      <c r="H170" s="36" t="s">
         <v>1222</v>
       </c>
-      <c r="I170" s="35"/>
+      <c r="I170" s="36"/>
     </row>
     <row r="171" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="22" t="s">
+      <c r="A171" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="B171" s="35" t="s">
+      <c r="B171" s="36" t="s">
         <v>2553</v>
       </c>
       <c r="C171" s="9" t="s">
@@ -29244,17 +29246,17 @@
       <c r="D171" s="9" t="s">
         <v>2555</v>
       </c>
-      <c r="G171" s="35"/>
-      <c r="H171" s="35" t="s">
+      <c r="G171" s="36"/>
+      <c r="H171" s="36" t="s">
         <v>1222</v>
       </c>
-      <c r="I171" s="35"/>
+      <c r="I171" s="36"/>
     </row>
     <row r="172" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="22" t="s">
+      <c r="A172" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="B172" s="35" t="s">
+      <c r="B172" s="36" t="s">
         <v>2556</v>
       </c>
       <c r="C172" s="9" t="s">
@@ -29263,17 +29265,17 @@
       <c r="D172" s="9" t="s">
         <v>2558</v>
       </c>
-      <c r="G172" s="35"/>
-      <c r="H172" s="35" t="s">
+      <c r="G172" s="36"/>
+      <c r="H172" s="36" t="s">
         <v>1222</v>
       </c>
-      <c r="I172" s="35"/>
+      <c r="I172" s="36"/>
     </row>
     <row r="173" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="22" t="s">
+      <c r="A173" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="B173" s="35" t="s">
+      <c r="B173" s="36" t="s">
         <v>2559</v>
       </c>
       <c r="C173" s="9" t="s">
@@ -29282,17 +29284,17 @@
       <c r="D173" s="9" t="s">
         <v>2561</v>
       </c>
-      <c r="G173" s="35"/>
-      <c r="H173" s="35" t="s">
+      <c r="G173" s="36"/>
+      <c r="H173" s="36" t="s">
         <v>1222</v>
       </c>
-      <c r="I173" s="35"/>
+      <c r="I173" s="36"/>
     </row>
     <row r="174" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="22" t="s">
+      <c r="A174" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="B174" s="35" t="s">
+      <c r="B174" s="36" t="s">
         <v>2562</v>
       </c>
       <c r="C174" s="9" t="s">
@@ -29301,17 +29303,17 @@
       <c r="D174" s="9" t="s">
         <v>2564</v>
       </c>
-      <c r="G174" s="35"/>
-      <c r="H174" s="35" t="s">
+      <c r="G174" s="36"/>
+      <c r="H174" s="36" t="s">
         <v>1222</v>
       </c>
-      <c r="I174" s="35"/>
+      <c r="I174" s="36"/>
     </row>
     <row r="175" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="22" t="s">
+      <c r="A175" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="B175" s="35" t="s">
+      <c r="B175" s="36" t="s">
         <v>2565</v>
       </c>
       <c r="C175" s="9" t="s">
@@ -29320,17 +29322,17 @@
       <c r="D175" s="9" t="s">
         <v>2567</v>
       </c>
-      <c r="G175" s="35"/>
-      <c r="H175" s="35" t="s">
+      <c r="G175" s="36"/>
+      <c r="H175" s="36" t="s">
         <v>1222</v>
       </c>
-      <c r="I175" s="35"/>
+      <c r="I175" s="36"/>
     </row>
     <row r="176" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="22" t="s">
+      <c r="A176" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="B176" s="35" t="s">
+      <c r="B176" s="36" t="s">
         <v>2568</v>
       </c>
       <c r="C176" s="9" t="s">
@@ -29339,17 +29341,17 @@
       <c r="D176" s="9" t="s">
         <v>2570</v>
       </c>
-      <c r="G176" s="35"/>
-      <c r="H176" s="35" t="s">
+      <c r="G176" s="36"/>
+      <c r="H176" s="36" t="s">
         <v>1222</v>
       </c>
-      <c r="I176" s="35"/>
+      <c r="I176" s="36"/>
     </row>
     <row r="177" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="22" t="s">
+      <c r="A177" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="B177" s="22" t="s">
+      <c r="B177" s="23" t="s">
         <v>232</v>
       </c>
       <c r="C177" s="9" t="s">
@@ -29358,28 +29360,28 @@
       <c r="D177" s="9" t="s">
         <v>2228</v>
       </c>
-      <c r="G177" s="35"/>
-      <c r="H177" s="35" t="s">
+      <c r="G177" s="36"/>
+      <c r="H177" s="36" t="s">
         <v>1222</v>
       </c>
-      <c r="I177" s="35"/>
+      <c r="I177" s="36"/>
     </row>
     <row r="178" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="22" t="s">
+      <c r="A178" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="B178" s="35"/>
-      <c r="G178" s="35" t="s">
+      <c r="B178" s="36"/>
+      <c r="G178" s="36" t="s">
         <v>1188</v>
       </c>
-      <c r="H178" s="35"/>
-      <c r="I178" s="35"/>
+      <c r="H178" s="36"/>
+      <c r="I178" s="36"/>
     </row>
     <row r="179" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="35" t="s">
+      <c r="A179" s="36" t="s">
         <v>260</v>
       </c>
-      <c r="B179" s="35" t="s">
+      <c r="B179" s="36" t="s">
         <v>2571</v>
       </c>
       <c r="C179" s="9" t="s">
@@ -29388,17 +29390,17 @@
       <c r="D179" s="9" t="s">
         <v>2573</v>
       </c>
-      <c r="G179" s="35"/>
-      <c r="H179" s="35" t="s">
+      <c r="G179" s="36"/>
+      <c r="H179" s="36" t="s">
         <v>1224</v>
       </c>
-      <c r="I179" s="35"/>
+      <c r="I179" s="36"/>
     </row>
     <row r="180" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="35" t="s">
+      <c r="A180" s="36" t="s">
         <v>260</v>
       </c>
-      <c r="B180" s="35" t="s">
+      <c r="B180" s="36" t="s">
         <v>2574</v>
       </c>
       <c r="C180" s="9" t="s">
@@ -29407,17 +29409,17 @@
       <c r="D180" s="9" t="s">
         <v>2576</v>
       </c>
-      <c r="G180" s="35"/>
-      <c r="H180" s="35" t="s">
+      <c r="G180" s="36"/>
+      <c r="H180" s="36" t="s">
         <v>1224</v>
       </c>
-      <c r="I180" s="35"/>
+      <c r="I180" s="36"/>
     </row>
     <row r="181" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="35" t="s">
+      <c r="A181" s="36" t="s">
         <v>260</v>
       </c>
-      <c r="B181" s="35" t="s">
+      <c r="B181" s="36" t="s">
         <v>2577</v>
       </c>
       <c r="C181" s="9" t="s">
@@ -29426,17 +29428,17 @@
       <c r="D181" s="9" t="s">
         <v>2579</v>
       </c>
-      <c r="G181" s="35"/>
-      <c r="H181" s="35" t="s">
+      <c r="G181" s="36"/>
+      <c r="H181" s="36" t="s">
         <v>1224</v>
       </c>
-      <c r="I181" s="35"/>
+      <c r="I181" s="36"/>
     </row>
     <row r="182" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="35" t="s">
+      <c r="A182" s="36" t="s">
         <v>260</v>
       </c>
-      <c r="B182" s="35" t="s">
+      <c r="B182" s="36" t="s">
         <v>2580</v>
       </c>
       <c r="C182" s="9" t="s">
@@ -29445,17 +29447,17 @@
       <c r="D182" s="9" t="s">
         <v>2582</v>
       </c>
-      <c r="G182" s="35"/>
-      <c r="H182" s="35" t="s">
+      <c r="G182" s="36"/>
+      <c r="H182" s="36" t="s">
         <v>1224</v>
       </c>
-      <c r="I182" s="35"/>
+      <c r="I182" s="36"/>
     </row>
     <row r="183" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="35" t="s">
+      <c r="A183" s="36" t="s">
         <v>260</v>
       </c>
-      <c r="B183" s="35" t="s">
+      <c r="B183" s="36" t="s">
         <v>2583</v>
       </c>
       <c r="C183" s="9" t="s">
@@ -29464,17 +29466,17 @@
       <c r="D183" s="9" t="s">
         <v>2585</v>
       </c>
-      <c r="G183" s="35"/>
-      <c r="H183" s="35" t="s">
+      <c r="G183" s="36"/>
+      <c r="H183" s="36" t="s">
         <v>1224</v>
       </c>
-      <c r="I183" s="35"/>
+      <c r="I183" s="36"/>
     </row>
     <row r="184" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="35" t="s">
+      <c r="A184" s="36" t="s">
         <v>260</v>
       </c>
-      <c r="B184" s="35" t="s">
+      <c r="B184" s="36" t="s">
         <v>2586</v>
       </c>
       <c r="C184" s="9" t="s">
@@ -29483,17 +29485,17 @@
       <c r="D184" s="9" t="s">
         <v>2588</v>
       </c>
-      <c r="G184" s="35"/>
-      <c r="H184" s="35" t="s">
+      <c r="G184" s="36"/>
+      <c r="H184" s="36" t="s">
         <v>1224</v>
       </c>
-      <c r="I184" s="35"/>
+      <c r="I184" s="36"/>
     </row>
     <row r="185" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="35" t="s">
+      <c r="A185" s="36" t="s">
         <v>260</v>
       </c>
-      <c r="B185" s="35" t="s">
+      <c r="B185" s="36" t="s">
         <v>2589</v>
       </c>
       <c r="C185" s="9" t="s">
@@ -29502,17 +29504,17 @@
       <c r="D185" s="9" t="s">
         <v>2591</v>
       </c>
-      <c r="G185" s="35"/>
-      <c r="H185" s="35" t="s">
+      <c r="G185" s="36"/>
+      <c r="H185" s="36" t="s">
         <v>1224</v>
       </c>
-      <c r="I185" s="35"/>
+      <c r="I185" s="36"/>
     </row>
     <row r="186" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="35" t="s">
+      <c r="A186" s="36" t="s">
         <v>260</v>
       </c>
-      <c r="B186" s="35" t="s">
+      <c r="B186" s="36" t="s">
         <v>1226</v>
       </c>
       <c r="C186" s="9" t="s">
@@ -29521,17 +29523,17 @@
       <c r="D186" s="9" t="s">
         <v>2593</v>
       </c>
-      <c r="G186" s="47"/>
-      <c r="H186" s="35" t="s">
+      <c r="G186" s="48"/>
+      <c r="H186" s="36" t="s">
         <v>1229</v>
       </c>
-      <c r="I186" s="35"/>
+      <c r="I186" s="36"/>
     </row>
     <row r="187" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="35" t="s">
+      <c r="A187" s="36" t="s">
         <v>260</v>
       </c>
-      <c r="B187" s="22" t="s">
+      <c r="B187" s="23" t="s">
         <v>232</v>
       </c>
       <c r="C187" s="9" t="s">
@@ -29540,17 +29542,17 @@
       <c r="D187" s="9" t="s">
         <v>2228</v>
       </c>
-      <c r="G187" s="35"/>
-      <c r="H187" s="35" t="s">
+      <c r="G187" s="36"/>
+      <c r="H187" s="36" t="s">
         <v>1224</v>
       </c>
-      <c r="I187" s="35"/>
+      <c r="I187" s="36"/>
     </row>
     <row r="188" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="35" t="s">
+      <c r="A188" s="36" t="s">
         <v>260</v>
       </c>
-      <c r="B188" s="35" t="s">
+      <c r="B188" s="36" t="s">
         <v>1188</v>
       </c>
       <c r="C188" s="9" t="s">
@@ -29559,17 +29561,17 @@
       <c r="D188" s="9" t="s">
         <v>2234</v>
       </c>
-      <c r="G188" s="47"/>
-      <c r="H188" s="35" t="s">
+      <c r="G188" s="48"/>
+      <c r="H188" s="36" t="s">
         <v>1230</v>
       </c>
-      <c r="I188" s="35"/>
+      <c r="I188" s="36"/>
     </row>
     <row r="189" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="22" t="s">
+      <c r="A189" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="B189" s="35" t="s">
+      <c r="B189" s="36" t="s">
         <v>2594</v>
       </c>
       <c r="C189" s="9" t="s">
@@ -29578,15 +29580,15 @@
       <c r="D189" s="9" t="s">
         <v>2596</v>
       </c>
-      <c r="G189" s="35"/>
-      <c r="H189" s="72"/>
-      <c r="I189" s="35"/>
+      <c r="G189" s="36"/>
+      <c r="H189" s="73"/>
+      <c r="I189" s="36"/>
     </row>
     <row r="190" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="22" t="s">
+      <c r="A190" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="B190" s="35" t="s">
+      <c r="B190" s="36" t="s">
         <v>2597</v>
       </c>
       <c r="C190" s="9" t="s">
@@ -29595,15 +29597,15 @@
       <c r="D190" s="9" t="s">
         <v>2599</v>
       </c>
-      <c r="G190" s="35"/>
-      <c r="H190" s="35"/>
-      <c r="I190" s="35"/>
+      <c r="G190" s="36"/>
+      <c r="H190" s="36"/>
+      <c r="I190" s="36"/>
     </row>
     <row r="191" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="22" t="s">
+      <c r="A191" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="B191" s="35" t="s">
+      <c r="B191" s="36" t="s">
         <v>2600</v>
       </c>
       <c r="C191" s="9" t="s">
@@ -29612,15 +29614,15 @@
       <c r="D191" s="9" t="s">
         <v>2602</v>
       </c>
-      <c r="G191" s="35"/>
-      <c r="H191" s="35"/>
-      <c r="I191" s="35"/>
+      <c r="G191" s="36"/>
+      <c r="H191" s="36"/>
+      <c r="I191" s="36"/>
     </row>
     <row r="192" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="22" t="s">
+      <c r="A192" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="B192" s="35" t="s">
+      <c r="B192" s="36" t="s">
         <v>2603</v>
       </c>
       <c r="C192" s="9" t="s">
@@ -29629,15 +29631,15 @@
       <c r="D192" s="9" t="s">
         <v>2605</v>
       </c>
-      <c r="G192" s="35"/>
-      <c r="H192" s="35"/>
-      <c r="I192" s="35"/>
+      <c r="G192" s="36"/>
+      <c r="H192" s="36"/>
+      <c r="I192" s="36"/>
     </row>
     <row r="193" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="22" t="s">
+      <c r="A193" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="B193" s="35" t="s">
+      <c r="B193" s="36" t="s">
         <v>2606</v>
       </c>
       <c r="C193" s="9" t="s">
@@ -29646,15 +29648,15 @@
       <c r="D193" s="9" t="s">
         <v>2608</v>
       </c>
-      <c r="G193" s="35"/>
-      <c r="H193" s="35"/>
-      <c r="I193" s="35"/>
+      <c r="G193" s="36"/>
+      <c r="H193" s="36"/>
+      <c r="I193" s="36"/>
     </row>
     <row r="194" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="22" t="s">
+      <c r="A194" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="B194" s="35" t="s">
+      <c r="B194" s="36" t="s">
         <v>2594</v>
       </c>
       <c r="C194" s="9" t="s">
@@ -29663,17 +29665,17 @@
       <c r="D194" s="9" t="s">
         <v>2596</v>
       </c>
-      <c r="G194" s="35"/>
-      <c r="H194" s="72" t="s">
+      <c r="G194" s="36"/>
+      <c r="H194" s="73" t="s">
         <v>1242</v>
       </c>
-      <c r="I194" s="35"/>
+      <c r="I194" s="36"/>
     </row>
     <row r="195" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="22" t="s">
+      <c r="A195" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="B195" s="35" t="s">
+      <c r="B195" s="36" t="s">
         <v>2597</v>
       </c>
       <c r="C195" s="9" t="s">
@@ -29682,15 +29684,15 @@
       <c r="D195" s="9" t="s">
         <v>2599</v>
       </c>
-      <c r="G195" s="35"/>
-      <c r="H195" s="35"/>
-      <c r="I195" s="35"/>
+      <c r="G195" s="36"/>
+      <c r="H195" s="36"/>
+      <c r="I195" s="36"/>
     </row>
     <row r="196" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="22" t="s">
+      <c r="A196" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="B196" s="35" t="s">
+      <c r="B196" s="36" t="s">
         <v>2600</v>
       </c>
       <c r="C196" s="9" t="s">
@@ -29699,15 +29701,15 @@
       <c r="D196" s="9" t="s">
         <v>2602</v>
       </c>
-      <c r="G196" s="35"/>
-      <c r="H196" s="35"/>
-      <c r="I196" s="35"/>
+      <c r="G196" s="36"/>
+      <c r="H196" s="36"/>
+      <c r="I196" s="36"/>
     </row>
     <row r="197" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="22" t="s">
+      <c r="A197" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="B197" s="35" t="s">
+      <c r="B197" s="36" t="s">
         <v>2603</v>
       </c>
       <c r="C197" s="9" t="s">
@@ -29716,15 +29718,15 @@
       <c r="D197" s="9" t="s">
         <v>2605</v>
       </c>
-      <c r="G197" s="35"/>
-      <c r="H197" s="35"/>
-      <c r="I197" s="35"/>
+      <c r="G197" s="36"/>
+      <c r="H197" s="36"/>
+      <c r="I197" s="36"/>
     </row>
     <row r="198" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="22" t="s">
+      <c r="A198" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="B198" s="35" t="s">
+      <c r="B198" s="36" t="s">
         <v>2606</v>
       </c>
       <c r="C198" s="9" t="s">
@@ -29733,15 +29735,15 @@
       <c r="D198" s="9" t="s">
         <v>2608</v>
       </c>
-      <c r="G198" s="35"/>
-      <c r="H198" s="35"/>
-      <c r="I198" s="35"/>
+      <c r="G198" s="36"/>
+      <c r="H198" s="36"/>
+      <c r="I198" s="36"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="47" t="s">
+      <c r="A199" s="48" t="s">
         <v>850</v>
       </c>
-      <c r="B199" s="47" t="s">
+      <c r="B199" s="48" t="s">
         <v>2464</v>
       </c>
       <c r="C199" s="9" t="s">
@@ -29752,10 +29754,10 @@
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="47" t="s">
+      <c r="A200" s="48" t="s">
         <v>850</v>
       </c>
-      <c r="B200" s="47" t="s">
+      <c r="B200" s="48" t="s">
         <v>2472</v>
       </c>
       <c r="C200" s="9" t="s">
@@ -29766,10 +29768,10 @@
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="47" t="s">
+      <c r="A201" s="48" t="s">
         <v>850</v>
       </c>
-      <c r="B201" s="47" t="s">
+      <c r="B201" s="48" t="s">
         <v>2609</v>
       </c>
       <c r="C201" s="9" t="s">
@@ -29780,10 +29782,10 @@
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="47" t="s">
+      <c r="A202" s="48" t="s">
         <v>850</v>
       </c>
-      <c r="B202" s="47" t="s">
+      <c r="B202" s="48" t="s">
         <v>2476</v>
       </c>
       <c r="C202" s="9" t="s">
@@ -29794,18 +29796,18 @@
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="47" t="s">
+      <c r="A203" s="48" t="s">
         <v>850</v>
       </c>
-      <c r="G203" s="47" t="s">
+      <c r="G203" s="48" t="s">
         <v>2229</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="47" t="s">
+      <c r="A204" s="48" t="s">
         <v>875</v>
       </c>
-      <c r="B204" s="47" t="s">
+      <c r="B204" s="48" t="s">
         <v>2614</v>
       </c>
       <c r="C204" s="9" t="s">
@@ -29816,10 +29818,10 @@
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="47" t="s">
+      <c r="A205" s="48" t="s">
         <v>875</v>
       </c>
-      <c r="B205" s="47" t="s">
+      <c r="B205" s="48" t="s">
         <v>2617</v>
       </c>
       <c r="C205" s="9" t="s">
@@ -29830,10 +29832,10 @@
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="47" t="s">
+      <c r="A206" s="48" t="s">
         <v>875</v>
       </c>
-      <c r="B206" s="47" t="s">
+      <c r="B206" s="48" t="s">
         <v>2620</v>
       </c>
       <c r="C206" s="9" t="s">
@@ -29844,10 +29846,10 @@
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="47" t="s">
+      <c r="A207" s="48" t="s">
         <v>875</v>
       </c>
-      <c r="B207" s="47" t="s">
+      <c r="B207" s="48" t="s">
         <v>2623</v>
       </c>
       <c r="C207" s="9" t="s">
@@ -29858,10 +29860,10 @@
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="47" t="s">
+      <c r="A208" s="48" t="s">
         <v>875</v>
       </c>
-      <c r="B208" s="47" t="s">
+      <c r="B208" s="48" t="s">
         <v>2626</v>
       </c>
       <c r="C208" s="9" t="s">
@@ -29872,10 +29874,10 @@
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="47" t="s">
+      <c r="A209" s="48" t="s">
         <v>875</v>
       </c>
-      <c r="B209" s="47" t="s">
+      <c r="B209" s="48" t="s">
         <v>2629</v>
       </c>
       <c r="C209" s="9" t="s">
@@ -29886,10 +29888,10 @@
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="47" t="s">
+      <c r="A210" s="48" t="s">
         <v>875</v>
       </c>
-      <c r="B210" s="47" t="s">
+      <c r="B210" s="48" t="s">
         <v>232</v>
       </c>
       <c r="C210" s="9" t="s">
@@ -29900,10 +29902,10 @@
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="47" t="s">
+      <c r="A211" s="48" t="s">
         <v>880</v>
       </c>
-      <c r="B211" s="47" t="s">
+      <c r="B211" s="48" t="s">
         <v>2464</v>
       </c>
       <c r="C211" s="9" t="s">
@@ -29914,10 +29916,10 @@
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="47" t="s">
+      <c r="A212" s="48" t="s">
         <v>880</v>
       </c>
-      <c r="B212" s="47" t="s">
+      <c r="B212" s="48" t="s">
         <v>2472</v>
       </c>
       <c r="C212" s="9" t="s">
@@ -29928,10 +29930,10 @@
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="47" t="s">
+      <c r="A213" s="48" t="s">
         <v>880</v>
       </c>
-      <c r="B213" s="47" t="s">
+      <c r="B213" s="48" t="s">
         <v>2470</v>
       </c>
       <c r="C213" s="9" t="s">
@@ -29942,10 +29944,10 @@
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="47" t="s">
+      <c r="A214" s="48" t="s">
         <v>880</v>
       </c>
-      <c r="B214" s="47" t="s">
+      <c r="B214" s="48" t="s">
         <v>2471</v>
       </c>
       <c r="C214" s="9" t="s">
@@ -29956,10 +29958,10 @@
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="47" t="s">
+      <c r="A215" s="48" t="s">
         <v>880</v>
       </c>
-      <c r="B215" s="47" t="s">
+      <c r="B215" s="48" t="s">
         <v>2476</v>
       </c>
       <c r="C215" s="9" t="s">
@@ -29970,10 +29972,10 @@
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="47" t="s">
+      <c r="A216" s="48" t="s">
         <v>880</v>
       </c>
-      <c r="B216" s="47" t="s">
+      <c r="B216" s="48" t="s">
         <v>232</v>
       </c>
       <c r="C216" s="9" t="s">
@@ -29983,140 +29985,140 @@
         <v>2639</v>
       </c>
     </row>
-    <row r="217" s="41" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="62" t="s">
+    <row r="217" s="42" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="63" t="s">
         <v>1071</v>
       </c>
-      <c r="B217" s="47" t="s">
+      <c r="B217" s="48" t="s">
         <v>2640</v>
       </c>
-      <c r="C217" s="41" t="s">
+      <c r="C217" s="42" t="s">
         <v>2641</v>
       </c>
-      <c r="D217" s="41" t="s">
+      <c r="D217" s="42" t="s">
         <v>2642</v>
       </c>
-      <c r="G217" s="47"/>
-      <c r="H217" s="22" t="s">
+      <c r="G217" s="48"/>
+      <c r="H217" s="23" t="s">
         <v>1185</v>
       </c>
-      <c r="I217" s="47"/>
-    </row>
-    <row r="218" s="41" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="62" t="s">
+      <c r="I217" s="48"/>
+    </row>
+    <row r="218" s="42" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="63" t="s">
         <v>1071</v>
       </c>
-      <c r="B218" s="47" t="s">
+      <c r="B218" s="48" t="s">
         <v>2643</v>
       </c>
-      <c r="C218" s="41" t="s">
+      <c r="C218" s="42" t="s">
         <v>2644</v>
       </c>
-      <c r="D218" s="41" t="s">
+      <c r="D218" s="42" t="s">
         <v>2645</v>
       </c>
-      <c r="G218" s="47"/>
-      <c r="H218" s="22" t="s">
+      <c r="G218" s="48"/>
+      <c r="H218" s="23" t="s">
         <v>1185</v>
       </c>
-      <c r="I218" s="47"/>
-    </row>
-    <row r="219" s="41" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="62" t="s">
+      <c r="I218" s="48"/>
+    </row>
+    <row r="219" s="42" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="63" t="s">
         <v>1071</v>
       </c>
-      <c r="B219" s="47" t="s">
+      <c r="B219" s="48" t="s">
         <v>2646</v>
       </c>
-      <c r="C219" s="41" t="s">
+      <c r="C219" s="42" t="s">
         <v>2647</v>
       </c>
-      <c r="D219" s="41" t="s">
+      <c r="D219" s="42" t="s">
         <v>2648</v>
       </c>
-      <c r="G219" s="47"/>
-      <c r="H219" s="22" t="s">
+      <c r="G219" s="48"/>
+      <c r="H219" s="23" t="s">
         <v>1185</v>
       </c>
-      <c r="I219" s="47"/>
-    </row>
-    <row r="220" s="41" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="62" t="s">
+      <c r="I219" s="48"/>
+    </row>
+    <row r="220" s="42" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="63" t="s">
         <v>1071</v>
       </c>
-      <c r="B220" s="47" t="s">
+      <c r="B220" s="48" t="s">
         <v>2649</v>
       </c>
-      <c r="C220" s="41" t="s">
+      <c r="C220" s="42" t="s">
         <v>2650</v>
       </c>
-      <c r="D220" s="41" t="s">
+      <c r="D220" s="42" t="s">
         <v>2651</v>
       </c>
-      <c r="G220" s="47"/>
-      <c r="H220" s="22" t="s">
+      <c r="G220" s="48"/>
+      <c r="H220" s="23" t="s">
         <v>1185</v>
       </c>
-      <c r="I220" s="47"/>
-    </row>
-    <row r="221" s="41" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="62" t="s">
+      <c r="I220" s="48"/>
+    </row>
+    <row r="221" s="42" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="63" t="s">
         <v>1071</v>
       </c>
-      <c r="B221" s="47" t="s">
+      <c r="B221" s="48" t="s">
         <v>2652</v>
       </c>
-      <c r="C221" s="41" t="s">
+      <c r="C221" s="42" t="s">
         <v>2653</v>
       </c>
-      <c r="D221" s="41" t="s">
+      <c r="D221" s="42" t="s">
         <v>2654</v>
       </c>
-      <c r="G221" s="47"/>
-      <c r="H221" s="22" t="s">
+      <c r="G221" s="48"/>
+      <c r="H221" s="23" t="s">
         <v>1184</v>
       </c>
-      <c r="I221" s="47"/>
-    </row>
-    <row r="222" s="41" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="62" t="s">
+      <c r="I221" s="48"/>
+    </row>
+    <row r="222" s="42" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="63" t="s">
         <v>1071</v>
       </c>
-      <c r="B222" s="47" t="s">
+      <c r="B222" s="48" t="s">
         <v>2655</v>
       </c>
-      <c r="C222" s="41" t="s">
+      <c r="C222" s="42" t="s">
         <v>2656</v>
       </c>
-      <c r="D222" s="41" t="s">
+      <c r="D222" s="42" t="s">
         <v>2657</v>
       </c>
-      <c r="G222" s="47"/>
-      <c r="H222" s="47"/>
-      <c r="I222" s="47"/>
-    </row>
-    <row r="223" s="41" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="62" t="s">
+      <c r="G222" s="48"/>
+      <c r="H222" s="48"/>
+      <c r="I222" s="48"/>
+    </row>
+    <row r="223" s="42" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="63" t="s">
         <v>1071</v>
       </c>
-      <c r="B223" s="47" t="s">
+      <c r="B223" s="48" t="s">
         <v>2658</v>
       </c>
-      <c r="C223" s="41" t="s">
+      <c r="C223" s="42" t="s">
         <v>2659</v>
       </c>
-      <c r="D223" s="41" t="s">
+      <c r="D223" s="42" t="s">
         <v>2660</v>
       </c>
-      <c r="G223" s="47"/>
-      <c r="H223" s="47"/>
-      <c r="I223" s="47"/>
+      <c r="G223" s="48"/>
+      <c r="H223" s="48"/>
+      <c r="I223" s="48"/>
     </row>
     <row r="224" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="22" t="s">
+      <c r="A224" s="23" t="s">
         <v>2661</v>
       </c>
-      <c r="B224" s="47" t="s">
+      <c r="B224" s="48" t="s">
         <v>1208</v>
       </c>
       <c r="C224" s="9" t="s">
@@ -30127,10 +30129,10 @@
       </c>
     </row>
     <row r="225" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="22" t="s">
+      <c r="A225" s="23" t="s">
         <v>2661</v>
       </c>
-      <c r="B225" s="47" t="s">
+      <c r="B225" s="48" t="s">
         <v>1244</v>
       </c>
       <c r="C225" s="9" t="s">
@@ -30141,10 +30143,10 @@
       </c>
     </row>
     <row r="226" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="22" t="s">
+      <c r="A226" s="23" t="s">
         <v>1107</v>
       </c>
-      <c r="B226" s="47" t="s">
+      <c r="B226" s="48" t="s">
         <v>2666</v>
       </c>
       <c r="C226" s="9" t="s">
@@ -30155,10 +30157,10 @@
       </c>
     </row>
     <row r="227" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="22" t="s">
+      <c r="A227" s="23" t="s">
         <v>1107</v>
       </c>
-      <c r="B227" s="47" t="s">
+      <c r="B227" s="48" t="s">
         <v>2669</v>
       </c>
       <c r="C227" s="9" t="s">
@@ -30169,10 +30171,10 @@
       </c>
     </row>
     <row r="228" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="22" t="s">
+      <c r="A228" s="23" t="s">
         <v>1107</v>
       </c>
-      <c r="B228" s="47" t="s">
+      <c r="B228" s="48" t="s">
         <v>2672</v>
       </c>
       <c r="C228" s="9" t="s">
@@ -30183,10 +30185,10 @@
       </c>
     </row>
     <row r="229" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="22" t="s">
+      <c r="A229" s="23" t="s">
         <v>1107</v>
       </c>
-      <c r="B229" s="47" t="s">
+      <c r="B229" s="48" t="s">
         <v>2675</v>
       </c>
       <c r="C229" s="9" t="s">
@@ -30197,10 +30199,10 @@
       </c>
     </row>
     <row r="230" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="22" t="s">
+      <c r="A230" s="23" t="s">
         <v>1107</v>
       </c>
-      <c r="B230" s="47" t="s">
+      <c r="B230" s="48" t="s">
         <v>2678</v>
       </c>
       <c r="C230" s="9" t="s">
@@ -30211,10 +30213,10 @@
       </c>
     </row>
     <row r="231" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="22" t="s">
+      <c r="A231" s="23" t="s">
         <v>1107</v>
       </c>
-      <c r="B231" s="47" t="s">
+      <c r="B231" s="48" t="s">
         <v>2681</v>
       </c>
       <c r="C231" s="9" t="s">
@@ -30225,10 +30227,10 @@
       </c>
     </row>
     <row r="232" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="22" t="s">
+      <c r="A232" s="23" t="s">
         <v>1107</v>
       </c>
-      <c r="G232" s="35" t="s">
+      <c r="G232" s="36" t="s">
         <v>2229</v>
       </c>
     </row>
@@ -30318,10 +30320,10 @@
       <c r="I237" s="9"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="47" t="s">
+      <c r="A238" s="48" t="s">
         <v>1025</v>
       </c>
-      <c r="B238" s="47" t="n">
+      <c r="B238" s="48" t="n">
         <v>-2</v>
       </c>
       <c r="C238" s="9" t="s">
@@ -30332,10 +30334,10 @@
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="47" t="s">
+      <c r="A239" s="48" t="s">
         <v>1025</v>
       </c>
-      <c r="B239" s="47" t="n">
+      <c r="B239" s="48" t="n">
         <v>-1</v>
       </c>
       <c r="C239" s="9" t="s">
@@ -30346,10 +30348,10 @@
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="47" t="s">
+      <c r="A240" s="48" t="s">
         <v>1025</v>
       </c>
-      <c r="B240" s="47" t="n">
+      <c r="B240" s="48" t="n">
         <v>0</v>
       </c>
       <c r="C240" s="9" t="s">
@@ -30360,10 +30362,10 @@
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="47" t="s">
+      <c r="A241" s="48" t="s">
         <v>1025</v>
       </c>
-      <c r="B241" s="47" t="n">
+      <c r="B241" s="48" t="n">
         <v>1</v>
       </c>
       <c r="C241" s="9" t="s">
@@ -30374,10 +30376,10 @@
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="47" t="s">
+      <c r="A242" s="48" t="s">
         <v>1025</v>
       </c>
-      <c r="B242" s="47" t="n">
+      <c r="B242" s="48" t="n">
         <v>2</v>
       </c>
       <c r="C242" s="9" t="s">
@@ -30388,10 +30390,10 @@
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="47" t="s">
+      <c r="A243" s="48" t="s">
         <v>947</v>
       </c>
-      <c r="B243" s="47" t="n">
+      <c r="B243" s="48" t="n">
         <v>0</v>
       </c>
       <c r="C243" s="9" t="s">
@@ -30402,10 +30404,10 @@
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="47" t="s">
+      <c r="A244" s="48" t="s">
         <v>947</v>
       </c>
-      <c r="B244" s="47" t="n">
+      <c r="B244" s="48" t="n">
         <v>1</v>
       </c>
       <c r="C244" s="9" t="s">
@@ -30416,10 +30418,10 @@
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="47" t="s">
+      <c r="A245" s="48" t="s">
         <v>947</v>
       </c>
-      <c r="B245" s="47" t="n">
+      <c r="B245" s="48" t="n">
         <v>2</v>
       </c>
       <c r="C245" s="9" t="s">
@@ -30430,10 +30432,10 @@
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="47" t="s">
+      <c r="A246" s="48" t="s">
         <v>947</v>
       </c>
-      <c r="B246" s="47" t="n">
+      <c r="B246" s="48" t="n">
         <v>3</v>
       </c>
       <c r="C246" s="9" t="s">
@@ -30444,10 +30446,10 @@
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="47" t="s">
+      <c r="A247" s="48" t="s">
         <v>947</v>
       </c>
-      <c r="B247" s="47" t="n">
+      <c r="B247" s="48" t="n">
         <v>4</v>
       </c>
       <c r="C247" s="9" t="s">
@@ -30458,10 +30460,10 @@
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="47" t="s">
+      <c r="A248" s="48" t="s">
         <v>947</v>
       </c>
-      <c r="B248" s="47" t="n">
+      <c r="B248" s="48" t="n">
         <v>-1</v>
       </c>
       <c r="C248" s="9" t="s">
@@ -30472,10 +30474,10 @@
       </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="47" t="s">
+      <c r="A249" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="B249" s="47" t="s">
+      <c r="B249" s="48" t="s">
         <v>2720</v>
       </c>
       <c r="C249" s="9" t="s">

--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -3626,7 +3626,8 @@
   </si>
   <si>
     <t xml:space="preserve">min=0
-max=household.carNumber</t>
+Max=4
+OverMaxAllowed</t>
   </si>
   <si>
     <t xml:space="preserve">householdHasCars</t>
@@ -9094,7 +9095,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="85">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9236,10 +9237,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -18340,7 +18337,7 @@
       <c r="H219" s="10" t="s">
         <v>1094</v>
       </c>
-      <c r="K219" s="36" t="s">
+      <c r="K219" s="10" t="s">
         <v>1088</v>
       </c>
       <c r="M219" s="1" t="s">
@@ -18876,10 +18873,10 @@
       <c r="F234" s="16" t="s">
         <v>1167</v>
       </c>
-      <c r="G234" s="37" t="s">
+      <c r="G234" s="36" t="s">
         <v>1169</v>
       </c>
-      <c r="H234" s="37" t="s">
+      <c r="H234" s="36" t="s">
         <v>1170</v>
       </c>
       <c r="I234" s="16"/>
@@ -19105,7 +19102,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="27.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="15.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="38" width="20.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="37" width="20.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="8" width="19.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="12.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="23.5"/>
@@ -19113,29 +19110,29 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="8" width="8.5"/>
   </cols>
   <sheetData>
-    <row r="1" s="43" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="39" t="s">
+    <row r="1" s="42" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="38" t="s">
         <v>1182</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="38" t="s">
         <v>1183</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="39" t="s">
         <v>1184</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="38" t="s">
         <v>1185</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="38" t="s">
         <v>1186</v>
       </c>
-      <c r="G1" s="41" t="s">
+      <c r="G1" s="40" t="s">
         <v>1187</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="41" t="s">
         <v>23</v>
       </c>
     </row>
@@ -19146,7 +19143,7 @@
       <c r="C2" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E2" s="8" t="n">
@@ -19160,7 +19157,7 @@
       <c r="C3" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="37" t="s">
         <v>1190</v>
       </c>
       <c r="E3" s="8" t="n">
@@ -19174,7 +19171,7 @@
       <c r="C4" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E4" s="8" t="n">
@@ -19188,7 +19185,7 @@
       <c r="C5" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="37" t="s">
         <v>1190</v>
       </c>
       <c r="E5" s="8" t="n">
@@ -19202,7 +19199,7 @@
       <c r="C6" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="37" t="s">
         <v>1190</v>
       </c>
       <c r="E6" s="8" t="n">
@@ -19210,13 +19207,13 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="43" t="s">
         <v>1193</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>1194</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E7" s="8" t="s">
@@ -19230,7 +19227,7 @@
       <c r="C8" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="37" t="s">
         <v>1190</v>
       </c>
       <c r="E8" s="8" t="n">
@@ -19247,7 +19244,7 @@
       <c r="C9" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="37" t="s">
         <v>1199</v>
       </c>
       <c r="E9" s="8" t="n">
@@ -19261,7 +19258,7 @@
       <c r="C10" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="37" t="s">
         <v>1190</v>
       </c>
       <c r="E10" s="8" t="n">
@@ -19278,7 +19275,7 @@
       <c r="C11" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="37" t="s">
         <v>1199</v>
       </c>
       <c r="E11" s="8" t="n">
@@ -19292,7 +19289,7 @@
       <c r="C12" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="37" t="s">
         <v>1190</v>
       </c>
       <c r="E12" s="8" t="n">
@@ -19309,7 +19306,7 @@
       <c r="C13" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="37" t="s">
         <v>1199</v>
       </c>
       <c r="E13" s="8" t="n">
@@ -19323,7 +19320,7 @@
       <c r="C14" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="37" t="s">
         <v>1199</v>
       </c>
       <c r="E14" s="8" t="n">
@@ -19337,7 +19334,7 @@
       <c r="C15" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D15" s="38" t="s">
+      <c r="D15" s="37" t="s">
         <v>1190</v>
       </c>
       <c r="E15" s="8" t="n">
@@ -19351,7 +19348,7 @@
       <c r="C16" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="D16" s="37" t="s">
         <v>1190</v>
       </c>
       <c r="E16" s="8" t="n">
@@ -19365,7 +19362,7 @@
       <c r="C17" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="D17" s="37" t="s">
         <v>1190</v>
       </c>
       <c r="E17" s="8" t="n">
@@ -19379,7 +19376,7 @@
       <c r="C18" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="D18" s="37" t="s">
         <v>1190</v>
       </c>
       <c r="E18" s="8" t="n">
@@ -19393,7 +19390,7 @@
       <c r="C19" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D19" s="38" t="s">
+      <c r="D19" s="37" t="s">
         <v>1199</v>
       </c>
       <c r="E19" s="8" t="n">
@@ -19410,7 +19407,7 @@
       <c r="C20" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="37" t="s">
         <v>1206</v>
       </c>
       <c r="E20" s="8" t="s">
@@ -19424,7 +19421,7 @@
       <c r="C21" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D21" s="38" t="s">
+      <c r="D21" s="37" t="s">
         <v>1190</v>
       </c>
       <c r="E21" s="8" t="n">
@@ -19438,7 +19435,7 @@
       <c r="C22" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D22" s="37" t="s">
         <v>1190</v>
       </c>
       <c r="E22" s="8" t="n">
@@ -19452,7 +19449,7 @@
       <c r="C23" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D23" s="38" t="s">
+      <c r="D23" s="37" t="s">
         <v>1199</v>
       </c>
       <c r="E23" s="8" t="n">
@@ -19469,7 +19466,7 @@
       <c r="C24" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="D24" s="37" t="s">
         <v>1206</v>
       </c>
       <c r="E24" s="8" t="s">
@@ -19484,7 +19481,7 @@
       <c r="C25" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D25" s="38" t="s">
+      <c r="D25" s="37" t="s">
         <v>1190</v>
       </c>
       <c r="E25" s="8" t="n">
@@ -19502,7 +19499,7 @@
       <c r="C26" s="31" t="s">
         <v>1197</v>
       </c>
-      <c r="D26" s="45" t="s">
+      <c r="D26" s="44" t="s">
         <v>1199</v>
       </c>
       <c r="E26" s="31" t="n">
@@ -19519,7 +19516,7 @@
       <c r="C27" s="31" t="s">
         <v>1197</v>
       </c>
-      <c r="D27" s="45" t="s">
+      <c r="D27" s="44" t="s">
         <v>1190</v>
       </c>
       <c r="E27" s="31" t="n">
@@ -19536,7 +19533,7 @@
       <c r="C28" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="D28" s="38" t="s">
+      <c r="D28" s="37" t="s">
         <v>1190</v>
       </c>
       <c r="E28" s="8" t="n">
@@ -19555,7 +19552,7 @@
       <c r="C29" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="D29" s="45" t="s">
+      <c r="D29" s="44" t="s">
         <v>1189</v>
       </c>
       <c r="E29" s="31" t="n">
@@ -19571,7 +19568,7 @@
       <c r="C30" s="8" t="s">
         <v>1214</v>
       </c>
-      <c r="D30" s="38" t="s">
+      <c r="D30" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E30" s="8" t="s">
@@ -19585,10 +19582,10 @@
       <c r="C31" s="8" t="s">
         <v>1216</v>
       </c>
-      <c r="D31" s="38" t="s">
+      <c r="D31" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E31" s="38" t="s">
+      <c r="E31" s="37" t="s">
         <v>1217</v>
       </c>
     </row>
@@ -19602,10 +19599,10 @@
       <c r="C32" s="8" t="s">
         <v>1216</v>
       </c>
-      <c r="D32" s="38" t="s">
+      <c r="D32" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E32" s="38" t="s">
+      <c r="E32" s="37" t="s">
         <v>1218</v>
       </c>
     </row>
@@ -19619,10 +19616,10 @@
       <c r="C33" s="8" t="s">
         <v>1216</v>
       </c>
-      <c r="D33" s="38" t="s">
+      <c r="D33" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E33" s="38" t="s">
+      <c r="E33" s="37" t="s">
         <v>1219</v>
       </c>
       <c r="F33" s="8"/>
@@ -19636,10 +19633,10 @@
       <c r="C34" s="8" t="s">
         <v>1216</v>
       </c>
-      <c r="D34" s="38" t="s">
+      <c r="D34" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E34" s="38" t="s">
+      <c r="E34" s="37" t="s">
         <v>1221</v>
       </c>
     </row>
@@ -19653,10 +19650,10 @@
       <c r="C35" s="8" t="s">
         <v>1216</v>
       </c>
-      <c r="D35" s="38" t="s">
+      <c r="D35" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E35" s="38" t="s">
+      <c r="E35" s="37" t="s">
         <v>1222</v>
       </c>
     </row>
@@ -19670,10 +19667,10 @@
       <c r="C36" s="8" t="s">
         <v>1216</v>
       </c>
-      <c r="D36" s="38" t="s">
+      <c r="D36" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E36" s="38" t="s">
+      <c r="E36" s="37" t="s">
         <v>1219</v>
       </c>
     </row>
@@ -19684,7 +19681,7 @@
       <c r="C37" s="8" t="s">
         <v>1224</v>
       </c>
-      <c r="D37" s="38" t="s">
+      <c r="D37" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E37" s="8" t="s">
@@ -19701,7 +19698,7 @@
       <c r="C38" s="8" t="s">
         <v>1224</v>
       </c>
-      <c r="D38" s="38" t="s">
+      <c r="D38" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E38" s="8" t="s">
@@ -19718,7 +19715,7 @@
       <c r="C39" s="8" t="s">
         <v>1224</v>
       </c>
-      <c r="D39" s="38" t="s">
+      <c r="D39" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E39" s="8" t="s">
@@ -19735,7 +19732,7 @@
       <c r="C40" s="8" t="s">
         <v>1228</v>
       </c>
-      <c r="D40" s="38" t="s">
+      <c r="D40" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E40" s="8" t="s">
@@ -19752,7 +19749,7 @@
       <c r="C41" s="8" t="s">
         <v>1228</v>
       </c>
-      <c r="D41" s="38" t="s">
+      <c r="D41" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E41" s="8" t="s">
@@ -19769,7 +19766,7 @@
       <c r="C42" s="8" t="s">
         <v>1228</v>
       </c>
-      <c r="D42" s="38" t="s">
+      <c r="D42" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E42" s="8" t="s">
@@ -19777,13 +19774,13 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="46" t="s">
+      <c r="A43" s="45" t="s">
         <v>1229</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>1230</v>
       </c>
-      <c r="D43" s="38" t="s">
+      <c r="D43" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E43" s="8" t="s">
@@ -19791,7 +19788,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="46" t="s">
+      <c r="A44" s="45" t="s">
         <v>1229</v>
       </c>
       <c r="B44" s="8" t="s">
@@ -19800,7 +19797,7 @@
       <c r="C44" s="8" t="s">
         <v>1230</v>
       </c>
-      <c r="D44" s="38" t="s">
+      <c r="D44" s="37" t="s">
         <v>1206</v>
       </c>
       <c r="E44" s="8" t="s">
@@ -19814,7 +19811,7 @@
       <c r="C45" s="8" t="s">
         <v>1230</v>
       </c>
-      <c r="D45" s="38" t="s">
+      <c r="D45" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E45" s="8" t="s">
@@ -19822,13 +19819,13 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="46" t="s">
+      <c r="A46" s="45" t="s">
         <v>1231</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>1232</v>
       </c>
-      <c r="D46" s="38" t="s">
+      <c r="D46" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E46" s="8" t="s">
@@ -19836,7 +19833,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="46" t="s">
+      <c r="A47" s="45" t="s">
         <v>1231</v>
       </c>
       <c r="B47" s="8" t="s">
@@ -19845,10 +19842,10 @@
       <c r="C47" s="8" t="s">
         <v>1232</v>
       </c>
-      <c r="D47" s="38" t="s">
+      <c r="D47" s="37" t="s">
         <v>1206</v>
       </c>
-      <c r="E47" s="46" t="s">
+      <c r="E47" s="45" t="s">
         <v>1233</v>
       </c>
       <c r="F47" s="8" t="s">
@@ -19856,7 +19853,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="46" t="s">
+      <c r="A48" s="45" t="s">
         <v>1231</v>
       </c>
       <c r="B48" s="8" t="s">
@@ -19865,7 +19862,7 @@
       <c r="C48" s="8" t="s">
         <v>1232</v>
       </c>
-      <c r="D48" s="38" t="s">
+      <c r="D48" s="37" t="s">
         <v>1206</v>
       </c>
       <c r="E48" s="8" t="s">
@@ -19876,13 +19873,13 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="46" t="s">
+      <c r="A49" s="45" t="s">
         <v>1236</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>1232</v>
       </c>
-      <c r="D49" s="38" t="s">
+      <c r="D49" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E49" s="8" t="s">
@@ -19890,7 +19887,7 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="46" t="s">
+      <c r="A50" s="45" t="s">
         <v>1236</v>
       </c>
       <c r="B50" s="8" t="s">
@@ -19899,7 +19896,7 @@
       <c r="C50" s="8" t="s">
         <v>1232</v>
       </c>
-      <c r="D50" s="38" t="s">
+      <c r="D50" s="37" t="s">
         <v>1206</v>
       </c>
       <c r="E50" s="8" t="s">
@@ -19907,13 +19904,13 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="46" t="s">
+      <c r="A51" s="45" t="s">
         <v>1237</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>1232</v>
       </c>
-      <c r="D51" s="38" t="s">
+      <c r="D51" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E51" s="8" t="s">
@@ -19921,7 +19918,7 @@
       </c>
     </row>
     <row r="52" s="11" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="46" t="s">
+      <c r="A52" s="45" t="s">
         <v>1237</v>
       </c>
       <c r="B52" s="8" t="s">
@@ -19930,10 +19927,10 @@
       <c r="C52" s="8" t="s">
         <v>1232</v>
       </c>
-      <c r="D52" s="38" t="s">
+      <c r="D52" s="37" t="s">
         <v>1206</v>
       </c>
-      <c r="E52" s="46" t="s">
+      <c r="E52" s="45" t="s">
         <v>1233</v>
       </c>
       <c r="F52" s="8"/>
@@ -19948,7 +19945,7 @@
       <c r="C53" s="8" t="s">
         <v>1232</v>
       </c>
-      <c r="D53" s="38" t="s">
+      <c r="D53" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E53" s="8" t="s">
@@ -19966,7 +19963,7 @@
       <c r="C54" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="D54" s="45" t="s">
+      <c r="D54" s="44" t="s">
         <v>1189</v>
       </c>
       <c r="E54" s="31" t="s">
@@ -19986,7 +19983,7 @@
       <c r="C55" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="D55" s="45" t="s">
+      <c r="D55" s="44" t="s">
         <v>1189</v>
       </c>
       <c r="E55" s="31" t="s">
@@ -19997,17 +19994,17 @@
       <c r="H55" s="8"/>
     </row>
     <row r="56" s="11" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="47" t="s">
+      <c r="A56" s="46" t="s">
         <v>1123</v>
       </c>
       <c r="B56" s="8"/>
       <c r="C56" s="8" t="s">
         <v>1116</v>
       </c>
-      <c r="D56" s="48" t="s">
+      <c r="D56" s="47" t="s">
         <v>1189</v>
       </c>
-      <c r="E56" s="43" t="s">
+      <c r="E56" s="42" t="s">
         <v>1215</v>
       </c>
       <c r="F56" s="8"/>
@@ -20015,14 +20012,14 @@
       <c r="H56" s="8"/>
     </row>
     <row r="57" s="11" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="47" t="s">
+      <c r="A57" s="46" t="s">
         <v>1089</v>
       </c>
       <c r="B57" s="8"/>
       <c r="C57" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="D57" s="38" t="s">
+      <c r="D57" s="37" t="s">
         <v>1190</v>
       </c>
       <c r="E57" s="8" t="n">
@@ -20033,14 +20030,14 @@
       <c r="H57" s="8"/>
     </row>
     <row r="58" s="11" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="49" t="s">
+      <c r="A58" s="48" t="s">
         <v>1238</v>
       </c>
       <c r="B58" s="8"/>
       <c r="C58" s="8" t="s">
         <v>1224</v>
       </c>
-      <c r="D58" s="38" t="s">
+      <c r="D58" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E58" s="8" t="s">
@@ -20051,14 +20048,14 @@
       <c r="H58" s="8"/>
     </row>
     <row r="59" s="11" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="50" t="s">
+      <c r="A59" s="49" t="s">
         <v>330</v>
       </c>
       <c r="B59" s="8"/>
       <c r="C59" s="8" t="s">
         <v>1224</v>
       </c>
-      <c r="D59" s="38" t="s">
+      <c r="D59" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E59" s="8" t="s">
@@ -20076,7 +20073,7 @@
       <c r="C60" s="31" t="s">
         <v>1224</v>
       </c>
-      <c r="D60" s="45" t="s">
+      <c r="D60" s="44" t="s">
         <v>1189</v>
       </c>
       <c r="E60" s="31" t="s">
@@ -20097,7 +20094,7 @@
       <c r="C61" s="31" t="s">
         <v>1239</v>
       </c>
-      <c r="D61" s="45" t="s">
+      <c r="D61" s="44" t="s">
         <v>1240</v>
       </c>
       <c r="E61" s="31" t="n">
@@ -20118,7 +20115,7 @@
       <c r="C62" s="31" t="s">
         <v>1224</v>
       </c>
-      <c r="D62" s="45" t="s">
+      <c r="D62" s="44" t="s">
         <v>1189</v>
       </c>
       <c r="E62" s="31" t="s">
@@ -20137,10 +20134,10 @@
       <c r="C63" s="31" t="s">
         <v>1224</v>
       </c>
-      <c r="D63" s="45" t="s">
+      <c r="D63" s="44" t="s">
         <v>1189</v>
       </c>
-      <c r="E63" s="46" t="s">
+      <c r="E63" s="45" t="s">
         <v>1227</v>
       </c>
       <c r="F63" s="31"/>
@@ -20156,10 +20153,10 @@
       <c r="C64" s="31" t="s">
         <v>1224</v>
       </c>
-      <c r="D64" s="45" t="s">
+      <c r="D64" s="44" t="s">
         <v>1189</v>
       </c>
-      <c r="E64" s="46" t="s">
+      <c r="E64" s="45" t="s">
         <v>1241</v>
       </c>
       <c r="F64" s="31"/>
@@ -20172,10 +20169,10 @@
       <c r="C65" s="31" t="s">
         <v>1242</v>
       </c>
-      <c r="D65" s="38" t="s">
+      <c r="D65" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E65" s="49" t="s">
+      <c r="E65" s="48" t="s">
         <v>1215</v>
       </c>
       <c r="H65" s="11"/>
@@ -20187,10 +20184,10 @@
       <c r="C66" s="31" t="s">
         <v>1243</v>
       </c>
-      <c r="D66" s="38" t="s">
+      <c r="D66" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E66" s="49" t="s">
+      <c r="E66" s="48" t="s">
         <v>1215</v>
       </c>
       <c r="H66" s="11"/>
@@ -20205,10 +20202,10 @@
       <c r="C67" s="31" t="s">
         <v>1244</v>
       </c>
-      <c r="D67" s="38" t="s">
+      <c r="D67" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E67" s="49" t="s">
+      <c r="E67" s="48" t="s">
         <v>1073</v>
       </c>
       <c r="F67" s="8" t="s">
@@ -20229,10 +20226,10 @@
       <c r="C68" s="31" t="s">
         <v>1244</v>
       </c>
-      <c r="D68" s="38" t="s">
+      <c r="D68" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E68" s="49" t="s">
+      <c r="E68" s="48" t="s">
         <v>1246</v>
       </c>
       <c r="H68" s="11"/>
@@ -20247,10 +20244,10 @@
       <c r="C69" s="31" t="s">
         <v>1244</v>
       </c>
-      <c r="D69" s="38" t="s">
+      <c r="D69" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E69" s="49" t="s">
+      <c r="E69" s="48" t="s">
         <v>1247</v>
       </c>
       <c r="H69" s="11"/>
@@ -20265,10 +20262,10 @@
       <c r="C70" s="31" t="s">
         <v>1244</v>
       </c>
-      <c r="D70" s="38" t="s">
+      <c r="D70" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E70" s="49" t="s">
+      <c r="E70" s="48" t="s">
         <v>1248</v>
       </c>
       <c r="F70" s="8" t="s">
@@ -20284,10 +20281,10 @@
       <c r="C71" s="8" t="s">
         <v>1250</v>
       </c>
-      <c r="D71" s="38" t="s">
+      <c r="D71" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E71" s="49" t="s">
+      <c r="E71" s="48" t="s">
         <v>1251</v>
       </c>
       <c r="F71" s="8"/>
@@ -20301,10 +20298,10 @@
       <c r="C72" s="31" t="s">
         <v>914</v>
       </c>
-      <c r="D72" s="38" t="s">
+      <c r="D72" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E72" s="49" t="s">
+      <c r="E72" s="48" t="s">
         <v>1215</v>
       </c>
       <c r="F72" s="8"/>
@@ -20319,7 +20316,7 @@
       <c r="C73" s="8" t="s">
         <v>886</v>
       </c>
-      <c r="D73" s="38" t="s">
+      <c r="D73" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E73" s="8" t="s">
@@ -20337,10 +20334,10 @@
       <c r="C74" s="8" t="s">
         <v>1253</v>
       </c>
-      <c r="D74" s="38" t="s">
+      <c r="D74" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E74" s="49" t="s">
+      <c r="E74" s="48" t="s">
         <v>1254</v>
       </c>
       <c r="F74" s="8"/>
@@ -20357,10 +20354,10 @@
       <c r="C75" s="31" t="s">
         <v>1224</v>
       </c>
-      <c r="D75" s="38" t="s">
+      <c r="D75" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E75" s="46" t="s">
+      <c r="E75" s="45" t="s">
         <v>1227</v>
       </c>
       <c r="F75" s="8"/>
@@ -20368,14 +20365,14 @@
       <c r="H75" s="8"/>
     </row>
     <row r="76" s="11" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="51" t="s">
+      <c r="A76" s="50" t="s">
         <v>405</v>
       </c>
       <c r="B76" s="8"/>
       <c r="C76" s="8" t="s">
         <v>1255</v>
       </c>
-      <c r="D76" s="38" t="s">
+      <c r="D76" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E76" s="8" t="s">
@@ -20386,7 +20383,7 @@
       <c r="H76" s="8"/>
     </row>
     <row r="77" s="11" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="51" t="s">
+      <c r="A77" s="50" t="s">
         <v>405</v>
       </c>
       <c r="B77" s="8" t="s">
@@ -20395,7 +20392,7 @@
       <c r="C77" s="8" t="s">
         <v>1256</v>
       </c>
-      <c r="D77" s="38" t="s">
+      <c r="D77" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E77" s="8" t="s">
@@ -20412,10 +20409,10 @@
       <c r="C78" s="31" t="s">
         <v>1257</v>
       </c>
-      <c r="D78" s="38" t="s">
+      <c r="D78" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E78" s="46" t="s">
+      <c r="E78" s="45" t="s">
         <v>1258</v>
       </c>
       <c r="H78" s="11"/>
@@ -20430,10 +20427,10 @@
       <c r="C79" s="31" t="s">
         <v>1257</v>
       </c>
-      <c r="D79" s="38" t="s">
+      <c r="D79" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E79" s="46" t="s">
+      <c r="E79" s="45" t="s">
         <v>1259</v>
       </c>
       <c r="H79" s="11"/>
@@ -20445,10 +20442,10 @@
       <c r="C80" s="31" t="s">
         <v>1257</v>
       </c>
-      <c r="D80" s="38" t="s">
+      <c r="D80" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E80" s="46" t="s">
+      <c r="E80" s="45" t="s">
         <v>1259</v>
       </c>
       <c r="H80" s="11"/>
@@ -20463,7 +20460,7 @@
       <c r="C81" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="D81" s="45" t="s">
+      <c r="D81" s="44" t="s">
         <v>1190</v>
       </c>
       <c r="E81" s="31" t="n">
@@ -20481,10 +20478,10 @@
       <c r="C82" s="31" t="s">
         <v>1260</v>
       </c>
-      <c r="D82" s="38" t="s">
+      <c r="D82" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E82" s="49" t="s">
+      <c r="E82" s="48" t="s">
         <v>1251</v>
       </c>
       <c r="H82" s="11"/>
@@ -20496,10 +20493,10 @@
       <c r="C83" s="8" t="s">
         <v>1261</v>
       </c>
-      <c r="D83" s="38" t="s">
+      <c r="D83" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E83" s="49" t="s">
+      <c r="E83" s="48" t="s">
         <v>1262</v>
       </c>
       <c r="H83" s="11"/>
@@ -20511,10 +20508,10 @@
       <c r="C84" s="8" t="s">
         <v>1261</v>
       </c>
-      <c r="D84" s="38" t="s">
+      <c r="D84" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E84" s="49" t="s">
+      <c r="E84" s="48" t="s">
         <v>1263</v>
       </c>
       <c r="H84" s="11"/>
@@ -20526,10 +20523,10 @@
       <c r="C85" s="8" t="s">
         <v>1261</v>
       </c>
-      <c r="D85" s="38" t="s">
+      <c r="D85" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E85" s="49" t="s">
+      <c r="E85" s="48" t="s">
         <v>1264</v>
       </c>
     </row>
@@ -20540,10 +20537,10 @@
       <c r="C86" s="8" t="s">
         <v>1261</v>
       </c>
-      <c r="D86" s="38" t="s">
+      <c r="D86" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E86" s="49" t="s">
+      <c r="E86" s="48" t="s">
         <v>1265</v>
       </c>
     </row>
@@ -20554,10 +20551,10 @@
       <c r="C87" s="8" t="s">
         <v>1266</v>
       </c>
-      <c r="D87" s="38" t="s">
+      <c r="D87" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E87" s="49" t="s">
+      <c r="E87" s="48" t="s">
         <v>1267</v>
       </c>
     </row>
@@ -20571,10 +20568,10 @@
       <c r="C88" s="8" t="s">
         <v>1268</v>
       </c>
-      <c r="D88" s="38" t="s">
+      <c r="D88" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E88" s="49" t="s">
+      <c r="E88" s="48" t="s">
         <v>1269</v>
       </c>
     </row>
@@ -20588,10 +20585,10 @@
       <c r="C89" s="8" t="s">
         <v>1266</v>
       </c>
-      <c r="D89" s="38" t="s">
+      <c r="D89" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E89" s="49" t="s">
+      <c r="E89" s="48" t="s">
         <v>1269</v>
       </c>
       <c r="F89" s="8" t="s">
@@ -20608,10 +20605,10 @@
       <c r="C90" s="8" t="s">
         <v>1268</v>
       </c>
-      <c r="D90" s="38" t="s">
+      <c r="D90" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E90" s="49" t="s">
+      <c r="E90" s="48" t="s">
         <v>1267</v>
       </c>
       <c r="F90" s="8" t="s">
@@ -20628,10 +20625,10 @@
       <c r="C91" s="8" t="s">
         <v>1266</v>
       </c>
-      <c r="D91" s="38" t="s">
+      <c r="D91" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E91" s="49" t="s">
+      <c r="E91" s="48" t="s">
         <v>1270</v>
       </c>
       <c r="F91" s="8" t="s">
@@ -20648,10 +20645,10 @@
       <c r="C92" s="8" t="s">
         <v>1268</v>
       </c>
-      <c r="D92" s="38" t="s">
+      <c r="D92" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E92" s="49" t="s">
+      <c r="E92" s="48" t="s">
         <v>1269</v>
       </c>
       <c r="F92" s="8" t="s">
@@ -20668,10 +20665,10 @@
       <c r="C93" s="8" t="s">
         <v>1266</v>
       </c>
-      <c r="D93" s="38" t="s">
+      <c r="D93" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E93" s="49" t="s">
+      <c r="E93" s="48" t="s">
         <v>1269</v>
       </c>
       <c r="F93" s="8" t="s">
@@ -20690,10 +20687,10 @@
       <c r="C94" s="8" t="s">
         <v>1268</v>
       </c>
-      <c r="D94" s="38" t="s">
+      <c r="D94" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E94" s="49" t="s">
+      <c r="E94" s="48" t="s">
         <v>1270</v>
       </c>
       <c r="F94" s="8" t="s">
@@ -20712,10 +20709,10 @@
       <c r="C95" s="8" t="s">
         <v>1266</v>
       </c>
-      <c r="D95" s="38" t="s">
+      <c r="D95" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E95" s="49" t="s">
+      <c r="E95" s="48" t="s">
         <v>1271</v>
       </c>
       <c r="F95" s="8" t="s">
@@ -20734,10 +20731,10 @@
       <c r="C96" s="8" t="s">
         <v>1268</v>
       </c>
-      <c r="D96" s="38" t="s">
+      <c r="D96" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E96" s="49" t="s">
+      <c r="E96" s="48" t="s">
         <v>1269</v>
       </c>
       <c r="F96" s="8" t="s">
@@ -20756,10 +20753,10 @@
       <c r="C97" s="8" t="s">
         <v>1266</v>
       </c>
-      <c r="D97" s="38" t="s">
+      <c r="D97" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E97" s="49" t="s">
+      <c r="E97" s="48" t="s">
         <v>1269</v>
       </c>
       <c r="F97" s="8" t="s">
@@ -20778,10 +20775,10 @@
       <c r="C98" s="8" t="s">
         <v>1268</v>
       </c>
-      <c r="D98" s="38" t="s">
+      <c r="D98" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E98" s="49" t="s">
+      <c r="E98" s="48" t="s">
         <v>1271</v>
       </c>
       <c r="F98" s="8" t="s">
@@ -20798,10 +20795,10 @@
       <c r="C99" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="D99" s="38" t="s">
+      <c r="D99" s="37" t="s">
         <v>1190</v>
       </c>
-      <c r="E99" s="49" t="n">
+      <c r="E99" s="48" t="n">
         <v>1</v>
       </c>
       <c r="F99" s="8"/>
@@ -20816,10 +20813,10 @@
       <c r="C100" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="D100" s="38" t="s">
+      <c r="D100" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E100" s="49" t="n">
+      <c r="E100" s="48" t="n">
         <v>0</v>
       </c>
       <c r="F100" s="8"/>
@@ -20834,10 +20831,10 @@
       <c r="C101" s="31" t="s">
         <v>1274</v>
       </c>
-      <c r="D101" s="38" t="s">
+      <c r="D101" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E101" s="49" t="s">
+      <c r="E101" s="48" t="s">
         <v>1215</v>
       </c>
       <c r="F101" s="8"/>
@@ -20851,10 +20848,10 @@
       <c r="C102" s="8" t="s">
         <v>1275</v>
       </c>
-      <c r="D102" s="38" t="s">
+      <c r="D102" s="37" t="s">
         <v>1199</v>
       </c>
-      <c r="E102" s="49" t="n">
+      <c r="E102" s="48" t="n">
         <v>2</v>
       </c>
     </row>
@@ -20868,10 +20865,10 @@
       <c r="C103" s="31" t="s">
         <v>1244</v>
       </c>
-      <c r="D103" s="38" t="s">
+      <c r="D103" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E103" s="49" t="s">
+      <c r="E103" s="48" t="s">
         <v>1276</v>
       </c>
       <c r="F103" s="8" t="s">
@@ -20890,10 +20887,10 @@
       <c r="C104" s="31" t="s">
         <v>1244</v>
       </c>
-      <c r="D104" s="38" t="s">
+      <c r="D104" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E104" s="49" t="s">
+      <c r="E104" s="48" t="s">
         <v>1277</v>
       </c>
       <c r="F104" s="8"/>
@@ -20910,10 +20907,10 @@
       <c r="C105" s="31" t="s">
         <v>1244</v>
       </c>
-      <c r="D105" s="38" t="s">
+      <c r="D105" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E105" s="49" t="s">
+      <c r="E105" s="48" t="s">
         <v>1278</v>
       </c>
       <c r="F105" s="8" t="s">
@@ -20931,10 +20928,10 @@
       <c r="C106" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="D106" s="38" t="s">
+      <c r="D106" s="37" t="s">
         <v>1190</v>
       </c>
-      <c r="E106" s="49" t="n">
+      <c r="E106" s="48" t="n">
         <v>1</v>
       </c>
       <c r="F106" s="8" t="s">
@@ -20952,10 +20949,10 @@
       <c r="C107" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="D107" s="38" t="s">
+      <c r="D107" s="37" t="s">
         <v>1190</v>
       </c>
-      <c r="E107" s="49" t="n">
+      <c r="E107" s="48" t="n">
         <v>1</v>
       </c>
       <c r="F107" s="8" t="s">
@@ -20970,10 +20967,10 @@
       <c r="C108" s="8" t="s">
         <v>1275</v>
       </c>
-      <c r="D108" s="38" t="s">
+      <c r="D108" s="37" t="s">
         <v>1199</v>
       </c>
-      <c r="E108" s="49" t="n">
+      <c r="E108" s="48" t="n">
         <v>2</v>
       </c>
       <c r="H108" s="11"/>
@@ -20988,10 +20985,10 @@
       <c r="C109" s="31" t="s">
         <v>1244</v>
       </c>
-      <c r="D109" s="38" t="s">
+      <c r="D109" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E109" s="49" t="s">
+      <c r="E109" s="48" t="s">
         <v>1276</v>
       </c>
       <c r="F109" s="8" t="s">
@@ -21009,10 +21006,10 @@
       <c r="C110" s="31" t="s">
         <v>1244</v>
       </c>
-      <c r="D110" s="38" t="s">
+      <c r="D110" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E110" s="49" t="s">
+      <c r="E110" s="48" t="s">
         <v>1277</v>
       </c>
       <c r="F110" s="8"/>
@@ -21028,10 +21025,10 @@
       <c r="C111" s="31" t="s">
         <v>1244</v>
       </c>
-      <c r="D111" s="38" t="s">
+      <c r="D111" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E111" s="49" t="s">
+      <c r="E111" s="48" t="s">
         <v>1278</v>
       </c>
       <c r="F111" s="8" t="s">
@@ -21049,10 +21046,10 @@
       <c r="C112" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="D112" s="38" t="s">
+      <c r="D112" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E112" s="49" t="n">
+      <c r="E112" s="48" t="n">
         <v>0</v>
       </c>
       <c r="F112" s="8"/>
@@ -21068,10 +21065,10 @@
       <c r="C113" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="D113" s="38" t="s">
+      <c r="D113" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E113" s="49" t="n">
+      <c r="E113" s="48" t="n">
         <v>0</v>
       </c>
       <c r="F113" s="8"/>
@@ -21085,7 +21082,7 @@
       <c r="C114" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="D114" s="45" t="s">
+      <c r="D114" s="44" t="s">
         <v>1190</v>
       </c>
       <c r="E114" s="31" t="n">
@@ -21105,22 +21102,22 @@
       <c r="C115" s="8" t="s">
         <v>1275</v>
       </c>
-      <c r="D115" s="38" t="s">
+      <c r="D115" s="37" t="s">
         <v>1199</v>
       </c>
-      <c r="E115" s="49" t="n">
+      <c r="E115" s="48" t="n">
         <v>6</v>
       </c>
       <c r="H115" s="11"/>
     </row>
-    <row r="116" s="52" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" s="51" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="8" t="s">
         <v>203</v>
       </c>
       <c r="C116" s="31" t="s">
         <v>1197</v>
       </c>
-      <c r="D116" s="45" t="s">
+      <c r="D116" s="44" t="s">
         <v>1190</v>
       </c>
       <c r="E116" s="31" t="n">
@@ -21139,7 +21136,7 @@
       <c r="C117" s="31" t="s">
         <v>1214</v>
       </c>
-      <c r="D117" s="45" t="s">
+      <c r="D117" s="44" t="s">
         <v>1189</v>
       </c>
       <c r="E117" s="31" t="s">
@@ -21157,10 +21154,10 @@
       <c r="C118" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="D118" s="38" t="s">
+      <c r="D118" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E118" s="49" t="s">
+      <c r="E118" s="48" t="s">
         <v>1215</v>
       </c>
       <c r="F118" s="8" t="s">
@@ -21177,10 +21174,10 @@
       <c r="C119" s="8" t="s">
         <v>1275</v>
       </c>
-      <c r="D119" s="38" t="s">
+      <c r="D119" s="37" t="s">
         <v>1199</v>
       </c>
-      <c r="E119" s="49" t="n">
+      <c r="E119" s="48" t="n">
         <v>6</v>
       </c>
     </row>
@@ -21194,7 +21191,7 @@
       <c r="C120" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="D120" s="45" t="s">
+      <c r="D120" s="44" t="s">
         <v>1189</v>
       </c>
       <c r="E120" s="31" t="n">
@@ -21211,7 +21208,7 @@
       <c r="C121" s="31" t="s">
         <v>1197</v>
       </c>
-      <c r="D121" s="45" t="s">
+      <c r="D121" s="44" t="s">
         <v>1190</v>
       </c>
       <c r="E121" s="31" t="n">
@@ -21228,10 +21225,10 @@
       <c r="C122" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="D122" s="38" t="s">
+      <c r="D122" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E122" s="49" t="s">
+      <c r="E122" s="48" t="s">
         <v>1215</v>
       </c>
       <c r="F122" s="8" t="s">
@@ -21249,10 +21246,10 @@
       <c r="C123" s="8" t="s">
         <v>1275</v>
       </c>
-      <c r="D123" s="38" t="s">
+      <c r="D123" s="37" t="s">
         <v>1199</v>
       </c>
-      <c r="E123" s="49" t="n">
+      <c r="E123" s="48" t="n">
         <v>6</v>
       </c>
       <c r="H123" s="11"/>
@@ -21267,7 +21264,7 @@
       <c r="C124" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="D124" s="45" t="s">
+      <c r="D124" s="44" t="s">
         <v>1189</v>
       </c>
       <c r="E124" s="31" t="n">
@@ -21285,10 +21282,10 @@
       <c r="C125" s="31" t="s">
         <v>1279</v>
       </c>
-      <c r="D125" s="38" t="s">
+      <c r="D125" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E125" s="49" t="s">
+      <c r="E125" s="48" t="s">
         <v>1215</v>
       </c>
       <c r="H125" s="11"/>
@@ -21300,7 +21297,7 @@
       <c r="C126" s="31" t="s">
         <v>1197</v>
       </c>
-      <c r="D126" s="45" t="s">
+      <c r="D126" s="44" t="s">
         <v>1190</v>
       </c>
       <c r="E126" s="31" t="n">
@@ -21317,10 +21314,10 @@
       <c r="C127" s="8" t="s">
         <v>1250</v>
       </c>
-      <c r="D127" s="38" t="s">
+      <c r="D127" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E127" s="49" t="s">
+      <c r="E127" s="48" t="s">
         <v>1215</v>
       </c>
     </row>
@@ -21331,10 +21328,10 @@
       <c r="C128" s="31" t="s">
         <v>1280</v>
       </c>
-      <c r="D128" s="38" t="s">
+      <c r="D128" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E128" s="49" t="s">
+      <c r="E128" s="48" t="s">
         <v>1281</v>
       </c>
     </row>
@@ -21348,7 +21345,7 @@
       <c r="C129" s="11" t="s">
         <v>1280</v>
       </c>
-      <c r="D129" s="53" t="s">
+      <c r="D129" s="52" t="s">
         <v>1189</v>
       </c>
       <c r="E129" s="11" t="s">
@@ -21365,7 +21362,7 @@
       <c r="C130" s="8" t="s">
         <v>829</v>
       </c>
-      <c r="D130" s="38" t="s">
+      <c r="D130" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E130" s="8" t="s">
@@ -21379,7 +21376,7 @@
       <c r="C131" s="8" t="s">
         <v>1244</v>
       </c>
-      <c r="D131" s="38" t="s">
+      <c r="D131" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E131" s="8" t="s">
@@ -21393,7 +21390,7 @@
       <c r="C132" s="8" t="s">
         <v>863</v>
       </c>
-      <c r="D132" s="38" t="s">
+      <c r="D132" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E132" s="8" t="s">
@@ -21401,20 +21398,20 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="54" t="s">
+      <c r="A133" s="53" t="s">
         <v>1078</v>
       </c>
-      <c r="B133" s="55"/>
-      <c r="C133" s="54" t="s">
+      <c r="B133" s="54"/>
+      <c r="C133" s="53" t="s">
         <v>1244</v>
       </c>
-      <c r="D133" s="56" t="s">
+      <c r="D133" s="55" t="s">
         <v>1189</v>
       </c>
-      <c r="E133" s="57" t="s">
+      <c r="E133" s="56" t="s">
         <v>1073</v>
       </c>
-      <c r="F133" s="55"/>
+      <c r="F133" s="54"/>
     </row>
     <row r="134" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="31" t="s">
@@ -21426,13 +21423,13 @@
       <c r="C134" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="D134" s="45" t="s">
+      <c r="D134" s="44" t="s">
         <v>1190</v>
       </c>
       <c r="E134" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H134" s="55" t="s">
+      <c r="H134" s="54" t="s">
         <v>1283</v>
       </c>
     </row>
@@ -21443,29 +21440,29 @@
       <c r="C135" s="8" t="s">
         <v>1075</v>
       </c>
-      <c r="D135" s="38" t="s">
+      <c r="D135" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E135" s="49" t="s">
+      <c r="E135" s="48" t="s">
         <v>1284</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="54" t="s">
+      <c r="A136" s="53" t="s">
         <v>1107</v>
       </c>
-      <c r="B136" s="55"/>
-      <c r="C136" s="54" t="s">
+      <c r="B136" s="54"/>
+      <c r="C136" s="53" t="s">
         <v>1244</v>
       </c>
-      <c r="D136" s="56" t="s">
+      <c r="D136" s="55" t="s">
         <v>1189</v>
       </c>
-      <c r="E136" s="57" t="s">
+      <c r="E136" s="56" t="s">
         <v>1248</v>
       </c>
-      <c r="F136" s="55"/>
-      <c r="H136" s="55" t="s">
+      <c r="F136" s="54"/>
+      <c r="H136" s="54" t="s">
         <v>1285</v>
       </c>
     </row>
@@ -21476,10 +21473,10 @@
       <c r="C137" s="31" t="s">
         <v>1103</v>
       </c>
-      <c r="D137" s="58" t="s">
+      <c r="D137" s="57" t="s">
         <v>1189</v>
       </c>
-      <c r="E137" s="49" t="s">
+      <c r="E137" s="48" t="s">
         <v>1251</v>
       </c>
     </row>
@@ -21490,7 +21487,7 @@
       <c r="C138" s="8" t="s">
         <v>1286</v>
       </c>
-      <c r="D138" s="38" t="s">
+      <c r="D138" s="37" t="s">
         <v>1206</v>
       </c>
       <c r="E138" s="8" t="s">
@@ -21504,7 +21501,7 @@
       <c r="C139" s="3" t="s">
         <v>931</v>
       </c>
-      <c r="D139" s="38" t="s">
+      <c r="D139" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E139" s="8" t="s">
@@ -21518,10 +21515,10 @@
       <c r="C140" s="8" t="s">
         <v>1216</v>
       </c>
-      <c r="D140" s="38" t="s">
+      <c r="D140" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E140" s="38" t="s">
+      <c r="E140" s="37" t="s">
         <v>1217</v>
       </c>
     </row>
@@ -21535,10 +21532,10 @@
       <c r="C141" s="8" t="s">
         <v>1216</v>
       </c>
-      <c r="D141" s="38" t="s">
+      <c r="D141" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E141" s="38" t="s">
+      <c r="E141" s="37" t="s">
         <v>1218</v>
       </c>
     </row>
@@ -21552,10 +21549,10 @@
       <c r="C142" s="8" t="s">
         <v>1216</v>
       </c>
-      <c r="D142" s="38" t="s">
+      <c r="D142" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E142" s="38" t="s">
+      <c r="E142" s="37" t="s">
         <v>1219</v>
       </c>
     </row>
@@ -21569,10 +21566,10 @@
       <c r="C143" s="8" t="s">
         <v>1216</v>
       </c>
-      <c r="D143" s="38" t="s">
+      <c r="D143" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E143" s="46" t="s">
+      <c r="E143" s="45" t="s">
         <v>1287</v>
       </c>
     </row>
@@ -21586,7 +21583,7 @@
       <c r="C144" s="8" t="s">
         <v>1216</v>
       </c>
-      <c r="D144" s="38" t="s">
+      <c r="D144" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E144" s="8" t="s">
@@ -21600,10 +21597,10 @@
       <c r="C145" s="31" t="s">
         <v>1244</v>
       </c>
-      <c r="D145" s="38" t="s">
+      <c r="D145" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E145" s="49" t="s">
+      <c r="E145" s="48" t="s">
         <v>1289</v>
       </c>
     </row>
@@ -21614,10 +21611,10 @@
       <c r="C146" s="8" t="s">
         <v>1290</v>
       </c>
-      <c r="D146" s="53" t="s">
+      <c r="D146" s="52" t="s">
         <v>1189</v>
       </c>
-      <c r="E146" s="53" t="s">
+      <c r="E146" s="52" t="s">
         <v>1291</v>
       </c>
     </row>
@@ -21628,10 +21625,10 @@
       <c r="C147" s="8" t="s">
         <v>1290</v>
       </c>
-      <c r="D147" s="53" t="s">
+      <c r="D147" s="52" t="s">
         <v>1189</v>
       </c>
-      <c r="E147" s="53" t="s">
+      <c r="E147" s="52" t="s">
         <v>1291</v>
       </c>
     </row>
@@ -21645,7 +21642,7 @@
       <c r="C148" s="8" t="s">
         <v>1290</v>
       </c>
-      <c r="D148" s="53" t="s">
+      <c r="D148" s="52" t="s">
         <v>1189</v>
       </c>
       <c r="E148" s="8" t="s">
@@ -21659,14 +21656,14 @@
       <c r="C149" s="8" t="s">
         <v>1292</v>
       </c>
-      <c r="D149" s="38" t="s">
+      <c r="D149" s="37" t="s">
         <v>1189</v>
       </c>
-      <c r="E149" s="53" t="s">
+      <c r="E149" s="52" t="s">
         <v>1293</v>
       </c>
     </row>
-    <row r="150" s="52" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" s="51" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="8" t="s">
         <v>765</v>
       </c>
@@ -21674,7 +21671,7 @@
       <c r="C150" s="8" t="s">
         <v>1294</v>
       </c>
-      <c r="D150" s="59" t="s">
+      <c r="D150" s="58" t="s">
         <v>1189</v>
       </c>
       <c r="E150" s="8" t="s">
@@ -21691,7 +21688,7 @@
       <c r="C151" s="8" t="s">
         <v>1295</v>
       </c>
-      <c r="D151" s="38" t="s">
+      <c r="D151" s="37" t="s">
         <v>1206</v>
       </c>
       <c r="E151" s="8" t="s">
@@ -21705,7 +21702,7 @@
       <c r="C152" s="8" t="s">
         <v>1295</v>
       </c>
-      <c r="D152" s="38" t="s">
+      <c r="D152" s="37" t="s">
         <v>1189</v>
       </c>
       <c r="E152" s="8" t="s">
@@ -21743,57 +21740,57 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="59" t="s">
         <v>1296</v>
       </c>
-      <c r="C1" s="60" t="s">
+      <c r="C1" s="59" t="s">
         <v>1297</v>
       </c>
-      <c r="D1" s="60" t="s">
+      <c r="D1" s="59" t="s">
         <v>1298</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="E1" s="59" t="s">
         <v>1299</v>
       </c>
-      <c r="F1" s="60" t="s">
+      <c r="F1" s="59" t="s">
         <v>1300</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="G1" s="60" t="s">
         <v>1301</v>
       </c>
-      <c r="H1" s="60" t="s">
+      <c r="H1" s="59" t="s">
         <v>1302</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="59" t="s">
         <v>1303</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="59" t="s">
         <v>1304</v>
       </c>
-      <c r="D2" s="60" t="s">
+      <c r="D2" s="59" t="s">
         <v>1305</v>
       </c>
-      <c r="E2" s="62" t="b">
+      <c r="E2" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F2" s="62" t="b">
+      <c r="F2" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G2" s="62" t="b">
+      <c r="G2" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="H2" s="60" t="s">
+      <c r="H2" s="59" t="s">
         <v>48</v>
       </c>
     </row>
@@ -21810,15 +21807,15 @@
       <c r="D3" s="8" t="s">
         <v>1308</v>
       </c>
-      <c r="E3" s="62" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F3" s="62" t="b">
+      <c r="E3" s="61" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="F3" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G3" s="62" t="b">
+      <c r="G3" s="61" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -21836,15 +21833,15 @@
       <c r="D4" s="8" t="s">
         <v>1311</v>
       </c>
-      <c r="E4" s="62" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F4" s="62" t="b">
+      <c r="E4" s="61" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="F4" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G4" s="62" t="b">
+      <c r="G4" s="61" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -21862,15 +21859,15 @@
       <c r="D5" s="8" t="s">
         <v>1315</v>
       </c>
-      <c r="E5" s="62" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F5" s="62" t="b">
+      <c r="E5" s="61" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="F5" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G5" s="62" t="b">
+      <c r="G5" s="61" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -21888,15 +21885,15 @@
       <c r="D6" s="8" t="s">
         <v>1318</v>
       </c>
-      <c r="E6" s="62" t="b">
+      <c r="E6" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F6" s="62" t="b">
+      <c r="F6" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G6" s="62" t="b">
+      <c r="G6" s="61" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -21905,7 +21902,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="63" t="s">
+      <c r="A7" s="62" t="s">
         <v>362</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -21917,15 +21914,15 @@
       <c r="D7" s="8" t="s">
         <v>1315</v>
       </c>
-      <c r="E7" s="62" t="b">
+      <c r="E7" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F7" s="62" t="b">
+      <c r="F7" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G7" s="62" t="b">
+      <c r="G7" s="61" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -21934,7 +21931,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="63" t="s">
+      <c r="A8" s="62" t="s">
         <v>449</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -21946,15 +21943,15 @@
       <c r="D8" s="8" t="s">
         <v>1314</v>
       </c>
-      <c r="E8" s="62" t="b">
+      <c r="E8" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F8" s="62" t="b">
+      <c r="F8" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G8" s="62" t="b">
+      <c r="G8" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -21963,7 +21960,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="63" t="s">
+      <c r="A9" s="62" t="s">
         <v>560</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -21975,15 +21972,15 @@
       <c r="D9" s="8" t="s">
         <v>1324</v>
       </c>
-      <c r="E9" s="62" t="b">
+      <c r="E9" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F9" s="62" t="b">
+      <c r="F9" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G9" s="62" t="b">
+      <c r="G9" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -21992,7 +21989,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="63" t="s">
+      <c r="A10" s="62" t="s">
         <v>745</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -22004,15 +22001,15 @@
       <c r="D10" s="8" t="s">
         <v>1327</v>
       </c>
-      <c r="E10" s="62" t="b">
+      <c r="E10" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F10" s="62" t="b">
+      <c r="F10" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G10" s="62" t="b">
+      <c r="G10" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -22021,7 +22018,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="63" t="s">
+      <c r="A11" s="62" t="s">
         <v>828</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -22033,15 +22030,15 @@
       <c r="D11" s="8" t="s">
         <v>1330</v>
       </c>
-      <c r="E11" s="62" t="b">
+      <c r="E11" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F11" s="62" t="b">
+      <c r="F11" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G11" s="62" t="b">
+      <c r="G11" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -22062,15 +22059,15 @@
       <c r="D12" s="8" t="s">
         <v>1333</v>
       </c>
-      <c r="E12" s="62" t="b">
+      <c r="E12" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F12" s="62" t="b">
+      <c r="F12" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G12" s="62" t="b">
+      <c r="G12" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -22091,15 +22088,15 @@
       <c r="D13" s="8" t="s">
         <v>1336</v>
       </c>
-      <c r="E13" s="62" t="b">
+      <c r="E13" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F13" s="62" t="b">
+      <c r="F13" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G13" s="62" t="b">
+      <c r="G13" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -22120,15 +22117,15 @@
       <c r="D14" s="8" t="s">
         <v>1339</v>
       </c>
-      <c r="E14" s="62" t="b">
+      <c r="E14" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F14" s="62" t="b">
+      <c r="F14" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G14" s="62" t="b">
+      <c r="G14" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -22149,15 +22146,15 @@
       <c r="D15" s="8" t="s">
         <v>1342</v>
       </c>
-      <c r="E15" s="62" t="b">
+      <c r="E15" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F15" s="62" t="b">
+      <c r="F15" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G15" s="62" t="b">
+      <c r="G15" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -22178,15 +22175,15 @@
       <c r="D16" s="8" t="s">
         <v>1345</v>
       </c>
-      <c r="E16" s="62" t="b">
+      <c r="E16" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F16" s="62" t="b">
+      <c r="F16" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G16" s="62" t="b">
+      <c r="G16" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -22207,15 +22204,15 @@
       <c r="D17" s="11" t="s">
         <v>1336</v>
       </c>
-      <c r="E17" s="62" t="b">
+      <c r="E17" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F17" s="62" t="b">
+      <c r="F17" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G17" s="62" t="b">
+      <c r="G17" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -22236,15 +22233,15 @@
       <c r="D18" s="8" t="s">
         <v>1349</v>
       </c>
-      <c r="E18" s="62" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F18" s="62" t="b">
+      <c r="E18" s="61" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="F18" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G18" s="62" t="b">
+      <c r="G18" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -22262,15 +22259,15 @@
       <c r="D19" s="8" t="s">
         <v>1352</v>
       </c>
-      <c r="E19" s="62" t="b">
+      <c r="E19" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F19" s="62" t="b">
+      <c r="F19" s="61" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G19" s="62" t="b">
+      <c r="G19" s="61" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -22310,40 +22307,40 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="63" t="s">
         <v>1353</v>
       </c>
-      <c r="B1" s="64" t="s">
+      <c r="B1" s="63" t="s">
         <v>1354</v>
       </c>
-      <c r="C1" s="64" t="s">
+      <c r="C1" s="63" t="s">
         <v>1355</v>
       </c>
-      <c r="D1" s="64" t="s">
+      <c r="D1" s="63" t="s">
         <v>1356</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="63" t="s">
         <v>1357</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="63" t="s">
         <v>1358</v>
       </c>
-      <c r="G1" s="64" t="s">
+      <c r="G1" s="63" t="s">
         <v>1359</v>
       </c>
-      <c r="H1" s="64" t="s">
+      <c r="H1" s="63" t="s">
         <v>1360</v>
       </c>
-      <c r="I1" s="64" t="s">
+      <c r="I1" s="63" t="s">
         <v>1361</v>
       </c>
-      <c r="J1" s="64" t="s">
+      <c r="J1" s="63" t="s">
         <v>1362</v>
       </c>
-      <c r="K1" s="64" t="s">
+      <c r="K1" s="63" t="s">
         <v>1363</v>
       </c>
-      <c r="L1" s="64" t="s">
+      <c r="L1" s="63" t="s">
         <v>1364</v>
       </c>
     </row>
@@ -22395,13 +22392,13 @@
       <c r="C3" s="31" t="s">
         <v>1374</v>
       </c>
-      <c r="D3" s="65" t="s">
+      <c r="D3" s="64" t="s">
         <v>1375</v>
       </c>
-      <c r="E3" s="65" t="s">
+      <c r="E3" s="64" t="s">
         <v>1376</v>
       </c>
-      <c r="F3" s="65" t="s">
+      <c r="F3" s="64" t="s">
         <v>1377</v>
       </c>
       <c r="G3" s="31" t="s">
@@ -22539,10 +22536,10 @@
       <c r="D1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="66" t="s">
+      <c r="E1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="66" t="s">
+      <c r="F1" s="65" t="s">
         <v>9</v>
       </c>
     </row>
@@ -22559,8 +22556,8 @@
       <c r="D2" s="11" t="s">
         <v>1394</v>
       </c>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
@@ -22575,8 +22572,8 @@
       <c r="D3" s="11" t="s">
         <v>1397</v>
       </c>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
@@ -22591,8 +22588,8 @@
       <c r="D4" s="11" t="s">
         <v>1400</v>
       </c>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
@@ -22607,8 +22604,8 @@
       <c r="D5" s="11" t="s">
         <v>1403</v>
       </c>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
@@ -22623,8 +22620,8 @@
       <c r="D6" s="11" t="s">
         <v>1406</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
     </row>
     <row r="7" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
@@ -22639,8 +22636,8 @@
       <c r="D7" s="8" t="s">
         <v>1409</v>
       </c>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
     </row>
     <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
@@ -22655,8 +22652,8 @@
       <c r="D8" s="8" t="s">
         <v>1412</v>
       </c>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
@@ -22671,8 +22668,8 @@
       <c r="D9" s="11" t="s">
         <v>1415</v>
       </c>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
     </row>
     <row r="10" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
@@ -22687,8 +22684,8 @@
       <c r="D10" s="8" t="s">
         <v>1418</v>
       </c>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
@@ -22703,8 +22700,8 @@
       <c r="D11" s="11" t="s">
         <v>1415</v>
       </c>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
     </row>
     <row r="12" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
@@ -22719,8 +22716,8 @@
       <c r="D12" s="8" t="s">
         <v>1422</v>
       </c>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
@@ -22729,14 +22726,14 @@
       <c r="B13" s="31" t="s">
         <v>1423</v>
       </c>
-      <c r="C13" s="67" t="s">
+      <c r="C13" s="66" t="s">
         <v>1424</v>
       </c>
-      <c r="D13" s="67" t="s">
+      <c r="D13" s="66" t="s">
         <v>1425</v>
       </c>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
@@ -22751,8 +22748,8 @@
       <c r="D14" s="8" t="s">
         <v>1428</v>
       </c>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
@@ -22767,8 +22764,8 @@
       <c r="D15" s="8" t="s">
         <v>1431</v>
       </c>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
@@ -22777,14 +22774,14 @@
       <c r="B16" s="31" t="s">
         <v>1432</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="67" t="s">
         <v>1433</v>
       </c>
-      <c r="D16" s="68" t="s">
+      <c r="D16" s="67" t="s">
         <v>1434</v>
       </c>
-      <c r="E16" s="66"/>
-      <c r="F16" s="66"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="65"/>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
@@ -22799,8 +22796,8 @@
       <c r="D17" s="11" t="s">
         <v>1437</v>
       </c>
-      <c r="E17" s="66"/>
-      <c r="F17" s="66"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="65"/>
     </row>
     <row r="18" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
@@ -22815,8 +22812,8 @@
       <c r="D18" s="8" t="s">
         <v>1440</v>
       </c>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="65"/>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
@@ -22831,8 +22828,8 @@
       <c r="D19" s="11" t="s">
         <v>1443</v>
       </c>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
     </row>
     <row r="20" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
@@ -22847,8 +22844,8 @@
       <c r="D20" s="8" t="s">
         <v>1446</v>
       </c>
-      <c r="E20" s="66"/>
-      <c r="F20" s="66"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
@@ -23389,10 +23386,10 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="46" t="s">
+      <c r="A59" s="45" t="s">
         <v>449</v>
       </c>
-      <c r="B59" s="69" t="s">
+      <c r="B59" s="68" t="s">
         <v>1560</v>
       </c>
       <c r="C59" s="11" t="s">
@@ -23409,10 +23406,10 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="46" t="s">
+      <c r="A60" s="45" t="s">
         <v>449</v>
       </c>
-      <c r="B60" s="69" t="s">
+      <c r="B60" s="68" t="s">
         <v>1565</v>
       </c>
       <c r="C60" s="11" t="s">
@@ -23424,12 +23421,12 @@
       <c r="E60" s="31" t="s">
         <v>1568</v>
       </c>
-      <c r="F60" s="69" t="s">
+      <c r="F60" s="68" t="s">
         <v>1569</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="46" t="s">
+      <c r="A61" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B61" s="8" t="s">
@@ -23449,7 +23446,7 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="156.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="46" t="s">
+      <c r="A62" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B62" s="8" t="s">
@@ -23469,7 +23466,7 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="46" t="s">
+      <c r="A63" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B63" s="31" t="s">
@@ -23489,7 +23486,7 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="46" t="s">
+      <c r="A64" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B64" s="31" t="s">
@@ -23509,7 +23506,7 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="46" t="s">
+      <c r="A65" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B65" s="31" t="s">
@@ -23529,7 +23526,7 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="46" t="s">
+      <c r="A66" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B66" s="31" t="s">
@@ -23549,7 +23546,7 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="46" t="s">
+      <c r="A67" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B67" s="31" t="s">
@@ -23569,7 +23566,7 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="46" t="s">
+      <c r="A68" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B68" s="8" t="s">
@@ -23589,7 +23586,7 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="46" t="s">
+      <c r="A69" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B69" s="31" t="s">
@@ -23609,7 +23606,7 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="46" t="s">
+      <c r="A70" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B70" s="8" t="s">
@@ -23629,7 +23626,7 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="46" t="s">
+      <c r="A71" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B71" s="8" t="s">
@@ -23649,7 +23646,7 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="46" t="s">
+      <c r="A72" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B72" s="8" t="s">
@@ -23679,7 +23676,7 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="46" t="s">
+      <c r="A74" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B74" s="8" t="s">
@@ -23695,7 +23692,7 @@
       <c r="F74" s="31"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="46" t="s">
+      <c r="A75" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B75" s="8" t="s">
@@ -23711,7 +23708,7 @@
       <c r="F75" s="31"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="46" t="s">
+      <c r="A76" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B76" s="8" t="s">
@@ -23727,7 +23724,7 @@
       <c r="F76" s="31"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="46" t="s">
+      <c r="A77" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B77" s="8" t="s">
@@ -23743,7 +23740,7 @@
       <c r="F77" s="31"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="46" t="s">
+      <c r="A78" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B78" s="8" t="s">
@@ -23759,7 +23756,7 @@
       <c r="F78" s="31"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="46" t="s">
+      <c r="A79" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B79" s="8" t="s">
@@ -23775,7 +23772,7 @@
       <c r="F79" s="31"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="46" t="s">
+      <c r="A80" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B80" s="8" t="s">
@@ -23791,7 +23788,7 @@
       <c r="F80" s="31"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="46" t="s">
+      <c r="A81" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B81" s="8" t="s">
@@ -23807,7 +23804,7 @@
       <c r="F81" s="31"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="46" t="s">
+      <c r="A82" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B82" s="8" t="s">
@@ -23823,7 +23820,7 @@
       <c r="F82" s="31"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="46" t="s">
+      <c r="A83" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B83" s="8" t="s">
@@ -23839,7 +23836,7 @@
       <c r="F83" s="31"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="46" t="s">
+      <c r="A84" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B84" s="8" t="s">
@@ -23855,7 +23852,7 @@
       <c r="F84" s="31"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="46" t="s">
+      <c r="A85" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B85" s="8" t="s">
@@ -23871,7 +23868,7 @@
       <c r="F85" s="31"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="46" t="s">
+      <c r="A86" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B86" s="8" t="s">
@@ -23887,7 +23884,7 @@
       <c r="F86" s="31"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="46" t="s">
+      <c r="A87" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B87" s="8" t="s">
@@ -23903,7 +23900,7 @@
       <c r="F87" s="31"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="46" t="s">
+      <c r="A88" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B88" s="8" t="s">
@@ -23919,7 +23916,7 @@
       <c r="F88" s="31"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="46" t="s">
+      <c r="A89" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B89" s="8" t="s">
@@ -23935,7 +23932,7 @@
       <c r="F89" s="31"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="46" t="s">
+      <c r="A90" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B90" s="8" t="s">
@@ -23951,7 +23948,7 @@
       <c r="F90" s="31"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="46" t="s">
+      <c r="A91" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B91" s="8" t="s">
@@ -23967,7 +23964,7 @@
       <c r="F91" s="31"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="46" t="s">
+      <c r="A92" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B92" s="8" t="s">
@@ -23983,7 +23980,7 @@
       <c r="F92" s="31"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="46" t="s">
+      <c r="A93" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B93" s="8" t="s">
@@ -23999,7 +23996,7 @@
       <c r="F93" s="31"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="46" t="s">
+      <c r="A94" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B94" s="8" t="s">
@@ -24015,7 +24012,7 @@
       <c r="F94" s="31"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="46" t="s">
+      <c r="A95" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B95" s="8" t="s">
@@ -24031,7 +24028,7 @@
       <c r="F95" s="31"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="46" t="s">
+      <c r="A96" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B96" s="8" t="s">
@@ -24047,7 +24044,7 @@
       <c r="F96" s="31"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="46" t="s">
+      <c r="A97" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B97" s="8" t="s">
@@ -24063,7 +24060,7 @@
       <c r="F97" s="31"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="46" t="s">
+      <c r="A98" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B98" s="8" t="s">
@@ -24078,24 +24075,24 @@
       <c r="E98" s="31"/>
       <c r="F98" s="31"/>
     </row>
-    <row r="99" s="52" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="46" t="s">
+    <row r="99" s="51" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B99" s="8" t="s">
         <v>1702</v>
       </c>
-      <c r="C99" s="52" t="s">
+      <c r="C99" s="51" t="s">
         <v>1703</v>
       </c>
-      <c r="D99" s="52" t="s">
+      <c r="D99" s="51" t="s">
         <v>1704</v>
       </c>
       <c r="E99" s="31"/>
       <c r="F99" s="31"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="46" t="s">
+      <c r="A100" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B100" s="8" t="s">
@@ -24111,7 +24108,7 @@
       <c r="F100" s="31"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="46" t="s">
+      <c r="A101" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B101" s="8" t="s">
@@ -24127,7 +24124,7 @@
       <c r="F101" s="31"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="46" t="s">
+      <c r="A102" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B102" s="8" t="s">
@@ -24143,7 +24140,7 @@
       <c r="F102" s="31"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="46" t="s">
+      <c r="A103" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B103" s="8" t="s">
@@ -24159,7 +24156,7 @@
       <c r="F103" s="31"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="46" t="s">
+      <c r="A104" s="45" t="s">
         <v>449</v>
       </c>
       <c r="B104" s="8" t="s">
@@ -24324,7 +24321,7 @@
       <c r="A115" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="B115" s="70" t="s">
+      <c r="B115" s="69" t="s">
         <v>1747</v>
       </c>
       <c r="C115" s="11" t="s">
@@ -24386,7 +24383,7 @@
       <c r="A119" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="B119" s="63" t="s">
+      <c r="B119" s="62" t="s">
         <v>1761</v>
       </c>
       <c r="C119" s="11" t="s">
@@ -24400,7 +24397,7 @@
       <c r="A120" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="B120" s="63" t="s">
+      <c r="B120" s="62" t="s">
         <v>1764</v>
       </c>
       <c r="C120" s="11" t="s">
@@ -24467,10 +24464,10 @@
       </c>
     </row>
     <row r="125" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="71" t="s">
+      <c r="A125" s="70" t="s">
         <v>449</v>
       </c>
-      <c r="B125" s="49" t="s">
+      <c r="B125" s="48" t="s">
         <v>1779</v>
       </c>
       <c r="C125" s="11" t="s">
@@ -24479,14 +24476,14 @@
       <c r="D125" s="11" t="s">
         <v>1308</v>
       </c>
-      <c r="E125" s="49"/>
-      <c r="F125" s="49"/>
+      <c r="E125" s="48"/>
+      <c r="F125" s="48"/>
     </row>
     <row r="126" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="71" t="s">
+      <c r="A126" s="70" t="s">
         <v>449</v>
       </c>
-      <c r="B126" s="49" t="s">
+      <c r="B126" s="48" t="s">
         <v>1780</v>
       </c>
       <c r="C126" s="11" t="s">
@@ -24495,14 +24492,14 @@
       <c r="D126" s="11" t="s">
         <v>1720</v>
       </c>
-      <c r="E126" s="49"/>
-      <c r="F126" s="49"/>
+      <c r="E126" s="48"/>
+      <c r="F126" s="48"/>
     </row>
     <row r="127" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="71" t="s">
+      <c r="A127" s="70" t="s">
         <v>449</v>
       </c>
-      <c r="B127" s="49" t="s">
+      <c r="B127" s="48" t="s">
         <v>1781</v>
       </c>
       <c r="C127" s="11" t="s">
@@ -24511,11 +24508,11 @@
       <c r="D127" s="11" t="s">
         <v>1723</v>
       </c>
-      <c r="E127" s="49"/>
-      <c r="F127" s="49"/>
+      <c r="E127" s="48"/>
+      <c r="F127" s="48"/>
     </row>
     <row r="128" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="71" t="s">
+      <c r="A128" s="70" t="s">
         <v>449</v>
       </c>
       <c r="B128" s="8" t="s">
@@ -24591,10 +24588,10 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="71" t="s">
+      <c r="A133" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B133" s="49" t="s">
+      <c r="B133" s="48" t="s">
         <v>1795</v>
       </c>
       <c r="C133" s="11" t="s">
@@ -24611,10 +24608,10 @@
       </c>
     </row>
     <row r="134" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="71" t="s">
+      <c r="A134" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B134" s="49" t="s">
+      <c r="B134" s="48" t="s">
         <v>1800</v>
       </c>
       <c r="C134" s="11" t="s">
@@ -24631,10 +24628,10 @@
       </c>
     </row>
     <row r="135" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="71" t="s">
+      <c r="A135" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B135" s="49" t="s">
+      <c r="B135" s="48" t="s">
         <v>1805</v>
       </c>
       <c r="C135" s="11" t="s">
@@ -24647,10 +24644,10 @@
       <c r="F135" s="8"/>
     </row>
     <row r="136" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="71" t="s">
+      <c r="A136" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B136" s="49" t="s">
+      <c r="B136" s="48" t="s">
         <v>1808</v>
       </c>
       <c r="C136" s="11" t="s">
@@ -24663,7 +24660,7 @@
       <c r="F136" s="8"/>
     </row>
     <row r="137" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="71" t="s">
+      <c r="A137" s="70" t="s">
         <v>560</v>
       </c>
       <c r="B137" s="8" t="s">
@@ -24679,7 +24676,7 @@
       <c r="F137" s="8"/>
     </row>
     <row r="138" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="71" t="s">
+      <c r="A138" s="70" t="s">
         <v>560</v>
       </c>
       <c r="B138" s="8" t="s">
@@ -24695,10 +24692,10 @@
       <c r="F138" s="8"/>
     </row>
     <row r="139" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="71" t="s">
+      <c r="A139" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B139" s="49" t="s">
+      <c r="B139" s="48" t="s">
         <v>1817</v>
       </c>
       <c r="C139" s="11" t="s">
@@ -24711,7 +24708,7 @@
       <c r="F139" s="8"/>
     </row>
     <row r="140" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="71" t="s">
+      <c r="A140" s="70" t="s">
         <v>560</v>
       </c>
       <c r="B140" s="8" t="s">
@@ -24727,7 +24724,7 @@
       <c r="F140" s="8"/>
     </row>
     <row r="141" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="71" t="s">
+      <c r="A141" s="70" t="s">
         <v>560</v>
       </c>
       <c r="B141" s="8" t="s">
@@ -24743,7 +24740,7 @@
       <c r="F141" s="8"/>
     </row>
     <row r="142" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="71" t="s">
+      <c r="A142" s="70" t="s">
         <v>560</v>
       </c>
       <c r="B142" s="8" t="s">
@@ -24759,7 +24756,7 @@
       <c r="F142" s="8"/>
     </row>
     <row r="143" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="71" t="s">
+      <c r="A143" s="70" t="s">
         <v>560</v>
       </c>
       <c r="B143" s="8" t="s">
@@ -24775,7 +24772,7 @@
       <c r="F143" s="8"/>
     </row>
     <row r="144" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="71" t="s">
+      <c r="A144" s="70" t="s">
         <v>560</v>
       </c>
       <c r="B144" s="8" t="s">
@@ -24791,10 +24788,10 @@
       <c r="F144" s="8"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="71" t="s">
+      <c r="A145" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B145" s="63" t="s">
+      <c r="B145" s="62" t="s">
         <v>1835</v>
       </c>
       <c r="C145" s="11" t="s">
@@ -24807,10 +24804,10 @@
       <c r="F145" s="8"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="71" t="s">
+      <c r="A146" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B146" s="63" t="s">
+      <c r="B146" s="62" t="s">
         <v>1838</v>
       </c>
       <c r="C146" s="11" t="s">
@@ -24823,10 +24820,10 @@
       <c r="F146" s="8"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="71" t="s">
+      <c r="A147" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B147" s="63" t="s">
+      <c r="B147" s="62" t="s">
         <v>1841</v>
       </c>
       <c r="C147" s="11" t="s">
@@ -24839,10 +24836,10 @@
       <c r="F147" s="8"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="71" t="s">
+      <c r="A148" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B148" s="63" t="s">
+      <c r="B148" s="62" t="s">
         <v>1844</v>
       </c>
       <c r="C148" s="11" t="s">
@@ -24855,10 +24852,10 @@
       <c r="F148" s="8"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="71" t="s">
+      <c r="A149" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B149" s="63" t="s">
+      <c r="B149" s="62" t="s">
         <v>1847</v>
       </c>
       <c r="C149" s="11" t="s">
@@ -24871,10 +24868,10 @@
       <c r="F149" s="8"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="71" t="s">
+      <c r="A150" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B150" s="63" t="s">
+      <c r="B150" s="62" t="s">
         <v>1850</v>
       </c>
       <c r="C150" s="11" t="s">
@@ -24887,10 +24884,10 @@
       <c r="F150" s="8"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="71" t="s">
+      <c r="A151" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B151" s="63" t="s">
+      <c r="B151" s="62" t="s">
         <v>1853</v>
       </c>
       <c r="C151" s="11" t="s">
@@ -24903,10 +24900,10 @@
       <c r="F151" s="8"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="71" t="s">
+      <c r="A152" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B152" s="63" t="s">
+      <c r="B152" s="62" t="s">
         <v>1856</v>
       </c>
       <c r="C152" s="11" t="s">
@@ -24919,10 +24916,10 @@
       <c r="F152" s="8"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="71" t="s">
+      <c r="A153" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B153" s="63" t="s">
+      <c r="B153" s="62" t="s">
         <v>1857</v>
       </c>
       <c r="C153" s="11" t="s">
@@ -24935,10 +24932,10 @@
       <c r="F153" s="8"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="71" t="s">
+      <c r="A154" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B154" s="63" t="s">
+      <c r="B154" s="62" t="s">
         <v>1860</v>
       </c>
       <c r="C154" s="11" t="s">
@@ -24951,10 +24948,10 @@
       <c r="F154" s="8"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="71" t="s">
+      <c r="A155" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B155" s="63" t="s">
+      <c r="B155" s="62" t="s">
         <v>1863</v>
       </c>
       <c r="C155" s="11" t="s">
@@ -24967,10 +24964,10 @@
       <c r="F155" s="8"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="71" t="s">
+      <c r="A156" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B156" s="63" t="s">
+      <c r="B156" s="62" t="s">
         <v>1866</v>
       </c>
       <c r="C156" s="11" t="s">
@@ -24983,10 +24980,10 @@
       <c r="F156" s="8"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="71" t="s">
+      <c r="A157" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B157" s="63" t="s">
+      <c r="B157" s="62" t="s">
         <v>1869</v>
       </c>
       <c r="C157" s="11" t="s">
@@ -24999,10 +24996,10 @@
       <c r="F157" s="8"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="71" t="s">
+      <c r="A158" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B158" s="63" t="s">
+      <c r="B158" s="62" t="s">
         <v>1872</v>
       </c>
       <c r="C158" s="11" t="s">
@@ -25015,10 +25012,10 @@
       <c r="F158" s="8"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="71" t="s">
+      <c r="A159" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B159" s="63" t="s">
+      <c r="B159" s="62" t="s">
         <v>1875</v>
       </c>
       <c r="C159" s="11" t="s">
@@ -25031,10 +25028,10 @@
       <c r="F159" s="8"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="71" t="s">
+      <c r="A160" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B160" s="63" t="s">
+      <c r="B160" s="62" t="s">
         <v>1878</v>
       </c>
       <c r="C160" s="11" t="s">
@@ -25047,10 +25044,10 @@
       <c r="F160" s="8"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="71" t="s">
+      <c r="A161" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B161" s="63" t="s">
+      <c r="B161" s="62" t="s">
         <v>1881</v>
       </c>
       <c r="C161" s="11" t="s">
@@ -25063,10 +25060,10 @@
       <c r="F161" s="8"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="71" t="s">
+      <c r="A162" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B162" s="63" t="s">
+      <c r="B162" s="62" t="s">
         <v>1884</v>
       </c>
       <c r="C162" s="11" t="s">
@@ -25079,10 +25076,10 @@
       <c r="F162" s="8"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="71" t="s">
+      <c r="A163" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B163" s="63" t="s">
+      <c r="B163" s="62" t="s">
         <v>1885</v>
       </c>
       <c r="C163" s="11" t="s">
@@ -25095,10 +25092,10 @@
       <c r="F163" s="8"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="71" t="s">
+      <c r="A164" s="70" t="s">
         <v>560</v>
       </c>
-      <c r="B164" s="63" t="s">
+      <c r="B164" s="62" t="s">
         <v>1888</v>
       </c>
       <c r="C164" s="11" t="s">
@@ -25111,10 +25108,10 @@
       <c r="F164" s="8"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="72" t="s">
+      <c r="A165" s="71" t="s">
         <v>560</v>
       </c>
-      <c r="B165" s="63" t="s">
+      <c r="B165" s="62" t="s">
         <v>1891</v>
       </c>
       <c r="C165" s="11" t="s">
@@ -25127,10 +25124,10 @@
       <c r="F165" s="8"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="72" t="s">
+      <c r="A166" s="71" t="s">
         <v>560</v>
       </c>
-      <c r="B166" s="63" t="s">
+      <c r="B166" s="62" t="s">
         <v>1894</v>
       </c>
       <c r="C166" s="11" t="s">
@@ -25155,10 +25152,10 @@
       <c r="D167" s="11" t="s">
         <v>1899</v>
       </c>
-      <c r="E167" s="46" t="s">
+      <c r="E167" s="45" t="s">
         <v>1900</v>
       </c>
-      <c r="F167" s="46" t="s">
+      <c r="F167" s="45" t="s">
         <v>1901</v>
       </c>
     </row>
@@ -25175,10 +25172,10 @@
       <c r="D168" s="11" t="s">
         <v>1904</v>
       </c>
-      <c r="E168" s="46" t="s">
+      <c r="E168" s="45" t="s">
         <v>1905</v>
       </c>
-      <c r="F168" s="46" t="s">
+      <c r="F168" s="45" t="s">
         <v>1906</v>
       </c>
     </row>
@@ -25186,7 +25183,7 @@
       <c r="A169" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="B169" s="50" t="s">
+      <c r="B169" s="49" t="s">
         <v>1907</v>
       </c>
       <c r="C169" s="11" t="s">
@@ -25195,10 +25192,10 @@
       <c r="D169" s="11" t="s">
         <v>1909</v>
       </c>
-      <c r="E169" s="46" t="s">
+      <c r="E169" s="45" t="s">
         <v>1910</v>
       </c>
-      <c r="F169" s="46" t="s">
+      <c r="F169" s="45" t="s">
         <v>1911</v>
       </c>
     </row>
@@ -25206,7 +25203,7 @@
       <c r="A170" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="B170" s="73" t="s">
+      <c r="B170" s="72" t="s">
         <v>1912</v>
       </c>
       <c r="C170" s="11" t="s">
@@ -25215,10 +25212,10 @@
       <c r="D170" s="11" t="s">
         <v>1914</v>
       </c>
-      <c r="E170" s="46" t="s">
+      <c r="E170" s="45" t="s">
         <v>1915</v>
       </c>
-      <c r="F170" s="46" t="s">
+      <c r="F170" s="45" t="s">
         <v>1916</v>
       </c>
     </row>
@@ -25226,7 +25223,7 @@
       <c r="A171" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="B171" s="73" t="s">
+      <c r="B171" s="72" t="s">
         <v>1917</v>
       </c>
       <c r="C171" s="11" t="s">
@@ -25235,10 +25232,10 @@
       <c r="D171" s="11" t="s">
         <v>1919</v>
       </c>
-      <c r="E171" s="46" t="s">
+      <c r="E171" s="45" t="s">
         <v>1920</v>
       </c>
-      <c r="F171" s="46" t="s">
+      <c r="F171" s="45" t="s">
         <v>1921</v>
       </c>
     </row>
@@ -25246,7 +25243,7 @@
       <c r="A172" s="11" t="s">
         <v>362</v>
       </c>
-      <c r="B172" s="74" t="s">
+      <c r="B172" s="73" t="s">
         <v>1922</v>
       </c>
       <c r="C172" s="11" t="s">
@@ -25912,7 +25909,7 @@
       <c r="A216" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="B216" s="58" t="s">
+      <c r="B216" s="57" t="s">
         <v>2064</v>
       </c>
       <c r="C216" s="11" t="s">
@@ -26010,7 +26007,7 @@
       <c r="A223" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="B223" s="58" t="s">
+      <c r="B223" s="57" t="s">
         <v>2085</v>
       </c>
       <c r="C223" s="11" t="s">
@@ -26024,7 +26021,7 @@
       <c r="A224" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="B224" s="58" t="s">
+      <c r="B224" s="57" t="s">
         <v>2088</v>
       </c>
       <c r="C224" s="11" t="s">
@@ -26038,7 +26035,7 @@
       <c r="A225" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="B225" s="58" t="s">
+      <c r="B225" s="57" t="s">
         <v>2091</v>
       </c>
       <c r="C225" s="11" t="s">
@@ -26052,7 +26049,7 @@
       <c r="A226" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="B226" s="58" t="s">
+      <c r="B226" s="57" t="s">
         <v>2094</v>
       </c>
       <c r="C226" s="11" t="s">
@@ -26066,7 +26063,7 @@
       <c r="A227" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="B227" s="58" t="s">
+      <c r="B227" s="57" t="s">
         <v>2095</v>
       </c>
       <c r="C227" s="11" t="s">
@@ -26080,7 +26077,7 @@
       <c r="A228" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="B228" s="58" t="s">
+      <c r="B228" s="57" t="s">
         <v>2098</v>
       </c>
       <c r="C228" s="11" t="s">
@@ -26094,7 +26091,7 @@
       <c r="A229" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="B229" s="58" t="s">
+      <c r="B229" s="57" t="s">
         <v>2099</v>
       </c>
       <c r="C229" s="11" t="s">
@@ -26108,7 +26105,7 @@
       <c r="A230" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="B230" s="58" t="s">
+      <c r="B230" s="57" t="s">
         <v>2100</v>
       </c>
       <c r="C230" s="11" t="s">
@@ -26122,7 +26119,7 @@
       <c r="A231" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="B231" s="58" t="s">
+      <c r="B231" s="57" t="s">
         <v>2101</v>
       </c>
       <c r="C231" s="11" t="s">
@@ -26136,7 +26133,7 @@
       <c r="A232" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="B232" s="58" t="s">
+      <c r="B232" s="57" t="s">
         <v>2102</v>
       </c>
       <c r="C232" s="11" t="s">
@@ -26150,7 +26147,7 @@
       <c r="A233" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="B233" s="58" t="s">
+      <c r="B233" s="57" t="s">
         <v>2104</v>
       </c>
       <c r="C233" s="11" t="s">
@@ -26623,7 +26620,7 @@
       </c>
     </row>
     <row r="267" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="43" t="s">
+      <c r="A267" s="42" t="s">
         <v>745</v>
       </c>
       <c r="B267" s="31" t="s">
@@ -26668,7 +26665,7 @@
       <c r="A270" s="11" t="s">
         <v>745</v>
       </c>
-      <c r="B270" s="46" t="s">
+      <c r="B270" s="45" t="s">
         <v>2198</v>
       </c>
       <c r="C270" s="8" t="s">
@@ -26677,10 +26674,10 @@
       <c r="D270" s="8" t="s">
         <v>2200</v>
       </c>
-      <c r="E270" s="75" t="s">
+      <c r="E270" s="74" t="s">
         <v>2201</v>
       </c>
-      <c r="F270" s="75" t="s">
+      <c r="F270" s="74" t="s">
         <v>2202</v>
       </c>
     </row>
@@ -26688,7 +26685,7 @@
       <c r="A271" s="11" t="s">
         <v>745</v>
       </c>
-      <c r="B271" s="46" t="s">
+      <c r="B271" s="45" t="s">
         <v>2203</v>
       </c>
       <c r="C271" s="8" t="s">
@@ -26697,10 +26694,10 @@
       <c r="D271" s="8" t="s">
         <v>2205</v>
       </c>
-      <c r="E271" s="75" t="s">
+      <c r="E271" s="74" t="s">
         <v>2206</v>
       </c>
-      <c r="F271" s="75" t="s">
+      <c r="F271" s="74" t="s">
         <v>2207</v>
       </c>
     </row>
@@ -26907,21 +26904,21 @@
   <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="58" width="21.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="58" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="57" width="21.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="57" width="15.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="11" width="78.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="11" width="81.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="11" width="71.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="11" width="72.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="58" width="24.33"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="58" width="9.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="57" width="24.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="57" width="9.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="75" t="s">
         <v>2240</v>
       </c>
-      <c r="B1" s="76" t="s">
+      <c r="B1" s="75" t="s">
         <v>1185</v>
       </c>
       <c r="C1" s="11" t="s">
@@ -26936,21 +26933,21 @@
       <c r="F1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="76" t="s">
+      <c r="G1" s="75" t="s">
         <v>2241</v>
       </c>
-      <c r="H1" s="76" t="s">
+      <c r="H1" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="58" t="s">
+      <c r="I1" s="57" t="s">
         <v>2242</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="45" t="s">
         <v>1215</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="45" t="s">
         <v>1215</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -26959,14 +26956,14 @@
       <c r="D2" s="11" t="s">
         <v>2244</v>
       </c>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="45" t="s">
         <v>1251</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="45" t="s">
         <v>1251</v>
       </c>
       <c r="C3" s="11" t="s">
@@ -26975,14 +26972,14 @@
       <c r="D3" s="11" t="s">
         <v>2246</v>
       </c>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="45" t="s">
         <v>233</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="45" t="s">
         <v>233</v>
       </c>
       <c r="C4" s="11" t="s">
@@ -26991,14 +26988,14 @@
       <c r="D4" s="11" t="s">
         <v>2248</v>
       </c>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="45" t="s">
         <v>2249</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="45" t="s">
         <v>233</v>
       </c>
       <c r="C5" s="11" t="s">
@@ -27007,14 +27004,14 @@
       <c r="D5" s="11" t="s">
         <v>1642</v>
       </c>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="45" t="s">
         <v>2250</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="45" t="s">
         <v>2250</v>
       </c>
       <c r="C6" s="11" t="s">
@@ -27023,14 +27020,14 @@
       <c r="D6" s="11" t="s">
         <v>2252</v>
       </c>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="45" t="s">
         <v>1195</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="45" t="s">
         <v>1195</v>
       </c>
       <c r="C7" s="11" t="s">
@@ -27039,86 +27036,86 @@
       <c r="D7" s="11" t="s">
         <v>2254</v>
       </c>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="46"/>
-      <c r="G8" s="46" t="s">
+      <c r="B8" s="45"/>
+      <c r="G8" s="45" t="s">
         <v>1215</v>
       </c>
-      <c r="H8" s="46"/>
+      <c r="H8" s="45"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="46" t="s">
+      <c r="A9" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="46"/>
-      <c r="G9" s="46" t="s">
+      <c r="B9" s="45"/>
+      <c r="G9" s="45" t="s">
         <v>1251</v>
       </c>
-      <c r="H9" s="46"/>
+      <c r="H9" s="45"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="G10" s="46" t="s">
+      <c r="B10" s="45"/>
+      <c r="G10" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H10" s="46"/>
+      <c r="H10" s="45"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="G11" s="46" t="s">
+      <c r="B11" s="45"/>
+      <c r="G11" s="45" t="s">
         <v>2250</v>
       </c>
-      <c r="H11" s="46"/>
+      <c r="H11" s="45"/>
     </row>
     <row r="12" s="11" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="46" t="s">
+      <c r="A12" s="45" t="s">
         <v>163</v>
       </c>
-      <c r="B12" s="46"/>
-      <c r="G12" s="46" t="s">
+      <c r="B12" s="45"/>
+      <c r="G12" s="45" t="s">
         <v>1215</v>
       </c>
-      <c r="H12" s="46"/>
-      <c r="I12" s="58"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="57"/>
     </row>
     <row r="13" s="11" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="45" t="s">
         <v>163</v>
       </c>
-      <c r="B13" s="46"/>
-      <c r="G13" s="46" t="s">
+      <c r="B13" s="45"/>
+      <c r="G13" s="45" t="s">
         <v>1251</v>
       </c>
-      <c r="H13" s="46"/>
-      <c r="I13" s="58"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="57"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="45" t="s">
         <v>163</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="G14" s="46" t="s">
+      <c r="B14" s="45"/>
+      <c r="G14" s="45" t="s">
         <v>1195</v>
       </c>
-      <c r="H14" s="46"/>
+      <c r="H14" s="45"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="45" t="s">
         <v>1215</v>
       </c>
       <c r="C15" s="11" t="s">
@@ -27127,15 +27124,15 @@
       <c r="D15" s="11" t="s">
         <v>2256</v>
       </c>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="46" t="s">
+      <c r="A16" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="45" t="s">
         <v>1251</v>
       </c>
       <c r="C16" s="11" t="s">
@@ -27144,15 +27141,15 @@
       <c r="D16" s="11" t="s">
         <v>2258</v>
       </c>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="77" t="s">
+      <c r="A17" s="76" t="s">
         <v>2259</v>
       </c>
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="45" t="s">
         <v>2260</v>
       </c>
       <c r="C17" s="11" t="s">
@@ -27161,14 +27158,14 @@
       <c r="D17" s="11" t="s">
         <v>2262</v>
       </c>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="77" t="s">
+      <c r="A18" s="76" t="s">
         <v>2259</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="45" t="s">
         <v>2263</v>
       </c>
       <c r="C18" s="11" t="s">
@@ -27177,24 +27174,24 @@
       <c r="D18" s="11" t="s">
         <v>2265</v>
       </c>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="77" t="s">
+      <c r="A19" s="76" t="s">
         <v>2259</v>
       </c>
-      <c r="B19" s="46"/>
-      <c r="G19" s="46" t="s">
+      <c r="B19" s="45"/>
+      <c r="G19" s="45" t="s">
         <v>1195</v>
       </c>
-      <c r="H19" s="46"/>
+      <c r="H19" s="45"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="77" t="s">
+      <c r="A20" s="76" t="s">
         <v>190</v>
       </c>
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="45" t="s">
         <v>2260</v>
       </c>
       <c r="C20" s="11" t="s">
@@ -27203,14 +27200,14 @@
       <c r="D20" s="11" t="s">
         <v>2262</v>
       </c>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="77" t="s">
+      <c r="A21" s="76" t="s">
         <v>190</v>
       </c>
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="45" t="s">
         <v>2263</v>
       </c>
       <c r="C21" s="11" t="s">
@@ -27219,14 +27216,14 @@
       <c r="D21" s="11" t="s">
         <v>2265</v>
       </c>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="77" t="s">
+      <c r="A22" s="76" t="s">
         <v>190</v>
       </c>
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="45" t="s">
         <v>192</v>
       </c>
       <c r="C22" s="11" t="s">
@@ -27235,24 +27232,24 @@
       <c r="D22" s="11" t="s">
         <v>2267</v>
       </c>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="77" t="s">
+      <c r="A23" s="76" t="s">
         <v>190</v>
       </c>
-      <c r="B23" s="46"/>
-      <c r="G23" s="46" t="s">
+      <c r="B23" s="45"/>
+      <c r="G23" s="45" t="s">
         <v>1195</v>
       </c>
-      <c r="H23" s="46"/>
+      <c r="H23" s="45"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="45" t="s">
         <v>308</v>
       </c>
-      <c r="B24" s="46" t="s">
+      <c r="B24" s="45" t="s">
         <v>2268</v>
       </c>
       <c r="C24" s="11" t="s">
@@ -27261,14 +27258,14 @@
       <c r="D24" s="11" t="s">
         <v>2270</v>
       </c>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="46" t="s">
+      <c r="A25" s="45" t="s">
         <v>308</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="45" t="s">
         <v>2271</v>
       </c>
       <c r="C25" s="11" t="s">
@@ -27277,24 +27274,24 @@
       <c r="D25" s="11" t="s">
         <v>2273</v>
       </c>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="46" t="s">
+      <c r="A26" s="45" t="s">
         <v>308</v>
       </c>
-      <c r="B26" s="46"/>
-      <c r="G26" s="46" t="s">
+      <c r="B26" s="45"/>
+      <c r="G26" s="45" t="s">
         <v>1251</v>
       </c>
-      <c r="H26" s="46"/>
+      <c r="H26" s="45"/>
     </row>
     <row r="27" s="11" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" colla